--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62512D36-052B-42F4-BEC0-D335AD8826F4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'13.5'!$A$2:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'15.5'!$A$2:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'18.5'!$A$2:$N$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'18.5'!$A$2:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'20.5'!$A$2:$N$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'21.5'!$A$2:$N$19</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -33215,7 +33215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB7AE26-D39B-4A79-A937-205FFF1964B5}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:N664"/>
@@ -33580,7 +33580,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="e">
         <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
@@ -33629,7 +33629,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="e">
         <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
@@ -33678,7 +33678,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="e">
         <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
@@ -33727,7 +33727,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="e">
         <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
@@ -33776,7 +33776,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="e">
         <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
@@ -33825,7 +33825,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17"/>
       <c r="B17" s="18" t="e">
         <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
@@ -33874,7 +33874,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17"/>
       <c r="B18" s="18" t="e">
         <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
@@ -33923,7 +33923,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="17"/>
       <c r="B19" s="18" t="e">
         <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
@@ -33972,7 +33972,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17"/>
       <c r="B20" s="18" t="e">
         <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
@@ -34534,17 +34534,7 @@
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E12:E20 E3:E11" name="Range1_1"/>
   </protectedRanges>
-  <autoFilter ref="A2:N21" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
-    <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="RPRO-260513-0945"/>
-        <filter val="RPRO-260513-0946"/>
-        <filter val="RPRO-260513-0947"/>
-        <filter val="RPRO-260513-0949"/>
-        <filter val="RPRO-260513-0950"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:N21" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}"/>
   <mergeCells count="1">
     <mergeCell ref="D1:F1"/>
   </mergeCells>
@@ -34581,7 +34571,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F5428D-F8E8-4268-960E-0C7709324729}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:N667"/>
@@ -34610,7 +34600,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.878920370371</v>
+        <v>46163.886088888888</v>
       </c>
       <c r="D1" s="62" t="s">
         <v>1</v>
@@ -35147,7 +35137,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17"/>
       <c r="B18" s="18" t="e">
         <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
@@ -35196,7 +35186,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="17"/>
       <c r="B19" s="18" t="e">
         <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
@@ -35245,7 +35235,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17"/>
       <c r="B20" s="18" t="e">
         <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
@@ -35294,7 +35284,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="e">
         <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
@@ -35343,7 +35333,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17"/>
       <c r="B22" s="18" t="e">
         <f>VLOOKUP(A22,'[2]master plan'!A:C,3,0)</f>
@@ -35392,7 +35382,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17"/>
       <c r="B23" s="18" t="e">
         <f>VLOOKUP(A23,'[2]master plan'!A:C,3,0)</f>
@@ -35954,21 +35944,7 @@
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E23" name="Range1_1"/>
   </protectedRanges>
-  <autoFilter ref="A2:N24" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
-    <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="RPRO-260515-0272"/>
-        <filter val="RPRO-260515-0273"/>
-        <filter val="RPRO-260515-0274"/>
-        <filter val="RPRO-260515-0275"/>
-        <filter val="RPRO-260515-0276"/>
-        <filter val="RPRO-260515-0277"/>
-        <filter val="RPRO-260515-0278"/>
-        <filter val="RPRO-260515-0279"/>
-        <filter val="RPRO-260515-0280"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:N24" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}"/>
   <mergeCells count="1">
     <mergeCell ref="D1:F1"/>
   </mergeCells>
@@ -36034,7 +36010,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.878920370371</v>
+        <v>46163.886088888888</v>
       </c>
       <c r="D1" s="62" t="s">
         <v>1</v>
@@ -37414,7 +37390,7 @@
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E28" name="Range1_1"/>
   </protectedRanges>
-  <autoFilter ref="A2:N29" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}"/>
+  <autoFilter ref="A2:N3" xr:uid="{C37AD070-2916-43CC-A604-A8704404E33C}"/>
   <mergeCells count="1">
     <mergeCell ref="D1:F1"/>
   </mergeCells>
@@ -37480,7 +37456,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.878920370371</v>
+        <v>46163.886088888888</v>
       </c>
       <c r="D1" s="62" t="s">
         <v>1</v>
@@ -38869,7 +38845,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7B6BC1-AB47-4E1B-BA30-0BF2D008E387}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:N662"/>
@@ -38883,8 +38859,7 @@
     <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
     <col min="7" max="7" width="19" style="54" customWidth="1"/>
     <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
-    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="20.1796875" style="53" customWidth="1"/>
     <col min="11" max="11" width="25.7265625" style="53" customWidth="1"/>
     <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
     <col min="13" max="13" width="22" style="57" customWidth="1"/>
@@ -38898,7 +38873,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.878920370371</v>
+        <v>46163.886088888888</v>
       </c>
       <c r="D1" s="62" t="s">
         <v>1</v>
@@ -39061,7 +39036,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="e">
         <f>VLOOKUP(A6,'[2]master plan'!A:C,3,0)</f>
@@ -39110,7 +39085,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="e">
         <f>VLOOKUP(A7,'[2]master plan'!A:C,3,0)</f>
@@ -39159,7 +39134,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="e">
         <f>VLOOKUP(A8,'[2]master plan'!A:C,3,0)</f>
@@ -39208,7 +39183,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="e">
         <f>VLOOKUP(A9,'[2]master plan'!A:C,3,0)</f>
@@ -39257,7 +39232,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17"/>
       <c r="B10" s="18" t="e">
         <f>VLOOKUP(A10,'[2]master plan'!A:C,3,0)</f>
@@ -39306,7 +39281,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="e">
         <f>VLOOKUP(A11,'[2]master plan'!A:C,3,0)</f>
@@ -39355,7 +39330,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="e">
         <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
@@ -39404,7 +39379,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="e">
         <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
@@ -39453,7 +39428,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="e">
         <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
@@ -39502,7 +39477,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="e">
         <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
@@ -39551,7 +39526,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="e">
         <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
@@ -39600,7 +39575,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17"/>
       <c r="B17" s="18" t="e">
         <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
@@ -39649,7 +39624,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17"/>
       <c r="B18" s="18" t="e">
         <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
@@ -40211,14 +40186,7 @@
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E18" name="Range1_1"/>
   </protectedRanges>
-  <autoFilter ref="A2:N19" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
-    <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="RPRO-260521-0669"/>
-        <filter val="RPRO-260521-0670"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:N19" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}"/>
   <mergeCells count="1">
     <mergeCell ref="D1:F1"/>
   </mergeCells>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62512D36-052B-42F4-BEC0-D335AD8826F4}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D762CD4A-EFE7-44D7-9ED4-B9E5074D5C65}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -171,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="247">
   <si>
     <t>Release Date</t>
   </si>
@@ -641,9 +641,6 @@
     <t>SSO-2605-00716</t>
   </si>
   <si>
-    <t>OV-0435</t>
-  </si>
-  <si>
     <t>S-2026-05-47</t>
   </si>
   <si>
@@ -677,9 +674,6 @@
     <t>SSO-2605-00651</t>
   </si>
   <si>
-    <t>OE-0111A</t>
-  </si>
-  <si>
     <t>S-2026-05-49</t>
   </si>
   <si>
@@ -693,9 +687,6 @@
   </si>
   <si>
     <t>OrthoLite Regular GREY/17-1501TPX Flat Sheet 0.11D 5-10 Asker C 1.1M 2M 3.5mm</t>
-  </si>
-  <si>
-    <t>OV-0272</t>
   </si>
   <si>
     <t>S-2026-05-50</t>
@@ -719,9 +710,6 @@
     <t>SSO-2605-00721</t>
   </si>
   <si>
-    <t>OV-0112</t>
-  </si>
-  <si>
     <t>S-2026-05-51</t>
   </si>
   <si>
@@ -735,9 +723,6 @@
   </si>
   <si>
     <t>SSO-2605-00722</t>
-  </si>
-  <si>
-    <t>OV-0085</t>
   </si>
   <si>
     <t>S-2026-05-53</t>
@@ -864,9 +849,6 @@
   </si>
   <si>
     <t>OrthoLite Regular-Nike SEEDPEARL/12-0703TPX Flat Sheet 0.11D 25+/-4 Asker C 1.1M 1.7M 2mm</t>
-  </si>
-  <si>
-    <t>DIE CUT</t>
   </si>
   <si>
     <t>S-2026-05-63</t>
@@ -1005,6 +987,9 @@
   </si>
   <si>
     <t>SSO-2605-01133   - URGENT (5-28)</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -1539,9 +1524,6 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1586,6 +1568,9 @@
     </xf>
     <xf numFmtId="14" fontId="25" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2117,8 +2102,8 @@
       <sheetName val="form 2 (11)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="1">
           <cell r="C1" t="str">
@@ -32488,7 +32473,7 @@
             <v xml:space="preserve">PUR2605210001S  </v>
           </cell>
           <cell r="E447" t="str">
-            <v/>
+            <v>BDB-000058</v>
           </cell>
           <cell r="F447" t="str">
             <v>PVN-001319</v>
@@ -32506,7 +32491,7 @@
             <v>0</v>
           </cell>
           <cell r="K447">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="L447" t="str">
             <v>ADIDAS</v>
@@ -32535,14 +32520,14 @@
           <cell r="T447">
             <v>7</v>
           </cell>
-          <cell r="U447" t="str">
-            <v/>
+          <cell r="U447">
+            <v>5</v>
           </cell>
           <cell r="V447">
-            <v>0</v>
+            <v>3.5709999999999999E-2</v>
           </cell>
           <cell r="W447">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="448">
@@ -32556,7 +32541,7 @@
             <v xml:space="preserve">PUR2605210002S   </v>
           </cell>
           <cell r="E448" t="str">
-            <v/>
+            <v>BDB-000076</v>
           </cell>
           <cell r="F448" t="str">
             <v>PVN-003742</v>
@@ -32574,7 +32559,7 @@
             <v>0</v>
           </cell>
           <cell r="K448">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="L448" t="str">
             <v>ADIDAS</v>
@@ -32603,14 +32588,14 @@
           <cell r="T448">
             <v>7</v>
           </cell>
-          <cell r="U448" t="str">
-            <v/>
+          <cell r="U448">
+            <v>5</v>
           </cell>
           <cell r="V448">
-            <v>0</v>
+            <v>3.5709999999999999E-2</v>
           </cell>
           <cell r="W448">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="449">
@@ -32814,105 +32799,111 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70"/>
-      <sheetData sheetId="71"/>
-      <sheetData sheetId="72"/>
-      <sheetData sheetId="73"/>
-      <sheetData sheetId="74"/>
-      <sheetData sheetId="75"/>
-      <sheetData sheetId="76"/>
-      <sheetData sheetId="77"/>
-      <sheetData sheetId="78"/>
-      <sheetData sheetId="79"/>
-      <sheetData sheetId="80"/>
-      <sheetData sheetId="81"/>
-      <sheetData sheetId="82"/>
-      <sheetData sheetId="83"/>
-      <sheetData sheetId="84"/>
-      <sheetData sheetId="85"/>
-      <sheetData sheetId="86"/>
-      <sheetData sheetId="87"/>
-      <sheetData sheetId="88"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
+      <sheetData sheetId="41" refreshError="1"/>
+      <sheetData sheetId="42" refreshError="1"/>
+      <sheetData sheetId="43" refreshError="1"/>
+      <sheetData sheetId="44" refreshError="1"/>
+      <sheetData sheetId="45" refreshError="1"/>
+      <sheetData sheetId="46" refreshError="1"/>
+      <sheetData sheetId="47" refreshError="1"/>
+      <sheetData sheetId="48" refreshError="1"/>
+      <sheetData sheetId="49" refreshError="1"/>
+      <sheetData sheetId="50" refreshError="1"/>
+      <sheetData sheetId="51" refreshError="1"/>
+      <sheetData sheetId="52" refreshError="1"/>
+      <sheetData sheetId="53" refreshError="1"/>
+      <sheetData sheetId="54" refreshError="1"/>
+      <sheetData sheetId="55" refreshError="1"/>
+      <sheetData sheetId="56" refreshError="1"/>
+      <sheetData sheetId="57" refreshError="1"/>
+      <sheetData sheetId="58" refreshError="1"/>
+      <sheetData sheetId="59" refreshError="1"/>
+      <sheetData sheetId="60" refreshError="1"/>
+      <sheetData sheetId="61" refreshError="1"/>
+      <sheetData sheetId="62" refreshError="1"/>
+      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="64" refreshError="1"/>
+      <sheetData sheetId="65" refreshError="1"/>
+      <sheetData sheetId="66" refreshError="1"/>
+      <sheetData sheetId="67" refreshError="1"/>
+      <sheetData sheetId="68" refreshError="1"/>
+      <sheetData sheetId="69" refreshError="1"/>
+      <sheetData sheetId="70" refreshError="1"/>
+      <sheetData sheetId="71" refreshError="1"/>
+      <sheetData sheetId="72" refreshError="1"/>
+      <sheetData sheetId="73" refreshError="1"/>
+      <sheetData sheetId="74" refreshError="1"/>
+      <sheetData sheetId="75" refreshError="1"/>
+      <sheetData sheetId="76" refreshError="1"/>
+      <sheetData sheetId="77" refreshError="1"/>
+      <sheetData sheetId="78" refreshError="1"/>
+      <sheetData sheetId="79" refreshError="1"/>
+      <sheetData sheetId="80" refreshError="1"/>
+      <sheetData sheetId="81" refreshError="1"/>
+      <sheetData sheetId="82" refreshError="1"/>
+      <sheetData sheetId="83" refreshError="1"/>
+      <sheetData sheetId="84" refreshError="1"/>
+      <sheetData sheetId="85" refreshError="1"/>
+      <sheetData sheetId="86" refreshError="1"/>
+      <sheetData sheetId="87" refreshError="1"/>
+      <sheetData sheetId="88" refreshError="1"/>
       <sheetData sheetId="89"/>
-      <sheetData sheetId="90"/>
-      <sheetData sheetId="91"/>
-      <sheetData sheetId="92"/>
-      <sheetData sheetId="93"/>
-      <sheetData sheetId="94"/>
-      <sheetData sheetId="95"/>
+      <sheetData sheetId="90" refreshError="1"/>
+      <sheetData sheetId="91">
+        <row r="1">
+          <cell r="F1" t="str">
+            <v>No_Item</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="92" refreshError="1"/>
+      <sheetData sheetId="93" refreshError="1"/>
+      <sheetData sheetId="94" refreshError="1"/>
+      <sheetData sheetId="95" refreshError="1"/>
       <sheetData sheetId="96"/>
-      <sheetData sheetId="97"/>
-      <sheetData sheetId="98"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
       <sheetData sheetId="99"/>
-      <sheetData sheetId="100"/>
-      <sheetData sheetId="101"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -33245,11 +33236,11 @@
       <c r="B1" s="1">
         <v>46155.681657291665</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -34600,13 +34591,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.886088888888</v>
-      </c>
-      <c r="D1" s="62" t="s">
+        <v>46164.418156597225</v>
+      </c>
+      <c r="D1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -34708,19 +34699,19 @@
       </c>
     </row>
     <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="71"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
       <c r="J4" s="25"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="73"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
       <c r="N4" s="28"/>
     </row>
     <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -34848,19 +34839,19 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="70"/>
       <c r="J8" s="25"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="73"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="72"/>
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -34906,19 +34897,19 @@
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="71"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
       <c r="J10" s="25"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="73"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="72"/>
       <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -34964,19 +34955,19 @@
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="71"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
       <c r="J12" s="25"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
       <c r="N12" s="28"/>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -35022,19 +35013,19 @@
       </c>
     </row>
     <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="63"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
+      <c r="A14" s="62"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
       <c r="J14" s="25"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="73"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="72"/>
       <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -35080,19 +35071,19 @@
       </c>
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="63"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="71"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
       <c r="J16" s="25"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="74"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="73"/>
       <c r="N16" s="28"/>
     </row>
     <row r="17" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -36010,13 +36001,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.886088888888</v>
-      </c>
-      <c r="D1" s="62" t="s">
+        <v>46164.418156597225</v>
+      </c>
+      <c r="D1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -36105,12 +36096,12 @@
         <v>114</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" s="75">
+        <v>246</v>
+      </c>
+      <c r="L3" s="74">
         <v>0</v>
       </c>
-      <c r="M3" s="76" t="s">
+      <c r="M3" s="75" t="s">
         <v>115</v>
       </c>
       <c r="N3" s="28">
@@ -36118,20 +36109,22 @@
       </c>
     </row>
     <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="71"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
       <c r="J4" s="25"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="77"/>
+      <c r="K4" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="76"/>
     </row>
     <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
@@ -36165,7 +36158,7 @@
         <v>121</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>59</v>
+        <v>246</v>
       </c>
       <c r="L5" s="26">
         <v>1</v>
@@ -36178,20 +36171,22 @@
       </c>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="63"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="71"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
       <c r="J6" s="25"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="73"/>
-      <c r="N6" s="77"/>
+      <c r="K6" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L6" s="71"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="76"/>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
@@ -36225,7 +36220,7 @@
         <v>129</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>130</v>
+        <v>246</v>
       </c>
       <c r="L7" s="26">
         <v>2</v>
@@ -36236,36 +36231,38 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="70"/>
       <c r="J8" s="25"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="73"/>
-      <c r="N8" s="77"/>
+      <c r="K8" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L8" s="71"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="76"/>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>134</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>135</v>
       </c>
       <c r="F9" s="22">
         <v>30</v>
@@ -36283,7 +36280,7 @@
         <v>129</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>130</v>
+        <v>246</v>
       </c>
       <c r="L9" s="26">
         <v>3</v>
@@ -36295,19 +36292,19 @@
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="C10" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>138</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>139</v>
       </c>
       <c r="F10" s="22">
         <v>30</v>
@@ -36319,13 +36316,13 @@
         <v>1</v>
       </c>
       <c r="I10" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="J10" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="J10" s="25" t="s">
-        <v>141</v>
-      </c>
       <c r="K10" s="25" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="L10" s="26"/>
       <c r="M10" s="27"/>
@@ -36334,36 +36331,38 @@
       </c>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="71"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="70"/>
       <c r="J11" s="25"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="73"/>
-      <c r="N11" s="77"/>
+      <c r="K11" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L11" s="71"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="76"/>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="D12" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="E12" s="21" t="s">
         <v>145</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>147</v>
       </c>
       <c r="F12" s="22">
         <v>30</v>
@@ -36381,7 +36380,7 @@
         <v>43</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>148</v>
+        <v>246</v>
       </c>
       <c r="L12" s="26">
         <v>1</v>
@@ -36392,36 +36391,38 @@
       </c>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="71"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="70"/>
       <c r="J13" s="25"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="73"/>
-      <c r="N13" s="77"/>
+      <c r="K13" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L13" s="71"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="76"/>
     </row>
     <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="E14" s="21" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="F14" s="22">
         <v>40</v>
@@ -36433,13 +36434,13 @@
         <v>2</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="L14" s="26">
         <v>3</v>
@@ -36451,19 +36452,19 @@
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F15" s="22">
         <v>20</v>
@@ -36475,13 +36476,13 @@
         <v>1</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="L15" s="26"/>
       <c r="M15" s="40"/>
@@ -36490,27 +36491,29 @@
       </c>
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="63"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="71"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
       <c r="J16" s="25"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="77"/>
+      <c r="K16" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L16" s="71"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>63</v>
@@ -36519,7 +36522,7 @@
         <v>71</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F17" s="22">
         <v>150</v>
@@ -36534,10 +36537,10 @@
         <v>57</v>
       </c>
       <c r="J17" s="25" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="L17" s="26">
         <v>9</v>
@@ -36549,10 +36552,10 @@
     </row>
     <row r="18" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>63</v>
@@ -36576,10 +36579,10 @@
         <v>57</v>
       </c>
       <c r="J18" s="25" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>67</v>
+        <v>246</v>
       </c>
       <c r="L18" s="26"/>
       <c r="M18" s="40"/>
@@ -36588,36 +36591,38 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="63"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
+      <c r="A19" s="62"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="70"/>
       <c r="J19" s="25"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="74"/>
-      <c r="N19" s="77"/>
+      <c r="K19" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L19" s="71"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="76"/>
     </row>
     <row r="20" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F20" s="22">
         <v>50</v>
@@ -36635,7 +36640,7 @@
         <v>27</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L20" s="26">
         <v>5</v>
@@ -36646,36 +36651,38 @@
       </c>
     </row>
     <row r="21" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="63"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="71"/>
+      <c r="A21" s="62"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="70"/>
       <c r="J21" s="25"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="74"/>
-      <c r="N21" s="77"/>
+      <c r="K21" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L21" s="71"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F22" s="22">
         <v>50</v>
@@ -36693,7 +36700,7 @@
         <v>27</v>
       </c>
       <c r="K22" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L22" s="26">
         <v>5</v>
@@ -36704,27 +36711,29 @@
       </c>
     </row>
     <row r="23" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="63"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="71"/>
+      <c r="A23" s="62"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="70"/>
       <c r="J23" s="25"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="77"/>
+      <c r="K23" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L23" s="71"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="76"/>
     </row>
     <row r="24" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>30</v>
@@ -36751,7 +36760,7 @@
         <v>27</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L24" s="26">
         <v>2</v>
@@ -36762,27 +36771,29 @@
       </c>
     </row>
     <row r="25" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="63"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
+      <c r="A25" s="62"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="70"/>
       <c r="J25" s="25"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="77"/>
+      <c r="K25" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L25" s="71"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="76"/>
     </row>
     <row r="26" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>35</v>
@@ -36809,7 +36820,7 @@
         <v>27</v>
       </c>
       <c r="K26" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L26" s="26">
         <v>2</v>
@@ -36820,36 +36831,38 @@
       </c>
     </row>
     <row r="27" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="63"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="71"/>
+      <c r="A27" s="62"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="70"/>
       <c r="J27" s="25"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="74"/>
-      <c r="N27" s="77"/>
+      <c r="K27" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L27" s="71"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F28" s="22">
         <v>40</v>
@@ -36867,7 +36880,7 @@
         <v>27</v>
       </c>
       <c r="K28" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L28" s="26">
         <v>2</v>
@@ -37456,13 +37469,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.886088888888</v>
-      </c>
-      <c r="D1" s="62" t="s">
+        <v>46164.418156481479</v>
+      </c>
+      <c r="D1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -37521,19 +37534,19 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F3" s="22">
         <v>70</v>
@@ -37548,10 +37561,10 @@
         <v>57</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="L3" s="26">
         <v>2</v>
@@ -37562,36 +37575,38 @@
       </c>
     </row>
     <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="73"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
       <c r="N4" s="28"/>
     </row>
     <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F5" s="22">
         <v>40</v>
@@ -37603,13 +37618,13 @@
         <v>2</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J5" s="25" t="s">
         <v>27</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L5" s="26">
         <v>2</v>
@@ -37620,36 +37635,38 @@
       </c>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="63"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="73"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L6" s="71"/>
+      <c r="M6" s="72"/>
       <c r="N6" s="28"/>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F7" s="22">
         <v>40</v>
@@ -37661,13 +37678,13 @@
         <v>1</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J7" s="25" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="L7" s="26">
         <v>1</v>
@@ -37678,36 +37695,38 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="73"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L8" s="71"/>
+      <c r="M8" s="72"/>
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F9" s="22">
         <v>40</v>
@@ -37719,13 +37738,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J9" s="25" t="s">
         <v>27</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="L9" s="26">
         <v>2</v>
@@ -37736,36 +37755,38 @@
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="73"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L10" s="71"/>
+      <c r="M10" s="72"/>
       <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F11" s="22">
         <v>30</v>
@@ -37777,13 +37798,13 @@
         <v>2</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>27</v>
       </c>
       <c r="K11" s="25" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="L11" s="26">
         <v>2</v>
@@ -37794,36 +37815,38 @@
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
       <c r="N12" s="28"/>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F13" s="22">
         <v>50</v>
@@ -37835,13 +37858,13 @@
         <v>2</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>27</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L13" s="26">
         <v>2</v>
@@ -37852,36 +37875,38 @@
       </c>
     </row>
     <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="63"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="73"/>
+      <c r="A14" s="62"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L14" s="71"/>
+      <c r="M14" s="72"/>
       <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F15" s="22">
         <v>30</v>
@@ -37899,7 +37924,7 @@
         <v>27</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="L15" s="26">
         <v>6</v>
@@ -37911,19 +37936,19 @@
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F16" s="22">
         <v>80</v>
@@ -37941,7 +37966,7 @@
         <v>27</v>
       </c>
       <c r="K16" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L16" s="26"/>
       <c r="M16" s="27"/>
@@ -37951,19 +37976,19 @@
     </row>
     <row r="17" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F17" s="22">
         <v>20</v>
@@ -37981,7 +38006,7 @@
         <v>27</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="L17" s="26"/>
       <c r="M17" s="27"/>
@@ -37990,36 +38015,38 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="63"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="73"/>
+      <c r="A18" s="62"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L18" s="71"/>
+      <c r="M18" s="72"/>
       <c r="N18" s="28"/>
     </row>
     <row r="19" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="17" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F19" s="22">
         <v>30</v>
@@ -38037,7 +38064,7 @@
         <v>27</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L19" s="26">
         <v>2</v>
@@ -38048,36 +38075,38 @@
       </c>
     </row>
     <row r="20" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="63"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="73"/>
+      <c r="A20" s="62"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L20" s="71"/>
+      <c r="M20" s="72"/>
       <c r="N20" s="28"/>
     </row>
     <row r="21" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F21" s="22">
         <v>20</v>
@@ -38095,7 +38124,7 @@
         <v>27</v>
       </c>
       <c r="K21" s="25" t="s">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="L21" s="26">
         <v>1</v>
@@ -38140,7 +38169,7 @@
       <c r="L22" s="26"/>
       <c r="M22" s="27"/>
       <c r="N22" s="28" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -38178,7 +38207,7 @@
       <c r="L23" s="26"/>
       <c r="M23" s="40"/>
       <c r="N23" s="28" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -38863,7 +38892,7 @@
     <col min="11" max="11" width="25.7265625" style="53" customWidth="1"/>
     <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
     <col min="13" max="13" width="22" style="57" customWidth="1"/>
-    <col min="14" max="14" width="21.7265625" style="58" customWidth="1"/>
+    <col min="14" max="14" width="39.36328125" style="58" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
@@ -38873,13 +38902,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46163.886088888888</v>
-      </c>
-      <c r="D1" s="62" t="s">
+        <v>46164.418156250002</v>
+      </c>
+      <c r="D1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -38938,19 +38967,19 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>105</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F3" s="22">
         <v>50</v>
@@ -38965,10 +38994,10 @@
         <v>57</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L3" s="26">
         <v>2</v>
@@ -38979,36 +39008,36 @@
       </c>
     </row>
     <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="71"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
       <c r="J4" s="25"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="73"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
       <c r="N4" s="28"/>
     </row>
     <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F5" s="22">
         <v>30</v>
@@ -39023,10 +39052,10 @@
         <v>57</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="L5" s="26">
         <v>2</v>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D762CD4A-EFE7-44D7-9ED4-B9E5074D5C65}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E15A7E6-94FB-44D2-9314-946FB6F15E4A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,11 @@
     <sheet name="18.5" sheetId="3" r:id="rId3"/>
     <sheet name="20.5" sheetId="4" r:id="rId4"/>
     <sheet name="21.5" sheetId="5" r:id="rId5"/>
+    <sheet name="25.5" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'13.5'!$A$2:$N$21</definedName>
@@ -29,126 +30,151 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'18.5'!$A$2:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'20.5'!$A$2:$N$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'21.5'!$A$2:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'25.5'!$A$2:$N$22</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="2">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="3">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="4">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="5">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'18.5'!$A$1:$N$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'20.5'!$A$1:$N$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'21.5'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'25.5'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'18.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'20.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'21.5'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'25.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="2" hidden="1">'18.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="3" hidden="1">'20.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="4" hidden="1">'21.5'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="5" hidden="1">'25.5'!#REF!</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -171,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="285">
   <si>
     <t>Release Date</t>
   </si>
@@ -991,6 +1017,120 @@
   <si>
     <t>OK</t>
   </si>
+  <si>
+    <t>S-2026-05-73</t>
+  </si>
+  <si>
+    <t>RPRO-260523-0221</t>
+  </si>
+  <si>
+    <t>BDB-000376</t>
+  </si>
+  <si>
+    <t>PVN-004323</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular BLACK/19-4007TPX Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 13mm</t>
+  </si>
+  <si>
+    <t>S-2026-05-74</t>
+  </si>
+  <si>
+    <t>RPRO-260523-0222</t>
+  </si>
+  <si>
+    <t>S-2026-05-75</t>
+  </si>
+  <si>
+    <t>RPRO-260523-0223</t>
+  </si>
+  <si>
+    <t>PVN-004056</t>
+  </si>
+  <si>
+    <t>OrthoLite X-25 BILLIARD/16-5427TPX Flat Sheet 0.12D 20+/-4 Asker C 1.1M 2M 12mm</t>
+  </si>
+  <si>
+    <t>FOOTJOY</t>
+  </si>
+  <si>
+    <t>S-2026-05-76</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0001</t>
+  </si>
+  <si>
+    <t>S-2026-05-77</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0002</t>
+  </si>
+  <si>
+    <t>S-2026-05-78</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0003</t>
+  </si>
+  <si>
+    <t>S-2026-05-79</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0004</t>
+  </si>
+  <si>
+    <t>PVN-003601</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 20mm</t>
+  </si>
+  <si>
+    <t>S-2026-05-81</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0006</t>
+  </si>
+  <si>
+    <t>PVN-003414</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.11D 25+/-4 Asker C 1.1M 2M 12mm</t>
+  </si>
+  <si>
+    <t>S-2026-05-80</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0005</t>
+  </si>
+  <si>
+    <t>PVN-002478</t>
+  </si>
+  <si>
+    <t>OrthoLite Eco LT-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.11D 25+/-4 Asker C 1.1M 2M 4mm</t>
+  </si>
+  <si>
+    <t>S-2026-05-85</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0009</t>
+  </si>
+  <si>
+    <t>OrthoLite Eco LT-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</t>
+  </si>
+  <si>
+    <t>SSO-2605-01304   - URGENT (6-2)</t>
+  </si>
+  <si>
+    <t>S-2026-05-82</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0007</t>
+  </si>
+  <si>
+    <t>S-2026-05-83</t>
+  </si>
+  <si>
+    <t>RPRO-260525-0008</t>
+  </si>
 </sst>
 </file>
 
@@ -1000,7 +1140,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1209,6 +1349,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1339,7 +1484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1572,12 +1717,158 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="49">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1999,13 +2290,13 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1 (2)"/>
+      <sheetName val="MỚI (2)"/>
       <sheetName val="Sheet1"/>
       <sheetName val="master plan"/>
       <sheetName val="Sheet5"/>
       <sheetName val="Sheet4"/>
       <sheetName val="Sheet3"/>
       <sheetName val="Sheet2"/>
-      <sheetName val="MỚI (2)"/>
       <sheetName val="MỚI"/>
       <sheetName val="master plan BCN"/>
       <sheetName val="Delivery"/>
@@ -2087,68 +2378,274 @@
       <sheetName val="8.5"/>
       <sheetName val="12.5"/>
       <sheetName val="13.5"/>
-      <sheetName val="form 2 (7)"/>
+      <sheetName val="15.5"/>
+      <sheetName val="18.5"/>
+      <sheetName val="20.5"/>
+      <sheetName val="21.5"/>
+      <sheetName val="23.5"/>
+      <sheetName val="25.5"/>
+      <sheetName val="form 2 (13)"/>
+      <sheetName val="Sheet6"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
-      <sheetName val="15.5"/>
+      <sheetName val="form 2 (12)"/>
+      <sheetName val="form 2 (7)"/>
       <sheetName val="form 2 (8)"/>
-      <sheetName val="18.5"/>
-      <sheetName val="20.5"/>
       <sheetName val="form 2 (10)"/>
-      <sheetName val="21.5"/>
       <sheetName val="form 2 (11)"/>
+      <sheetName val="form 2 (6)"/>
+      <sheetName val="form 2 (5)"/>
+      <sheetName val="Form (16)"/>
+      <sheetName val="4.3"/>
+      <sheetName val="6.3"/>
+      <sheetName val="11.3"/>
+      <sheetName val="12.3"/>
+      <sheetName val="13.3"/>
+      <sheetName val="20.3"/>
+      <sheetName val="26.3"/>
+      <sheetName val="28.3"/>
+      <sheetName val="31.03"/>
+      <sheetName val="4.4"/>
+      <sheetName val="8.4"/>
+      <sheetName val="11.4"/>
+      <sheetName val="15.4"/>
+      <sheetName val="16.4"/>
+      <sheetName val="18.4"/>
+      <sheetName val="19.4"/>
+      <sheetName val="24.4"/>
+      <sheetName val="29.04 "/>
+      <sheetName val="3.5"/>
+      <sheetName val="7.5 "/>
+      <sheetName val="9.5 "/>
+      <sheetName val="14.5"/>
+      <sheetName val="16.5"/>
+      <sheetName val="22.5"/>
+      <sheetName val="27.5"/>
+      <sheetName val="28.5"/>
+      <sheetName val="29.5"/>
+      <sheetName val="30.5"/>
+      <sheetName val="2.6"/>
+      <sheetName val="3.6"/>
+      <sheetName val="3.6 (L)"/>
+      <sheetName val="4.6"/>
+      <sheetName val="6.6"/>
+      <sheetName val="9.6"/>
+      <sheetName val="9.6 (L)"/>
+      <sheetName val="10.6"/>
+      <sheetName val="11.6"/>
+      <sheetName val="12.6"/>
+      <sheetName val="12.6 (L)"/>
+      <sheetName val="13.6"/>
+      <sheetName val="16.6"/>
+      <sheetName val="16.6 (2)"/>
+      <sheetName val="16.6 (L)"/>
+      <sheetName val="18.6"/>
+      <sheetName val="19.6"/>
+      <sheetName val="23.6"/>
+      <sheetName val="24.6"/>
+      <sheetName val="25.6"/>
+      <sheetName val="27.6"/>
+      <sheetName val="30.6"/>
+      <sheetName val="1.7"/>
+      <sheetName val="4.7"/>
+      <sheetName val="8.7"/>
+      <sheetName val="9.7"/>
+      <sheetName val="11.7"/>
+      <sheetName val="11.7 (2)"/>
+      <sheetName val="14.7"/>
+      <sheetName val="15.7"/>
+      <sheetName val="22.7"/>
+      <sheetName val="22.7 (L)"/>
+      <sheetName val="23.7"/>
+      <sheetName val="24.7"/>
+      <sheetName val="25.7"/>
+      <sheetName val="25.7 (2)"/>
+      <sheetName val="28.7"/>
+      <sheetName val="28.7 (L)"/>
+      <sheetName val="29.7"/>
+      <sheetName val="30.7"/>
+      <sheetName val="31.7"/>
+      <sheetName val="1.8"/>
+      <sheetName val="1.8 (2)"/>
+      <sheetName val="4.8"/>
+      <sheetName val="5.8"/>
+      <sheetName val="6.8"/>
+      <sheetName val="7.8"/>
+      <sheetName val="8.8"/>
+      <sheetName val="24.12 (3)"/>
+      <sheetName val="11.8"/>
+      <sheetName val="12.8"/>
+      <sheetName val="13.8"/>
+      <sheetName val="14.8"/>
+      <sheetName val="19.8"/>
+      <sheetName val="19.8 (2)"/>
+      <sheetName val="20.8"/>
+      <sheetName val="22.8 (L)"/>
+      <sheetName val="22.8 (L) (2)"/>
+      <sheetName val="25.8"/>
+      <sheetName val="26.8"/>
+      <sheetName val="29.8"/>
+      <sheetName val="3.9"/>
+      <sheetName val="4.9"/>
+      <sheetName val="5.9"/>
+      <sheetName val="8.9"/>
+      <sheetName val="9.9"/>
+      <sheetName val="11.9"/>
+      <sheetName val="12.9"/>
+      <sheetName val="12.9 (2)"/>
+      <sheetName val="16.9"/>
+      <sheetName val="17.9"/>
+      <sheetName val="17.9 (2)"/>
+      <sheetName val="19.9"/>
+      <sheetName val="22.9"/>
+      <sheetName val="23.9"/>
+      <sheetName val="24.9"/>
+      <sheetName val="29.9"/>
+      <sheetName val="29.9 (2)"/>
+      <sheetName val="1.10"/>
+      <sheetName val="2.10"/>
+      <sheetName val="3.10"/>
+      <sheetName val="6.10"/>
+      <sheetName val="9.10"/>
+      <sheetName val="10.10"/>
+      <sheetName val="10.10 (2)"/>
+      <sheetName val="13.10"/>
+      <sheetName val="15.10"/>
+      <sheetName val="16.10"/>
+      <sheetName val="17.10"/>
+      <sheetName val="17.10 (2)"/>
+      <sheetName val="20.10"/>
+      <sheetName val="21.10"/>
+      <sheetName val="22.10"/>
+      <sheetName val="23.8 (L)"/>
+      <sheetName val="23.10"/>
+      <sheetName val="27.10"/>
+      <sheetName val="28.10"/>
+      <sheetName val="29.10"/>
+      <sheetName val="30.10"/>
+      <sheetName val="31.10"/>
+      <sheetName val="4.11"/>
+      <sheetName val="5.11"/>
+      <sheetName val="6.11"/>
+      <sheetName val="6.11 (2)"/>
+      <sheetName val="7.11"/>
+      <sheetName val="11.11"/>
+      <sheetName val="14.11"/>
+      <sheetName val="18.11"/>
+      <sheetName val="19.11"/>
+      <sheetName val="20.11"/>
+      <sheetName val="21.11"/>
+      <sheetName val="24.11"/>
+      <sheetName val="26.11"/>
+      <sheetName val="27.11"/>
+      <sheetName val="01.12"/>
+      <sheetName val="02.12"/>
+      <sheetName val="03.12"/>
+      <sheetName val="5.12"/>
+      <sheetName val="5.12 (2)"/>
+      <sheetName val="10.12"/>
+      <sheetName val="11.12"/>
+      <sheetName val="12.12"/>
+      <sheetName val="16.12 "/>
+      <sheetName val="19.12 (L) "/>
+      <sheetName val="19.12"/>
+      <sheetName val="20.12 "/>
+      <sheetName val="23.12 "/>
+      <sheetName val="24.12"/>
+      <sheetName val="23.12 (L)"/>
+      <sheetName val="26.12 "/>
+      <sheetName val="30.12 "/>
+      <sheetName val="Form"/>
+      <sheetName val="BCN 22.4"/>
+      <sheetName val="form 2 (9)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
         <row r="1">
+          <cell r="A1"/>
+          <cell r="B1"/>
           <cell r="C1" t="str">
             <v>TẠM THỜI NGƯNG NHẬN LAZY</v>
           </cell>
+          <cell r="D1"/>
+          <cell r="E1"/>
+          <cell r="F1"/>
           <cell r="G1" t="str">
             <v>ASICS 12MM DÙNG BOM 132 (roundup(12/132),5)</v>
           </cell>
+          <cell r="H1"/>
+          <cell r="I1"/>
+          <cell r="J1"/>
+          <cell r="K1"/>
+          <cell r="L1"/>
+          <cell r="M1"/>
+          <cell r="N1"/>
+          <cell r="O1"/>
+          <cell r="P1"/>
+          <cell r="Q1"/>
+          <cell r="R1"/>
+          <cell r="S1"/>
+          <cell r="T1"/>
+          <cell r="U1"/>
+          <cell r="V1"/>
+          <cell r="W1"/>
         </row>
         <row r="2">
+          <cell r="A2"/>
+          <cell r="B2"/>
+          <cell r="C2"/>
+          <cell r="D2"/>
+          <cell r="E2"/>
+          <cell r="F2"/>
           <cell r="G2" t="str">
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>22635</v>
+            <v>23250</v>
           </cell>
           <cell r="I2">
-            <v>22635</v>
+            <v>23250</v>
           </cell>
           <cell r="J2">
-            <v>20947</v>
+            <v>21398</v>
           </cell>
           <cell r="K2">
-            <v>1688</v>
+            <v>1852</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
           </cell>
+          <cell r="M2"/>
+          <cell r="N2"/>
+          <cell r="O2"/>
+          <cell r="P2"/>
           <cell r="Q2" t="str">
             <v>ETD hệ thống+1ngay</v>
           </cell>
           <cell r="R2" t="e">
             <v>#VALUE!</v>
           </cell>
+          <cell r="S2"/>
+          <cell r="T2"/>
           <cell r="U2">
             <v>12</v>
           </cell>
+          <cell r="V2"/>
           <cell r="W2">
-            <v>1144</v>
+            <v>1165</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>NO.Order</v>
           </cell>
+          <cell r="B3"/>
           <cell r="C3" t="str">
             <v>Firm plan
 (PU PVN)</v>
@@ -2233,6 +2730,7 @@
           <cell r="A4" t="str">
             <v>S-2026-01-01</v>
           </cell>
+          <cell r="B4"/>
           <cell r="C4" t="str">
             <v>RPRO-260105-0668</v>
           </cell>
@@ -2585,6 +3083,7 @@
           <cell r="A9" t="str">
             <v>S-2026-01-06</v>
           </cell>
+          <cell r="B9"/>
           <cell r="C9" t="str">
             <v>RPRO-260105-0673</v>
           </cell>
@@ -2653,6 +3152,7 @@
           <cell r="A10" t="str">
             <v>S-2026-01-07</v>
           </cell>
+          <cell r="B10"/>
           <cell r="C10" t="str">
             <v>RPRO-260105-0674</v>
           </cell>
@@ -2721,6 +3221,7 @@
           <cell r="A11" t="str">
             <v>S-2026-01-08</v>
           </cell>
+          <cell r="B11"/>
           <cell r="C11" t="str">
             <v>RPRO-260105-0675</v>
           </cell>
@@ -2931,6 +3432,7 @@
           <cell r="A14" t="str">
             <v>L-2026-01-11</v>
           </cell>
+          <cell r="B14"/>
           <cell r="C14" t="str">
             <v>RPRO-260105-0678</v>
           </cell>
@@ -2964,6 +3466,7 @@
           <cell r="M14" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N14"/>
           <cell r="O14" t="str">
             <v>Lab test</v>
           </cell>
@@ -2996,6 +3499,7 @@
           <cell r="A15" t="str">
             <v>L-2026-01-12</v>
           </cell>
+          <cell r="B15"/>
           <cell r="C15" t="str">
             <v>RPRO-260105-0679</v>
           </cell>
@@ -3029,6 +3533,7 @@
           <cell r="M15" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N15"/>
           <cell r="O15" t="str">
             <v>Lab test</v>
           </cell>
@@ -3061,6 +3566,7 @@
           <cell r="A16" t="str">
             <v>L-2026-01-13</v>
           </cell>
+          <cell r="B16"/>
           <cell r="C16" t="str">
             <v>RPRO-260105-0680</v>
           </cell>
@@ -3094,6 +3600,7 @@
           <cell r="M16" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N16"/>
           <cell r="O16" t="str">
             <v>Lab test</v>
           </cell>
@@ -3126,6 +3633,7 @@
           <cell r="A17" t="str">
             <v>L-2026-01-14</v>
           </cell>
+          <cell r="B17"/>
           <cell r="C17" t="str">
             <v>RPRO-260105-0681</v>
           </cell>
@@ -3159,6 +3667,7 @@
           <cell r="M17" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N17"/>
           <cell r="O17" t="str">
             <v>Lab test</v>
           </cell>
@@ -3227,6 +3736,7 @@
           <cell r="M18" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N18"/>
           <cell r="O18" t="str">
             <v>Lab test</v>
           </cell>
@@ -3295,6 +3805,7 @@
           <cell r="M19" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N19"/>
           <cell r="O19" t="str">
             <v>Lab test</v>
           </cell>
@@ -3682,6 +4193,7 @@
           <cell r="A25" t="str">
             <v>L-2026-01-22</v>
           </cell>
+          <cell r="B25"/>
           <cell r="C25" t="str">
             <v>RPRO-260109-0095</v>
           </cell>
@@ -3715,6 +4227,7 @@
           <cell r="M25" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N25"/>
           <cell r="O25" t="str">
             <v>Lab test</v>
           </cell>
@@ -3747,6 +4260,7 @@
           <cell r="A26" t="str">
             <v>S-2026-01-23</v>
           </cell>
+          <cell r="B26"/>
           <cell r="C26" t="str">
             <v>RPRO-260113-0624</v>
           </cell>
@@ -3815,6 +4329,7 @@
           <cell r="A27" t="str">
             <v>S-2026-01-24</v>
           </cell>
+          <cell r="B27"/>
           <cell r="C27" t="str">
             <v>RPRO-260113-0625</v>
           </cell>
@@ -3883,6 +4398,7 @@
           <cell r="A28" t="str">
             <v>S-2026-01-25</v>
           </cell>
+          <cell r="B28"/>
           <cell r="C28" t="str">
             <v>RPRO-260113-0626</v>
           </cell>
@@ -3951,6 +4467,7 @@
           <cell r="A29" t="str">
             <v>S-2026-01-26</v>
           </cell>
+          <cell r="B29"/>
           <cell r="C29" t="str">
             <v>RPRO-260113-0627</v>
           </cell>
@@ -4019,6 +4536,7 @@
           <cell r="A30" t="str">
             <v>S-2026-01-27</v>
           </cell>
+          <cell r="B30"/>
           <cell r="C30" t="str">
             <v>RPRO-260113-0628</v>
           </cell>
@@ -4087,6 +4605,7 @@
           <cell r="A31" t="str">
             <v>S-2026-01-28</v>
           </cell>
+          <cell r="B31"/>
           <cell r="C31" t="str">
             <v>RPRO-260113-0629</v>
           </cell>
@@ -4155,6 +4674,7 @@
           <cell r="A32" t="str">
             <v>S-2026-01-29</v>
           </cell>
+          <cell r="B32"/>
           <cell r="C32" t="str">
             <v>RPRO-260113-0630</v>
           </cell>
@@ -4223,6 +4743,7 @@
           <cell r="A33" t="str">
             <v>S-2026-01-30</v>
           </cell>
+          <cell r="B33"/>
           <cell r="C33" t="str">
             <v>RPRO-260115-0298</v>
           </cell>
@@ -4291,6 +4812,7 @@
           <cell r="A34" t="str">
             <v>S-2026-01-31</v>
           </cell>
+          <cell r="B34"/>
           <cell r="C34" t="str">
             <v>RPRO-260115-0299</v>
           </cell>
@@ -4359,6 +4881,7 @@
           <cell r="A35" t="str">
             <v>S-2026-01-32</v>
           </cell>
+          <cell r="B35"/>
           <cell r="C35" t="str">
             <v>RPRO-260115-0300</v>
           </cell>
@@ -4427,6 +4950,7 @@
           <cell r="A36" t="str">
             <v>S-2026-01-33</v>
           </cell>
+          <cell r="B36"/>
           <cell r="C36" t="str">
             <v>RPRO-260115-0301</v>
           </cell>
@@ -4495,6 +5019,7 @@
           <cell r="A37" t="str">
             <v>S-2026-01-34</v>
           </cell>
+          <cell r="B37"/>
           <cell r="C37" t="str">
             <v>RPRO-260115-0302</v>
           </cell>
@@ -4563,6 +5088,7 @@
           <cell r="A38" t="str">
             <v>S-2026-01-35</v>
           </cell>
+          <cell r="B38"/>
           <cell r="C38" t="str">
             <v>RPRO-260115-0303</v>
           </cell>
@@ -4631,6 +5157,7 @@
           <cell r="A39" t="str">
             <v>S-2026-01-36</v>
           </cell>
+          <cell r="B39"/>
           <cell r="C39" t="str">
             <v>RPRO-260115-0304</v>
           </cell>
@@ -4699,6 +5226,7 @@
           <cell r="A40" t="str">
             <v>S-2026-01-37</v>
           </cell>
+          <cell r="B40"/>
           <cell r="C40" t="str">
             <v>RPRO-260115-0305</v>
           </cell>
@@ -4767,6 +5295,7 @@
           <cell r="A41" t="str">
             <v>S-2026-01-38</v>
           </cell>
+          <cell r="B41"/>
           <cell r="C41" t="str">
             <v>RPRO-260115-0306</v>
           </cell>
@@ -4835,6 +5364,7 @@
           <cell r="A42" t="str">
             <v>S-2026-01-39</v>
           </cell>
+          <cell r="B42"/>
           <cell r="C42" t="str">
             <v>RPRO-260115-0307</v>
           </cell>
@@ -4903,6 +5433,7 @@
           <cell r="A43" t="str">
             <v>S-2026-01-40</v>
           </cell>
+          <cell r="B43"/>
           <cell r="C43" t="str">
             <v>RPRO-260115-0308</v>
           </cell>
@@ -4971,6 +5502,7 @@
           <cell r="A44" t="str">
             <v>S-2026-01-41</v>
           </cell>
+          <cell r="B44"/>
           <cell r="C44" t="str">
             <v>RPRO-260115-0309</v>
           </cell>
@@ -5039,6 +5571,7 @@
           <cell r="A45" t="str">
             <v>S-2026-01-42</v>
           </cell>
+          <cell r="B45"/>
           <cell r="C45" t="str">
             <v>RPRO-260109-0096</v>
           </cell>
@@ -5107,6 +5640,7 @@
           <cell r="A46" t="str">
             <v>S-2026-01-43</v>
           </cell>
+          <cell r="B46"/>
           <cell r="C46" t="str">
             <v>RPRO-260109-0097</v>
           </cell>
@@ -5175,6 +5709,7 @@
           <cell r="A47" t="str">
             <v>S-2026-01-44</v>
           </cell>
+          <cell r="B47"/>
           <cell r="C47" t="str">
             <v>RPRO-260109-0098</v>
           </cell>
@@ -5243,6 +5778,7 @@
           <cell r="A48" t="str">
             <v>S-2026-01-45</v>
           </cell>
+          <cell r="B48"/>
           <cell r="C48" t="str">
             <v>RPRO-260109-0099</v>
           </cell>
@@ -5311,6 +5847,7 @@
           <cell r="A49" t="str">
             <v>S-2026-01-46</v>
           </cell>
+          <cell r="B49"/>
           <cell r="C49" t="str">
             <v>RPRO-260120-0349</v>
           </cell>
@@ -5379,6 +5916,7 @@
           <cell r="A50" t="str">
             <v>S-2026-01-47</v>
           </cell>
+          <cell r="B50"/>
           <cell r="C50" t="str">
             <v>RPRO-260120-0350</v>
           </cell>
@@ -5447,6 +5985,7 @@
           <cell r="A51" t="str">
             <v>S-2026-01-48</v>
           </cell>
+          <cell r="B51"/>
           <cell r="C51" t="str">
             <v>RPRO-260120-0351</v>
           </cell>
@@ -5515,6 +6054,7 @@
           <cell r="A52" t="str">
             <v>S-2026-01-49</v>
           </cell>
+          <cell r="B52"/>
           <cell r="C52" t="str">
             <v>RPRO-260120-0352</v>
           </cell>
@@ -5583,6 +6123,7 @@
           <cell r="A53" t="str">
             <v>S-2026-01-50</v>
           </cell>
+          <cell r="B53"/>
           <cell r="C53" t="str">
             <v>RPRO-260120-0353</v>
           </cell>
@@ -5651,6 +6192,7 @@
           <cell r="A54" t="str">
             <v>S-2026-01-51</v>
           </cell>
+          <cell r="B54"/>
           <cell r="C54" t="str">
             <v>RPRO-260120-0354</v>
           </cell>
@@ -5719,6 +6261,7 @@
           <cell r="A55" t="str">
             <v>S-2026-01-52</v>
           </cell>
+          <cell r="B55"/>
           <cell r="C55" t="str">
             <v>RPRO-260113-0631</v>
           </cell>
@@ -5787,6 +6330,7 @@
           <cell r="A56" t="str">
             <v>S-2026-01-53</v>
           </cell>
+          <cell r="B56"/>
           <cell r="C56" t="str">
             <v>RPRO-260120-0355</v>
           </cell>
@@ -5855,6 +6399,7 @@
           <cell r="A57" t="str">
             <v>S-2026-01-54</v>
           </cell>
+          <cell r="B57"/>
           <cell r="C57" t="str">
             <v>RPRO-260120-0356</v>
           </cell>
@@ -5923,6 +6468,7 @@
           <cell r="A58" t="str">
             <v>S-2026-01-55</v>
           </cell>
+          <cell r="B58"/>
           <cell r="C58" t="str">
             <v>RPRO-260120-0357</v>
           </cell>
@@ -5991,6 +6537,7 @@
           <cell r="A59" t="str">
             <v>S-2026-01-56</v>
           </cell>
+          <cell r="B59"/>
           <cell r="C59" t="str">
             <v>RPRO-260120-0358</v>
           </cell>
@@ -6059,6 +6606,7 @@
           <cell r="A60" t="str">
             <v>S-2026-01-57</v>
           </cell>
+          <cell r="B60"/>
           <cell r="C60" t="str">
             <v>RPRO-260120-0359</v>
           </cell>
@@ -6127,6 +6675,7 @@
           <cell r="A61" t="str">
             <v>S-2026-01-58</v>
           </cell>
+          <cell r="B61"/>
           <cell r="C61" t="str">
             <v>RPRO-260120-0360</v>
           </cell>
@@ -6195,6 +6744,7 @@
           <cell r="A62" t="str">
             <v>S-2026-01-59</v>
           </cell>
+          <cell r="B62"/>
           <cell r="C62" t="str">
             <v>RPRO-260116-0276</v>
           </cell>
@@ -6263,6 +6813,7 @@
           <cell r="A63" t="str">
             <v>S-2026-01-60</v>
           </cell>
+          <cell r="B63"/>
           <cell r="C63" t="str">
             <v>RPRO-260115-0310</v>
           </cell>
@@ -6331,6 +6882,7 @@
           <cell r="A64" t="str">
             <v>S-2026-01-61</v>
           </cell>
+          <cell r="B64"/>
           <cell r="C64" t="str">
             <v>RPRO-260120-0361</v>
           </cell>
@@ -6470,6 +7022,7 @@
           <cell r="A66" t="str">
             <v>S-2026-01-63</v>
           </cell>
+          <cell r="B66"/>
           <cell r="C66" t="str">
             <v>RPRO-260122-1562</v>
           </cell>
@@ -6538,6 +7091,7 @@
           <cell r="A67" t="str">
             <v>S-2026-01-64</v>
           </cell>
+          <cell r="B67"/>
           <cell r="C67" t="str">
             <v>RPRO-260122-1563</v>
           </cell>
@@ -6606,6 +7160,7 @@
           <cell r="A68" t="str">
             <v>S-2026-01-65</v>
           </cell>
+          <cell r="B68"/>
           <cell r="C68" t="str">
             <v>RPRO-260122-1564</v>
           </cell>
@@ -6674,6 +7229,7 @@
           <cell r="A69" t="str">
             <v>S-2026-01-66</v>
           </cell>
+          <cell r="B69"/>
           <cell r="C69" t="str">
             <v>RPRO-260122-1565</v>
           </cell>
@@ -6742,6 +7298,7 @@
           <cell r="A70" t="str">
             <v>S-2026-01-67</v>
           </cell>
+          <cell r="B70"/>
           <cell r="C70" t="str">
             <v>RPRO-260122-1566</v>
           </cell>
@@ -6810,6 +7367,7 @@
           <cell r="A71" t="str">
             <v>S-2026-01-68</v>
           </cell>
+          <cell r="B71"/>
           <cell r="C71" t="str">
             <v>RPRO-260122-1567</v>
           </cell>
@@ -6878,6 +7436,7 @@
           <cell r="A72" t="str">
             <v>S-2026-01-69</v>
           </cell>
+          <cell r="B72"/>
           <cell r="C72" t="str">
             <v>RPRO-260122-1568</v>
           </cell>
@@ -6946,6 +7505,7 @@
           <cell r="A73" t="str">
             <v>S-2026-01-70</v>
           </cell>
+          <cell r="B73"/>
           <cell r="C73" t="str">
             <v>RPRO-260122-1569</v>
           </cell>
@@ -7014,6 +7574,7 @@
           <cell r="A74" t="str">
             <v>S-2026-01-71</v>
           </cell>
+          <cell r="B74"/>
           <cell r="C74" t="str">
             <v>RPRO-260122-1570</v>
           </cell>
@@ -7082,6 +7643,7 @@
           <cell r="A75" t="str">
             <v>S-2026-01-72</v>
           </cell>
+          <cell r="B75"/>
           <cell r="C75" t="str">
             <v>RPRO-260122-1571</v>
           </cell>
@@ -7363,6 +7925,7 @@
           <cell r="A79" t="str">
             <v>S-2026-01-76</v>
           </cell>
+          <cell r="B79"/>
           <cell r="C79" t="str">
             <v>RPRO-260122-1573</v>
           </cell>
@@ -7431,6 +7994,7 @@
           <cell r="A80" t="str">
             <v>S-2026-01-77</v>
           </cell>
+          <cell r="B80"/>
           <cell r="C80" t="str">
             <v>RPRO-260122-1574</v>
           </cell>
@@ -7499,6 +8063,7 @@
           <cell r="A81" t="str">
             <v>S-2026-01-78</v>
           </cell>
+          <cell r="B81"/>
           <cell r="C81" t="str">
             <v>RPRO-260122-1575</v>
           </cell>
@@ -7567,6 +8132,7 @@
           <cell r="A82" t="str">
             <v>S-2026-01-79</v>
           </cell>
+          <cell r="B82"/>
           <cell r="C82" t="str">
             <v>RPRO-260122-1576</v>
           </cell>
@@ -7635,6 +8201,7 @@
           <cell r="A83" t="str">
             <v>S-2026-01-80</v>
           </cell>
+          <cell r="B83"/>
           <cell r="C83" t="str">
             <v>RPRO-260122-1577</v>
           </cell>
@@ -7703,6 +8270,7 @@
           <cell r="A84" t="str">
             <v>S-2026-01-81</v>
           </cell>
+          <cell r="B84"/>
           <cell r="C84" t="str">
             <v>RPRO-260122-1578</v>
           </cell>
@@ -7771,6 +8339,7 @@
           <cell r="A85" t="str">
             <v>S-2026-01-82</v>
           </cell>
+          <cell r="B85"/>
           <cell r="C85" t="str">
             <v>RPRO-260122-1579</v>
           </cell>
@@ -7839,6 +8408,7 @@
           <cell r="A86" t="str">
             <v>S-2026-01-83</v>
           </cell>
+          <cell r="B86"/>
           <cell r="C86" t="str">
             <v>RPRO-260122-1580</v>
           </cell>
@@ -7910,6 +8480,7 @@
           <cell r="B87" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C87"/>
           <cell r="D87" t="str">
             <v>OV-0385</v>
           </cell>
@@ -7978,6 +8549,7 @@
           <cell r="B88" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C88"/>
           <cell r="D88" t="str">
             <v>OV-0385</v>
           </cell>
@@ -8046,6 +8618,7 @@
           <cell r="B89" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C89"/>
           <cell r="D89" t="str">
             <v>OV-0385</v>
           </cell>
@@ -8111,6 +8684,7 @@
           <cell r="A90" t="str">
             <v>S-2026-01-87</v>
           </cell>
+          <cell r="B90"/>
           <cell r="C90" t="str">
             <v>RPRO-260127-0875</v>
           </cell>
@@ -8179,6 +8753,7 @@
           <cell r="A91" t="str">
             <v>S-2026-01-88</v>
           </cell>
+          <cell r="B91"/>
           <cell r="C91" t="str">
             <v>RPRO-260127-0877</v>
           </cell>
@@ -8247,6 +8822,7 @@
           <cell r="A92" t="str">
             <v>S-2026-01-89</v>
           </cell>
+          <cell r="B92"/>
           <cell r="C92" t="str">
             <v>RPRO-260127-0879</v>
           </cell>
@@ -8315,6 +8891,7 @@
           <cell r="A93" t="str">
             <v>S-2026-01-90</v>
           </cell>
+          <cell r="B93"/>
           <cell r="C93" t="str">
             <v>RPRO-260128-1270</v>
           </cell>
@@ -8383,6 +8960,7 @@
           <cell r="A94" t="str">
             <v>S-2026-01-91</v>
           </cell>
+          <cell r="B94"/>
           <cell r="C94" t="str">
             <v>RPRO-260128-1271</v>
           </cell>
@@ -8451,6 +9029,7 @@
           <cell r="A95" t="str">
             <v>S-2026-01-92</v>
           </cell>
+          <cell r="B95"/>
           <cell r="C95" t="str">
             <v>RPRO-260128-1272</v>
           </cell>
@@ -8519,6 +9098,7 @@
           <cell r="A96" t="str">
             <v>S-2026-01-93</v>
           </cell>
+          <cell r="B96"/>
           <cell r="C96" t="str">
             <v>RPRO-260128-1273</v>
           </cell>
@@ -8587,6 +9167,7 @@
           <cell r="A97" t="str">
             <v>S-2026-01-94</v>
           </cell>
+          <cell r="B97"/>
           <cell r="C97" t="str">
             <v>RPRO-260128-1274</v>
           </cell>
@@ -8655,6 +9236,7 @@
           <cell r="A98" t="str">
             <v>S-2026-01-95</v>
           </cell>
+          <cell r="B98"/>
           <cell r="C98" t="str">
             <v>RPRO-260128-1275</v>
           </cell>
@@ -8723,6 +9305,7 @@
           <cell r="A99" t="str">
             <v>S-2026-01-96</v>
           </cell>
+          <cell r="B99"/>
           <cell r="C99" t="str">
             <v>RPRO-260128-1276</v>
           </cell>
@@ -8791,6 +9374,7 @@
           <cell r="A100" t="str">
             <v>S-2026-01-97</v>
           </cell>
+          <cell r="B100"/>
           <cell r="C100" t="str">
             <v>RPRO-260128-1277</v>
           </cell>
@@ -8859,6 +9443,7 @@
           <cell r="A101" t="str">
             <v>S-2026-01-98</v>
           </cell>
+          <cell r="B101"/>
           <cell r="C101" t="str">
             <v>RPRO-260129-0656</v>
           </cell>
@@ -8927,6 +9512,7 @@
           <cell r="A102" t="str">
             <v>S-2026-02-01</v>
           </cell>
+          <cell r="B102"/>
           <cell r="C102" t="str">
             <v>RPRO-260203-0021</v>
           </cell>
@@ -8995,6 +9581,7 @@
           <cell r="A103" t="str">
             <v>S-2026-02-02</v>
           </cell>
+          <cell r="B103"/>
           <cell r="C103" t="str">
             <v>RPRO-260203-0022</v>
           </cell>
@@ -9063,6 +9650,7 @@
           <cell r="A104" t="str">
             <v>S-2026-02-03</v>
           </cell>
+          <cell r="B104"/>
           <cell r="C104" t="str">
             <v>RPRO-260203-0770</v>
           </cell>
@@ -9131,6 +9719,7 @@
           <cell r="A105" t="str">
             <v>S-2026-02-04</v>
           </cell>
+          <cell r="B105"/>
           <cell r="C105" t="str">
             <v>RPRO-260203-0771</v>
           </cell>
@@ -9199,6 +9788,7 @@
           <cell r="A106" t="str">
             <v>S-2026-02-05</v>
           </cell>
+          <cell r="B106"/>
           <cell r="C106" t="str">
             <v>RPRO-260203-0772</v>
           </cell>
@@ -9267,6 +9857,7 @@
           <cell r="A107" t="str">
             <v>S-2026-02-06</v>
           </cell>
+          <cell r="B107"/>
           <cell r="C107" t="str">
             <v>RPRO-260203-0773</v>
           </cell>
@@ -9335,6 +9926,7 @@
           <cell r="A108" t="str">
             <v>S-2026-02-07</v>
           </cell>
+          <cell r="B108"/>
           <cell r="C108" t="str">
             <v>RPRO-260203-0774</v>
           </cell>
@@ -9403,6 +9995,7 @@
           <cell r="A109" t="str">
             <v>S-2026-02-08</v>
           </cell>
+          <cell r="B109"/>
           <cell r="C109" t="str">
             <v>RPRO-260203-0775</v>
           </cell>
@@ -9471,6 +10064,7 @@
           <cell r="A110" t="str">
             <v>S-2026-02-09</v>
           </cell>
+          <cell r="B110"/>
           <cell r="C110" t="str">
             <v>RPRO-260203-0776</v>
           </cell>
@@ -9539,6 +10133,7 @@
           <cell r="A111" t="str">
             <v>S-2026-02-10</v>
           </cell>
+          <cell r="B111"/>
           <cell r="C111" t="str">
             <v>RPRO-260203-0777</v>
           </cell>
@@ -9607,6 +10202,7 @@
           <cell r="A112" t="str">
             <v>S-2026-02-11</v>
           </cell>
+          <cell r="B112"/>
           <cell r="C112" t="str">
             <v>RPRO-260203-0778</v>
           </cell>
@@ -9675,6 +10271,7 @@
           <cell r="A113" t="str">
             <v>S-2026-02-12</v>
           </cell>
+          <cell r="B113"/>
           <cell r="C113" t="str">
             <v>RPRO-260203-0779</v>
           </cell>
@@ -9743,6 +10340,7 @@
           <cell r="A114" t="str">
             <v>S-2026-02-13</v>
           </cell>
+          <cell r="B114"/>
           <cell r="C114" t="str">
             <v>RPRO-260203-0780</v>
           </cell>
@@ -9811,6 +10409,7 @@
           <cell r="A115" t="str">
             <v>S-2026-02-14</v>
           </cell>
+          <cell r="B115"/>
           <cell r="C115" t="str">
             <v>RPRO-260203-0781</v>
           </cell>
@@ -9879,6 +10478,7 @@
           <cell r="A116" t="str">
             <v>S-2026-02-15</v>
           </cell>
+          <cell r="B116"/>
           <cell r="C116" t="str">
             <v>RPRO-260203-0782</v>
           </cell>
@@ -9947,6 +10547,7 @@
           <cell r="A117" t="str">
             <v>S-2026-02-16</v>
           </cell>
+          <cell r="B117"/>
           <cell r="C117" t="str">
             <v>RPRO-260203-0783</v>
           </cell>
@@ -10015,6 +10616,7 @@
           <cell r="A118" t="str">
             <v>S-2026-02-17</v>
           </cell>
+          <cell r="B118"/>
           <cell r="C118" t="str">
             <v>RPRO-260203-0784</v>
           </cell>
@@ -10083,6 +10685,7 @@
           <cell r="A119" t="str">
             <v>S-2026-02-18</v>
           </cell>
+          <cell r="B119"/>
           <cell r="C119" t="str">
             <v>RPRO-260204-0399</v>
           </cell>
@@ -10151,6 +10754,7 @@
           <cell r="A120" t="str">
             <v>S-2026-02-19</v>
           </cell>
+          <cell r="B120"/>
           <cell r="C120" t="str">
             <v>RPRO-260204-0400</v>
           </cell>
@@ -10219,6 +10823,7 @@
           <cell r="A121" t="str">
             <v>L-2026-02-20</v>
           </cell>
+          <cell r="B121"/>
           <cell r="C121" t="str">
             <v>RPRO-260204-0401</v>
           </cell>
@@ -10252,6 +10857,7 @@
           <cell r="M121" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N121"/>
           <cell r="O121" t="str">
             <v>Lab test</v>
           </cell>
@@ -10284,6 +10890,7 @@
           <cell r="A122" t="str">
             <v>L-2026-02-21</v>
           </cell>
+          <cell r="B122"/>
           <cell r="C122" t="str">
             <v>RPRO-260204-0402</v>
           </cell>
@@ -10317,6 +10924,7 @@
           <cell r="M122" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N122"/>
           <cell r="O122" t="str">
             <v>Lab test</v>
           </cell>
@@ -10420,6 +11028,7 @@
           <cell r="A124" t="str">
             <v>S-2026-02-23</v>
           </cell>
+          <cell r="B124"/>
           <cell r="C124" t="str">
             <v>RPRO-260210-0003</v>
           </cell>
@@ -10559,6 +11168,7 @@
           <cell r="A126" t="str">
             <v>S-2026-02-25</v>
           </cell>
+          <cell r="B126"/>
           <cell r="C126" t="str">
             <v>RPRO-260210-0005</v>
           </cell>
@@ -10627,6 +11237,7 @@
           <cell r="A127" t="str">
             <v>S-2026-02-26</v>
           </cell>
+          <cell r="B127"/>
           <cell r="C127" t="str">
             <v>RPRO-260210-0006</v>
           </cell>
@@ -10695,6 +11306,7 @@
           <cell r="A128" t="str">
             <v>S-2026-02-27</v>
           </cell>
+          <cell r="B128"/>
           <cell r="C128" t="str">
             <v>RPRO-260210-0007</v>
           </cell>
@@ -10763,6 +11375,7 @@
           <cell r="A129" t="str">
             <v>S-2026-02-28</v>
           </cell>
+          <cell r="B129"/>
           <cell r="C129" t="str">
             <v>RPRO-260210-0008</v>
           </cell>
@@ -10831,6 +11444,7 @@
           <cell r="A130" t="str">
             <v>S-2026-02-29</v>
           </cell>
+          <cell r="B130"/>
           <cell r="C130" t="str">
             <v>RPRO-260210-0009</v>
           </cell>
@@ -10899,6 +11513,7 @@
           <cell r="A131" t="str">
             <v>S-2026-02-30</v>
           </cell>
+          <cell r="B131"/>
           <cell r="C131" t="str">
             <v>RPRO-260210-0010</v>
           </cell>
@@ -10967,6 +11582,7 @@
           <cell r="A132" t="str">
             <v>S-2026-02-31</v>
           </cell>
+          <cell r="B132"/>
           <cell r="C132" t="str">
             <v>RPRO-260210-0011</v>
           </cell>
@@ -11036,6 +11652,7 @@
           <cell r="A133" t="str">
             <v>S-2026-02-32</v>
           </cell>
+          <cell r="B133"/>
           <cell r="C133" t="str">
             <v>RPRO-260210-0012</v>
           </cell>
@@ -11105,6 +11722,7 @@
           <cell r="A134" t="str">
             <v>S-2026-02-33</v>
           </cell>
+          <cell r="B134"/>
           <cell r="C134" t="str">
             <v>RPRO-260210-0013</v>
           </cell>
@@ -11173,6 +11791,7 @@
           <cell r="A135" t="str">
             <v>S-2026-02-34</v>
           </cell>
+          <cell r="B135"/>
           <cell r="C135" t="str">
             <v>RPRO-260211-0001</v>
           </cell>
@@ -11243,6 +11862,7 @@
           <cell r="A136" t="str">
             <v>S-2026-02-35</v>
           </cell>
+          <cell r="B136"/>
           <cell r="C136" t="str">
             <v>RPRO-260227-0335</v>
           </cell>
@@ -11311,6 +11931,7 @@
           <cell r="A137" t="str">
             <v>S-2026-02-36</v>
           </cell>
+          <cell r="B137"/>
           <cell r="C137" t="str">
             <v>RPRO-260227-0336</v>
           </cell>
@@ -11379,6 +12000,7 @@
           <cell r="A138" t="str">
             <v>S-2026-02-37</v>
           </cell>
+          <cell r="B138"/>
           <cell r="C138" t="str">
             <v>RPRO-260227-0337</v>
           </cell>
@@ -11447,6 +12069,7 @@
           <cell r="A139" t="str">
             <v>S-2026-02-38</v>
           </cell>
+          <cell r="B139"/>
           <cell r="C139" t="str">
             <v>RPRO-260227-0338</v>
           </cell>
@@ -11515,6 +12138,7 @@
           <cell r="A140" t="str">
             <v>S-2026-02-39</v>
           </cell>
+          <cell r="B140"/>
           <cell r="C140" t="str">
             <v>RPRO-260227-0339</v>
           </cell>
@@ -11583,6 +12207,7 @@
           <cell r="A141" t="str">
             <v>L-2026-02-40</v>
           </cell>
+          <cell r="B141"/>
           <cell r="C141" t="str">
             <v>RPRO-260227-0340</v>
           </cell>
@@ -11616,6 +12241,7 @@
           <cell r="M141" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N141"/>
           <cell r="O141" t="str">
             <v>Lab test</v>
           </cell>
@@ -11648,6 +12274,7 @@
           <cell r="A142" t="str">
             <v>S-2026-02-41</v>
           </cell>
+          <cell r="B142"/>
           <cell r="C142" t="str">
             <v>RPRO-260227-0341</v>
           </cell>
@@ -11716,6 +12343,7 @@
           <cell r="A143" t="str">
             <v>S-2026-02-42</v>
           </cell>
+          <cell r="B143"/>
           <cell r="C143" t="str">
             <v>RPRO-260227-0342</v>
           </cell>
@@ -11784,6 +12412,7 @@
           <cell r="A144" t="str">
             <v>S-2026-02-43</v>
           </cell>
+          <cell r="B144"/>
           <cell r="C144" t="str">
             <v>RPRO-260227-0343</v>
           </cell>
@@ -11852,6 +12481,7 @@
           <cell r="A145" t="str">
             <v>S-2026-02-44</v>
           </cell>
+          <cell r="B145"/>
           <cell r="C145" t="str">
             <v>RPRO-260227-0344</v>
           </cell>
@@ -11920,6 +12550,7 @@
           <cell r="A146" t="str">
             <v>S-2026-02-45</v>
           </cell>
+          <cell r="B146"/>
           <cell r="C146" t="str">
             <v>RPRO-260227-0345</v>
           </cell>
@@ -12059,6 +12690,7 @@
           <cell r="A148" t="str">
             <v>S-2026-02-47</v>
           </cell>
+          <cell r="B148"/>
           <cell r="C148" t="str">
             <v>RPRO-260227-0347</v>
           </cell>
@@ -12127,6 +12759,7 @@
           <cell r="A149" t="str">
             <v>S-2026-02-48</v>
           </cell>
+          <cell r="B149"/>
           <cell r="C149" t="str">
             <v>RPRO-260227-0348</v>
           </cell>
@@ -12195,6 +12828,7 @@
           <cell r="A150" t="str">
             <v>S-2026-02-49</v>
           </cell>
+          <cell r="B150"/>
           <cell r="C150" t="str">
             <v>RPRO-260302-0004</v>
           </cell>
@@ -12263,6 +12897,7 @@
           <cell r="A151" t="str">
             <v>S-2026-02-50</v>
           </cell>
+          <cell r="B151"/>
           <cell r="C151" t="str">
             <v>RPRO-260227-0349</v>
           </cell>
@@ -12331,6 +12966,7 @@
           <cell r="A152" t="str">
             <v>S-2026-02-51</v>
           </cell>
+          <cell r="B152"/>
           <cell r="C152" t="str">
             <v>RPRO-260227-0350</v>
           </cell>
@@ -12399,6 +13035,7 @@
           <cell r="A153" t="str">
             <v>S-2026-02-52</v>
           </cell>
+          <cell r="B153"/>
           <cell r="C153" t="str">
             <v>RPRO-260227-0351</v>
           </cell>
@@ -12467,6 +13104,7 @@
           <cell r="A154" t="str">
             <v>S-2026-02-53</v>
           </cell>
+          <cell r="B154"/>
           <cell r="C154" t="str">
             <v>RPRO-260227-0352</v>
           </cell>
@@ -12535,6 +13173,7 @@
           <cell r="A155" t="str">
             <v>L-2026-03-01</v>
           </cell>
+          <cell r="B155"/>
           <cell r="C155" t="str">
             <v>RPRO-260303-0005</v>
           </cell>
@@ -12568,6 +13207,7 @@
           <cell r="M155" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N155"/>
           <cell r="O155" t="str">
             <v>Lab test</v>
           </cell>
@@ -12600,6 +13240,7 @@
           <cell r="A156" t="str">
             <v>L-2026-03-02</v>
           </cell>
+          <cell r="B156"/>
           <cell r="C156" t="str">
             <v>RPRO-260303-0006</v>
           </cell>
@@ -12633,6 +13274,7 @@
           <cell r="M156" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N156"/>
           <cell r="O156" t="str">
             <v>Lab test</v>
           </cell>
@@ -12949,6 +13591,7 @@
           <cell r="A161" t="str">
             <v>S-2026-03-07</v>
           </cell>
+          <cell r="B161"/>
           <cell r="C161" t="str">
             <v>RPRO-260303-0011</v>
           </cell>
@@ -13017,6 +13660,7 @@
           <cell r="A162" t="str">
             <v>S-2026-03-08</v>
           </cell>
+          <cell r="B162"/>
           <cell r="C162" t="str">
             <v>RPRO-260303-0012</v>
           </cell>
@@ -13085,6 +13729,7 @@
           <cell r="A163" t="str">
             <v>S-2026-03-09</v>
           </cell>
+          <cell r="B163"/>
           <cell r="C163" t="str">
             <v>RPRO-260303-0013</v>
           </cell>
@@ -13153,6 +13798,7 @@
           <cell r="A164" t="str">
             <v>S-2026-03-10</v>
           </cell>
+          <cell r="B164"/>
           <cell r="C164" t="str">
             <v>RPRO-260303-0014</v>
           </cell>
@@ -13221,6 +13867,7 @@
           <cell r="A165" t="str">
             <v>S-2026-03-11</v>
           </cell>
+          <cell r="B165"/>
           <cell r="C165" t="str">
             <v>RPRO-260313-0139</v>
           </cell>
@@ -13254,6 +13901,7 @@
           <cell r="M165" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N165"/>
           <cell r="O165" t="str">
             <v>Sample</v>
           </cell>
@@ -13286,6 +13934,7 @@
           <cell r="A166" t="str">
             <v>S-2026-03-12</v>
           </cell>
+          <cell r="B166"/>
           <cell r="C166" t="str">
             <v>RPRO-260313-0140</v>
           </cell>
@@ -13319,6 +13968,7 @@
           <cell r="M166" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N166"/>
           <cell r="O166" t="str">
             <v>Sample</v>
           </cell>
@@ -13351,6 +14001,7 @@
           <cell r="A167" t="str">
             <v>S-2026-03-13</v>
           </cell>
+          <cell r="B167"/>
           <cell r="C167" t="str">
             <v>RPRO-260313-0141</v>
           </cell>
@@ -13384,6 +14035,7 @@
           <cell r="M167" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N167"/>
           <cell r="O167" t="str">
             <v>Sample</v>
           </cell>
@@ -13487,6 +14139,7 @@
           <cell r="A169" t="str">
             <v>S-2026-03-15</v>
           </cell>
+          <cell r="B169"/>
           <cell r="C169" t="str">
             <v>RPRO-260306-1547</v>
           </cell>
@@ -13555,6 +14208,7 @@
           <cell r="A170" t="str">
             <v>S-2026-03-16</v>
           </cell>
+          <cell r="B170"/>
           <cell r="C170" t="str">
             <v>RPRO-260306-1548</v>
           </cell>
@@ -13623,6 +14277,7 @@
           <cell r="A171" t="str">
             <v>S-2026-03-17</v>
           </cell>
+          <cell r="B171"/>
           <cell r="C171" t="str">
             <v>RPRO-260306-1549</v>
           </cell>
@@ -13691,6 +14346,7 @@
           <cell r="A172" t="str">
             <v>S-2026-03-18</v>
           </cell>
+          <cell r="B172"/>
           <cell r="C172" t="str">
             <v>RPRO-260306-1550</v>
           </cell>
@@ -13759,6 +14415,7 @@
           <cell r="A173" t="str">
             <v>S-2026-03-19</v>
           </cell>
+          <cell r="B173"/>
           <cell r="C173" t="str">
             <v>RPRO-260306-1551</v>
           </cell>
@@ -13827,6 +14484,7 @@
           <cell r="A174" t="str">
             <v>S-2026-03-20</v>
           </cell>
+          <cell r="B174"/>
           <cell r="C174" t="str">
             <v>RPRO-260306-1552</v>
           </cell>
@@ -13895,6 +14553,7 @@
           <cell r="A175" t="str">
             <v>S-2026-03-21</v>
           </cell>
+          <cell r="B175"/>
           <cell r="C175" t="str">
             <v>RPRO-260306-1553</v>
           </cell>
@@ -13963,6 +14622,7 @@
           <cell r="A176" t="str">
             <v>S-2026-03-22</v>
           </cell>
+          <cell r="B176"/>
           <cell r="C176" t="str">
             <v>RPRO-260306-1554</v>
           </cell>
@@ -14031,6 +14691,7 @@
           <cell r="A177" t="str">
             <v>S-2026-03-23</v>
           </cell>
+          <cell r="B177"/>
           <cell r="C177" t="str">
             <v>RPRO-260306-1555</v>
           </cell>
@@ -14099,6 +14760,7 @@
           <cell r="A178" t="str">
             <v>S-2026-03-24</v>
           </cell>
+          <cell r="B178"/>
           <cell r="C178" t="str">
             <v>RPRO-260306-1556</v>
           </cell>
@@ -14228,7 +14890,7 @@
             <v>4</v>
           </cell>
           <cell r="V179">
-            <v>2.7779999999999999E-2</v>
+            <v>2.8570000000000002E-2</v>
           </cell>
           <cell r="W179">
             <v>1</v>
@@ -14238,6 +14900,7 @@
           <cell r="A180" t="str">
             <v>L-2026-03-26</v>
           </cell>
+          <cell r="B180"/>
           <cell r="C180" t="str">
             <v>RPRO-260305-1288</v>
           </cell>
@@ -14271,6 +14934,7 @@
           <cell r="M180" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N180"/>
           <cell r="O180" t="str">
             <v>Lab test</v>
           </cell>
@@ -14374,6 +15038,7 @@
           <cell r="A182" t="str">
             <v>S-2026-03-28</v>
           </cell>
+          <cell r="B182"/>
           <cell r="C182" t="str">
             <v>RPRO-260306-1559</v>
           </cell>
@@ -14442,6 +15107,7 @@
           <cell r="A183" t="str">
             <v>S-2026-03-29</v>
           </cell>
+          <cell r="B183"/>
           <cell r="C183" t="str">
             <v>RPRO-260306-1560</v>
           </cell>
@@ -14510,6 +15176,7 @@
           <cell r="A184" t="str">
             <v>S-2026-03-30</v>
           </cell>
+          <cell r="B184"/>
           <cell r="C184" t="str">
             <v>RPRO-260306-1561</v>
           </cell>
@@ -14578,6 +15245,7 @@
           <cell r="A185" t="str">
             <v>S-2026-03-31</v>
           </cell>
+          <cell r="B185"/>
           <cell r="C185" t="str">
             <v>RPRO-260306-1562</v>
           </cell>
@@ -14646,6 +15314,7 @@
           <cell r="A186" t="str">
             <v>S-2026-03-32</v>
           </cell>
+          <cell r="B186"/>
           <cell r="C186" t="str">
             <v>RPRO-260306-1563</v>
           </cell>
@@ -14714,6 +15383,7 @@
           <cell r="A187" t="str">
             <v>S-2026-03-33</v>
           </cell>
+          <cell r="B187"/>
           <cell r="C187" t="str">
             <v>RPRO-260306-1564</v>
           </cell>
@@ -14782,6 +15452,7 @@
           <cell r="A188" t="str">
             <v>S-2026-03-34</v>
           </cell>
+          <cell r="B188"/>
           <cell r="C188" t="str">
             <v>RPRO-260306-1565</v>
           </cell>
@@ -14850,6 +15521,7 @@
           <cell r="A189" t="str">
             <v>S-2026-03-35</v>
           </cell>
+          <cell r="B189"/>
           <cell r="C189" t="str">
             <v>RPRO-260306-1566</v>
           </cell>
@@ -14918,6 +15590,7 @@
           <cell r="A190" t="str">
             <v>S-2026-03-36</v>
           </cell>
+          <cell r="B190"/>
           <cell r="C190" t="str">
             <v>RPRO-260307-0080</v>
           </cell>
@@ -14986,6 +15659,7 @@
           <cell r="A191" t="str">
             <v>S-2026-03-37</v>
           </cell>
+          <cell r="B191"/>
           <cell r="C191" t="str">
             <v>RPRO-260306-1736</v>
           </cell>
@@ -15054,6 +15728,7 @@
           <cell r="A192" t="str">
             <v>S-2026-03-38</v>
           </cell>
+          <cell r="B192"/>
           <cell r="C192" t="str">
             <v>RPRO-260306-1737</v>
           </cell>
@@ -15122,6 +15797,7 @@
           <cell r="A193" t="str">
             <v>S-2026-03-39</v>
           </cell>
+          <cell r="B193"/>
           <cell r="C193" t="str">
             <v>RPRO-260306-1738</v>
           </cell>
@@ -15190,6 +15866,7 @@
           <cell r="A194" t="str">
             <v>S-2026-03-40</v>
           </cell>
+          <cell r="B194"/>
           <cell r="C194" t="str">
             <v>RPRO-260306-1739</v>
           </cell>
@@ -15258,6 +15935,7 @@
           <cell r="A195" t="str">
             <v>S-2026-03-41</v>
           </cell>
+          <cell r="B195"/>
           <cell r="C195" t="str">
             <v>RPRO-260306-1740</v>
           </cell>
@@ -15326,6 +16004,7 @@
           <cell r="A196" t="str">
             <v>S-2026-03-42</v>
           </cell>
+          <cell r="B196"/>
           <cell r="C196" t="str">
             <v>RPRO-260307-0081</v>
           </cell>
@@ -15394,6 +16073,7 @@
           <cell r="A197" t="str">
             <v>S-2026-03-43</v>
           </cell>
+          <cell r="B197"/>
           <cell r="C197" t="str">
             <v>RPRO-260307-0082</v>
           </cell>
@@ -15462,6 +16142,7 @@
           <cell r="A198" t="str">
             <v>S-2026-03-44</v>
           </cell>
+          <cell r="B198"/>
           <cell r="C198" t="str">
             <v>RPRO-260307-0083</v>
           </cell>
@@ -15530,6 +16211,7 @@
           <cell r="A199" t="str">
             <v>S-2026-03-45</v>
           </cell>
+          <cell r="B199"/>
           <cell r="C199" t="str">
             <v>RPRO-260307-0084</v>
           </cell>
@@ -15598,6 +16280,7 @@
           <cell r="A200" t="str">
             <v>S-2026-03-46</v>
           </cell>
+          <cell r="B200"/>
           <cell r="C200" t="str">
             <v>RPRO-260307-0085</v>
           </cell>
@@ -15666,6 +16349,7 @@
           <cell r="A201" t="str">
             <v>S-2026-03-47</v>
           </cell>
+          <cell r="B201"/>
           <cell r="C201" t="str">
             <v>RPRO-260310-0362</v>
           </cell>
@@ -15805,6 +16489,7 @@
           <cell r="A203" t="str">
             <v>S-2026-03-49</v>
           </cell>
+          <cell r="B203"/>
           <cell r="C203" t="str">
             <v>RPRO-260310-0364</v>
           </cell>
@@ -15873,6 +16558,7 @@
           <cell r="A204" t="str">
             <v>S-2026-03-50</v>
           </cell>
+          <cell r="B204"/>
           <cell r="C204" t="str">
             <v>RPRO-260310-0365</v>
           </cell>
@@ -16012,6 +16698,7 @@
           <cell r="A206" t="str">
             <v>S-2026-03-52</v>
           </cell>
+          <cell r="B206"/>
           <cell r="C206" t="str">
             <v>RPRO-260310-0367</v>
           </cell>
@@ -16080,6 +16767,7 @@
           <cell r="A207" t="str">
             <v>S-2026-03-53</v>
           </cell>
+          <cell r="B207"/>
           <cell r="C207" t="str">
             <v>RPRO-260310-0368</v>
           </cell>
@@ -16148,6 +16836,7 @@
           <cell r="A208" t="str">
             <v>S-2026-03-54</v>
           </cell>
+          <cell r="B208"/>
           <cell r="C208" t="str">
             <v>RPRO-260310-0369</v>
           </cell>
@@ -16216,6 +16905,7 @@
           <cell r="A209" t="str">
             <v>S-2026-03-55</v>
           </cell>
+          <cell r="B209"/>
           <cell r="C209" t="str">
             <v>RPRO-260310-0370</v>
           </cell>
@@ -16284,6 +16974,7 @@
           <cell r="A210" t="str">
             <v>S-2026-03-56</v>
           </cell>
+          <cell r="B210"/>
           <cell r="C210" t="str">
             <v>RPRO-260310-0371</v>
           </cell>
@@ -16352,6 +17043,7 @@
           <cell r="A211" t="str">
             <v>S-2026-03-57</v>
           </cell>
+          <cell r="B211"/>
           <cell r="C211" t="str">
             <v>RPRO-260310-0372</v>
           </cell>
@@ -16420,6 +17112,7 @@
           <cell r="A212" t="str">
             <v>S-2026-03-58</v>
           </cell>
+          <cell r="B212"/>
           <cell r="C212" t="str">
             <v>RPRO-260310-0373</v>
           </cell>
@@ -16488,6 +17181,7 @@
           <cell r="A213" t="str">
             <v>S-2026-03-59</v>
           </cell>
+          <cell r="B213"/>
           <cell r="C213" t="str">
             <v>RPRO-260310-0374</v>
           </cell>
@@ -16556,6 +17250,7 @@
           <cell r="A214" t="str">
             <v>S-2026-03-60</v>
           </cell>
+          <cell r="B214"/>
           <cell r="C214" t="str">
             <v>RPRO-260310-0375</v>
           </cell>
@@ -16624,6 +17319,7 @@
           <cell r="A215" t="str">
             <v>S-2026-03-61</v>
           </cell>
+          <cell r="B215"/>
           <cell r="C215" t="str">
             <v>RPRO-260310-0376</v>
           </cell>
@@ -16695,6 +17391,7 @@
           <cell r="B216" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C216"/>
           <cell r="D216" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -16725,6 +17422,7 @@
           <cell r="M216" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N216"/>
           <cell r="O216" t="str">
             <v>Lab test</v>
           </cell>
@@ -16760,6 +17458,7 @@
           <cell r="B217" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C217"/>
           <cell r="D217" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -16790,6 +17489,7 @@
           <cell r="M217" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N217"/>
           <cell r="O217" t="str">
             <v>Lab test</v>
           </cell>
@@ -16822,6 +17522,7 @@
           <cell r="A218" t="str">
             <v>S-2026-03-64</v>
           </cell>
+          <cell r="B218"/>
           <cell r="C218" t="str">
             <v>RPRO-260313-0142</v>
           </cell>
@@ -16890,6 +17591,7 @@
           <cell r="A219" t="str">
             <v>S-2026-03-65</v>
           </cell>
+          <cell r="B219"/>
           <cell r="C219" t="str">
             <v>RPRO-260313-0143</v>
           </cell>
@@ -16958,6 +17660,7 @@
           <cell r="A220" t="str">
             <v>S-2026-03-66</v>
           </cell>
+          <cell r="B220"/>
           <cell r="C220" t="str">
             <v>RPRO-260313-0144</v>
           </cell>
@@ -17026,6 +17729,7 @@
           <cell r="A221" t="str">
             <v>S-2026-03-67</v>
           </cell>
+          <cell r="B221"/>
           <cell r="C221" t="str">
             <v>RPRO-260313-0145</v>
           </cell>
@@ -17094,6 +17798,7 @@
           <cell r="A222" t="str">
             <v>S-2026-03-68</v>
           </cell>
+          <cell r="B222"/>
           <cell r="C222" t="str">
             <v>RPRO-260313-0146</v>
           </cell>
@@ -17162,6 +17867,7 @@
           <cell r="A223" t="str">
             <v>S-2026-03-69</v>
           </cell>
+          <cell r="B223"/>
           <cell r="C223" t="str">
             <v>RPRO-260313-0147</v>
           </cell>
@@ -17230,6 +17936,7 @@
           <cell r="A224" t="str">
             <v>S-2026-03-70</v>
           </cell>
+          <cell r="B224"/>
           <cell r="C224" t="str">
             <v>RPRO-260313-0148</v>
           </cell>
@@ -17298,6 +18005,7 @@
           <cell r="A225" t="str">
             <v>S-2026-03-71</v>
           </cell>
+          <cell r="B225"/>
           <cell r="C225" t="str">
             <v>RPRO-260313-0149</v>
           </cell>
@@ -17366,6 +18074,7 @@
           <cell r="A226" t="str">
             <v>S-2026-03-72</v>
           </cell>
+          <cell r="B226"/>
           <cell r="C226" t="str">
             <v>RPRO-260313-0150</v>
           </cell>
@@ -17434,6 +18143,7 @@
           <cell r="A227" t="str">
             <v>S-2026-03-73</v>
           </cell>
+          <cell r="B227"/>
           <cell r="C227" t="str">
             <v>RPRO-260313-0151</v>
           </cell>
@@ -17502,6 +18212,7 @@
           <cell r="A228" t="str">
             <v>S-2026-03-74</v>
           </cell>
+          <cell r="B228"/>
           <cell r="C228" t="str">
             <v>RPRO-260313-0152</v>
           </cell>
@@ -17570,6 +18281,7 @@
           <cell r="A229" t="str">
             <v>S-2026-03-75</v>
           </cell>
+          <cell r="B229"/>
           <cell r="C229" t="str">
             <v>RPRO-260313-0318</v>
           </cell>
@@ -17638,6 +18350,7 @@
           <cell r="A230" t="str">
             <v>S-2026-03-76</v>
           </cell>
+          <cell r="B230"/>
           <cell r="C230" t="str">
             <v>RPRO-260313-0319</v>
           </cell>
@@ -17706,6 +18419,7 @@
           <cell r="A231" t="str">
             <v>S-2026-03-77</v>
           </cell>
+          <cell r="B231"/>
           <cell r="C231" t="str">
             <v>RPRO-260314-0198</v>
           </cell>
@@ -17774,6 +18488,7 @@
           <cell r="A232" t="str">
             <v>S-2026-03-78</v>
           </cell>
+          <cell r="B232"/>
           <cell r="C232" t="str">
             <v>RPRO-260314-0199</v>
           </cell>
@@ -17842,6 +18557,7 @@
           <cell r="A233" t="str">
             <v>S-2026-03-79</v>
           </cell>
+          <cell r="B233"/>
           <cell r="C233" t="str">
             <v>RPRO-260317-0628</v>
           </cell>
@@ -17910,6 +18626,7 @@
           <cell r="A234" t="str">
             <v>S-2026-03-80</v>
           </cell>
+          <cell r="B234"/>
           <cell r="C234" t="str">
             <v>RPRO-260317-0629</v>
           </cell>
@@ -17978,6 +18695,7 @@
           <cell r="A235" t="str">
             <v>S-2026-03-81</v>
           </cell>
+          <cell r="B235"/>
           <cell r="C235" t="str">
             <v>RPRO-260317-0630</v>
           </cell>
@@ -18046,6 +18764,7 @@
           <cell r="A236" t="str">
             <v>S-2026-03-82</v>
           </cell>
+          <cell r="B236"/>
           <cell r="C236" t="str">
             <v>RPRO-260317-0631</v>
           </cell>
@@ -18114,6 +18833,7 @@
           <cell r="A237" t="str">
             <v>S-2026-03-83</v>
           </cell>
+          <cell r="B237"/>
           <cell r="C237" t="str">
             <v>RPRO-260317-0632</v>
           </cell>
@@ -18182,6 +18902,7 @@
           <cell r="A238" t="str">
             <v>S-2026-03-84</v>
           </cell>
+          <cell r="B238"/>
           <cell r="C238" t="str">
             <v>RPRO-260317-0633</v>
           </cell>
@@ -18250,6 +18971,7 @@
           <cell r="A239" t="str">
             <v>S-2026-03-85</v>
           </cell>
+          <cell r="B239"/>
           <cell r="C239" t="str">
             <v>RPRO-260317-0634</v>
           </cell>
@@ -18318,6 +19040,7 @@
           <cell r="A240" t="str">
             <v>S-2026-03-86</v>
           </cell>
+          <cell r="B240"/>
           <cell r="C240" t="str">
             <v>RPRO-260317-0635</v>
           </cell>
@@ -18386,6 +19109,7 @@
           <cell r="A241" t="str">
             <v>S-2026-03-87</v>
           </cell>
+          <cell r="B241"/>
           <cell r="C241" t="str">
             <v>RPRO-260317-0636</v>
           </cell>
@@ -18454,6 +19178,7 @@
           <cell r="A242" t="str">
             <v>L-2026-03-88</v>
           </cell>
+          <cell r="B242"/>
           <cell r="C242" t="str">
             <v>RPRO-260317-0637</v>
           </cell>
@@ -18487,6 +19212,7 @@
           <cell r="M242" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N242"/>
           <cell r="O242" t="str">
             <v>Lab test</v>
           </cell>
@@ -18555,6 +19281,7 @@
           <cell r="M243" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N243"/>
           <cell r="O243" t="str">
             <v>Lab test</v>
           </cell>
@@ -18587,6 +19314,7 @@
           <cell r="A244" t="str">
             <v>S-2026-03-90</v>
           </cell>
+          <cell r="B244"/>
           <cell r="C244" t="str">
             <v>RPRO-260317-0639</v>
           </cell>
@@ -18655,6 +19383,7 @@
           <cell r="A245" t="str">
             <v>S-2026-03-91</v>
           </cell>
+          <cell r="B245"/>
           <cell r="C245" t="str">
             <v>RPRO-260317-0640</v>
           </cell>
@@ -18723,6 +19452,7 @@
           <cell r="A246" t="str">
             <v>S-2026-03-92</v>
           </cell>
+          <cell r="B246"/>
           <cell r="C246" t="str">
             <v>RPRO-260317-0641</v>
           </cell>
@@ -18791,6 +19521,7 @@
           <cell r="A247" t="str">
             <v>L-2026-03-93</v>
           </cell>
+          <cell r="B247"/>
           <cell r="C247" t="str">
             <v>RPRO-260318-0477</v>
           </cell>
@@ -18824,6 +19555,7 @@
           <cell r="M247" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N247"/>
           <cell r="O247" t="str">
             <v>Lab test</v>
           </cell>
@@ -18856,6 +19588,7 @@
           <cell r="A248" t="str">
             <v>L-2026-03-94</v>
           </cell>
+          <cell r="B248"/>
           <cell r="C248" t="str">
             <v>RPRO-260318-0478</v>
           </cell>
@@ -18889,6 +19622,7 @@
           <cell r="M248" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N248"/>
           <cell r="O248" t="str">
             <v>Lab test</v>
           </cell>
@@ -18992,6 +19726,7 @@
           <cell r="A250" t="str">
             <v>S-2026-03-96</v>
           </cell>
+          <cell r="B250"/>
           <cell r="C250" t="str">
             <v>RPRO-260318-0482</v>
           </cell>
@@ -19060,6 +19795,7 @@
           <cell r="A251" t="str">
             <v>S-2026-03-97</v>
           </cell>
+          <cell r="B251"/>
           <cell r="C251" t="str">
             <v>RPRO-260324-0278</v>
           </cell>
@@ -19128,6 +19864,7 @@
           <cell r="A252" t="str">
             <v>S-2026-03-98</v>
           </cell>
+          <cell r="B252"/>
           <cell r="C252" t="str">
             <v>RPRO-260324-0279</v>
           </cell>
@@ -19267,6 +20004,7 @@
           <cell r="A254" t="str">
             <v>S-2026-03-100</v>
           </cell>
+          <cell r="B254"/>
           <cell r="C254" t="str">
             <v>RPRO-260324-0281</v>
           </cell>
@@ -19335,6 +20073,7 @@
           <cell r="A255" t="str">
             <v>S-2026-03-101</v>
           </cell>
+          <cell r="B255"/>
           <cell r="C255" t="str">
             <v>RPRO-260324-0282</v>
           </cell>
@@ -19403,6 +20142,7 @@
           <cell r="A256" t="str">
             <v>S-2026-03-102</v>
           </cell>
+          <cell r="B256"/>
           <cell r="C256" t="str">
             <v>RPRO-260324-0531</v>
           </cell>
@@ -19471,6 +20211,7 @@
           <cell r="A257" t="str">
             <v>S-2026-03-103</v>
           </cell>
+          <cell r="B257"/>
           <cell r="C257" t="str">
             <v>RPRO-260324-0283</v>
           </cell>
@@ -19539,6 +20280,7 @@
           <cell r="A258" t="str">
             <v>S-2026-03-104</v>
           </cell>
+          <cell r="B258"/>
           <cell r="C258" t="str">
             <v>RPRO-260324-0284</v>
           </cell>
@@ -19607,6 +20349,7 @@
           <cell r="A259" t="str">
             <v>L-2026-03-105</v>
           </cell>
+          <cell r="B259"/>
           <cell r="C259" t="str">
             <v>RPRO-260321-0027</v>
           </cell>
@@ -19640,6 +20383,7 @@
           <cell r="M259" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N259"/>
           <cell r="O259" t="str">
             <v>Lab test</v>
           </cell>
@@ -19672,6 +20416,7 @@
           <cell r="A260" t="str">
             <v>L-2026-03-106</v>
           </cell>
+          <cell r="B260"/>
           <cell r="C260" t="str">
             <v>RPRO-260321-0028</v>
           </cell>
@@ -19705,6 +20450,7 @@
           <cell r="M260" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N260"/>
           <cell r="O260" t="str">
             <v>Lab test</v>
           </cell>
@@ -19737,6 +20483,7 @@
           <cell r="A261" t="str">
             <v>S-2026-03-107</v>
           </cell>
+          <cell r="B261"/>
           <cell r="C261" t="str">
             <v>RPRO-260321-0029</v>
           </cell>
@@ -19805,6 +20552,7 @@
           <cell r="A262" t="str">
             <v>S-2026-03-108</v>
           </cell>
+          <cell r="B262"/>
           <cell r="C262" t="str">
             <v>RPRO-260324-0285</v>
           </cell>
@@ -19873,6 +20621,7 @@
           <cell r="A263" t="str">
             <v>L-2026-03-109</v>
           </cell>
+          <cell r="B263"/>
           <cell r="C263" t="str">
             <v>RPRO-260324-0286</v>
           </cell>
@@ -19900,9 +20649,11 @@
           <cell r="K263">
             <v>0</v>
           </cell>
+          <cell r="L263"/>
           <cell r="M263" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N263"/>
           <cell r="O263" t="str">
             <v>Lab test</v>
           </cell>
@@ -19935,6 +20686,7 @@
           <cell r="A264" t="str">
             <v>S-2026-03-110</v>
           </cell>
+          <cell r="B264"/>
           <cell r="C264" t="str">
             <v>RPRO-260324-0287</v>
           </cell>
@@ -20003,6 +20755,7 @@
           <cell r="A265" t="str">
             <v>S-2026-03-111</v>
           </cell>
+          <cell r="B265"/>
           <cell r="C265" t="str">
             <v>RPRO-260324-0288</v>
           </cell>
@@ -20071,6 +20824,7 @@
           <cell r="A266" t="str">
             <v>S-2026-03-112</v>
           </cell>
+          <cell r="B266"/>
           <cell r="C266" t="str">
             <v>RPRO-260324-0289</v>
           </cell>
@@ -20139,6 +20893,7 @@
           <cell r="A267" t="str">
             <v>S-2026-03-113</v>
           </cell>
+          <cell r="B267"/>
           <cell r="C267" t="str">
             <v>RPRO-260324-0532</v>
           </cell>
@@ -20207,6 +20962,7 @@
           <cell r="A268" t="str">
             <v>S-2026-03-114</v>
           </cell>
+          <cell r="B268"/>
           <cell r="C268" t="str">
             <v>RPRO-260324-0533</v>
           </cell>
@@ -20275,6 +21031,7 @@
           <cell r="A269" t="str">
             <v>S-2026-03-115</v>
           </cell>
+          <cell r="B269"/>
           <cell r="C269" t="str">
             <v>RPRO-260324-0534</v>
           </cell>
@@ -20343,6 +21100,7 @@
           <cell r="A270" t="str">
             <v>S-2026-03-116</v>
           </cell>
+          <cell r="B270"/>
           <cell r="C270" t="str">
             <v>RPRO-260325-0407</v>
           </cell>
@@ -20411,6 +21169,7 @@
           <cell r="A271" t="str">
             <v>S-2026-03-117</v>
           </cell>
+          <cell r="B271"/>
           <cell r="C271" t="str">
             <v>RPRO-260325-0408</v>
           </cell>
@@ -20479,6 +21238,7 @@
           <cell r="A272" t="str">
             <v>S-2026-03-118</v>
           </cell>
+          <cell r="B272"/>
           <cell r="C272" t="str">
             <v>RPRO-260325-0409</v>
           </cell>
@@ -20547,6 +21307,7 @@
           <cell r="A273" t="str">
             <v>S-2026-03-119</v>
           </cell>
+          <cell r="B273"/>
           <cell r="C273" t="str">
             <v>RPRO-260325-0410</v>
           </cell>
@@ -20615,6 +21376,7 @@
           <cell r="A274" t="str">
             <v>S-2026-03-120</v>
           </cell>
+          <cell r="B274"/>
           <cell r="C274" t="str">
             <v>RPRO-260325-0411</v>
           </cell>
@@ -20683,6 +21445,7 @@
           <cell r="A275" t="str">
             <v>S-2026-03-121</v>
           </cell>
+          <cell r="B275"/>
           <cell r="C275" t="str">
             <v>RPRO-260325-0412</v>
           </cell>
@@ -20751,6 +21514,7 @@
           <cell r="A276" t="str">
             <v>S-2026-03-122</v>
           </cell>
+          <cell r="B276"/>
           <cell r="C276" t="str">
             <v>RPRO-260325-0413</v>
           </cell>
@@ -20819,6 +21583,7 @@
           <cell r="A277" t="str">
             <v>S-2026-03-123</v>
           </cell>
+          <cell r="B277"/>
           <cell r="C277" t="str">
             <v>RPRO-260325-0414</v>
           </cell>
@@ -20887,6 +21652,7 @@
           <cell r="A278" t="str">
             <v>S-2026-03-124</v>
           </cell>
+          <cell r="B278"/>
           <cell r="C278" t="str">
             <v>RPRO-260325-0415</v>
           </cell>
@@ -21016,7 +21782,7 @@
             <v>4</v>
           </cell>
           <cell r="V279">
-            <v>2.7779999999999999E-2</v>
+            <v>2.8570000000000002E-2</v>
           </cell>
           <cell r="W279">
             <v>2</v>
@@ -21026,6 +21792,7 @@
           <cell r="A280" t="str">
             <v>S-2026-03-126</v>
           </cell>
+          <cell r="B280"/>
           <cell r="C280" t="str">
             <v>RPRO-260325-0417</v>
           </cell>
@@ -21094,6 +21861,7 @@
           <cell r="A281" t="str">
             <v>S-2026-03-127</v>
           </cell>
+          <cell r="B281"/>
           <cell r="C281" t="str">
             <v>RPRO-260325-0418</v>
           </cell>
@@ -21162,6 +21930,7 @@
           <cell r="A282" t="str">
             <v>S-2026-03-128</v>
           </cell>
+          <cell r="B282"/>
           <cell r="C282" t="str">
             <v>RPRO-260325-0419</v>
           </cell>
@@ -21230,6 +21999,7 @@
           <cell r="A283" t="str">
             <v>S-2026-03-129</v>
           </cell>
+          <cell r="B283"/>
           <cell r="C283" t="str">
             <v>RPRO-260325-0421</v>
           </cell>
@@ -21298,6 +22068,7 @@
           <cell r="A284" t="str">
             <v>S-2026-03-130</v>
           </cell>
+          <cell r="B284"/>
           <cell r="C284" t="str">
             <v>RPRO-260327-0930</v>
           </cell>
@@ -21375,9 +22146,7 @@
           <cell r="D285" t="str">
             <v>PUR2603250004S</v>
           </cell>
-          <cell r="E285" t="str">
-            <v>BDB-000316</v>
-          </cell>
+          <cell r="E285"/>
           <cell r="F285" t="str">
             <v>PVN-004358</v>
           </cell>
@@ -21426,8 +22195,8 @@
           <cell r="U285">
             <v>8</v>
           </cell>
-          <cell r="V285">
-            <v>5.8819999999999997E-2</v>
+          <cell r="V285" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="W285">
             <v>5</v>
@@ -21508,6 +22277,7 @@
           <cell r="A287" t="str">
             <v>S-2026-03-133</v>
           </cell>
+          <cell r="B287"/>
           <cell r="C287" t="str">
             <v>RPRO-260327-0933</v>
           </cell>
@@ -21576,6 +22346,7 @@
           <cell r="A288" t="str">
             <v>S-2026-03-134</v>
           </cell>
+          <cell r="B288"/>
           <cell r="C288" t="str">
             <v>RPRO-260327-0934</v>
           </cell>
@@ -21786,6 +22557,7 @@
           <cell r="A291" t="str">
             <v>S-2026-03-137</v>
           </cell>
+          <cell r="B291"/>
           <cell r="C291" t="str">
             <v>RPRO-260327-0937</v>
           </cell>
@@ -21925,6 +22697,7 @@
           <cell r="A293" t="str">
             <v>S-2026-03-139</v>
           </cell>
+          <cell r="B293"/>
           <cell r="C293" t="str">
             <v>RPRO-260327-0939</v>
           </cell>
@@ -22002,9 +22775,7 @@
           <cell r="D294" t="str">
             <v xml:space="preserve">PUR2603270001S  </v>
           </cell>
-          <cell r="E294" t="str">
-            <v>BDB-000316</v>
-          </cell>
+          <cell r="E294"/>
           <cell r="F294" t="str">
             <v>PVN-004358</v>
           </cell>
@@ -22053,8 +22824,8 @@
           <cell r="U294">
             <v>8</v>
           </cell>
-          <cell r="V294">
-            <v>5.8819999999999997E-2</v>
+          <cell r="V294" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="W294">
             <v>6</v>
@@ -22064,15 +22835,14 @@
           <cell r="A295" t="str">
             <v>S-2026-03-141</v>
           </cell>
+          <cell r="B295"/>
           <cell r="C295" t="str">
             <v>RPRO-260327-0941</v>
           </cell>
           <cell r="D295" t="str">
             <v xml:space="preserve">PUR2603270001S  </v>
           </cell>
-          <cell r="E295" t="str">
-            <v>BDB-000081</v>
-          </cell>
+          <cell r="E295"/>
           <cell r="F295" t="str">
             <v>PVN-004361</v>
           </cell>
@@ -22132,6 +22902,7 @@
           <cell r="A296" t="str">
             <v>S-2026-03-142</v>
           </cell>
+          <cell r="B296"/>
           <cell r="C296" t="str">
             <v>RPRO-260401-0245</v>
           </cell>
@@ -22209,9 +22980,7 @@
           <cell r="D297" t="str">
             <v>PUR-202603300001S</v>
           </cell>
-          <cell r="E297" t="str">
-            <v>BDB-000275</v>
-          </cell>
+          <cell r="E297"/>
           <cell r="F297" t="str">
             <v>PVN-004362</v>
           </cell>
@@ -22260,8 +23029,8 @@
           <cell r="U297">
             <v>2</v>
           </cell>
-          <cell r="V297">
-            <v>1.4290000000000001E-2</v>
+          <cell r="V297" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="W297">
             <v>1</v>
@@ -22271,6 +23040,7 @@
           <cell r="A298" t="str">
             <v>S-2026-03-144</v>
           </cell>
+          <cell r="B298"/>
           <cell r="C298" t="str">
             <v>RPRO-260401-0247</v>
           </cell>
@@ -22339,15 +23109,14 @@
           <cell r="A299" t="str">
             <v>S-2026-03-145</v>
           </cell>
+          <cell r="B299"/>
           <cell r="C299" t="str">
             <v>RPRO-260401-0248</v>
           </cell>
           <cell r="D299" t="str">
             <v>PUR-202603300001S</v>
           </cell>
-          <cell r="E299" t="str">
-            <v>BDB-000367</v>
-          </cell>
+          <cell r="E299"/>
           <cell r="F299" t="str">
             <v>PVN-004370</v>
           </cell>
@@ -22407,6 +23176,7 @@
           <cell r="A300" t="str">
             <v>S-2026-03-146</v>
           </cell>
+          <cell r="B300"/>
           <cell r="C300" t="str">
             <v>RPRO-260401-0249</v>
           </cell>
@@ -22475,6 +23245,7 @@
           <cell r="A301" t="str">
             <v>S-2026-04-01</v>
           </cell>
+          <cell r="B301"/>
           <cell r="C301" t="str">
             <v>RPRO-260401-0250</v>
           </cell>
@@ -22543,15 +23314,14 @@
           <cell r="A302" t="str">
             <v>S-2026-04-02</v>
           </cell>
+          <cell r="B302"/>
           <cell r="C302" t="str">
             <v>RPRO-260401-0251</v>
           </cell>
           <cell r="D302" t="str">
             <v>PUR260040100001S</v>
           </cell>
-          <cell r="E302" t="str">
-            <v>BDB-000382</v>
-          </cell>
+          <cell r="E302"/>
           <cell r="F302" t="str">
             <v>PVN-004363</v>
           </cell>
@@ -22611,6 +23381,7 @@
           <cell r="A303" t="str">
             <v>S-2026-04-03</v>
           </cell>
+          <cell r="B303"/>
           <cell r="C303" t="str">
             <v>RPRO-260402-0737</v>
           </cell>
@@ -22679,6 +23450,7 @@
           <cell r="A304" t="str">
             <v>S-2026-04-04</v>
           </cell>
+          <cell r="B304"/>
           <cell r="C304" t="str">
             <v>RPRO-260402-0738</v>
           </cell>
@@ -22747,6 +23519,7 @@
           <cell r="A305" t="str">
             <v>S-2026-04-05</v>
           </cell>
+          <cell r="B305"/>
           <cell r="C305" t="str">
             <v>RPRO-260403-0489</v>
           </cell>
@@ -22815,6 +23588,7 @@
           <cell r="A306" t="str">
             <v>S-2026-04-06</v>
           </cell>
+          <cell r="B306"/>
           <cell r="C306" t="str">
             <v>RPRO-260403-0490</v>
           </cell>
@@ -22883,6 +23657,7 @@
           <cell r="A307" t="str">
             <v>S-2026-04-07</v>
           </cell>
+          <cell r="B307"/>
           <cell r="C307" t="str">
             <v>RPRO-260403-0491</v>
           </cell>
@@ -22951,6 +23726,7 @@
           <cell r="A308" t="str">
             <v>S-2026-04-08</v>
           </cell>
+          <cell r="B308"/>
           <cell r="C308" t="str">
             <v>RPRO-260403-0492</v>
           </cell>
@@ -23019,15 +23795,14 @@
           <cell r="A309" t="str">
             <v>S-2026-04-09</v>
           </cell>
+          <cell r="B309"/>
           <cell r="C309" t="str">
             <v>RPRO-260406-1201</v>
           </cell>
           <cell r="D309" t="str">
             <v>PUR2604030002S</v>
           </cell>
-          <cell r="E309" t="str">
-            <v>BDB-000384</v>
-          </cell>
+          <cell r="E309"/>
           <cell r="F309" t="str">
             <v>PVN-004377</v>
           </cell>
@@ -23087,15 +23862,14 @@
           <cell r="A310" t="str">
             <v>S-2026-04-10</v>
           </cell>
+          <cell r="B310"/>
           <cell r="C310" t="str">
             <v>RPRO-260406-1202</v>
           </cell>
           <cell r="D310" t="str">
             <v>PUR2604030002S</v>
           </cell>
-          <cell r="E310" t="str">
-            <v>BDB-000384</v>
-          </cell>
+          <cell r="E310"/>
           <cell r="F310" t="str">
             <v>PVN-004378</v>
           </cell>
@@ -23155,6 +23929,7 @@
           <cell r="A311" t="str">
             <v>S-2026-04-11</v>
           </cell>
+          <cell r="B311"/>
           <cell r="C311" t="str">
             <v>RPRO-260406-1203</v>
           </cell>
@@ -23223,6 +23998,7 @@
           <cell r="A312" t="str">
             <v>S-2026-04-12</v>
           </cell>
+          <cell r="B312"/>
           <cell r="C312" t="str">
             <v>RPRO-260407-0417</v>
           </cell>
@@ -23291,6 +24067,7 @@
           <cell r="A313" t="str">
             <v>S-2026-04-13</v>
           </cell>
+          <cell r="B313"/>
           <cell r="C313" t="str">
             <v>RPRO-260407-0418</v>
           </cell>
@@ -23359,6 +24136,7 @@
           <cell r="A314" t="str">
             <v>S-2026-04-14</v>
           </cell>
+          <cell r="B314"/>
           <cell r="C314" t="str">
             <v>RPRO-260407-0419</v>
           </cell>
@@ -23427,6 +24205,7 @@
           <cell r="A315" t="str">
             <v>S-2026-04-15</v>
           </cell>
+          <cell r="B315"/>
           <cell r="C315" t="str">
             <v>RPRO-260407-0420</v>
           </cell>
@@ -23495,15 +24274,14 @@
           <cell r="A316" t="str">
             <v>S-2026-04-16</v>
           </cell>
+          <cell r="B316"/>
           <cell r="C316" t="str">
             <v>RPRO-260409-0346</v>
           </cell>
           <cell r="D316" t="str">
             <v>PUR2604080002S</v>
           </cell>
-          <cell r="E316" t="str">
-            <v>BDB-000179</v>
-          </cell>
+          <cell r="E316"/>
           <cell r="F316" t="str">
             <v>PVN-004383</v>
           </cell>
@@ -23563,6 +24341,7 @@
           <cell r="A317" t="str">
             <v>S-2026-04-17</v>
           </cell>
+          <cell r="B317"/>
           <cell r="C317" t="str">
             <v>RPRO-260409-0347</v>
           </cell>
@@ -23631,6 +24410,7 @@
           <cell r="A318" t="str">
             <v>S-2026-04-18</v>
           </cell>
+          <cell r="B318"/>
           <cell r="C318" t="str">
             <v>RPRO-260409-0348</v>
           </cell>
@@ -23699,6 +24479,7 @@
           <cell r="A319" t="str">
             <v>S-2026-04-19</v>
           </cell>
+          <cell r="B319"/>
           <cell r="C319" t="str">
             <v>RPRO-260409-0349</v>
           </cell>
@@ -23767,6 +24548,7 @@
           <cell r="A320" t="str">
             <v>S-2026-04-20</v>
           </cell>
+          <cell r="B320"/>
           <cell r="C320" t="str">
             <v>RPRO-260409-0350</v>
           </cell>
@@ -23835,6 +24617,7 @@
           <cell r="A321" t="str">
             <v>L-2026-04-21</v>
           </cell>
+          <cell r="B321"/>
           <cell r="C321" t="str">
             <v>RPRO-260410-0280</v>
           </cell>
@@ -23868,6 +24651,7 @@
           <cell r="M321" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N321"/>
           <cell r="O321" t="str">
             <v>Lab test</v>
           </cell>
@@ -23900,6 +24684,7 @@
           <cell r="A322" t="str">
             <v>L-2026-04-22</v>
           </cell>
+          <cell r="B322"/>
           <cell r="C322" t="str">
             <v>RPRO-260410-0281</v>
           </cell>
@@ -23933,6 +24718,7 @@
           <cell r="M322" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N322"/>
           <cell r="O322" t="str">
             <v>Lab test</v>
           </cell>
@@ -23965,6 +24751,7 @@
           <cell r="A323" t="str">
             <v>S-2026-04-23</v>
           </cell>
+          <cell r="B323"/>
           <cell r="C323" t="str">
             <v>RPRO-260410-0282</v>
           </cell>
@@ -24033,6 +24820,7 @@
           <cell r="A324" t="str">
             <v>S-2026-04-24</v>
           </cell>
+          <cell r="B324"/>
           <cell r="C324" t="str">
             <v>RPRO-260410-0283</v>
           </cell>
@@ -24101,15 +24889,14 @@
           <cell r="A325" t="str">
             <v>S-2026-04-25</v>
           </cell>
+          <cell r="B325"/>
           <cell r="C325" t="str">
             <v>RPRO-260410-0284</v>
           </cell>
           <cell r="D325" t="str">
             <v>PUR2600401000002S</v>
           </cell>
-          <cell r="E325" t="str">
-            <v>BDB-000387</v>
-          </cell>
+          <cell r="E325"/>
           <cell r="F325" t="str">
             <v>PVN-004385</v>
           </cell>
@@ -24169,6 +24956,7 @@
           <cell r="A326" t="str">
             <v>S-2026-04-26</v>
           </cell>
+          <cell r="B326"/>
           <cell r="C326" t="str">
             <v>RPRO-260410-0285</v>
           </cell>
@@ -24237,6 +25025,7 @@
           <cell r="A327" t="str">
             <v>S-2026-04-27</v>
           </cell>
+          <cell r="B327"/>
           <cell r="C327" t="str">
             <v>RPRO-260410-0286</v>
           </cell>
@@ -24305,6 +25094,7 @@
           <cell r="A328" t="str">
             <v>S-2026-04-28</v>
           </cell>
+          <cell r="B328"/>
           <cell r="C328" t="str">
             <v>RPRO-260410-0287</v>
           </cell>
@@ -24382,9 +25172,7 @@
           <cell r="D329" t="str">
             <v xml:space="preserve">PUR2604100004S   </v>
           </cell>
-          <cell r="E329" t="str">
-            <v>BDB-000324</v>
-          </cell>
+          <cell r="E329"/>
           <cell r="F329" t="str">
             <v>PVN-004386</v>
           </cell>
@@ -24433,8 +25221,8 @@
           <cell r="U329">
             <v>8</v>
           </cell>
-          <cell r="V329">
-            <v>5.5559999999999998E-2</v>
+          <cell r="V329" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="W329">
             <v>1</v>
@@ -24444,15 +25232,14 @@
           <cell r="A330" t="str">
             <v>S-2026-04-30</v>
           </cell>
+          <cell r="B330"/>
           <cell r="C330" t="str">
             <v>RPRO-260414-0202</v>
           </cell>
           <cell r="D330" t="str">
             <v>PUR2600401000005S</v>
           </cell>
-          <cell r="E330" t="str">
-            <v>BDB-000388</v>
-          </cell>
+          <cell r="E330"/>
           <cell r="F330" t="str">
             <v>PVN-004387</v>
           </cell>
@@ -24512,6 +25299,7 @@
           <cell r="A331" t="str">
             <v>S-2026-04-31</v>
           </cell>
+          <cell r="B331"/>
           <cell r="C331" t="str">
             <v>RPRO-260414-0203</v>
           </cell>
@@ -24580,15 +25368,14 @@
           <cell r="A332" t="str">
             <v>S-2026-04-32</v>
           </cell>
+          <cell r="B332"/>
           <cell r="C332" t="str">
             <v>RPRO-260414-0204</v>
           </cell>
           <cell r="D332" t="str">
             <v>PUR2604130002S</v>
           </cell>
-          <cell r="E332" t="str">
-            <v>BDB-000083</v>
-          </cell>
+          <cell r="E332"/>
           <cell r="F332" t="str">
             <v>PVN-004390</v>
           </cell>
@@ -24648,6 +25435,7 @@
           <cell r="A333" t="str">
             <v>S-2026-04-33</v>
           </cell>
+          <cell r="B333"/>
           <cell r="C333" t="str">
             <v>RPRO-260414-0205</v>
           </cell>
@@ -24716,6 +25504,7 @@
           <cell r="A334" t="str">
             <v>S-2026-04-34</v>
           </cell>
+          <cell r="B334"/>
           <cell r="C334" t="str">
             <v>RPRO-260414-0206</v>
           </cell>
@@ -24784,6 +25573,7 @@
           <cell r="A335" t="str">
             <v>S-2026-04-35</v>
           </cell>
+          <cell r="B335"/>
           <cell r="C335" t="str">
             <v>RPRO-260414-0207</v>
           </cell>
@@ -24852,6 +25642,7 @@
           <cell r="A336" t="str">
             <v>S-2026-04-36</v>
           </cell>
+          <cell r="B336"/>
           <cell r="C336" t="str">
             <v>RPRO-260414-0208</v>
           </cell>
@@ -24920,6 +25711,7 @@
           <cell r="A337" t="str">
             <v>S-2026-04-37</v>
           </cell>
+          <cell r="B337"/>
           <cell r="C337" t="str">
             <v>RPRO-260414-0209</v>
           </cell>
@@ -24988,6 +25780,7 @@
           <cell r="A338" t="str">
             <v>S-2026-04-38</v>
           </cell>
+          <cell r="B338"/>
           <cell r="C338" t="str">
             <v>RPRO-260414-0210</v>
           </cell>
@@ -25056,6 +25849,7 @@
           <cell r="A339" t="str">
             <v>S-2026-04-39</v>
           </cell>
+          <cell r="B339"/>
           <cell r="C339" t="str">
             <v>RPRO-260414-0211</v>
           </cell>
@@ -25124,15 +25918,14 @@
           <cell r="A340" t="str">
             <v>S-2026-04-40</v>
           </cell>
+          <cell r="B340"/>
           <cell r="C340" t="str">
             <v>RPRO-260414-0212</v>
           </cell>
           <cell r="D340" t="str">
             <v>PUR2604130005S</v>
           </cell>
-          <cell r="E340" t="str">
-            <v>BDB-000352</v>
-          </cell>
+          <cell r="E340"/>
           <cell r="F340" t="str">
             <v>PVN-004372</v>
           </cell>
@@ -25228,6 +26021,7 @@
           <cell r="M341" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N341"/>
           <cell r="O341" t="str">
             <v>Lab test</v>
           </cell>
@@ -25296,6 +26090,7 @@
           <cell r="M342" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N342"/>
           <cell r="O342" t="str">
             <v>Lab test</v>
           </cell>
@@ -25328,6 +26123,7 @@
           <cell r="A343" t="str">
             <v>S-2026-04-43</v>
           </cell>
+          <cell r="B343"/>
           <cell r="C343" t="str">
             <v>RPRO-260417-0243</v>
           </cell>
@@ -25396,15 +26192,14 @@
           <cell r="A344" t="str">
             <v>S-2026-04-44</v>
           </cell>
+          <cell r="B344"/>
           <cell r="C344" t="str">
             <v>RPRO-260417-0244</v>
           </cell>
           <cell r="D344" t="str">
             <v>PUR2600401700002S</v>
           </cell>
-          <cell r="E344" t="str">
-            <v>BDB-000224</v>
-          </cell>
+          <cell r="E344"/>
           <cell r="F344" t="str">
             <v>PVN-004393</v>
           </cell>
@@ -25464,6 +26259,7 @@
           <cell r="A345" t="str">
             <v>S-2026-04-45</v>
           </cell>
+          <cell r="B345"/>
           <cell r="C345" t="str">
             <v>RPRO-260417-0245</v>
           </cell>
@@ -25532,6 +26328,7 @@
           <cell r="A346" t="str">
             <v>S-2026-04-46</v>
           </cell>
+          <cell r="B346"/>
           <cell r="C346" t="str">
             <v>RPRO-260417-0246</v>
           </cell>
@@ -25600,6 +26397,7 @@
           <cell r="A347" t="str">
             <v>S-2026-04-47</v>
           </cell>
+          <cell r="B347"/>
           <cell r="C347" t="str">
             <v>RPRO-260417-0247</v>
           </cell>
@@ -25668,6 +26466,7 @@
           <cell r="A348" t="str">
             <v>S-2026-04-48</v>
           </cell>
+          <cell r="B348"/>
           <cell r="C348" t="str">
             <v>RPRO-260421-0623</v>
           </cell>
@@ -25736,6 +26535,7 @@
           <cell r="A349" t="str">
             <v>S-2026-04-49</v>
           </cell>
+          <cell r="B349"/>
           <cell r="C349" t="str">
             <v>RPRO-260421-0624</v>
           </cell>
@@ -25804,6 +26604,7 @@
           <cell r="A350" t="str">
             <v>S-2026-04-50</v>
           </cell>
+          <cell r="B350"/>
           <cell r="C350" t="str">
             <v>RPRO-260421-0625</v>
           </cell>
@@ -25872,15 +26673,14 @@
           <cell r="A351" t="str">
             <v>S-2026-04-51</v>
           </cell>
+          <cell r="B351"/>
           <cell r="C351" t="str">
             <v>RPRO-260421-0626</v>
           </cell>
           <cell r="D351" t="str">
             <v xml:space="preserve">PUR2604200001S   </v>
           </cell>
-          <cell r="E351" t="str">
-            <v>BDB-000081</v>
-          </cell>
+          <cell r="E351"/>
           <cell r="F351" t="str">
             <v>PVN-004361</v>
           </cell>
@@ -25940,6 +26740,7 @@
           <cell r="A352" t="str">
             <v>S-2026-04-52</v>
           </cell>
+          <cell r="B352"/>
           <cell r="C352" t="str">
             <v>RPRO-260421-0627</v>
           </cell>
@@ -26008,6 +26809,7 @@
           <cell r="A353" t="str">
             <v>S-2026-04-53</v>
           </cell>
+          <cell r="B353"/>
           <cell r="C353" t="str">
             <v>RPRO-260421-0628</v>
           </cell>
@@ -26076,6 +26878,7 @@
           <cell r="A354" t="str">
             <v>S-2026-04-54</v>
           </cell>
+          <cell r="B354"/>
           <cell r="C354" t="str">
             <v>RPRO-260421-0629</v>
           </cell>
@@ -26144,6 +26947,7 @@
           <cell r="A355" t="str">
             <v>S-2026-04-55</v>
           </cell>
+          <cell r="B355"/>
           <cell r="C355" t="str">
             <v>RPRO-260421-0630</v>
           </cell>
@@ -26212,6 +27016,7 @@
           <cell r="A356" t="str">
             <v>S-2026-04-56</v>
           </cell>
+          <cell r="B356"/>
           <cell r="C356" t="str">
             <v>RPRO-260421-0631</v>
           </cell>
@@ -26280,6 +27085,7 @@
           <cell r="A357" t="str">
             <v>S-2026-04-57</v>
           </cell>
+          <cell r="B357"/>
           <cell r="C357" t="str">
             <v>RPRO-260421-0632</v>
           </cell>
@@ -26348,6 +27154,7 @@
           <cell r="A358" t="str">
             <v>S-2026-04-58</v>
           </cell>
+          <cell r="B358"/>
           <cell r="C358" t="str">
             <v>RPRO-260421-0633</v>
           </cell>
@@ -26416,6 +27223,7 @@
           <cell r="A359" t="str">
             <v>S-2026-04-59</v>
           </cell>
+          <cell r="B359"/>
           <cell r="C359" t="str">
             <v>RPRO-260422-0268</v>
           </cell>
@@ -26484,6 +27292,7 @@
           <cell r="A360" t="str">
             <v>S-2026-04-60</v>
           </cell>
+          <cell r="B360"/>
           <cell r="C360" t="str">
             <v>RPRO-260423-0486</v>
           </cell>
@@ -26552,15 +27361,14 @@
           <cell r="A361" t="str">
             <v>S-2026-04-61</v>
           </cell>
+          <cell r="B361"/>
           <cell r="C361" t="str">
             <v>RPRO-260423-0487</v>
           </cell>
           <cell r="D361" t="str">
             <v>PUR2604230001S</v>
           </cell>
-          <cell r="E361" t="str">
-            <v>BDB-000028</v>
-          </cell>
+          <cell r="E361"/>
           <cell r="F361" t="str">
             <v>PVN-004397</v>
           </cell>
@@ -26620,15 +27428,14 @@
           <cell r="A362" t="str">
             <v>S-2026-04-62</v>
           </cell>
+          <cell r="B362"/>
           <cell r="C362" t="str">
             <v>RPRO-260424-1197</v>
           </cell>
           <cell r="D362" t="str">
             <v xml:space="preserve"> PUR2604230002S</v>
           </cell>
-          <cell r="E362" t="str">
-            <v>BDB-000384</v>
-          </cell>
+          <cell r="E362"/>
           <cell r="F362" t="str">
             <v>PVN-004399</v>
           </cell>
@@ -26688,15 +27495,14 @@
           <cell r="A363" t="str">
             <v>S-2026-04-63</v>
           </cell>
+          <cell r="B363"/>
           <cell r="C363" t="str">
             <v>RPRO-260424-1198</v>
           </cell>
           <cell r="D363" t="str">
             <v xml:space="preserve"> PUR2604230002S</v>
           </cell>
-          <cell r="E363" t="str">
-            <v>BDB-000384</v>
-          </cell>
+          <cell r="E363"/>
           <cell r="F363" t="str">
             <v>PVN-004377</v>
           </cell>
@@ -26756,15 +27562,14 @@
           <cell r="A364" t="str">
             <v>S-2026-04-64</v>
           </cell>
+          <cell r="B364"/>
           <cell r="C364" t="str">
             <v>RPRO-260424-1199</v>
           </cell>
           <cell r="D364" t="str">
             <v xml:space="preserve"> PUR2604230002S</v>
           </cell>
-          <cell r="E364" t="str">
-            <v>BDB-000384</v>
-          </cell>
+          <cell r="E364"/>
           <cell r="F364" t="str">
             <v>PVN-004378</v>
           </cell>
@@ -26824,6 +27629,7 @@
           <cell r="A365" t="str">
             <v>S-2026-04-65</v>
           </cell>
+          <cell r="B365"/>
           <cell r="C365" t="str">
             <v>RPRO-260424-1200</v>
           </cell>
@@ -26892,6 +27698,7 @@
           <cell r="A366" t="str">
             <v>S-2026-04-66</v>
           </cell>
+          <cell r="B366"/>
           <cell r="C366" t="str">
             <v>RPRO-260424-1201</v>
           </cell>
@@ -26969,9 +27776,7 @@
           <cell r="D367" t="str">
             <v>PUR-202604240001S</v>
           </cell>
-          <cell r="E367" t="str">
-            <v>BDB-000229</v>
-          </cell>
+          <cell r="E367"/>
           <cell r="F367" t="str">
             <v>PVN-004373</v>
           </cell>
@@ -27020,8 +27825,8 @@
           <cell r="U367">
             <v>5.2</v>
           </cell>
-          <cell r="V367">
-            <v>3.8460000000000001E-2</v>
+          <cell r="V367" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="W367">
             <v>1</v>
@@ -27031,6 +27836,7 @@
           <cell r="A368" t="str">
             <v>S-2026-04-68</v>
           </cell>
+          <cell r="B368"/>
           <cell r="C368" t="str">
             <v>RPRO-260424-1203</v>
           </cell>
@@ -27099,6 +27905,7 @@
           <cell r="A369" t="str">
             <v>S-2026-04-69</v>
           </cell>
+          <cell r="B369"/>
           <cell r="C369" t="str">
             <v>RPRO-260424-1204</v>
           </cell>
@@ -27167,6 +27974,7 @@
           <cell r="A370" t="str">
             <v>S-2026-04-70</v>
           </cell>
+          <cell r="B370"/>
           <cell r="C370" t="str">
             <v>RPRO-260424-1205</v>
           </cell>
@@ -27235,15 +28043,14 @@
           <cell r="A371" t="str">
             <v>S-2026-04-71</v>
           </cell>
+          <cell r="B371"/>
           <cell r="C371" t="str">
             <v>RPRO-260424-1206</v>
           </cell>
           <cell r="D371" t="str">
             <v>PUR2604240002S</v>
           </cell>
-          <cell r="E371" t="str">
-            <v>BDB-000386</v>
-          </cell>
+          <cell r="E371"/>
           <cell r="F371" t="str">
             <v>PVN-004384</v>
           </cell>
@@ -27303,6 +28110,7 @@
           <cell r="A372" t="str">
             <v>S-2026-04-72</v>
           </cell>
+          <cell r="B372"/>
           <cell r="C372" t="str">
             <v>RPRO-260428-0920</v>
           </cell>
@@ -27371,6 +28179,7 @@
           <cell r="A373" t="str">
             <v>S-2026-04-73</v>
           </cell>
+          <cell r="B373"/>
           <cell r="C373" t="str">
             <v>RPRO-260429-0109</v>
           </cell>
@@ -27439,6 +28248,7 @@
           <cell r="A374" t="str">
             <v>S-2026-04-74</v>
           </cell>
+          <cell r="B374"/>
           <cell r="C374" t="str">
             <v>RPRO-260429-0110</v>
           </cell>
@@ -27507,15 +28317,14 @@
           <cell r="A375" t="str">
             <v>S-2026-04-75</v>
           </cell>
+          <cell r="B375"/>
           <cell r="C375" t="str">
             <v>RPRO-260429-0126</v>
           </cell>
           <cell r="D375" t="str">
             <v>PUR2600402900002S</v>
           </cell>
-          <cell r="E375" t="str">
-            <v>BDB-000389</v>
-          </cell>
+          <cell r="E375"/>
           <cell r="F375" t="str">
             <v>PVN-004404</v>
           </cell>
@@ -27575,6 +28384,7 @@
           <cell r="A376" t="str">
             <v>S-2026-04-76</v>
           </cell>
+          <cell r="B376"/>
           <cell r="C376" t="str">
             <v>RPRO-260429-0127</v>
           </cell>
@@ -27643,15 +28453,14 @@
           <cell r="A377" t="str">
             <v>S-2026-05-01</v>
           </cell>
+          <cell r="B377"/>
           <cell r="C377" t="str">
             <v>RPRO-260505-0654</v>
           </cell>
           <cell r="D377" t="str">
             <v>PUR2600402900003S</v>
           </cell>
-          <cell r="E377" t="str">
-            <v>BDB-000371</v>
-          </cell>
+          <cell r="E377"/>
           <cell r="F377" t="str">
             <v>PVN-004391</v>
           </cell>
@@ -27782,6 +28591,7 @@
           <cell r="A379" t="str">
             <v>S-2026-05-03</v>
           </cell>
+          <cell r="B379"/>
           <cell r="C379" t="str">
             <v>RPRO-260505-0656</v>
           </cell>
@@ -27850,6 +28660,7 @@
           <cell r="A380" t="str">
             <v>S-2026-05-04</v>
           </cell>
+          <cell r="B380"/>
           <cell r="C380" t="str">
             <v>RPRO-260505-0657</v>
           </cell>
@@ -27918,6 +28729,7 @@
           <cell r="A381" t="str">
             <v>S-2026-05-05</v>
           </cell>
+          <cell r="B381"/>
           <cell r="C381" t="str">
             <v>RPRO-260505-0658</v>
           </cell>
@@ -27986,6 +28798,7 @@
           <cell r="A382" t="str">
             <v>S-2026-05-06</v>
           </cell>
+          <cell r="B382"/>
           <cell r="C382" t="str">
             <v>RPRO-260505-0659</v>
           </cell>
@@ -28054,6 +28867,7 @@
           <cell r="A383" t="str">
             <v>S-2026-05-07</v>
           </cell>
+          <cell r="B383"/>
           <cell r="C383" t="str">
             <v>RPRO-260505-0660</v>
           </cell>
@@ -28193,6 +29007,7 @@
           <cell r="A385" t="str">
             <v>S-2026-05-09</v>
           </cell>
+          <cell r="B385"/>
           <cell r="C385" t="str">
             <v>RPRO-260505-0662</v>
           </cell>
@@ -28261,15 +29076,14 @@
           <cell r="A386" t="str">
             <v>S-2026-05-10</v>
           </cell>
+          <cell r="B386"/>
           <cell r="C386" t="str">
             <v>RPRO-260505-0663</v>
           </cell>
           <cell r="D386" t="str">
             <v>PUR2605040003S</v>
           </cell>
-          <cell r="E386" t="str">
-            <v>BDB-000318</v>
-          </cell>
+          <cell r="E386"/>
           <cell r="F386" t="str">
             <v>PVN-004406</v>
           </cell>
@@ -28400,6 +29214,7 @@
           <cell r="A388" t="str">
             <v>S-2026-05-12</v>
           </cell>
+          <cell r="B388"/>
           <cell r="C388" t="str">
             <v>RPRO-260505-0802</v>
           </cell>
@@ -28468,6 +29283,7 @@
           <cell r="A389" t="str">
             <v>S-2026-05-13</v>
           </cell>
+          <cell r="B389"/>
           <cell r="C389" t="str">
             <v>RPRO-260505-0803</v>
           </cell>
@@ -28536,15 +29352,14 @@
           <cell r="A390" t="str">
             <v>S-2026-05-14</v>
           </cell>
+          <cell r="B390"/>
           <cell r="C390" t="str">
             <v>RPRO-260506-0394</v>
           </cell>
           <cell r="D390" t="str">
             <v>PUR2605060001S</v>
           </cell>
-          <cell r="E390" t="str">
-            <v>BDB-000371</v>
-          </cell>
+          <cell r="E390"/>
           <cell r="F390" t="str">
             <v>PVN-004391</v>
           </cell>
@@ -28604,6 +29419,7 @@
           <cell r="A391" t="str">
             <v>S-2026-05-15</v>
           </cell>
+          <cell r="B391"/>
           <cell r="C391" t="str">
             <v>RPRO-260506-0395</v>
           </cell>
@@ -28672,6 +29488,7 @@
           <cell r="A392" t="str">
             <v>S-2026-05-16</v>
           </cell>
+          <cell r="B392"/>
           <cell r="C392" t="str">
             <v>RPRO-260506-0396</v>
           </cell>
@@ -28740,6 +29557,7 @@
           <cell r="A393" t="str">
             <v>S-2026-05-17</v>
           </cell>
+          <cell r="B393"/>
           <cell r="C393" t="str">
             <v>RPRO-260506-0397</v>
           </cell>
@@ -28808,15 +29626,14 @@
           <cell r="A394" t="str">
             <v>S-2026-05-18</v>
           </cell>
+          <cell r="B394"/>
           <cell r="C394" t="str">
             <v>RPRO-260506-0415</v>
           </cell>
           <cell r="D394" t="str">
             <v xml:space="preserve">PUR2605060002S   </v>
           </cell>
-          <cell r="E394" t="str">
-            <v>BDB-000348</v>
-          </cell>
+          <cell r="E394"/>
           <cell r="F394" t="str">
             <v>PVN-004405</v>
           </cell>
@@ -28876,6 +29693,7 @@
           <cell r="A395" t="str">
             <v>S-2026-05-19</v>
           </cell>
+          <cell r="B395"/>
           <cell r="C395" t="str">
             <v>RPRO-260508-0581</v>
           </cell>
@@ -28944,6 +29762,7 @@
           <cell r="A396" t="str">
             <v>S-2026-05-20</v>
           </cell>
+          <cell r="B396"/>
           <cell r="C396" t="str">
             <v>RPRO-260508-0582</v>
           </cell>
@@ -29012,6 +29831,7 @@
           <cell r="A397" t="str">
             <v>S-2026-05-21</v>
           </cell>
+          <cell r="B397"/>
           <cell r="C397" t="str">
             <v>RPRO-260508-0583</v>
           </cell>
@@ -29080,6 +29900,7 @@
           <cell r="A398" t="str">
             <v>S-2026-05-22</v>
           </cell>
+          <cell r="B398"/>
           <cell r="C398" t="str">
             <v>RPRO-260508-0584</v>
           </cell>
@@ -29148,6 +29969,7 @@
           <cell r="A399" t="str">
             <v>S-2026-05-23</v>
           </cell>
+          <cell r="B399"/>
           <cell r="C399" t="str">
             <v>RPRO-260508-0585</v>
           </cell>
@@ -29216,6 +30038,7 @@
           <cell r="A400" t="str">
             <v>S-2026-05-24</v>
           </cell>
+          <cell r="B400"/>
           <cell r="C400" t="str">
             <v>RPRO-260508-0586</v>
           </cell>
@@ -29284,6 +30107,7 @@
           <cell r="A401" t="str">
             <v>S-2026-05-25</v>
           </cell>
+          <cell r="B401"/>
           <cell r="C401" t="str">
             <v>RPRO-260508-0587</v>
           </cell>
@@ -29352,6 +30176,7 @@
           <cell r="A402" t="str">
             <v>S-2026-05-26</v>
           </cell>
+          <cell r="B402"/>
           <cell r="C402" t="str">
             <v>RPRO-260508-0588</v>
           </cell>
@@ -29420,15 +30245,14 @@
           <cell r="A403" t="str">
             <v>S-2026-05-27</v>
           </cell>
+          <cell r="B403"/>
           <cell r="C403" t="str">
             <v>RPRO-260512-0580</v>
           </cell>
           <cell r="D403" t="str">
             <v>thuy.tao@ortholite.vn</v>
           </cell>
-          <cell r="E403" t="str">
-            <v>BDB-000321</v>
-          </cell>
+          <cell r="E403"/>
           <cell r="F403" t="str">
             <v>PVN-004414</v>
           </cell>
@@ -29450,6 +30274,7 @@
           <cell r="L403" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M403"/>
           <cell r="N403" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -29485,15 +30310,14 @@
           <cell r="A404" t="str">
             <v>S-2026-05-28</v>
           </cell>
+          <cell r="B404"/>
           <cell r="C404" t="str">
             <v>RPRO-260512-0581</v>
           </cell>
           <cell r="D404" t="str">
             <v>thuy.tao@ortholite.vn</v>
           </cell>
-          <cell r="E404" t="str">
-            <v>BDB-000058</v>
-          </cell>
+          <cell r="E404"/>
           <cell r="F404" t="str">
             <v>PVN-004415</v>
           </cell>
@@ -29507,14 +30331,15 @@
             <v>1</v>
           </cell>
           <cell r="J404">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="K404">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="L404" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M404"/>
           <cell r="N404" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -29550,6 +30375,7 @@
           <cell r="A405" t="str">
             <v>S-2026-05-29</v>
           </cell>
+          <cell r="B405"/>
           <cell r="C405" t="str">
             <v>RPRO-260512-0582</v>
           </cell>
@@ -29618,6 +30444,7 @@
           <cell r="A406" t="str">
             <v>S-2026-05-30</v>
           </cell>
+          <cell r="B406"/>
           <cell r="C406" t="str">
             <v>RPRO-260512-0583</v>
           </cell>
@@ -29686,9 +30513,7 @@
           <cell r="A407" t="str">
             <v>S-2026-05-31</v>
           </cell>
-          <cell r="B407" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B407"/>
           <cell r="C407" t="str">
             <v>RPRO-260513-0945</v>
           </cell>
@@ -29711,10 +30536,10 @@
             <v>40</v>
           </cell>
           <cell r="J407">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K407">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L407" t="str">
             <v>NEW BALANCE</v>
@@ -29757,9 +30582,7 @@
           <cell r="A408" t="str">
             <v>S-2026-05-32</v>
           </cell>
-          <cell r="B408" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B408"/>
           <cell r="C408" t="str">
             <v>RPRO-260513-0946</v>
           </cell>
@@ -29782,10 +30605,10 @@
             <v>50</v>
           </cell>
           <cell r="J408">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K408">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L408" t="str">
             <v>PUMA</v>
@@ -29828,9 +30651,7 @@
           <cell r="A409" t="str">
             <v>S-2026-05-33</v>
           </cell>
-          <cell r="B409" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B409"/>
           <cell r="C409" t="str">
             <v>RPRO-260513-0947</v>
           </cell>
@@ -29899,18 +30720,14 @@
           <cell r="A410" t="str">
             <v>S-2026-05-34</v>
           </cell>
-          <cell r="B410" t="str">
-            <v xml:space="preserve">chờ xác nhận </v>
-          </cell>
+          <cell r="B410"/>
           <cell r="C410" t="str">
             <v>RPRO-260513-0948</v>
           </cell>
           <cell r="D410" t="str">
             <v>PUR2605130003S</v>
           </cell>
-          <cell r="E410" t="str">
-            <v>BDB-000371</v>
-          </cell>
+          <cell r="E410"/>
           <cell r="F410" t="str">
             <v>PVN-004417</v>
           </cell>
@@ -29924,10 +30741,10 @@
             <v>10</v>
           </cell>
           <cell r="J410">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="K410">
-            <v>10</v>
+            <v>0</v>
           </cell>
           <cell r="L410" t="str">
             <v>ADIDAS</v>
@@ -29959,11 +30776,11 @@
           <cell r="U410">
             <v>5</v>
           </cell>
-          <cell r="V410">
-            <v>3.5709999999999999E-2</v>
-          </cell>
-          <cell r="W410">
-            <v>1</v>
+          <cell r="V410" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="W410" t="str">
+            <v/>
           </cell>
         </row>
         <row r="411">
@@ -29995,10 +30812,10 @@
             <v>20</v>
           </cell>
           <cell r="J411">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="K411">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="L411" t="str">
             <v>ONE8</v>
@@ -30041,9 +30858,7 @@
           <cell r="A412" t="str">
             <v>S-2026-05-36</v>
           </cell>
-          <cell r="B412" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B412"/>
           <cell r="C412" t="str">
             <v>RPRO-260513-0950</v>
           </cell>
@@ -30112,6 +30927,7 @@
           <cell r="A413" t="str">
             <v>S-2026-05-37</v>
           </cell>
+          <cell r="B413"/>
           <cell r="C413" t="str">
             <v>RPRO-260515-0272</v>
           </cell>
@@ -30134,10 +30950,10 @@
             <v>20</v>
           </cell>
           <cell r="J413">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="K413">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="L413" t="str">
             <v>ONE8</v>
@@ -30180,6 +30996,7 @@
           <cell r="A414" t="str">
             <v>S-2026-05-38</v>
           </cell>
+          <cell r="B414"/>
           <cell r="C414" t="str">
             <v>RPRO-260515-0273</v>
           </cell>
@@ -30202,10 +31019,10 @@
             <v>15</v>
           </cell>
           <cell r="J414">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="K414">
-            <v>15</v>
+            <v>0</v>
           </cell>
           <cell r="L414" t="str">
             <v>ASICS</v>
@@ -30248,6 +31065,7 @@
           <cell r="A415" t="str">
             <v>S-2026-05-39</v>
           </cell>
+          <cell r="B415"/>
           <cell r="C415" t="str">
             <v>RPRO-260515-0274</v>
           </cell>
@@ -30270,10 +31088,10 @@
             <v>50</v>
           </cell>
           <cell r="J415">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K415">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L415" t="str">
             <v>SALOMON</v>
@@ -30316,6 +31134,7 @@
           <cell r="A416" t="str">
             <v>S-2026-05-40</v>
           </cell>
+          <cell r="B416"/>
           <cell r="C416" t="str">
             <v>RPRO-260515-0275</v>
           </cell>
@@ -30384,15 +31203,14 @@
           <cell r="A417" t="str">
             <v>S-2026-05-41</v>
           </cell>
+          <cell r="B417"/>
           <cell r="C417" t="str">
             <v>RPRO-260515-0276</v>
           </cell>
           <cell r="D417" t="str">
             <v>PUR2605150003S</v>
           </cell>
-          <cell r="E417" t="str">
-            <v>BDB-000028</v>
-          </cell>
+          <cell r="E417"/>
           <cell r="F417" t="str">
             <v>PVN-004397</v>
           </cell>
@@ -30452,6 +31270,7 @@
           <cell r="A418" t="str">
             <v>S-2026-05-42</v>
           </cell>
+          <cell r="B418"/>
           <cell r="C418" t="str">
             <v>RPRO-260515-0277</v>
           </cell>
@@ -30520,6 +31339,7 @@
           <cell r="A419" t="str">
             <v>S-2026-05-43</v>
           </cell>
+          <cell r="B419"/>
           <cell r="C419" t="str">
             <v>RPRO-260515-0278</v>
           </cell>
@@ -30588,6 +31408,7 @@
           <cell r="A420" t="str">
             <v>S-2026-05-44</v>
           </cell>
+          <cell r="B420"/>
           <cell r="C420" t="str">
             <v>RPRO-260515-0279</v>
           </cell>
@@ -30610,10 +31431,10 @@
             <v>50</v>
           </cell>
           <cell r="J420">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K420">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L420" t="str">
             <v>ADIDAS</v>
@@ -30656,6 +31477,7 @@
           <cell r="A421" t="str">
             <v>S-2026-05-45</v>
           </cell>
+          <cell r="B421"/>
           <cell r="C421" t="str">
             <v>RPRO-260515-0280</v>
           </cell>
@@ -30724,6 +31546,7 @@
           <cell r="A422" t="str">
             <v>S-2026-05-46</v>
           </cell>
+          <cell r="B422"/>
           <cell r="C422" t="str">
             <v>RPRO-260518-0853</v>
           </cell>
@@ -30792,6 +31615,7 @@
           <cell r="A423" t="str">
             <v>S-2026-05-47</v>
           </cell>
+          <cell r="B423"/>
           <cell r="C423" t="str">
             <v>RPRO-260518-0854</v>
           </cell>
@@ -30860,6 +31684,7 @@
           <cell r="A424" t="str">
             <v>S-2026-05-48</v>
           </cell>
+          <cell r="B424"/>
           <cell r="C424" t="str">
             <v>RPRO-260518-0855</v>
           </cell>
@@ -30928,6 +31753,7 @@
           <cell r="A425" t="str">
             <v>S-2026-05-49</v>
           </cell>
+          <cell r="B425"/>
           <cell r="C425" t="str">
             <v>RPRO-260518-0856</v>
           </cell>
@@ -31147,9 +31973,7 @@
           <cell r="D428" t="str">
             <v xml:space="preserve">PUR2605160001S   </v>
           </cell>
-          <cell r="E428" t="str">
-            <v>BDB-000343</v>
-          </cell>
+          <cell r="E428"/>
           <cell r="F428" t="str">
             <v>PVN-004420</v>
           </cell>
@@ -31163,10 +31987,10 @@
             <v>5</v>
           </cell>
           <cell r="J428">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="K428">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="L428" t="str">
             <v>ADIDAS</v>
@@ -31198,17 +32022,18 @@
           <cell r="U428">
             <v>6.2</v>
           </cell>
-          <cell r="V428">
-            <v>4.3479999999999998E-2</v>
-          </cell>
-          <cell r="W428">
-            <v>1</v>
+          <cell r="V428" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="W428" t="str">
+            <v/>
           </cell>
         </row>
         <row r="429">
           <cell r="A429" t="str">
             <v>S-2026-05-53</v>
           </cell>
+          <cell r="B429"/>
           <cell r="C429" t="str">
             <v>RPRO-260518-0860</v>
           </cell>
@@ -31277,6 +32102,7 @@
           <cell r="A430" t="str">
             <v>S-2026-05-54</v>
           </cell>
+          <cell r="B430"/>
           <cell r="C430" t="str">
             <v>RPRO-260518-0861</v>
           </cell>
@@ -31345,6 +32171,7 @@
           <cell r="A431" t="str">
             <v>S-2026-05-55</v>
           </cell>
+          <cell r="B431"/>
           <cell r="C431" t="str">
             <v>RPRO-260518-0862</v>
           </cell>
@@ -31413,6 +32240,7 @@
           <cell r="A432" t="str">
             <v>S-2026-05-56</v>
           </cell>
+          <cell r="B432"/>
           <cell r="C432" t="str">
             <v>RPRO-260518-0863</v>
           </cell>
@@ -31481,6 +32309,7 @@
           <cell r="A433" t="str">
             <v>S-2026-05-57</v>
           </cell>
+          <cell r="B433"/>
           <cell r="C433" t="str">
             <v>RPRO-260518-0864</v>
           </cell>
@@ -31549,6 +32378,7 @@
           <cell r="A434" t="str">
             <v>S-2026-05-58</v>
           </cell>
+          <cell r="B434"/>
           <cell r="C434" t="str">
             <v>RPRO-260518-0865</v>
           </cell>
@@ -31617,6 +32447,7 @@
           <cell r="A435" t="str">
             <v>S-2026-05-59</v>
           </cell>
+          <cell r="B435"/>
           <cell r="C435" t="str">
             <v>RPRO-260518-0866</v>
           </cell>
@@ -31685,9 +32516,7 @@
           <cell r="A436" t="str">
             <v>S-2026-05-60</v>
           </cell>
-          <cell r="B436" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B436"/>
           <cell r="C436" t="str">
             <v>RPRO-260520-0192</v>
           </cell>
@@ -31710,10 +32539,10 @@
             <v>70</v>
           </cell>
           <cell r="J436">
-            <v>0</v>
+            <v>70</v>
           </cell>
           <cell r="K436">
-            <v>70</v>
+            <v>0</v>
           </cell>
           <cell r="L436" t="str">
             <v>ADIDAS</v>
@@ -31756,9 +32585,7 @@
           <cell r="A437" t="str">
             <v>S-2026-05-61</v>
           </cell>
-          <cell r="B437" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B437"/>
           <cell r="C437" t="str">
             <v>RPRO-260520-0193</v>
           </cell>
@@ -31827,9 +32654,7 @@
           <cell r="A438" t="str">
             <v>S-2026-05-62</v>
           </cell>
-          <cell r="B438" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B438"/>
           <cell r="C438" t="str">
             <v>RPRO-260520-0194</v>
           </cell>
@@ -31852,10 +32677,10 @@
             <v>40</v>
           </cell>
           <cell r="J438">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K438">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L438" t="str">
             <v>NIKE</v>
@@ -31898,9 +32723,7 @@
           <cell r="A439" t="str">
             <v>S-2026-05-63</v>
           </cell>
-          <cell r="B439" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B439"/>
           <cell r="C439" t="str">
             <v>RPRO-260520-0195</v>
           </cell>
@@ -31969,9 +32792,7 @@
           <cell r="A440" t="str">
             <v>S-2026-05-64</v>
           </cell>
-          <cell r="B440" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B440"/>
           <cell r="C440" t="str">
             <v>RPRO-260520-0196</v>
           </cell>
@@ -32040,9 +32861,7 @@
           <cell r="A441" t="str">
             <v>S-2026-05-65</v>
           </cell>
-          <cell r="B441" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B441"/>
           <cell r="C441" t="str">
             <v>RPRO-260520-0197</v>
           </cell>
@@ -32111,9 +32930,7 @@
           <cell r="A442" t="str">
             <v>S-2026-05-66</v>
           </cell>
-          <cell r="B442" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B442"/>
           <cell r="C442" t="str">
             <v>RPRO-260520-0225</v>
           </cell>
@@ -32182,9 +32999,7 @@
           <cell r="A443" t="str">
             <v>S-2026-05-67</v>
           </cell>
-          <cell r="B443" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B443"/>
           <cell r="C443" t="str">
             <v>RPRO-260520-0226</v>
           </cell>
@@ -32253,9 +33068,7 @@
           <cell r="A444" t="str">
             <v>S-2026-05-68</v>
           </cell>
-          <cell r="B444" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B444"/>
           <cell r="C444" t="str">
             <v>RPRO-260520-0227</v>
           </cell>
@@ -32324,9 +33137,7 @@
           <cell r="A445" t="str">
             <v>S-2026-05-69</v>
           </cell>
-          <cell r="B445" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B445"/>
           <cell r="C445" t="str">
             <v>RPRO-260520-0228</v>
           </cell>
@@ -32395,9 +33206,7 @@
           <cell r="A446" t="str">
             <v>S-2026-05-70</v>
           </cell>
-          <cell r="B446" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B446"/>
           <cell r="C446" t="str">
             <v>RPRO-260520-0229</v>
           </cell>
@@ -32405,7 +33214,7 @@
             <v>PUR-202605200002S</v>
           </cell>
           <cell r="E446" t="str">
-            <v>BDB-000234</v>
+            <v/>
           </cell>
           <cell r="F446" t="str">
             <v>PVN-004424</v>
@@ -32455,17 +33264,18 @@
           <cell r="U446">
             <v>6</v>
           </cell>
-          <cell r="V446">
-            <v>4.1669999999999999E-2</v>
-          </cell>
-          <cell r="W446">
-            <v>1</v>
+          <cell r="V446" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="W446" t="str">
+            <v/>
           </cell>
         </row>
         <row r="447">
           <cell r="A447" t="str">
             <v>S-2026-05-71</v>
           </cell>
+          <cell r="B447"/>
           <cell r="C447" t="str">
             <v>RPRO-260521-0669</v>
           </cell>
@@ -32488,7 +33298,7 @@
             <v>50</v>
           </cell>
           <cell r="J447">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K447">
             <v>50</v>
@@ -32534,6 +33344,7 @@
           <cell r="A448" t="str">
             <v>S-2026-05-72</v>
           </cell>
+          <cell r="B448"/>
           <cell r="C448" t="str">
             <v>RPRO-260521-0670</v>
           </cell>
@@ -32556,7 +33367,7 @@
             <v>30</v>
           </cell>
           <cell r="J448">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K448">
             <v>30</v>
@@ -32599,311 +33410,1765 @@
           </cell>
         </row>
         <row r="449">
+          <cell r="A449" t="str">
+            <v>S-2026-05-73</v>
+          </cell>
+          <cell r="B449"/>
+          <cell r="C449" t="str">
+            <v>RPRO-260523-0221</v>
+          </cell>
+          <cell r="D449" t="str">
+            <v>PUR2605220001S</v>
+          </cell>
           <cell r="E449" t="str">
+            <v>BDB-000376</v>
+          </cell>
+          <cell r="F449" t="str">
+            <v>PVN-004323</v>
+          </cell>
+          <cell r="G449" t="str">
+            <v>OrthoLite Regular BLACK/19-4007TPX Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 13mm</v>
+          </cell>
+          <cell r="H449">
+            <v>15</v>
+          </cell>
+          <cell r="I449">
+            <v>15</v>
+          </cell>
+          <cell r="J449">
+            <v>0</v>
+          </cell>
+          <cell r="K449">
+            <v>15</v>
+          </cell>
+          <cell r="L449" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M449" t="str">
+            <v>SSO-2605-01170   - URGENT (5-30)</v>
+          </cell>
+          <cell r="N449" t="str">
+            <v>Molded</v>
+          </cell>
+          <cell r="O449" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P449">
+            <v>46164</v>
+          </cell>
+          <cell r="Q449">
+            <v>46172</v>
+          </cell>
+          <cell r="R449">
+            <v>46169</v>
+          </cell>
+          <cell r="S449">
+            <v>6</v>
+          </cell>
+          <cell r="T449">
+            <v>8</v>
+          </cell>
+          <cell r="U449">
+            <v>13</v>
+          </cell>
+          <cell r="V449">
+            <v>0.1</v>
+          </cell>
+          <cell r="W449">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="450">
+          <cell r="A450" t="str">
+            <v>S-2026-05-74</v>
+          </cell>
+          <cell r="B450"/>
+          <cell r="C450" t="str">
+            <v>RPRO-260523-0222</v>
+          </cell>
+          <cell r="D450" t="str">
+            <v>PUR2605220001S</v>
+          </cell>
+          <cell r="E450" t="str">
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F450" t="str">
+            <v>PVN-003299</v>
+          </cell>
+          <cell r="G450" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H450">
+            <v>100</v>
+          </cell>
+          <cell r="I450">
+            <v>100</v>
+          </cell>
+          <cell r="J450">
+            <v>0</v>
+          </cell>
+          <cell r="K450">
+            <v>100</v>
+          </cell>
+          <cell r="L450" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M450" t="str">
+            <v>SSO-2605-01174   - URGENT (5-30)</v>
+          </cell>
+          <cell r="N450" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O450" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P450">
+            <v>46164</v>
+          </cell>
+          <cell r="Q450">
+            <v>46172</v>
+          </cell>
+          <cell r="R450">
+            <v>46169</v>
+          </cell>
+          <cell r="S450">
+            <v>6</v>
+          </cell>
+          <cell r="T450">
+            <v>8</v>
+          </cell>
+          <cell r="U450">
+            <v>3</v>
+          </cell>
+          <cell r="V450">
+            <v>2.1739999999999999E-2</v>
+          </cell>
+          <cell r="W450">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="451">
+          <cell r="A451" t="str">
+            <v>S-2026-05-75</v>
+          </cell>
+          <cell r="B451"/>
+          <cell r="C451" t="str">
+            <v>RPRO-260523-0223</v>
+          </cell>
+          <cell r="D451" t="str">
+            <v>PUR2600502300001S</v>
+          </cell>
+          <cell r="E451" t="str">
+            <v>BDB-000076</v>
+          </cell>
+          <cell r="F451" t="str">
+            <v>PVN-004056</v>
+          </cell>
+          <cell r="G451" t="str">
+            <v>OrthoLite X-25 BILLIARD/16-5427TPX Flat Sheet 0.12D 20+/-4 Asker C 1.1M 2M 12mm</v>
+          </cell>
+          <cell r="H451">
+            <v>20</v>
+          </cell>
+          <cell r="I451">
+            <v>20</v>
+          </cell>
+          <cell r="J451">
+            <v>0</v>
+          </cell>
+          <cell r="K451">
+            <v>20</v>
+          </cell>
+          <cell r="L451" t="str">
+            <v>FOOTJOY</v>
+          </cell>
+          <cell r="M451" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N451" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O451" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P451">
+            <v>46165</v>
+          </cell>
+          <cell r="Q451">
+            <v>46172</v>
+          </cell>
+          <cell r="R451">
+            <v>46169</v>
+          </cell>
+          <cell r="S451">
+            <v>6</v>
+          </cell>
+          <cell r="T451">
+            <v>7</v>
+          </cell>
+          <cell r="U451">
+            <v>12</v>
+          </cell>
+          <cell r="V451">
+            <v>9.0910000000000005E-2</v>
+          </cell>
+          <cell r="W451">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="452">
+          <cell r="A452" t="str">
+            <v>S-2026-05-76</v>
+          </cell>
+          <cell r="B452"/>
+          <cell r="C452" t="str">
+            <v>RPRO-260525-0001</v>
+          </cell>
+          <cell r="D452" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E452" t="str">
+            <v>BDB-000235</v>
+          </cell>
+          <cell r="F452" t="str">
+            <v>PVN-003576</v>
+          </cell>
+          <cell r="G452" t="str">
+            <v>OrthoLite X-55-Hybrid FOSSIL/17-0909TPX Hybrid 0.16D 25+/-4 Asker C 1.1M 1.7M 12mm</v>
+          </cell>
+          <cell r="H452">
+            <v>30</v>
+          </cell>
+          <cell r="I452">
+            <v>30</v>
+          </cell>
+          <cell r="J452">
+            <v>0</v>
+          </cell>
+          <cell r="K452">
+            <v>30</v>
+          </cell>
+          <cell r="L452" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M452" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N452" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O452" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P452">
+            <v>46167</v>
+          </cell>
+          <cell r="Q452">
+            <v>46174</v>
+          </cell>
+          <cell r="R452">
+            <v>46171</v>
+          </cell>
+          <cell r="S452">
+            <v>6</v>
+          </cell>
+          <cell r="T452">
+            <v>7</v>
+          </cell>
+          <cell r="U452">
+            <v>12</v>
+          </cell>
+          <cell r="V452">
+            <v>9.0909999999999991E-2</v>
+          </cell>
+          <cell r="W452">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="453">
+          <cell r="A453" t="str">
+            <v>S-2026-05-77</v>
+          </cell>
+          <cell r="B453"/>
+          <cell r="C453" t="str">
+            <v>RPRO-260525-0002</v>
+          </cell>
+          <cell r="D453" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E453" t="str">
+            <v>BDB-000113</v>
+          </cell>
+          <cell r="F453" t="str">
+            <v>PVN-002688</v>
+          </cell>
+          <cell r="G453" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.11D 25+/-4 Asker C 1.1M 2M 6mm</v>
+          </cell>
+          <cell r="H453">
+            <v>100</v>
+          </cell>
+          <cell r="I453">
+            <v>100</v>
+          </cell>
+          <cell r="J453">
+            <v>0</v>
+          </cell>
+          <cell r="K453">
+            <v>100</v>
+          </cell>
+          <cell r="L453" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M453" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N453" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O453" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P453">
+            <v>46167</v>
+          </cell>
+          <cell r="Q453">
+            <v>46174</v>
+          </cell>
+          <cell r="R453">
+            <v>46171</v>
+          </cell>
+          <cell r="S453">
+            <v>6</v>
+          </cell>
+          <cell r="T453">
+            <v>7</v>
+          </cell>
+          <cell r="U453">
+            <v>6</v>
+          </cell>
+          <cell r="V453">
+            <v>4.3479999999999998E-2</v>
+          </cell>
+          <cell r="W453">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="454">
+          <cell r="A454" t="str">
+            <v>S-2026-05-78</v>
+          </cell>
+          <cell r="B454"/>
+          <cell r="C454" t="str">
+            <v>RPRO-260525-0003</v>
+          </cell>
+          <cell r="D454" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E454" t="str">
+            <v>BDB-000113</v>
+          </cell>
+          <cell r="F454" t="str">
+            <v>PVN-002887</v>
+          </cell>
+          <cell r="G454" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 5.5mm</v>
+          </cell>
+          <cell r="H454">
+            <v>20</v>
+          </cell>
+          <cell r="I454">
+            <v>20</v>
+          </cell>
+          <cell r="J454">
+            <v>0</v>
+          </cell>
+          <cell r="K454">
+            <v>20</v>
+          </cell>
+          <cell r="L454" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M454" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N454" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O454" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P454">
+            <v>46167</v>
+          </cell>
+          <cell r="Q454">
+            <v>46174</v>
+          </cell>
+          <cell r="R454">
+            <v>46171</v>
+          </cell>
+          <cell r="S454">
+            <v>6</v>
+          </cell>
+          <cell r="T454">
+            <v>7</v>
+          </cell>
+          <cell r="U454">
+            <v>5.5</v>
+          </cell>
+          <cell r="V454">
+            <v>0.04</v>
+          </cell>
+          <cell r="W454">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="455">
+          <cell r="A455" t="str">
+            <v>S-2026-05-79</v>
+          </cell>
+          <cell r="B455"/>
+          <cell r="C455" t="str">
+            <v>RPRO-260525-0004</v>
+          </cell>
+          <cell r="D455" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E455" t="str">
+            <v>BDB-000113</v>
+          </cell>
+          <cell r="F455" t="str">
+            <v>PVN-003601</v>
+          </cell>
+          <cell r="G455" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 20mm</v>
+          </cell>
+          <cell r="H455">
+            <v>10</v>
+          </cell>
+          <cell r="I455">
+            <v>10</v>
+          </cell>
+          <cell r="J455">
+            <v>0</v>
+          </cell>
+          <cell r="K455">
+            <v>10</v>
+          </cell>
+          <cell r="L455" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M455" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N455" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O455" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P455">
+            <v>46167</v>
+          </cell>
+          <cell r="Q455">
+            <v>46174</v>
+          </cell>
+          <cell r="R455">
+            <v>46171</v>
+          </cell>
+          <cell r="S455">
+            <v>6</v>
+          </cell>
+          <cell r="T455">
+            <v>7</v>
+          </cell>
+          <cell r="U455">
+            <v>20</v>
+          </cell>
+          <cell r="V455">
+            <v>0.16667000000000001</v>
+          </cell>
+          <cell r="W455">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="456">
+          <cell r="A456" t="str">
+            <v>S-2026-05-80</v>
+          </cell>
+          <cell r="B456"/>
+          <cell r="C456" t="str">
+            <v>RPRO-260525-0005</v>
+          </cell>
+          <cell r="D456" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E456" t="str">
+            <v>BDB-000097</v>
+          </cell>
+          <cell r="F456" t="str">
+            <v>PVN-002478</v>
+          </cell>
+          <cell r="G456" t="str">
+            <v>OrthoLite Eco LT-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.11D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H456">
+            <v>50</v>
+          </cell>
+          <cell r="I456">
+            <v>50</v>
+          </cell>
+          <cell r="J456">
+            <v>0</v>
+          </cell>
+          <cell r="K456">
+            <v>50</v>
+          </cell>
+          <cell r="L456" t="str">
+            <v>NEW BALANCE</v>
+          </cell>
+          <cell r="M456" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N456" t="str">
+            <v>DIE-CUT</v>
+          </cell>
+          <cell r="O456" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P456">
+            <v>46167</v>
+          </cell>
+          <cell r="Q456">
+            <v>46174</v>
+          </cell>
+          <cell r="R456">
+            <v>46171</v>
+          </cell>
+          <cell r="S456">
+            <v>6</v>
+          </cell>
+          <cell r="T456">
+            <v>7</v>
+          </cell>
+          <cell r="U456">
+            <v>4</v>
+          </cell>
+          <cell r="V456">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W456">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="457">
+          <cell r="A457" t="str">
+            <v>S-2026-05-81</v>
+          </cell>
+          <cell r="B457"/>
+          <cell r="C457" t="str">
+            <v>RPRO-260525-0006</v>
+          </cell>
+          <cell r="D457" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E457" t="str">
+            <v>BDB-000113</v>
+          </cell>
+          <cell r="F457" t="str">
+            <v>PVN-003414</v>
+          </cell>
+          <cell r="G457" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.11D 25+/-4 Asker C 1.1M 2M 12mm</v>
+          </cell>
+          <cell r="H457">
+            <v>50</v>
+          </cell>
+          <cell r="I457">
+            <v>50</v>
+          </cell>
+          <cell r="J457">
+            <v>0</v>
+          </cell>
+          <cell r="K457">
+            <v>50</v>
+          </cell>
+          <cell r="L457" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M457" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N457" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O457" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P457">
+            <v>46167</v>
+          </cell>
+          <cell r="Q457">
+            <v>46175</v>
+          </cell>
+          <cell r="R457">
+            <v>46172</v>
+          </cell>
+          <cell r="S457">
+            <v>6</v>
+          </cell>
+          <cell r="T457">
+            <v>8</v>
+          </cell>
+          <cell r="U457">
+            <v>12</v>
+          </cell>
+          <cell r="V457">
+            <v>9.0909999999999991E-2</v>
+          </cell>
+          <cell r="W457">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="458">
+          <cell r="A458" t="str">
+            <v>S-2026-05-82</v>
+          </cell>
+          <cell r="B458"/>
+          <cell r="C458" t="str">
+            <v>RPRO-260525-0007</v>
+          </cell>
+          <cell r="D458" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E458" t="str">
+            <v>BDB-000051</v>
+          </cell>
+          <cell r="F458" t="str">
+            <v>PVN-003450</v>
+          </cell>
+          <cell r="G458" t="str">
+            <v>OrthoLite X-40 TRUE BLUE/19-4057TPX Flat Sheet 0.16D 25+/-4 Asker C 1.1M 1.7M 6mm</v>
+          </cell>
+          <cell r="H458">
+            <v>100</v>
+          </cell>
+          <cell r="I458">
+            <v>100</v>
+          </cell>
+          <cell r="J458">
+            <v>0</v>
+          </cell>
+          <cell r="K458">
+            <v>100</v>
+          </cell>
+          <cell r="L458" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M458" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N458" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O458" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P458">
+            <v>46167</v>
+          </cell>
+          <cell r="Q458">
+            <v>46175</v>
+          </cell>
+          <cell r="R458">
+            <v>46172</v>
+          </cell>
+          <cell r="S458">
+            <v>6</v>
+          </cell>
+          <cell r="T458">
+            <v>8</v>
+          </cell>
+          <cell r="U458">
+            <v>6</v>
+          </cell>
+          <cell r="V458">
+            <v>4.3479999999999998E-2</v>
+          </cell>
+          <cell r="W458">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="459">
+          <cell r="A459" t="str">
+            <v>S-2026-05-83</v>
+          </cell>
+          <cell r="B459"/>
+          <cell r="C459" t="str">
+            <v>RPRO-260525-0008</v>
+          </cell>
+          <cell r="D459" t="str">
+            <v xml:space="preserve">PUR-202605250001S </v>
+          </cell>
+          <cell r="E459" t="str">
+            <v>BDB-000234</v>
+          </cell>
+          <cell r="F459" t="str">
+            <v>PVN-003581</v>
+          </cell>
+          <cell r="G459" t="str">
+            <v>OrthoLite X-30-Hybrid BROWN SUGAR/17-1134TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 12mm</v>
+          </cell>
+          <cell r="H459">
+            <v>30</v>
+          </cell>
+          <cell r="I459">
+            <v>30</v>
+          </cell>
+          <cell r="J459">
+            <v>0</v>
+          </cell>
+          <cell r="K459">
+            <v>30</v>
+          </cell>
+          <cell r="L459" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M459" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N459" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O459" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P459">
+            <v>46167</v>
+          </cell>
+          <cell r="Q459">
+            <v>46175</v>
+          </cell>
+          <cell r="R459">
+            <v>46172</v>
+          </cell>
+          <cell r="S459">
+            <v>6</v>
+          </cell>
+          <cell r="T459">
+            <v>8</v>
+          </cell>
+          <cell r="U459">
+            <v>12</v>
+          </cell>
+          <cell r="V459">
+            <v>9.0909999999999991E-2</v>
+          </cell>
+          <cell r="W459">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="460">
+          <cell r="A460" t="str">
+            <v>S-2026-05-84</v>
+          </cell>
+          <cell r="B460" t="str">
+            <v>chờ cfm ETD</v>
+          </cell>
+          <cell r="C460"/>
+          <cell r="D460" t="str">
+            <v>PUR2605250002S</v>
+          </cell>
+          <cell r="E460" t="str">
             <v/>
           </cell>
-          <cell r="J449">
-            <v>0</v>
-          </cell>
-          <cell r="K449">
-            <v>0</v>
-          </cell>
-          <cell r="U449" t="str">
+          <cell r="F460" t="str">
+            <v>PVN-004430</v>
+          </cell>
+          <cell r="G460" t="str">
+            <v>OrthoLite HybridPlus-Recycled COLORO 063-98-46 (fluorescent) Hybrid 0.12D 25+/-4 Asker C 1.1M 2M 6mm</v>
+          </cell>
+          <cell r="H460">
+            <v>40</v>
+          </cell>
+          <cell r="I460">
+            <v>40</v>
+          </cell>
+          <cell r="J460">
+            <v>0</v>
+          </cell>
+          <cell r="K460">
+            <v>40</v>
+          </cell>
+          <cell r="L460" t="str">
+            <v>ON RUNNING</v>
+          </cell>
+          <cell r="M460" t="str">
+            <v>SSO-2605-00765</v>
+          </cell>
+          <cell r="N460" t="str">
+            <v>OV-0408</v>
+          </cell>
+          <cell r="O460" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P460">
+            <v>46167</v>
+          </cell>
+          <cell r="Q460"/>
+          <cell r="R460"/>
+          <cell r="S460"/>
+          <cell r="T460"/>
+          <cell r="U460" t="str">
             <v/>
           </cell>
-          <cell r="V449">
-            <v>0</v>
-          </cell>
-          <cell r="W449">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="450">
-          <cell r="E450" t="str">
+          <cell r="V460" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="W460" t="str">
             <v/>
           </cell>
-          <cell r="J450">
-            <v>0</v>
-          </cell>
-          <cell r="K450">
-            <v>0</v>
-          </cell>
-          <cell r="U450" t="str">
+        </row>
+        <row r="461">
+          <cell r="A461" t="str">
+            <v>S-2026-05-85</v>
+          </cell>
+          <cell r="B461"/>
+          <cell r="C461" t="str">
+            <v>RPRO-260525-0009</v>
+          </cell>
+          <cell r="D461" t="str">
+            <v xml:space="preserve">PUR2605250003S </v>
+          </cell>
+          <cell r="E461" t="str">
+            <v>BDB-000097</v>
+          </cell>
+          <cell r="F461" t="str">
+            <v>PVN-002478</v>
+          </cell>
+          <cell r="G461" t="str">
+            <v>OrthoLite Eco LT-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H461">
+            <v>50</v>
+          </cell>
+          <cell r="I461">
+            <v>50</v>
+          </cell>
+          <cell r="J461">
+            <v>0</v>
+          </cell>
+          <cell r="K461">
+            <v>50</v>
+          </cell>
+          <cell r="L461" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M461" t="str">
+            <v>SSO-2605-01304   - URGENT (6-2)</v>
+          </cell>
+          <cell r="N461" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O461" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P461">
+            <v>46167</v>
+          </cell>
+          <cell r="Q461">
+            <v>46174</v>
+          </cell>
+          <cell r="R461">
+            <v>46171</v>
+          </cell>
+          <cell r="S461">
+            <v>6</v>
+          </cell>
+          <cell r="T461">
+            <v>7</v>
+          </cell>
+          <cell r="U461">
+            <v>4</v>
+          </cell>
+          <cell r="V461">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W461">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="462">
+          <cell r="A462"/>
+          <cell r="B462"/>
+          <cell r="C462"/>
+          <cell r="D462"/>
+          <cell r="E462" t="str">
             <v/>
           </cell>
-          <cell r="V450">
-            <v>0</v>
-          </cell>
-          <cell r="W450">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="451">
-          <cell r="E451" t="str">
+          <cell r="F462"/>
+          <cell r="G462"/>
+          <cell r="H462"/>
+          <cell r="I462"/>
+          <cell r="J462">
+            <v>0</v>
+          </cell>
+          <cell r="K462">
+            <v>0</v>
+          </cell>
+          <cell r="L462"/>
+          <cell r="M462"/>
+          <cell r="N462"/>
+          <cell r="O462"/>
+          <cell r="P462"/>
+          <cell r="Q462"/>
+          <cell r="R462"/>
+          <cell r="S462"/>
+          <cell r="T462"/>
+          <cell r="U462" t="str">
             <v/>
           </cell>
-          <cell r="J451">
-            <v>0</v>
-          </cell>
-          <cell r="K451">
-            <v>0</v>
-          </cell>
-          <cell r="U451" t="str">
+          <cell r="V462">
+            <v>0</v>
+          </cell>
+          <cell r="W462">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="463">
+          <cell r="A463"/>
+          <cell r="B463"/>
+          <cell r="C463"/>
+          <cell r="D463"/>
+          <cell r="E463" t="str">
             <v/>
           </cell>
-          <cell r="V451">
-            <v>0</v>
-          </cell>
-          <cell r="W451">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="452">
-          <cell r="E452" t="str">
+          <cell r="F463"/>
+          <cell r="G463"/>
+          <cell r="H463"/>
+          <cell r="I463"/>
+          <cell r="J463">
+            <v>0</v>
+          </cell>
+          <cell r="K463">
+            <v>0</v>
+          </cell>
+          <cell r="L463"/>
+          <cell r="M463"/>
+          <cell r="N463"/>
+          <cell r="O463"/>
+          <cell r="P463"/>
+          <cell r="Q463"/>
+          <cell r="R463"/>
+          <cell r="S463"/>
+          <cell r="T463"/>
+          <cell r="U463" t="str">
             <v/>
           </cell>
-          <cell r="J452">
-            <v>0</v>
-          </cell>
-          <cell r="K452">
-            <v>0</v>
-          </cell>
-          <cell r="U452" t="str">
+          <cell r="V463">
+            <v>0</v>
+          </cell>
+          <cell r="W463">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="464">
+          <cell r="A464"/>
+          <cell r="B464"/>
+          <cell r="C464"/>
+          <cell r="D464"/>
+          <cell r="E464" t="str">
             <v/>
           </cell>
-          <cell r="V452">
-            <v>0</v>
-          </cell>
-          <cell r="W452">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="453">
-          <cell r="E453" t="str">
+          <cell r="F464"/>
+          <cell r="G464"/>
+          <cell r="H464"/>
+          <cell r="I464"/>
+          <cell r="J464">
+            <v>0</v>
+          </cell>
+          <cell r="K464">
+            <v>0</v>
+          </cell>
+          <cell r="L464"/>
+          <cell r="M464"/>
+          <cell r="N464"/>
+          <cell r="O464"/>
+          <cell r="P464"/>
+          <cell r="Q464"/>
+          <cell r="R464"/>
+          <cell r="S464"/>
+          <cell r="T464"/>
+          <cell r="U464" t="str">
             <v/>
           </cell>
-          <cell r="J453">
-            <v>0</v>
-          </cell>
-          <cell r="K453">
-            <v>0</v>
-          </cell>
-          <cell r="U453" t="str">
+          <cell r="V464">
+            <v>0</v>
+          </cell>
+          <cell r="W464">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="465">
+          <cell r="A465"/>
+          <cell r="B465"/>
+          <cell r="C465"/>
+          <cell r="D465"/>
+          <cell r="E465" t="str">
             <v/>
           </cell>
-          <cell r="V453">
-            <v>0</v>
-          </cell>
-          <cell r="W453">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="454">
-          <cell r="E454" t="str">
+          <cell r="F465"/>
+          <cell r="G465"/>
+          <cell r="H465"/>
+          <cell r="I465"/>
+          <cell r="J465">
+            <v>0</v>
+          </cell>
+          <cell r="K465">
+            <v>0</v>
+          </cell>
+          <cell r="L465"/>
+          <cell r="M465"/>
+          <cell r="N465"/>
+          <cell r="O465"/>
+          <cell r="P465"/>
+          <cell r="Q465"/>
+          <cell r="R465"/>
+          <cell r="S465"/>
+          <cell r="T465"/>
+          <cell r="U465" t="str">
             <v/>
           </cell>
-          <cell r="J454">
-            <v>0</v>
-          </cell>
-          <cell r="K454">
-            <v>0</v>
-          </cell>
-          <cell r="U454" t="str">
+          <cell r="V465">
+            <v>0</v>
+          </cell>
+          <cell r="W465">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="466">
+          <cell r="A466"/>
+          <cell r="B466"/>
+          <cell r="C466"/>
+          <cell r="D466"/>
+          <cell r="E466" t="str">
             <v/>
           </cell>
-          <cell r="V454">
-            <v>0</v>
-          </cell>
-          <cell r="W454">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="455">
-          <cell r="E455" t="str">
+          <cell r="F466"/>
+          <cell r="G466"/>
+          <cell r="H466"/>
+          <cell r="I466"/>
+          <cell r="J466">
+            <v>0</v>
+          </cell>
+          <cell r="K466">
+            <v>0</v>
+          </cell>
+          <cell r="L466"/>
+          <cell r="M466"/>
+          <cell r="N466"/>
+          <cell r="O466"/>
+          <cell r="P466"/>
+          <cell r="Q466"/>
+          <cell r="R466"/>
+          <cell r="S466"/>
+          <cell r="T466"/>
+          <cell r="U466" t="str">
             <v/>
           </cell>
-          <cell r="J455">
-            <v>0</v>
-          </cell>
-          <cell r="K455">
-            <v>0</v>
-          </cell>
-          <cell r="U455" t="str">
+          <cell r="V466">
+            <v>0</v>
+          </cell>
+          <cell r="W466">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="467">
+          <cell r="A467"/>
+          <cell r="B467"/>
+          <cell r="C467"/>
+          <cell r="D467"/>
+          <cell r="E467" t="str">
             <v/>
           </cell>
-          <cell r="V455">
-            <v>0</v>
-          </cell>
-          <cell r="W455">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="456">
-          <cell r="E456" t="str">
+          <cell r="F467"/>
+          <cell r="G467"/>
+          <cell r="H467"/>
+          <cell r="I467"/>
+          <cell r="J467">
+            <v>0</v>
+          </cell>
+          <cell r="K467">
+            <v>0</v>
+          </cell>
+          <cell r="L467"/>
+          <cell r="M467"/>
+          <cell r="N467"/>
+          <cell r="O467"/>
+          <cell r="P467"/>
+          <cell r="Q467"/>
+          <cell r="R467"/>
+          <cell r="S467"/>
+          <cell r="T467"/>
+          <cell r="U467" t="str">
             <v/>
           </cell>
-          <cell r="J456">
-            <v>0</v>
-          </cell>
-          <cell r="K456">
-            <v>0</v>
-          </cell>
-          <cell r="U456" t="str">
+          <cell r="V467">
+            <v>0</v>
+          </cell>
+          <cell r="W467">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="468">
+          <cell r="A468"/>
+          <cell r="B468"/>
+          <cell r="C468"/>
+          <cell r="D468"/>
+          <cell r="E468" t="str">
             <v/>
           </cell>
-          <cell r="V456">
-            <v>0</v>
-          </cell>
-          <cell r="W456">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="457">
-          <cell r="E457" t="str">
+          <cell r="F468"/>
+          <cell r="G468"/>
+          <cell r="H468"/>
+          <cell r="I468"/>
+          <cell r="J468">
+            <v>0</v>
+          </cell>
+          <cell r="K468">
+            <v>0</v>
+          </cell>
+          <cell r="L468"/>
+          <cell r="M468"/>
+          <cell r="N468"/>
+          <cell r="O468"/>
+          <cell r="P468"/>
+          <cell r="Q468"/>
+          <cell r="R468"/>
+          <cell r="S468"/>
+          <cell r="T468"/>
+          <cell r="U468" t="str">
             <v/>
           </cell>
-          <cell r="J457">
-            <v>0</v>
-          </cell>
-          <cell r="K457">
-            <v>0</v>
-          </cell>
-          <cell r="U457" t="str">
+          <cell r="V468">
+            <v>0</v>
+          </cell>
+          <cell r="W468">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="469">
+          <cell r="A469"/>
+          <cell r="B469"/>
+          <cell r="C469"/>
+          <cell r="D469"/>
+          <cell r="E469" t="str">
             <v/>
           </cell>
-          <cell r="V457">
-            <v>0</v>
-          </cell>
-          <cell r="W457">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="458">
-          <cell r="E458" t="str">
+          <cell r="F469"/>
+          <cell r="G469"/>
+          <cell r="H469"/>
+          <cell r="I469"/>
+          <cell r="J469">
+            <v>0</v>
+          </cell>
+          <cell r="K469">
+            <v>0</v>
+          </cell>
+          <cell r="L469"/>
+          <cell r="M469"/>
+          <cell r="N469"/>
+          <cell r="O469"/>
+          <cell r="P469"/>
+          <cell r="Q469"/>
+          <cell r="R469"/>
+          <cell r="S469"/>
+          <cell r="T469"/>
+          <cell r="U469" t="str">
             <v/>
           </cell>
-          <cell r="J458">
-            <v>0</v>
-          </cell>
-          <cell r="K458">
-            <v>0</v>
-          </cell>
-          <cell r="U458" t="str">
+          <cell r="V469">
+            <v>0</v>
+          </cell>
+          <cell r="W469">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="470">
+          <cell r="A470"/>
+          <cell r="B470"/>
+          <cell r="C470"/>
+          <cell r="D470"/>
+          <cell r="E470" t="str">
             <v/>
           </cell>
-          <cell r="V458">
-            <v>0</v>
-          </cell>
-          <cell r="W458">
+          <cell r="F470"/>
+          <cell r="G470"/>
+          <cell r="H470"/>
+          <cell r="I470"/>
+          <cell r="J470">
+            <v>0</v>
+          </cell>
+          <cell r="K470">
+            <v>0</v>
+          </cell>
+          <cell r="L470"/>
+          <cell r="M470"/>
+          <cell r="N470"/>
+          <cell r="O470"/>
+          <cell r="P470"/>
+          <cell r="Q470"/>
+          <cell r="R470"/>
+          <cell r="S470"/>
+          <cell r="T470"/>
+          <cell r="U470" t="str">
+            <v/>
+          </cell>
+          <cell r="V470">
+            <v>0</v>
+          </cell>
+          <cell r="W470">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="471">
+          <cell r="A471"/>
+          <cell r="B471"/>
+          <cell r="C471"/>
+          <cell r="D471"/>
+          <cell r="E471" t="str">
+            <v/>
+          </cell>
+          <cell r="F471"/>
+          <cell r="G471"/>
+          <cell r="H471"/>
+          <cell r="I471"/>
+          <cell r="J471">
+            <v>0</v>
+          </cell>
+          <cell r="K471">
+            <v>0</v>
+          </cell>
+          <cell r="L471"/>
+          <cell r="M471"/>
+          <cell r="N471"/>
+          <cell r="O471"/>
+          <cell r="P471"/>
+          <cell r="Q471"/>
+          <cell r="R471"/>
+          <cell r="S471"/>
+          <cell r="T471"/>
+          <cell r="U471" t="str">
+            <v/>
+          </cell>
+          <cell r="V471">
+            <v>0</v>
+          </cell>
+          <cell r="W471">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="472">
+          <cell r="A472"/>
+          <cell r="B472"/>
+          <cell r="C472"/>
+          <cell r="D472"/>
+          <cell r="E472" t="str">
+            <v/>
+          </cell>
+          <cell r="F472"/>
+          <cell r="G472"/>
+          <cell r="H472"/>
+          <cell r="I472"/>
+          <cell r="J472">
+            <v>0</v>
+          </cell>
+          <cell r="K472">
+            <v>0</v>
+          </cell>
+          <cell r="L472"/>
+          <cell r="M472"/>
+          <cell r="N472"/>
+          <cell r="O472"/>
+          <cell r="P472"/>
+          <cell r="Q472"/>
+          <cell r="R472"/>
+          <cell r="S472"/>
+          <cell r="T472"/>
+          <cell r="U472" t="str">
+            <v/>
+          </cell>
+          <cell r="V472">
+            <v>0</v>
+          </cell>
+          <cell r="W472">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="473">
+          <cell r="A473"/>
+          <cell r="B473"/>
+          <cell r="C473"/>
+          <cell r="D473"/>
+          <cell r="E473" t="str">
+            <v/>
+          </cell>
+          <cell r="F473"/>
+          <cell r="G473"/>
+          <cell r="H473"/>
+          <cell r="I473"/>
+          <cell r="J473">
+            <v>0</v>
+          </cell>
+          <cell r="K473">
+            <v>0</v>
+          </cell>
+          <cell r="L473"/>
+          <cell r="M473"/>
+          <cell r="N473"/>
+          <cell r="O473"/>
+          <cell r="P473"/>
+          <cell r="Q473"/>
+          <cell r="R473"/>
+          <cell r="S473"/>
+          <cell r="T473"/>
+          <cell r="U473" t="str">
+            <v/>
+          </cell>
+          <cell r="V473">
+            <v>0</v>
+          </cell>
+          <cell r="W473">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="474">
+          <cell r="A474"/>
+          <cell r="B474"/>
+          <cell r="C474"/>
+          <cell r="D474"/>
+          <cell r="E474" t="str">
+            <v/>
+          </cell>
+          <cell r="F474"/>
+          <cell r="G474"/>
+          <cell r="H474"/>
+          <cell r="I474"/>
+          <cell r="J474">
+            <v>0</v>
+          </cell>
+          <cell r="K474">
+            <v>0</v>
+          </cell>
+          <cell r="L474"/>
+          <cell r="M474"/>
+          <cell r="N474"/>
+          <cell r="O474"/>
+          <cell r="P474"/>
+          <cell r="Q474"/>
+          <cell r="R474"/>
+          <cell r="S474"/>
+          <cell r="T474"/>
+          <cell r="U474" t="str">
+            <v/>
+          </cell>
+          <cell r="V474">
+            <v>0</v>
+          </cell>
+          <cell r="W474">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="475">
+          <cell r="A475"/>
+          <cell r="B475"/>
+          <cell r="C475"/>
+          <cell r="D475"/>
+          <cell r="E475" t="str">
+            <v/>
+          </cell>
+          <cell r="F475"/>
+          <cell r="G475"/>
+          <cell r="H475"/>
+          <cell r="I475"/>
+          <cell r="J475">
+            <v>0</v>
+          </cell>
+          <cell r="K475">
+            <v>0</v>
+          </cell>
+          <cell r="L475"/>
+          <cell r="M475"/>
+          <cell r="N475"/>
+          <cell r="O475"/>
+          <cell r="P475"/>
+          <cell r="Q475"/>
+          <cell r="R475"/>
+          <cell r="S475"/>
+          <cell r="T475"/>
+          <cell r="U475" t="str">
+            <v/>
+          </cell>
+          <cell r="V475">
+            <v>0</v>
+          </cell>
+          <cell r="W475">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="476">
+          <cell r="A476"/>
+          <cell r="B476"/>
+          <cell r="C476"/>
+          <cell r="D476"/>
+          <cell r="E476" t="str">
+            <v/>
+          </cell>
+          <cell r="F476"/>
+          <cell r="G476"/>
+          <cell r="H476"/>
+          <cell r="I476"/>
+          <cell r="J476">
+            <v>0</v>
+          </cell>
+          <cell r="K476">
+            <v>0</v>
+          </cell>
+          <cell r="L476"/>
+          <cell r="M476"/>
+          <cell r="N476"/>
+          <cell r="O476"/>
+          <cell r="P476"/>
+          <cell r="Q476"/>
+          <cell r="R476"/>
+          <cell r="S476"/>
+          <cell r="T476"/>
+          <cell r="U476" t="str">
+            <v/>
+          </cell>
+          <cell r="V476">
+            <v>0</v>
+          </cell>
+          <cell r="W476">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="477">
+          <cell r="A477"/>
+          <cell r="B477"/>
+          <cell r="C477"/>
+          <cell r="D477"/>
+          <cell r="E477" t="str">
+            <v/>
+          </cell>
+          <cell r="F477"/>
+          <cell r="G477"/>
+          <cell r="H477"/>
+          <cell r="I477"/>
+          <cell r="J477">
+            <v>0</v>
+          </cell>
+          <cell r="K477">
+            <v>0</v>
+          </cell>
+          <cell r="L477"/>
+          <cell r="M477"/>
+          <cell r="N477"/>
+          <cell r="O477"/>
+          <cell r="P477"/>
+          <cell r="Q477"/>
+          <cell r="R477"/>
+          <cell r="S477"/>
+          <cell r="T477"/>
+          <cell r="U477" t="str">
+            <v/>
+          </cell>
+          <cell r="V477">
+            <v>0</v>
+          </cell>
+          <cell r="W477">
             <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-      <sheetData sheetId="42" refreshError="1"/>
-      <sheetData sheetId="43" refreshError="1"/>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
-      <sheetData sheetId="46" refreshError="1"/>
-      <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48" refreshError="1"/>
-      <sheetData sheetId="49" refreshError="1"/>
-      <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51" refreshError="1"/>
-      <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53" refreshError="1"/>
-      <sheetData sheetId="54" refreshError="1"/>
-      <sheetData sheetId="55" refreshError="1"/>
-      <sheetData sheetId="56" refreshError="1"/>
-      <sheetData sheetId="57" refreshError="1"/>
-      <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60" refreshError="1"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
-      <sheetData sheetId="65" refreshError="1"/>
-      <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67" refreshError="1"/>
-      <sheetData sheetId="68" refreshError="1"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
-      <sheetData sheetId="71" refreshError="1"/>
-      <sheetData sheetId="72" refreshError="1"/>
-      <sheetData sheetId="73" refreshError="1"/>
-      <sheetData sheetId="74" refreshError="1"/>
-      <sheetData sheetId="75" refreshError="1"/>
-      <sheetData sheetId="76" refreshError="1"/>
-      <sheetData sheetId="77" refreshError="1"/>
-      <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
-      <sheetData sheetId="80" refreshError="1"/>
-      <sheetData sheetId="81" refreshError="1"/>
-      <sheetData sheetId="82" refreshError="1"/>
-      <sheetData sheetId="83" refreshError="1"/>
-      <sheetData sheetId="84" refreshError="1"/>
-      <sheetData sheetId="85" refreshError="1"/>
-      <sheetData sheetId="86" refreshError="1"/>
-      <sheetData sheetId="87" refreshError="1"/>
-      <sheetData sheetId="88" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="1">
+          <cell r="A1"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+      <sheetData sheetId="48"/>
+      <sheetData sheetId="49"/>
+      <sheetData sheetId="50"/>
+      <sheetData sheetId="51"/>
+      <sheetData sheetId="52"/>
+      <sheetData sheetId="53"/>
+      <sheetData sheetId="54"/>
+      <sheetData sheetId="55"/>
+      <sheetData sheetId="56"/>
+      <sheetData sheetId="57"/>
+      <sheetData sheetId="58"/>
+      <sheetData sheetId="59"/>
+      <sheetData sheetId="60"/>
+      <sheetData sheetId="61"/>
+      <sheetData sheetId="62"/>
+      <sheetData sheetId="63"/>
+      <sheetData sheetId="64"/>
+      <sheetData sheetId="65"/>
+      <sheetData sheetId="66"/>
+      <sheetData sheetId="67"/>
+      <sheetData sheetId="68"/>
+      <sheetData sheetId="69"/>
+      <sheetData sheetId="70"/>
+      <sheetData sheetId="71"/>
+      <sheetData sheetId="72"/>
+      <sheetData sheetId="73"/>
+      <sheetData sheetId="74"/>
+      <sheetData sheetId="75"/>
+      <sheetData sheetId="76"/>
+      <sheetData sheetId="77"/>
+      <sheetData sheetId="78"/>
+      <sheetData sheetId="79"/>
+      <sheetData sheetId="80"/>
+      <sheetData sheetId="81"/>
+      <sheetData sheetId="82"/>
+      <sheetData sheetId="83"/>
+      <sheetData sheetId="84"/>
+      <sheetData sheetId="85"/>
+      <sheetData sheetId="86"/>
+      <sheetData sheetId="87"/>
+      <sheetData sheetId="88"/>
       <sheetData sheetId="89"/>
-      <sheetData sheetId="90" refreshError="1"/>
-      <sheetData sheetId="91">
+      <sheetData sheetId="90"/>
+      <sheetData sheetId="91"/>
+      <sheetData sheetId="92"/>
+      <sheetData sheetId="93"/>
+      <sheetData sheetId="94"/>
+      <sheetData sheetId="95"/>
+      <sheetData sheetId="96"/>
+      <sheetData sheetId="97"/>
+      <sheetData sheetId="98">
         <row r="1">
           <cell r="F1" t="str">
             <v>No_Item</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="92" refreshError="1"/>
-      <sheetData sheetId="93" refreshError="1"/>
-      <sheetData sheetId="94" refreshError="1"/>
-      <sheetData sheetId="95" refreshError="1"/>
-      <sheetData sheetId="96"/>
-      <sheetData sheetId="97" refreshError="1"/>
-      <sheetData sheetId="98" refreshError="1"/>
       <sheetData sheetId="99"/>
-      <sheetData sheetId="100" refreshError="1"/>
-      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="100"/>
+      <sheetData sheetId="101"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
+      <sheetData sheetId="172" refreshError="1"/>
+      <sheetData sheetId="173" refreshError="1"/>
+      <sheetData sheetId="174" refreshError="1"/>
+      <sheetData sheetId="175" refreshError="1"/>
+      <sheetData sheetId="176" refreshError="1"/>
+      <sheetData sheetId="177" refreshError="1"/>
+      <sheetData sheetId="178" refreshError="1"/>
+      <sheetData sheetId="179" refreshError="1"/>
+      <sheetData sheetId="180" refreshError="1"/>
+      <sheetData sheetId="181" refreshError="1"/>
+      <sheetData sheetId="182" refreshError="1"/>
+      <sheetData sheetId="183" refreshError="1"/>
+      <sheetData sheetId="184" refreshError="1"/>
+      <sheetData sheetId="185" refreshError="1"/>
+      <sheetData sheetId="186" refreshError="1"/>
+      <sheetData sheetId="187" refreshError="1"/>
+      <sheetData sheetId="188" refreshError="1"/>
+      <sheetData sheetId="189" refreshError="1"/>
+      <sheetData sheetId="190" refreshError="1"/>
+      <sheetData sheetId="191" refreshError="1"/>
+      <sheetData sheetId="192" refreshError="1"/>
+      <sheetData sheetId="193" refreshError="1"/>
+      <sheetData sheetId="194" refreshError="1"/>
+      <sheetData sheetId="195" refreshError="1"/>
+      <sheetData sheetId="196" refreshError="1"/>
+      <sheetData sheetId="197" refreshError="1"/>
+      <sheetData sheetId="198" refreshError="1"/>
+      <sheetData sheetId="199" refreshError="1"/>
+      <sheetData sheetId="200" refreshError="1"/>
+      <sheetData sheetId="201" refreshError="1"/>
+      <sheetData sheetId="202" refreshError="1"/>
+      <sheetData sheetId="203" refreshError="1"/>
+      <sheetData sheetId="204" refreshError="1"/>
+      <sheetData sheetId="205" refreshError="1"/>
+      <sheetData sheetId="206" refreshError="1"/>
+      <sheetData sheetId="207" refreshError="1"/>
+      <sheetData sheetId="208" refreshError="1"/>
+      <sheetData sheetId="209" refreshError="1"/>
+      <sheetData sheetId="210" refreshError="1"/>
+      <sheetData sheetId="211" refreshError="1"/>
+      <sheetData sheetId="212" refreshError="1"/>
+      <sheetData sheetId="213" refreshError="1"/>
+      <sheetData sheetId="214" refreshError="1"/>
+      <sheetData sheetId="215" refreshError="1"/>
+      <sheetData sheetId="216" refreshError="1"/>
+      <sheetData sheetId="217" refreshError="1"/>
+      <sheetData sheetId="218" refreshError="1"/>
+      <sheetData sheetId="219" refreshError="1"/>
+      <sheetData sheetId="220" refreshError="1"/>
+      <sheetData sheetId="221" refreshError="1"/>
+      <sheetData sheetId="222" refreshError="1"/>
+      <sheetData sheetId="223" refreshError="1"/>
+      <sheetData sheetId="224" refreshError="1"/>
+      <sheetData sheetId="225" refreshError="1"/>
+      <sheetData sheetId="226" refreshError="1"/>
+      <sheetData sheetId="227" refreshError="1"/>
+      <sheetData sheetId="228" refreshError="1"/>
+      <sheetData sheetId="229" refreshError="1"/>
+      <sheetData sheetId="230" refreshError="1"/>
+      <sheetData sheetId="231" refreshError="1"/>
+      <sheetData sheetId="232" refreshError="1"/>
+      <sheetData sheetId="233" refreshError="1"/>
+      <sheetData sheetId="234" refreshError="1"/>
+      <sheetData sheetId="235" refreshError="1"/>
+      <sheetData sheetId="236" refreshError="1"/>
+      <sheetData sheetId="237" refreshError="1"/>
+      <sheetData sheetId="238" refreshError="1"/>
+      <sheetData sheetId="239" refreshError="1"/>
+      <sheetData sheetId="240" refreshError="1"/>
+      <sheetData sheetId="241" refreshError="1"/>
+      <sheetData sheetId="242" refreshError="1"/>
+      <sheetData sheetId="243" refreshError="1"/>
+      <sheetData sheetId="244" refreshError="1"/>
+      <sheetData sheetId="245" refreshError="1"/>
+      <sheetData sheetId="246" refreshError="1"/>
+      <sheetData sheetId="247" refreshError="1"/>
+      <sheetData sheetId="248" refreshError="1"/>
+      <sheetData sheetId="249" refreshError="1"/>
+      <sheetData sheetId="250" refreshError="1"/>
+      <sheetData sheetId="251" refreshError="1"/>
+      <sheetData sheetId="252" refreshError="1"/>
+      <sheetData sheetId="253" refreshError="1"/>
+      <sheetData sheetId="254" refreshError="1"/>
+      <sheetData sheetId="255" refreshError="1"/>
+      <sheetData sheetId="256" refreshError="1"/>
+      <sheetData sheetId="257" refreshError="1"/>
+      <sheetData sheetId="258" refreshError="1"/>
+      <sheetData sheetId="259" refreshError="1"/>
+      <sheetData sheetId="260" refreshError="1"/>
+      <sheetData sheetId="261" refreshError="1"/>
+      <sheetData sheetId="262" refreshError="1"/>
+      <sheetData sheetId="263" refreshError="1"/>
+      <sheetData sheetId="264" refreshError="1"/>
+      <sheetData sheetId="265" refreshError="1"/>
+      <sheetData sheetId="266" refreshError="1"/>
+      <sheetData sheetId="267" refreshError="1"/>
+      <sheetData sheetId="268" refreshError="1"/>
+      <sheetData sheetId="269" refreshError="1"/>
+      <sheetData sheetId="270" refreshError="1"/>
+      <sheetData sheetId="271" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -34530,23 +36795,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="34" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="33" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -34591,7 +36856,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46164.418156597225</v>
+        <v>46168.374173958335</v>
       </c>
       <c r="D1" s="77" t="s">
         <v>1</v>
@@ -35940,23 +38205,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -36001,7 +38266,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46164.418156597225</v>
+        <v>46168.374173958335</v>
       </c>
       <c r="D1" s="77" t="s">
         <v>1</v>
@@ -37408,23 +39673,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -37469,7 +39734,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46164.418156481479</v>
+        <v>46168.374173958335</v>
       </c>
       <c r="D1" s="77" t="s">
         <v>1</v>
@@ -38842,23 +41107,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -38902,7 +41167,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46164.418156250002</v>
+        <v>46168.374173958335</v>
       </c>
       <c r="D1" s="77" t="s">
         <v>1</v>
@@ -39114,347 +41379,242 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18" t="e">
-        <f>VLOOKUP(A7,'[2]master plan'!A:C,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C7" s="19" t="e">
-        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,5,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D7" s="20" t="e">
-        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E7" s="21" t="e">
-        <f>VLOOKUP(A7,'[2]master plan'!A:G,7,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F7" s="22" t="e">
-        <f>VLOOKUP(A7,'[2]master plan'!A:H,8,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G7" s="23" t="e">
-        <f>VLOOKUP(A7,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H7" s="24" t="e">
-        <f>VLOOKUP(A7,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I7" s="25" t="e">
-        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,12,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J7" s="25" t="e">
-        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,13,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K7" s="25" t="e">
-        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,14,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L7" s="26"/>
-      <c r="M7" s="27"/>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46167.440663078705</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8">
+        <v>7</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="9"/>
       <c r="N7" s="28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A7,'[2]master plan'!A:R,18,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18" t="e">
-        <f>VLOOKUP(A8,'[2]master plan'!A:C,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C8" s="19" t="e">
-        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,5,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D8" s="20" t="e">
-        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E8" s="21" t="e">
-        <f>VLOOKUP(A8,'[2]master plan'!A:G,7,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F8" s="22" t="e">
-        <f>VLOOKUP(A8,'[2]master plan'!A:H,8,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G8" s="23" t="e">
-        <f>VLOOKUP(A8,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H8" s="24" t="e">
-        <f>VLOOKUP(A8,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I8" s="25" t="e">
-        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,12,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J8" s="25" t="e">
-        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,13,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K8" s="25" t="e">
-        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,14,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L8" s="26"/>
-      <c r="M8" s="27"/>
+      <c r="A8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>15</v>
+      </c>
       <c r="N8" s="28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A8,'[2]master plan'!A:R,18,0),"")</f>
-        <v/>
+        <v>Ngày gửi Lab</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18" t="e">
-        <f>VLOOKUP(A9,'[2]master plan'!A:C,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C9" s="19" t="e">
-        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,5,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D9" s="20" t="e">
-        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E9" s="21" t="e">
-        <f>VLOOKUP(A9,'[2]master plan'!A:G,7,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F9" s="22" t="e">
-        <f>VLOOKUP(A9,'[2]master plan'!A:H,8,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G9" s="23" t="e">
-        <f>VLOOKUP(A9,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H9" s="24" t="e">
-        <f>VLOOKUP(A9,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I9" s="25" t="e">
-        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,12,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J9" s="25" t="e">
-        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,13,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K9" s="25" t="e">
-        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,14,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L9" s="26"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="28" t="str">
+      <c r="A9" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9" s="22">
+        <v>15</v>
+      </c>
+      <c r="G9" s="23">
+        <v>2</v>
+      </c>
+      <c r="H9" s="24">
+        <v>2</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="26">
+        <v>2</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="28">
+        <v>46169</v>
+      </c>
+      <c r="N9" s="28">
         <f>_xlfn.IFNA(VLOOKUP(A9,'[2]master plan'!A:R,18,0),"")</f>
-        <v/>
+        <v>46169</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18" t="e">
-        <f>VLOOKUP(A10,'[2]master plan'!A:C,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C10" s="19" t="e">
-        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,5,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D10" s="20" t="e">
-        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E10" s="21" t="e">
-        <f>VLOOKUP(A10,'[2]master plan'!A:G,7,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F10" s="22" t="e">
-        <f>VLOOKUP(A10,'[2]master plan'!A:H,8,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G10" s="23" t="e">
-        <f>VLOOKUP(A10,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H10" s="24" t="e">
-        <f>VLOOKUP(A10,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I10" s="25" t="e">
-        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,12,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J10" s="25" t="e">
-        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,13,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K10" s="25" t="e">
-        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,14,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L10" s="26"/>
-      <c r="M10" s="40"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="76"/>
       <c r="N10" s="28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A10,'[2]master plan'!A:R,18,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18" t="e">
-        <f>VLOOKUP(A11,'[2]master plan'!A:C,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C11" s="19" t="e">
-        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,5,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D11" s="20" t="e">
-        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E11" s="21" t="e">
-        <f>VLOOKUP(A11,'[2]master plan'!A:G,7,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F11" s="22" t="e">
-        <f>VLOOKUP(A11,'[2]master plan'!A:H,8,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G11" s="23" t="e">
-        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H11" s="24" t="e">
-        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I11" s="25" t="e">
-        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,12,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J11" s="25" t="e">
-        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,13,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K11" s="25" t="e">
-        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,14,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L11" s="26"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="28" t="str">
+      <c r="A11" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="22">
+        <v>100</v>
+      </c>
+      <c r="G11" s="23">
+        <v>3</v>
+      </c>
+      <c r="H11" s="24">
+        <v>3</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="26">
+        <v>3</v>
+      </c>
+      <c r="L11" s="27"/>
+      <c r="M11" s="28">
+        <v>46169</v>
+      </c>
+      <c r="N11" s="28">
         <f>_xlfn.IFNA(VLOOKUP(A11,'[2]master plan'!A:R,18,0),"")</f>
-        <v/>
+        <v>46169</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18" t="e">
-        <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C12" s="19" t="e">
-        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,5,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D12" s="20" t="e">
-        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E12" s="21" t="e">
-        <f>VLOOKUP(A12,'[2]master plan'!A:G,7,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F12" s="22" t="e">
-        <f>VLOOKUP(A12,'[2]master plan'!A:H,8,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G12" s="23" t="e">
-        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H12" s="24" t="e">
-        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I12" s="25" t="e">
-        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,12,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J12" s="25" t="e">
-        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,13,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K12" s="25" t="e">
-        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,14,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L12" s="26"/>
-      <c r="M12" s="27"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="76"/>
       <c r="N12" s="28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A12,'[2]master plan'!A:R,18,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18" t="e">
-        <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C13" s="19" t="e">
-        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D13" s="20" t="e">
-        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E13" s="21" t="e">
-        <f>VLOOKUP(A13,'[2]master plan'!A:G,7,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F13" s="22" t="e">
-        <f>VLOOKUP(A13,'[2]master plan'!A:H,8,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G13" s="23" t="e">
-        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H13" s="24" t="e">
-        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I13" s="25" t="e">
-        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J13" s="25" t="e">
-        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K13" s="25" t="e">
-        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L13" s="26"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="28" t="str">
+      <c r="A13" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="F13" s="22">
+        <v>20</v>
+      </c>
+      <c r="G13" s="23">
+        <v>2</v>
+      </c>
+      <c r="H13" s="24">
+        <v>2</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="26">
+        <v>2</v>
+      </c>
+      <c r="L13" s="40"/>
+      <c r="M13" s="28">
+        <v>46169</v>
+      </c>
+      <c r="N13" s="28">
         <f>_xlfn.IFNA(VLOOKUP(A13,'[2]master plan'!A:R,18,0),"")</f>
-        <v/>
+        <v>46169</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -40213,19 +42373,1426 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E18" name="Range1_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E6 E14:E18" name="Range1_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E9:E13" name="Range1_1_1"/>
   </protectedRanges>
   <autoFilter ref="A2:N19" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}"/>
+  <mergeCells count="2">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D7:F7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A6 A14:A18">
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:A13">
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:A1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C6 C14:C1048576">
+    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C13">
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8:L8">
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="19" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C923CD7D-34C5-42FC-9669-845822F69DA3}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:N665"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="152.81640625" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46168.374173958335</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>28</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="22">
+        <v>30</v>
+      </c>
+      <c r="G3" s="23">
+        <v>3</v>
+      </c>
+      <c r="H3" s="24">
+        <v>3</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="26">
+        <v>3</v>
+      </c>
+      <c r="M3" s="27"/>
+      <c r="N3" s="28">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="79"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="28"/>
+    </row>
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F5" s="22">
+        <v>100</v>
+      </c>
+      <c r="G5" s="23">
+        <v>5</v>
+      </c>
+      <c r="H5" s="24">
+        <v>5</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="26">
+        <v>13</v>
+      </c>
+      <c r="M5" s="27"/>
+      <c r="N5" s="28">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="22">
+        <v>20</v>
+      </c>
+      <c r="G6" s="23">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24">
+        <v>1</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="26"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="28">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="78" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="F7" s="22">
+        <v>10</v>
+      </c>
+      <c r="G7" s="23">
+        <v>2</v>
+      </c>
+      <c r="H7" s="24">
+        <v>2</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="26"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="28">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="78" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="22">
+        <v>50</v>
+      </c>
+      <c r="G8" s="23">
+        <v>5</v>
+      </c>
+      <c r="H8" s="24">
+        <v>5</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="26"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="28">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="79"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="28"/>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="78" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" s="22">
+        <v>50</v>
+      </c>
+      <c r="G10" s="23">
+        <v>2</v>
+      </c>
+      <c r="H10" s="24">
+        <v>2</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="L10" s="26">
+        <v>4</v>
+      </c>
+      <c r="M10" s="27"/>
+      <c r="N10" s="28">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="78" t="s">
+        <v>277</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11" s="22">
+        <v>50</v>
+      </c>
+      <c r="G11" s="23">
+        <v>2</v>
+      </c>
+      <c r="H11" s="24">
+        <v>2</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="26"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="28">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="79"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="28"/>
+    </row>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="78" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="22">
+        <v>100</v>
+      </c>
+      <c r="G13" s="23">
+        <v>5</v>
+      </c>
+      <c r="H13" s="24">
+        <v>5</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" s="26">
+        <v>5</v>
+      </c>
+      <c r="M13" s="40"/>
+      <c r="N13" s="28">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="79"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="28"/>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="78" t="s">
+        <v>283</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" s="22">
+        <v>30</v>
+      </c>
+      <c r="G15" s="23">
+        <v>3</v>
+      </c>
+      <c r="H15" s="24">
+        <v>3</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="26">
+        <v>3</v>
+      </c>
+      <c r="M15" s="27"/>
+      <c r="N15" s="28">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C16" s="19" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="20" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="21" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="22" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="23" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H16" s="24" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L16" s="26"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A16,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C17" s="19" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="20" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="21" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="22" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="23" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H17" s="24" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="19" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="20" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="21" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="22" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="23" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H18" s="24" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A18,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="19" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="20" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="21" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F19" s="22" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="23" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H19" s="24" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="19" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="20" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="21" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="22" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="23" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="24" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="19" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="20" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="21" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="22" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="23" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="24" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="26"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A21,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="51"/>
+    </row>
+    <row r="23" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L23" s="56"/>
+    </row>
+    <row r="24" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="56"/>
+    </row>
+    <row r="26" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="55"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="58"/>
+    </row>
+    <row r="27" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="56"/>
+    </row>
+    <row r="28" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L28" s="56"/>
+    </row>
+    <row r="29" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="58"/>
+    </row>
+    <row r="30" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="665" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A665" s="2"/>
+      <c r="B665" s="52"/>
+      <c r="C665" s="2"/>
+      <c r="D665" s="2"/>
+      <c r="E665" s="60"/>
+      <c r="H665" s="55"/>
+      <c r="I665" s="53"/>
+      <c r="J665" s="53"/>
+      <c r="K665" s="53"/>
+      <c r="L665" s="61"/>
+      <c r="M665" s="57"/>
+      <c r="N665" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E21" name="Range1_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="A13:A15 A3:A10" name="Range1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="A11:A12" name="Range1_2"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N22" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="RPRO-260525-0001"/>
+        <filter val="RPRO-260525-0002"/>
+        <filter val="RPRO-260525-0003"/>
+        <filter val="RPRO-260525-0004"/>
+        <filter val="RPRO-260525-0005"/>
+        <filter val="RPRO-260525-0006"/>
+        <filter val="RPRO-260525-0007"/>
+        <filter val="RPRO-260525-0008"/>
+        <filter val="RPRO-260525-0009"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A18">
+  <conditionalFormatting sqref="A3:A15">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:A21">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:A1048576">
+  <conditionalFormatting sqref="A24:A1048576">
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
@@ -40240,12 +43807,12 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
-  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="29" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="19" max="15" man="1"/>
+    <brk id="22" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08481B9F-BFF0-4955-8A0E-BE6A8A15391F}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC64ABE-46D3-4F48-8D3B-04C5A1BCF438}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="8" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,14 @@
     <sheet name="25.5" sheetId="6" r:id="rId6"/>
     <sheet name="27.5" sheetId="7" r:id="rId7"/>
     <sheet name="29.5 - L2" sheetId="8" r:id="rId8"/>
+    <sheet name="1.6" sheetId="9" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'13.5'!$A$2:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'15.5'!$A$2:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'18.5'!$A$2:$N$3</definedName>
@@ -35,6 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'25.5'!$A$2:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'27.5'!$A$2:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$25</definedName>
+    <definedName name="AE" localSheetId="8">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="2">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -43,6 +46,7 @@
     <definedName name="AE" localSheetId="5">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="6">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="7">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'1.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'18.5'!$A$1:$N$29</definedName>
@@ -51,6 +55,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'25.5'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'27.5'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'29.5 - L2'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'1.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'18.5'!$1:$2</definedName>
@@ -59,6 +64,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'25.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'27.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -67,6 +73,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -75,6 +82,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -83,6 +91,7 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -91,6 +100,7 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -99,6 +109,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -107,6 +118,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="8" hidden="1">'1.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="2" hidden="1">'18.5'!#REF!</definedName>
@@ -115,6 +127,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="5" hidden="1">'25.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="6" hidden="1">'27.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="7" hidden="1">'29.5 - L2'!#REF!</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -123,6 +136,7 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
@@ -131,6 +145,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -139,6 +154,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -147,6 +163,7 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -155,6 +172,7 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -163,6 +181,7 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
@@ -171,6 +190,7 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -179,6 +199,7 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -187,6 +208,7 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
@@ -195,6 +217,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -203,6 +226,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -211,6 +235,7 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -219,6 +244,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -249,7 +275,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="378">
   <si>
     <t>Release Date</t>
   </si>
@@ -1393,6 +1419,75 @@
   <si>
     <t>OrthoLite Regular NEUTRAL GRAY/17-4402TPX Flat Sheet 0.15D 45+/-4 Asker C 1.1M 1.7M 9.8mm</t>
   </si>
+  <si>
+    <t>S-2026-05-102</t>
+  </si>
+  <si>
+    <t>RPRO-260601-0847</t>
+  </si>
+  <si>
+    <t>S-2026-05-103</t>
+  </si>
+  <si>
+    <t>RPRO-260601-0848</t>
+  </si>
+  <si>
+    <t>PVN-002973</t>
+  </si>
+  <si>
+    <t>UltraLite-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</t>
+  </si>
+  <si>
+    <t>S-2026-05-104</t>
+  </si>
+  <si>
+    <t>RPRO-260601-0849</t>
+  </si>
+  <si>
+    <t>PVN-002465</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 5mm</t>
+  </si>
+  <si>
+    <t>S-2026-05-105</t>
+  </si>
+  <si>
+    <t>RPRO-260601-0850</t>
+  </si>
+  <si>
+    <t>PVN-003630</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 2mm</t>
+  </si>
+  <si>
+    <t>UNDER ARMOUR</t>
+  </si>
+  <si>
+    <t>SSO-2606-00021    - URGENT (6-8)</t>
+  </si>
+  <si>
+    <t>S-2026-05-106</t>
+  </si>
+  <si>
+    <t>RPRO-260601-0851</t>
+  </si>
+  <si>
+    <t>BDB-000180</t>
+  </si>
+  <si>
+    <t>PVN-003236</t>
+  </si>
+  <si>
+    <t>OrthoLite Eco LT-Hybrid-Converse SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 5mm</t>
+  </si>
+  <si>
+    <t>CONVERSE</t>
+  </si>
+  <si>
+    <t>Die cut</t>
+  </si>
 </sst>
 </file>
 
@@ -1993,7 +2088,77 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2794,6 +2959,7 @@
       <sheetName val="12.5"/>
       <sheetName val="13.5"/>
       <sheetName val="15.5"/>
+      <sheetName val="BCN 1.6"/>
       <sheetName val="18.5"/>
       <sheetName val="20.5"/>
       <sheetName val="21.5"/>
@@ -2801,13 +2967,15 @@
       <sheetName val="25.5"/>
       <sheetName val="27.5"/>
       <sheetName val="29.5"/>
-      <sheetName val="form 2 (14)"/>
+      <sheetName val="29.5 - L2"/>
+      <sheetName val="1.6"/>
+      <sheetName val="form 2 (16)"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
-      <sheetName val="29.5 - L2"/>
+      <sheetName val="form 2 (14)"/>
       <sheetName val="form 2 (15)"/>
       <sheetName val="MỚI (2)"/>
       <sheetName val="Sheet1"/>
@@ -34345,10 +34513,10 @@
             <v>100</v>
           </cell>
           <cell r="J462">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="K462">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="L462" t="str">
             <v>ADIDAS</v>
@@ -34416,10 +34584,10 @@
             <v>100</v>
           </cell>
           <cell r="J463">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="K463">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="L463" t="str">
             <v>ADIDAS</v>
@@ -34724,7 +34892,7 @@
             <v>46176</v>
           </cell>
           <cell r="R467">
-            <v>46173</v>
+            <v>46172</v>
           </cell>
           <cell r="S467">
             <v>6</v>
@@ -34824,7 +34992,7 @@
             <v>PUR2605280001S</v>
           </cell>
           <cell r="E469" t="str">
-            <v/>
+            <v>BDB-000058</v>
           </cell>
           <cell r="F469" t="str">
             <v>PVN-001277</v>
@@ -34842,7 +35010,7 @@
             <v>0</v>
           </cell>
           <cell r="K469">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="L469" t="str">
             <v>ADIDAS</v>
@@ -34871,14 +35039,14 @@
           <cell r="T469">
             <v>7</v>
           </cell>
-          <cell r="U469" t="str">
-            <v/>
+          <cell r="U469">
+            <v>4</v>
           </cell>
           <cell r="V469">
-            <v>0</v>
+            <v>2.8570000000000002E-2</v>
           </cell>
           <cell r="W469">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="470">
@@ -34895,7 +35063,7 @@
             <v>PUR2600502900001S</v>
           </cell>
           <cell r="E470" t="str">
-            <v/>
+            <v>BDB-000123</v>
           </cell>
           <cell r="F470" t="str">
             <v>PVN-003815</v>
@@ -34913,7 +35081,7 @@
             <v>0</v>
           </cell>
           <cell r="K470">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="L470" t="str">
             <v>FOOTJOY</v>
@@ -34942,14 +35110,14 @@
           <cell r="T470">
             <v>6</v>
           </cell>
-          <cell r="U470" t="str">
-            <v/>
+          <cell r="U470">
+            <v>6</v>
           </cell>
           <cell r="V470">
-            <v>0</v>
+            <v>4.3479999999999998E-2</v>
           </cell>
           <cell r="W470">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="471">
@@ -34966,7 +35134,7 @@
             <v>PUR2600502900001S</v>
           </cell>
           <cell r="E471" t="str">
-            <v/>
+            <v>BDB-000314</v>
           </cell>
           <cell r="F471" t="str">
             <v>PVN-004066</v>
@@ -34984,7 +35152,7 @@
             <v>0</v>
           </cell>
           <cell r="K471">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="L471" t="str">
             <v>FOOTJOY</v>
@@ -35013,14 +35181,14 @@
           <cell r="T471">
             <v>7</v>
           </cell>
-          <cell r="U471" t="str">
-            <v/>
+          <cell r="U471">
+            <v>9.5</v>
           </cell>
           <cell r="V471">
-            <v>0</v>
+            <v>7.1429999999999993E-2</v>
           </cell>
           <cell r="W471">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="472">
@@ -35037,7 +35205,7 @@
             <v>PUR2600502900001S</v>
           </cell>
           <cell r="E472" t="str">
-            <v/>
+            <v>BDB-000382</v>
           </cell>
           <cell r="F472" t="str">
             <v>PVN-004363</v>
@@ -35055,7 +35223,7 @@
             <v>0</v>
           </cell>
           <cell r="K472">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="L472" t="str">
             <v>FOOTJOY</v>
@@ -35084,14 +35252,14 @@
           <cell r="T472">
             <v>7</v>
           </cell>
-          <cell r="U472" t="str">
-            <v/>
+          <cell r="U472">
+            <v>9.5</v>
           </cell>
           <cell r="V472">
-            <v>0</v>
+            <v>6.6669999999999993E-2</v>
           </cell>
           <cell r="W472">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="473">
@@ -35108,7 +35276,7 @@
             <v>PUR2600502900001S</v>
           </cell>
           <cell r="E473" t="str">
-            <v/>
+            <v>BDB-000387</v>
           </cell>
           <cell r="F473" t="str">
             <v>PVN-004385</v>
@@ -35126,7 +35294,7 @@
             <v>0</v>
           </cell>
           <cell r="K473">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="L473" t="str">
             <v>FOOTJOY</v>
@@ -35155,14 +35323,14 @@
           <cell r="T473">
             <v>7</v>
           </cell>
-          <cell r="U473" t="str">
-            <v/>
+          <cell r="U473">
+            <v>9.5</v>
           </cell>
           <cell r="V473">
-            <v>0</v>
+            <v>6.6669999999999993E-2</v>
           </cell>
           <cell r="W473">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="474">
@@ -35179,7 +35347,7 @@
             <v>PUR2600502900001S</v>
           </cell>
           <cell r="E474" t="str">
-            <v/>
+            <v>BDB-000378</v>
           </cell>
           <cell r="F474" t="str">
             <v>PVN-004336</v>
@@ -35197,7 +35365,7 @@
             <v>0</v>
           </cell>
           <cell r="K474">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="L474" t="str">
             <v>FOOTJOY</v>
@@ -35226,14 +35394,14 @@
           <cell r="T474">
             <v>7</v>
           </cell>
-          <cell r="U474" t="str">
-            <v/>
+          <cell r="U474">
+            <v>9.8000000000000007</v>
           </cell>
           <cell r="V474">
-            <v>0</v>
+            <v>7.1429999999999993E-2</v>
           </cell>
           <cell r="W474">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="475">
@@ -35250,7 +35418,7 @@
             <v>PUR2600502900001S</v>
           </cell>
           <cell r="E475" t="str">
-            <v/>
+            <v>BDB-000291</v>
           </cell>
           <cell r="F475" t="str">
             <v>PVN-004250</v>
@@ -35268,7 +35436,7 @@
             <v>0</v>
           </cell>
           <cell r="K475">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="L475" t="str">
             <v>FOOTJOY</v>
@@ -35297,14 +35465,14 @@
           <cell r="T475">
             <v>7</v>
           </cell>
-          <cell r="U475" t="str">
-            <v/>
+          <cell r="U475">
+            <v>9.8000000000000007</v>
           </cell>
           <cell r="V475">
-            <v>0</v>
+            <v>7.1429999999999993E-2</v>
           </cell>
           <cell r="W475">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="476">
@@ -35321,7 +35489,7 @@
             <v>PUR2600502900001S</v>
           </cell>
           <cell r="E476" t="str">
-            <v/>
+            <v>BDB-000051</v>
           </cell>
           <cell r="F476" t="str">
             <v>PVN-003324</v>
@@ -35339,7 +35507,7 @@
             <v>0</v>
           </cell>
           <cell r="K476">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="L476" t="str">
             <v>FOOTJOY</v>
@@ -35368,25 +35536,71 @@
           <cell r="T476">
             <v>6</v>
           </cell>
-          <cell r="U476" t="str">
-            <v/>
+          <cell r="U476">
+            <v>7.5</v>
           </cell>
           <cell r="V476">
-            <v>0</v>
+            <v>5.5559999999999998E-2</v>
           </cell>
           <cell r="W476">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="477">
+          <cell r="A477" t="str">
+            <v>S-2026-05-101</v>
+          </cell>
+          <cell r="D477" t="str">
+            <v>PUR-202606010001S</v>
+          </cell>
           <cell r="E477" t="str">
             <v/>
           </cell>
+          <cell r="F477" t="str">
+            <v>PVN-004433</v>
+          </cell>
+          <cell r="G477" t="str">
+            <v>OrthoLite X-30-Hybrid BROWN SUGAR/17-1134TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 15mm</v>
+          </cell>
+          <cell r="H477">
+            <v>10</v>
+          </cell>
+          <cell r="I477">
+            <v>10</v>
+          </cell>
           <cell r="J477">
             <v>0</v>
           </cell>
           <cell r="K477">
             <v>0</v>
+          </cell>
+          <cell r="L477" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M477" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N477" t="str">
+            <v xml:space="preserve">DIE-CUT
+URGENT </v>
+          </cell>
+          <cell r="O477" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P477">
+            <v>46174</v>
+          </cell>
+          <cell r="Q477">
+            <v>46181</v>
+          </cell>
+          <cell r="R477">
+            <v>46178</v>
+          </cell>
+          <cell r="S477">
+            <v>6</v>
+          </cell>
+          <cell r="T477">
+            <v>7</v>
           </cell>
           <cell r="U477" t="str">
             <v/>
@@ -35399,14 +35613,62 @@
           </cell>
         </row>
         <row r="478">
+          <cell r="A478" t="str">
+            <v>S-2026-05-102</v>
+          </cell>
+          <cell r="C478" t="str">
+            <v>RPRO-260601-0847</v>
+          </cell>
+          <cell r="D478" t="str">
+            <v>PUR-202606010001S</v>
+          </cell>
           <cell r="E478" t="str">
             <v/>
           </cell>
+          <cell r="F478" t="str">
+            <v>PVN-003298</v>
+          </cell>
+          <cell r="G478" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H478">
+            <v>100</v>
+          </cell>
+          <cell r="I478">
+            <v>100</v>
+          </cell>
           <cell r="J478">
             <v>0</v>
           </cell>
           <cell r="K478">
             <v>0</v>
+          </cell>
+          <cell r="L478" t="str">
+            <v>SALOMON</v>
+          </cell>
+          <cell r="M478" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N478" t="str">
+            <v>FL SHEET</v>
+          </cell>
+          <cell r="O478" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P478">
+            <v>46174</v>
+          </cell>
+          <cell r="Q478">
+            <v>46181</v>
+          </cell>
+          <cell r="R478">
+            <v>46178</v>
+          </cell>
+          <cell r="S478">
+            <v>6</v>
+          </cell>
+          <cell r="T478">
+            <v>7</v>
           </cell>
           <cell r="U478" t="str">
             <v/>
@@ -35419,14 +35681,62 @@
           </cell>
         </row>
         <row r="479">
+          <cell r="A479" t="str">
+            <v>S-2026-05-103</v>
+          </cell>
+          <cell r="C479" t="str">
+            <v>RPRO-260601-0848</v>
+          </cell>
+          <cell r="D479" t="str">
+            <v>PUR-202606010001S</v>
+          </cell>
           <cell r="E479" t="str">
             <v/>
           </cell>
+          <cell r="F479" t="str">
+            <v>PVN-002973</v>
+          </cell>
+          <cell r="G479" t="str">
+            <v>UltraLite-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+          </cell>
+          <cell r="H479">
+            <v>30</v>
+          </cell>
+          <cell r="I479">
+            <v>30</v>
+          </cell>
           <cell r="J479">
             <v>0</v>
           </cell>
           <cell r="K479">
             <v>0</v>
+          </cell>
+          <cell r="L479" t="str">
+            <v>SALOMON</v>
+          </cell>
+          <cell r="M479" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N479" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O479" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P479">
+            <v>46174</v>
+          </cell>
+          <cell r="Q479">
+            <v>46181</v>
+          </cell>
+          <cell r="R479">
+            <v>46178</v>
+          </cell>
+          <cell r="S479">
+            <v>6</v>
+          </cell>
+          <cell r="T479">
+            <v>7</v>
           </cell>
           <cell r="U479" t="str">
             <v/>
@@ -35439,14 +35749,62 @@
           </cell>
         </row>
         <row r="480">
+          <cell r="A480" t="str">
+            <v>S-2026-05-104</v>
+          </cell>
+          <cell r="C480" t="str">
+            <v>RPRO-260601-0849</v>
+          </cell>
+          <cell r="D480" t="str">
+            <v>PUR-202606010001S</v>
+          </cell>
           <cell r="E480" t="str">
             <v/>
           </cell>
+          <cell r="F480" t="str">
+            <v>PVN-002465</v>
+          </cell>
+          <cell r="G480" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 5mm</v>
+          </cell>
+          <cell r="H480">
+            <v>50</v>
+          </cell>
+          <cell r="I480">
+            <v>50</v>
+          </cell>
           <cell r="J480">
             <v>0</v>
           </cell>
           <cell r="K480">
             <v>0</v>
+          </cell>
+          <cell r="L480" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M480" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N480" t="str">
+            <v>DIE-CUT</v>
+          </cell>
+          <cell r="O480" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P480">
+            <v>46174</v>
+          </cell>
+          <cell r="Q480">
+            <v>46181</v>
+          </cell>
+          <cell r="R480">
+            <v>46178</v>
+          </cell>
+          <cell r="S480">
+            <v>6</v>
+          </cell>
+          <cell r="T480">
+            <v>7</v>
           </cell>
           <cell r="U480" t="str">
             <v/>
@@ -35459,14 +35817,62 @@
           </cell>
         </row>
         <row r="481">
+          <cell r="A481" t="str">
+            <v>S-2026-05-105</v>
+          </cell>
+          <cell r="C481" t="str">
+            <v>RPRO-260601-0850</v>
+          </cell>
+          <cell r="D481" t="str">
+            <v xml:space="preserve">PUR-202606010001S </v>
+          </cell>
           <cell r="E481" t="str">
             <v/>
           </cell>
+          <cell r="F481" t="str">
+            <v>PVN-003630</v>
+          </cell>
+          <cell r="G481" t="str">
+            <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 2mm</v>
+          </cell>
+          <cell r="H481">
+            <v>30</v>
+          </cell>
+          <cell r="I481">
+            <v>30</v>
+          </cell>
           <cell r="J481">
             <v>0</v>
           </cell>
           <cell r="K481">
             <v>0</v>
+          </cell>
+          <cell r="L481" t="str">
+            <v>UNDER ARMOUR</v>
+          </cell>
+          <cell r="M481" t="str">
+            <v>SSO-2606-00021    - URGENT (6-8)</v>
+          </cell>
+          <cell r="N481" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O481" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P481">
+            <v>46174</v>
+          </cell>
+          <cell r="Q481">
+            <v>46181</v>
+          </cell>
+          <cell r="R481">
+            <v>46178</v>
+          </cell>
+          <cell r="S481">
+            <v>6</v>
+          </cell>
+          <cell r="T481">
+            <v>7</v>
           </cell>
           <cell r="U481" t="str">
             <v/>
@@ -35479,14 +35885,62 @@
           </cell>
         </row>
         <row r="482">
+          <cell r="A482" t="str">
+            <v>S-2026-05-106</v>
+          </cell>
+          <cell r="C482" t="str">
+            <v>RPRO-260601-0851</v>
+          </cell>
+          <cell r="D482" t="str">
+            <v xml:space="preserve">PUR-202606010001S </v>
+          </cell>
           <cell r="E482" t="str">
             <v/>
           </cell>
+          <cell r="F482" t="str">
+            <v>PVN-003236</v>
+          </cell>
+          <cell r="G482" t="str">
+            <v>OrthoLite Eco LT-Hybrid-Converse SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 5mm</v>
+          </cell>
+          <cell r="H482">
+            <v>50</v>
+          </cell>
+          <cell r="I482">
+            <v>50</v>
+          </cell>
           <cell r="J482">
             <v>0</v>
           </cell>
           <cell r="K482">
             <v>0</v>
+          </cell>
+          <cell r="L482" t="str">
+            <v>CONVERSE</v>
+          </cell>
+          <cell r="M482" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N482" t="str">
+            <v>Die cut</v>
+          </cell>
+          <cell r="O482" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P482">
+            <v>46174</v>
+          </cell>
+          <cell r="Q482">
+            <v>46181</v>
+          </cell>
+          <cell r="R482">
+            <v>46178</v>
+          </cell>
+          <cell r="S482">
+            <v>6</v>
+          </cell>
+          <cell r="T482">
+            <v>7</v>
           </cell>
           <cell r="U482" t="str">
             <v/>
@@ -35831,24 +36285,24 @@
       <sheetData sheetId="87" refreshError="1"/>
       <sheetData sheetId="88" refreshError="1"/>
       <sheetData sheetId="89" refreshError="1"/>
-      <sheetData sheetId="90" refreshError="1"/>
+      <sheetData sheetId="90"/>
       <sheetData sheetId="91" refreshError="1"/>
       <sheetData sheetId="92" refreshError="1"/>
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
       <sheetData sheetId="96" refreshError="1"/>
-      <sheetData sheetId="97"/>
-      <sheetData sheetId="98" refreshError="1"/>
-      <sheetData sheetId="99" refreshError="1"/>
-      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98"/>
+      <sheetData sheetId="99"/>
+      <sheetData sheetId="100"/>
       <sheetData sheetId="101" refreshError="1"/>
       <sheetData sheetId="102" refreshError="1"/>
-      <sheetData sheetId="103"/>
-      <sheetData sheetId="104"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
       <sheetData sheetId="105" refreshError="1"/>
-      <sheetData sheetId="106" refreshError="1"/>
-      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="106"/>
+      <sheetData sheetId="107"/>
       <sheetData sheetId="108" refreshError="1"/>
       <sheetData sheetId="109" refreshError="1"/>
       <sheetData sheetId="110" refreshError="1"/>
@@ -36018,6 +36472,9 @@
       <sheetData sheetId="274" refreshError="1"/>
       <sheetData sheetId="275" refreshError="1"/>
       <sheetData sheetId="276" refreshError="1"/>
+      <sheetData sheetId="277" refreshError="1"/>
+      <sheetData sheetId="278" refreshError="1"/>
+      <sheetData sheetId="279" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -37644,23 +38101,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="63" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="62" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="58" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="57" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -37705,7 +38162,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46172.903662268516</v>
+        <v>46174.661814930558</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -39054,23 +39511,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -39115,7 +39572,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46172.903662268516</v>
+        <v>46174.661814930558</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -40522,23 +40979,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="49" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="44" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -40583,7 +41040,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46172.903662268516</v>
+        <v>46174.661814930558</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -41956,23 +42413,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="42" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="40" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -42016,7 +42473,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46172.903662268516</v>
+        <v>46174.661814930558</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -43231,39 +43688,39 @@
     <mergeCell ref="D7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A6 A14:A18">
-    <cfRule type="duplicateValues" dxfId="34" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="33" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A13">
-    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C6 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="30" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C13">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:L8">
-    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="25" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -43308,7 +43765,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46172.903662268516</v>
+        <v>46174.661814930558</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -44633,26 +45090,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A15">
-    <cfRule type="duplicateValues" dxfId="21" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A21">
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -44698,7 +45155,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46172.903662268516</v>
+        <v>46174.661814930558</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -46053,23 +46510,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -46114,7 +46571,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46172.903662268516</v>
+        <v>46174.661814930558</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -47515,24 +47972,24 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -47544,4 +48001,1403 @@
     <brk id="25" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0C7FDD-C476-4FE6-B890-05884597F111}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:N664"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="175.54296875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46174.661814930558</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>9</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="22">
+        <v>100</v>
+      </c>
+      <c r="G3" s="23">
+        <v>3</v>
+      </c>
+      <c r="H3" s="24">
+        <v>3</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="26">
+        <v>4</v>
+      </c>
+      <c r="M3" s="27"/>
+      <c r="N3" s="28">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="F4" s="22">
+        <v>30</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1</v>
+      </c>
+      <c r="H4" s="24">
+        <v>1</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="28">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="62"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="28"/>
+    </row>
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="F6" s="22">
+        <v>50</v>
+      </c>
+      <c r="G6" s="23">
+        <v>2</v>
+      </c>
+      <c r="H6" s="24">
+        <v>2</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="26">
+        <v>2</v>
+      </c>
+      <c r="M6" s="40"/>
+      <c r="N6" s="28">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="28"/>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="F8" s="22">
+        <v>30</v>
+      </c>
+      <c r="G8" s="23">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24">
+        <v>1</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="26">
+        <v>1</v>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="28">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="28"/>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="F10" s="22">
+        <v>50</v>
+      </c>
+      <c r="G10" s="23">
+        <v>2</v>
+      </c>
+      <c r="H10" s="24">
+        <v>2</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="L10" s="26">
+        <v>2</v>
+      </c>
+      <c r="M10" s="27"/>
+      <c r="N10" s="28">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C11" s="19" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D11" s="20" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="21" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" s="22" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G11" s="23" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H11" s="24" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L11" s="26"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A11,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C12" s="19" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D12" s="20" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" s="21" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F12" s="22" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G12" s="23" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H12" s="24" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L12" s="26"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A12,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C13" s="19" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="20" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="21" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" s="22" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="23" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H13" s="24" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L13" s="26"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A13,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C14" s="19" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D14" s="20" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="21" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="22" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="23" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H14" s="24" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A14,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C15" s="19" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D15" s="20" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="21" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" s="22" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="23" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H15" s="24" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L15" s="26"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C16" s="19" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="20" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="21" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="22" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="23" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H16" s="24" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L16" s="26"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A16,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C17" s="19" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="20" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="21" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="22" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="23" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H17" s="24" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="19" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="20" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="21" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="22" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="23" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H18" s="24" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A18,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="19" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="20" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="21" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F19" s="22" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="23" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H19" s="24" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="19" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="20" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="21" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="22" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="23" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="24" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="51"/>
+    </row>
+    <row r="22" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L22" s="56"/>
+    </row>
+    <row r="23" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L23" s="56"/>
+    </row>
+    <row r="24" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="55"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="58"/>
+    </row>
+    <row r="26" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="56"/>
+    </row>
+    <row r="28" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="58"/>
+    </row>
+    <row r="29" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="58"/>
+    </row>
+    <row r="30" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="664" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A664" s="2"/>
+      <c r="B664" s="52"/>
+      <c r="C664" s="2"/>
+      <c r="D664" s="2"/>
+      <c r="E664" s="60"/>
+      <c r="H664" s="55"/>
+      <c r="I664" s="53"/>
+      <c r="J664" s="53"/>
+      <c r="K664" s="53"/>
+      <c r="L664" s="61"/>
+      <c r="M664" s="57"/>
+      <c r="N664" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E20" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N21" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="RPRO-260601-0847"/>
+        <filter val="RPRO-260601-0848"/>
+        <filter val="RPRO-260601-0849"/>
+        <filter val="RPRO-260601-0850"/>
+        <filter val="RPRO-260601-0851"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A20">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="21" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
 </file>
--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC64ABE-46D3-4F48-8D3B-04C5A1BCF438}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80962CD4-88DD-4667-994F-8F71CAB5ACE7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="8" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="9" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,18 @@
     <sheet name="27.5" sheetId="7" r:id="rId7"/>
     <sheet name="29.5 - L2" sheetId="8" r:id="rId8"/>
     <sheet name="1.6" sheetId="9" r:id="rId9"/>
+    <sheet name="2.6" sheetId="10" r:id="rId10"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'13.5'!$A$2:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'15.5'!$A$2:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'18.5'!$A$2:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.6'!$A$2:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'20.5'!$A$2:$N$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'21.5'!$A$2:$N$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'25.5'!$A$2:$N$22</definedName>
@@ -41,6 +43,7 @@
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="2">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="9">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="3">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="4">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="5">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -50,6 +53,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'18.5'!$A$1:$N$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'2.6'!$A$1:$N$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'20.5'!$A$1:$N$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'21.5'!$A$1:$N$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'25.5'!$A$1:$N$22</definedName>
@@ -59,6 +63,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'18.5'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'2.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'20.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'21.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'25.5'!$1:$2</definedName>
@@ -68,6 +73,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
@@ -77,6 +83,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="9" hidden="1">'2.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
@@ -86,6 +93,7 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
@@ -95,6 +103,7 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
@@ -104,6 +113,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
@@ -113,6 +123,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="9" hidden="1">'2.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
@@ -122,6 +133,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="2" hidden="1">'18.5'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="9" hidden="1">'2.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="3" hidden="1">'20.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="4" hidden="1">'21.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="5" hidden="1">'25.5'!#REF!</definedName>
@@ -131,6 +143,7 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
@@ -140,6 +153,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
@@ -149,6 +163,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="9" hidden="1">'2.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
@@ -158,6 +173,7 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
@@ -167,6 +183,7 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
@@ -176,6 +193,7 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
@@ -185,6 +203,7 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
@@ -194,6 +213,7 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
@@ -203,6 +223,7 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
@@ -212,6 +233,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
@@ -221,6 +243,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="9" hidden="1">'2.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
@@ -230,6 +253,7 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
@@ -239,6 +263,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="9" hidden="1">'2.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="3" hidden="1">'20.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="4" hidden="1">'21.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
@@ -248,6 +273,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="9" hidden="1">'2.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="3" hidden="1">'20.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="4" hidden="1">'21.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
@@ -275,7 +301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="417">
   <si>
     <t>Release Date</t>
   </si>
@@ -1488,6 +1514,124 @@
   <si>
     <t>Die cut</t>
   </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>S-2026-06-01</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0720</t>
+  </si>
+  <si>
+    <t>PVN-004433</t>
+  </si>
+  <si>
+    <t>OrthoLite X-30-Hybrid BROWN SUGAR/17-1134TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 15mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE-CUT
+URGENT </t>
+  </si>
+  <si>
+    <t>S-2026-06-02</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0721</t>
+  </si>
+  <si>
+    <t>BDB-000212</t>
+  </si>
+  <si>
+    <t>PVN-003764</t>
+  </si>
+  <si>
+    <t>OrthoLite X-25-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.12D 20+/-4 Asker C 1.1M 2M 5mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-03</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0722</t>
+  </si>
+  <si>
+    <t>BDB-000321</t>
+  </si>
+  <si>
+    <t>PVN-004092</t>
+  </si>
+  <si>
+    <t>OrthoLite Float BLUE ATOLL/16-4535TPX Flat Sheet 0.12D 21+/-4 Asker C 1.1M 2M 14.5mm</t>
+  </si>
+  <si>
+    <t>LOWA</t>
+  </si>
+  <si>
+    <t>S-2026-06-04</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0723</t>
+  </si>
+  <si>
+    <t>PVN-004057</t>
+  </si>
+  <si>
+    <t>OrthoLite X-40 TRUE BLUE/19-4057TPX Flat Sheet 0.16D 25+/-4 Asker C 1.1M 1.7M 14.5mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-05</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0724</t>
+  </si>
+  <si>
+    <t>PVN-003743</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 5.5mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-07</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0726</t>
+  </si>
+  <si>
+    <t>PVN-003300</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 2mm</t>
+  </si>
+  <si>
+    <t>SSO-2606-00031    - URGENT (6-10)</t>
+  </si>
+  <si>
+    <t>S-2026-06-06</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0725</t>
+  </si>
+  <si>
+    <t>PVN-004098</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-08</t>
+  </si>
+  <si>
+    <t>RPRO-260602-0727</t>
+  </si>
+  <si>
+    <t>PVN-004330</t>
+  </si>
+  <si>
+    <t>OrthoLite IMPERIAL SEEDPEARL/12-0703TPX Flat Sheet 0.22D 25+/-4 Asker C 1.1M 1.47M 2mm</t>
+  </si>
+  <si>
+    <t>SSO-2606-00031</t>
+  </si>
 </sst>
 </file>
 
@@ -2088,7 +2232,77 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="78">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2975,17 +3189,18 @@
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
+      <sheetName val="form 2 (15)"/>
       <sheetName val="form 2 (14)"/>
-      <sheetName val="form 2 (15)"/>
+      <sheetName val="28.5"/>
       <sheetName val="MỚI (2)"/>
       <sheetName val="Sheet1"/>
       <sheetName val="form 2 (13)"/>
       <sheetName val="Sheet6"/>
       <sheetName val="form 2 (12)"/>
+      <sheetName val="form 2 (11)"/>
+      <sheetName val="form 2 (10)"/>
+      <sheetName val="form 2 (8)"/>
       <sheetName val="form 2 (7)"/>
-      <sheetName val="form 2 (8)"/>
-      <sheetName val="form 2 (10)"/>
-      <sheetName val="form 2 (11)"/>
       <sheetName val="form 2 (6)"/>
       <sheetName val="form 2 (5)"/>
       <sheetName val="Form (16)"/>
@@ -3013,7 +3228,6 @@
       <sheetName val="14.5"/>
       <sheetName val="16.5"/>
       <sheetName val="22.5"/>
-      <sheetName val="28.5"/>
       <sheetName val="30.5"/>
       <sheetName val="2.6"/>
       <sheetName val="3.6"/>
@@ -3148,57 +3362,97 @@
       <sheetName val="30.12 "/>
       <sheetName val="Form"/>
       <sheetName val="BCN 22.4"/>
+      <sheetName val="form 2 (4)"/>
+      <sheetName val="form 2 (3)"/>
+      <sheetName val="form 2"/>
+      <sheetName val="25.4 (2)"/>
+      <sheetName val="form 2 (17)"/>
       <sheetName val="form 2 (9)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
+          <cell r="A1"/>
+          <cell r="B1"/>
           <cell r="C1" t="str">
             <v>TẠM THỜI NGƯNG NHẬN LAZY</v>
           </cell>
+          <cell r="D1"/>
+          <cell r="E1"/>
+          <cell r="F1"/>
           <cell r="G1" t="str">
             <v>ASICS 12MM DÙNG BOM 132 (roundup(12/132),5)</v>
           </cell>
+          <cell r="H1"/>
+          <cell r="I1"/>
+          <cell r="J1"/>
+          <cell r="K1"/>
+          <cell r="L1"/>
+          <cell r="M1"/>
+          <cell r="N1"/>
+          <cell r="O1"/>
+          <cell r="P1"/>
+          <cell r="Q1"/>
+          <cell r="R1"/>
+          <cell r="S1"/>
+          <cell r="T1"/>
+          <cell r="U1"/>
+          <cell r="V1"/>
+          <cell r="W1"/>
         </row>
         <row r="2">
+          <cell r="A2"/>
+          <cell r="B2"/>
+          <cell r="C2"/>
+          <cell r="D2"/>
+          <cell r="E2"/>
+          <cell r="F2"/>
           <cell r="G2" t="str">
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>1762</v>
+            <v>24460</v>
           </cell>
           <cell r="I2">
-            <v>1762</v>
+            <v>24460</v>
           </cell>
           <cell r="J2">
-            <v>140</v>
+            <v>23333</v>
           </cell>
           <cell r="K2">
-            <v>1622</v>
+            <v>1127</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
           </cell>
+          <cell r="M2"/>
+          <cell r="N2"/>
+          <cell r="O2"/>
+          <cell r="P2"/>
           <cell r="Q2" t="str">
             <v>ETD hệ thống+1ngay</v>
           </cell>
           <cell r="R2" t="e">
             <v>#VALUE!</v>
           </cell>
+          <cell r="S2"/>
+          <cell r="T2"/>
           <cell r="U2">
             <v>12</v>
           </cell>
+          <cell r="V2"/>
           <cell r="W2">
-            <v>98</v>
+            <v>1239</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>NO.Order</v>
           </cell>
+          <cell r="B3"/>
           <cell r="C3" t="str">
             <v>Firm plan
 (PU PVN)</v>
@@ -3283,6 +3537,7 @@
           <cell r="A4" t="str">
             <v>S-2026-01-01</v>
           </cell>
+          <cell r="B4"/>
           <cell r="C4" t="str">
             <v>RPRO-260105-0668</v>
           </cell>
@@ -3635,6 +3890,7 @@
           <cell r="A9" t="str">
             <v>S-2026-01-06</v>
           </cell>
+          <cell r="B9"/>
           <cell r="C9" t="str">
             <v>RPRO-260105-0673</v>
           </cell>
@@ -3703,6 +3959,7 @@
           <cell r="A10" t="str">
             <v>S-2026-01-07</v>
           </cell>
+          <cell r="B10"/>
           <cell r="C10" t="str">
             <v>RPRO-260105-0674</v>
           </cell>
@@ -3771,6 +4028,7 @@
           <cell r="A11" t="str">
             <v>S-2026-01-08</v>
           </cell>
+          <cell r="B11"/>
           <cell r="C11" t="str">
             <v>RPRO-260105-0675</v>
           </cell>
@@ -3981,6 +4239,7 @@
           <cell r="A14" t="str">
             <v>L-2026-01-11</v>
           </cell>
+          <cell r="B14"/>
           <cell r="C14" t="str">
             <v>RPRO-260105-0678</v>
           </cell>
@@ -4014,6 +4273,7 @@
           <cell r="M14" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N14"/>
           <cell r="O14" t="str">
             <v>Lab test</v>
           </cell>
@@ -4046,6 +4306,7 @@
           <cell r="A15" t="str">
             <v>L-2026-01-12</v>
           </cell>
+          <cell r="B15"/>
           <cell r="C15" t="str">
             <v>RPRO-260105-0679</v>
           </cell>
@@ -4079,6 +4340,7 @@
           <cell r="M15" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N15"/>
           <cell r="O15" t="str">
             <v>Lab test</v>
           </cell>
@@ -4111,6 +4373,7 @@
           <cell r="A16" t="str">
             <v>L-2026-01-13</v>
           </cell>
+          <cell r="B16"/>
           <cell r="C16" t="str">
             <v>RPRO-260105-0680</v>
           </cell>
@@ -4144,6 +4407,7 @@
           <cell r="M16" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N16"/>
           <cell r="O16" t="str">
             <v>Lab test</v>
           </cell>
@@ -4176,6 +4440,7 @@
           <cell r="A17" t="str">
             <v>L-2026-01-14</v>
           </cell>
+          <cell r="B17"/>
           <cell r="C17" t="str">
             <v>RPRO-260105-0681</v>
           </cell>
@@ -4209,6 +4474,7 @@
           <cell r="M17" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N17"/>
           <cell r="O17" t="str">
             <v>Lab test</v>
           </cell>
@@ -4277,6 +4543,7 @@
           <cell r="M18" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N18"/>
           <cell r="O18" t="str">
             <v>Lab test</v>
           </cell>
@@ -4345,6 +4612,7 @@
           <cell r="M19" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N19"/>
           <cell r="O19" t="str">
             <v>Lab test</v>
           </cell>
@@ -4732,6 +5000,7 @@
           <cell r="A25" t="str">
             <v>L-2026-01-22</v>
           </cell>
+          <cell r="B25"/>
           <cell r="C25" t="str">
             <v>RPRO-260109-0095</v>
           </cell>
@@ -4765,6 +5034,7 @@
           <cell r="M25" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N25"/>
           <cell r="O25" t="str">
             <v>Lab test</v>
           </cell>
@@ -4797,6 +5067,7 @@
           <cell r="A26" t="str">
             <v>S-2026-01-23</v>
           </cell>
+          <cell r="B26"/>
           <cell r="C26" t="str">
             <v>RPRO-260113-0624</v>
           </cell>
@@ -4865,6 +5136,7 @@
           <cell r="A27" t="str">
             <v>S-2026-01-24</v>
           </cell>
+          <cell r="B27"/>
           <cell r="C27" t="str">
             <v>RPRO-260113-0625</v>
           </cell>
@@ -4933,6 +5205,7 @@
           <cell r="A28" t="str">
             <v>S-2026-01-25</v>
           </cell>
+          <cell r="B28"/>
           <cell r="C28" t="str">
             <v>RPRO-260113-0626</v>
           </cell>
@@ -5001,6 +5274,7 @@
           <cell r="A29" t="str">
             <v>S-2026-01-26</v>
           </cell>
+          <cell r="B29"/>
           <cell r="C29" t="str">
             <v>RPRO-260113-0627</v>
           </cell>
@@ -5069,6 +5343,7 @@
           <cell r="A30" t="str">
             <v>S-2026-01-27</v>
           </cell>
+          <cell r="B30"/>
           <cell r="C30" t="str">
             <v>RPRO-260113-0628</v>
           </cell>
@@ -5137,6 +5412,7 @@
           <cell r="A31" t="str">
             <v>S-2026-01-28</v>
           </cell>
+          <cell r="B31"/>
           <cell r="C31" t="str">
             <v>RPRO-260113-0629</v>
           </cell>
@@ -5205,6 +5481,7 @@
           <cell r="A32" t="str">
             <v>S-2026-01-29</v>
           </cell>
+          <cell r="B32"/>
           <cell r="C32" t="str">
             <v>RPRO-260113-0630</v>
           </cell>
@@ -5273,6 +5550,7 @@
           <cell r="A33" t="str">
             <v>S-2026-01-30</v>
           </cell>
+          <cell r="B33"/>
           <cell r="C33" t="str">
             <v>RPRO-260115-0298</v>
           </cell>
@@ -5341,6 +5619,7 @@
           <cell r="A34" t="str">
             <v>S-2026-01-31</v>
           </cell>
+          <cell r="B34"/>
           <cell r="C34" t="str">
             <v>RPRO-260115-0299</v>
           </cell>
@@ -5409,6 +5688,7 @@
           <cell r="A35" t="str">
             <v>S-2026-01-32</v>
           </cell>
+          <cell r="B35"/>
           <cell r="C35" t="str">
             <v>RPRO-260115-0300</v>
           </cell>
@@ -5477,6 +5757,7 @@
           <cell r="A36" t="str">
             <v>S-2026-01-33</v>
           </cell>
+          <cell r="B36"/>
           <cell r="C36" t="str">
             <v>RPRO-260115-0301</v>
           </cell>
@@ -5545,6 +5826,7 @@
           <cell r="A37" t="str">
             <v>S-2026-01-34</v>
           </cell>
+          <cell r="B37"/>
           <cell r="C37" t="str">
             <v>RPRO-260115-0302</v>
           </cell>
@@ -5613,6 +5895,7 @@
           <cell r="A38" t="str">
             <v>S-2026-01-35</v>
           </cell>
+          <cell r="B38"/>
           <cell r="C38" t="str">
             <v>RPRO-260115-0303</v>
           </cell>
@@ -5681,6 +5964,7 @@
           <cell r="A39" t="str">
             <v>S-2026-01-36</v>
           </cell>
+          <cell r="B39"/>
           <cell r="C39" t="str">
             <v>RPRO-260115-0304</v>
           </cell>
@@ -5749,6 +6033,7 @@
           <cell r="A40" t="str">
             <v>S-2026-01-37</v>
           </cell>
+          <cell r="B40"/>
           <cell r="C40" t="str">
             <v>RPRO-260115-0305</v>
           </cell>
@@ -5817,6 +6102,7 @@
           <cell r="A41" t="str">
             <v>S-2026-01-38</v>
           </cell>
+          <cell r="B41"/>
           <cell r="C41" t="str">
             <v>RPRO-260115-0306</v>
           </cell>
@@ -5885,6 +6171,7 @@
           <cell r="A42" t="str">
             <v>S-2026-01-39</v>
           </cell>
+          <cell r="B42"/>
           <cell r="C42" t="str">
             <v>RPRO-260115-0307</v>
           </cell>
@@ -5953,6 +6240,7 @@
           <cell r="A43" t="str">
             <v>S-2026-01-40</v>
           </cell>
+          <cell r="B43"/>
           <cell r="C43" t="str">
             <v>RPRO-260115-0308</v>
           </cell>
@@ -6021,6 +6309,7 @@
           <cell r="A44" t="str">
             <v>S-2026-01-41</v>
           </cell>
+          <cell r="B44"/>
           <cell r="C44" t="str">
             <v>RPRO-260115-0309</v>
           </cell>
@@ -6089,6 +6378,7 @@
           <cell r="A45" t="str">
             <v>S-2026-01-42</v>
           </cell>
+          <cell r="B45"/>
           <cell r="C45" t="str">
             <v>RPRO-260109-0096</v>
           </cell>
@@ -6157,6 +6447,7 @@
           <cell r="A46" t="str">
             <v>S-2026-01-43</v>
           </cell>
+          <cell r="B46"/>
           <cell r="C46" t="str">
             <v>RPRO-260109-0097</v>
           </cell>
@@ -6225,6 +6516,7 @@
           <cell r="A47" t="str">
             <v>S-2026-01-44</v>
           </cell>
+          <cell r="B47"/>
           <cell r="C47" t="str">
             <v>RPRO-260109-0098</v>
           </cell>
@@ -6293,6 +6585,7 @@
           <cell r="A48" t="str">
             <v>S-2026-01-45</v>
           </cell>
+          <cell r="B48"/>
           <cell r="C48" t="str">
             <v>RPRO-260109-0099</v>
           </cell>
@@ -6361,6 +6654,7 @@
           <cell r="A49" t="str">
             <v>S-2026-01-46</v>
           </cell>
+          <cell r="B49"/>
           <cell r="C49" t="str">
             <v>RPRO-260120-0349</v>
           </cell>
@@ -6429,6 +6723,7 @@
           <cell r="A50" t="str">
             <v>S-2026-01-47</v>
           </cell>
+          <cell r="B50"/>
           <cell r="C50" t="str">
             <v>RPRO-260120-0350</v>
           </cell>
@@ -6497,6 +6792,7 @@
           <cell r="A51" t="str">
             <v>S-2026-01-48</v>
           </cell>
+          <cell r="B51"/>
           <cell r="C51" t="str">
             <v>RPRO-260120-0351</v>
           </cell>
@@ -6565,6 +6861,7 @@
           <cell r="A52" t="str">
             <v>S-2026-01-49</v>
           </cell>
+          <cell r="B52"/>
           <cell r="C52" t="str">
             <v>RPRO-260120-0352</v>
           </cell>
@@ -6633,6 +6930,7 @@
           <cell r="A53" t="str">
             <v>S-2026-01-50</v>
           </cell>
+          <cell r="B53"/>
           <cell r="C53" t="str">
             <v>RPRO-260120-0353</v>
           </cell>
@@ -6701,6 +6999,7 @@
           <cell r="A54" t="str">
             <v>S-2026-01-51</v>
           </cell>
+          <cell r="B54"/>
           <cell r="C54" t="str">
             <v>RPRO-260120-0354</v>
           </cell>
@@ -6769,6 +7068,7 @@
           <cell r="A55" t="str">
             <v>S-2026-01-52</v>
           </cell>
+          <cell r="B55"/>
           <cell r="C55" t="str">
             <v>RPRO-260113-0631</v>
           </cell>
@@ -6837,6 +7137,7 @@
           <cell r="A56" t="str">
             <v>S-2026-01-53</v>
           </cell>
+          <cell r="B56"/>
           <cell r="C56" t="str">
             <v>RPRO-260120-0355</v>
           </cell>
@@ -6905,6 +7206,7 @@
           <cell r="A57" t="str">
             <v>S-2026-01-54</v>
           </cell>
+          <cell r="B57"/>
           <cell r="C57" t="str">
             <v>RPRO-260120-0356</v>
           </cell>
@@ -6973,6 +7275,7 @@
           <cell r="A58" t="str">
             <v>S-2026-01-55</v>
           </cell>
+          <cell r="B58"/>
           <cell r="C58" t="str">
             <v>RPRO-260120-0357</v>
           </cell>
@@ -7041,6 +7344,7 @@
           <cell r="A59" t="str">
             <v>S-2026-01-56</v>
           </cell>
+          <cell r="B59"/>
           <cell r="C59" t="str">
             <v>RPRO-260120-0358</v>
           </cell>
@@ -7109,6 +7413,7 @@
           <cell r="A60" t="str">
             <v>S-2026-01-57</v>
           </cell>
+          <cell r="B60"/>
           <cell r="C60" t="str">
             <v>RPRO-260120-0359</v>
           </cell>
@@ -7177,6 +7482,7 @@
           <cell r="A61" t="str">
             <v>S-2026-01-58</v>
           </cell>
+          <cell r="B61"/>
           <cell r="C61" t="str">
             <v>RPRO-260120-0360</v>
           </cell>
@@ -7245,6 +7551,7 @@
           <cell r="A62" t="str">
             <v>S-2026-01-59</v>
           </cell>
+          <cell r="B62"/>
           <cell r="C62" t="str">
             <v>RPRO-260116-0276</v>
           </cell>
@@ -7313,6 +7620,7 @@
           <cell r="A63" t="str">
             <v>S-2026-01-60</v>
           </cell>
+          <cell r="B63"/>
           <cell r="C63" t="str">
             <v>RPRO-260115-0310</v>
           </cell>
@@ -7381,6 +7689,7 @@
           <cell r="A64" t="str">
             <v>S-2026-01-61</v>
           </cell>
+          <cell r="B64"/>
           <cell r="C64" t="str">
             <v>RPRO-260120-0361</v>
           </cell>
@@ -7520,6 +7829,7 @@
           <cell r="A66" t="str">
             <v>S-2026-01-63</v>
           </cell>
+          <cell r="B66"/>
           <cell r="C66" t="str">
             <v>RPRO-260122-1562</v>
           </cell>
@@ -7588,6 +7898,7 @@
           <cell r="A67" t="str">
             <v>S-2026-01-64</v>
           </cell>
+          <cell r="B67"/>
           <cell r="C67" t="str">
             <v>RPRO-260122-1563</v>
           </cell>
@@ -7656,6 +7967,7 @@
           <cell r="A68" t="str">
             <v>S-2026-01-65</v>
           </cell>
+          <cell r="B68"/>
           <cell r="C68" t="str">
             <v>RPRO-260122-1564</v>
           </cell>
@@ -7724,6 +8036,7 @@
           <cell r="A69" t="str">
             <v>S-2026-01-66</v>
           </cell>
+          <cell r="B69"/>
           <cell r="C69" t="str">
             <v>RPRO-260122-1565</v>
           </cell>
@@ -7792,6 +8105,7 @@
           <cell r="A70" t="str">
             <v>S-2026-01-67</v>
           </cell>
+          <cell r="B70"/>
           <cell r="C70" t="str">
             <v>RPRO-260122-1566</v>
           </cell>
@@ -7860,6 +8174,7 @@
           <cell r="A71" t="str">
             <v>S-2026-01-68</v>
           </cell>
+          <cell r="B71"/>
           <cell r="C71" t="str">
             <v>RPRO-260122-1567</v>
           </cell>
@@ -7928,6 +8243,7 @@
           <cell r="A72" t="str">
             <v>S-2026-01-69</v>
           </cell>
+          <cell r="B72"/>
           <cell r="C72" t="str">
             <v>RPRO-260122-1568</v>
           </cell>
@@ -7996,6 +8312,7 @@
           <cell r="A73" t="str">
             <v>S-2026-01-70</v>
           </cell>
+          <cell r="B73"/>
           <cell r="C73" t="str">
             <v>RPRO-260122-1569</v>
           </cell>
@@ -8064,6 +8381,7 @@
           <cell r="A74" t="str">
             <v>S-2026-01-71</v>
           </cell>
+          <cell r="B74"/>
           <cell r="C74" t="str">
             <v>RPRO-260122-1570</v>
           </cell>
@@ -8132,6 +8450,7 @@
           <cell r="A75" t="str">
             <v>S-2026-01-72</v>
           </cell>
+          <cell r="B75"/>
           <cell r="C75" t="str">
             <v>RPRO-260122-1571</v>
           </cell>
@@ -8413,6 +8732,7 @@
           <cell r="A79" t="str">
             <v>S-2026-01-76</v>
           </cell>
+          <cell r="B79"/>
           <cell r="C79" t="str">
             <v>RPRO-260122-1573</v>
           </cell>
@@ -8481,6 +8801,7 @@
           <cell r="A80" t="str">
             <v>S-2026-01-77</v>
           </cell>
+          <cell r="B80"/>
           <cell r="C80" t="str">
             <v>RPRO-260122-1574</v>
           </cell>
@@ -8549,6 +8870,7 @@
           <cell r="A81" t="str">
             <v>S-2026-01-78</v>
           </cell>
+          <cell r="B81"/>
           <cell r="C81" t="str">
             <v>RPRO-260122-1575</v>
           </cell>
@@ -8617,6 +8939,7 @@
           <cell r="A82" t="str">
             <v>S-2026-01-79</v>
           </cell>
+          <cell r="B82"/>
           <cell r="C82" t="str">
             <v>RPRO-260122-1576</v>
           </cell>
@@ -8685,6 +9008,7 @@
           <cell r="A83" t="str">
             <v>S-2026-01-80</v>
           </cell>
+          <cell r="B83"/>
           <cell r="C83" t="str">
             <v>RPRO-260122-1577</v>
           </cell>
@@ -8753,6 +9077,7 @@
           <cell r="A84" t="str">
             <v>S-2026-01-81</v>
           </cell>
+          <cell r="B84"/>
           <cell r="C84" t="str">
             <v>RPRO-260122-1578</v>
           </cell>
@@ -8821,6 +9146,7 @@
           <cell r="A85" t="str">
             <v>S-2026-01-82</v>
           </cell>
+          <cell r="B85"/>
           <cell r="C85" t="str">
             <v>RPRO-260122-1579</v>
           </cell>
@@ -8889,6 +9215,7 @@
           <cell r="A86" t="str">
             <v>S-2026-01-83</v>
           </cell>
+          <cell r="B86"/>
           <cell r="C86" t="str">
             <v>RPRO-260122-1580</v>
           </cell>
@@ -8960,6 +9287,7 @@
           <cell r="B87" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C87"/>
           <cell r="D87" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9028,6 +9356,7 @@
           <cell r="B88" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C88"/>
           <cell r="D88" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9096,6 +9425,7 @@
           <cell r="B89" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C89"/>
           <cell r="D89" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9161,6 +9491,7 @@
           <cell r="A90" t="str">
             <v>S-2026-01-87</v>
           </cell>
+          <cell r="B90"/>
           <cell r="C90" t="str">
             <v>RPRO-260127-0875</v>
           </cell>
@@ -9229,6 +9560,7 @@
           <cell r="A91" t="str">
             <v>S-2026-01-88</v>
           </cell>
+          <cell r="B91"/>
           <cell r="C91" t="str">
             <v>RPRO-260127-0877</v>
           </cell>
@@ -9297,6 +9629,7 @@
           <cell r="A92" t="str">
             <v>S-2026-01-89</v>
           </cell>
+          <cell r="B92"/>
           <cell r="C92" t="str">
             <v>RPRO-260127-0879</v>
           </cell>
@@ -9365,6 +9698,7 @@
           <cell r="A93" t="str">
             <v>S-2026-01-90</v>
           </cell>
+          <cell r="B93"/>
           <cell r="C93" t="str">
             <v>RPRO-260128-1270</v>
           </cell>
@@ -9433,6 +9767,7 @@
           <cell r="A94" t="str">
             <v>S-2026-01-91</v>
           </cell>
+          <cell r="B94"/>
           <cell r="C94" t="str">
             <v>RPRO-260128-1271</v>
           </cell>
@@ -9501,6 +9836,7 @@
           <cell r="A95" t="str">
             <v>S-2026-01-92</v>
           </cell>
+          <cell r="B95"/>
           <cell r="C95" t="str">
             <v>RPRO-260128-1272</v>
           </cell>
@@ -9569,6 +9905,7 @@
           <cell r="A96" t="str">
             <v>S-2026-01-93</v>
           </cell>
+          <cell r="B96"/>
           <cell r="C96" t="str">
             <v>RPRO-260128-1273</v>
           </cell>
@@ -9637,6 +9974,7 @@
           <cell r="A97" t="str">
             <v>S-2026-01-94</v>
           </cell>
+          <cell r="B97"/>
           <cell r="C97" t="str">
             <v>RPRO-260128-1274</v>
           </cell>
@@ -9705,6 +10043,7 @@
           <cell r="A98" t="str">
             <v>S-2026-01-95</v>
           </cell>
+          <cell r="B98"/>
           <cell r="C98" t="str">
             <v>RPRO-260128-1275</v>
           </cell>
@@ -9773,6 +10112,7 @@
           <cell r="A99" t="str">
             <v>S-2026-01-96</v>
           </cell>
+          <cell r="B99"/>
           <cell r="C99" t="str">
             <v>RPRO-260128-1276</v>
           </cell>
@@ -9841,6 +10181,7 @@
           <cell r="A100" t="str">
             <v>S-2026-01-97</v>
           </cell>
+          <cell r="B100"/>
           <cell r="C100" t="str">
             <v>RPRO-260128-1277</v>
           </cell>
@@ -9909,6 +10250,7 @@
           <cell r="A101" t="str">
             <v>S-2026-01-98</v>
           </cell>
+          <cell r="B101"/>
           <cell r="C101" t="str">
             <v>RPRO-260129-0656</v>
           </cell>
@@ -9977,6 +10319,7 @@
           <cell r="A102" t="str">
             <v>S-2026-02-01</v>
           </cell>
+          <cell r="B102"/>
           <cell r="C102" t="str">
             <v>RPRO-260203-0021</v>
           </cell>
@@ -10045,6 +10388,7 @@
           <cell r="A103" t="str">
             <v>S-2026-02-02</v>
           </cell>
+          <cell r="B103"/>
           <cell r="C103" t="str">
             <v>RPRO-260203-0022</v>
           </cell>
@@ -10113,6 +10457,7 @@
           <cell r="A104" t="str">
             <v>S-2026-02-03</v>
           </cell>
+          <cell r="B104"/>
           <cell r="C104" t="str">
             <v>RPRO-260203-0770</v>
           </cell>
@@ -10181,6 +10526,7 @@
           <cell r="A105" t="str">
             <v>S-2026-02-04</v>
           </cell>
+          <cell r="B105"/>
           <cell r="C105" t="str">
             <v>RPRO-260203-0771</v>
           </cell>
@@ -10249,6 +10595,7 @@
           <cell r="A106" t="str">
             <v>S-2026-02-05</v>
           </cell>
+          <cell r="B106"/>
           <cell r="C106" t="str">
             <v>RPRO-260203-0772</v>
           </cell>
@@ -10317,6 +10664,7 @@
           <cell r="A107" t="str">
             <v>S-2026-02-06</v>
           </cell>
+          <cell r="B107"/>
           <cell r="C107" t="str">
             <v>RPRO-260203-0773</v>
           </cell>
@@ -10385,6 +10733,7 @@
           <cell r="A108" t="str">
             <v>S-2026-02-07</v>
           </cell>
+          <cell r="B108"/>
           <cell r="C108" t="str">
             <v>RPRO-260203-0774</v>
           </cell>
@@ -10453,6 +10802,7 @@
           <cell r="A109" t="str">
             <v>S-2026-02-08</v>
           </cell>
+          <cell r="B109"/>
           <cell r="C109" t="str">
             <v>RPRO-260203-0775</v>
           </cell>
@@ -10521,6 +10871,7 @@
           <cell r="A110" t="str">
             <v>S-2026-02-09</v>
           </cell>
+          <cell r="B110"/>
           <cell r="C110" t="str">
             <v>RPRO-260203-0776</v>
           </cell>
@@ -10589,6 +10940,7 @@
           <cell r="A111" t="str">
             <v>S-2026-02-10</v>
           </cell>
+          <cell r="B111"/>
           <cell r="C111" t="str">
             <v>RPRO-260203-0777</v>
           </cell>
@@ -10657,6 +11009,7 @@
           <cell r="A112" t="str">
             <v>S-2026-02-11</v>
           </cell>
+          <cell r="B112"/>
           <cell r="C112" t="str">
             <v>RPRO-260203-0778</v>
           </cell>
@@ -10725,6 +11078,7 @@
           <cell r="A113" t="str">
             <v>S-2026-02-12</v>
           </cell>
+          <cell r="B113"/>
           <cell r="C113" t="str">
             <v>RPRO-260203-0779</v>
           </cell>
@@ -10793,6 +11147,7 @@
           <cell r="A114" t="str">
             <v>S-2026-02-13</v>
           </cell>
+          <cell r="B114"/>
           <cell r="C114" t="str">
             <v>RPRO-260203-0780</v>
           </cell>
@@ -10861,6 +11216,7 @@
           <cell r="A115" t="str">
             <v>S-2026-02-14</v>
           </cell>
+          <cell r="B115"/>
           <cell r="C115" t="str">
             <v>RPRO-260203-0781</v>
           </cell>
@@ -10929,6 +11285,7 @@
           <cell r="A116" t="str">
             <v>S-2026-02-15</v>
           </cell>
+          <cell r="B116"/>
           <cell r="C116" t="str">
             <v>RPRO-260203-0782</v>
           </cell>
@@ -10997,6 +11354,7 @@
           <cell r="A117" t="str">
             <v>S-2026-02-16</v>
           </cell>
+          <cell r="B117"/>
           <cell r="C117" t="str">
             <v>RPRO-260203-0783</v>
           </cell>
@@ -11065,6 +11423,7 @@
           <cell r="A118" t="str">
             <v>S-2026-02-17</v>
           </cell>
+          <cell r="B118"/>
           <cell r="C118" t="str">
             <v>RPRO-260203-0784</v>
           </cell>
@@ -11133,6 +11492,7 @@
           <cell r="A119" t="str">
             <v>S-2026-02-18</v>
           </cell>
+          <cell r="B119"/>
           <cell r="C119" t="str">
             <v>RPRO-260204-0399</v>
           </cell>
@@ -11201,6 +11561,7 @@
           <cell r="A120" t="str">
             <v>S-2026-02-19</v>
           </cell>
+          <cell r="B120"/>
           <cell r="C120" t="str">
             <v>RPRO-260204-0400</v>
           </cell>
@@ -11269,6 +11630,7 @@
           <cell r="A121" t="str">
             <v>L-2026-02-20</v>
           </cell>
+          <cell r="B121"/>
           <cell r="C121" t="str">
             <v>RPRO-260204-0401</v>
           </cell>
@@ -11302,6 +11664,7 @@
           <cell r="M121" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N121"/>
           <cell r="O121" t="str">
             <v>Lab test</v>
           </cell>
@@ -11334,6 +11697,7 @@
           <cell r="A122" t="str">
             <v>L-2026-02-21</v>
           </cell>
+          <cell r="B122"/>
           <cell r="C122" t="str">
             <v>RPRO-260204-0402</v>
           </cell>
@@ -11367,6 +11731,7 @@
           <cell r="M122" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N122"/>
           <cell r="O122" t="str">
             <v>Lab test</v>
           </cell>
@@ -11470,6 +11835,7 @@
           <cell r="A124" t="str">
             <v>S-2026-02-23</v>
           </cell>
+          <cell r="B124"/>
           <cell r="C124" t="str">
             <v>RPRO-260210-0003</v>
           </cell>
@@ -11609,6 +11975,7 @@
           <cell r="A126" t="str">
             <v>S-2026-02-25</v>
           </cell>
+          <cell r="B126"/>
           <cell r="C126" t="str">
             <v>RPRO-260210-0005</v>
           </cell>
@@ -11677,6 +12044,7 @@
           <cell r="A127" t="str">
             <v>S-2026-02-26</v>
           </cell>
+          <cell r="B127"/>
           <cell r="C127" t="str">
             <v>RPRO-260210-0006</v>
           </cell>
@@ -11745,6 +12113,7 @@
           <cell r="A128" t="str">
             <v>S-2026-02-27</v>
           </cell>
+          <cell r="B128"/>
           <cell r="C128" t="str">
             <v>RPRO-260210-0007</v>
           </cell>
@@ -11813,6 +12182,7 @@
           <cell r="A129" t="str">
             <v>S-2026-02-28</v>
           </cell>
+          <cell r="B129"/>
           <cell r="C129" t="str">
             <v>RPRO-260210-0008</v>
           </cell>
@@ -11881,6 +12251,7 @@
           <cell r="A130" t="str">
             <v>S-2026-02-29</v>
           </cell>
+          <cell r="B130"/>
           <cell r="C130" t="str">
             <v>RPRO-260210-0009</v>
           </cell>
@@ -11949,6 +12320,7 @@
           <cell r="A131" t="str">
             <v>S-2026-02-30</v>
           </cell>
+          <cell r="B131"/>
           <cell r="C131" t="str">
             <v>RPRO-260210-0010</v>
           </cell>
@@ -12017,6 +12389,7 @@
           <cell r="A132" t="str">
             <v>S-2026-02-31</v>
           </cell>
+          <cell r="B132"/>
           <cell r="C132" t="str">
             <v>RPRO-260210-0011</v>
           </cell>
@@ -12086,6 +12459,7 @@
           <cell r="A133" t="str">
             <v>S-2026-02-32</v>
           </cell>
+          <cell r="B133"/>
           <cell r="C133" t="str">
             <v>RPRO-260210-0012</v>
           </cell>
@@ -12155,6 +12529,7 @@
           <cell r="A134" t="str">
             <v>S-2026-02-33</v>
           </cell>
+          <cell r="B134"/>
           <cell r="C134" t="str">
             <v>RPRO-260210-0013</v>
           </cell>
@@ -12223,6 +12598,7 @@
           <cell r="A135" t="str">
             <v>S-2026-02-34</v>
           </cell>
+          <cell r="B135"/>
           <cell r="C135" t="str">
             <v>RPRO-260211-0001</v>
           </cell>
@@ -12293,6 +12669,7 @@
           <cell r="A136" t="str">
             <v>S-2026-02-35</v>
           </cell>
+          <cell r="B136"/>
           <cell r="C136" t="str">
             <v>RPRO-260227-0335</v>
           </cell>
@@ -12361,6 +12738,7 @@
           <cell r="A137" t="str">
             <v>S-2026-02-36</v>
           </cell>
+          <cell r="B137"/>
           <cell r="C137" t="str">
             <v>RPRO-260227-0336</v>
           </cell>
@@ -12429,6 +12807,7 @@
           <cell r="A138" t="str">
             <v>S-2026-02-37</v>
           </cell>
+          <cell r="B138"/>
           <cell r="C138" t="str">
             <v>RPRO-260227-0337</v>
           </cell>
@@ -12497,6 +12876,7 @@
           <cell r="A139" t="str">
             <v>S-2026-02-38</v>
           </cell>
+          <cell r="B139"/>
           <cell r="C139" t="str">
             <v>RPRO-260227-0338</v>
           </cell>
@@ -12565,6 +12945,7 @@
           <cell r="A140" t="str">
             <v>S-2026-02-39</v>
           </cell>
+          <cell r="B140"/>
           <cell r="C140" t="str">
             <v>RPRO-260227-0339</v>
           </cell>
@@ -12633,6 +13014,7 @@
           <cell r="A141" t="str">
             <v>L-2026-02-40</v>
           </cell>
+          <cell r="B141"/>
           <cell r="C141" t="str">
             <v>RPRO-260227-0340</v>
           </cell>
@@ -12666,6 +13048,7 @@
           <cell r="M141" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N141"/>
           <cell r="O141" t="str">
             <v>Lab test</v>
           </cell>
@@ -12698,6 +13081,7 @@
           <cell r="A142" t="str">
             <v>S-2026-02-41</v>
           </cell>
+          <cell r="B142"/>
           <cell r="C142" t="str">
             <v>RPRO-260227-0341</v>
           </cell>
@@ -12766,6 +13150,7 @@
           <cell r="A143" t="str">
             <v>S-2026-02-42</v>
           </cell>
+          <cell r="B143"/>
           <cell r="C143" t="str">
             <v>RPRO-260227-0342</v>
           </cell>
@@ -12834,6 +13219,7 @@
           <cell r="A144" t="str">
             <v>S-2026-02-43</v>
           </cell>
+          <cell r="B144"/>
           <cell r="C144" t="str">
             <v>RPRO-260227-0343</v>
           </cell>
@@ -12902,6 +13288,7 @@
           <cell r="A145" t="str">
             <v>S-2026-02-44</v>
           </cell>
+          <cell r="B145"/>
           <cell r="C145" t="str">
             <v>RPRO-260227-0344</v>
           </cell>
@@ -12970,6 +13357,7 @@
           <cell r="A146" t="str">
             <v>S-2026-02-45</v>
           </cell>
+          <cell r="B146"/>
           <cell r="C146" t="str">
             <v>RPRO-260227-0345</v>
           </cell>
@@ -13109,6 +13497,7 @@
           <cell r="A148" t="str">
             <v>S-2026-02-47</v>
           </cell>
+          <cell r="B148"/>
           <cell r="C148" t="str">
             <v>RPRO-260227-0347</v>
           </cell>
@@ -13177,6 +13566,7 @@
           <cell r="A149" t="str">
             <v>S-2026-02-48</v>
           </cell>
+          <cell r="B149"/>
           <cell r="C149" t="str">
             <v>RPRO-260227-0348</v>
           </cell>
@@ -13245,6 +13635,7 @@
           <cell r="A150" t="str">
             <v>S-2026-02-49</v>
           </cell>
+          <cell r="B150"/>
           <cell r="C150" t="str">
             <v>RPRO-260302-0004</v>
           </cell>
@@ -13313,6 +13704,7 @@
           <cell r="A151" t="str">
             <v>S-2026-02-50</v>
           </cell>
+          <cell r="B151"/>
           <cell r="C151" t="str">
             <v>RPRO-260227-0349</v>
           </cell>
@@ -13381,6 +13773,7 @@
           <cell r="A152" t="str">
             <v>S-2026-02-51</v>
           </cell>
+          <cell r="B152"/>
           <cell r="C152" t="str">
             <v>RPRO-260227-0350</v>
           </cell>
@@ -13449,6 +13842,7 @@
           <cell r="A153" t="str">
             <v>S-2026-02-52</v>
           </cell>
+          <cell r="B153"/>
           <cell r="C153" t="str">
             <v>RPRO-260227-0351</v>
           </cell>
@@ -13517,6 +13911,7 @@
           <cell r="A154" t="str">
             <v>S-2026-02-53</v>
           </cell>
+          <cell r="B154"/>
           <cell r="C154" t="str">
             <v>RPRO-260227-0352</v>
           </cell>
@@ -13585,6 +13980,7 @@
           <cell r="A155" t="str">
             <v>L-2026-03-01</v>
           </cell>
+          <cell r="B155"/>
           <cell r="C155" t="str">
             <v>RPRO-260303-0005</v>
           </cell>
@@ -13618,6 +14014,7 @@
           <cell r="M155" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N155"/>
           <cell r="O155" t="str">
             <v>Lab test</v>
           </cell>
@@ -13650,6 +14047,7 @@
           <cell r="A156" t="str">
             <v>L-2026-03-02</v>
           </cell>
+          <cell r="B156"/>
           <cell r="C156" t="str">
             <v>RPRO-260303-0006</v>
           </cell>
@@ -13683,6 +14081,7 @@
           <cell r="M156" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N156"/>
           <cell r="O156" t="str">
             <v>Lab test</v>
           </cell>
@@ -13999,6 +14398,7 @@
           <cell r="A161" t="str">
             <v>S-2026-03-07</v>
           </cell>
+          <cell r="B161"/>
           <cell r="C161" t="str">
             <v>RPRO-260303-0011</v>
           </cell>
@@ -14067,6 +14467,7 @@
           <cell r="A162" t="str">
             <v>S-2026-03-08</v>
           </cell>
+          <cell r="B162"/>
           <cell r="C162" t="str">
             <v>RPRO-260303-0012</v>
           </cell>
@@ -14135,6 +14536,7 @@
           <cell r="A163" t="str">
             <v>S-2026-03-09</v>
           </cell>
+          <cell r="B163"/>
           <cell r="C163" t="str">
             <v>RPRO-260303-0013</v>
           </cell>
@@ -14203,6 +14605,7 @@
           <cell r="A164" t="str">
             <v>S-2026-03-10</v>
           </cell>
+          <cell r="B164"/>
           <cell r="C164" t="str">
             <v>RPRO-260303-0014</v>
           </cell>
@@ -14271,6 +14674,7 @@
           <cell r="A165" t="str">
             <v>S-2026-03-11</v>
           </cell>
+          <cell r="B165"/>
           <cell r="C165" t="str">
             <v>RPRO-260313-0139</v>
           </cell>
@@ -14304,6 +14708,7 @@
           <cell r="M165" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N165"/>
           <cell r="O165" t="str">
             <v>Sample</v>
           </cell>
@@ -14336,6 +14741,7 @@
           <cell r="A166" t="str">
             <v>S-2026-03-12</v>
           </cell>
+          <cell r="B166"/>
           <cell r="C166" t="str">
             <v>RPRO-260313-0140</v>
           </cell>
@@ -14369,6 +14775,7 @@
           <cell r="M166" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N166"/>
           <cell r="O166" t="str">
             <v>Sample</v>
           </cell>
@@ -14401,6 +14808,7 @@
           <cell r="A167" t="str">
             <v>S-2026-03-13</v>
           </cell>
+          <cell r="B167"/>
           <cell r="C167" t="str">
             <v>RPRO-260313-0141</v>
           </cell>
@@ -14434,6 +14842,7 @@
           <cell r="M167" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N167"/>
           <cell r="O167" t="str">
             <v>Sample</v>
           </cell>
@@ -14537,6 +14946,7 @@
           <cell r="A169" t="str">
             <v>S-2026-03-15</v>
           </cell>
+          <cell r="B169"/>
           <cell r="C169" t="str">
             <v>RPRO-260306-1547</v>
           </cell>
@@ -14605,6 +15015,7 @@
           <cell r="A170" t="str">
             <v>S-2026-03-16</v>
           </cell>
+          <cell r="B170"/>
           <cell r="C170" t="str">
             <v>RPRO-260306-1548</v>
           </cell>
@@ -14673,6 +15084,7 @@
           <cell r="A171" t="str">
             <v>S-2026-03-17</v>
           </cell>
+          <cell r="B171"/>
           <cell r="C171" t="str">
             <v>RPRO-260306-1549</v>
           </cell>
@@ -14741,6 +15153,7 @@
           <cell r="A172" t="str">
             <v>S-2026-03-18</v>
           </cell>
+          <cell r="B172"/>
           <cell r="C172" t="str">
             <v>RPRO-260306-1550</v>
           </cell>
@@ -14809,6 +15222,7 @@
           <cell r="A173" t="str">
             <v>S-2026-03-19</v>
           </cell>
+          <cell r="B173"/>
           <cell r="C173" t="str">
             <v>RPRO-260306-1551</v>
           </cell>
@@ -14877,6 +15291,7 @@
           <cell r="A174" t="str">
             <v>S-2026-03-20</v>
           </cell>
+          <cell r="B174"/>
           <cell r="C174" t="str">
             <v>RPRO-260306-1552</v>
           </cell>
@@ -14945,6 +15360,7 @@
           <cell r="A175" t="str">
             <v>S-2026-03-21</v>
           </cell>
+          <cell r="B175"/>
           <cell r="C175" t="str">
             <v>RPRO-260306-1553</v>
           </cell>
@@ -15013,6 +15429,7 @@
           <cell r="A176" t="str">
             <v>S-2026-03-22</v>
           </cell>
+          <cell r="B176"/>
           <cell r="C176" t="str">
             <v>RPRO-260306-1554</v>
           </cell>
@@ -15081,6 +15498,7 @@
           <cell r="A177" t="str">
             <v>S-2026-03-23</v>
           </cell>
+          <cell r="B177"/>
           <cell r="C177" t="str">
             <v>RPRO-260306-1555</v>
           </cell>
@@ -15149,6 +15567,7 @@
           <cell r="A178" t="str">
             <v>S-2026-03-24</v>
           </cell>
+          <cell r="B178"/>
           <cell r="C178" t="str">
             <v>RPRO-260306-1556</v>
           </cell>
@@ -15288,6 +15707,7 @@
           <cell r="A180" t="str">
             <v>L-2026-03-26</v>
           </cell>
+          <cell r="B180"/>
           <cell r="C180" t="str">
             <v>RPRO-260305-1288</v>
           </cell>
@@ -15321,6 +15741,7 @@
           <cell r="M180" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N180"/>
           <cell r="O180" t="str">
             <v>Lab test</v>
           </cell>
@@ -15424,6 +15845,7 @@
           <cell r="A182" t="str">
             <v>S-2026-03-28</v>
           </cell>
+          <cell r="B182"/>
           <cell r="C182" t="str">
             <v>RPRO-260306-1559</v>
           </cell>
@@ -15492,6 +15914,7 @@
           <cell r="A183" t="str">
             <v>S-2026-03-29</v>
           </cell>
+          <cell r="B183"/>
           <cell r="C183" t="str">
             <v>RPRO-260306-1560</v>
           </cell>
@@ -15560,6 +15983,7 @@
           <cell r="A184" t="str">
             <v>S-2026-03-30</v>
           </cell>
+          <cell r="B184"/>
           <cell r="C184" t="str">
             <v>RPRO-260306-1561</v>
           </cell>
@@ -15628,6 +16052,7 @@
           <cell r="A185" t="str">
             <v>S-2026-03-31</v>
           </cell>
+          <cell r="B185"/>
           <cell r="C185" t="str">
             <v>RPRO-260306-1562</v>
           </cell>
@@ -15696,6 +16121,7 @@
           <cell r="A186" t="str">
             <v>S-2026-03-32</v>
           </cell>
+          <cell r="B186"/>
           <cell r="C186" t="str">
             <v>RPRO-260306-1563</v>
           </cell>
@@ -15764,6 +16190,7 @@
           <cell r="A187" t="str">
             <v>S-2026-03-33</v>
           </cell>
+          <cell r="B187"/>
           <cell r="C187" t="str">
             <v>RPRO-260306-1564</v>
           </cell>
@@ -15832,6 +16259,7 @@
           <cell r="A188" t="str">
             <v>S-2026-03-34</v>
           </cell>
+          <cell r="B188"/>
           <cell r="C188" t="str">
             <v>RPRO-260306-1565</v>
           </cell>
@@ -15900,6 +16328,7 @@
           <cell r="A189" t="str">
             <v>S-2026-03-35</v>
           </cell>
+          <cell r="B189"/>
           <cell r="C189" t="str">
             <v>RPRO-260306-1566</v>
           </cell>
@@ -15968,6 +16397,7 @@
           <cell r="A190" t="str">
             <v>S-2026-03-36</v>
           </cell>
+          <cell r="B190"/>
           <cell r="C190" t="str">
             <v>RPRO-260307-0080</v>
           </cell>
@@ -16036,6 +16466,7 @@
           <cell r="A191" t="str">
             <v>S-2026-03-37</v>
           </cell>
+          <cell r="B191"/>
           <cell r="C191" t="str">
             <v>RPRO-260306-1736</v>
           </cell>
@@ -16104,6 +16535,7 @@
           <cell r="A192" t="str">
             <v>S-2026-03-38</v>
           </cell>
+          <cell r="B192"/>
           <cell r="C192" t="str">
             <v>RPRO-260306-1737</v>
           </cell>
@@ -16172,6 +16604,7 @@
           <cell r="A193" t="str">
             <v>S-2026-03-39</v>
           </cell>
+          <cell r="B193"/>
           <cell r="C193" t="str">
             <v>RPRO-260306-1738</v>
           </cell>
@@ -16240,6 +16673,7 @@
           <cell r="A194" t="str">
             <v>S-2026-03-40</v>
           </cell>
+          <cell r="B194"/>
           <cell r="C194" t="str">
             <v>RPRO-260306-1739</v>
           </cell>
@@ -16308,6 +16742,7 @@
           <cell r="A195" t="str">
             <v>S-2026-03-41</v>
           </cell>
+          <cell r="B195"/>
           <cell r="C195" t="str">
             <v>RPRO-260306-1740</v>
           </cell>
@@ -16376,6 +16811,7 @@
           <cell r="A196" t="str">
             <v>S-2026-03-42</v>
           </cell>
+          <cell r="B196"/>
           <cell r="C196" t="str">
             <v>RPRO-260307-0081</v>
           </cell>
@@ -16444,6 +16880,7 @@
           <cell r="A197" t="str">
             <v>S-2026-03-43</v>
           </cell>
+          <cell r="B197"/>
           <cell r="C197" t="str">
             <v>RPRO-260307-0082</v>
           </cell>
@@ -16512,6 +16949,7 @@
           <cell r="A198" t="str">
             <v>S-2026-03-44</v>
           </cell>
+          <cell r="B198"/>
           <cell r="C198" t="str">
             <v>RPRO-260307-0083</v>
           </cell>
@@ -16580,6 +17018,7 @@
           <cell r="A199" t="str">
             <v>S-2026-03-45</v>
           </cell>
+          <cell r="B199"/>
           <cell r="C199" t="str">
             <v>RPRO-260307-0084</v>
           </cell>
@@ -16648,6 +17087,7 @@
           <cell r="A200" t="str">
             <v>S-2026-03-46</v>
           </cell>
+          <cell r="B200"/>
           <cell r="C200" t="str">
             <v>RPRO-260307-0085</v>
           </cell>
@@ -16716,6 +17156,7 @@
           <cell r="A201" t="str">
             <v>S-2026-03-47</v>
           </cell>
+          <cell r="B201"/>
           <cell r="C201" t="str">
             <v>RPRO-260310-0362</v>
           </cell>
@@ -16855,6 +17296,7 @@
           <cell r="A203" t="str">
             <v>S-2026-03-49</v>
           </cell>
+          <cell r="B203"/>
           <cell r="C203" t="str">
             <v>RPRO-260310-0364</v>
           </cell>
@@ -16923,6 +17365,7 @@
           <cell r="A204" t="str">
             <v>S-2026-03-50</v>
           </cell>
+          <cell r="B204"/>
           <cell r="C204" t="str">
             <v>RPRO-260310-0365</v>
           </cell>
@@ -17062,6 +17505,7 @@
           <cell r="A206" t="str">
             <v>S-2026-03-52</v>
           </cell>
+          <cell r="B206"/>
           <cell r="C206" t="str">
             <v>RPRO-260310-0367</v>
           </cell>
@@ -17130,6 +17574,7 @@
           <cell r="A207" t="str">
             <v>S-2026-03-53</v>
           </cell>
+          <cell r="B207"/>
           <cell r="C207" t="str">
             <v>RPRO-260310-0368</v>
           </cell>
@@ -17198,6 +17643,7 @@
           <cell r="A208" t="str">
             <v>S-2026-03-54</v>
           </cell>
+          <cell r="B208"/>
           <cell r="C208" t="str">
             <v>RPRO-260310-0369</v>
           </cell>
@@ -17266,6 +17712,7 @@
           <cell r="A209" t="str">
             <v>S-2026-03-55</v>
           </cell>
+          <cell r="B209"/>
           <cell r="C209" t="str">
             <v>RPRO-260310-0370</v>
           </cell>
@@ -17334,6 +17781,7 @@
           <cell r="A210" t="str">
             <v>S-2026-03-56</v>
           </cell>
+          <cell r="B210"/>
           <cell r="C210" t="str">
             <v>RPRO-260310-0371</v>
           </cell>
@@ -17402,6 +17850,7 @@
           <cell r="A211" t="str">
             <v>S-2026-03-57</v>
           </cell>
+          <cell r="B211"/>
           <cell r="C211" t="str">
             <v>RPRO-260310-0372</v>
           </cell>
@@ -17470,6 +17919,7 @@
           <cell r="A212" t="str">
             <v>S-2026-03-58</v>
           </cell>
+          <cell r="B212"/>
           <cell r="C212" t="str">
             <v>RPRO-260310-0373</v>
           </cell>
@@ -17538,6 +17988,7 @@
           <cell r="A213" t="str">
             <v>S-2026-03-59</v>
           </cell>
+          <cell r="B213"/>
           <cell r="C213" t="str">
             <v>RPRO-260310-0374</v>
           </cell>
@@ -17606,6 +18057,7 @@
           <cell r="A214" t="str">
             <v>S-2026-03-60</v>
           </cell>
+          <cell r="B214"/>
           <cell r="C214" t="str">
             <v>RPRO-260310-0375</v>
           </cell>
@@ -17674,6 +18126,7 @@
           <cell r="A215" t="str">
             <v>S-2026-03-61</v>
           </cell>
+          <cell r="B215"/>
           <cell r="C215" t="str">
             <v>RPRO-260310-0376</v>
           </cell>
@@ -17745,6 +18198,7 @@
           <cell r="B216" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C216"/>
           <cell r="D216" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -17775,6 +18229,7 @@
           <cell r="M216" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N216"/>
           <cell r="O216" t="str">
             <v>Lab test</v>
           </cell>
@@ -17810,6 +18265,7 @@
           <cell r="B217" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C217"/>
           <cell r="D217" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -17840,6 +18296,7 @@
           <cell r="M217" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N217"/>
           <cell r="O217" t="str">
             <v>Lab test</v>
           </cell>
@@ -17872,6 +18329,7 @@
           <cell r="A218" t="str">
             <v>S-2026-03-64</v>
           </cell>
+          <cell r="B218"/>
           <cell r="C218" t="str">
             <v>RPRO-260313-0142</v>
           </cell>
@@ -17940,6 +18398,7 @@
           <cell r="A219" t="str">
             <v>S-2026-03-65</v>
           </cell>
+          <cell r="B219"/>
           <cell r="C219" t="str">
             <v>RPRO-260313-0143</v>
           </cell>
@@ -18008,6 +18467,7 @@
           <cell r="A220" t="str">
             <v>S-2026-03-66</v>
           </cell>
+          <cell r="B220"/>
           <cell r="C220" t="str">
             <v>RPRO-260313-0144</v>
           </cell>
@@ -18076,6 +18536,7 @@
           <cell r="A221" t="str">
             <v>S-2026-03-67</v>
           </cell>
+          <cell r="B221"/>
           <cell r="C221" t="str">
             <v>RPRO-260313-0145</v>
           </cell>
@@ -18144,6 +18605,7 @@
           <cell r="A222" t="str">
             <v>S-2026-03-68</v>
           </cell>
+          <cell r="B222"/>
           <cell r="C222" t="str">
             <v>RPRO-260313-0146</v>
           </cell>
@@ -18212,6 +18674,7 @@
           <cell r="A223" t="str">
             <v>S-2026-03-69</v>
           </cell>
+          <cell r="B223"/>
           <cell r="C223" t="str">
             <v>RPRO-260313-0147</v>
           </cell>
@@ -18280,6 +18743,7 @@
           <cell r="A224" t="str">
             <v>S-2026-03-70</v>
           </cell>
+          <cell r="B224"/>
           <cell r="C224" t="str">
             <v>RPRO-260313-0148</v>
           </cell>
@@ -18348,6 +18812,7 @@
           <cell r="A225" t="str">
             <v>S-2026-03-71</v>
           </cell>
+          <cell r="B225"/>
           <cell r="C225" t="str">
             <v>RPRO-260313-0149</v>
           </cell>
@@ -18416,6 +18881,7 @@
           <cell r="A226" t="str">
             <v>S-2026-03-72</v>
           </cell>
+          <cell r="B226"/>
           <cell r="C226" t="str">
             <v>RPRO-260313-0150</v>
           </cell>
@@ -18484,6 +18950,7 @@
           <cell r="A227" t="str">
             <v>S-2026-03-73</v>
           </cell>
+          <cell r="B227"/>
           <cell r="C227" t="str">
             <v>RPRO-260313-0151</v>
           </cell>
@@ -18552,6 +19019,7 @@
           <cell r="A228" t="str">
             <v>S-2026-03-74</v>
           </cell>
+          <cell r="B228"/>
           <cell r="C228" t="str">
             <v>RPRO-260313-0152</v>
           </cell>
@@ -18620,6 +19088,7 @@
           <cell r="A229" t="str">
             <v>S-2026-03-75</v>
           </cell>
+          <cell r="B229"/>
           <cell r="C229" t="str">
             <v>RPRO-260313-0318</v>
           </cell>
@@ -18688,6 +19157,7 @@
           <cell r="A230" t="str">
             <v>S-2026-03-76</v>
           </cell>
+          <cell r="B230"/>
           <cell r="C230" t="str">
             <v>RPRO-260313-0319</v>
           </cell>
@@ -18756,6 +19226,7 @@
           <cell r="A231" t="str">
             <v>S-2026-03-77</v>
           </cell>
+          <cell r="B231"/>
           <cell r="C231" t="str">
             <v>RPRO-260314-0198</v>
           </cell>
@@ -18824,6 +19295,7 @@
           <cell r="A232" t="str">
             <v>S-2026-03-78</v>
           </cell>
+          <cell r="B232"/>
           <cell r="C232" t="str">
             <v>RPRO-260314-0199</v>
           </cell>
@@ -18892,6 +19364,7 @@
           <cell r="A233" t="str">
             <v>S-2026-03-79</v>
           </cell>
+          <cell r="B233"/>
           <cell r="C233" t="str">
             <v>RPRO-260317-0628</v>
           </cell>
@@ -18960,6 +19433,7 @@
           <cell r="A234" t="str">
             <v>S-2026-03-80</v>
           </cell>
+          <cell r="B234"/>
           <cell r="C234" t="str">
             <v>RPRO-260317-0629</v>
           </cell>
@@ -19028,6 +19502,7 @@
           <cell r="A235" t="str">
             <v>S-2026-03-81</v>
           </cell>
+          <cell r="B235"/>
           <cell r="C235" t="str">
             <v>RPRO-260317-0630</v>
           </cell>
@@ -19096,6 +19571,7 @@
           <cell r="A236" t="str">
             <v>S-2026-03-82</v>
           </cell>
+          <cell r="B236"/>
           <cell r="C236" t="str">
             <v>RPRO-260317-0631</v>
           </cell>
@@ -19164,6 +19640,7 @@
           <cell r="A237" t="str">
             <v>S-2026-03-83</v>
           </cell>
+          <cell r="B237"/>
           <cell r="C237" t="str">
             <v>RPRO-260317-0632</v>
           </cell>
@@ -19232,6 +19709,7 @@
           <cell r="A238" t="str">
             <v>S-2026-03-84</v>
           </cell>
+          <cell r="B238"/>
           <cell r="C238" t="str">
             <v>RPRO-260317-0633</v>
           </cell>
@@ -19300,6 +19778,7 @@
           <cell r="A239" t="str">
             <v>S-2026-03-85</v>
           </cell>
+          <cell r="B239"/>
           <cell r="C239" t="str">
             <v>RPRO-260317-0634</v>
           </cell>
@@ -19368,6 +19847,7 @@
           <cell r="A240" t="str">
             <v>S-2026-03-86</v>
           </cell>
+          <cell r="B240"/>
           <cell r="C240" t="str">
             <v>RPRO-260317-0635</v>
           </cell>
@@ -19436,6 +19916,7 @@
           <cell r="A241" t="str">
             <v>S-2026-03-87</v>
           </cell>
+          <cell r="B241"/>
           <cell r="C241" t="str">
             <v>RPRO-260317-0636</v>
           </cell>
@@ -19504,6 +19985,7 @@
           <cell r="A242" t="str">
             <v>L-2026-03-88</v>
           </cell>
+          <cell r="B242"/>
           <cell r="C242" t="str">
             <v>RPRO-260317-0637</v>
           </cell>
@@ -19537,6 +20019,7 @@
           <cell r="M242" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N242"/>
           <cell r="O242" t="str">
             <v>Lab test</v>
           </cell>
@@ -19605,6 +20088,7 @@
           <cell r="M243" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N243"/>
           <cell r="O243" t="str">
             <v>Lab test</v>
           </cell>
@@ -19637,6 +20121,7 @@
           <cell r="A244" t="str">
             <v>S-2026-03-90</v>
           </cell>
+          <cell r="B244"/>
           <cell r="C244" t="str">
             <v>RPRO-260317-0639</v>
           </cell>
@@ -19705,6 +20190,7 @@
           <cell r="A245" t="str">
             <v>S-2026-03-91</v>
           </cell>
+          <cell r="B245"/>
           <cell r="C245" t="str">
             <v>RPRO-260317-0640</v>
           </cell>
@@ -19773,6 +20259,7 @@
           <cell r="A246" t="str">
             <v>S-2026-03-92</v>
           </cell>
+          <cell r="B246"/>
           <cell r="C246" t="str">
             <v>RPRO-260317-0641</v>
           </cell>
@@ -19841,6 +20328,7 @@
           <cell r="A247" t="str">
             <v>L-2026-03-93</v>
           </cell>
+          <cell r="B247"/>
           <cell r="C247" t="str">
             <v>RPRO-260318-0477</v>
           </cell>
@@ -19874,6 +20362,7 @@
           <cell r="M247" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N247"/>
           <cell r="O247" t="str">
             <v>Lab test</v>
           </cell>
@@ -19906,6 +20395,7 @@
           <cell r="A248" t="str">
             <v>L-2026-03-94</v>
           </cell>
+          <cell r="B248"/>
           <cell r="C248" t="str">
             <v>RPRO-260318-0478</v>
           </cell>
@@ -19939,6 +20429,7 @@
           <cell r="M248" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N248"/>
           <cell r="O248" t="str">
             <v>Lab test</v>
           </cell>
@@ -20042,6 +20533,7 @@
           <cell r="A250" t="str">
             <v>S-2026-03-96</v>
           </cell>
+          <cell r="B250"/>
           <cell r="C250" t="str">
             <v>RPRO-260318-0482</v>
           </cell>
@@ -20110,6 +20602,7 @@
           <cell r="A251" t="str">
             <v>S-2026-03-97</v>
           </cell>
+          <cell r="B251"/>
           <cell r="C251" t="str">
             <v>RPRO-260324-0278</v>
           </cell>
@@ -20178,6 +20671,7 @@
           <cell r="A252" t="str">
             <v>S-2026-03-98</v>
           </cell>
+          <cell r="B252"/>
           <cell r="C252" t="str">
             <v>RPRO-260324-0279</v>
           </cell>
@@ -20317,6 +20811,7 @@
           <cell r="A254" t="str">
             <v>S-2026-03-100</v>
           </cell>
+          <cell r="B254"/>
           <cell r="C254" t="str">
             <v>RPRO-260324-0281</v>
           </cell>
@@ -20385,6 +20880,7 @@
           <cell r="A255" t="str">
             <v>S-2026-03-101</v>
           </cell>
+          <cell r="B255"/>
           <cell r="C255" t="str">
             <v>RPRO-260324-0282</v>
           </cell>
@@ -20453,6 +20949,7 @@
           <cell r="A256" t="str">
             <v>S-2026-03-102</v>
           </cell>
+          <cell r="B256"/>
           <cell r="C256" t="str">
             <v>RPRO-260324-0531</v>
           </cell>
@@ -20521,6 +21018,7 @@
           <cell r="A257" t="str">
             <v>S-2026-03-103</v>
           </cell>
+          <cell r="B257"/>
           <cell r="C257" t="str">
             <v>RPRO-260324-0283</v>
           </cell>
@@ -20589,6 +21087,7 @@
           <cell r="A258" t="str">
             <v>S-2026-03-104</v>
           </cell>
+          <cell r="B258"/>
           <cell r="C258" t="str">
             <v>RPRO-260324-0284</v>
           </cell>
@@ -20657,6 +21156,7 @@
           <cell r="A259" t="str">
             <v>L-2026-03-105</v>
           </cell>
+          <cell r="B259"/>
           <cell r="C259" t="str">
             <v>RPRO-260321-0027</v>
           </cell>
@@ -20690,6 +21190,7 @@
           <cell r="M259" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N259"/>
           <cell r="O259" t="str">
             <v>Lab test</v>
           </cell>
@@ -20722,6 +21223,7 @@
           <cell r="A260" t="str">
             <v>L-2026-03-106</v>
           </cell>
+          <cell r="B260"/>
           <cell r="C260" t="str">
             <v>RPRO-260321-0028</v>
           </cell>
@@ -20755,6 +21257,7 @@
           <cell r="M260" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N260"/>
           <cell r="O260" t="str">
             <v>Lab test</v>
           </cell>
@@ -20787,6 +21290,7 @@
           <cell r="A261" t="str">
             <v>S-2026-03-107</v>
           </cell>
+          <cell r="B261"/>
           <cell r="C261" t="str">
             <v>RPRO-260321-0029</v>
           </cell>
@@ -20855,6 +21359,7 @@
           <cell r="A262" t="str">
             <v>S-2026-03-108</v>
           </cell>
+          <cell r="B262"/>
           <cell r="C262" t="str">
             <v>RPRO-260324-0285</v>
           </cell>
@@ -20923,6 +21428,7 @@
           <cell r="A263" t="str">
             <v>L-2026-03-109</v>
           </cell>
+          <cell r="B263"/>
           <cell r="C263" t="str">
             <v>RPRO-260324-0286</v>
           </cell>
@@ -20950,9 +21456,11 @@
           <cell r="K263">
             <v>0</v>
           </cell>
+          <cell r="L263"/>
           <cell r="M263" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N263"/>
           <cell r="O263" t="str">
             <v>Lab test</v>
           </cell>
@@ -20985,6 +21493,7 @@
           <cell r="A264" t="str">
             <v>S-2026-03-110</v>
           </cell>
+          <cell r="B264"/>
           <cell r="C264" t="str">
             <v>RPRO-260324-0287</v>
           </cell>
@@ -21053,6 +21562,7 @@
           <cell r="A265" t="str">
             <v>S-2026-03-111</v>
           </cell>
+          <cell r="B265"/>
           <cell r="C265" t="str">
             <v>RPRO-260324-0288</v>
           </cell>
@@ -21121,6 +21631,7 @@
           <cell r="A266" t="str">
             <v>S-2026-03-112</v>
           </cell>
+          <cell r="B266"/>
           <cell r="C266" t="str">
             <v>RPRO-260324-0289</v>
           </cell>
@@ -21189,6 +21700,7 @@
           <cell r="A267" t="str">
             <v>S-2026-03-113</v>
           </cell>
+          <cell r="B267"/>
           <cell r="C267" t="str">
             <v>RPRO-260324-0532</v>
           </cell>
@@ -21257,6 +21769,7 @@
           <cell r="A268" t="str">
             <v>S-2026-03-114</v>
           </cell>
+          <cell r="B268"/>
           <cell r="C268" t="str">
             <v>RPRO-260324-0533</v>
           </cell>
@@ -21325,6 +21838,7 @@
           <cell r="A269" t="str">
             <v>S-2026-03-115</v>
           </cell>
+          <cell r="B269"/>
           <cell r="C269" t="str">
             <v>RPRO-260324-0534</v>
           </cell>
@@ -21393,6 +21907,7 @@
           <cell r="A270" t="str">
             <v>S-2026-03-116</v>
           </cell>
+          <cell r="B270"/>
           <cell r="C270" t="str">
             <v>RPRO-260325-0407</v>
           </cell>
@@ -21461,6 +21976,7 @@
           <cell r="A271" t="str">
             <v>S-2026-03-117</v>
           </cell>
+          <cell r="B271"/>
           <cell r="C271" t="str">
             <v>RPRO-260325-0408</v>
           </cell>
@@ -21529,6 +22045,7 @@
           <cell r="A272" t="str">
             <v>S-2026-03-118</v>
           </cell>
+          <cell r="B272"/>
           <cell r="C272" t="str">
             <v>RPRO-260325-0409</v>
           </cell>
@@ -21597,6 +22114,7 @@
           <cell r="A273" t="str">
             <v>S-2026-03-119</v>
           </cell>
+          <cell r="B273"/>
           <cell r="C273" t="str">
             <v>RPRO-260325-0410</v>
           </cell>
@@ -21665,6 +22183,7 @@
           <cell r="A274" t="str">
             <v>S-2026-03-120</v>
           </cell>
+          <cell r="B274"/>
           <cell r="C274" t="str">
             <v>RPRO-260325-0411</v>
           </cell>
@@ -21733,6 +22252,7 @@
           <cell r="A275" t="str">
             <v>S-2026-03-121</v>
           </cell>
+          <cell r="B275"/>
           <cell r="C275" t="str">
             <v>RPRO-260325-0412</v>
           </cell>
@@ -21801,6 +22321,7 @@
           <cell r="A276" t="str">
             <v>S-2026-03-122</v>
           </cell>
+          <cell r="B276"/>
           <cell r="C276" t="str">
             <v>RPRO-260325-0413</v>
           </cell>
@@ -21869,6 +22390,7 @@
           <cell r="A277" t="str">
             <v>S-2026-03-123</v>
           </cell>
+          <cell r="B277"/>
           <cell r="C277" t="str">
             <v>RPRO-260325-0414</v>
           </cell>
@@ -21937,6 +22459,7 @@
           <cell r="A278" t="str">
             <v>S-2026-03-124</v>
           </cell>
+          <cell r="B278"/>
           <cell r="C278" t="str">
             <v>RPRO-260325-0415</v>
           </cell>
@@ -22076,6 +22599,7 @@
           <cell r="A280" t="str">
             <v>S-2026-03-126</v>
           </cell>
+          <cell r="B280"/>
           <cell r="C280" t="str">
             <v>RPRO-260325-0417</v>
           </cell>
@@ -22144,6 +22668,7 @@
           <cell r="A281" t="str">
             <v>S-2026-03-127</v>
           </cell>
+          <cell r="B281"/>
           <cell r="C281" t="str">
             <v>RPRO-260325-0418</v>
           </cell>
@@ -22212,6 +22737,7 @@
           <cell r="A282" t="str">
             <v>S-2026-03-128</v>
           </cell>
+          <cell r="B282"/>
           <cell r="C282" t="str">
             <v>RPRO-260325-0419</v>
           </cell>
@@ -22280,6 +22806,7 @@
           <cell r="A283" t="str">
             <v>S-2026-03-129</v>
           </cell>
+          <cell r="B283"/>
           <cell r="C283" t="str">
             <v>RPRO-260325-0421</v>
           </cell>
@@ -22348,6 +22875,7 @@
           <cell r="A284" t="str">
             <v>S-2026-03-130</v>
           </cell>
+          <cell r="B284"/>
           <cell r="C284" t="str">
             <v>RPRO-260327-0930</v>
           </cell>
@@ -22558,6 +23086,7 @@
           <cell r="A287" t="str">
             <v>S-2026-03-133</v>
           </cell>
+          <cell r="B287"/>
           <cell r="C287" t="str">
             <v>RPRO-260327-0933</v>
           </cell>
@@ -22626,6 +23155,7 @@
           <cell r="A288" t="str">
             <v>S-2026-03-134</v>
           </cell>
+          <cell r="B288"/>
           <cell r="C288" t="str">
             <v>RPRO-260327-0934</v>
           </cell>
@@ -22836,6 +23366,7 @@
           <cell r="A291" t="str">
             <v>S-2026-03-137</v>
           </cell>
+          <cell r="B291"/>
           <cell r="C291" t="str">
             <v>RPRO-260327-0937</v>
           </cell>
@@ -22975,6 +23506,7 @@
           <cell r="A293" t="str">
             <v>S-2026-03-139</v>
           </cell>
+          <cell r="B293"/>
           <cell r="C293" t="str">
             <v>RPRO-260327-0939</v>
           </cell>
@@ -23114,6 +23646,7 @@
           <cell r="A295" t="str">
             <v>S-2026-03-141</v>
           </cell>
+          <cell r="B295"/>
           <cell r="C295" t="str">
             <v>RPRO-260327-0941</v>
           </cell>
@@ -23182,6 +23715,7 @@
           <cell r="A296" t="str">
             <v>S-2026-03-142</v>
           </cell>
+          <cell r="B296"/>
           <cell r="C296" t="str">
             <v>RPRO-260401-0245</v>
           </cell>
@@ -23321,6 +23855,7 @@
           <cell r="A298" t="str">
             <v>S-2026-03-144</v>
           </cell>
+          <cell r="B298"/>
           <cell r="C298" t="str">
             <v>RPRO-260401-0247</v>
           </cell>
@@ -23389,6 +23924,7 @@
           <cell r="A299" t="str">
             <v>S-2026-03-145</v>
           </cell>
+          <cell r="B299"/>
           <cell r="C299" t="str">
             <v>RPRO-260401-0248</v>
           </cell>
@@ -23457,6 +23993,7 @@
           <cell r="A300" t="str">
             <v>S-2026-03-146</v>
           </cell>
+          <cell r="B300"/>
           <cell r="C300" t="str">
             <v>RPRO-260401-0249</v>
           </cell>
@@ -23525,6 +24062,7 @@
           <cell r="A301" t="str">
             <v>S-2026-04-01</v>
           </cell>
+          <cell r="B301"/>
           <cell r="C301" t="str">
             <v>RPRO-260401-0250</v>
           </cell>
@@ -23593,6 +24131,7 @@
           <cell r="A302" t="str">
             <v>S-2026-04-02</v>
           </cell>
+          <cell r="B302"/>
           <cell r="C302" t="str">
             <v>RPRO-260401-0251</v>
           </cell>
@@ -23661,6 +24200,7 @@
           <cell r="A303" t="str">
             <v>S-2026-04-03</v>
           </cell>
+          <cell r="B303"/>
           <cell r="C303" t="str">
             <v>RPRO-260402-0737</v>
           </cell>
@@ -23729,6 +24269,7 @@
           <cell r="A304" t="str">
             <v>S-2026-04-04</v>
           </cell>
+          <cell r="B304"/>
           <cell r="C304" t="str">
             <v>RPRO-260402-0738</v>
           </cell>
@@ -23797,6 +24338,7 @@
           <cell r="A305" t="str">
             <v>S-2026-04-05</v>
           </cell>
+          <cell r="B305"/>
           <cell r="C305" t="str">
             <v>RPRO-260403-0489</v>
           </cell>
@@ -23865,6 +24407,7 @@
           <cell r="A306" t="str">
             <v>S-2026-04-06</v>
           </cell>
+          <cell r="B306"/>
           <cell r="C306" t="str">
             <v>RPRO-260403-0490</v>
           </cell>
@@ -23933,6 +24476,7 @@
           <cell r="A307" t="str">
             <v>S-2026-04-07</v>
           </cell>
+          <cell r="B307"/>
           <cell r="C307" t="str">
             <v>RPRO-260403-0491</v>
           </cell>
@@ -24001,6 +24545,7 @@
           <cell r="A308" t="str">
             <v>S-2026-04-08</v>
           </cell>
+          <cell r="B308"/>
           <cell r="C308" t="str">
             <v>RPRO-260403-0492</v>
           </cell>
@@ -24069,6 +24614,7 @@
           <cell r="A309" t="str">
             <v>S-2026-04-09</v>
           </cell>
+          <cell r="B309"/>
           <cell r="C309" t="str">
             <v>RPRO-260406-1201</v>
           </cell>
@@ -24137,6 +24683,7 @@
           <cell r="A310" t="str">
             <v>S-2026-04-10</v>
           </cell>
+          <cell r="B310"/>
           <cell r="C310" t="str">
             <v>RPRO-260406-1202</v>
           </cell>
@@ -24205,6 +24752,7 @@
           <cell r="A311" t="str">
             <v>S-2026-04-11</v>
           </cell>
+          <cell r="B311"/>
           <cell r="C311" t="str">
             <v>RPRO-260406-1203</v>
           </cell>
@@ -24273,6 +24821,7 @@
           <cell r="A312" t="str">
             <v>S-2026-04-12</v>
           </cell>
+          <cell r="B312"/>
           <cell r="C312" t="str">
             <v>RPRO-260407-0417</v>
           </cell>
@@ -24341,6 +24890,7 @@
           <cell r="A313" t="str">
             <v>S-2026-04-13</v>
           </cell>
+          <cell r="B313"/>
           <cell r="C313" t="str">
             <v>RPRO-260407-0418</v>
           </cell>
@@ -24409,6 +24959,7 @@
           <cell r="A314" t="str">
             <v>S-2026-04-14</v>
           </cell>
+          <cell r="B314"/>
           <cell r="C314" t="str">
             <v>RPRO-260407-0419</v>
           </cell>
@@ -24477,6 +25028,7 @@
           <cell r="A315" t="str">
             <v>S-2026-04-15</v>
           </cell>
+          <cell r="B315"/>
           <cell r="C315" t="str">
             <v>RPRO-260407-0420</v>
           </cell>
@@ -24545,6 +25097,7 @@
           <cell r="A316" t="str">
             <v>S-2026-04-16</v>
           </cell>
+          <cell r="B316"/>
           <cell r="C316" t="str">
             <v>RPRO-260409-0346</v>
           </cell>
@@ -24613,6 +25166,7 @@
           <cell r="A317" t="str">
             <v>S-2026-04-17</v>
           </cell>
+          <cell r="B317"/>
           <cell r="C317" t="str">
             <v>RPRO-260409-0347</v>
           </cell>
@@ -24681,6 +25235,7 @@
           <cell r="A318" t="str">
             <v>S-2026-04-18</v>
           </cell>
+          <cell r="B318"/>
           <cell r="C318" t="str">
             <v>RPRO-260409-0348</v>
           </cell>
@@ -24749,6 +25304,7 @@
           <cell r="A319" t="str">
             <v>S-2026-04-19</v>
           </cell>
+          <cell r="B319"/>
           <cell r="C319" t="str">
             <v>RPRO-260409-0349</v>
           </cell>
@@ -24817,6 +25373,7 @@
           <cell r="A320" t="str">
             <v>S-2026-04-20</v>
           </cell>
+          <cell r="B320"/>
           <cell r="C320" t="str">
             <v>RPRO-260409-0350</v>
           </cell>
@@ -24885,6 +25442,7 @@
           <cell r="A321" t="str">
             <v>L-2026-04-21</v>
           </cell>
+          <cell r="B321"/>
           <cell r="C321" t="str">
             <v>RPRO-260410-0280</v>
           </cell>
@@ -24918,6 +25476,7 @@
           <cell r="M321" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N321"/>
           <cell r="O321" t="str">
             <v>Lab test</v>
           </cell>
@@ -24950,6 +25509,7 @@
           <cell r="A322" t="str">
             <v>L-2026-04-22</v>
           </cell>
+          <cell r="B322"/>
           <cell r="C322" t="str">
             <v>RPRO-260410-0281</v>
           </cell>
@@ -24983,6 +25543,7 @@
           <cell r="M322" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N322"/>
           <cell r="O322" t="str">
             <v>Lab test</v>
           </cell>
@@ -25015,6 +25576,7 @@
           <cell r="A323" t="str">
             <v>S-2026-04-23</v>
           </cell>
+          <cell r="B323"/>
           <cell r="C323" t="str">
             <v>RPRO-260410-0282</v>
           </cell>
@@ -25083,6 +25645,7 @@
           <cell r="A324" t="str">
             <v>S-2026-04-24</v>
           </cell>
+          <cell r="B324"/>
           <cell r="C324" t="str">
             <v>RPRO-260410-0283</v>
           </cell>
@@ -25151,6 +25714,7 @@
           <cell r="A325" t="str">
             <v>S-2026-04-25</v>
           </cell>
+          <cell r="B325"/>
           <cell r="C325" t="str">
             <v>RPRO-260410-0284</v>
           </cell>
@@ -25219,6 +25783,7 @@
           <cell r="A326" t="str">
             <v>S-2026-04-26</v>
           </cell>
+          <cell r="B326"/>
           <cell r="C326" t="str">
             <v>RPRO-260410-0285</v>
           </cell>
@@ -25287,6 +25852,7 @@
           <cell r="A327" t="str">
             <v>S-2026-04-27</v>
           </cell>
+          <cell r="B327"/>
           <cell r="C327" t="str">
             <v>RPRO-260410-0286</v>
           </cell>
@@ -25355,6 +25921,7 @@
           <cell r="A328" t="str">
             <v>S-2026-04-28</v>
           </cell>
+          <cell r="B328"/>
           <cell r="C328" t="str">
             <v>RPRO-260410-0287</v>
           </cell>
@@ -25494,6 +26061,7 @@
           <cell r="A330" t="str">
             <v>S-2026-04-30</v>
           </cell>
+          <cell r="B330"/>
           <cell r="C330" t="str">
             <v>RPRO-260414-0202</v>
           </cell>
@@ -25562,6 +26130,7 @@
           <cell r="A331" t="str">
             <v>S-2026-04-31</v>
           </cell>
+          <cell r="B331"/>
           <cell r="C331" t="str">
             <v>RPRO-260414-0203</v>
           </cell>
@@ -25630,6 +26199,7 @@
           <cell r="A332" t="str">
             <v>S-2026-04-32</v>
           </cell>
+          <cell r="B332"/>
           <cell r="C332" t="str">
             <v>RPRO-260414-0204</v>
           </cell>
@@ -25698,6 +26268,7 @@
           <cell r="A333" t="str">
             <v>S-2026-04-33</v>
           </cell>
+          <cell r="B333"/>
           <cell r="C333" t="str">
             <v>RPRO-260414-0205</v>
           </cell>
@@ -25766,6 +26337,7 @@
           <cell r="A334" t="str">
             <v>S-2026-04-34</v>
           </cell>
+          <cell r="B334"/>
           <cell r="C334" t="str">
             <v>RPRO-260414-0206</v>
           </cell>
@@ -25834,6 +26406,7 @@
           <cell r="A335" t="str">
             <v>S-2026-04-35</v>
           </cell>
+          <cell r="B335"/>
           <cell r="C335" t="str">
             <v>RPRO-260414-0207</v>
           </cell>
@@ -25902,6 +26475,7 @@
           <cell r="A336" t="str">
             <v>S-2026-04-36</v>
           </cell>
+          <cell r="B336"/>
           <cell r="C336" t="str">
             <v>RPRO-260414-0208</v>
           </cell>
@@ -25970,6 +26544,7 @@
           <cell r="A337" t="str">
             <v>S-2026-04-37</v>
           </cell>
+          <cell r="B337"/>
           <cell r="C337" t="str">
             <v>RPRO-260414-0209</v>
           </cell>
@@ -26038,6 +26613,7 @@
           <cell r="A338" t="str">
             <v>S-2026-04-38</v>
           </cell>
+          <cell r="B338"/>
           <cell r="C338" t="str">
             <v>RPRO-260414-0210</v>
           </cell>
@@ -26106,6 +26682,7 @@
           <cell r="A339" t="str">
             <v>S-2026-04-39</v>
           </cell>
+          <cell r="B339"/>
           <cell r="C339" t="str">
             <v>RPRO-260414-0211</v>
           </cell>
@@ -26174,6 +26751,7 @@
           <cell r="A340" t="str">
             <v>S-2026-04-40</v>
           </cell>
+          <cell r="B340"/>
           <cell r="C340" t="str">
             <v>RPRO-260414-0212</v>
           </cell>
@@ -26278,6 +26856,7 @@
           <cell r="M341" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N341"/>
           <cell r="O341" t="str">
             <v>Lab test</v>
           </cell>
@@ -26346,6 +26925,7 @@
           <cell r="M342" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N342"/>
           <cell r="O342" t="str">
             <v>Lab test</v>
           </cell>
@@ -26378,6 +26958,7 @@
           <cell r="A343" t="str">
             <v>S-2026-04-43</v>
           </cell>
+          <cell r="B343"/>
           <cell r="C343" t="str">
             <v>RPRO-260417-0243</v>
           </cell>
@@ -26446,6 +27027,7 @@
           <cell r="A344" t="str">
             <v>S-2026-04-44</v>
           </cell>
+          <cell r="B344"/>
           <cell r="C344" t="str">
             <v>RPRO-260417-0244</v>
           </cell>
@@ -26514,6 +27096,7 @@
           <cell r="A345" t="str">
             <v>S-2026-04-45</v>
           </cell>
+          <cell r="B345"/>
           <cell r="C345" t="str">
             <v>RPRO-260417-0245</v>
           </cell>
@@ -26582,6 +27165,7 @@
           <cell r="A346" t="str">
             <v>S-2026-04-46</v>
           </cell>
+          <cell r="B346"/>
           <cell r="C346" t="str">
             <v>RPRO-260417-0246</v>
           </cell>
@@ -26650,6 +27234,7 @@
           <cell r="A347" t="str">
             <v>S-2026-04-47</v>
           </cell>
+          <cell r="B347"/>
           <cell r="C347" t="str">
             <v>RPRO-260417-0247</v>
           </cell>
@@ -26718,6 +27303,7 @@
           <cell r="A348" t="str">
             <v>S-2026-04-48</v>
           </cell>
+          <cell r="B348"/>
           <cell r="C348" t="str">
             <v>RPRO-260421-0623</v>
           </cell>
@@ -26786,6 +27372,7 @@
           <cell r="A349" t="str">
             <v>S-2026-04-49</v>
           </cell>
+          <cell r="B349"/>
           <cell r="C349" t="str">
             <v>RPRO-260421-0624</v>
           </cell>
@@ -26854,6 +27441,7 @@
           <cell r="A350" t="str">
             <v>S-2026-04-50</v>
           </cell>
+          <cell r="B350"/>
           <cell r="C350" t="str">
             <v>RPRO-260421-0625</v>
           </cell>
@@ -26922,6 +27510,7 @@
           <cell r="A351" t="str">
             <v>S-2026-04-51</v>
           </cell>
+          <cell r="B351"/>
           <cell r="C351" t="str">
             <v>RPRO-260421-0626</v>
           </cell>
@@ -26990,6 +27579,7 @@
           <cell r="A352" t="str">
             <v>S-2026-04-52</v>
           </cell>
+          <cell r="B352"/>
           <cell r="C352" t="str">
             <v>RPRO-260421-0627</v>
           </cell>
@@ -27058,6 +27648,7 @@
           <cell r="A353" t="str">
             <v>S-2026-04-53</v>
           </cell>
+          <cell r="B353"/>
           <cell r="C353" t="str">
             <v>RPRO-260421-0628</v>
           </cell>
@@ -27126,6 +27717,7 @@
           <cell r="A354" t="str">
             <v>S-2026-04-54</v>
           </cell>
+          <cell r="B354"/>
           <cell r="C354" t="str">
             <v>RPRO-260421-0629</v>
           </cell>
@@ -27194,6 +27786,7 @@
           <cell r="A355" t="str">
             <v>S-2026-04-55</v>
           </cell>
+          <cell r="B355"/>
           <cell r="C355" t="str">
             <v>RPRO-260421-0630</v>
           </cell>
@@ -27262,6 +27855,7 @@
           <cell r="A356" t="str">
             <v>S-2026-04-56</v>
           </cell>
+          <cell r="B356"/>
           <cell r="C356" t="str">
             <v>RPRO-260421-0631</v>
           </cell>
@@ -27330,6 +27924,7 @@
           <cell r="A357" t="str">
             <v>S-2026-04-57</v>
           </cell>
+          <cell r="B357"/>
           <cell r="C357" t="str">
             <v>RPRO-260421-0632</v>
           </cell>
@@ -27398,6 +27993,7 @@
           <cell r="A358" t="str">
             <v>S-2026-04-58</v>
           </cell>
+          <cell r="B358"/>
           <cell r="C358" t="str">
             <v>RPRO-260421-0633</v>
           </cell>
@@ -27466,6 +28062,7 @@
           <cell r="A359" t="str">
             <v>S-2026-04-59</v>
           </cell>
+          <cell r="B359"/>
           <cell r="C359" t="str">
             <v>RPRO-260422-0268</v>
           </cell>
@@ -27534,6 +28131,7 @@
           <cell r="A360" t="str">
             <v>S-2026-04-60</v>
           </cell>
+          <cell r="B360"/>
           <cell r="C360" t="str">
             <v>RPRO-260423-0486</v>
           </cell>
@@ -27602,6 +28200,7 @@
           <cell r="A361" t="str">
             <v>S-2026-04-61</v>
           </cell>
+          <cell r="B361"/>
           <cell r="C361" t="str">
             <v>RPRO-260423-0487</v>
           </cell>
@@ -27670,6 +28269,7 @@
           <cell r="A362" t="str">
             <v>S-2026-04-62</v>
           </cell>
+          <cell r="B362"/>
           <cell r="C362" t="str">
             <v>RPRO-260424-1197</v>
           </cell>
@@ -27738,6 +28338,7 @@
           <cell r="A363" t="str">
             <v>S-2026-04-63</v>
           </cell>
+          <cell r="B363"/>
           <cell r="C363" t="str">
             <v>RPRO-260424-1198</v>
           </cell>
@@ -27806,6 +28407,7 @@
           <cell r="A364" t="str">
             <v>S-2026-04-64</v>
           </cell>
+          <cell r="B364"/>
           <cell r="C364" t="str">
             <v>RPRO-260424-1199</v>
           </cell>
@@ -27874,6 +28476,7 @@
           <cell r="A365" t="str">
             <v>S-2026-04-65</v>
           </cell>
+          <cell r="B365"/>
           <cell r="C365" t="str">
             <v>RPRO-260424-1200</v>
           </cell>
@@ -27942,6 +28545,7 @@
           <cell r="A366" t="str">
             <v>S-2026-04-66</v>
           </cell>
+          <cell r="B366"/>
           <cell r="C366" t="str">
             <v>RPRO-260424-1201</v>
           </cell>
@@ -28081,6 +28685,7 @@
           <cell r="A368" t="str">
             <v>S-2026-04-68</v>
           </cell>
+          <cell r="B368"/>
           <cell r="C368" t="str">
             <v>RPRO-260424-1203</v>
           </cell>
@@ -28149,6 +28754,7 @@
           <cell r="A369" t="str">
             <v>S-2026-04-69</v>
           </cell>
+          <cell r="B369"/>
           <cell r="C369" t="str">
             <v>RPRO-260424-1204</v>
           </cell>
@@ -28217,6 +28823,7 @@
           <cell r="A370" t="str">
             <v>S-2026-04-70</v>
           </cell>
+          <cell r="B370"/>
           <cell r="C370" t="str">
             <v>RPRO-260424-1205</v>
           </cell>
@@ -28285,6 +28892,7 @@
           <cell r="A371" t="str">
             <v>S-2026-04-71</v>
           </cell>
+          <cell r="B371"/>
           <cell r="C371" t="str">
             <v>RPRO-260424-1206</v>
           </cell>
@@ -28353,6 +28961,7 @@
           <cell r="A372" t="str">
             <v>S-2026-04-72</v>
           </cell>
+          <cell r="B372"/>
           <cell r="C372" t="str">
             <v>RPRO-260428-0920</v>
           </cell>
@@ -28421,6 +29030,7 @@
           <cell r="A373" t="str">
             <v>S-2026-04-73</v>
           </cell>
+          <cell r="B373"/>
           <cell r="C373" t="str">
             <v>RPRO-260429-0109</v>
           </cell>
@@ -28489,6 +29099,7 @@
           <cell r="A374" t="str">
             <v>S-2026-04-74</v>
           </cell>
+          <cell r="B374"/>
           <cell r="C374" t="str">
             <v>RPRO-260429-0110</v>
           </cell>
@@ -28557,6 +29168,7 @@
           <cell r="A375" t="str">
             <v>S-2026-04-75</v>
           </cell>
+          <cell r="B375"/>
           <cell r="C375" t="str">
             <v>RPRO-260429-0126</v>
           </cell>
@@ -28625,6 +29237,7 @@
           <cell r="A376" t="str">
             <v>S-2026-04-76</v>
           </cell>
+          <cell r="B376"/>
           <cell r="C376" t="str">
             <v>RPRO-260429-0127</v>
           </cell>
@@ -28693,6 +29306,7 @@
           <cell r="A377" t="str">
             <v>S-2026-05-01</v>
           </cell>
+          <cell r="B377"/>
           <cell r="C377" t="str">
             <v>RPRO-260505-0654</v>
           </cell>
@@ -28832,6 +29446,7 @@
           <cell r="A379" t="str">
             <v>S-2026-05-03</v>
           </cell>
+          <cell r="B379"/>
           <cell r="C379" t="str">
             <v>RPRO-260505-0656</v>
           </cell>
@@ -28900,6 +29515,7 @@
           <cell r="A380" t="str">
             <v>S-2026-05-04</v>
           </cell>
+          <cell r="B380"/>
           <cell r="C380" t="str">
             <v>RPRO-260505-0657</v>
           </cell>
@@ -28968,6 +29584,7 @@
           <cell r="A381" t="str">
             <v>S-2026-05-05</v>
           </cell>
+          <cell r="B381"/>
           <cell r="C381" t="str">
             <v>RPRO-260505-0658</v>
           </cell>
@@ -29036,6 +29653,7 @@
           <cell r="A382" t="str">
             <v>S-2026-05-06</v>
           </cell>
+          <cell r="B382"/>
           <cell r="C382" t="str">
             <v>RPRO-260505-0659</v>
           </cell>
@@ -29104,6 +29722,7 @@
           <cell r="A383" t="str">
             <v>S-2026-05-07</v>
           </cell>
+          <cell r="B383"/>
           <cell r="C383" t="str">
             <v>RPRO-260505-0660</v>
           </cell>
@@ -29243,6 +29862,7 @@
           <cell r="A385" t="str">
             <v>S-2026-05-09</v>
           </cell>
+          <cell r="B385"/>
           <cell r="C385" t="str">
             <v>RPRO-260505-0662</v>
           </cell>
@@ -29311,6 +29931,7 @@
           <cell r="A386" t="str">
             <v>S-2026-05-10</v>
           </cell>
+          <cell r="B386"/>
           <cell r="C386" t="str">
             <v>RPRO-260505-0663</v>
           </cell>
@@ -29450,6 +30071,7 @@
           <cell r="A388" t="str">
             <v>S-2026-05-12</v>
           </cell>
+          <cell r="B388"/>
           <cell r="C388" t="str">
             <v>RPRO-260505-0802</v>
           </cell>
@@ -29518,6 +30140,7 @@
           <cell r="A389" t="str">
             <v>S-2026-05-13</v>
           </cell>
+          <cell r="B389"/>
           <cell r="C389" t="str">
             <v>RPRO-260505-0803</v>
           </cell>
@@ -29586,6 +30209,7 @@
           <cell r="A390" t="str">
             <v>S-2026-05-14</v>
           </cell>
+          <cell r="B390"/>
           <cell r="C390" t="str">
             <v>RPRO-260506-0394</v>
           </cell>
@@ -29654,6 +30278,7 @@
           <cell r="A391" t="str">
             <v>S-2026-05-15</v>
           </cell>
+          <cell r="B391"/>
           <cell r="C391" t="str">
             <v>RPRO-260506-0395</v>
           </cell>
@@ -29722,6 +30347,7 @@
           <cell r="A392" t="str">
             <v>S-2026-05-16</v>
           </cell>
+          <cell r="B392"/>
           <cell r="C392" t="str">
             <v>RPRO-260506-0396</v>
           </cell>
@@ -29790,6 +30416,7 @@
           <cell r="A393" t="str">
             <v>S-2026-05-17</v>
           </cell>
+          <cell r="B393"/>
           <cell r="C393" t="str">
             <v>RPRO-260506-0397</v>
           </cell>
@@ -29858,6 +30485,7 @@
           <cell r="A394" t="str">
             <v>S-2026-05-18</v>
           </cell>
+          <cell r="B394"/>
           <cell r="C394" t="str">
             <v>RPRO-260506-0415</v>
           </cell>
@@ -29926,6 +30554,7 @@
           <cell r="A395" t="str">
             <v>S-2026-05-19</v>
           </cell>
+          <cell r="B395"/>
           <cell r="C395" t="str">
             <v>RPRO-260508-0581</v>
           </cell>
@@ -29994,6 +30623,7 @@
           <cell r="A396" t="str">
             <v>S-2026-05-20</v>
           </cell>
+          <cell r="B396"/>
           <cell r="C396" t="str">
             <v>RPRO-260508-0582</v>
           </cell>
@@ -30062,6 +30692,7 @@
           <cell r="A397" t="str">
             <v>S-2026-05-21</v>
           </cell>
+          <cell r="B397"/>
           <cell r="C397" t="str">
             <v>RPRO-260508-0583</v>
           </cell>
@@ -30130,6 +30761,7 @@
           <cell r="A398" t="str">
             <v>S-2026-05-22</v>
           </cell>
+          <cell r="B398"/>
           <cell r="C398" t="str">
             <v>RPRO-260508-0584</v>
           </cell>
@@ -30198,6 +30830,7 @@
           <cell r="A399" t="str">
             <v>S-2026-05-23</v>
           </cell>
+          <cell r="B399"/>
           <cell r="C399" t="str">
             <v>RPRO-260508-0585</v>
           </cell>
@@ -30266,6 +30899,7 @@
           <cell r="A400" t="str">
             <v>S-2026-05-24</v>
           </cell>
+          <cell r="B400"/>
           <cell r="C400" t="str">
             <v>RPRO-260508-0586</v>
           </cell>
@@ -30334,6 +30968,7 @@
           <cell r="A401" t="str">
             <v>S-2026-05-25</v>
           </cell>
+          <cell r="B401"/>
           <cell r="C401" t="str">
             <v>RPRO-260508-0587</v>
           </cell>
@@ -30402,6 +31037,7 @@
           <cell r="A402" t="str">
             <v>S-2026-05-26</v>
           </cell>
+          <cell r="B402"/>
           <cell r="C402" t="str">
             <v>RPRO-260508-0588</v>
           </cell>
@@ -30470,6 +31106,7 @@
           <cell r="A403" t="str">
             <v>S-2026-05-27</v>
           </cell>
+          <cell r="B403"/>
           <cell r="C403" t="str">
             <v>RPRO-260512-0580</v>
           </cell>
@@ -30500,6 +31137,7 @@
           <cell r="L403" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M403"/>
           <cell r="N403" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -30535,6 +31173,7 @@
           <cell r="A404" t="str">
             <v>S-2026-05-28</v>
           </cell>
+          <cell r="B404"/>
           <cell r="C404" t="str">
             <v>RPRO-260512-0581</v>
           </cell>
@@ -30565,6 +31204,7 @@
           <cell r="L404" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M404"/>
           <cell r="N404" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -30600,6 +31240,7 @@
           <cell r="A405" t="str">
             <v>S-2026-05-29</v>
           </cell>
+          <cell r="B405"/>
           <cell r="C405" t="str">
             <v>RPRO-260512-0582</v>
           </cell>
@@ -30668,6 +31309,7 @@
           <cell r="A406" t="str">
             <v>S-2026-05-30</v>
           </cell>
+          <cell r="B406"/>
           <cell r="C406" t="str">
             <v>RPRO-260512-0583</v>
           </cell>
@@ -30736,6 +31378,7 @@
           <cell r="A407" t="str">
             <v>S-2026-05-31</v>
           </cell>
+          <cell r="B407"/>
           <cell r="C407" t="str">
             <v>RPRO-260513-0945</v>
           </cell>
@@ -30804,6 +31447,7 @@
           <cell r="A408" t="str">
             <v>S-2026-05-32</v>
           </cell>
+          <cell r="B408"/>
           <cell r="C408" t="str">
             <v>RPRO-260513-0946</v>
           </cell>
@@ -30872,6 +31516,7 @@
           <cell r="A409" t="str">
             <v>S-2026-05-33</v>
           </cell>
+          <cell r="B409"/>
           <cell r="C409" t="str">
             <v>RPRO-260513-0947</v>
           </cell>
@@ -30940,6 +31585,7 @@
           <cell r="A410" t="str">
             <v>S-2026-05-34</v>
           </cell>
+          <cell r="B410"/>
           <cell r="C410" t="str">
             <v>RPRO-260513-0948</v>
           </cell>
@@ -31079,6 +31725,7 @@
           <cell r="A412" t="str">
             <v>S-2026-05-36</v>
           </cell>
+          <cell r="B412"/>
           <cell r="C412" t="str">
             <v>RPRO-260513-0950</v>
           </cell>
@@ -31147,6 +31794,7 @@
           <cell r="A413" t="str">
             <v>S-2026-05-37</v>
           </cell>
+          <cell r="B413"/>
           <cell r="C413" t="str">
             <v>RPRO-260515-0272</v>
           </cell>
@@ -31215,6 +31863,7 @@
           <cell r="A414" t="str">
             <v>S-2026-05-38</v>
           </cell>
+          <cell r="B414"/>
           <cell r="C414" t="str">
             <v>RPRO-260515-0273</v>
           </cell>
@@ -31283,6 +31932,7 @@
           <cell r="A415" t="str">
             <v>S-2026-05-39</v>
           </cell>
+          <cell r="B415"/>
           <cell r="C415" t="str">
             <v>RPRO-260515-0274</v>
           </cell>
@@ -31351,6 +32001,7 @@
           <cell r="A416" t="str">
             <v>S-2026-05-40</v>
           </cell>
+          <cell r="B416"/>
           <cell r="C416" t="str">
             <v>RPRO-260515-0275</v>
           </cell>
@@ -31419,6 +32070,7 @@
           <cell r="A417" t="str">
             <v>S-2026-05-41</v>
           </cell>
+          <cell r="B417"/>
           <cell r="C417" t="str">
             <v>RPRO-260515-0276</v>
           </cell>
@@ -31487,6 +32139,7 @@
           <cell r="A418" t="str">
             <v>S-2026-05-42</v>
           </cell>
+          <cell r="B418"/>
           <cell r="C418" t="str">
             <v>RPRO-260515-0277</v>
           </cell>
@@ -31555,6 +32208,7 @@
           <cell r="A419" t="str">
             <v>S-2026-05-43</v>
           </cell>
+          <cell r="B419"/>
           <cell r="C419" t="str">
             <v>RPRO-260515-0278</v>
           </cell>
@@ -31623,6 +32277,7 @@
           <cell r="A420" t="str">
             <v>S-2026-05-44</v>
           </cell>
+          <cell r="B420"/>
           <cell r="C420" t="str">
             <v>RPRO-260515-0279</v>
           </cell>
@@ -31691,6 +32346,7 @@
           <cell r="A421" t="str">
             <v>S-2026-05-45</v>
           </cell>
+          <cell r="B421"/>
           <cell r="C421" t="str">
             <v>RPRO-260515-0280</v>
           </cell>
@@ -31713,10 +32369,10 @@
             <v>50</v>
           </cell>
           <cell r="J421">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K421">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L421" t="str">
             <v>ADIDAS</v>
@@ -31759,6 +32415,7 @@
           <cell r="A422" t="str">
             <v>S-2026-05-46</v>
           </cell>
+          <cell r="B422"/>
           <cell r="C422" t="str">
             <v>RPRO-260518-0853</v>
           </cell>
@@ -31781,10 +32438,10 @@
             <v>40</v>
           </cell>
           <cell r="J422">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K422">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L422" t="str">
             <v>ON RUNNING</v>
@@ -31827,6 +32484,7 @@
           <cell r="A423" t="str">
             <v>S-2026-05-47</v>
           </cell>
+          <cell r="B423"/>
           <cell r="C423" t="str">
             <v>RPRO-260518-0854</v>
           </cell>
@@ -31895,6 +32553,7 @@
           <cell r="A424" t="str">
             <v>S-2026-05-48</v>
           </cell>
+          <cell r="B424"/>
           <cell r="C424" t="str">
             <v>RPRO-260518-0855</v>
           </cell>
@@ -31963,6 +32622,7 @@
           <cell r="A425" t="str">
             <v>S-2026-05-49</v>
           </cell>
+          <cell r="B425"/>
           <cell r="C425" t="str">
             <v>RPRO-260518-0856</v>
           </cell>
@@ -31985,10 +32645,10 @@
             <v>30</v>
           </cell>
           <cell r="J425">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K425">
-            <v>30</v>
+            <v>0</v>
           </cell>
           <cell r="L425" t="str">
             <v>TRAVIS MATHEW</v>
@@ -32244,6 +32904,7 @@
           <cell r="A429" t="str">
             <v>S-2026-05-53</v>
           </cell>
+          <cell r="B429"/>
           <cell r="C429" t="str">
             <v>RPRO-260518-0860</v>
           </cell>
@@ -32266,10 +32927,10 @@
             <v>150</v>
           </cell>
           <cell r="J429">
-            <v>0</v>
+            <v>150</v>
           </cell>
           <cell r="K429">
-            <v>150</v>
+            <v>0</v>
           </cell>
           <cell r="L429" t="str">
             <v>ADIDAS</v>
@@ -32312,6 +32973,7 @@
           <cell r="A430" t="str">
             <v>S-2026-05-54</v>
           </cell>
+          <cell r="B430"/>
           <cell r="C430" t="str">
             <v>RPRO-260518-0861</v>
           </cell>
@@ -32334,10 +32996,10 @@
             <v>150</v>
           </cell>
           <cell r="J430">
-            <v>0</v>
+            <v>150</v>
           </cell>
           <cell r="K430">
-            <v>150</v>
+            <v>0</v>
           </cell>
           <cell r="L430" t="str">
             <v>ADIDAS</v>
@@ -32380,6 +33042,7 @@
           <cell r="A431" t="str">
             <v>S-2026-05-55</v>
           </cell>
+          <cell r="B431"/>
           <cell r="C431" t="str">
             <v>RPRO-260518-0862</v>
           </cell>
@@ -32402,10 +33065,10 @@
             <v>50</v>
           </cell>
           <cell r="J431">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K431">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L431" t="str">
             <v>ASICS</v>
@@ -32448,6 +33111,7 @@
           <cell r="A432" t="str">
             <v>S-2026-05-56</v>
           </cell>
+          <cell r="B432"/>
           <cell r="C432" t="str">
             <v>RPRO-260518-0863</v>
           </cell>
@@ -32470,10 +33134,10 @@
             <v>50</v>
           </cell>
           <cell r="J432">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K432">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L432" t="str">
             <v>ASICS</v>
@@ -32516,6 +33180,7 @@
           <cell r="A433" t="str">
             <v>S-2026-05-57</v>
           </cell>
+          <cell r="B433"/>
           <cell r="C433" t="str">
             <v>RPRO-260518-0864</v>
           </cell>
@@ -32538,10 +33203,10 @@
             <v>40</v>
           </cell>
           <cell r="J433">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K433">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L433" t="str">
             <v>PUMA</v>
@@ -32584,6 +33249,7 @@
           <cell r="A434" t="str">
             <v>S-2026-05-58</v>
           </cell>
+          <cell r="B434"/>
           <cell r="C434" t="str">
             <v>RPRO-260518-0865</v>
           </cell>
@@ -32606,10 +33272,10 @@
             <v>40</v>
           </cell>
           <cell r="J434">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K434">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L434" t="str">
             <v>PUMA</v>
@@ -32652,6 +33318,7 @@
           <cell r="A435" t="str">
             <v>S-2026-05-59</v>
           </cell>
+          <cell r="B435"/>
           <cell r="C435" t="str">
             <v>RPRO-260518-0866</v>
           </cell>
@@ -32674,10 +33341,10 @@
             <v>40</v>
           </cell>
           <cell r="J435">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K435">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L435" t="str">
             <v>ASICS</v>
@@ -32720,6 +33387,7 @@
           <cell r="A436" t="str">
             <v>S-2026-05-60</v>
           </cell>
+          <cell r="B436"/>
           <cell r="C436" t="str">
             <v>RPRO-260520-0192</v>
           </cell>
@@ -32788,6 +33456,7 @@
           <cell r="A437" t="str">
             <v>S-2026-05-61</v>
           </cell>
+          <cell r="B437"/>
           <cell r="C437" t="str">
             <v>RPRO-260520-0193</v>
           </cell>
@@ -32810,10 +33479,10 @@
             <v>40</v>
           </cell>
           <cell r="J437">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K437">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L437" t="str">
             <v>NIKE</v>
@@ -32856,6 +33525,7 @@
           <cell r="A438" t="str">
             <v>S-2026-05-62</v>
           </cell>
+          <cell r="B438"/>
           <cell r="C438" t="str">
             <v>RPRO-260520-0194</v>
           </cell>
@@ -32924,6 +33594,7 @@
           <cell r="A439" t="str">
             <v>S-2026-05-63</v>
           </cell>
+          <cell r="B439"/>
           <cell r="C439" t="str">
             <v>RPRO-260520-0195</v>
           </cell>
@@ -32946,10 +33617,10 @@
             <v>40</v>
           </cell>
           <cell r="J439">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K439">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L439" t="str">
             <v>NIKE</v>
@@ -32992,6 +33663,7 @@
           <cell r="A440" t="str">
             <v>S-2026-05-64</v>
           </cell>
+          <cell r="B440"/>
           <cell r="C440" t="str">
             <v>RPRO-260520-0196</v>
           </cell>
@@ -33014,10 +33686,10 @@
             <v>30</v>
           </cell>
           <cell r="J440">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K440">
-            <v>30</v>
+            <v>0</v>
           </cell>
           <cell r="L440" t="str">
             <v>NIKE</v>
@@ -33060,6 +33732,7 @@
           <cell r="A441" t="str">
             <v>S-2026-05-65</v>
           </cell>
+          <cell r="B441"/>
           <cell r="C441" t="str">
             <v>RPRO-260520-0197</v>
           </cell>
@@ -33082,10 +33755,10 @@
             <v>50</v>
           </cell>
           <cell r="J441">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K441">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L441" t="str">
             <v>NIKE</v>
@@ -33128,6 +33801,7 @@
           <cell r="A442" t="str">
             <v>S-2026-05-66</v>
           </cell>
+          <cell r="B442"/>
           <cell r="C442" t="str">
             <v>RPRO-260520-0225</v>
           </cell>
@@ -33150,10 +33824,10 @@
             <v>30</v>
           </cell>
           <cell r="J442">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K442">
-            <v>30</v>
+            <v>0</v>
           </cell>
           <cell r="L442" t="str">
             <v>ASICS</v>
@@ -33196,6 +33870,7 @@
           <cell r="A443" t="str">
             <v>S-2026-05-67</v>
           </cell>
+          <cell r="B443"/>
           <cell r="C443" t="str">
             <v>RPRO-260520-0226</v>
           </cell>
@@ -33218,10 +33893,10 @@
             <v>80</v>
           </cell>
           <cell r="J443">
-            <v>0</v>
+            <v>80</v>
           </cell>
           <cell r="K443">
-            <v>80</v>
+            <v>0</v>
           </cell>
           <cell r="L443" t="str">
             <v>ASICS</v>
@@ -33264,6 +33939,7 @@
           <cell r="A444" t="str">
             <v>S-2026-05-68</v>
           </cell>
+          <cell r="B444"/>
           <cell r="C444" t="str">
             <v>RPRO-260520-0227</v>
           </cell>
@@ -33286,10 +33962,10 @@
             <v>20</v>
           </cell>
           <cell r="J444">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="K444">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="L444" t="str">
             <v>ASICS</v>
@@ -33332,6 +34008,7 @@
           <cell r="A445" t="str">
             <v>S-2026-05-69</v>
           </cell>
+          <cell r="B445"/>
           <cell r="C445" t="str">
             <v>RPRO-260520-0228</v>
           </cell>
@@ -33354,10 +34031,10 @@
             <v>30</v>
           </cell>
           <cell r="J445">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K445">
-            <v>30</v>
+            <v>0</v>
           </cell>
           <cell r="L445" t="str">
             <v>NEW BALANCE</v>
@@ -33400,6 +34077,7 @@
           <cell r="A446" t="str">
             <v>S-2026-05-70</v>
           </cell>
+          <cell r="B446"/>
           <cell r="C446" t="str">
             <v>RPRO-260520-0229</v>
           </cell>
@@ -33422,10 +34100,10 @@
             <v>20</v>
           </cell>
           <cell r="J446">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="K446">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="L446" t="str">
             <v>ASICS</v>
@@ -33468,6 +34146,7 @@
           <cell r="A447" t="str">
             <v>S-2026-05-71</v>
           </cell>
+          <cell r="B447"/>
           <cell r="C447" t="str">
             <v>RPRO-260521-0669</v>
           </cell>
@@ -33536,6 +34215,7 @@
           <cell r="A448" t="str">
             <v>S-2026-05-72</v>
           </cell>
+          <cell r="B448"/>
           <cell r="C448" t="str">
             <v>RPRO-260521-0670</v>
           </cell>
@@ -33604,6 +34284,7 @@
           <cell r="A449" t="str">
             <v>S-2026-05-73</v>
           </cell>
+          <cell r="B449"/>
           <cell r="C449" t="str">
             <v>RPRO-260523-0221</v>
           </cell>
@@ -33626,10 +34307,10 @@
             <v>15</v>
           </cell>
           <cell r="J449">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="K449">
-            <v>15</v>
+            <v>0</v>
           </cell>
           <cell r="L449" t="str">
             <v>ADIDAS</v>
@@ -33672,6 +34353,7 @@
           <cell r="A450" t="str">
             <v>S-2026-05-74</v>
           </cell>
+          <cell r="B450"/>
           <cell r="C450" t="str">
             <v>RPRO-260523-0222</v>
           </cell>
@@ -33694,10 +34376,10 @@
             <v>100</v>
           </cell>
           <cell r="J450">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="K450">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="L450" t="str">
             <v>ADIDAS</v>
@@ -33740,6 +34422,7 @@
           <cell r="A451" t="str">
             <v>S-2026-05-75</v>
           </cell>
+          <cell r="B451"/>
           <cell r="C451" t="str">
             <v>RPRO-260523-0223</v>
           </cell>
@@ -33762,10 +34445,10 @@
             <v>20</v>
           </cell>
           <cell r="J451">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="K451">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="L451" t="str">
             <v>FOOTJOY</v>
@@ -33808,6 +34491,7 @@
           <cell r="A452" t="str">
             <v>S-2026-05-76</v>
           </cell>
+          <cell r="B452"/>
           <cell r="C452" t="str">
             <v>RPRO-260526-0394</v>
           </cell>
@@ -33830,10 +34514,10 @@
             <v>30</v>
           </cell>
           <cell r="J452">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K452">
-            <v>30</v>
+            <v>0</v>
           </cell>
           <cell r="L452" t="str">
             <v>ASICS</v>
@@ -33876,6 +34560,7 @@
           <cell r="A453" t="str">
             <v>S-2026-05-77</v>
           </cell>
+          <cell r="B453"/>
           <cell r="C453" t="str">
             <v>RPRO-260526-0395</v>
           </cell>
@@ -33898,10 +34583,10 @@
             <v>100</v>
           </cell>
           <cell r="J453">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="K453">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="L453" t="str">
             <v>ASICS</v>
@@ -33944,6 +34629,7 @@
           <cell r="A454" t="str">
             <v>S-2026-05-78</v>
           </cell>
+          <cell r="B454"/>
           <cell r="C454" t="str">
             <v>RPRO-260526-0396</v>
           </cell>
@@ -33966,10 +34652,10 @@
             <v>20</v>
           </cell>
           <cell r="J454">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="K454">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="L454" t="str">
             <v>ASICS</v>
@@ -34012,6 +34698,7 @@
           <cell r="A455" t="str">
             <v>S-2026-05-79</v>
           </cell>
+          <cell r="B455"/>
           <cell r="C455" t="str">
             <v>RPRO-260526-0397</v>
           </cell>
@@ -34034,10 +34721,10 @@
             <v>10</v>
           </cell>
           <cell r="J455">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="K455">
-            <v>10</v>
+            <v>0</v>
           </cell>
           <cell r="L455" t="str">
             <v>ASICS</v>
@@ -34080,6 +34767,7 @@
           <cell r="A456" t="str">
             <v>S-2026-05-80</v>
           </cell>
+          <cell r="B456"/>
           <cell r="C456" t="str">
             <v>RPRO-260526-0398</v>
           </cell>
@@ -34102,10 +34790,10 @@
             <v>50</v>
           </cell>
           <cell r="J456">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K456">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L456" t="str">
             <v>NEW BALANCE</v>
@@ -34148,6 +34836,7 @@
           <cell r="A457" t="str">
             <v>S-2026-05-81</v>
           </cell>
+          <cell r="B457"/>
           <cell r="C457" t="str">
             <v>RPRO-260526-0399</v>
           </cell>
@@ -34170,10 +34859,10 @@
             <v>50</v>
           </cell>
           <cell r="J457">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K457">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L457" t="str">
             <v>ASICS</v>
@@ -34216,6 +34905,7 @@
           <cell r="A458" t="str">
             <v>S-2026-05-82</v>
           </cell>
+          <cell r="B458"/>
           <cell r="C458" t="str">
             <v>RPRO-260526-0400</v>
           </cell>
@@ -34284,6 +34974,7 @@
           <cell r="A459" t="str">
             <v>S-2026-05-83</v>
           </cell>
+          <cell r="B459"/>
           <cell r="C459" t="str">
             <v>RPRO-260526-0401</v>
           </cell>
@@ -34306,10 +34997,10 @@
             <v>30</v>
           </cell>
           <cell r="J459">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K459">
-            <v>30</v>
+            <v>0</v>
           </cell>
           <cell r="L459" t="str">
             <v>ASICS</v>
@@ -34353,8 +35044,9 @@
             <v>S-2026-05-84</v>
           </cell>
           <cell r="B460" t="str">
-            <v>chờ cfm ETD</v>
-          </cell>
+            <v>ƯU TIÊN GIAO 06-JUN KHI CÓ LIỆU</v>
+          </cell>
+          <cell r="C460"/>
           <cell r="D460" t="str">
             <v>PUR2605250002S</v>
           </cell>
@@ -34420,6 +35112,7 @@
           <cell r="A461" t="str">
             <v>S-2026-05-85</v>
           </cell>
+          <cell r="B461"/>
           <cell r="C461" t="str">
             <v>RPRO-260526-0402</v>
           </cell>
@@ -34442,10 +35135,10 @@
             <v>50</v>
           </cell>
           <cell r="J461">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="K461">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="L461" t="str">
             <v>ADIDAS</v>
@@ -34655,10 +35348,10 @@
             <v>70</v>
           </cell>
           <cell r="J464">
-            <v>0</v>
+            <v>70</v>
           </cell>
           <cell r="K464">
-            <v>70</v>
+            <v>0</v>
           </cell>
           <cell r="L464" t="str">
             <v>NIKE</v>
@@ -34797,10 +35490,10 @@
             <v>40</v>
           </cell>
           <cell r="J466">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="K466">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="L466" t="str">
             <v>NIKE</v>
@@ -34914,6 +35607,7 @@
           <cell r="A468" t="str">
             <v>S-2026-05-92</v>
           </cell>
+          <cell r="B468"/>
           <cell r="C468" t="str">
             <v>RPRO-260528-0001</v>
           </cell>
@@ -34921,7 +35615,7 @@
             <v>PUR2605270002S</v>
           </cell>
           <cell r="E468" t="str">
-            <v/>
+            <v>BDB-000179</v>
           </cell>
           <cell r="F468" t="str">
             <v>PVN-004107</v>
@@ -34936,7 +35630,7 @@
             <v>30</v>
           </cell>
           <cell r="J468">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="K468">
             <v>0</v>
@@ -34968,14 +35662,14 @@
           <cell r="T468">
             <v>7</v>
           </cell>
-          <cell r="U468" t="str">
-            <v/>
+          <cell r="U468">
+            <v>5.5</v>
           </cell>
           <cell r="V468">
-            <v>0</v>
+            <v>0.04</v>
           </cell>
           <cell r="W468">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="469">
@@ -35548,41 +36242,46 @@
         </row>
         <row r="477">
           <cell r="A477" t="str">
-            <v>S-2026-05-101</v>
+            <v>S-2026-05-102</v>
+          </cell>
+          <cell r="B477" t="str">
+            <v>chờ tạo bom</v>
+          </cell>
+          <cell r="C477" t="str">
+            <v>RPRO-260601-0847</v>
           </cell>
           <cell r="D477" t="str">
             <v>PUR-202606010001S</v>
           </cell>
           <cell r="E477" t="str">
-            <v/>
+            <v>BDB-000123</v>
           </cell>
           <cell r="F477" t="str">
-            <v>PVN-004433</v>
+            <v>PVN-003298</v>
           </cell>
           <cell r="G477" t="str">
-            <v>OrthoLite X-30-Hybrid BROWN SUGAR/17-1134TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 15mm</v>
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
           </cell>
           <cell r="H477">
-            <v>10</v>
+            <v>100</v>
           </cell>
           <cell r="I477">
-            <v>10</v>
+            <v>100</v>
           </cell>
           <cell r="J477">
             <v>0</v>
           </cell>
           <cell r="K477">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="L477" t="str">
-            <v>ASICS</v>
+            <v>SALOMON</v>
           </cell>
           <cell r="M477" t="str">
             <v>Sample</v>
           </cell>
           <cell r="N477" t="str">
-            <v xml:space="preserve">DIE-CUT
-URGENT </v>
+            <v>FL SHEET</v>
           </cell>
           <cell r="O477" t="str">
             <v>Sample</v>
@@ -35602,46 +36301,47 @@
           <cell r="T477">
             <v>7</v>
           </cell>
-          <cell r="U477" t="str">
-            <v/>
+          <cell r="U477">
+            <v>4</v>
           </cell>
           <cell r="V477">
-            <v>0</v>
+            <v>2.8570000000000002E-2</v>
           </cell>
           <cell r="W477">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="478">
           <cell r="A478" t="str">
-            <v>S-2026-05-102</v>
-          </cell>
+            <v>S-2026-05-103</v>
+          </cell>
+          <cell r="B478"/>
           <cell r="C478" t="str">
-            <v>RPRO-260601-0847</v>
+            <v>RPRO-260601-0848</v>
           </cell>
           <cell r="D478" t="str">
             <v>PUR-202606010001S</v>
           </cell>
           <cell r="E478" t="str">
-            <v/>
+            <v>BDB-000123</v>
           </cell>
           <cell r="F478" t="str">
-            <v>PVN-003298</v>
+            <v>PVN-002973</v>
           </cell>
           <cell r="G478" t="str">
-            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+            <v>UltraLite-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
           </cell>
           <cell r="H478">
-            <v>100</v>
+            <v>30</v>
           </cell>
           <cell r="I478">
-            <v>100</v>
+            <v>30</v>
           </cell>
           <cell r="J478">
             <v>0</v>
           </cell>
           <cell r="K478">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="L478" t="str">
             <v>SALOMON</v>
@@ -35650,7 +36350,7 @@
             <v>Sample</v>
           </cell>
           <cell r="N478" t="str">
-            <v>FL SHEET</v>
+            <v>MOLDED</v>
           </cell>
           <cell r="O478" t="str">
             <v>Sample</v>
@@ -35670,55 +36370,56 @@
           <cell r="T478">
             <v>7</v>
           </cell>
-          <cell r="U478" t="str">
-            <v/>
+          <cell r="U478">
+            <v>4.5</v>
           </cell>
           <cell r="V478">
-            <v>0</v>
+            <v>3.2259999999999997E-2</v>
           </cell>
           <cell r="W478">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="479">
           <cell r="A479" t="str">
-            <v>S-2026-05-103</v>
-          </cell>
+            <v>S-2026-05-104</v>
+          </cell>
+          <cell r="B479"/>
           <cell r="C479" t="str">
-            <v>RPRO-260601-0848</v>
+            <v>RPRO-260601-0849</v>
           </cell>
           <cell r="D479" t="str">
             <v>PUR-202606010001S</v>
           </cell>
           <cell r="E479" t="str">
-            <v/>
+            <v>BDB-000113</v>
           </cell>
           <cell r="F479" t="str">
-            <v>PVN-002973</v>
+            <v>PVN-002465</v>
           </cell>
           <cell r="G479" t="str">
-            <v>UltraLite-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 5mm</v>
           </cell>
           <cell r="H479">
-            <v>30</v>
+            <v>50</v>
           </cell>
           <cell r="I479">
-            <v>30</v>
+            <v>50</v>
           </cell>
           <cell r="J479">
             <v>0</v>
           </cell>
           <cell r="K479">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="L479" t="str">
-            <v>SALOMON</v>
+            <v>ASICS</v>
           </cell>
           <cell r="M479" t="str">
             <v>Sample</v>
           </cell>
           <cell r="N479" t="str">
-            <v>MOLDED</v>
+            <v>DIE-CUT</v>
           </cell>
           <cell r="O479" t="str">
             <v>Sample</v>
@@ -35738,55 +36439,56 @@
           <cell r="T479">
             <v>7</v>
           </cell>
-          <cell r="U479" t="str">
-            <v/>
+          <cell r="U479">
+            <v>5</v>
           </cell>
           <cell r="V479">
-            <v>0</v>
+            <v>3.5709999999999999E-2</v>
           </cell>
           <cell r="W479">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="480">
           <cell r="A480" t="str">
-            <v>S-2026-05-104</v>
-          </cell>
+            <v>S-2026-05-105</v>
+          </cell>
+          <cell r="B480"/>
           <cell r="C480" t="str">
-            <v>RPRO-260601-0849</v>
+            <v>RPRO-260601-0850</v>
           </cell>
           <cell r="D480" t="str">
-            <v>PUR-202606010001S</v>
+            <v xml:space="preserve">PUR-202606010001S </v>
           </cell>
           <cell r="E480" t="str">
-            <v/>
+            <v>BDB-000058</v>
           </cell>
           <cell r="F480" t="str">
-            <v>PVN-002465</v>
+            <v>PVN-003630</v>
           </cell>
           <cell r="G480" t="str">
-            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 5mm</v>
+            <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 2mm</v>
           </cell>
           <cell r="H480">
-            <v>50</v>
+            <v>30</v>
           </cell>
           <cell r="I480">
-            <v>50</v>
+            <v>30</v>
           </cell>
           <cell r="J480">
             <v>0</v>
           </cell>
           <cell r="K480">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="L480" t="str">
-            <v>ASICS</v>
+            <v>UNDER ARMOUR</v>
           </cell>
           <cell r="M480" t="str">
-            <v>Sample</v>
+            <v>SSO-2606-00021    - URGENT (6-8)</v>
           </cell>
           <cell r="N480" t="str">
-            <v>DIE-CUT</v>
+            <v>Flat sheet</v>
           </cell>
           <cell r="O480" t="str">
             <v>Sample</v>
@@ -35806,55 +36508,56 @@
           <cell r="T480">
             <v>7</v>
           </cell>
-          <cell r="U480" t="str">
-            <v/>
+          <cell r="U480">
+            <v>2</v>
           </cell>
           <cell r="V480">
-            <v>0</v>
+            <v>1.4290000000000001E-2</v>
           </cell>
           <cell r="W480">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="481">
           <cell r="A481" t="str">
-            <v>S-2026-05-105</v>
-          </cell>
+            <v>S-2026-05-106</v>
+          </cell>
+          <cell r="B481"/>
           <cell r="C481" t="str">
-            <v>RPRO-260601-0850</v>
+            <v>RPRO-260601-0851</v>
           </cell>
           <cell r="D481" t="str">
             <v xml:space="preserve">PUR-202606010001S </v>
           </cell>
           <cell r="E481" t="str">
-            <v/>
+            <v>BDB-000180</v>
           </cell>
           <cell r="F481" t="str">
-            <v>PVN-003630</v>
+            <v>PVN-003236</v>
           </cell>
           <cell r="G481" t="str">
-            <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 2mm</v>
+            <v>OrthoLite Eco LT-Hybrid-Converse SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 5mm</v>
           </cell>
           <cell r="H481">
-            <v>30</v>
+            <v>50</v>
           </cell>
           <cell r="I481">
-            <v>30</v>
+            <v>50</v>
           </cell>
           <cell r="J481">
             <v>0</v>
           </cell>
           <cell r="K481">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="L481" t="str">
-            <v>UNDER ARMOUR</v>
+            <v>CONVERSE</v>
           </cell>
           <cell r="M481" t="str">
-            <v>SSO-2606-00021    - URGENT (6-8)</v>
+            <v>Sample</v>
           </cell>
           <cell r="N481" t="str">
-            <v>Flat sheet</v>
+            <v>Die cut</v>
           </cell>
           <cell r="O481" t="str">
             <v>Sample</v>
@@ -35874,55 +36577,59 @@
           <cell r="T481">
             <v>7</v>
           </cell>
-          <cell r="U481" t="str">
-            <v/>
+          <cell r="U481">
+            <v>5</v>
           </cell>
           <cell r="V481">
-            <v>0</v>
+            <v>3.5709999999999999E-2</v>
           </cell>
           <cell r="W481">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="482">
           <cell r="A482" t="str">
-            <v>S-2026-05-106</v>
+            <v>S-2026-06-01</v>
+          </cell>
+          <cell r="B482" t="str">
+            <v>chua rl</v>
           </cell>
           <cell r="C482" t="str">
-            <v>RPRO-260601-0851</v>
+            <v>RPRO-260602-0720</v>
           </cell>
           <cell r="D482" t="str">
-            <v xml:space="preserve">PUR-202606010001S </v>
+            <v>PUR-202606010001S</v>
           </cell>
           <cell r="E482" t="str">
-            <v/>
+            <v>BDB-000234</v>
           </cell>
           <cell r="F482" t="str">
-            <v>PVN-003236</v>
+            <v>PVN-004433</v>
           </cell>
           <cell r="G482" t="str">
-            <v>OrthoLite Eco LT-Hybrid-Converse SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 5mm</v>
+            <v>OrthoLite X-30-Hybrid BROWN SUGAR/17-1134TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 15mm</v>
           </cell>
           <cell r="H482">
-            <v>50</v>
+            <v>10</v>
           </cell>
           <cell r="I482">
-            <v>50</v>
+            <v>10</v>
           </cell>
           <cell r="J482">
             <v>0</v>
           </cell>
           <cell r="K482">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="L482" t="str">
-            <v>CONVERSE</v>
+            <v>ASICS</v>
           </cell>
           <cell r="M482" t="str">
             <v>Sample</v>
           </cell>
           <cell r="N482" t="str">
-            <v>Die cut</v>
+            <v xml:space="preserve">DIE-CUT
+URGENT </v>
           </cell>
           <cell r="O482" t="str">
             <v>Sample</v>
@@ -35946,182 +36653,601 @@
             <v/>
           </cell>
           <cell r="V482">
-            <v>0</v>
+            <v>0.11111</v>
           </cell>
           <cell r="W482">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="483">
+          <cell r="A483" t="str">
+            <v>S-2026-06-02</v>
+          </cell>
+          <cell r="B483" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C483" t="str">
+            <v>RPRO-260602-0721</v>
+          </cell>
+          <cell r="D483" t="str">
+            <v>PUR2600600100003S</v>
+          </cell>
           <cell r="E483" t="str">
-            <v/>
+            <v>BDB-000212</v>
+          </cell>
+          <cell r="F483" t="str">
+            <v>PVN-003764</v>
+          </cell>
+          <cell r="G483" t="str">
+            <v>OrthoLite X-25-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.12D 20+/-4 Asker C 1.1M 2M 5mm</v>
+          </cell>
+          <cell r="H483">
+            <v>30</v>
+          </cell>
+          <cell r="I483">
+            <v>30</v>
           </cell>
           <cell r="J483">
             <v>0</v>
           </cell>
           <cell r="K483">
-            <v>0</v>
-          </cell>
-          <cell r="U483" t="str">
-            <v/>
+            <v>30</v>
+          </cell>
+          <cell r="L483" t="str">
+            <v>FOOTJOY</v>
+          </cell>
+          <cell r="M483" t="str">
+            <v xml:space="preserve"> Sample/ URGENT</v>
+          </cell>
+          <cell r="N483" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O483" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P483">
+            <v>46174</v>
+          </cell>
+          <cell r="Q483">
+            <v>46181</v>
+          </cell>
+          <cell r="R483">
+            <v>46178</v>
+          </cell>
+          <cell r="S483">
+            <v>6</v>
+          </cell>
+          <cell r="T483">
+            <v>7</v>
+          </cell>
+          <cell r="U483">
+            <v>5</v>
           </cell>
           <cell r="V483">
-            <v>0</v>
+            <v>3.5709999999999999E-2</v>
           </cell>
           <cell r="W483">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="484">
+          <cell r="A484" t="str">
+            <v>S-2026-06-03</v>
+          </cell>
+          <cell r="B484" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C484" t="str">
+            <v>RPRO-260602-0722</v>
+          </cell>
+          <cell r="D484" t="str">
+            <v>PUR-202606020001S</v>
+          </cell>
           <cell r="E484" t="str">
-            <v/>
+            <v>BDB-000321</v>
+          </cell>
+          <cell r="F484" t="str">
+            <v>PVN-004092</v>
+          </cell>
+          <cell r="G484" t="str">
+            <v>OrthoLite Float BLUE ATOLL/16-4535TPX Flat Sheet 0.12D 21+/-4 Asker C 1.1M 2M 14.5mm</v>
+          </cell>
+          <cell r="H484">
+            <v>30</v>
+          </cell>
+          <cell r="I484">
+            <v>30</v>
           </cell>
           <cell r="J484">
             <v>0</v>
           </cell>
           <cell r="K484">
-            <v>0</v>
-          </cell>
-          <cell r="U484" t="str">
-            <v/>
+            <v>30</v>
+          </cell>
+          <cell r="L484" t="str">
+            <v>LOWA</v>
+          </cell>
+          <cell r="M484" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N484" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O484" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P484">
+            <v>46175</v>
+          </cell>
+          <cell r="Q484">
+            <v>46182</v>
+          </cell>
+          <cell r="R484">
+            <v>46179</v>
+          </cell>
+          <cell r="S484">
+            <v>6</v>
+          </cell>
+          <cell r="T484">
+            <v>7</v>
+          </cell>
+          <cell r="U484">
+            <v>14.5</v>
           </cell>
           <cell r="V484">
-            <v>0</v>
+            <v>0.11111</v>
           </cell>
           <cell r="W484">
-            <v>0</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="485">
+          <cell r="A485" t="str">
+            <v>S-2026-06-04</v>
+          </cell>
+          <cell r="B485" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C485" t="str">
+            <v>RPRO-260602-0723</v>
+          </cell>
+          <cell r="D485" t="str">
+            <v>PUR-202606020001S</v>
+          </cell>
           <cell r="E485" t="str">
-            <v/>
+            <v>BDB-000051</v>
+          </cell>
+          <cell r="F485" t="str">
+            <v>PVN-004057</v>
+          </cell>
+          <cell r="G485" t="str">
+            <v>OrthoLite X-40 TRUE BLUE/19-4057TPX Flat Sheet 0.16D 25+/-4 Asker C 1.1M 1.7M 14.5mm</v>
+          </cell>
+          <cell r="H485">
+            <v>20</v>
+          </cell>
+          <cell r="I485">
+            <v>20</v>
           </cell>
           <cell r="J485">
             <v>0</v>
           </cell>
           <cell r="K485">
-            <v>0</v>
-          </cell>
-          <cell r="U485" t="str">
-            <v/>
+            <v>20</v>
+          </cell>
+          <cell r="L485" t="str">
+            <v>LOWA</v>
+          </cell>
+          <cell r="M485" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N485" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O485" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P485">
+            <v>46175</v>
+          </cell>
+          <cell r="Q485">
+            <v>46182</v>
+          </cell>
+          <cell r="R485">
+            <v>46179</v>
+          </cell>
+          <cell r="S485">
+            <v>6</v>
+          </cell>
+          <cell r="T485">
+            <v>7</v>
+          </cell>
+          <cell r="U485">
+            <v>14.5</v>
           </cell>
           <cell r="V485">
-            <v>0</v>
+            <v>0.11111</v>
           </cell>
           <cell r="W485">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="486">
+          <cell r="A486" t="str">
+            <v>S-2026-06-05</v>
+          </cell>
+          <cell r="B486" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C486" t="str">
+            <v>RPRO-260602-0724</v>
+          </cell>
+          <cell r="D486" t="str">
+            <v>PUR-202606020001S</v>
+          </cell>
           <cell r="E486" t="str">
-            <v/>
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F486" t="str">
+            <v>PVN-003743</v>
+          </cell>
+          <cell r="G486" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 5.5mm</v>
+          </cell>
+          <cell r="H486">
+            <v>30</v>
+          </cell>
+          <cell r="I486">
+            <v>30</v>
           </cell>
           <cell r="J486">
             <v>0</v>
           </cell>
           <cell r="K486">
-            <v>0</v>
-          </cell>
-          <cell r="U486" t="str">
-            <v/>
+            <v>30</v>
+          </cell>
+          <cell r="L486" t="str">
+            <v>LOWA</v>
+          </cell>
+          <cell r="M486" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N486" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O486" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P486">
+            <v>46175</v>
+          </cell>
+          <cell r="Q486">
+            <v>46182</v>
+          </cell>
+          <cell r="R486">
+            <v>46179</v>
+          </cell>
+          <cell r="S486">
+            <v>6</v>
+          </cell>
+          <cell r="T486">
+            <v>7</v>
+          </cell>
+          <cell r="U486">
+            <v>5.5</v>
           </cell>
           <cell r="V486">
-            <v>0</v>
+            <v>0.04</v>
           </cell>
           <cell r="W486">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="487">
+          <cell r="A487" t="str">
+            <v>S-2026-06-06</v>
+          </cell>
+          <cell r="B487" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C487" t="str">
+            <v>RPRO-260602-0725</v>
+          </cell>
+          <cell r="D487" t="str">
+            <v xml:space="preserve">PUR2606020002S   </v>
+          </cell>
           <cell r="E487" t="str">
-            <v/>
+            <v>BDB-000058</v>
+          </cell>
+          <cell r="F487" t="str">
+            <v>PVN-004098</v>
+          </cell>
+          <cell r="G487" t="str">
+            <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H487">
+            <v>30</v>
+          </cell>
+          <cell r="I487">
+            <v>30</v>
           </cell>
           <cell r="J487">
             <v>0</v>
           </cell>
           <cell r="K487">
-            <v>0</v>
-          </cell>
-          <cell r="U487" t="str">
-            <v/>
+            <v>30</v>
+          </cell>
+          <cell r="L487" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M487" t="str">
+            <v>SSO-2606-00031    - URGENT (6-10)</v>
+          </cell>
+          <cell r="N487" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O487" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P487">
+            <v>46175</v>
+          </cell>
+          <cell r="Q487">
+            <v>46182</v>
+          </cell>
+          <cell r="R487">
+            <v>46179</v>
+          </cell>
+          <cell r="S487">
+            <v>6</v>
+          </cell>
+          <cell r="T487">
+            <v>7</v>
+          </cell>
+          <cell r="U487">
+            <v>3</v>
           </cell>
           <cell r="V487">
-            <v>0</v>
+            <v>2.1739999999999999E-2</v>
           </cell>
           <cell r="W487">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="488">
+          <cell r="A488" t="str">
+            <v>S-2026-06-07</v>
+          </cell>
+          <cell r="B488" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C488" t="str">
+            <v>RPRO-260602-0726</v>
+          </cell>
+          <cell r="D488" t="str">
+            <v xml:space="preserve">PUR2606020002S   </v>
+          </cell>
           <cell r="E488" t="str">
-            <v/>
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F488" t="str">
+            <v>PVN-003300</v>
+          </cell>
+          <cell r="G488" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 2mm</v>
+          </cell>
+          <cell r="H488">
+            <v>60</v>
+          </cell>
+          <cell r="I488">
+            <v>60</v>
           </cell>
           <cell r="J488">
             <v>0</v>
           </cell>
           <cell r="K488">
-            <v>0</v>
-          </cell>
-          <cell r="U488" t="str">
-            <v/>
+            <v>60</v>
+          </cell>
+          <cell r="L488" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M488" t="str">
+            <v>SSO-2606-00031    - URGENT (6-10)</v>
+          </cell>
+          <cell r="N488" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O488" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P488">
+            <v>46175</v>
+          </cell>
+          <cell r="Q488">
+            <v>46182</v>
+          </cell>
+          <cell r="R488">
+            <v>46179</v>
+          </cell>
+          <cell r="S488">
+            <v>6</v>
+          </cell>
+          <cell r="T488">
+            <v>7</v>
+          </cell>
+          <cell r="U488">
+            <v>2</v>
           </cell>
           <cell r="V488">
-            <v>0</v>
+            <v>1.4290000000000001E-2</v>
           </cell>
           <cell r="W488">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="489">
+          <cell r="A489" t="str">
+            <v>S-2026-06-08</v>
+          </cell>
+          <cell r="B489" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C489" t="str">
+            <v>RPRO-260602-0727</v>
+          </cell>
+          <cell r="D489" t="str">
+            <v xml:space="preserve">PUR2606020002S   </v>
+          </cell>
           <cell r="E489" t="str">
-            <v/>
+            <v>BDB-000348</v>
+          </cell>
+          <cell r="F489" t="str">
+            <v>PVN-004330</v>
+          </cell>
+          <cell r="G489" t="str">
+            <v>OrthoLite IMPERIAL SEEDPEARL/12-0703TPX Flat Sheet 0.22D 25+/-4 Asker C 1.1M 1.47M 2mm</v>
+          </cell>
+          <cell r="H489">
+            <v>50</v>
+          </cell>
+          <cell r="I489">
+            <v>50</v>
           </cell>
           <cell r="J489">
             <v>0</v>
           </cell>
           <cell r="K489">
-            <v>0</v>
-          </cell>
-          <cell r="U489" t="str">
-            <v/>
+            <v>50</v>
+          </cell>
+          <cell r="L489" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M489" t="str">
+            <v>SSO-2606-00031</v>
+          </cell>
+          <cell r="N489" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O489" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P489">
+            <v>46175</v>
+          </cell>
+          <cell r="Q489">
+            <v>46182</v>
+          </cell>
+          <cell r="R489">
+            <v>46179</v>
+          </cell>
+          <cell r="S489">
+            <v>6</v>
+          </cell>
+          <cell r="T489">
+            <v>7</v>
+          </cell>
+          <cell r="U489">
+            <v>2</v>
           </cell>
           <cell r="V489">
-            <v>0</v>
+            <v>1.389E-2</v>
           </cell>
           <cell r="W489">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="490">
+          <cell r="A490"/>
+          <cell r="B490" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C490"/>
+          <cell r="D490"/>
           <cell r="E490" t="str">
             <v/>
           </cell>
+          <cell r="F490" t="str">
+            <v>PVN-004436</v>
+          </cell>
+          <cell r="G490" t="str">
+            <v>OrthoLite X-55-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.16D 25+/-4 Asker C 1.1M 2M 5mm</v>
+          </cell>
+          <cell r="H490">
+            <v>20</v>
+          </cell>
+          <cell r="I490">
+            <v>20</v>
+          </cell>
           <cell r="J490">
             <v>0</v>
           </cell>
           <cell r="K490">
-            <v>0</v>
+            <v>20</v>
+          </cell>
+          <cell r="L490" t="str">
+            <v>PAYNTR</v>
+          </cell>
+          <cell r="M490" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N490" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O490" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P490">
+            <v>46175</v>
+          </cell>
+          <cell r="Q490">
+            <v>46182</v>
+          </cell>
+          <cell r="R490">
+            <v>46179</v>
+          </cell>
+          <cell r="S490">
+            <v>6</v>
+          </cell>
+          <cell r="T490">
+            <v>7</v>
           </cell>
           <cell r="U490" t="str">
             <v/>
           </cell>
-          <cell r="V490">
-            <v>0</v>
-          </cell>
-          <cell r="W490">
-            <v>0</v>
+          <cell r="V490" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="W490" t="str">
+            <v/>
           </cell>
         </row>
         <row r="491">
+          <cell r="A491"/>
+          <cell r="B491"/>
+          <cell r="C491"/>
+          <cell r="D491"/>
           <cell r="E491" t="str">
             <v/>
           </cell>
+          <cell r="F491"/>
+          <cell r="G491"/>
+          <cell r="H491"/>
+          <cell r="I491"/>
           <cell r="J491">
             <v>0</v>
           </cell>
           <cell r="K491">
             <v>0</v>
           </cell>
+          <cell r="L491"/>
+          <cell r="M491"/>
+          <cell r="N491"/>
+          <cell r="O491"/>
+          <cell r="P491"/>
+          <cell r="Q491"/>
+          <cell r="R491"/>
+          <cell r="S491"/>
+          <cell r="T491"/>
           <cell r="U491" t="str">
             <v/>
           </cell>
@@ -36133,15 +37259,32 @@
           </cell>
         </row>
         <row r="492">
+          <cell r="A492"/>
+          <cell r="B492"/>
+          <cell r="C492"/>
+          <cell r="D492"/>
           <cell r="E492" t="str">
             <v/>
           </cell>
+          <cell r="F492"/>
+          <cell r="G492"/>
+          <cell r="H492"/>
+          <cell r="I492"/>
           <cell r="J492">
             <v>0</v>
           </cell>
           <cell r="K492">
             <v>0</v>
           </cell>
+          <cell r="L492"/>
+          <cell r="M492"/>
+          <cell r="N492"/>
+          <cell r="O492"/>
+          <cell r="P492"/>
+          <cell r="Q492"/>
+          <cell r="R492"/>
+          <cell r="S492"/>
+          <cell r="T492"/>
           <cell r="U492" t="str">
             <v/>
           </cell>
@@ -36153,15 +37296,32 @@
           </cell>
         </row>
         <row r="493">
+          <cell r="A493"/>
+          <cell r="B493"/>
+          <cell r="C493"/>
+          <cell r="D493"/>
           <cell r="E493" t="str">
             <v/>
           </cell>
+          <cell r="F493"/>
+          <cell r="G493"/>
+          <cell r="H493"/>
+          <cell r="I493"/>
           <cell r="J493">
             <v>0</v>
           </cell>
           <cell r="K493">
             <v>0</v>
           </cell>
+          <cell r="L493"/>
+          <cell r="M493"/>
+          <cell r="N493"/>
+          <cell r="O493"/>
+          <cell r="P493"/>
+          <cell r="Q493"/>
+          <cell r="R493"/>
+          <cell r="S493"/>
+          <cell r="T493"/>
           <cell r="U493" t="str">
             <v/>
           </cell>
@@ -36173,15 +37333,32 @@
           </cell>
         </row>
         <row r="494">
+          <cell r="A494"/>
+          <cell r="B494"/>
+          <cell r="C494"/>
+          <cell r="D494"/>
           <cell r="E494" t="str">
             <v/>
           </cell>
+          <cell r="F494"/>
+          <cell r="G494"/>
+          <cell r="H494"/>
+          <cell r="I494"/>
           <cell r="J494">
             <v>0</v>
           </cell>
           <cell r="K494">
             <v>0</v>
           </cell>
+          <cell r="L494"/>
+          <cell r="M494"/>
+          <cell r="N494"/>
+          <cell r="O494"/>
+          <cell r="P494"/>
+          <cell r="Q494"/>
+          <cell r="R494"/>
+          <cell r="S494"/>
+          <cell r="T494"/>
           <cell r="U494" t="str">
             <v/>
           </cell>
@@ -36192,12 +37369,257 @@
             <v>0</v>
           </cell>
         </row>
+        <row r="495">
+          <cell r="E495" t="str">
+            <v/>
+          </cell>
+          <cell r="J495">
+            <v>0</v>
+          </cell>
+          <cell r="K495">
+            <v>0</v>
+          </cell>
+          <cell r="N495"/>
+          <cell r="O495"/>
+          <cell r="U495" t="str">
+            <v/>
+          </cell>
+          <cell r="V495">
+            <v>0</v>
+          </cell>
+          <cell r="W495">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="496">
+          <cell r="E496" t="str">
+            <v/>
+          </cell>
+          <cell r="J496">
+            <v>0</v>
+          </cell>
+          <cell r="K496">
+            <v>0</v>
+          </cell>
+          <cell r="O496"/>
+          <cell r="U496" t="str">
+            <v/>
+          </cell>
+          <cell r="V496">
+            <v>0</v>
+          </cell>
+          <cell r="W496">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="497">
+          <cell r="E497" t="str">
+            <v/>
+          </cell>
+          <cell r="J497">
+            <v>0</v>
+          </cell>
+          <cell r="K497">
+            <v>0</v>
+          </cell>
+          <cell r="O497"/>
+          <cell r="U497" t="str">
+            <v/>
+          </cell>
+          <cell r="V497">
+            <v>0</v>
+          </cell>
+          <cell r="W497">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="498">
+          <cell r="E498" t="str">
+            <v/>
+          </cell>
+          <cell r="J498">
+            <v>0</v>
+          </cell>
+          <cell r="K498">
+            <v>0</v>
+          </cell>
+          <cell r="O498"/>
+          <cell r="U498" t="str">
+            <v/>
+          </cell>
+          <cell r="V498">
+            <v>0</v>
+          </cell>
+          <cell r="W498">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="499">
+          <cell r="E499" t="str">
+            <v/>
+          </cell>
+          <cell r="J499">
+            <v>0</v>
+          </cell>
+          <cell r="K499">
+            <v>0</v>
+          </cell>
+          <cell r="U499" t="str">
+            <v/>
+          </cell>
+          <cell r="V499">
+            <v>0</v>
+          </cell>
+          <cell r="W499">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="500">
+          <cell r="E500" t="str">
+            <v/>
+          </cell>
+          <cell r="J500">
+            <v>0</v>
+          </cell>
+          <cell r="K500">
+            <v>0</v>
+          </cell>
+          <cell r="U500" t="str">
+            <v/>
+          </cell>
+          <cell r="V500">
+            <v>0</v>
+          </cell>
+          <cell r="W500">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="501">
+          <cell r="E501" t="str">
+            <v/>
+          </cell>
+          <cell r="J501">
+            <v>0</v>
+          </cell>
+          <cell r="K501">
+            <v>0</v>
+          </cell>
+          <cell r="U501" t="str">
+            <v/>
+          </cell>
+          <cell r="V501">
+            <v>0</v>
+          </cell>
+          <cell r="W501">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="502">
+          <cell r="E502" t="str">
+            <v/>
+          </cell>
+          <cell r="J502">
+            <v>0</v>
+          </cell>
+          <cell r="K502">
+            <v>0</v>
+          </cell>
+          <cell r="U502" t="str">
+            <v/>
+          </cell>
+          <cell r="V502">
+            <v>0</v>
+          </cell>
+          <cell r="W502">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="503">
+          <cell r="E503" t="str">
+            <v/>
+          </cell>
+          <cell r="J503">
+            <v>0</v>
+          </cell>
+          <cell r="K503">
+            <v>0</v>
+          </cell>
+          <cell r="U503" t="str">
+            <v/>
+          </cell>
+          <cell r="V503">
+            <v>0</v>
+          </cell>
+          <cell r="W503">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="504">
+          <cell r="E504" t="str">
+            <v/>
+          </cell>
+          <cell r="J504">
+            <v>0</v>
+          </cell>
+          <cell r="K504">
+            <v>0</v>
+          </cell>
+          <cell r="U504" t="str">
+            <v/>
+          </cell>
+          <cell r="V504">
+            <v>0</v>
+          </cell>
+          <cell r="W504">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="505">
+          <cell r="E505" t="str">
+            <v/>
+          </cell>
+          <cell r="J505">
+            <v>0</v>
+          </cell>
+          <cell r="K505">
+            <v>0</v>
+          </cell>
+          <cell r="U505" t="str">
+            <v/>
+          </cell>
+          <cell r="V505">
+            <v>0</v>
+          </cell>
+          <cell r="W505">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="506">
+          <cell r="E506" t="str">
+            <v/>
+          </cell>
+          <cell r="J506">
+            <v>0</v>
+          </cell>
+          <cell r="K506">
+            <v>0</v>
+          </cell>
+          <cell r="U506" t="str">
+            <v/>
+          </cell>
+          <cell r="V506">
+            <v>0</v>
+          </cell>
+          <cell r="W506">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
       <sheetData sheetId="9">
         <row r="1">
           <cell r="C1" t="str">
@@ -36205,102 +37627,108 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-      <sheetData sheetId="42" refreshError="1"/>
-      <sheetData sheetId="43" refreshError="1"/>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
-      <sheetData sheetId="46" refreshError="1"/>
-      <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48" refreshError="1"/>
-      <sheetData sheetId="49" refreshError="1"/>
-      <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51" refreshError="1"/>
-      <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53" refreshError="1"/>
-      <sheetData sheetId="54" refreshError="1"/>
-      <sheetData sheetId="55" refreshError="1"/>
-      <sheetData sheetId="56" refreshError="1"/>
-      <sheetData sheetId="57" refreshError="1"/>
-      <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60" refreshError="1"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
-      <sheetData sheetId="65" refreshError="1"/>
-      <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67" refreshError="1"/>
-      <sheetData sheetId="68" refreshError="1"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
-      <sheetData sheetId="71" refreshError="1"/>
-      <sheetData sheetId="72" refreshError="1"/>
-      <sheetData sheetId="73" refreshError="1"/>
-      <sheetData sheetId="74" refreshError="1"/>
-      <sheetData sheetId="75" refreshError="1"/>
-      <sheetData sheetId="76" refreshError="1"/>
-      <sheetData sheetId="77" refreshError="1"/>
-      <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
-      <sheetData sheetId="80" refreshError="1"/>
-      <sheetData sheetId="81" refreshError="1"/>
-      <sheetData sheetId="82" refreshError="1"/>
-      <sheetData sheetId="83" refreshError="1"/>
-      <sheetData sheetId="84" refreshError="1"/>
-      <sheetData sheetId="85" refreshError="1"/>
-      <sheetData sheetId="86" refreshError="1"/>
-      <sheetData sheetId="87" refreshError="1"/>
-      <sheetData sheetId="88" refreshError="1"/>
-      <sheetData sheetId="89" refreshError="1"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+      <sheetData sheetId="48"/>
+      <sheetData sheetId="49"/>
+      <sheetData sheetId="50"/>
+      <sheetData sheetId="51"/>
+      <sheetData sheetId="52"/>
+      <sheetData sheetId="53"/>
+      <sheetData sheetId="54"/>
+      <sheetData sheetId="55"/>
+      <sheetData sheetId="56"/>
+      <sheetData sheetId="57"/>
+      <sheetData sheetId="58"/>
+      <sheetData sheetId="59"/>
+      <sheetData sheetId="60"/>
+      <sheetData sheetId="61"/>
+      <sheetData sheetId="62"/>
+      <sheetData sheetId="63"/>
+      <sheetData sheetId="64"/>
+      <sheetData sheetId="65"/>
+      <sheetData sheetId="66"/>
+      <sheetData sheetId="67"/>
+      <sheetData sheetId="68"/>
+      <sheetData sheetId="69"/>
+      <sheetData sheetId="70"/>
+      <sheetData sheetId="71"/>
+      <sheetData sheetId="72"/>
+      <sheetData sheetId="73"/>
+      <sheetData sheetId="74"/>
+      <sheetData sheetId="75"/>
+      <sheetData sheetId="76"/>
+      <sheetData sheetId="77"/>
+      <sheetData sheetId="78"/>
+      <sheetData sheetId="79"/>
+      <sheetData sheetId="80"/>
+      <sheetData sheetId="81"/>
+      <sheetData sheetId="82"/>
+      <sheetData sheetId="83"/>
+      <sheetData sheetId="84"/>
+      <sheetData sheetId="85"/>
+      <sheetData sheetId="86"/>
+      <sheetData sheetId="87"/>
+      <sheetData sheetId="88"/>
+      <sheetData sheetId="89"/>
       <sheetData sheetId="90"/>
-      <sheetData sheetId="91" refreshError="1"/>
-      <sheetData sheetId="92" refreshError="1"/>
-      <sheetData sheetId="93" refreshError="1"/>
-      <sheetData sheetId="94" refreshError="1"/>
-      <sheetData sheetId="95" refreshError="1"/>
-      <sheetData sheetId="96" refreshError="1"/>
-      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="91"/>
+      <sheetData sheetId="92"/>
+      <sheetData sheetId="93"/>
+      <sheetData sheetId="94"/>
+      <sheetData sheetId="95"/>
+      <sheetData sheetId="96"/>
+      <sheetData sheetId="97"/>
       <sheetData sheetId="98"/>
       <sheetData sheetId="99"/>
       <sheetData sheetId="100"/>
-      <sheetData sheetId="101" refreshError="1"/>
-      <sheetData sheetId="102" refreshError="1"/>
-      <sheetData sheetId="103" refreshError="1"/>
-      <sheetData sheetId="104" refreshError="1"/>
-      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="101"/>
+      <sheetData sheetId="102">
+        <row r="1">
+          <cell r="F1" t="str">
+            <v>No_Item</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="103"/>
+      <sheetData sheetId="104"/>
+      <sheetData sheetId="105"/>
       <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
       <sheetData sheetId="108" refreshError="1"/>
@@ -36341,7 +37769,7 @@
       <sheetData sheetId="143" refreshError="1"/>
       <sheetData sheetId="144" refreshError="1"/>
       <sheetData sheetId="145" refreshError="1"/>
-      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="146"/>
       <sheetData sheetId="147" refreshError="1"/>
       <sheetData sheetId="148" refreshError="1"/>
       <sheetData sheetId="149" refreshError="1"/>
@@ -36475,6 +37903,11 @@
       <sheetData sheetId="277" refreshError="1"/>
       <sheetData sheetId="278" refreshError="1"/>
       <sheetData sheetId="279" refreshError="1"/>
+      <sheetData sheetId="280" refreshError="1"/>
+      <sheetData sheetId="281" refreshError="1"/>
+      <sheetData sheetId="282" refreshError="1"/>
+      <sheetData sheetId="283"/>
+      <sheetData sheetId="284" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -38101,23 +39534,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="69" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="68" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="65" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="64" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -38127,6 +39560,1449 @@
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="21" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FA68E0-ADB4-4444-A4B8-EE9F960C9A25}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:N667"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="140.1796875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46176.399045833336</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>16</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="F3" s="22">
+        <v>10</v>
+      </c>
+      <c r="G3" s="23">
+        <v>2</v>
+      </c>
+      <c r="H3" s="24">
+        <v>2</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="L3" s="26">
+        <v>2</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="N3" s="28">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="76"/>
+    </row>
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="F5" s="22">
+        <v>30</v>
+      </c>
+      <c r="G5" s="23">
+        <v>2</v>
+      </c>
+      <c r="H5" s="24">
+        <v>2</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="26">
+        <v>2</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="N5" s="28">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="76"/>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="F7" s="22">
+        <v>30</v>
+      </c>
+      <c r="G7" s="23">
+        <v>4</v>
+      </c>
+      <c r="H7" s="24">
+        <v>4</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="26">
+        <v>4</v>
+      </c>
+      <c r="M7" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="N7" s="28">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="76"/>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="F9" s="22">
+        <v>20</v>
+      </c>
+      <c r="G9" s="23">
+        <v>3</v>
+      </c>
+      <c r="H9" s="24">
+        <v>3</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="26">
+        <v>3</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="N9" s="28">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="76"/>
+    </row>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="F11" s="22">
+        <v>30</v>
+      </c>
+      <c r="G11" s="23">
+        <v>2</v>
+      </c>
+      <c r="H11" s="24">
+        <v>2</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="26">
+        <v>3</v>
+      </c>
+      <c r="M11" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="N11" s="28">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="F12" s="22">
+        <v>60</v>
+      </c>
+      <c r="G12" s="23">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24">
+        <v>1</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="26"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="28">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="76"/>
+    </row>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="F14" s="22">
+        <v>30</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24">
+        <v>1</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="26">
+        <v>1</v>
+      </c>
+      <c r="M14" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="N14" s="28">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="62"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="76"/>
+    </row>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="F16" s="22">
+        <v>50</v>
+      </c>
+      <c r="G16" s="23">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24">
+        <v>1</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>416</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="26">
+        <v>1</v>
+      </c>
+      <c r="M16" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="N16" s="28">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C17" s="19" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="20" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="21" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="22" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="23" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H17" s="24" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="19" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="20" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="21" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="22" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="23" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H18" s="24" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A18,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="19" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="20" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="21" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F19" s="22" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="23" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H19" s="24" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="19" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="20" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="21" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="22" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="23" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="24" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="19" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="20" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="21" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="22" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="23" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="24" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="26"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A21,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="17"/>
+      <c r="B22" s="18" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C22" s="19" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D22" s="20" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" s="21" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F22" s="22" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G22" s="23" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H22" s="24" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L22" s="26"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A22,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C23" s="19" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D23" s="20" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E23" s="21" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F23" s="22" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G23" s="23" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H23" s="24" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I23" s="25" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J23" s="25" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K23" s="25" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L23" s="26"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A23,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:14" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="41"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="51"/>
+    </row>
+    <row r="25" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="56"/>
+    </row>
+    <row r="26" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="56"/>
+    </row>
+    <row r="28" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="55"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="58"/>
+    </row>
+    <row r="29" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L29" s="56"/>
+    </row>
+    <row r="30" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L30" s="56"/>
+    </row>
+    <row r="31" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="57" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="58"/>
+    </row>
+    <row r="58" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="56"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="58"/>
+    </row>
+    <row r="667" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A667" s="2"/>
+      <c r="B667" s="52"/>
+      <c r="C667" s="2"/>
+      <c r="D667" s="2"/>
+      <c r="E667" s="60"/>
+      <c r="H667" s="55"/>
+      <c r="I667" s="53"/>
+      <c r="J667" s="53"/>
+      <c r="K667" s="53"/>
+      <c r="L667" s="61"/>
+      <c r="M667" s="57"/>
+      <c r="N667" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E23" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N24" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="RPRO-260602-0720"/>
+        <filter val="RPRO-260602-0721"/>
+        <filter val="RPRO-260602-0722"/>
+        <filter val="RPRO-260602-0723"/>
+        <filter val="RPRO-260602-0724"/>
+        <filter val="RPRO-260602-0725"/>
+        <filter val="RPRO-260602-0726"/>
+        <filter val="RPRO-260602-0727"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A23">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -38162,7 +41038,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -39511,23 +42387,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -39572,7 +42448,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -40979,23 +43855,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -41040,7 +43916,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -42413,23 +45289,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="49" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="44" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -42473,7 +45349,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -43688,39 +46564,39 @@
     <mergeCell ref="D7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="42" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A6 A14:A18">
-    <cfRule type="duplicateValues" dxfId="41" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="40" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A13">
-    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A1048576">
-    <cfRule type="duplicateValues" dxfId="38" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C6 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="37" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C13">
-    <cfRule type="duplicateValues" dxfId="35" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:L8">
-    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="32" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="9"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -43765,7 +46641,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -45090,26 +47966,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A15">
-    <cfRule type="duplicateValues" dxfId="28" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A21">
-    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -45155,7 +48031,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -46510,23 +49386,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -46542,7 +49418,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22925852-BF71-4530-A0E5-2256D89D5807}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:N668"/>
@@ -46571,7 +49447,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -47098,7 +49974,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17"/>
       <c r="B18" s="18" t="e">
         <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
@@ -47147,7 +50023,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="17"/>
       <c r="B19" s="18" t="e">
         <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
@@ -47196,7 +50072,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17"/>
       <c r="B20" s="18" t="e">
         <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
@@ -47245,7 +50121,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="e">
         <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
@@ -47294,7 +50170,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17"/>
       <c r="B22" s="18" t="e">
         <f>VLOOKUP(A22,'[2]master plan'!A:C,3,0)</f>
@@ -47343,7 +50219,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17"/>
       <c r="B23" s="18" t="e">
         <f>VLOOKUP(A23,'[2]master plan'!A:C,3,0)</f>
@@ -47392,7 +50268,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17"/>
       <c r="B24" s="18" t="e">
         <f>VLOOKUP(A24,'[2]master plan'!A:C,3,0)</f>
@@ -47954,42 +50830,29 @@
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E24" name="Range1_1"/>
   </protectedRanges>
-  <autoFilter ref="A2:N25" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
-    <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="RPRO-260529-0339"/>
-        <filter val="RPRO-260529-0340"/>
-        <filter val="RPRO-260529-0341"/>
-        <filter val="RPRO-260529-0342"/>
-        <filter val="RPRO-260529-0343"/>
-        <filter val="RPRO-260529-0344"/>
-        <filter val="RPRO-260529-0345"/>
-        <filter val="RPRO-260529-0346"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:N25" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}"/>
   <mergeCells count="1">
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -48035,7 +50898,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46174.661814930558</v>
+        <v>46176.399045833336</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -48135,7 +50998,9 @@
       <c r="L3" s="26">
         <v>4</v>
       </c>
-      <c r="M3" s="27"/>
+      <c r="M3" s="27" t="s">
+        <v>246</v>
+      </c>
       <c r="N3" s="28">
         <v>46178</v>
       </c>
@@ -48233,7 +51098,9 @@
       <c r="L6" s="26">
         <v>2</v>
       </c>
-      <c r="M6" s="40"/>
+      <c r="M6" s="40" t="s">
+        <v>246</v>
+      </c>
       <c r="N6" s="28">
         <v>46178</v>
       </c>
@@ -48291,7 +51158,9 @@
       <c r="L8" s="26">
         <v>1</v>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="27" t="s">
+        <v>378</v>
+      </c>
       <c r="N8" s="28">
         <v>46178</v>
       </c>
@@ -48349,7 +51218,9 @@
       <c r="L10" s="26">
         <v>2</v>
       </c>
-      <c r="M10" s="27"/>
+      <c r="M10" s="27" t="s">
+        <v>246</v>
+      </c>
       <c r="N10" s="28">
         <v>46178</v>
       </c>
@@ -49372,23 +52243,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -39596,7 +39596,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -41038,7 +41038,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -43916,7 +43916,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -45349,7 +45349,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -46641,7 +46641,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -48031,7 +48031,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -49447,7 +49447,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>
@@ -50898,7 +50898,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.399045833336</v>
+        <v>46176.520486574074</v>
       </c>
       <c r="D1" s="80" t="s">
         <v>1</v>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80962CD4-88DD-4667-994F-8F71CAB5ACE7}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A4A1B7B-B216-41BB-AE5C-84739BA2A93F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="9" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="11" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -23,10 +23,12 @@
     <sheet name="29.5 - L2" sheetId="8" r:id="rId8"/>
     <sheet name="1.6" sheetId="9" r:id="rId9"/>
     <sheet name="2.6" sheetId="10" r:id="rId10"/>
+    <sheet name="3.6" sheetId="11" r:id="rId11"/>
+    <sheet name="4.6" sheetId="12" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId11"/>
-    <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
@@ -39,6 +41,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'25.5'!$A$2:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'27.5'!$A$2:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'3.6'!$A$2:$N$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'4.6'!$A$2:$N$22</definedName>
     <definedName name="AE" localSheetId="8">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -49,6 +53,8 @@
     <definedName name="AE" localSheetId="5">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="6">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="7">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="10">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="11">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'1.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
@@ -59,6 +65,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'25.5'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'27.5'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'29.5 - L2'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'3.6'!$A$1:$N$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'4.6'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'1.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
@@ -69,6 +77,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'25.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'27.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'3.6'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'4.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -79,6 +89,8 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -89,6 +101,8 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -99,6 +113,8 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -109,6 +125,8 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -119,6 +137,8 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -129,6 +149,8 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="8" hidden="1">'1.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
@@ -139,6 +161,8 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="5" hidden="1">'25.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="6" hidden="1">'27.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="7" hidden="1">'29.5 - L2'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="10" hidden="1">'3.6'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="11" hidden="1">'4.6'!#REF!</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -149,6 +173,8 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -159,6 +185,8 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -169,6 +197,8 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -179,6 +209,8 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -189,6 +221,8 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -199,6 +233,8 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -209,6 +245,8 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -219,6 +257,8 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -229,6 +269,8 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -239,6 +281,8 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -249,6 +293,8 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -259,6 +305,8 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -269,6 +317,8 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="5" hidden="1">'25.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="6" hidden="1">'27.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -279,6 +329,8 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="5" hidden="1">'25.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="6" hidden="1">'27.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -301,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="476">
   <si>
     <t>Release Date</t>
   </si>
@@ -1515,9 +1567,6 @@
     <t>Die cut</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>S-2026-06-01</t>
   </si>
   <si>
@@ -1631,6 +1680,186 @@
   </si>
   <si>
     <t>SSO-2606-00031</t>
+  </si>
+  <si>
+    <t>S-2026-06-09</t>
+  </si>
+  <si>
+    <t>RPRO-260603-0481</t>
+  </si>
+  <si>
+    <t>BDB-000347</t>
+  </si>
+  <si>
+    <t>PVN-004436</t>
+  </si>
+  <si>
+    <t>OrthoLite X-55-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.16D 25+/-4 Asker C 1.1M 2M 5mm</t>
+  </si>
+  <si>
+    <t>PAYNTR</t>
+  </si>
+  <si>
+    <t>S-2026-06-10</t>
+  </si>
+  <si>
+    <t>RPRO-260603-0482</t>
+  </si>
+  <si>
+    <t>SSO-2606-00082 - URGENT (6-10)</t>
+  </si>
+  <si>
+    <t>S-2026-06-11</t>
+  </si>
+  <si>
+    <t>RPRO-260603-0483</t>
+  </si>
+  <si>
+    <t>BDB-000195</t>
+  </si>
+  <si>
+    <t>PVN-004435</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra-Nike GREY/17-1501TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 1.7M 4mm</t>
+  </si>
+  <si>
+    <t>Sample/ URGENT</t>
+  </si>
+  <si>
+    <t>S-2026-06-12</t>
+  </si>
+  <si>
+    <t>RPRO-260603-0484</t>
+  </si>
+  <si>
+    <t>BDB-000392</t>
+  </si>
+  <si>
+    <t>PVN-004434</t>
+  </si>
+  <si>
+    <t>OrthoLite X-40-Nike TRUE BLUE/19-4057TPX Flat Sheet 0.16D 35+/-4 Asker C 1.1M 2M 4mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-14</t>
+  </si>
+  <si>
+    <t>RPRO-260603-0485</t>
+  </si>
+  <si>
+    <t>SSO-2606-00089/00070/00128  - URGENT (6-10)</t>
+  </si>
+  <si>
+    <t>S-2026-06-15</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0522</t>
+  </si>
+  <si>
+    <t>BDB-000307</t>
+  </si>
+  <si>
+    <t>PVN-004437</t>
+  </si>
+  <si>
+    <t>OrthoLite X-35 SEEDPEARL/12-0703TPX Flat Sheet 0.145D 25+/-4 Asker C 1.1M 2M 8mm</t>
+  </si>
+  <si>
+    <t>SSO-2606-00111</t>
+  </si>
+  <si>
+    <t>L-2026-06-07</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0529</t>
+  </si>
+  <si>
+    <t>PVN-002699</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4.5mm</t>
+  </si>
+  <si>
+    <t>SHYANG HUNG TAH</t>
+  </si>
+  <si>
+    <t>L-2026-06-01</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0523</t>
+  </si>
+  <si>
+    <t>BDB-000131</t>
+  </si>
+  <si>
+    <t>PVN-002424</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular-Nike AIR BLUE/16-4134TPX 0.11D 15+/-4 Asker C 1.1M 2M 3.5mm</t>
+  </si>
+  <si>
+    <t>NIKE-POU CHEN VÀ CONVERSE</t>
+  </si>
+  <si>
+    <t>L-2026-06-02</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0524</t>
+  </si>
+  <si>
+    <t>PVN-001635</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular-Nike AIR BLUE/16-4134TPX 0.11D 15+/-4 Asker C 1.1M 2M 10mm</t>
+  </si>
+  <si>
+    <t>L-2026-06-03</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0525</t>
+  </si>
+  <si>
+    <t>BDB-000221</t>
+  </si>
+  <si>
+    <t>PVN-004123</t>
+  </si>
+  <si>
+    <t>OrthoLite X-40-Hybrid-Nike SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.16D 25+/-4 Asker C 1.1M 1.7M 3mm</t>
+  </si>
+  <si>
+    <t>L-2026-06-04</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0526</t>
+  </si>
+  <si>
+    <t>PVN-004124</t>
+  </si>
+  <si>
+    <t>OrthoLite X-40-Hybrid-Nike SEEDPEARL/12-0703TPX 0.16D 25+/-4 Asker C 1.1M 1.7M 10mm</t>
+  </si>
+  <si>
+    <t>L-2026-06-05</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0527</t>
+  </si>
+  <si>
+    <t>PVN-002512</t>
+  </si>
+  <si>
+    <t>Eco LT-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 10mm</t>
+  </si>
+  <si>
+    <t>L-2026-06-06</t>
+  </si>
+  <si>
+    <t>RPRO-260604-0528</t>
+  </si>
+  <si>
+    <t>Eco LT-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</t>
   </si>
 </sst>
 </file>
@@ -1985,7 +2214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2224,6 +2453,9 @@
     <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2232,7 +2464,147 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="92">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3183,12 +3555,18 @@
       <sheetName val="29.5"/>
       <sheetName val="29.5 - L2"/>
       <sheetName val="1.6"/>
-      <sheetName val="form 2 (16)"/>
+      <sheetName val="2.6"/>
+      <sheetName val="3.6"/>
+      <sheetName val="form 2 (18)"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
+      <sheetName val="4.6"/>
+      <sheetName val="form 2 (19)"/>
+      <sheetName val="form 2 (17)"/>
+      <sheetName val="form 2 (16)"/>
       <sheetName val="form 2 (15)"/>
       <sheetName val="form 2 (14)"/>
       <sheetName val="28.5"/>
@@ -3229,10 +3607,7 @@
       <sheetName val="16.5"/>
       <sheetName val="22.5"/>
       <sheetName val="30.5"/>
-      <sheetName val="2.6"/>
-      <sheetName val="3.6"/>
       <sheetName val="3.6 (L)"/>
-      <sheetName val="4.6"/>
       <sheetName val="6.6"/>
       <sheetName val="9.6"/>
       <sheetName val="9.6 (L)"/>
@@ -3366,7 +3741,6 @@
       <sheetName val="form 2 (3)"/>
       <sheetName val="form 2"/>
       <sheetName val="25.4 (2)"/>
-      <sheetName val="form 2 (17)"/>
       <sheetName val="form 2 (9)"/>
     </sheetNames>
     <sheetDataSet>
@@ -3375,84 +3749,49 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
-          <cell r="A1"/>
-          <cell r="B1"/>
           <cell r="C1" t="str">
             <v>TẠM THỜI NGƯNG NHẬN LAZY</v>
           </cell>
-          <cell r="D1"/>
-          <cell r="E1"/>
-          <cell r="F1"/>
           <cell r="G1" t="str">
             <v>ASICS 12MM DÙNG BOM 132 (roundup(12/132),5)</v>
           </cell>
-          <cell r="H1"/>
-          <cell r="I1"/>
-          <cell r="J1"/>
-          <cell r="K1"/>
-          <cell r="L1"/>
-          <cell r="M1"/>
-          <cell r="N1"/>
-          <cell r="O1"/>
-          <cell r="P1"/>
-          <cell r="Q1"/>
-          <cell r="R1"/>
-          <cell r="S1"/>
-          <cell r="T1"/>
-          <cell r="U1"/>
-          <cell r="V1"/>
-          <cell r="W1"/>
         </row>
         <row r="2">
-          <cell r="A2"/>
-          <cell r="B2"/>
-          <cell r="C2"/>
-          <cell r="D2"/>
-          <cell r="E2"/>
-          <cell r="F2"/>
           <cell r="G2" t="str">
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>24460</v>
+            <v>70</v>
           </cell>
           <cell r="I2">
-            <v>24460</v>
+            <v>70</v>
           </cell>
           <cell r="J2">
-            <v>23333</v>
+            <v>55</v>
           </cell>
           <cell r="K2">
-            <v>1127</v>
+            <v>15</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
           </cell>
-          <cell r="M2"/>
-          <cell r="N2"/>
-          <cell r="O2"/>
-          <cell r="P2"/>
           <cell r="Q2" t="str">
             <v>ETD hệ thống+1ngay</v>
           </cell>
           <cell r="R2" t="e">
             <v>#VALUE!</v>
           </cell>
-          <cell r="S2"/>
-          <cell r="T2"/>
           <cell r="U2">
             <v>12</v>
           </cell>
-          <cell r="V2"/>
           <cell r="W2">
-            <v>1239</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>NO.Order</v>
           </cell>
-          <cell r="B3"/>
           <cell r="C3" t="str">
             <v>Firm plan
 (PU PVN)</v>
@@ -3537,7 +3876,6 @@
           <cell r="A4" t="str">
             <v>S-2026-01-01</v>
           </cell>
-          <cell r="B4"/>
           <cell r="C4" t="str">
             <v>RPRO-260105-0668</v>
           </cell>
@@ -3890,7 +4228,6 @@
           <cell r="A9" t="str">
             <v>S-2026-01-06</v>
           </cell>
-          <cell r="B9"/>
           <cell r="C9" t="str">
             <v>RPRO-260105-0673</v>
           </cell>
@@ -3959,7 +4296,6 @@
           <cell r="A10" t="str">
             <v>S-2026-01-07</v>
           </cell>
-          <cell r="B10"/>
           <cell r="C10" t="str">
             <v>RPRO-260105-0674</v>
           </cell>
@@ -4028,7 +4364,6 @@
           <cell r="A11" t="str">
             <v>S-2026-01-08</v>
           </cell>
-          <cell r="B11"/>
           <cell r="C11" t="str">
             <v>RPRO-260105-0675</v>
           </cell>
@@ -4239,7 +4574,6 @@
           <cell r="A14" t="str">
             <v>L-2026-01-11</v>
           </cell>
-          <cell r="B14"/>
           <cell r="C14" t="str">
             <v>RPRO-260105-0678</v>
           </cell>
@@ -4273,7 +4607,6 @@
           <cell r="M14" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N14"/>
           <cell r="O14" t="str">
             <v>Lab test</v>
           </cell>
@@ -4306,7 +4639,6 @@
           <cell r="A15" t="str">
             <v>L-2026-01-12</v>
           </cell>
-          <cell r="B15"/>
           <cell r="C15" t="str">
             <v>RPRO-260105-0679</v>
           </cell>
@@ -4340,7 +4672,6 @@
           <cell r="M15" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N15"/>
           <cell r="O15" t="str">
             <v>Lab test</v>
           </cell>
@@ -4373,7 +4704,6 @@
           <cell r="A16" t="str">
             <v>L-2026-01-13</v>
           </cell>
-          <cell r="B16"/>
           <cell r="C16" t="str">
             <v>RPRO-260105-0680</v>
           </cell>
@@ -4407,7 +4737,6 @@
           <cell r="M16" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N16"/>
           <cell r="O16" t="str">
             <v>Lab test</v>
           </cell>
@@ -4440,7 +4769,6 @@
           <cell r="A17" t="str">
             <v>L-2026-01-14</v>
           </cell>
-          <cell r="B17"/>
           <cell r="C17" t="str">
             <v>RPRO-260105-0681</v>
           </cell>
@@ -4474,7 +4802,6 @@
           <cell r="M17" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N17"/>
           <cell r="O17" t="str">
             <v>Lab test</v>
           </cell>
@@ -4543,7 +4870,6 @@
           <cell r="M18" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N18"/>
           <cell r="O18" t="str">
             <v>Lab test</v>
           </cell>
@@ -4612,7 +4938,6 @@
           <cell r="M19" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N19"/>
           <cell r="O19" t="str">
             <v>Lab test</v>
           </cell>
@@ -5000,7 +5325,6 @@
           <cell r="A25" t="str">
             <v>L-2026-01-22</v>
           </cell>
-          <cell r="B25"/>
           <cell r="C25" t="str">
             <v>RPRO-260109-0095</v>
           </cell>
@@ -5034,7 +5358,6 @@
           <cell r="M25" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N25"/>
           <cell r="O25" t="str">
             <v>Lab test</v>
           </cell>
@@ -5067,7 +5390,6 @@
           <cell r="A26" t="str">
             <v>S-2026-01-23</v>
           </cell>
-          <cell r="B26"/>
           <cell r="C26" t="str">
             <v>RPRO-260113-0624</v>
           </cell>
@@ -5136,7 +5458,6 @@
           <cell r="A27" t="str">
             <v>S-2026-01-24</v>
           </cell>
-          <cell r="B27"/>
           <cell r="C27" t="str">
             <v>RPRO-260113-0625</v>
           </cell>
@@ -5205,7 +5526,6 @@
           <cell r="A28" t="str">
             <v>S-2026-01-25</v>
           </cell>
-          <cell r="B28"/>
           <cell r="C28" t="str">
             <v>RPRO-260113-0626</v>
           </cell>
@@ -5274,7 +5594,6 @@
           <cell r="A29" t="str">
             <v>S-2026-01-26</v>
           </cell>
-          <cell r="B29"/>
           <cell r="C29" t="str">
             <v>RPRO-260113-0627</v>
           </cell>
@@ -5343,7 +5662,6 @@
           <cell r="A30" t="str">
             <v>S-2026-01-27</v>
           </cell>
-          <cell r="B30"/>
           <cell r="C30" t="str">
             <v>RPRO-260113-0628</v>
           </cell>
@@ -5412,7 +5730,6 @@
           <cell r="A31" t="str">
             <v>S-2026-01-28</v>
           </cell>
-          <cell r="B31"/>
           <cell r="C31" t="str">
             <v>RPRO-260113-0629</v>
           </cell>
@@ -5481,7 +5798,6 @@
           <cell r="A32" t="str">
             <v>S-2026-01-29</v>
           </cell>
-          <cell r="B32"/>
           <cell r="C32" t="str">
             <v>RPRO-260113-0630</v>
           </cell>
@@ -5550,7 +5866,6 @@
           <cell r="A33" t="str">
             <v>S-2026-01-30</v>
           </cell>
-          <cell r="B33"/>
           <cell r="C33" t="str">
             <v>RPRO-260115-0298</v>
           </cell>
@@ -5619,7 +5934,6 @@
           <cell r="A34" t="str">
             <v>S-2026-01-31</v>
           </cell>
-          <cell r="B34"/>
           <cell r="C34" t="str">
             <v>RPRO-260115-0299</v>
           </cell>
@@ -5688,7 +6002,6 @@
           <cell r="A35" t="str">
             <v>S-2026-01-32</v>
           </cell>
-          <cell r="B35"/>
           <cell r="C35" t="str">
             <v>RPRO-260115-0300</v>
           </cell>
@@ -5757,7 +6070,6 @@
           <cell r="A36" t="str">
             <v>S-2026-01-33</v>
           </cell>
-          <cell r="B36"/>
           <cell r="C36" t="str">
             <v>RPRO-260115-0301</v>
           </cell>
@@ -5826,7 +6138,6 @@
           <cell r="A37" t="str">
             <v>S-2026-01-34</v>
           </cell>
-          <cell r="B37"/>
           <cell r="C37" t="str">
             <v>RPRO-260115-0302</v>
           </cell>
@@ -5895,7 +6206,6 @@
           <cell r="A38" t="str">
             <v>S-2026-01-35</v>
           </cell>
-          <cell r="B38"/>
           <cell r="C38" t="str">
             <v>RPRO-260115-0303</v>
           </cell>
@@ -5964,7 +6274,6 @@
           <cell r="A39" t="str">
             <v>S-2026-01-36</v>
           </cell>
-          <cell r="B39"/>
           <cell r="C39" t="str">
             <v>RPRO-260115-0304</v>
           </cell>
@@ -6033,7 +6342,6 @@
           <cell r="A40" t="str">
             <v>S-2026-01-37</v>
           </cell>
-          <cell r="B40"/>
           <cell r="C40" t="str">
             <v>RPRO-260115-0305</v>
           </cell>
@@ -6102,7 +6410,6 @@
           <cell r="A41" t="str">
             <v>S-2026-01-38</v>
           </cell>
-          <cell r="B41"/>
           <cell r="C41" t="str">
             <v>RPRO-260115-0306</v>
           </cell>
@@ -6171,7 +6478,6 @@
           <cell r="A42" t="str">
             <v>S-2026-01-39</v>
           </cell>
-          <cell r="B42"/>
           <cell r="C42" t="str">
             <v>RPRO-260115-0307</v>
           </cell>
@@ -6240,7 +6546,6 @@
           <cell r="A43" t="str">
             <v>S-2026-01-40</v>
           </cell>
-          <cell r="B43"/>
           <cell r="C43" t="str">
             <v>RPRO-260115-0308</v>
           </cell>
@@ -6309,7 +6614,6 @@
           <cell r="A44" t="str">
             <v>S-2026-01-41</v>
           </cell>
-          <cell r="B44"/>
           <cell r="C44" t="str">
             <v>RPRO-260115-0309</v>
           </cell>
@@ -6378,7 +6682,6 @@
           <cell r="A45" t="str">
             <v>S-2026-01-42</v>
           </cell>
-          <cell r="B45"/>
           <cell r="C45" t="str">
             <v>RPRO-260109-0096</v>
           </cell>
@@ -6447,7 +6750,6 @@
           <cell r="A46" t="str">
             <v>S-2026-01-43</v>
           </cell>
-          <cell r="B46"/>
           <cell r="C46" t="str">
             <v>RPRO-260109-0097</v>
           </cell>
@@ -6516,7 +6818,6 @@
           <cell r="A47" t="str">
             <v>S-2026-01-44</v>
           </cell>
-          <cell r="B47"/>
           <cell r="C47" t="str">
             <v>RPRO-260109-0098</v>
           </cell>
@@ -6585,7 +6886,6 @@
           <cell r="A48" t="str">
             <v>S-2026-01-45</v>
           </cell>
-          <cell r="B48"/>
           <cell r="C48" t="str">
             <v>RPRO-260109-0099</v>
           </cell>
@@ -6654,7 +6954,6 @@
           <cell r="A49" t="str">
             <v>S-2026-01-46</v>
           </cell>
-          <cell r="B49"/>
           <cell r="C49" t="str">
             <v>RPRO-260120-0349</v>
           </cell>
@@ -6723,7 +7022,6 @@
           <cell r="A50" t="str">
             <v>S-2026-01-47</v>
           </cell>
-          <cell r="B50"/>
           <cell r="C50" t="str">
             <v>RPRO-260120-0350</v>
           </cell>
@@ -6792,7 +7090,6 @@
           <cell r="A51" t="str">
             <v>S-2026-01-48</v>
           </cell>
-          <cell r="B51"/>
           <cell r="C51" t="str">
             <v>RPRO-260120-0351</v>
           </cell>
@@ -6861,7 +7158,6 @@
           <cell r="A52" t="str">
             <v>S-2026-01-49</v>
           </cell>
-          <cell r="B52"/>
           <cell r="C52" t="str">
             <v>RPRO-260120-0352</v>
           </cell>
@@ -6930,7 +7226,6 @@
           <cell r="A53" t="str">
             <v>S-2026-01-50</v>
           </cell>
-          <cell r="B53"/>
           <cell r="C53" t="str">
             <v>RPRO-260120-0353</v>
           </cell>
@@ -6999,7 +7294,6 @@
           <cell r="A54" t="str">
             <v>S-2026-01-51</v>
           </cell>
-          <cell r="B54"/>
           <cell r="C54" t="str">
             <v>RPRO-260120-0354</v>
           </cell>
@@ -7068,7 +7362,6 @@
           <cell r="A55" t="str">
             <v>S-2026-01-52</v>
           </cell>
-          <cell r="B55"/>
           <cell r="C55" t="str">
             <v>RPRO-260113-0631</v>
           </cell>
@@ -7137,7 +7430,6 @@
           <cell r="A56" t="str">
             <v>S-2026-01-53</v>
           </cell>
-          <cell r="B56"/>
           <cell r="C56" t="str">
             <v>RPRO-260120-0355</v>
           </cell>
@@ -7206,7 +7498,6 @@
           <cell r="A57" t="str">
             <v>S-2026-01-54</v>
           </cell>
-          <cell r="B57"/>
           <cell r="C57" t="str">
             <v>RPRO-260120-0356</v>
           </cell>
@@ -7275,7 +7566,6 @@
           <cell r="A58" t="str">
             <v>S-2026-01-55</v>
           </cell>
-          <cell r="B58"/>
           <cell r="C58" t="str">
             <v>RPRO-260120-0357</v>
           </cell>
@@ -7344,7 +7634,6 @@
           <cell r="A59" t="str">
             <v>S-2026-01-56</v>
           </cell>
-          <cell r="B59"/>
           <cell r="C59" t="str">
             <v>RPRO-260120-0358</v>
           </cell>
@@ -7413,7 +7702,6 @@
           <cell r="A60" t="str">
             <v>S-2026-01-57</v>
           </cell>
-          <cell r="B60"/>
           <cell r="C60" t="str">
             <v>RPRO-260120-0359</v>
           </cell>
@@ -7482,7 +7770,6 @@
           <cell r="A61" t="str">
             <v>S-2026-01-58</v>
           </cell>
-          <cell r="B61"/>
           <cell r="C61" t="str">
             <v>RPRO-260120-0360</v>
           </cell>
@@ -7551,7 +7838,6 @@
           <cell r="A62" t="str">
             <v>S-2026-01-59</v>
           </cell>
-          <cell r="B62"/>
           <cell r="C62" t="str">
             <v>RPRO-260116-0276</v>
           </cell>
@@ -7620,7 +7906,6 @@
           <cell r="A63" t="str">
             <v>S-2026-01-60</v>
           </cell>
-          <cell r="B63"/>
           <cell r="C63" t="str">
             <v>RPRO-260115-0310</v>
           </cell>
@@ -7689,7 +7974,6 @@
           <cell r="A64" t="str">
             <v>S-2026-01-61</v>
           </cell>
-          <cell r="B64"/>
           <cell r="C64" t="str">
             <v>RPRO-260120-0361</v>
           </cell>
@@ -7829,7 +8113,6 @@
           <cell r="A66" t="str">
             <v>S-2026-01-63</v>
           </cell>
-          <cell r="B66"/>
           <cell r="C66" t="str">
             <v>RPRO-260122-1562</v>
           </cell>
@@ -7898,7 +8181,6 @@
           <cell r="A67" t="str">
             <v>S-2026-01-64</v>
           </cell>
-          <cell r="B67"/>
           <cell r="C67" t="str">
             <v>RPRO-260122-1563</v>
           </cell>
@@ -7967,7 +8249,6 @@
           <cell r="A68" t="str">
             <v>S-2026-01-65</v>
           </cell>
-          <cell r="B68"/>
           <cell r="C68" t="str">
             <v>RPRO-260122-1564</v>
           </cell>
@@ -8036,7 +8317,6 @@
           <cell r="A69" t="str">
             <v>S-2026-01-66</v>
           </cell>
-          <cell r="B69"/>
           <cell r="C69" t="str">
             <v>RPRO-260122-1565</v>
           </cell>
@@ -8105,7 +8385,6 @@
           <cell r="A70" t="str">
             <v>S-2026-01-67</v>
           </cell>
-          <cell r="B70"/>
           <cell r="C70" t="str">
             <v>RPRO-260122-1566</v>
           </cell>
@@ -8174,7 +8453,6 @@
           <cell r="A71" t="str">
             <v>S-2026-01-68</v>
           </cell>
-          <cell r="B71"/>
           <cell r="C71" t="str">
             <v>RPRO-260122-1567</v>
           </cell>
@@ -8243,7 +8521,6 @@
           <cell r="A72" t="str">
             <v>S-2026-01-69</v>
           </cell>
-          <cell r="B72"/>
           <cell r="C72" t="str">
             <v>RPRO-260122-1568</v>
           </cell>
@@ -8312,7 +8589,6 @@
           <cell r="A73" t="str">
             <v>S-2026-01-70</v>
           </cell>
-          <cell r="B73"/>
           <cell r="C73" t="str">
             <v>RPRO-260122-1569</v>
           </cell>
@@ -8381,7 +8657,6 @@
           <cell r="A74" t="str">
             <v>S-2026-01-71</v>
           </cell>
-          <cell r="B74"/>
           <cell r="C74" t="str">
             <v>RPRO-260122-1570</v>
           </cell>
@@ -8450,7 +8725,6 @@
           <cell r="A75" t="str">
             <v>S-2026-01-72</v>
           </cell>
-          <cell r="B75"/>
           <cell r="C75" t="str">
             <v>RPRO-260122-1571</v>
           </cell>
@@ -8732,7 +9006,6 @@
           <cell r="A79" t="str">
             <v>S-2026-01-76</v>
           </cell>
-          <cell r="B79"/>
           <cell r="C79" t="str">
             <v>RPRO-260122-1573</v>
           </cell>
@@ -8801,7 +9074,6 @@
           <cell r="A80" t="str">
             <v>S-2026-01-77</v>
           </cell>
-          <cell r="B80"/>
           <cell r="C80" t="str">
             <v>RPRO-260122-1574</v>
           </cell>
@@ -8870,7 +9142,6 @@
           <cell r="A81" t="str">
             <v>S-2026-01-78</v>
           </cell>
-          <cell r="B81"/>
           <cell r="C81" t="str">
             <v>RPRO-260122-1575</v>
           </cell>
@@ -8939,7 +9210,6 @@
           <cell r="A82" t="str">
             <v>S-2026-01-79</v>
           </cell>
-          <cell r="B82"/>
           <cell r="C82" t="str">
             <v>RPRO-260122-1576</v>
           </cell>
@@ -9008,7 +9278,6 @@
           <cell r="A83" t="str">
             <v>S-2026-01-80</v>
           </cell>
-          <cell r="B83"/>
           <cell r="C83" t="str">
             <v>RPRO-260122-1577</v>
           </cell>
@@ -9077,7 +9346,6 @@
           <cell r="A84" t="str">
             <v>S-2026-01-81</v>
           </cell>
-          <cell r="B84"/>
           <cell r="C84" t="str">
             <v>RPRO-260122-1578</v>
           </cell>
@@ -9146,7 +9414,6 @@
           <cell r="A85" t="str">
             <v>S-2026-01-82</v>
           </cell>
-          <cell r="B85"/>
           <cell r="C85" t="str">
             <v>RPRO-260122-1579</v>
           </cell>
@@ -9215,7 +9482,6 @@
           <cell r="A86" t="str">
             <v>S-2026-01-83</v>
           </cell>
-          <cell r="B86"/>
           <cell r="C86" t="str">
             <v>RPRO-260122-1580</v>
           </cell>
@@ -9287,7 +9553,6 @@
           <cell r="B87" t="str">
             <v>hủy</v>
           </cell>
-          <cell r="C87"/>
           <cell r="D87" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9356,7 +9621,6 @@
           <cell r="B88" t="str">
             <v>hủy</v>
           </cell>
-          <cell r="C88"/>
           <cell r="D88" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9425,7 +9689,6 @@
           <cell r="B89" t="str">
             <v>hủy</v>
           </cell>
-          <cell r="C89"/>
           <cell r="D89" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9491,7 +9754,6 @@
           <cell r="A90" t="str">
             <v>S-2026-01-87</v>
           </cell>
-          <cell r="B90"/>
           <cell r="C90" t="str">
             <v>RPRO-260127-0875</v>
           </cell>
@@ -9560,7 +9822,6 @@
           <cell r="A91" t="str">
             <v>S-2026-01-88</v>
           </cell>
-          <cell r="B91"/>
           <cell r="C91" t="str">
             <v>RPRO-260127-0877</v>
           </cell>
@@ -9629,7 +9890,6 @@
           <cell r="A92" t="str">
             <v>S-2026-01-89</v>
           </cell>
-          <cell r="B92"/>
           <cell r="C92" t="str">
             <v>RPRO-260127-0879</v>
           </cell>
@@ -9698,7 +9958,6 @@
           <cell r="A93" t="str">
             <v>S-2026-01-90</v>
           </cell>
-          <cell r="B93"/>
           <cell r="C93" t="str">
             <v>RPRO-260128-1270</v>
           </cell>
@@ -9767,7 +10026,6 @@
           <cell r="A94" t="str">
             <v>S-2026-01-91</v>
           </cell>
-          <cell r="B94"/>
           <cell r="C94" t="str">
             <v>RPRO-260128-1271</v>
           </cell>
@@ -9836,7 +10094,6 @@
           <cell r="A95" t="str">
             <v>S-2026-01-92</v>
           </cell>
-          <cell r="B95"/>
           <cell r="C95" t="str">
             <v>RPRO-260128-1272</v>
           </cell>
@@ -9905,7 +10162,6 @@
           <cell r="A96" t="str">
             <v>S-2026-01-93</v>
           </cell>
-          <cell r="B96"/>
           <cell r="C96" t="str">
             <v>RPRO-260128-1273</v>
           </cell>
@@ -9974,7 +10230,6 @@
           <cell r="A97" t="str">
             <v>S-2026-01-94</v>
           </cell>
-          <cell r="B97"/>
           <cell r="C97" t="str">
             <v>RPRO-260128-1274</v>
           </cell>
@@ -10043,7 +10298,6 @@
           <cell r="A98" t="str">
             <v>S-2026-01-95</v>
           </cell>
-          <cell r="B98"/>
           <cell r="C98" t="str">
             <v>RPRO-260128-1275</v>
           </cell>
@@ -10112,7 +10366,6 @@
           <cell r="A99" t="str">
             <v>S-2026-01-96</v>
           </cell>
-          <cell r="B99"/>
           <cell r="C99" t="str">
             <v>RPRO-260128-1276</v>
           </cell>
@@ -10181,7 +10434,6 @@
           <cell r="A100" t="str">
             <v>S-2026-01-97</v>
           </cell>
-          <cell r="B100"/>
           <cell r="C100" t="str">
             <v>RPRO-260128-1277</v>
           </cell>
@@ -10250,7 +10502,6 @@
           <cell r="A101" t="str">
             <v>S-2026-01-98</v>
           </cell>
-          <cell r="B101"/>
           <cell r="C101" t="str">
             <v>RPRO-260129-0656</v>
           </cell>
@@ -10319,7 +10570,6 @@
           <cell r="A102" t="str">
             <v>S-2026-02-01</v>
           </cell>
-          <cell r="B102"/>
           <cell r="C102" t="str">
             <v>RPRO-260203-0021</v>
           </cell>
@@ -10388,7 +10638,6 @@
           <cell r="A103" t="str">
             <v>S-2026-02-02</v>
           </cell>
-          <cell r="B103"/>
           <cell r="C103" t="str">
             <v>RPRO-260203-0022</v>
           </cell>
@@ -10457,7 +10706,6 @@
           <cell r="A104" t="str">
             <v>S-2026-02-03</v>
           </cell>
-          <cell r="B104"/>
           <cell r="C104" t="str">
             <v>RPRO-260203-0770</v>
           </cell>
@@ -10526,7 +10774,6 @@
           <cell r="A105" t="str">
             <v>S-2026-02-04</v>
           </cell>
-          <cell r="B105"/>
           <cell r="C105" t="str">
             <v>RPRO-260203-0771</v>
           </cell>
@@ -10595,7 +10842,6 @@
           <cell r="A106" t="str">
             <v>S-2026-02-05</v>
           </cell>
-          <cell r="B106"/>
           <cell r="C106" t="str">
             <v>RPRO-260203-0772</v>
           </cell>
@@ -10664,7 +10910,6 @@
           <cell r="A107" t="str">
             <v>S-2026-02-06</v>
           </cell>
-          <cell r="B107"/>
           <cell r="C107" t="str">
             <v>RPRO-260203-0773</v>
           </cell>
@@ -10733,7 +10978,6 @@
           <cell r="A108" t="str">
             <v>S-2026-02-07</v>
           </cell>
-          <cell r="B108"/>
           <cell r="C108" t="str">
             <v>RPRO-260203-0774</v>
           </cell>
@@ -10802,7 +11046,6 @@
           <cell r="A109" t="str">
             <v>S-2026-02-08</v>
           </cell>
-          <cell r="B109"/>
           <cell r="C109" t="str">
             <v>RPRO-260203-0775</v>
           </cell>
@@ -10871,7 +11114,6 @@
           <cell r="A110" t="str">
             <v>S-2026-02-09</v>
           </cell>
-          <cell r="B110"/>
           <cell r="C110" t="str">
             <v>RPRO-260203-0776</v>
           </cell>
@@ -10940,7 +11182,6 @@
           <cell r="A111" t="str">
             <v>S-2026-02-10</v>
           </cell>
-          <cell r="B111"/>
           <cell r="C111" t="str">
             <v>RPRO-260203-0777</v>
           </cell>
@@ -11009,7 +11250,6 @@
           <cell r="A112" t="str">
             <v>S-2026-02-11</v>
           </cell>
-          <cell r="B112"/>
           <cell r="C112" t="str">
             <v>RPRO-260203-0778</v>
           </cell>
@@ -11078,7 +11318,6 @@
           <cell r="A113" t="str">
             <v>S-2026-02-12</v>
           </cell>
-          <cell r="B113"/>
           <cell r="C113" t="str">
             <v>RPRO-260203-0779</v>
           </cell>
@@ -11147,7 +11386,6 @@
           <cell r="A114" t="str">
             <v>S-2026-02-13</v>
           </cell>
-          <cell r="B114"/>
           <cell r="C114" t="str">
             <v>RPRO-260203-0780</v>
           </cell>
@@ -11216,7 +11454,6 @@
           <cell r="A115" t="str">
             <v>S-2026-02-14</v>
           </cell>
-          <cell r="B115"/>
           <cell r="C115" t="str">
             <v>RPRO-260203-0781</v>
           </cell>
@@ -11285,7 +11522,6 @@
           <cell r="A116" t="str">
             <v>S-2026-02-15</v>
           </cell>
-          <cell r="B116"/>
           <cell r="C116" t="str">
             <v>RPRO-260203-0782</v>
           </cell>
@@ -11354,7 +11590,6 @@
           <cell r="A117" t="str">
             <v>S-2026-02-16</v>
           </cell>
-          <cell r="B117"/>
           <cell r="C117" t="str">
             <v>RPRO-260203-0783</v>
           </cell>
@@ -11423,7 +11658,6 @@
           <cell r="A118" t="str">
             <v>S-2026-02-17</v>
           </cell>
-          <cell r="B118"/>
           <cell r="C118" t="str">
             <v>RPRO-260203-0784</v>
           </cell>
@@ -11492,7 +11726,6 @@
           <cell r="A119" t="str">
             <v>S-2026-02-18</v>
           </cell>
-          <cell r="B119"/>
           <cell r="C119" t="str">
             <v>RPRO-260204-0399</v>
           </cell>
@@ -11561,7 +11794,6 @@
           <cell r="A120" t="str">
             <v>S-2026-02-19</v>
           </cell>
-          <cell r="B120"/>
           <cell r="C120" t="str">
             <v>RPRO-260204-0400</v>
           </cell>
@@ -11630,7 +11862,6 @@
           <cell r="A121" t="str">
             <v>L-2026-02-20</v>
           </cell>
-          <cell r="B121"/>
           <cell r="C121" t="str">
             <v>RPRO-260204-0401</v>
           </cell>
@@ -11664,7 +11895,6 @@
           <cell r="M121" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N121"/>
           <cell r="O121" t="str">
             <v>Lab test</v>
           </cell>
@@ -11697,7 +11927,6 @@
           <cell r="A122" t="str">
             <v>L-2026-02-21</v>
           </cell>
-          <cell r="B122"/>
           <cell r="C122" t="str">
             <v>RPRO-260204-0402</v>
           </cell>
@@ -11731,7 +11960,6 @@
           <cell r="M122" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N122"/>
           <cell r="O122" t="str">
             <v>Lab test</v>
           </cell>
@@ -11835,7 +12063,6 @@
           <cell r="A124" t="str">
             <v>S-2026-02-23</v>
           </cell>
-          <cell r="B124"/>
           <cell r="C124" t="str">
             <v>RPRO-260210-0003</v>
           </cell>
@@ -11975,7 +12202,6 @@
           <cell r="A126" t="str">
             <v>S-2026-02-25</v>
           </cell>
-          <cell r="B126"/>
           <cell r="C126" t="str">
             <v>RPRO-260210-0005</v>
           </cell>
@@ -12044,7 +12270,6 @@
           <cell r="A127" t="str">
             <v>S-2026-02-26</v>
           </cell>
-          <cell r="B127"/>
           <cell r="C127" t="str">
             <v>RPRO-260210-0006</v>
           </cell>
@@ -12113,7 +12338,6 @@
           <cell r="A128" t="str">
             <v>S-2026-02-27</v>
           </cell>
-          <cell r="B128"/>
           <cell r="C128" t="str">
             <v>RPRO-260210-0007</v>
           </cell>
@@ -12182,7 +12406,6 @@
           <cell r="A129" t="str">
             <v>S-2026-02-28</v>
           </cell>
-          <cell r="B129"/>
           <cell r="C129" t="str">
             <v>RPRO-260210-0008</v>
           </cell>
@@ -12251,7 +12474,6 @@
           <cell r="A130" t="str">
             <v>S-2026-02-29</v>
           </cell>
-          <cell r="B130"/>
           <cell r="C130" t="str">
             <v>RPRO-260210-0009</v>
           </cell>
@@ -12320,7 +12542,6 @@
           <cell r="A131" t="str">
             <v>S-2026-02-30</v>
           </cell>
-          <cell r="B131"/>
           <cell r="C131" t="str">
             <v>RPRO-260210-0010</v>
           </cell>
@@ -12389,7 +12610,6 @@
           <cell r="A132" t="str">
             <v>S-2026-02-31</v>
           </cell>
-          <cell r="B132"/>
           <cell r="C132" t="str">
             <v>RPRO-260210-0011</v>
           </cell>
@@ -12459,7 +12679,6 @@
           <cell r="A133" t="str">
             <v>S-2026-02-32</v>
           </cell>
-          <cell r="B133"/>
           <cell r="C133" t="str">
             <v>RPRO-260210-0012</v>
           </cell>
@@ -12529,7 +12748,6 @@
           <cell r="A134" t="str">
             <v>S-2026-02-33</v>
           </cell>
-          <cell r="B134"/>
           <cell r="C134" t="str">
             <v>RPRO-260210-0013</v>
           </cell>
@@ -12598,7 +12816,6 @@
           <cell r="A135" t="str">
             <v>S-2026-02-34</v>
           </cell>
-          <cell r="B135"/>
           <cell r="C135" t="str">
             <v>RPRO-260211-0001</v>
           </cell>
@@ -12669,7 +12886,6 @@
           <cell r="A136" t="str">
             <v>S-2026-02-35</v>
           </cell>
-          <cell r="B136"/>
           <cell r="C136" t="str">
             <v>RPRO-260227-0335</v>
           </cell>
@@ -12738,7 +12954,6 @@
           <cell r="A137" t="str">
             <v>S-2026-02-36</v>
           </cell>
-          <cell r="B137"/>
           <cell r="C137" t="str">
             <v>RPRO-260227-0336</v>
           </cell>
@@ -12807,7 +13022,6 @@
           <cell r="A138" t="str">
             <v>S-2026-02-37</v>
           </cell>
-          <cell r="B138"/>
           <cell r="C138" t="str">
             <v>RPRO-260227-0337</v>
           </cell>
@@ -12876,7 +13090,6 @@
           <cell r="A139" t="str">
             <v>S-2026-02-38</v>
           </cell>
-          <cell r="B139"/>
           <cell r="C139" t="str">
             <v>RPRO-260227-0338</v>
           </cell>
@@ -12945,7 +13158,6 @@
           <cell r="A140" t="str">
             <v>S-2026-02-39</v>
           </cell>
-          <cell r="B140"/>
           <cell r="C140" t="str">
             <v>RPRO-260227-0339</v>
           </cell>
@@ -13014,7 +13226,6 @@
           <cell r="A141" t="str">
             <v>L-2026-02-40</v>
           </cell>
-          <cell r="B141"/>
           <cell r="C141" t="str">
             <v>RPRO-260227-0340</v>
           </cell>
@@ -13048,7 +13259,6 @@
           <cell r="M141" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N141"/>
           <cell r="O141" t="str">
             <v>Lab test</v>
           </cell>
@@ -13081,7 +13291,6 @@
           <cell r="A142" t="str">
             <v>S-2026-02-41</v>
           </cell>
-          <cell r="B142"/>
           <cell r="C142" t="str">
             <v>RPRO-260227-0341</v>
           </cell>
@@ -13150,7 +13359,6 @@
           <cell r="A143" t="str">
             <v>S-2026-02-42</v>
           </cell>
-          <cell r="B143"/>
           <cell r="C143" t="str">
             <v>RPRO-260227-0342</v>
           </cell>
@@ -13219,7 +13427,6 @@
           <cell r="A144" t="str">
             <v>S-2026-02-43</v>
           </cell>
-          <cell r="B144"/>
           <cell r="C144" t="str">
             <v>RPRO-260227-0343</v>
           </cell>
@@ -13288,7 +13495,6 @@
           <cell r="A145" t="str">
             <v>S-2026-02-44</v>
           </cell>
-          <cell r="B145"/>
           <cell r="C145" t="str">
             <v>RPRO-260227-0344</v>
           </cell>
@@ -13357,7 +13563,6 @@
           <cell r="A146" t="str">
             <v>S-2026-02-45</v>
           </cell>
-          <cell r="B146"/>
           <cell r="C146" t="str">
             <v>RPRO-260227-0345</v>
           </cell>
@@ -13497,7 +13702,6 @@
           <cell r="A148" t="str">
             <v>S-2026-02-47</v>
           </cell>
-          <cell r="B148"/>
           <cell r="C148" t="str">
             <v>RPRO-260227-0347</v>
           </cell>
@@ -13566,7 +13770,6 @@
           <cell r="A149" t="str">
             <v>S-2026-02-48</v>
           </cell>
-          <cell r="B149"/>
           <cell r="C149" t="str">
             <v>RPRO-260227-0348</v>
           </cell>
@@ -13635,7 +13838,6 @@
           <cell r="A150" t="str">
             <v>S-2026-02-49</v>
           </cell>
-          <cell r="B150"/>
           <cell r="C150" t="str">
             <v>RPRO-260302-0004</v>
           </cell>
@@ -13704,7 +13906,6 @@
           <cell r="A151" t="str">
             <v>S-2026-02-50</v>
           </cell>
-          <cell r="B151"/>
           <cell r="C151" t="str">
             <v>RPRO-260227-0349</v>
           </cell>
@@ -13773,7 +13974,6 @@
           <cell r="A152" t="str">
             <v>S-2026-02-51</v>
           </cell>
-          <cell r="B152"/>
           <cell r="C152" t="str">
             <v>RPRO-260227-0350</v>
           </cell>
@@ -13842,7 +14042,6 @@
           <cell r="A153" t="str">
             <v>S-2026-02-52</v>
           </cell>
-          <cell r="B153"/>
           <cell r="C153" t="str">
             <v>RPRO-260227-0351</v>
           </cell>
@@ -13911,7 +14110,6 @@
           <cell r="A154" t="str">
             <v>S-2026-02-53</v>
           </cell>
-          <cell r="B154"/>
           <cell r="C154" t="str">
             <v>RPRO-260227-0352</v>
           </cell>
@@ -13980,7 +14178,6 @@
           <cell r="A155" t="str">
             <v>L-2026-03-01</v>
           </cell>
-          <cell r="B155"/>
           <cell r="C155" t="str">
             <v>RPRO-260303-0005</v>
           </cell>
@@ -14014,7 +14211,6 @@
           <cell r="M155" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N155"/>
           <cell r="O155" t="str">
             <v>Lab test</v>
           </cell>
@@ -14047,7 +14243,6 @@
           <cell r="A156" t="str">
             <v>L-2026-03-02</v>
           </cell>
-          <cell r="B156"/>
           <cell r="C156" t="str">
             <v>RPRO-260303-0006</v>
           </cell>
@@ -14081,7 +14276,6 @@
           <cell r="M156" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N156"/>
           <cell r="O156" t="str">
             <v>Lab test</v>
           </cell>
@@ -14398,7 +14592,6 @@
           <cell r="A161" t="str">
             <v>S-2026-03-07</v>
           </cell>
-          <cell r="B161"/>
           <cell r="C161" t="str">
             <v>RPRO-260303-0011</v>
           </cell>
@@ -14467,7 +14660,6 @@
           <cell r="A162" t="str">
             <v>S-2026-03-08</v>
           </cell>
-          <cell r="B162"/>
           <cell r="C162" t="str">
             <v>RPRO-260303-0012</v>
           </cell>
@@ -14536,7 +14728,6 @@
           <cell r="A163" t="str">
             <v>S-2026-03-09</v>
           </cell>
-          <cell r="B163"/>
           <cell r="C163" t="str">
             <v>RPRO-260303-0013</v>
           </cell>
@@ -14605,7 +14796,6 @@
           <cell r="A164" t="str">
             <v>S-2026-03-10</v>
           </cell>
-          <cell r="B164"/>
           <cell r="C164" t="str">
             <v>RPRO-260303-0014</v>
           </cell>
@@ -14674,7 +14864,6 @@
           <cell r="A165" t="str">
             <v>S-2026-03-11</v>
           </cell>
-          <cell r="B165"/>
           <cell r="C165" t="str">
             <v>RPRO-260313-0139</v>
           </cell>
@@ -14708,7 +14897,6 @@
           <cell r="M165" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
-          <cell r="N165"/>
           <cell r="O165" t="str">
             <v>Sample</v>
           </cell>
@@ -14741,7 +14929,6 @@
           <cell r="A166" t="str">
             <v>S-2026-03-12</v>
           </cell>
-          <cell r="B166"/>
           <cell r="C166" t="str">
             <v>RPRO-260313-0140</v>
           </cell>
@@ -14775,7 +14962,6 @@
           <cell r="M166" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
-          <cell r="N166"/>
           <cell r="O166" t="str">
             <v>Sample</v>
           </cell>
@@ -14808,7 +14994,6 @@
           <cell r="A167" t="str">
             <v>S-2026-03-13</v>
           </cell>
-          <cell r="B167"/>
           <cell r="C167" t="str">
             <v>RPRO-260313-0141</v>
           </cell>
@@ -14842,7 +15027,6 @@
           <cell r="M167" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
-          <cell r="N167"/>
           <cell r="O167" t="str">
             <v>Sample</v>
           </cell>
@@ -14946,7 +15130,6 @@
           <cell r="A169" t="str">
             <v>S-2026-03-15</v>
           </cell>
-          <cell r="B169"/>
           <cell r="C169" t="str">
             <v>RPRO-260306-1547</v>
           </cell>
@@ -15015,7 +15198,6 @@
           <cell r="A170" t="str">
             <v>S-2026-03-16</v>
           </cell>
-          <cell r="B170"/>
           <cell r="C170" t="str">
             <v>RPRO-260306-1548</v>
           </cell>
@@ -15084,7 +15266,6 @@
           <cell r="A171" t="str">
             <v>S-2026-03-17</v>
           </cell>
-          <cell r="B171"/>
           <cell r="C171" t="str">
             <v>RPRO-260306-1549</v>
           </cell>
@@ -15153,7 +15334,6 @@
           <cell r="A172" t="str">
             <v>S-2026-03-18</v>
           </cell>
-          <cell r="B172"/>
           <cell r="C172" t="str">
             <v>RPRO-260306-1550</v>
           </cell>
@@ -15222,7 +15402,6 @@
           <cell r="A173" t="str">
             <v>S-2026-03-19</v>
           </cell>
-          <cell r="B173"/>
           <cell r="C173" t="str">
             <v>RPRO-260306-1551</v>
           </cell>
@@ -15291,7 +15470,6 @@
           <cell r="A174" t="str">
             <v>S-2026-03-20</v>
           </cell>
-          <cell r="B174"/>
           <cell r="C174" t="str">
             <v>RPRO-260306-1552</v>
           </cell>
@@ -15360,7 +15538,6 @@
           <cell r="A175" t="str">
             <v>S-2026-03-21</v>
           </cell>
-          <cell r="B175"/>
           <cell r="C175" t="str">
             <v>RPRO-260306-1553</v>
           </cell>
@@ -15429,7 +15606,6 @@
           <cell r="A176" t="str">
             <v>S-2026-03-22</v>
           </cell>
-          <cell r="B176"/>
           <cell r="C176" t="str">
             <v>RPRO-260306-1554</v>
           </cell>
@@ -15498,7 +15674,6 @@
           <cell r="A177" t="str">
             <v>S-2026-03-23</v>
           </cell>
-          <cell r="B177"/>
           <cell r="C177" t="str">
             <v>RPRO-260306-1555</v>
           </cell>
@@ -15567,7 +15742,6 @@
           <cell r="A178" t="str">
             <v>S-2026-03-24</v>
           </cell>
-          <cell r="B178"/>
           <cell r="C178" t="str">
             <v>RPRO-260306-1556</v>
           </cell>
@@ -15707,7 +15881,6 @@
           <cell r="A180" t="str">
             <v>L-2026-03-26</v>
           </cell>
-          <cell r="B180"/>
           <cell r="C180" t="str">
             <v>RPRO-260305-1288</v>
           </cell>
@@ -15741,7 +15914,6 @@
           <cell r="M180" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N180"/>
           <cell r="O180" t="str">
             <v>Lab test</v>
           </cell>
@@ -15845,7 +16017,6 @@
           <cell r="A182" t="str">
             <v>S-2026-03-28</v>
           </cell>
-          <cell r="B182"/>
           <cell r="C182" t="str">
             <v>RPRO-260306-1559</v>
           </cell>
@@ -15914,7 +16085,6 @@
           <cell r="A183" t="str">
             <v>S-2026-03-29</v>
           </cell>
-          <cell r="B183"/>
           <cell r="C183" t="str">
             <v>RPRO-260306-1560</v>
           </cell>
@@ -15983,7 +16153,6 @@
           <cell r="A184" t="str">
             <v>S-2026-03-30</v>
           </cell>
-          <cell r="B184"/>
           <cell r="C184" t="str">
             <v>RPRO-260306-1561</v>
           </cell>
@@ -16052,7 +16221,6 @@
           <cell r="A185" t="str">
             <v>S-2026-03-31</v>
           </cell>
-          <cell r="B185"/>
           <cell r="C185" t="str">
             <v>RPRO-260306-1562</v>
           </cell>
@@ -16121,7 +16289,6 @@
           <cell r="A186" t="str">
             <v>S-2026-03-32</v>
           </cell>
-          <cell r="B186"/>
           <cell r="C186" t="str">
             <v>RPRO-260306-1563</v>
           </cell>
@@ -16190,7 +16357,6 @@
           <cell r="A187" t="str">
             <v>S-2026-03-33</v>
           </cell>
-          <cell r="B187"/>
           <cell r="C187" t="str">
             <v>RPRO-260306-1564</v>
           </cell>
@@ -16259,7 +16425,6 @@
           <cell r="A188" t="str">
             <v>S-2026-03-34</v>
           </cell>
-          <cell r="B188"/>
           <cell r="C188" t="str">
             <v>RPRO-260306-1565</v>
           </cell>
@@ -16328,7 +16493,6 @@
           <cell r="A189" t="str">
             <v>S-2026-03-35</v>
           </cell>
-          <cell r="B189"/>
           <cell r="C189" t="str">
             <v>RPRO-260306-1566</v>
           </cell>
@@ -16397,7 +16561,6 @@
           <cell r="A190" t="str">
             <v>S-2026-03-36</v>
           </cell>
-          <cell r="B190"/>
           <cell r="C190" t="str">
             <v>RPRO-260307-0080</v>
           </cell>
@@ -16466,7 +16629,6 @@
           <cell r="A191" t="str">
             <v>S-2026-03-37</v>
           </cell>
-          <cell r="B191"/>
           <cell r="C191" t="str">
             <v>RPRO-260306-1736</v>
           </cell>
@@ -16535,7 +16697,6 @@
           <cell r="A192" t="str">
             <v>S-2026-03-38</v>
           </cell>
-          <cell r="B192"/>
           <cell r="C192" t="str">
             <v>RPRO-260306-1737</v>
           </cell>
@@ -16604,7 +16765,6 @@
           <cell r="A193" t="str">
             <v>S-2026-03-39</v>
           </cell>
-          <cell r="B193"/>
           <cell r="C193" t="str">
             <v>RPRO-260306-1738</v>
           </cell>
@@ -16673,7 +16833,6 @@
           <cell r="A194" t="str">
             <v>S-2026-03-40</v>
           </cell>
-          <cell r="B194"/>
           <cell r="C194" t="str">
             <v>RPRO-260306-1739</v>
           </cell>
@@ -16742,7 +16901,6 @@
           <cell r="A195" t="str">
             <v>S-2026-03-41</v>
           </cell>
-          <cell r="B195"/>
           <cell r="C195" t="str">
             <v>RPRO-260306-1740</v>
           </cell>
@@ -16811,7 +16969,6 @@
           <cell r="A196" t="str">
             <v>S-2026-03-42</v>
           </cell>
-          <cell r="B196"/>
           <cell r="C196" t="str">
             <v>RPRO-260307-0081</v>
           </cell>
@@ -16880,7 +17037,6 @@
           <cell r="A197" t="str">
             <v>S-2026-03-43</v>
           </cell>
-          <cell r="B197"/>
           <cell r="C197" t="str">
             <v>RPRO-260307-0082</v>
           </cell>
@@ -16949,7 +17105,6 @@
           <cell r="A198" t="str">
             <v>S-2026-03-44</v>
           </cell>
-          <cell r="B198"/>
           <cell r="C198" t="str">
             <v>RPRO-260307-0083</v>
           </cell>
@@ -17018,7 +17173,6 @@
           <cell r="A199" t="str">
             <v>S-2026-03-45</v>
           </cell>
-          <cell r="B199"/>
           <cell r="C199" t="str">
             <v>RPRO-260307-0084</v>
           </cell>
@@ -17087,7 +17241,6 @@
           <cell r="A200" t="str">
             <v>S-2026-03-46</v>
           </cell>
-          <cell r="B200"/>
           <cell r="C200" t="str">
             <v>RPRO-260307-0085</v>
           </cell>
@@ -17156,7 +17309,6 @@
           <cell r="A201" t="str">
             <v>S-2026-03-47</v>
           </cell>
-          <cell r="B201"/>
           <cell r="C201" t="str">
             <v>RPRO-260310-0362</v>
           </cell>
@@ -17296,7 +17448,6 @@
           <cell r="A203" t="str">
             <v>S-2026-03-49</v>
           </cell>
-          <cell r="B203"/>
           <cell r="C203" t="str">
             <v>RPRO-260310-0364</v>
           </cell>
@@ -17365,7 +17516,6 @@
           <cell r="A204" t="str">
             <v>S-2026-03-50</v>
           </cell>
-          <cell r="B204"/>
           <cell r="C204" t="str">
             <v>RPRO-260310-0365</v>
           </cell>
@@ -17505,7 +17655,6 @@
           <cell r="A206" t="str">
             <v>S-2026-03-52</v>
           </cell>
-          <cell r="B206"/>
           <cell r="C206" t="str">
             <v>RPRO-260310-0367</v>
           </cell>
@@ -17574,7 +17723,6 @@
           <cell r="A207" t="str">
             <v>S-2026-03-53</v>
           </cell>
-          <cell r="B207"/>
           <cell r="C207" t="str">
             <v>RPRO-260310-0368</v>
           </cell>
@@ -17643,7 +17791,6 @@
           <cell r="A208" t="str">
             <v>S-2026-03-54</v>
           </cell>
-          <cell r="B208"/>
           <cell r="C208" t="str">
             <v>RPRO-260310-0369</v>
           </cell>
@@ -17712,7 +17859,6 @@
           <cell r="A209" t="str">
             <v>S-2026-03-55</v>
           </cell>
-          <cell r="B209"/>
           <cell r="C209" t="str">
             <v>RPRO-260310-0370</v>
           </cell>
@@ -17781,7 +17927,6 @@
           <cell r="A210" t="str">
             <v>S-2026-03-56</v>
           </cell>
-          <cell r="B210"/>
           <cell r="C210" t="str">
             <v>RPRO-260310-0371</v>
           </cell>
@@ -17850,7 +17995,6 @@
           <cell r="A211" t="str">
             <v>S-2026-03-57</v>
           </cell>
-          <cell r="B211"/>
           <cell r="C211" t="str">
             <v>RPRO-260310-0372</v>
           </cell>
@@ -17919,7 +18063,6 @@
           <cell r="A212" t="str">
             <v>S-2026-03-58</v>
           </cell>
-          <cell r="B212"/>
           <cell r="C212" t="str">
             <v>RPRO-260310-0373</v>
           </cell>
@@ -17988,7 +18131,6 @@
           <cell r="A213" t="str">
             <v>S-2026-03-59</v>
           </cell>
-          <cell r="B213"/>
           <cell r="C213" t="str">
             <v>RPRO-260310-0374</v>
           </cell>
@@ -18057,7 +18199,6 @@
           <cell r="A214" t="str">
             <v>S-2026-03-60</v>
           </cell>
-          <cell r="B214"/>
           <cell r="C214" t="str">
             <v>RPRO-260310-0375</v>
           </cell>
@@ -18126,7 +18267,6 @@
           <cell r="A215" t="str">
             <v>S-2026-03-61</v>
           </cell>
-          <cell r="B215"/>
           <cell r="C215" t="str">
             <v>RPRO-260310-0376</v>
           </cell>
@@ -18198,7 +18338,6 @@
           <cell r="B216" t="str">
             <v>huy</v>
           </cell>
-          <cell r="C216"/>
           <cell r="D216" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -18229,7 +18368,6 @@
           <cell r="M216" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N216"/>
           <cell r="O216" t="str">
             <v>Lab test</v>
           </cell>
@@ -18265,7 +18403,6 @@
           <cell r="B217" t="str">
             <v>huy</v>
           </cell>
-          <cell r="C217"/>
           <cell r="D217" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -18296,7 +18433,6 @@
           <cell r="M217" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N217"/>
           <cell r="O217" t="str">
             <v>Lab test</v>
           </cell>
@@ -18329,7 +18465,6 @@
           <cell r="A218" t="str">
             <v>S-2026-03-64</v>
           </cell>
-          <cell r="B218"/>
           <cell r="C218" t="str">
             <v>RPRO-260313-0142</v>
           </cell>
@@ -18398,7 +18533,6 @@
           <cell r="A219" t="str">
             <v>S-2026-03-65</v>
           </cell>
-          <cell r="B219"/>
           <cell r="C219" t="str">
             <v>RPRO-260313-0143</v>
           </cell>
@@ -18467,7 +18601,6 @@
           <cell r="A220" t="str">
             <v>S-2026-03-66</v>
           </cell>
-          <cell r="B220"/>
           <cell r="C220" t="str">
             <v>RPRO-260313-0144</v>
           </cell>
@@ -18536,7 +18669,6 @@
           <cell r="A221" t="str">
             <v>S-2026-03-67</v>
           </cell>
-          <cell r="B221"/>
           <cell r="C221" t="str">
             <v>RPRO-260313-0145</v>
           </cell>
@@ -18605,7 +18737,6 @@
           <cell r="A222" t="str">
             <v>S-2026-03-68</v>
           </cell>
-          <cell r="B222"/>
           <cell r="C222" t="str">
             <v>RPRO-260313-0146</v>
           </cell>
@@ -18674,7 +18805,6 @@
           <cell r="A223" t="str">
             <v>S-2026-03-69</v>
           </cell>
-          <cell r="B223"/>
           <cell r="C223" t="str">
             <v>RPRO-260313-0147</v>
           </cell>
@@ -18743,7 +18873,6 @@
           <cell r="A224" t="str">
             <v>S-2026-03-70</v>
           </cell>
-          <cell r="B224"/>
           <cell r="C224" t="str">
             <v>RPRO-260313-0148</v>
           </cell>
@@ -18812,7 +18941,6 @@
           <cell r="A225" t="str">
             <v>S-2026-03-71</v>
           </cell>
-          <cell r="B225"/>
           <cell r="C225" t="str">
             <v>RPRO-260313-0149</v>
           </cell>
@@ -18881,7 +19009,6 @@
           <cell r="A226" t="str">
             <v>S-2026-03-72</v>
           </cell>
-          <cell r="B226"/>
           <cell r="C226" t="str">
             <v>RPRO-260313-0150</v>
           </cell>
@@ -18950,7 +19077,6 @@
           <cell r="A227" t="str">
             <v>S-2026-03-73</v>
           </cell>
-          <cell r="B227"/>
           <cell r="C227" t="str">
             <v>RPRO-260313-0151</v>
           </cell>
@@ -19019,7 +19145,6 @@
           <cell r="A228" t="str">
             <v>S-2026-03-74</v>
           </cell>
-          <cell r="B228"/>
           <cell r="C228" t="str">
             <v>RPRO-260313-0152</v>
           </cell>
@@ -19088,7 +19213,6 @@
           <cell r="A229" t="str">
             <v>S-2026-03-75</v>
           </cell>
-          <cell r="B229"/>
           <cell r="C229" t="str">
             <v>RPRO-260313-0318</v>
           </cell>
@@ -19157,7 +19281,6 @@
           <cell r="A230" t="str">
             <v>S-2026-03-76</v>
           </cell>
-          <cell r="B230"/>
           <cell r="C230" t="str">
             <v>RPRO-260313-0319</v>
           </cell>
@@ -19226,7 +19349,6 @@
           <cell r="A231" t="str">
             <v>S-2026-03-77</v>
           </cell>
-          <cell r="B231"/>
           <cell r="C231" t="str">
             <v>RPRO-260314-0198</v>
           </cell>
@@ -19295,7 +19417,6 @@
           <cell r="A232" t="str">
             <v>S-2026-03-78</v>
           </cell>
-          <cell r="B232"/>
           <cell r="C232" t="str">
             <v>RPRO-260314-0199</v>
           </cell>
@@ -19364,7 +19485,6 @@
           <cell r="A233" t="str">
             <v>S-2026-03-79</v>
           </cell>
-          <cell r="B233"/>
           <cell r="C233" t="str">
             <v>RPRO-260317-0628</v>
           </cell>
@@ -19433,7 +19553,6 @@
           <cell r="A234" t="str">
             <v>S-2026-03-80</v>
           </cell>
-          <cell r="B234"/>
           <cell r="C234" t="str">
             <v>RPRO-260317-0629</v>
           </cell>
@@ -19502,7 +19621,6 @@
           <cell r="A235" t="str">
             <v>S-2026-03-81</v>
           </cell>
-          <cell r="B235"/>
           <cell r="C235" t="str">
             <v>RPRO-260317-0630</v>
           </cell>
@@ -19571,7 +19689,6 @@
           <cell r="A236" t="str">
             <v>S-2026-03-82</v>
           </cell>
-          <cell r="B236"/>
           <cell r="C236" t="str">
             <v>RPRO-260317-0631</v>
           </cell>
@@ -19640,7 +19757,6 @@
           <cell r="A237" t="str">
             <v>S-2026-03-83</v>
           </cell>
-          <cell r="B237"/>
           <cell r="C237" t="str">
             <v>RPRO-260317-0632</v>
           </cell>
@@ -19709,7 +19825,6 @@
           <cell r="A238" t="str">
             <v>S-2026-03-84</v>
           </cell>
-          <cell r="B238"/>
           <cell r="C238" t="str">
             <v>RPRO-260317-0633</v>
           </cell>
@@ -19778,7 +19893,6 @@
           <cell r="A239" t="str">
             <v>S-2026-03-85</v>
           </cell>
-          <cell r="B239"/>
           <cell r="C239" t="str">
             <v>RPRO-260317-0634</v>
           </cell>
@@ -19847,7 +19961,6 @@
           <cell r="A240" t="str">
             <v>S-2026-03-86</v>
           </cell>
-          <cell r="B240"/>
           <cell r="C240" t="str">
             <v>RPRO-260317-0635</v>
           </cell>
@@ -19916,7 +20029,6 @@
           <cell r="A241" t="str">
             <v>S-2026-03-87</v>
           </cell>
-          <cell r="B241"/>
           <cell r="C241" t="str">
             <v>RPRO-260317-0636</v>
           </cell>
@@ -19985,7 +20097,6 @@
           <cell r="A242" t="str">
             <v>L-2026-03-88</v>
           </cell>
-          <cell r="B242"/>
           <cell r="C242" t="str">
             <v>RPRO-260317-0637</v>
           </cell>
@@ -20019,7 +20130,6 @@
           <cell r="M242" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N242"/>
           <cell r="O242" t="str">
             <v>Lab test</v>
           </cell>
@@ -20088,7 +20198,6 @@
           <cell r="M243" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N243"/>
           <cell r="O243" t="str">
             <v>Lab test</v>
           </cell>
@@ -20121,7 +20230,6 @@
           <cell r="A244" t="str">
             <v>S-2026-03-90</v>
           </cell>
-          <cell r="B244"/>
           <cell r="C244" t="str">
             <v>RPRO-260317-0639</v>
           </cell>
@@ -20190,7 +20298,6 @@
           <cell r="A245" t="str">
             <v>S-2026-03-91</v>
           </cell>
-          <cell r="B245"/>
           <cell r="C245" t="str">
             <v>RPRO-260317-0640</v>
           </cell>
@@ -20259,7 +20366,6 @@
           <cell r="A246" t="str">
             <v>S-2026-03-92</v>
           </cell>
-          <cell r="B246"/>
           <cell r="C246" t="str">
             <v>RPRO-260317-0641</v>
           </cell>
@@ -20328,7 +20434,6 @@
           <cell r="A247" t="str">
             <v>L-2026-03-93</v>
           </cell>
-          <cell r="B247"/>
           <cell r="C247" t="str">
             <v>RPRO-260318-0477</v>
           </cell>
@@ -20362,7 +20467,6 @@
           <cell r="M247" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N247"/>
           <cell r="O247" t="str">
             <v>Lab test</v>
           </cell>
@@ -20395,7 +20499,6 @@
           <cell r="A248" t="str">
             <v>L-2026-03-94</v>
           </cell>
-          <cell r="B248"/>
           <cell r="C248" t="str">
             <v>RPRO-260318-0478</v>
           </cell>
@@ -20429,7 +20532,6 @@
           <cell r="M248" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N248"/>
           <cell r="O248" t="str">
             <v>Lab test</v>
           </cell>
@@ -20533,7 +20635,6 @@
           <cell r="A250" t="str">
             <v>S-2026-03-96</v>
           </cell>
-          <cell r="B250"/>
           <cell r="C250" t="str">
             <v>RPRO-260318-0482</v>
           </cell>
@@ -20602,7 +20703,6 @@
           <cell r="A251" t="str">
             <v>S-2026-03-97</v>
           </cell>
-          <cell r="B251"/>
           <cell r="C251" t="str">
             <v>RPRO-260324-0278</v>
           </cell>
@@ -20671,7 +20771,6 @@
           <cell r="A252" t="str">
             <v>S-2026-03-98</v>
           </cell>
-          <cell r="B252"/>
           <cell r="C252" t="str">
             <v>RPRO-260324-0279</v>
           </cell>
@@ -20811,7 +20910,6 @@
           <cell r="A254" t="str">
             <v>S-2026-03-100</v>
           </cell>
-          <cell r="B254"/>
           <cell r="C254" t="str">
             <v>RPRO-260324-0281</v>
           </cell>
@@ -20880,7 +20978,6 @@
           <cell r="A255" t="str">
             <v>S-2026-03-101</v>
           </cell>
-          <cell r="B255"/>
           <cell r="C255" t="str">
             <v>RPRO-260324-0282</v>
           </cell>
@@ -20949,7 +21046,6 @@
           <cell r="A256" t="str">
             <v>S-2026-03-102</v>
           </cell>
-          <cell r="B256"/>
           <cell r="C256" t="str">
             <v>RPRO-260324-0531</v>
           </cell>
@@ -21018,7 +21114,6 @@
           <cell r="A257" t="str">
             <v>S-2026-03-103</v>
           </cell>
-          <cell r="B257"/>
           <cell r="C257" t="str">
             <v>RPRO-260324-0283</v>
           </cell>
@@ -21087,7 +21182,6 @@
           <cell r="A258" t="str">
             <v>S-2026-03-104</v>
           </cell>
-          <cell r="B258"/>
           <cell r="C258" t="str">
             <v>RPRO-260324-0284</v>
           </cell>
@@ -21156,7 +21250,6 @@
           <cell r="A259" t="str">
             <v>L-2026-03-105</v>
           </cell>
-          <cell r="B259"/>
           <cell r="C259" t="str">
             <v>RPRO-260321-0027</v>
           </cell>
@@ -21190,7 +21283,6 @@
           <cell r="M259" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N259"/>
           <cell r="O259" t="str">
             <v>Lab test</v>
           </cell>
@@ -21223,7 +21315,6 @@
           <cell r="A260" t="str">
             <v>L-2026-03-106</v>
           </cell>
-          <cell r="B260"/>
           <cell r="C260" t="str">
             <v>RPRO-260321-0028</v>
           </cell>
@@ -21257,7 +21348,6 @@
           <cell r="M260" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N260"/>
           <cell r="O260" t="str">
             <v>Lab test</v>
           </cell>
@@ -21290,7 +21380,6 @@
           <cell r="A261" t="str">
             <v>S-2026-03-107</v>
           </cell>
-          <cell r="B261"/>
           <cell r="C261" t="str">
             <v>RPRO-260321-0029</v>
           </cell>
@@ -21359,7 +21448,6 @@
           <cell r="A262" t="str">
             <v>S-2026-03-108</v>
           </cell>
-          <cell r="B262"/>
           <cell r="C262" t="str">
             <v>RPRO-260324-0285</v>
           </cell>
@@ -21428,7 +21516,6 @@
           <cell r="A263" t="str">
             <v>L-2026-03-109</v>
           </cell>
-          <cell r="B263"/>
           <cell r="C263" t="str">
             <v>RPRO-260324-0286</v>
           </cell>
@@ -21456,11 +21543,9 @@
           <cell r="K263">
             <v>0</v>
           </cell>
-          <cell r="L263"/>
           <cell r="M263" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N263"/>
           <cell r="O263" t="str">
             <v>Lab test</v>
           </cell>
@@ -21493,7 +21578,6 @@
           <cell r="A264" t="str">
             <v>S-2026-03-110</v>
           </cell>
-          <cell r="B264"/>
           <cell r="C264" t="str">
             <v>RPRO-260324-0287</v>
           </cell>
@@ -21562,7 +21646,6 @@
           <cell r="A265" t="str">
             <v>S-2026-03-111</v>
           </cell>
-          <cell r="B265"/>
           <cell r="C265" t="str">
             <v>RPRO-260324-0288</v>
           </cell>
@@ -21631,7 +21714,6 @@
           <cell r="A266" t="str">
             <v>S-2026-03-112</v>
           </cell>
-          <cell r="B266"/>
           <cell r="C266" t="str">
             <v>RPRO-260324-0289</v>
           </cell>
@@ -21700,7 +21782,6 @@
           <cell r="A267" t="str">
             <v>S-2026-03-113</v>
           </cell>
-          <cell r="B267"/>
           <cell r="C267" t="str">
             <v>RPRO-260324-0532</v>
           </cell>
@@ -21769,7 +21850,6 @@
           <cell r="A268" t="str">
             <v>S-2026-03-114</v>
           </cell>
-          <cell r="B268"/>
           <cell r="C268" t="str">
             <v>RPRO-260324-0533</v>
           </cell>
@@ -21838,7 +21918,6 @@
           <cell r="A269" t="str">
             <v>S-2026-03-115</v>
           </cell>
-          <cell r="B269"/>
           <cell r="C269" t="str">
             <v>RPRO-260324-0534</v>
           </cell>
@@ -21907,7 +21986,6 @@
           <cell r="A270" t="str">
             <v>S-2026-03-116</v>
           </cell>
-          <cell r="B270"/>
           <cell r="C270" t="str">
             <v>RPRO-260325-0407</v>
           </cell>
@@ -21976,7 +22054,6 @@
           <cell r="A271" t="str">
             <v>S-2026-03-117</v>
           </cell>
-          <cell r="B271"/>
           <cell r="C271" t="str">
             <v>RPRO-260325-0408</v>
           </cell>
@@ -22045,7 +22122,6 @@
           <cell r="A272" t="str">
             <v>S-2026-03-118</v>
           </cell>
-          <cell r="B272"/>
           <cell r="C272" t="str">
             <v>RPRO-260325-0409</v>
           </cell>
@@ -22114,7 +22190,6 @@
           <cell r="A273" t="str">
             <v>S-2026-03-119</v>
           </cell>
-          <cell r="B273"/>
           <cell r="C273" t="str">
             <v>RPRO-260325-0410</v>
           </cell>
@@ -22183,7 +22258,6 @@
           <cell r="A274" t="str">
             <v>S-2026-03-120</v>
           </cell>
-          <cell r="B274"/>
           <cell r="C274" t="str">
             <v>RPRO-260325-0411</v>
           </cell>
@@ -22252,7 +22326,6 @@
           <cell r="A275" t="str">
             <v>S-2026-03-121</v>
           </cell>
-          <cell r="B275"/>
           <cell r="C275" t="str">
             <v>RPRO-260325-0412</v>
           </cell>
@@ -22321,7 +22394,6 @@
           <cell r="A276" t="str">
             <v>S-2026-03-122</v>
           </cell>
-          <cell r="B276"/>
           <cell r="C276" t="str">
             <v>RPRO-260325-0413</v>
           </cell>
@@ -22390,7 +22462,6 @@
           <cell r="A277" t="str">
             <v>S-2026-03-123</v>
           </cell>
-          <cell r="B277"/>
           <cell r="C277" t="str">
             <v>RPRO-260325-0414</v>
           </cell>
@@ -22459,7 +22530,6 @@
           <cell r="A278" t="str">
             <v>S-2026-03-124</v>
           </cell>
-          <cell r="B278"/>
           <cell r="C278" t="str">
             <v>RPRO-260325-0415</v>
           </cell>
@@ -22599,7 +22669,6 @@
           <cell r="A280" t="str">
             <v>S-2026-03-126</v>
           </cell>
-          <cell r="B280"/>
           <cell r="C280" t="str">
             <v>RPRO-260325-0417</v>
           </cell>
@@ -22668,7 +22737,6 @@
           <cell r="A281" t="str">
             <v>S-2026-03-127</v>
           </cell>
-          <cell r="B281"/>
           <cell r="C281" t="str">
             <v>RPRO-260325-0418</v>
           </cell>
@@ -22737,7 +22805,6 @@
           <cell r="A282" t="str">
             <v>S-2026-03-128</v>
           </cell>
-          <cell r="B282"/>
           <cell r="C282" t="str">
             <v>RPRO-260325-0419</v>
           </cell>
@@ -22806,7 +22873,6 @@
           <cell r="A283" t="str">
             <v>S-2026-03-129</v>
           </cell>
-          <cell r="B283"/>
           <cell r="C283" t="str">
             <v>RPRO-260325-0421</v>
           </cell>
@@ -22875,7 +22941,6 @@
           <cell r="A284" t="str">
             <v>S-2026-03-130</v>
           </cell>
-          <cell r="B284"/>
           <cell r="C284" t="str">
             <v>RPRO-260327-0930</v>
           </cell>
@@ -23086,7 +23151,6 @@
           <cell r="A287" t="str">
             <v>S-2026-03-133</v>
           </cell>
-          <cell r="B287"/>
           <cell r="C287" t="str">
             <v>RPRO-260327-0933</v>
           </cell>
@@ -23155,7 +23219,6 @@
           <cell r="A288" t="str">
             <v>S-2026-03-134</v>
           </cell>
-          <cell r="B288"/>
           <cell r="C288" t="str">
             <v>RPRO-260327-0934</v>
           </cell>
@@ -23366,7 +23429,6 @@
           <cell r="A291" t="str">
             <v>S-2026-03-137</v>
           </cell>
-          <cell r="B291"/>
           <cell r="C291" t="str">
             <v>RPRO-260327-0937</v>
           </cell>
@@ -23506,7 +23568,6 @@
           <cell r="A293" t="str">
             <v>S-2026-03-139</v>
           </cell>
-          <cell r="B293"/>
           <cell r="C293" t="str">
             <v>RPRO-260327-0939</v>
           </cell>
@@ -23646,7 +23707,6 @@
           <cell r="A295" t="str">
             <v>S-2026-03-141</v>
           </cell>
-          <cell r="B295"/>
           <cell r="C295" t="str">
             <v>RPRO-260327-0941</v>
           </cell>
@@ -23715,7 +23775,6 @@
           <cell r="A296" t="str">
             <v>S-2026-03-142</v>
           </cell>
-          <cell r="B296"/>
           <cell r="C296" t="str">
             <v>RPRO-260401-0245</v>
           </cell>
@@ -23855,7 +23914,6 @@
           <cell r="A298" t="str">
             <v>S-2026-03-144</v>
           </cell>
-          <cell r="B298"/>
           <cell r="C298" t="str">
             <v>RPRO-260401-0247</v>
           </cell>
@@ -23924,7 +23982,6 @@
           <cell r="A299" t="str">
             <v>S-2026-03-145</v>
           </cell>
-          <cell r="B299"/>
           <cell r="C299" t="str">
             <v>RPRO-260401-0248</v>
           </cell>
@@ -23993,7 +24050,6 @@
           <cell r="A300" t="str">
             <v>S-2026-03-146</v>
           </cell>
-          <cell r="B300"/>
           <cell r="C300" t="str">
             <v>RPRO-260401-0249</v>
           </cell>
@@ -24062,7 +24118,6 @@
           <cell r="A301" t="str">
             <v>S-2026-04-01</v>
           </cell>
-          <cell r="B301"/>
           <cell r="C301" t="str">
             <v>RPRO-260401-0250</v>
           </cell>
@@ -24131,7 +24186,6 @@
           <cell r="A302" t="str">
             <v>S-2026-04-02</v>
           </cell>
-          <cell r="B302"/>
           <cell r="C302" t="str">
             <v>RPRO-260401-0251</v>
           </cell>
@@ -24200,7 +24254,6 @@
           <cell r="A303" t="str">
             <v>S-2026-04-03</v>
           </cell>
-          <cell r="B303"/>
           <cell r="C303" t="str">
             <v>RPRO-260402-0737</v>
           </cell>
@@ -24269,7 +24322,6 @@
           <cell r="A304" t="str">
             <v>S-2026-04-04</v>
           </cell>
-          <cell r="B304"/>
           <cell r="C304" t="str">
             <v>RPRO-260402-0738</v>
           </cell>
@@ -24338,7 +24390,6 @@
           <cell r="A305" t="str">
             <v>S-2026-04-05</v>
           </cell>
-          <cell r="B305"/>
           <cell r="C305" t="str">
             <v>RPRO-260403-0489</v>
           </cell>
@@ -24407,7 +24458,6 @@
           <cell r="A306" t="str">
             <v>S-2026-04-06</v>
           </cell>
-          <cell r="B306"/>
           <cell r="C306" t="str">
             <v>RPRO-260403-0490</v>
           </cell>
@@ -24476,7 +24526,6 @@
           <cell r="A307" t="str">
             <v>S-2026-04-07</v>
           </cell>
-          <cell r="B307"/>
           <cell r="C307" t="str">
             <v>RPRO-260403-0491</v>
           </cell>
@@ -24545,7 +24594,6 @@
           <cell r="A308" t="str">
             <v>S-2026-04-08</v>
           </cell>
-          <cell r="B308"/>
           <cell r="C308" t="str">
             <v>RPRO-260403-0492</v>
           </cell>
@@ -24614,7 +24662,6 @@
           <cell r="A309" t="str">
             <v>S-2026-04-09</v>
           </cell>
-          <cell r="B309"/>
           <cell r="C309" t="str">
             <v>RPRO-260406-1201</v>
           </cell>
@@ -24683,7 +24730,6 @@
           <cell r="A310" t="str">
             <v>S-2026-04-10</v>
           </cell>
-          <cell r="B310"/>
           <cell r="C310" t="str">
             <v>RPRO-260406-1202</v>
           </cell>
@@ -24752,7 +24798,6 @@
           <cell r="A311" t="str">
             <v>S-2026-04-11</v>
           </cell>
-          <cell r="B311"/>
           <cell r="C311" t="str">
             <v>RPRO-260406-1203</v>
           </cell>
@@ -24821,7 +24866,6 @@
           <cell r="A312" t="str">
             <v>S-2026-04-12</v>
           </cell>
-          <cell r="B312"/>
           <cell r="C312" t="str">
             <v>RPRO-260407-0417</v>
           </cell>
@@ -24890,7 +24934,6 @@
           <cell r="A313" t="str">
             <v>S-2026-04-13</v>
           </cell>
-          <cell r="B313"/>
           <cell r="C313" t="str">
             <v>RPRO-260407-0418</v>
           </cell>
@@ -24959,7 +25002,6 @@
           <cell r="A314" t="str">
             <v>S-2026-04-14</v>
           </cell>
-          <cell r="B314"/>
           <cell r="C314" t="str">
             <v>RPRO-260407-0419</v>
           </cell>
@@ -25028,7 +25070,6 @@
           <cell r="A315" t="str">
             <v>S-2026-04-15</v>
           </cell>
-          <cell r="B315"/>
           <cell r="C315" t="str">
             <v>RPRO-260407-0420</v>
           </cell>
@@ -25097,7 +25138,6 @@
           <cell r="A316" t="str">
             <v>S-2026-04-16</v>
           </cell>
-          <cell r="B316"/>
           <cell r="C316" t="str">
             <v>RPRO-260409-0346</v>
           </cell>
@@ -25166,7 +25206,6 @@
           <cell r="A317" t="str">
             <v>S-2026-04-17</v>
           </cell>
-          <cell r="B317"/>
           <cell r="C317" t="str">
             <v>RPRO-260409-0347</v>
           </cell>
@@ -25235,7 +25274,6 @@
           <cell r="A318" t="str">
             <v>S-2026-04-18</v>
           </cell>
-          <cell r="B318"/>
           <cell r="C318" t="str">
             <v>RPRO-260409-0348</v>
           </cell>
@@ -25304,7 +25342,6 @@
           <cell r="A319" t="str">
             <v>S-2026-04-19</v>
           </cell>
-          <cell r="B319"/>
           <cell r="C319" t="str">
             <v>RPRO-260409-0349</v>
           </cell>
@@ -25373,7 +25410,6 @@
           <cell r="A320" t="str">
             <v>S-2026-04-20</v>
           </cell>
-          <cell r="B320"/>
           <cell r="C320" t="str">
             <v>RPRO-260409-0350</v>
           </cell>
@@ -25442,7 +25478,6 @@
           <cell r="A321" t="str">
             <v>L-2026-04-21</v>
           </cell>
-          <cell r="B321"/>
           <cell r="C321" t="str">
             <v>RPRO-260410-0280</v>
           </cell>
@@ -25476,7 +25511,6 @@
           <cell r="M321" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N321"/>
           <cell r="O321" t="str">
             <v>Lab test</v>
           </cell>
@@ -25509,7 +25543,6 @@
           <cell r="A322" t="str">
             <v>L-2026-04-22</v>
           </cell>
-          <cell r="B322"/>
           <cell r="C322" t="str">
             <v>RPRO-260410-0281</v>
           </cell>
@@ -25543,7 +25576,6 @@
           <cell r="M322" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N322"/>
           <cell r="O322" t="str">
             <v>Lab test</v>
           </cell>
@@ -25576,7 +25608,6 @@
           <cell r="A323" t="str">
             <v>S-2026-04-23</v>
           </cell>
-          <cell r="B323"/>
           <cell r="C323" t="str">
             <v>RPRO-260410-0282</v>
           </cell>
@@ -25645,7 +25676,6 @@
           <cell r="A324" t="str">
             <v>S-2026-04-24</v>
           </cell>
-          <cell r="B324"/>
           <cell r="C324" t="str">
             <v>RPRO-260410-0283</v>
           </cell>
@@ -25714,7 +25744,6 @@
           <cell r="A325" t="str">
             <v>S-2026-04-25</v>
           </cell>
-          <cell r="B325"/>
           <cell r="C325" t="str">
             <v>RPRO-260410-0284</v>
           </cell>
@@ -25783,7 +25812,6 @@
           <cell r="A326" t="str">
             <v>S-2026-04-26</v>
           </cell>
-          <cell r="B326"/>
           <cell r="C326" t="str">
             <v>RPRO-260410-0285</v>
           </cell>
@@ -25852,7 +25880,6 @@
           <cell r="A327" t="str">
             <v>S-2026-04-27</v>
           </cell>
-          <cell r="B327"/>
           <cell r="C327" t="str">
             <v>RPRO-260410-0286</v>
           </cell>
@@ -25921,7 +25948,6 @@
           <cell r="A328" t="str">
             <v>S-2026-04-28</v>
           </cell>
-          <cell r="B328"/>
           <cell r="C328" t="str">
             <v>RPRO-260410-0287</v>
           </cell>
@@ -26061,7 +26087,6 @@
           <cell r="A330" t="str">
             <v>S-2026-04-30</v>
           </cell>
-          <cell r="B330"/>
           <cell r="C330" t="str">
             <v>RPRO-260414-0202</v>
           </cell>
@@ -26130,7 +26155,6 @@
           <cell r="A331" t="str">
             <v>S-2026-04-31</v>
           </cell>
-          <cell r="B331"/>
           <cell r="C331" t="str">
             <v>RPRO-260414-0203</v>
           </cell>
@@ -26199,7 +26223,6 @@
           <cell r="A332" t="str">
             <v>S-2026-04-32</v>
           </cell>
-          <cell r="B332"/>
           <cell r="C332" t="str">
             <v>RPRO-260414-0204</v>
           </cell>
@@ -26268,7 +26291,6 @@
           <cell r="A333" t="str">
             <v>S-2026-04-33</v>
           </cell>
-          <cell r="B333"/>
           <cell r="C333" t="str">
             <v>RPRO-260414-0205</v>
           </cell>
@@ -26337,7 +26359,6 @@
           <cell r="A334" t="str">
             <v>S-2026-04-34</v>
           </cell>
-          <cell r="B334"/>
           <cell r="C334" t="str">
             <v>RPRO-260414-0206</v>
           </cell>
@@ -26406,7 +26427,6 @@
           <cell r="A335" t="str">
             <v>S-2026-04-35</v>
           </cell>
-          <cell r="B335"/>
           <cell r="C335" t="str">
             <v>RPRO-260414-0207</v>
           </cell>
@@ -26475,7 +26495,6 @@
           <cell r="A336" t="str">
             <v>S-2026-04-36</v>
           </cell>
-          <cell r="B336"/>
           <cell r="C336" t="str">
             <v>RPRO-260414-0208</v>
           </cell>
@@ -26544,7 +26563,6 @@
           <cell r="A337" t="str">
             <v>S-2026-04-37</v>
           </cell>
-          <cell r="B337"/>
           <cell r="C337" t="str">
             <v>RPRO-260414-0209</v>
           </cell>
@@ -26613,7 +26631,6 @@
           <cell r="A338" t="str">
             <v>S-2026-04-38</v>
           </cell>
-          <cell r="B338"/>
           <cell r="C338" t="str">
             <v>RPRO-260414-0210</v>
           </cell>
@@ -26682,7 +26699,6 @@
           <cell r="A339" t="str">
             <v>S-2026-04-39</v>
           </cell>
-          <cell r="B339"/>
           <cell r="C339" t="str">
             <v>RPRO-260414-0211</v>
           </cell>
@@ -26751,7 +26767,6 @@
           <cell r="A340" t="str">
             <v>S-2026-04-40</v>
           </cell>
-          <cell r="B340"/>
           <cell r="C340" t="str">
             <v>RPRO-260414-0212</v>
           </cell>
@@ -26856,7 +26871,6 @@
           <cell r="M341" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N341"/>
           <cell r="O341" t="str">
             <v>Lab test</v>
           </cell>
@@ -26925,7 +26939,6 @@
           <cell r="M342" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N342"/>
           <cell r="O342" t="str">
             <v>Lab test</v>
           </cell>
@@ -26958,7 +26971,6 @@
           <cell r="A343" t="str">
             <v>S-2026-04-43</v>
           </cell>
-          <cell r="B343"/>
           <cell r="C343" t="str">
             <v>RPRO-260417-0243</v>
           </cell>
@@ -27027,7 +27039,6 @@
           <cell r="A344" t="str">
             <v>S-2026-04-44</v>
           </cell>
-          <cell r="B344"/>
           <cell r="C344" t="str">
             <v>RPRO-260417-0244</v>
           </cell>
@@ -27096,7 +27107,6 @@
           <cell r="A345" t="str">
             <v>S-2026-04-45</v>
           </cell>
-          <cell r="B345"/>
           <cell r="C345" t="str">
             <v>RPRO-260417-0245</v>
           </cell>
@@ -27165,7 +27175,6 @@
           <cell r="A346" t="str">
             <v>S-2026-04-46</v>
           </cell>
-          <cell r="B346"/>
           <cell r="C346" t="str">
             <v>RPRO-260417-0246</v>
           </cell>
@@ -27234,7 +27243,6 @@
           <cell r="A347" t="str">
             <v>S-2026-04-47</v>
           </cell>
-          <cell r="B347"/>
           <cell r="C347" t="str">
             <v>RPRO-260417-0247</v>
           </cell>
@@ -27303,7 +27311,6 @@
           <cell r="A348" t="str">
             <v>S-2026-04-48</v>
           </cell>
-          <cell r="B348"/>
           <cell r="C348" t="str">
             <v>RPRO-260421-0623</v>
           </cell>
@@ -27372,7 +27379,6 @@
           <cell r="A349" t="str">
             <v>S-2026-04-49</v>
           </cell>
-          <cell r="B349"/>
           <cell r="C349" t="str">
             <v>RPRO-260421-0624</v>
           </cell>
@@ -27441,7 +27447,6 @@
           <cell r="A350" t="str">
             <v>S-2026-04-50</v>
           </cell>
-          <cell r="B350"/>
           <cell r="C350" t="str">
             <v>RPRO-260421-0625</v>
           </cell>
@@ -27510,7 +27515,6 @@
           <cell r="A351" t="str">
             <v>S-2026-04-51</v>
           </cell>
-          <cell r="B351"/>
           <cell r="C351" t="str">
             <v>RPRO-260421-0626</v>
           </cell>
@@ -27579,7 +27583,6 @@
           <cell r="A352" t="str">
             <v>S-2026-04-52</v>
           </cell>
-          <cell r="B352"/>
           <cell r="C352" t="str">
             <v>RPRO-260421-0627</v>
           </cell>
@@ -27648,7 +27651,6 @@
           <cell r="A353" t="str">
             <v>S-2026-04-53</v>
           </cell>
-          <cell r="B353"/>
           <cell r="C353" t="str">
             <v>RPRO-260421-0628</v>
           </cell>
@@ -27717,7 +27719,6 @@
           <cell r="A354" t="str">
             <v>S-2026-04-54</v>
           </cell>
-          <cell r="B354"/>
           <cell r="C354" t="str">
             <v>RPRO-260421-0629</v>
           </cell>
@@ -27786,7 +27787,6 @@
           <cell r="A355" t="str">
             <v>S-2026-04-55</v>
           </cell>
-          <cell r="B355"/>
           <cell r="C355" t="str">
             <v>RPRO-260421-0630</v>
           </cell>
@@ -27855,7 +27855,6 @@
           <cell r="A356" t="str">
             <v>S-2026-04-56</v>
           </cell>
-          <cell r="B356"/>
           <cell r="C356" t="str">
             <v>RPRO-260421-0631</v>
           </cell>
@@ -27924,7 +27923,6 @@
           <cell r="A357" t="str">
             <v>S-2026-04-57</v>
           </cell>
-          <cell r="B357"/>
           <cell r="C357" t="str">
             <v>RPRO-260421-0632</v>
           </cell>
@@ -27993,7 +27991,6 @@
           <cell r="A358" t="str">
             <v>S-2026-04-58</v>
           </cell>
-          <cell r="B358"/>
           <cell r="C358" t="str">
             <v>RPRO-260421-0633</v>
           </cell>
@@ -28062,7 +28059,6 @@
           <cell r="A359" t="str">
             <v>S-2026-04-59</v>
           </cell>
-          <cell r="B359"/>
           <cell r="C359" t="str">
             <v>RPRO-260422-0268</v>
           </cell>
@@ -28131,7 +28127,6 @@
           <cell r="A360" t="str">
             <v>S-2026-04-60</v>
           </cell>
-          <cell r="B360"/>
           <cell r="C360" t="str">
             <v>RPRO-260423-0486</v>
           </cell>
@@ -28200,7 +28195,6 @@
           <cell r="A361" t="str">
             <v>S-2026-04-61</v>
           </cell>
-          <cell r="B361"/>
           <cell r="C361" t="str">
             <v>RPRO-260423-0487</v>
           </cell>
@@ -28269,7 +28263,6 @@
           <cell r="A362" t="str">
             <v>S-2026-04-62</v>
           </cell>
-          <cell r="B362"/>
           <cell r="C362" t="str">
             <v>RPRO-260424-1197</v>
           </cell>
@@ -28338,7 +28331,6 @@
           <cell r="A363" t="str">
             <v>S-2026-04-63</v>
           </cell>
-          <cell r="B363"/>
           <cell r="C363" t="str">
             <v>RPRO-260424-1198</v>
           </cell>
@@ -28407,7 +28399,6 @@
           <cell r="A364" t="str">
             <v>S-2026-04-64</v>
           </cell>
-          <cell r="B364"/>
           <cell r="C364" t="str">
             <v>RPRO-260424-1199</v>
           </cell>
@@ -28476,7 +28467,6 @@
           <cell r="A365" t="str">
             <v>S-2026-04-65</v>
           </cell>
-          <cell r="B365"/>
           <cell r="C365" t="str">
             <v>RPRO-260424-1200</v>
           </cell>
@@ -28545,7 +28535,6 @@
           <cell r="A366" t="str">
             <v>S-2026-04-66</v>
           </cell>
-          <cell r="B366"/>
           <cell r="C366" t="str">
             <v>RPRO-260424-1201</v>
           </cell>
@@ -28685,7 +28674,6 @@
           <cell r="A368" t="str">
             <v>S-2026-04-68</v>
           </cell>
-          <cell r="B368"/>
           <cell r="C368" t="str">
             <v>RPRO-260424-1203</v>
           </cell>
@@ -28754,7 +28742,6 @@
           <cell r="A369" t="str">
             <v>S-2026-04-69</v>
           </cell>
-          <cell r="B369"/>
           <cell r="C369" t="str">
             <v>RPRO-260424-1204</v>
           </cell>
@@ -28823,7 +28810,6 @@
           <cell r="A370" t="str">
             <v>S-2026-04-70</v>
           </cell>
-          <cell r="B370"/>
           <cell r="C370" t="str">
             <v>RPRO-260424-1205</v>
           </cell>
@@ -28892,7 +28878,6 @@
           <cell r="A371" t="str">
             <v>S-2026-04-71</v>
           </cell>
-          <cell r="B371"/>
           <cell r="C371" t="str">
             <v>RPRO-260424-1206</v>
           </cell>
@@ -28961,7 +28946,6 @@
           <cell r="A372" t="str">
             <v>S-2026-04-72</v>
           </cell>
-          <cell r="B372"/>
           <cell r="C372" t="str">
             <v>RPRO-260428-0920</v>
           </cell>
@@ -29030,7 +29014,6 @@
           <cell r="A373" t="str">
             <v>S-2026-04-73</v>
           </cell>
-          <cell r="B373"/>
           <cell r="C373" t="str">
             <v>RPRO-260429-0109</v>
           </cell>
@@ -29099,7 +29082,6 @@
           <cell r="A374" t="str">
             <v>S-2026-04-74</v>
           </cell>
-          <cell r="B374"/>
           <cell r="C374" t="str">
             <v>RPRO-260429-0110</v>
           </cell>
@@ -29168,7 +29150,6 @@
           <cell r="A375" t="str">
             <v>S-2026-04-75</v>
           </cell>
-          <cell r="B375"/>
           <cell r="C375" t="str">
             <v>RPRO-260429-0126</v>
           </cell>
@@ -29237,7 +29218,6 @@
           <cell r="A376" t="str">
             <v>S-2026-04-76</v>
           </cell>
-          <cell r="B376"/>
           <cell r="C376" t="str">
             <v>RPRO-260429-0127</v>
           </cell>
@@ -29306,7 +29286,6 @@
           <cell r="A377" t="str">
             <v>S-2026-05-01</v>
           </cell>
-          <cell r="B377"/>
           <cell r="C377" t="str">
             <v>RPRO-260505-0654</v>
           </cell>
@@ -29446,7 +29425,6 @@
           <cell r="A379" t="str">
             <v>S-2026-05-03</v>
           </cell>
-          <cell r="B379"/>
           <cell r="C379" t="str">
             <v>RPRO-260505-0656</v>
           </cell>
@@ -29515,7 +29493,6 @@
           <cell r="A380" t="str">
             <v>S-2026-05-04</v>
           </cell>
-          <cell r="B380"/>
           <cell r="C380" t="str">
             <v>RPRO-260505-0657</v>
           </cell>
@@ -29584,7 +29561,6 @@
           <cell r="A381" t="str">
             <v>S-2026-05-05</v>
           </cell>
-          <cell r="B381"/>
           <cell r="C381" t="str">
             <v>RPRO-260505-0658</v>
           </cell>
@@ -29653,7 +29629,6 @@
           <cell r="A382" t="str">
             <v>S-2026-05-06</v>
           </cell>
-          <cell r="B382"/>
           <cell r="C382" t="str">
             <v>RPRO-260505-0659</v>
           </cell>
@@ -29722,7 +29697,6 @@
           <cell r="A383" t="str">
             <v>S-2026-05-07</v>
           </cell>
-          <cell r="B383"/>
           <cell r="C383" t="str">
             <v>RPRO-260505-0660</v>
           </cell>
@@ -29862,7 +29836,6 @@
           <cell r="A385" t="str">
             <v>S-2026-05-09</v>
           </cell>
-          <cell r="B385"/>
           <cell r="C385" t="str">
             <v>RPRO-260505-0662</v>
           </cell>
@@ -29931,7 +29904,6 @@
           <cell r="A386" t="str">
             <v>S-2026-05-10</v>
           </cell>
-          <cell r="B386"/>
           <cell r="C386" t="str">
             <v>RPRO-260505-0663</v>
           </cell>
@@ -30071,7 +30043,6 @@
           <cell r="A388" t="str">
             <v>S-2026-05-12</v>
           </cell>
-          <cell r="B388"/>
           <cell r="C388" t="str">
             <v>RPRO-260505-0802</v>
           </cell>
@@ -30140,7 +30111,6 @@
           <cell r="A389" t="str">
             <v>S-2026-05-13</v>
           </cell>
-          <cell r="B389"/>
           <cell r="C389" t="str">
             <v>RPRO-260505-0803</v>
           </cell>
@@ -30209,7 +30179,6 @@
           <cell r="A390" t="str">
             <v>S-2026-05-14</v>
           </cell>
-          <cell r="B390"/>
           <cell r="C390" t="str">
             <v>RPRO-260506-0394</v>
           </cell>
@@ -30278,7 +30247,6 @@
           <cell r="A391" t="str">
             <v>S-2026-05-15</v>
           </cell>
-          <cell r="B391"/>
           <cell r="C391" t="str">
             <v>RPRO-260506-0395</v>
           </cell>
@@ -30347,7 +30315,6 @@
           <cell r="A392" t="str">
             <v>S-2026-05-16</v>
           </cell>
-          <cell r="B392"/>
           <cell r="C392" t="str">
             <v>RPRO-260506-0396</v>
           </cell>
@@ -30416,7 +30383,6 @@
           <cell r="A393" t="str">
             <v>S-2026-05-17</v>
           </cell>
-          <cell r="B393"/>
           <cell r="C393" t="str">
             <v>RPRO-260506-0397</v>
           </cell>
@@ -30485,7 +30451,6 @@
           <cell r="A394" t="str">
             <v>S-2026-05-18</v>
           </cell>
-          <cell r="B394"/>
           <cell r="C394" t="str">
             <v>RPRO-260506-0415</v>
           </cell>
@@ -30554,7 +30519,6 @@
           <cell r="A395" t="str">
             <v>S-2026-05-19</v>
           </cell>
-          <cell r="B395"/>
           <cell r="C395" t="str">
             <v>RPRO-260508-0581</v>
           </cell>
@@ -30623,7 +30587,6 @@
           <cell r="A396" t="str">
             <v>S-2026-05-20</v>
           </cell>
-          <cell r="B396"/>
           <cell r="C396" t="str">
             <v>RPRO-260508-0582</v>
           </cell>
@@ -30692,7 +30655,6 @@
           <cell r="A397" t="str">
             <v>S-2026-05-21</v>
           </cell>
-          <cell r="B397"/>
           <cell r="C397" t="str">
             <v>RPRO-260508-0583</v>
           </cell>
@@ -30761,7 +30723,6 @@
           <cell r="A398" t="str">
             <v>S-2026-05-22</v>
           </cell>
-          <cell r="B398"/>
           <cell r="C398" t="str">
             <v>RPRO-260508-0584</v>
           </cell>
@@ -30830,7 +30791,6 @@
           <cell r="A399" t="str">
             <v>S-2026-05-23</v>
           </cell>
-          <cell r="B399"/>
           <cell r="C399" t="str">
             <v>RPRO-260508-0585</v>
           </cell>
@@ -30899,7 +30859,6 @@
           <cell r="A400" t="str">
             <v>S-2026-05-24</v>
           </cell>
-          <cell r="B400"/>
           <cell r="C400" t="str">
             <v>RPRO-260508-0586</v>
           </cell>
@@ -30968,7 +30927,6 @@
           <cell r="A401" t="str">
             <v>S-2026-05-25</v>
           </cell>
-          <cell r="B401"/>
           <cell r="C401" t="str">
             <v>RPRO-260508-0587</v>
           </cell>
@@ -31037,7 +30995,6 @@
           <cell r="A402" t="str">
             <v>S-2026-05-26</v>
           </cell>
-          <cell r="B402"/>
           <cell r="C402" t="str">
             <v>RPRO-260508-0588</v>
           </cell>
@@ -31106,7 +31063,6 @@
           <cell r="A403" t="str">
             <v>S-2026-05-27</v>
           </cell>
-          <cell r="B403"/>
           <cell r="C403" t="str">
             <v>RPRO-260512-0580</v>
           </cell>
@@ -31137,7 +31093,6 @@
           <cell r="L403" t="str">
             <v>TBS</v>
           </cell>
-          <cell r="M403"/>
           <cell r="N403" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -31173,7 +31128,6 @@
           <cell r="A404" t="str">
             <v>S-2026-05-28</v>
           </cell>
-          <cell r="B404"/>
           <cell r="C404" t="str">
             <v>RPRO-260512-0581</v>
           </cell>
@@ -31204,7 +31158,6 @@
           <cell r="L404" t="str">
             <v>TBS</v>
           </cell>
-          <cell r="M404"/>
           <cell r="N404" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -31240,7 +31193,6 @@
           <cell r="A405" t="str">
             <v>S-2026-05-29</v>
           </cell>
-          <cell r="B405"/>
           <cell r="C405" t="str">
             <v>RPRO-260512-0582</v>
           </cell>
@@ -31309,7 +31261,6 @@
           <cell r="A406" t="str">
             <v>S-2026-05-30</v>
           </cell>
-          <cell r="B406"/>
           <cell r="C406" t="str">
             <v>RPRO-260512-0583</v>
           </cell>
@@ -31378,7 +31329,6 @@
           <cell r="A407" t="str">
             <v>S-2026-05-31</v>
           </cell>
-          <cell r="B407"/>
           <cell r="C407" t="str">
             <v>RPRO-260513-0945</v>
           </cell>
@@ -31447,7 +31397,6 @@
           <cell r="A408" t="str">
             <v>S-2026-05-32</v>
           </cell>
-          <cell r="B408"/>
           <cell r="C408" t="str">
             <v>RPRO-260513-0946</v>
           </cell>
@@ -31516,7 +31465,6 @@
           <cell r="A409" t="str">
             <v>S-2026-05-33</v>
           </cell>
-          <cell r="B409"/>
           <cell r="C409" t="str">
             <v>RPRO-260513-0947</v>
           </cell>
@@ -31585,7 +31533,6 @@
           <cell r="A410" t="str">
             <v>S-2026-05-34</v>
           </cell>
-          <cell r="B410"/>
           <cell r="C410" t="str">
             <v>RPRO-260513-0948</v>
           </cell>
@@ -31725,7 +31672,6 @@
           <cell r="A412" t="str">
             <v>S-2026-05-36</v>
           </cell>
-          <cell r="B412"/>
           <cell r="C412" t="str">
             <v>RPRO-260513-0950</v>
           </cell>
@@ -31794,7 +31740,6 @@
           <cell r="A413" t="str">
             <v>S-2026-05-37</v>
           </cell>
-          <cell r="B413"/>
           <cell r="C413" t="str">
             <v>RPRO-260515-0272</v>
           </cell>
@@ -31863,7 +31808,6 @@
           <cell r="A414" t="str">
             <v>S-2026-05-38</v>
           </cell>
-          <cell r="B414"/>
           <cell r="C414" t="str">
             <v>RPRO-260515-0273</v>
           </cell>
@@ -31932,7 +31876,6 @@
           <cell r="A415" t="str">
             <v>S-2026-05-39</v>
           </cell>
-          <cell r="B415"/>
           <cell r="C415" t="str">
             <v>RPRO-260515-0274</v>
           </cell>
@@ -32001,7 +31944,6 @@
           <cell r="A416" t="str">
             <v>S-2026-05-40</v>
           </cell>
-          <cell r="B416"/>
           <cell r="C416" t="str">
             <v>RPRO-260515-0275</v>
           </cell>
@@ -32070,7 +32012,6 @@
           <cell r="A417" t="str">
             <v>S-2026-05-41</v>
           </cell>
-          <cell r="B417"/>
           <cell r="C417" t="str">
             <v>RPRO-260515-0276</v>
           </cell>
@@ -32139,7 +32080,6 @@
           <cell r="A418" t="str">
             <v>S-2026-05-42</v>
           </cell>
-          <cell r="B418"/>
           <cell r="C418" t="str">
             <v>RPRO-260515-0277</v>
           </cell>
@@ -32208,7 +32148,6 @@
           <cell r="A419" t="str">
             <v>S-2026-05-43</v>
           </cell>
-          <cell r="B419"/>
           <cell r="C419" t="str">
             <v>RPRO-260515-0278</v>
           </cell>
@@ -32277,7 +32216,6 @@
           <cell r="A420" t="str">
             <v>S-2026-05-44</v>
           </cell>
-          <cell r="B420"/>
           <cell r="C420" t="str">
             <v>RPRO-260515-0279</v>
           </cell>
@@ -32346,7 +32284,6 @@
           <cell r="A421" t="str">
             <v>S-2026-05-45</v>
           </cell>
-          <cell r="B421"/>
           <cell r="C421" t="str">
             <v>RPRO-260515-0280</v>
           </cell>
@@ -32415,7 +32352,6 @@
           <cell r="A422" t="str">
             <v>S-2026-05-46</v>
           </cell>
-          <cell r="B422"/>
           <cell r="C422" t="str">
             <v>RPRO-260518-0853</v>
           </cell>
@@ -32484,7 +32420,6 @@
           <cell r="A423" t="str">
             <v>S-2026-05-47</v>
           </cell>
-          <cell r="B423"/>
           <cell r="C423" t="str">
             <v>RPRO-260518-0854</v>
           </cell>
@@ -32553,7 +32488,6 @@
           <cell r="A424" t="str">
             <v>S-2026-05-48</v>
           </cell>
-          <cell r="B424"/>
           <cell r="C424" t="str">
             <v>RPRO-260518-0855</v>
           </cell>
@@ -32622,7 +32556,6 @@
           <cell r="A425" t="str">
             <v>S-2026-05-49</v>
           </cell>
-          <cell r="B425"/>
           <cell r="C425" t="str">
             <v>RPRO-260518-0856</v>
           </cell>
@@ -32904,7 +32837,6 @@
           <cell r="A429" t="str">
             <v>S-2026-05-53</v>
           </cell>
-          <cell r="B429"/>
           <cell r="C429" t="str">
             <v>RPRO-260518-0860</v>
           </cell>
@@ -32973,7 +32905,6 @@
           <cell r="A430" t="str">
             <v>S-2026-05-54</v>
           </cell>
-          <cell r="B430"/>
           <cell r="C430" t="str">
             <v>RPRO-260518-0861</v>
           </cell>
@@ -33042,7 +32973,6 @@
           <cell r="A431" t="str">
             <v>S-2026-05-55</v>
           </cell>
-          <cell r="B431"/>
           <cell r="C431" t="str">
             <v>RPRO-260518-0862</v>
           </cell>
@@ -33111,7 +33041,6 @@
           <cell r="A432" t="str">
             <v>S-2026-05-56</v>
           </cell>
-          <cell r="B432"/>
           <cell r="C432" t="str">
             <v>RPRO-260518-0863</v>
           </cell>
@@ -33180,7 +33109,6 @@
           <cell r="A433" t="str">
             <v>S-2026-05-57</v>
           </cell>
-          <cell r="B433"/>
           <cell r="C433" t="str">
             <v>RPRO-260518-0864</v>
           </cell>
@@ -33249,7 +33177,6 @@
           <cell r="A434" t="str">
             <v>S-2026-05-58</v>
           </cell>
-          <cell r="B434"/>
           <cell r="C434" t="str">
             <v>RPRO-260518-0865</v>
           </cell>
@@ -33318,7 +33245,6 @@
           <cell r="A435" t="str">
             <v>S-2026-05-59</v>
           </cell>
-          <cell r="B435"/>
           <cell r="C435" t="str">
             <v>RPRO-260518-0866</v>
           </cell>
@@ -33387,7 +33313,6 @@
           <cell r="A436" t="str">
             <v>S-2026-05-60</v>
           </cell>
-          <cell r="B436"/>
           <cell r="C436" t="str">
             <v>RPRO-260520-0192</v>
           </cell>
@@ -33456,7 +33381,6 @@
           <cell r="A437" t="str">
             <v>S-2026-05-61</v>
           </cell>
-          <cell r="B437"/>
           <cell r="C437" t="str">
             <v>RPRO-260520-0193</v>
           </cell>
@@ -33525,7 +33449,6 @@
           <cell r="A438" t="str">
             <v>S-2026-05-62</v>
           </cell>
-          <cell r="B438"/>
           <cell r="C438" t="str">
             <v>RPRO-260520-0194</v>
           </cell>
@@ -33594,7 +33517,6 @@
           <cell r="A439" t="str">
             <v>S-2026-05-63</v>
           </cell>
-          <cell r="B439"/>
           <cell r="C439" t="str">
             <v>RPRO-260520-0195</v>
           </cell>
@@ -33663,7 +33585,6 @@
           <cell r="A440" t="str">
             <v>S-2026-05-64</v>
           </cell>
-          <cell r="B440"/>
           <cell r="C440" t="str">
             <v>RPRO-260520-0196</v>
           </cell>
@@ -33732,7 +33653,6 @@
           <cell r="A441" t="str">
             <v>S-2026-05-65</v>
           </cell>
-          <cell r="B441"/>
           <cell r="C441" t="str">
             <v>RPRO-260520-0197</v>
           </cell>
@@ -33801,7 +33721,6 @@
           <cell r="A442" t="str">
             <v>S-2026-05-66</v>
           </cell>
-          <cell r="B442"/>
           <cell r="C442" t="str">
             <v>RPRO-260520-0225</v>
           </cell>
@@ -33870,7 +33789,6 @@
           <cell r="A443" t="str">
             <v>S-2026-05-67</v>
           </cell>
-          <cell r="B443"/>
           <cell r="C443" t="str">
             <v>RPRO-260520-0226</v>
           </cell>
@@ -33939,7 +33857,6 @@
           <cell r="A444" t="str">
             <v>S-2026-05-68</v>
           </cell>
-          <cell r="B444"/>
           <cell r="C444" t="str">
             <v>RPRO-260520-0227</v>
           </cell>
@@ -34008,7 +33925,6 @@
           <cell r="A445" t="str">
             <v>S-2026-05-69</v>
           </cell>
-          <cell r="B445"/>
           <cell r="C445" t="str">
             <v>RPRO-260520-0228</v>
           </cell>
@@ -34077,7 +33993,6 @@
           <cell r="A446" t="str">
             <v>S-2026-05-70</v>
           </cell>
-          <cell r="B446"/>
           <cell r="C446" t="str">
             <v>RPRO-260520-0229</v>
           </cell>
@@ -34146,7 +34061,6 @@
           <cell r="A447" t="str">
             <v>S-2026-05-71</v>
           </cell>
-          <cell r="B447"/>
           <cell r="C447" t="str">
             <v>RPRO-260521-0669</v>
           </cell>
@@ -34215,7 +34129,6 @@
           <cell r="A448" t="str">
             <v>S-2026-05-72</v>
           </cell>
-          <cell r="B448"/>
           <cell r="C448" t="str">
             <v>RPRO-260521-0670</v>
           </cell>
@@ -34284,7 +34197,6 @@
           <cell r="A449" t="str">
             <v>S-2026-05-73</v>
           </cell>
-          <cell r="B449"/>
           <cell r="C449" t="str">
             <v>RPRO-260523-0221</v>
           </cell>
@@ -34353,7 +34265,6 @@
           <cell r="A450" t="str">
             <v>S-2026-05-74</v>
           </cell>
-          <cell r="B450"/>
           <cell r="C450" t="str">
             <v>RPRO-260523-0222</v>
           </cell>
@@ -34422,7 +34333,6 @@
           <cell r="A451" t="str">
             <v>S-2026-05-75</v>
           </cell>
-          <cell r="B451"/>
           <cell r="C451" t="str">
             <v>RPRO-260523-0223</v>
           </cell>
@@ -34491,7 +34401,6 @@
           <cell r="A452" t="str">
             <v>S-2026-05-76</v>
           </cell>
-          <cell r="B452"/>
           <cell r="C452" t="str">
             <v>RPRO-260526-0394</v>
           </cell>
@@ -34560,7 +34469,6 @@
           <cell r="A453" t="str">
             <v>S-2026-05-77</v>
           </cell>
-          <cell r="B453"/>
           <cell r="C453" t="str">
             <v>RPRO-260526-0395</v>
           </cell>
@@ -34629,7 +34537,6 @@
           <cell r="A454" t="str">
             <v>S-2026-05-78</v>
           </cell>
-          <cell r="B454"/>
           <cell r="C454" t="str">
             <v>RPRO-260526-0396</v>
           </cell>
@@ -34698,7 +34605,6 @@
           <cell r="A455" t="str">
             <v>S-2026-05-79</v>
           </cell>
-          <cell r="B455"/>
           <cell r="C455" t="str">
             <v>RPRO-260526-0397</v>
           </cell>
@@ -34767,7 +34673,6 @@
           <cell r="A456" t="str">
             <v>S-2026-05-80</v>
           </cell>
-          <cell r="B456"/>
           <cell r="C456" t="str">
             <v>RPRO-260526-0398</v>
           </cell>
@@ -34836,7 +34741,6 @@
           <cell r="A457" t="str">
             <v>S-2026-05-81</v>
           </cell>
-          <cell r="B457"/>
           <cell r="C457" t="str">
             <v>RPRO-260526-0399</v>
           </cell>
@@ -34905,7 +34809,9 @@
           <cell r="A458" t="str">
             <v>S-2026-05-82</v>
           </cell>
-          <cell r="B458"/>
+          <cell r="B458" t="str">
+            <v>xin dời ETD 2-Jun-&gt; 6-Jun</v>
+          </cell>
           <cell r="C458" t="str">
             <v>RPRO-260526-0400</v>
           </cell>
@@ -34974,7 +34880,6 @@
           <cell r="A459" t="str">
             <v>S-2026-05-83</v>
           </cell>
-          <cell r="B459"/>
           <cell r="C459" t="str">
             <v>RPRO-260526-0401</v>
           </cell>
@@ -35046,7 +34951,6 @@
           <cell r="B460" t="str">
             <v>ƯU TIÊN GIAO 06-JUN KHI CÓ LIỆU</v>
           </cell>
-          <cell r="C460"/>
           <cell r="D460" t="str">
             <v>PUR2605250002S</v>
           </cell>
@@ -35112,7 +35016,6 @@
           <cell r="A461" t="str">
             <v>S-2026-05-85</v>
           </cell>
-          <cell r="B461"/>
           <cell r="C461" t="str">
             <v>RPRO-260526-0402</v>
           </cell>
@@ -35181,9 +35084,6 @@
           <cell r="A462" t="str">
             <v>S-2026-05-86</v>
           </cell>
-          <cell r="B462" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C462" t="str">
             <v>RPRO-260527-0578</v>
           </cell>
@@ -35252,9 +35152,6 @@
           <cell r="A463" t="str">
             <v>S-2026-05-87</v>
           </cell>
-          <cell r="B463" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C463" t="str">
             <v>RPRO-260527-0579</v>
           </cell>
@@ -35323,9 +35220,6 @@
           <cell r="A464" t="str">
             <v>S-2026-05-88</v>
           </cell>
-          <cell r="B464" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C464" t="str">
             <v>RPRO-260527-0580</v>
           </cell>
@@ -35394,9 +35288,6 @@
           <cell r="A465" t="str">
             <v>S-2026-05-89</v>
           </cell>
-          <cell r="B465" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C465" t="str">
             <v>RPRO-260527-0581</v>
           </cell>
@@ -35419,10 +35310,10 @@
             <v>50</v>
           </cell>
           <cell r="J465">
+            <v>50</v>
+          </cell>
+          <cell r="K465">
             <v>0</v>
-          </cell>
-          <cell r="K465">
-            <v>50</v>
           </cell>
           <cell r="L465" t="str">
             <v>NIKE</v>
@@ -35465,9 +35356,6 @@
           <cell r="A466" t="str">
             <v>S-2026-05-90</v>
           </cell>
-          <cell r="B466" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C466" t="str">
             <v>RPRO-260527-0582</v>
           </cell>
@@ -35536,9 +35424,6 @@
           <cell r="A467" t="str">
             <v>S-2026-05-91</v>
           </cell>
-          <cell r="B467" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C467" t="str">
             <v>RPRO-260527-0583</v>
           </cell>
@@ -35561,10 +35446,10 @@
             <v>70</v>
           </cell>
           <cell r="J467">
+            <v>70</v>
+          </cell>
+          <cell r="K467">
             <v>0</v>
-          </cell>
-          <cell r="K467">
-            <v>70</v>
           </cell>
           <cell r="L467" t="str">
             <v>NIKE</v>
@@ -35607,7 +35492,6 @@
           <cell r="A468" t="str">
             <v>S-2026-05-92</v>
           </cell>
-          <cell r="B468"/>
           <cell r="C468" t="str">
             <v>RPRO-260528-0001</v>
           </cell>
@@ -35676,9 +35560,6 @@
           <cell r="A469" t="str">
             <v>S-2026-05-93</v>
           </cell>
-          <cell r="B469" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C469" t="str">
             <v>RPRO-260529-0339</v>
           </cell>
@@ -35747,9 +35628,6 @@
           <cell r="A470" t="str">
             <v>S-2026-05-94</v>
           </cell>
-          <cell r="B470" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C470" t="str">
             <v>RPRO-260529-0340</v>
           </cell>
@@ -35818,9 +35696,6 @@
           <cell r="A471" t="str">
             <v>S-2026-05-95</v>
           </cell>
-          <cell r="B471" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C471" t="str">
             <v>RPRO-260529-0341</v>
           </cell>
@@ -35890,7 +35765,7 @@
             <v>S-2026-05-96</v>
           </cell>
           <cell r="B472" t="str">
-            <v>CHUA RL</v>
+            <v>có kq lab sớm nên dời ETD 5/Jun-&gt;3/Jun giao hàng</v>
           </cell>
           <cell r="C472" t="str">
             <v>RPRO-260529-0342</v>
@@ -35914,10 +35789,10 @@
             <v>20</v>
           </cell>
           <cell r="J472">
+            <v>20</v>
+          </cell>
+          <cell r="K472">
             <v>0</v>
-          </cell>
-          <cell r="K472">
-            <v>20</v>
           </cell>
           <cell r="L472" t="str">
             <v>FOOTJOY</v>
@@ -35961,7 +35836,7 @@
             <v>S-2026-05-97</v>
           </cell>
           <cell r="B473" t="str">
-            <v>CHUA RL</v>
+            <v>có kq lab sớm nên dời ETD 5/Jun-&gt;3/Jun giao hàng</v>
           </cell>
           <cell r="C473" t="str">
             <v>RPRO-260529-0343</v>
@@ -35985,10 +35860,10 @@
             <v>20</v>
           </cell>
           <cell r="J473">
+            <v>20</v>
+          </cell>
+          <cell r="K473">
             <v>0</v>
-          </cell>
-          <cell r="K473">
-            <v>20</v>
           </cell>
           <cell r="L473" t="str">
             <v>FOOTJOY</v>
@@ -36031,9 +35906,6 @@
           <cell r="A474" t="str">
             <v>S-2026-05-98</v>
           </cell>
-          <cell r="B474" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C474" t="str">
             <v>RPRO-260529-0344</v>
           </cell>
@@ -36102,9 +35974,6 @@
           <cell r="A475" t="str">
             <v>S-2026-05-99</v>
           </cell>
-          <cell r="B475" t="str">
-            <v>CHUA RL</v>
-          </cell>
           <cell r="C475" t="str">
             <v>RPRO-260529-0345</v>
           </cell>
@@ -36174,7 +36043,7 @@
             <v>S-2026-05-100</v>
           </cell>
           <cell r="B476" t="str">
-            <v>CHUA RL</v>
+            <v>có kq lab sớm nên dời ETD 4/Jun-&gt;3/Jun giao hàng</v>
           </cell>
           <cell r="C476" t="str">
             <v>RPRO-260529-0346</v>
@@ -36198,10 +36067,10 @@
             <v>10</v>
           </cell>
           <cell r="J476">
+            <v>10</v>
+          </cell>
+          <cell r="K476">
             <v>0</v>
-          </cell>
-          <cell r="K476">
-            <v>10</v>
           </cell>
           <cell r="L476" t="str">
             <v>FOOTJOY</v>
@@ -36244,9 +36113,6 @@
           <cell r="A477" t="str">
             <v>S-2026-05-102</v>
           </cell>
-          <cell r="B477" t="str">
-            <v>chờ tạo bom</v>
-          </cell>
           <cell r="C477" t="str">
             <v>RPRO-260601-0847</v>
           </cell>
@@ -36315,7 +36181,6 @@
           <cell r="A478" t="str">
             <v>S-2026-05-103</v>
           </cell>
-          <cell r="B478"/>
           <cell r="C478" t="str">
             <v>RPRO-260601-0848</v>
           </cell>
@@ -36384,7 +36249,6 @@
           <cell r="A479" t="str">
             <v>S-2026-05-104</v>
           </cell>
-          <cell r="B479"/>
           <cell r="C479" t="str">
             <v>RPRO-260601-0849</v>
           </cell>
@@ -36453,7 +36317,6 @@
           <cell r="A480" t="str">
             <v>S-2026-05-105</v>
           </cell>
-          <cell r="B480"/>
           <cell r="C480" t="str">
             <v>RPRO-260601-0850</v>
           </cell>
@@ -36522,7 +36385,6 @@
           <cell r="A481" t="str">
             <v>S-2026-05-106</v>
           </cell>
-          <cell r="B481"/>
           <cell r="C481" t="str">
             <v>RPRO-260601-0851</v>
           </cell>
@@ -36591,9 +36453,6 @@
           <cell r="A482" t="str">
             <v>S-2026-06-01</v>
           </cell>
-          <cell r="B482" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C482" t="str">
             <v>RPRO-260602-0720</v>
           </cell>
@@ -36663,9 +36522,6 @@
           <cell r="A483" t="str">
             <v>S-2026-06-02</v>
           </cell>
-          <cell r="B483" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C483" t="str">
             <v>RPRO-260602-0721</v>
           </cell>
@@ -36734,9 +36590,6 @@
           <cell r="A484" t="str">
             <v>S-2026-06-03</v>
           </cell>
-          <cell r="B484" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C484" t="str">
             <v>RPRO-260602-0722</v>
           </cell>
@@ -36805,9 +36658,6 @@
           <cell r="A485" t="str">
             <v>S-2026-06-04</v>
           </cell>
-          <cell r="B485" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C485" t="str">
             <v>RPRO-260602-0723</v>
           </cell>
@@ -36876,9 +36726,6 @@
           <cell r="A486" t="str">
             <v>S-2026-06-05</v>
           </cell>
-          <cell r="B486" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C486" t="str">
             <v>RPRO-260602-0724</v>
           </cell>
@@ -36947,9 +36794,6 @@
           <cell r="A487" t="str">
             <v>S-2026-06-06</v>
           </cell>
-          <cell r="B487" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C487" t="str">
             <v>RPRO-260602-0725</v>
           </cell>
@@ -37018,9 +36862,6 @@
           <cell r="A488" t="str">
             <v>S-2026-06-07</v>
           </cell>
-          <cell r="B488" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C488" t="str">
             <v>RPRO-260602-0726</v>
           </cell>
@@ -37089,9 +36930,6 @@
           <cell r="A489" t="str">
             <v>S-2026-06-08</v>
           </cell>
-          <cell r="B489" t="str">
-            <v>chua rl</v>
-          </cell>
           <cell r="C489" t="str">
             <v>RPRO-260602-0727</v>
           </cell>
@@ -37157,14 +36995,20 @@
           </cell>
         </row>
         <row r="490">
-          <cell r="A490"/>
+          <cell r="A490" t="str">
+            <v>S-2026-06-09</v>
+          </cell>
           <cell r="B490" t="str">
-            <v>chua rl</v>
-          </cell>
-          <cell r="C490"/>
-          <cell r="D490"/>
+            <v>gấp</v>
+          </cell>
+          <cell r="C490" t="str">
+            <v>RPRO-260603-0481</v>
+          </cell>
+          <cell r="D490" t="str">
+            <v xml:space="preserve">PUR-202606020004S </v>
+          </cell>
           <cell r="E490" t="str">
-            <v/>
+            <v>BDB-000347</v>
           </cell>
           <cell r="F490" t="str">
             <v>PVN-004436</v>
@@ -37214,194 +37058,420 @@
           <cell r="U490" t="str">
             <v/>
           </cell>
-          <cell r="V490" t="e">
-            <v>#N/A</v>
-          </cell>
-          <cell r="W490" t="str">
-            <v/>
+          <cell r="V490">
+            <v>3.5709999999999999E-2</v>
+          </cell>
+          <cell r="W490">
+            <v>1</v>
           </cell>
         </row>
         <row r="491">
-          <cell r="A491"/>
-          <cell r="B491"/>
-          <cell r="C491"/>
-          <cell r="D491"/>
+          <cell r="A491" t="str">
+            <v>S-2026-06-10</v>
+          </cell>
+          <cell r="B491" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C491" t="str">
+            <v>RPRO-260603-0482</v>
+          </cell>
+          <cell r="D491" t="str">
+            <v xml:space="preserve"> PUR2606020005S   </v>
+          </cell>
           <cell r="E491" t="str">
-            <v/>
-          </cell>
-          <cell r="F491"/>
-          <cell r="G491"/>
-          <cell r="H491"/>
-          <cell r="I491"/>
+            <v>BDB-000348</v>
+          </cell>
+          <cell r="F491" t="str">
+            <v>PVN-004195</v>
+          </cell>
+          <cell r="G491" t="str">
+            <v>OrthoLite IMPERIAL SEEDPEARL/12-0703TPX Flat Sheet 0.22D 25+/-4 Asker C 1.1M 1.47M 4mm</v>
+          </cell>
+          <cell r="H491">
+            <v>50</v>
+          </cell>
+          <cell r="I491">
+            <v>50</v>
+          </cell>
           <cell r="J491">
             <v>0</v>
           </cell>
           <cell r="K491">
-            <v>0</v>
-          </cell>
-          <cell r="L491"/>
-          <cell r="M491"/>
-          <cell r="N491"/>
-          <cell r="O491"/>
-          <cell r="P491"/>
-          <cell r="Q491"/>
-          <cell r="R491"/>
-          <cell r="S491"/>
-          <cell r="T491"/>
-          <cell r="U491" t="str">
-            <v/>
+            <v>50</v>
+          </cell>
+          <cell r="L491" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M491" t="str">
+            <v>SSO-2606-00082 - URGENT (6-10)</v>
+          </cell>
+          <cell r="N491" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O491" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P491">
+            <v>46176</v>
+          </cell>
+          <cell r="Q491">
+            <v>46183</v>
+          </cell>
+          <cell r="R491">
+            <v>46180</v>
+          </cell>
+          <cell r="S491">
+            <v>6</v>
+          </cell>
+          <cell r="T491">
+            <v>7</v>
+          </cell>
+          <cell r="U491">
+            <v>4</v>
           </cell>
           <cell r="V491">
-            <v>0</v>
+            <v>2.8570000000000002E-2</v>
           </cell>
           <cell r="W491">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="492">
-          <cell r="A492"/>
-          <cell r="B492"/>
-          <cell r="C492"/>
-          <cell r="D492"/>
+          <cell r="A492" t="str">
+            <v>S-2026-06-11</v>
+          </cell>
+          <cell r="B492" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C492" t="str">
+            <v>RPRO-260603-0483</v>
+          </cell>
+          <cell r="D492" t="str">
+            <v>PUR2600600300001S</v>
+          </cell>
           <cell r="E492" t="str">
-            <v/>
-          </cell>
-          <cell r="F492"/>
-          <cell r="G492"/>
-          <cell r="H492"/>
-          <cell r="I492"/>
+            <v>BDB-000195</v>
+          </cell>
+          <cell r="F492" t="str">
+            <v>PVN-004435</v>
+          </cell>
+          <cell r="G492" t="str">
+            <v>OrthoLite Ultra-Nike GREY/17-1501TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 1.7M 4mm</v>
+          </cell>
+          <cell r="H492">
+            <v>25</v>
+          </cell>
+          <cell r="I492">
+            <v>25</v>
+          </cell>
           <cell r="J492">
             <v>0</v>
           </cell>
           <cell r="K492">
-            <v>0</v>
-          </cell>
-          <cell r="L492"/>
-          <cell r="M492"/>
-          <cell r="N492"/>
-          <cell r="O492"/>
-          <cell r="P492"/>
-          <cell r="Q492"/>
-          <cell r="R492"/>
-          <cell r="S492"/>
-          <cell r="T492"/>
-          <cell r="U492" t="str">
-            <v/>
+            <v>25</v>
+          </cell>
+          <cell r="L492" t="str">
+            <v>NIKE</v>
+          </cell>
+          <cell r="M492" t="str">
+            <v>Sample/ URGENT</v>
+          </cell>
+          <cell r="N492" t="str">
+            <v>DIE CUT</v>
+          </cell>
+          <cell r="O492" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P492">
+            <v>46176</v>
+          </cell>
+          <cell r="Q492">
+            <v>46183</v>
+          </cell>
+          <cell r="R492">
+            <v>46180</v>
+          </cell>
+          <cell r="S492">
+            <v>6</v>
+          </cell>
+          <cell r="T492">
+            <v>7</v>
+          </cell>
+          <cell r="U492">
+            <v>4</v>
           </cell>
           <cell r="V492">
-            <v>0</v>
+            <v>2.8570000000000002E-2</v>
           </cell>
           <cell r="W492">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="493">
-          <cell r="A493"/>
-          <cell r="B493"/>
-          <cell r="C493"/>
-          <cell r="D493"/>
+          <cell r="A493" t="str">
+            <v>S-2026-06-12</v>
+          </cell>
+          <cell r="B493" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C493" t="str">
+            <v>RPRO-260603-0484</v>
+          </cell>
+          <cell r="D493" t="str">
+            <v>PUR2600600300001S</v>
+          </cell>
           <cell r="E493" t="str">
-            <v/>
-          </cell>
-          <cell r="F493"/>
-          <cell r="G493"/>
-          <cell r="H493"/>
-          <cell r="I493"/>
+            <v>BDB-000392</v>
+          </cell>
+          <cell r="F493" t="str">
+            <v>PVN-004434</v>
+          </cell>
+          <cell r="G493" t="str">
+            <v>OrthoLite X-40-Nike TRUE BLUE/19-4057TPX Flat Sheet 0.16D 35+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H493">
+            <v>25</v>
+          </cell>
+          <cell r="I493">
+            <v>25</v>
+          </cell>
           <cell r="J493">
             <v>0</v>
           </cell>
           <cell r="K493">
-            <v>0</v>
-          </cell>
-          <cell r="L493"/>
-          <cell r="M493"/>
-          <cell r="N493"/>
-          <cell r="O493"/>
-          <cell r="P493"/>
-          <cell r="Q493"/>
-          <cell r="R493"/>
-          <cell r="S493"/>
-          <cell r="T493"/>
-          <cell r="U493" t="str">
-            <v/>
+            <v>25</v>
+          </cell>
+          <cell r="L493" t="str">
+            <v>NIKE</v>
+          </cell>
+          <cell r="M493" t="str">
+            <v>Sample/ URGENT</v>
+          </cell>
+          <cell r="N493" t="str">
+            <v>DIE CUT</v>
+          </cell>
+          <cell r="O493" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P493">
+            <v>46176</v>
+          </cell>
+          <cell r="Q493">
+            <v>46183</v>
+          </cell>
+          <cell r="R493">
+            <v>46180</v>
+          </cell>
+          <cell r="S493">
+            <v>6</v>
+          </cell>
+          <cell r="T493">
+            <v>7</v>
+          </cell>
+          <cell r="U493">
+            <v>4</v>
           </cell>
           <cell r="V493">
-            <v>0</v>
+            <v>2.7779999999999999E-2</v>
           </cell>
           <cell r="W493">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="494">
-          <cell r="A494"/>
-          <cell r="B494"/>
-          <cell r="C494"/>
-          <cell r="D494"/>
+          <cell r="A494" t="str">
+            <v>S-2026-06-14</v>
+          </cell>
+          <cell r="B494" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C494" t="str">
+            <v>RPRO-260603-0485</v>
+          </cell>
+          <cell r="D494" t="str">
+            <v>PUR2606030002S</v>
+          </cell>
           <cell r="E494" t="str">
-            <v/>
-          </cell>
-          <cell r="F494"/>
-          <cell r="G494"/>
-          <cell r="H494"/>
-          <cell r="I494"/>
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F494" t="str">
+            <v>PVN-003299</v>
+          </cell>
+          <cell r="G494" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H494">
+            <v>50</v>
+          </cell>
+          <cell r="I494">
+            <v>50</v>
+          </cell>
           <cell r="J494">
             <v>0</v>
           </cell>
           <cell r="K494">
-            <v>0</v>
-          </cell>
-          <cell r="L494"/>
-          <cell r="M494"/>
-          <cell r="N494"/>
-          <cell r="O494"/>
-          <cell r="P494"/>
-          <cell r="Q494"/>
-          <cell r="R494"/>
-          <cell r="S494"/>
-          <cell r="T494"/>
-          <cell r="U494" t="str">
-            <v/>
+            <v>50</v>
+          </cell>
+          <cell r="L494" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M494" t="str">
+            <v>SSO-2606-00089/00070/00128  - URGENT (6-10)</v>
+          </cell>
+          <cell r="N494" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O494" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P494">
+            <v>46176</v>
+          </cell>
+          <cell r="Q494">
+            <v>46183</v>
+          </cell>
+          <cell r="R494">
+            <v>46180</v>
+          </cell>
+          <cell r="S494">
+            <v>6</v>
+          </cell>
+          <cell r="T494">
+            <v>7</v>
+          </cell>
+          <cell r="U494">
+            <v>3</v>
           </cell>
           <cell r="V494">
-            <v>0</v>
+            <v>2.1739999999999999E-2</v>
           </cell>
           <cell r="W494">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="495">
+          <cell r="A495" t="str">
+            <v>S-2026-06-15</v>
+          </cell>
+          <cell r="B495" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="C495" t="str">
+            <v>RPRO-260604-0522</v>
+          </cell>
+          <cell r="D495" t="str">
+            <v>PUR2606030002S</v>
+          </cell>
           <cell r="E495" t="str">
             <v/>
           </cell>
+          <cell r="F495" t="str">
+            <v>PVN-004437</v>
+          </cell>
+          <cell r="G495" t="str">
+            <v>OrthoLite X-35 SEEDPEARL/12-0703TPX Flat Sheet 0.145D 25+/-4 Asker C 1.1M 2M 8mm</v>
+          </cell>
+          <cell r="H495">
+            <v>20</v>
+          </cell>
+          <cell r="I495">
+            <v>20</v>
+          </cell>
           <cell r="J495">
             <v>0</v>
           </cell>
           <cell r="K495">
-            <v>0</v>
-          </cell>
-          <cell r="N495"/>
-          <cell r="O495"/>
+            <v>20</v>
+          </cell>
+          <cell r="L495" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M495" t="str">
+            <v>SSO-2606-00111</v>
+          </cell>
+          <cell r="N495" t="str">
+            <v>Molded</v>
+          </cell>
+          <cell r="O495" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P495">
+            <v>46176</v>
+          </cell>
+          <cell r="Q495">
+            <v>46183</v>
+          </cell>
+          <cell r="R495">
+            <v>46180</v>
+          </cell>
+          <cell r="S495">
+            <v>6</v>
+          </cell>
+          <cell r="T495">
+            <v>7</v>
+          </cell>
           <cell r="U495" t="str">
             <v/>
           </cell>
-          <cell r="V495">
-            <v>0</v>
-          </cell>
-          <cell r="W495">
-            <v>0</v>
+          <cell r="V495" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="W495" t="str">
+            <v/>
           </cell>
         </row>
         <row r="496">
+          <cell r="A496" t="str">
+            <v>L-2026-06-01</v>
+          </cell>
+          <cell r="C496" t="str">
+            <v>RPRO-260604-0523</v>
+          </cell>
+          <cell r="D496" t="str">
+            <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
+          </cell>
           <cell r="E496" t="str">
             <v/>
           </cell>
+          <cell r="F496" t="str">
+            <v>PVN-002424</v>
+          </cell>
+          <cell r="G496" t="str">
+            <v>OrthoLite Regular-Nike AIR BLUE/16-4134TPX 0.11D 15+/-4 Asker C 1.1M 2M 3.5mm</v>
+          </cell>
+          <cell r="H496">
+            <v>5</v>
+          </cell>
+          <cell r="I496">
+            <v>5</v>
+          </cell>
           <cell r="J496">
             <v>0</v>
           </cell>
           <cell r="K496">
             <v>0</v>
           </cell>
-          <cell r="O496"/>
+          <cell r="L496" t="str">
+            <v>NIKE-POU CHEN VÀ CONVERSE</v>
+          </cell>
+          <cell r="O496" t="str">
+            <v>Lab test</v>
+          </cell>
+          <cell r="P496">
+            <v>46177</v>
+          </cell>
+          <cell r="Q496">
+            <v>46184</v>
+          </cell>
+          <cell r="R496">
+            <v>46181</v>
+          </cell>
+          <cell r="S496">
+            <v>6</v>
+          </cell>
+          <cell r="T496">
+            <v>7</v>
+          </cell>
           <cell r="U496" t="str">
             <v/>
           </cell>
@@ -37413,16 +37483,57 @@
           </cell>
         </row>
         <row r="497">
+          <cell r="A497" t="str">
+            <v>L-2026-06-02</v>
+          </cell>
+          <cell r="C497" t="str">
+            <v>RPRO-260604-0524</v>
+          </cell>
+          <cell r="D497" t="str">
+            <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
+          </cell>
           <cell r="E497" t="str">
             <v/>
           </cell>
+          <cell r="F497" t="str">
+            <v>PVN-001635</v>
+          </cell>
+          <cell r="G497" t="str">
+            <v>OrthoLite Regular-Nike AIR BLUE/16-4134TPX 0.11D 15+/-4 Asker C 1.1M 2M 10mm</v>
+          </cell>
+          <cell r="H497">
+            <v>4</v>
+          </cell>
+          <cell r="I497">
+            <v>4</v>
+          </cell>
           <cell r="J497">
             <v>0</v>
           </cell>
           <cell r="K497">
             <v>0</v>
           </cell>
-          <cell r="O497"/>
+          <cell r="L497" t="str">
+            <v>NIKE-POU CHEN VÀ CONVERSE</v>
+          </cell>
+          <cell r="O497" t="str">
+            <v>Lab test</v>
+          </cell>
+          <cell r="P497">
+            <v>46177</v>
+          </cell>
+          <cell r="Q497">
+            <v>46184</v>
+          </cell>
+          <cell r="R497">
+            <v>46181</v>
+          </cell>
+          <cell r="S497">
+            <v>6</v>
+          </cell>
+          <cell r="T497">
+            <v>7</v>
+          </cell>
           <cell r="U497" t="str">
             <v/>
           </cell>
@@ -37434,16 +37545,57 @@
           </cell>
         </row>
         <row r="498">
+          <cell r="A498" t="str">
+            <v>L-2026-06-03</v>
+          </cell>
+          <cell r="C498" t="str">
+            <v>RPRO-260604-0525</v>
+          </cell>
+          <cell r="D498" t="str">
+            <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
+          </cell>
           <cell r="E498" t="str">
             <v/>
           </cell>
+          <cell r="F498" t="str">
+            <v>PVN-004123</v>
+          </cell>
+          <cell r="G498" t="str">
+            <v>OrthoLite X-40-Hybrid-Nike SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.16D 25+/-4 Asker C 1.1M 1.7M 3mm</v>
+          </cell>
+          <cell r="H498">
+            <v>5</v>
+          </cell>
+          <cell r="I498">
+            <v>5</v>
+          </cell>
           <cell r="J498">
             <v>0</v>
           </cell>
           <cell r="K498">
             <v>0</v>
           </cell>
-          <cell r="O498"/>
+          <cell r="L498" t="str">
+            <v>NIKE-POU CHEN VÀ CONVERSE</v>
+          </cell>
+          <cell r="O498" t="str">
+            <v>Lab test</v>
+          </cell>
+          <cell r="P498">
+            <v>46177</v>
+          </cell>
+          <cell r="Q498">
+            <v>46184</v>
+          </cell>
+          <cell r="R498">
+            <v>46181</v>
+          </cell>
+          <cell r="S498">
+            <v>6</v>
+          </cell>
+          <cell r="T498">
+            <v>7</v>
+          </cell>
           <cell r="U498" t="str">
             <v/>
           </cell>
@@ -37455,15 +37607,57 @@
           </cell>
         </row>
         <row r="499">
+          <cell r="A499" t="str">
+            <v>L-2026-06-04</v>
+          </cell>
+          <cell r="C499" t="str">
+            <v>RPRO-260604-0526</v>
+          </cell>
+          <cell r="D499" t="str">
+            <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
+          </cell>
           <cell r="E499" t="str">
             <v/>
           </cell>
+          <cell r="F499" t="str">
+            <v>PVN-004124</v>
+          </cell>
+          <cell r="G499" t="str">
+            <v>OrthoLite X-40-Hybrid-Nike SEEDPEARL/12-0703TPX 0.16D 25+/-4 Asker C 1.1M 1.7M 10mm</v>
+          </cell>
+          <cell r="H499">
+            <v>4</v>
+          </cell>
+          <cell r="I499">
+            <v>4</v>
+          </cell>
           <cell r="J499">
             <v>0</v>
           </cell>
           <cell r="K499">
             <v>0</v>
           </cell>
+          <cell r="L499" t="str">
+            <v>NIKE-POU CHEN VÀ CONVERSE</v>
+          </cell>
+          <cell r="O499" t="str">
+            <v>Lab test</v>
+          </cell>
+          <cell r="P499">
+            <v>46177</v>
+          </cell>
+          <cell r="Q499">
+            <v>46184</v>
+          </cell>
+          <cell r="R499">
+            <v>46181</v>
+          </cell>
+          <cell r="S499">
+            <v>6</v>
+          </cell>
+          <cell r="T499">
+            <v>7</v>
+          </cell>
           <cell r="U499" t="str">
             <v/>
           </cell>
@@ -37475,15 +37669,57 @@
           </cell>
         </row>
         <row r="500">
+          <cell r="A500" t="str">
+            <v>L-2026-06-05</v>
+          </cell>
+          <cell r="C500" t="str">
+            <v>RPRO-260604-0527</v>
+          </cell>
+          <cell r="D500" t="str">
+            <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
+          </cell>
           <cell r="E500" t="str">
             <v/>
           </cell>
+          <cell r="F500" t="str">
+            <v>PVN-002512</v>
+          </cell>
+          <cell r="G500" t="str">
+            <v>Eco LT-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 10mm</v>
+          </cell>
+          <cell r="H500">
+            <v>5</v>
+          </cell>
+          <cell r="I500">
+            <v>5</v>
+          </cell>
           <cell r="J500">
             <v>0</v>
           </cell>
           <cell r="K500">
             <v>0</v>
           </cell>
+          <cell r="L500" t="str">
+            <v>NIKE-POU CHEN VÀ CONVERSE</v>
+          </cell>
+          <cell r="O500" t="str">
+            <v>Lab test</v>
+          </cell>
+          <cell r="P500">
+            <v>46177</v>
+          </cell>
+          <cell r="Q500">
+            <v>46184</v>
+          </cell>
+          <cell r="R500">
+            <v>46181</v>
+          </cell>
+          <cell r="S500">
+            <v>6</v>
+          </cell>
+          <cell r="T500">
+            <v>7</v>
+          </cell>
           <cell r="U500" t="str">
             <v/>
           </cell>
@@ -37495,15 +37731,57 @@
           </cell>
         </row>
         <row r="501">
+          <cell r="A501" t="str">
+            <v>L-2026-06-06</v>
+          </cell>
+          <cell r="C501" t="str">
+            <v>RPRO-260604-0528</v>
+          </cell>
+          <cell r="D501" t="str">
+            <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
+          </cell>
           <cell r="E501" t="str">
             <v/>
           </cell>
+          <cell r="F501" t="str">
+            <v>PVN-002478</v>
+          </cell>
+          <cell r="G501" t="str">
+            <v>Eco LT-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H501">
+            <v>4</v>
+          </cell>
+          <cell r="I501">
+            <v>4</v>
+          </cell>
           <cell r="J501">
             <v>0</v>
           </cell>
           <cell r="K501">
             <v>0</v>
           </cell>
+          <cell r="L501" t="str">
+            <v>NIKE-POU CHEN VÀ CONVERSE</v>
+          </cell>
+          <cell r="O501" t="str">
+            <v>Lab test</v>
+          </cell>
+          <cell r="P501">
+            <v>46177</v>
+          </cell>
+          <cell r="Q501">
+            <v>46184</v>
+          </cell>
+          <cell r="R501">
+            <v>46181</v>
+          </cell>
+          <cell r="S501">
+            <v>6</v>
+          </cell>
+          <cell r="T501">
+            <v>7</v>
+          </cell>
           <cell r="U501" t="str">
             <v/>
           </cell>
@@ -37515,15 +37793,57 @@
           </cell>
         </row>
         <row r="502">
+          <cell r="A502" t="str">
+            <v>L-2026-06-07</v>
+          </cell>
+          <cell r="C502" t="str">
+            <v>RPRO-260604-0529</v>
+          </cell>
+          <cell r="D502" t="str">
+            <v xml:space="preserve">&lt;anne.tran@ortholite.vn&gt; </v>
+          </cell>
           <cell r="E502" t="str">
             <v/>
           </cell>
+          <cell r="F502" t="str">
+            <v>PVN-002699</v>
+          </cell>
+          <cell r="G502" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+          </cell>
+          <cell r="H502">
+            <v>2</v>
+          </cell>
+          <cell r="I502">
+            <v>2</v>
+          </cell>
           <cell r="J502">
             <v>0</v>
           </cell>
           <cell r="K502">
             <v>0</v>
           </cell>
+          <cell r="L502" t="str">
+            <v>SHYANG HUNG TAH</v>
+          </cell>
+          <cell r="O502" t="str">
+            <v>Lab test</v>
+          </cell>
+          <cell r="P502">
+            <v>46177</v>
+          </cell>
+          <cell r="Q502">
+            <v>46183</v>
+          </cell>
+          <cell r="R502">
+            <v>46180</v>
+          </cell>
+          <cell r="S502">
+            <v>6</v>
+          </cell>
+          <cell r="T502">
+            <v>6</v>
+          </cell>
           <cell r="U502" t="str">
             <v/>
           </cell>
@@ -37535,14 +37855,62 @@
           </cell>
         </row>
         <row r="503">
+          <cell r="A503" t="str">
+            <v>S-2026-06-16</v>
+          </cell>
+          <cell r="B503" t="str">
+            <v>chua rl</v>
+          </cell>
+          <cell r="D503" t="str">
+            <v>PUR2606040001S</v>
+          </cell>
           <cell r="E503" t="str">
             <v/>
           </cell>
+          <cell r="F503" t="str">
+            <v>PVN-004438</v>
+          </cell>
+          <cell r="G503" t="str">
+            <v>Ortholite X-25 GREEN/16-5932TPX Flat Sheet 0.12D 20+/-4 Asker C 1.1M 2M 6.2mm</v>
+          </cell>
+          <cell r="H503">
+            <v>70</v>
+          </cell>
+          <cell r="I503">
+            <v>70</v>
+          </cell>
           <cell r="J503">
             <v>0</v>
           </cell>
           <cell r="K503">
             <v>0</v>
+          </cell>
+          <cell r="L503" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M503" t="str">
+            <v>SSO-2606-00156  - URGENT (6-10)</v>
+          </cell>
+          <cell r="N503" t="str">
+            <v>Molded</v>
+          </cell>
+          <cell r="O503" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P503">
+            <v>46177</v>
+          </cell>
+          <cell r="Q503">
+            <v>46183</v>
+          </cell>
+          <cell r="R503">
+            <v>46180</v>
+          </cell>
+          <cell r="S503">
+            <v>6</v>
+          </cell>
+          <cell r="T503">
+            <v>6</v>
           </cell>
           <cell r="U503" t="str">
             <v/>
@@ -37622,9 +37990,7 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9">
         <row r="1">
-          <cell r="C1" t="str">
-            <v>TẠM THỜI NGƯNG NHẬN LAZY</v>
-          </cell>
+          <cell r="A1"/>
         </row>
       </sheetData>
       <sheetData sheetId="10"/>
@@ -37719,21 +38085,21 @@
       <sheetData sheetId="99"/>
       <sheetData sheetId="100"/>
       <sheetData sheetId="101"/>
-      <sheetData sheetId="102">
+      <sheetData sheetId="102"/>
+      <sheetData sheetId="103"/>
+      <sheetData sheetId="104">
         <row r="1">
           <cell r="F1" t="str">
             <v>No_Item</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="103"/>
-      <sheetData sheetId="104"/>
       <sheetData sheetId="105"/>
       <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
       <sheetData sheetId="108" refreshError="1"/>
-      <sheetData sheetId="109" refreshError="1"/>
-      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="109"/>
+      <sheetData sheetId="110"/>
       <sheetData sheetId="111" refreshError="1"/>
       <sheetData sheetId="112" refreshError="1"/>
       <sheetData sheetId="113" refreshError="1"/>
@@ -37769,7 +38135,7 @@
       <sheetData sheetId="143" refreshError="1"/>
       <sheetData sheetId="144" refreshError="1"/>
       <sheetData sheetId="145" refreshError="1"/>
-      <sheetData sheetId="146"/>
+      <sheetData sheetId="146" refreshError="1"/>
       <sheetData sheetId="147" refreshError="1"/>
       <sheetData sheetId="148" refreshError="1"/>
       <sheetData sheetId="149" refreshError="1"/>
@@ -37906,8 +38272,10 @@
       <sheetData sheetId="280" refreshError="1"/>
       <sheetData sheetId="281" refreshError="1"/>
       <sheetData sheetId="282" refreshError="1"/>
-      <sheetData sheetId="283"/>
+      <sheetData sheetId="283" refreshError="1"/>
       <sheetData sheetId="284" refreshError="1"/>
+      <sheetData sheetId="285" refreshError="1"/>
+      <sheetData sheetId="286" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -38240,11 +38608,11 @@
       <c r="B1" s="1">
         <v>46155.681657291665</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -39534,23 +39902,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="77" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="76" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="75" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="74" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="72" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="71" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -39596,13 +39964,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122916665</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -39661,19 +40029,19 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>379</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>380</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>172</v>
       </c>
       <c r="D3" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>381</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>382</v>
       </c>
       <c r="F3" s="22">
         <v>10</v>
@@ -39691,7 +40059,7 @@
         <v>27</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L3" s="26">
         <v>2</v>
@@ -39721,19 +40089,19 @@
     </row>
     <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>387</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>388</v>
       </c>
       <c r="F5" s="22">
         <v>30</v>
@@ -39781,19 +40149,19 @@
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="E7" s="21" t="s">
         <v>392</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>393</v>
       </c>
       <c r="F7" s="22">
         <v>30</v>
@@ -39805,7 +40173,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J7" s="25" t="s">
         <v>27</v>
@@ -39841,19 +40209,19 @@
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>395</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>396</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>181</v>
       </c>
       <c r="D9" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>397</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>398</v>
       </c>
       <c r="F9" s="22">
         <v>20</v>
@@ -39865,7 +40233,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J9" s="25" t="s">
         <v>27</v>
@@ -39901,19 +40269,19 @@
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>399</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>400</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D11" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>401</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>402</v>
       </c>
       <c r="F11" s="22">
         <v>30</v>
@@ -39925,7 +40293,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>27</v>
@@ -39945,19 +40313,19 @@
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>403</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>404</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>405</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>406</v>
       </c>
       <c r="F12" s="22">
         <v>60</v>
@@ -39972,7 +40340,7 @@
         <v>57</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K12" s="25" t="s">
         <v>67</v>
@@ -40001,19 +40369,19 @@
     </row>
     <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>408</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>409</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>105</v>
       </c>
       <c r="D14" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="E14" s="21" t="s">
         <v>410</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>411</v>
       </c>
       <c r="F14" s="22">
         <v>30</v>
@@ -40028,7 +40396,7 @@
         <v>57</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K14" s="25" t="s">
         <v>67</v>
@@ -40061,19 +40429,19 @@
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>412</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>413</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>98</v>
       </c>
       <c r="D16" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>414</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>415</v>
       </c>
       <c r="F16" s="22">
         <v>50</v>
@@ -40088,7 +40456,7 @@
         <v>57</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K16" s="25" t="s">
         <v>67</v>
@@ -40977,12 +41345,2800 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A23">
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26:A1048576">
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE5B080-A4F1-4729-80BF-D97CEABD7F46}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:N666"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="124.453125" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46178.475122800926</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>12</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="F3" s="22">
+        <v>20</v>
+      </c>
+      <c r="G3" s="23">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24">
+        <v>1</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>421</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="26">
+        <v>1</v>
+      </c>
+      <c r="M3" s="75" t="s">
+        <v>246</v>
+      </c>
+      <c r="N3" s="28">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="76"/>
+    </row>
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="22">
+        <v>50</v>
+      </c>
+      <c r="G5" s="23">
+        <v>2</v>
+      </c>
+      <c r="H5" s="24">
+        <v>2</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="26">
+        <v>2</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="N5" s="28">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="76"/>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="F7" s="22">
+        <v>25</v>
+      </c>
+      <c r="G7" s="23">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24">
+        <v>1</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="L7" s="26">
+        <v>1</v>
+      </c>
+      <c r="M7" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="N7" s="28">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="28"/>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="76"/>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="F10" s="22">
+        <v>25</v>
+      </c>
+      <c r="G10" s="23">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24">
+        <v>1</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="L10" s="26">
+        <v>6</v>
+      </c>
+      <c r="M10" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="N10" s="28">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="76"/>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="22">
+        <v>50</v>
+      </c>
+      <c r="G12" s="23">
+        <v>2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>2</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="26">
+        <v>2</v>
+      </c>
+      <c r="M12" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="N12" s="28">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C13" s="19" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="20" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="21" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" s="22" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="23" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H13" s="24" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L13" s="26"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A13,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C14" s="19" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D14" s="20" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="21" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="22" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="23" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H14" s="24" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A14,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C15" s="19" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D15" s="20" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="21" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" s="22" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="23" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H15" s="24" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C16" s="19" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="20" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="21" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="22" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="23" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H16" s="24" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L16" s="26"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A16,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C17" s="19" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="20" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="21" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="22" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="23" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H17" s="24" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="19" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="20" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="21" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="22" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="23" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H18" s="24" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A18,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="19" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="20" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="21" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F19" s="22" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="23" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H19" s="24" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="19" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="20" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="21" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="22" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="23" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="24" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="19" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="20" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="21" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="22" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="23" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="24" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="26"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A21,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="17"/>
+      <c r="B22" s="18" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C22" s="19" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D22" s="20" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" s="21" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F22" s="22" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G22" s="23" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H22" s="24" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L22" s="26"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A22,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="41"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+    </row>
+    <row r="24" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="56"/>
+    </row>
+    <row r="26" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="55"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="58"/>
+    </row>
+    <row r="28" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L28" s="56"/>
+    </row>
+    <row r="29" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L29" s="56"/>
+    </row>
+    <row r="30" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="57" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="58"/>
+    </row>
+    <row r="666" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A666" s="2"/>
+      <c r="B666" s="52"/>
+      <c r="C666" s="2"/>
+      <c r="D666" s="2"/>
+      <c r="E666" s="60"/>
+      <c r="H666" s="55"/>
+      <c r="I666" s="53"/>
+      <c r="J666" s="53"/>
+      <c r="K666" s="53"/>
+      <c r="L666" s="61"/>
+      <c r="M666" s="57"/>
+      <c r="N666" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E22" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N23" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="RPRO-260603-0481"/>
+        <filter val="RPRO-260603-0482"/>
+        <filter val="RPRO-260603-0483"/>
+        <filter val="RPRO-260603-0484"/>
+        <filter val="RPRO-260603-0485"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A22">
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25:A1048576">
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="23" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3BEF0C0-E48B-4301-87EB-D033DC6D8EEE}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:N665"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="138.7265625" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46178.475122800926</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>9</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18" t="e">
+        <f>VLOOKUP(A3,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C3" s="19" t="e">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D3" s="20" t="e">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E3" s="21" t="e">
+        <f>VLOOKUP(A3,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F3" s="22" t="e">
+        <f>VLOOKUP(A3,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G3" s="23" t="e">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H3" s="24" t="e">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I3" s="25" t="e">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J3" s="25" t="e">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K3" s="25" t="e">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L3" s="26"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A3,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C4" s="19" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D4" s="20" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E4" s="21" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F4" s="22" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G4" s="23" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H4" s="24" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I4" s="25" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J4" s="25" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K4" s="25" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A4,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C5" s="19" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D5" s="20" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E5" s="21" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F5" s="22" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G5" s="23" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H5" s="24" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I5" s="25" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J5" s="25" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K5" s="25" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L5" s="26"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A5,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="F6" s="22">
+        <v>20</v>
+      </c>
+      <c r="G6" s="23">
+        <v>2</v>
+      </c>
+      <c r="H6" s="24">
+        <v>2</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>444</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="26">
+        <v>2</v>
+      </c>
+      <c r="M6" s="27"/>
+      <c r="N6" s="28">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="76"/>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="F8" s="22">
+        <v>2</v>
+      </c>
+      <c r="G8" s="23">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24">
+        <v>1</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="J8" s="25">
+        <v>0</v>
+      </c>
+      <c r="K8" s="25">
+        <v>0</v>
+      </c>
+      <c r="L8" s="26">
+        <v>1</v>
+      </c>
+      <c r="M8" s="40"/>
+      <c r="N8" s="28">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="76"/>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="F10" s="22">
+        <v>5</v>
+      </c>
+      <c r="G10" s="23">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24">
+        <v>1</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="J10" s="25">
+        <v>0</v>
+      </c>
+      <c r="K10" s="25">
+        <v>0</v>
+      </c>
+      <c r="L10" s="26">
+        <v>2</v>
+      </c>
+      <c r="M10" s="27"/>
+      <c r="N10" s="28">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="F11" s="22">
+        <v>4</v>
+      </c>
+      <c r="G11" s="23">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24">
+        <v>1</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="J11" s="25">
+        <v>0</v>
+      </c>
+      <c r="K11" s="25">
+        <v>0</v>
+      </c>
+      <c r="L11" s="26"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="28">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="76"/>
+    </row>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="F13" s="22">
+        <v>5</v>
+      </c>
+      <c r="G13" s="23">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24">
+        <v>1</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="J13" s="25">
+        <v>0</v>
+      </c>
+      <c r="K13" s="25">
+        <v>0</v>
+      </c>
+      <c r="L13" s="26">
+        <v>2</v>
+      </c>
+      <c r="M13" s="40"/>
+      <c r="N13" s="28">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="F14" s="22">
+        <v>4</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24">
+        <v>1</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="J14" s="25">
+        <v>0</v>
+      </c>
+      <c r="K14" s="25">
+        <v>0</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="28">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="62"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="76"/>
+    </row>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="F16" s="22">
+        <v>5</v>
+      </c>
+      <c r="G16" s="23">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24">
+        <v>1</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="J16" s="25">
+        <v>0</v>
+      </c>
+      <c r="K16" s="25">
+        <v>0</v>
+      </c>
+      <c r="L16" s="26">
+        <v>2</v>
+      </c>
+      <c r="M16" s="27"/>
+      <c r="N16" s="28">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="F17" s="22">
+        <v>4</v>
+      </c>
+      <c r="G17" s="23">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24">
+        <v>1</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="J17" s="25">
+        <v>0</v>
+      </c>
+      <c r="K17" s="25">
+        <v>0</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="28">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H18" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="28" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F19" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H19" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I19" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J19" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K19" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="28" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="28" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I21" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="26"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="28" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="51"/>
+    </row>
+    <row r="23" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L23" s="56"/>
+    </row>
+    <row r="24" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="56"/>
+    </row>
+    <row r="26" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="55"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="58"/>
+    </row>
+    <row r="27" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="56"/>
+    </row>
+    <row r="28" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L28" s="56"/>
+    </row>
+    <row r="29" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="58"/>
+    </row>
+    <row r="30" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="665" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A665" s="2"/>
+      <c r="B665" s="52"/>
+      <c r="C665" s="2"/>
+      <c r="D665" s="2"/>
+      <c r="E665" s="60"/>
+      <c r="H665" s="55"/>
+      <c r="I665" s="53"/>
+      <c r="J665" s="53"/>
+      <c r="K665" s="53"/>
+      <c r="L665" s="61"/>
+      <c r="M665" s="57"/>
+      <c r="N665" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E21" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N22" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="2">
+      <filters blank="1">
+        <filter val="BDB-000097"/>
+        <filter val="BDB-000113"/>
+        <filter val="BDB-000131"/>
+        <filter val="BDB-000221"/>
+        <filter val="BDB-000307"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A23">
+  <conditionalFormatting sqref="A3:A21">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A1048576">
+  <conditionalFormatting sqref="A24:A1048576">
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
@@ -41002,7 +44158,7 @@
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="24" max="15" man="1"/>
+    <brk id="22" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -41038,13 +44194,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122800926</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -42387,23 +45543,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="70" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -42448,13 +45604,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122800926</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -43855,23 +47011,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -43916,13 +47072,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122916665</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -45289,23 +48445,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -45349,13 +48505,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122916665</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -45569,11 +48725,11 @@
         <v>46167.440663078705</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="80" t="s">
+      <c r="D7" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
       <c r="H7" s="4"/>
       <c r="I7" s="5"/>
       <c r="J7" s="7"/>
@@ -46564,39 +49720,39 @@
     <mergeCell ref="D7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="49" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A6 A14:A18">
-    <cfRule type="duplicateValues" dxfId="48" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="47" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A13">
-    <cfRule type="duplicateValues" dxfId="46" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A1048576">
-    <cfRule type="duplicateValues" dxfId="45" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C6 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="44" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C13">
-    <cfRule type="duplicateValues" dxfId="42" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:L8">
-    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="39" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="37" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="9"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -46641,13 +49797,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122916665</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -47966,26 +51122,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A15">
-    <cfRule type="duplicateValues" dxfId="35" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A21">
-    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="30" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -48031,13 +51187,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122916665</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -49386,23 +52542,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -49447,13 +52603,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122916665</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -50835,24 +53991,24 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="20" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -50898,13 +54054,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46176.520486574074</v>
-      </c>
-      <c r="D1" s="80" t="s">
+        <v>46178.475122916665</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -51159,7 +54315,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="27" t="s">
-        <v>378</v>
+        <v>246</v>
       </c>
       <c r="N8" s="28">
         <v>46178</v>
@@ -52243,23 +55399,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A4A1B7B-B216-41BB-AE5C-84739BA2A93F}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D650652-9D11-44C1-8210-99001EF99009}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="11" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="12" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,11 @@
     <sheet name="2.6" sheetId="10" r:id="rId10"/>
     <sheet name="3.6" sheetId="11" r:id="rId11"/>
     <sheet name="4.6" sheetId="12" r:id="rId12"/>
+    <sheet name="5.6" sheetId="13" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
+    <externalReference r:id="rId15"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
@@ -43,6 +44,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'3.6'!$A$2:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'4.6'!$A$2:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'5.6'!$A$2:$N$25</definedName>
     <definedName name="AE" localSheetId="8">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -55,6 +57,7 @@
     <definedName name="AE" localSheetId="7">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="10">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="11">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="12">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'1.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
@@ -67,6 +70,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'29.5 - L2'!$A$1:$N$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'3.6'!$A$1:$N$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'4.6'!$A$1:$N$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'5.6'!$A$1:$N$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'1.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
@@ -79,6 +83,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'29.5 - L2'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'3.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'4.6'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'5.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -91,6 +96,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -103,6 +109,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -115,6 +122,7 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -127,6 +135,7 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -139,6 +148,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -151,6 +161,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="8" hidden="1">'1.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
@@ -163,6 +174,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="7" hidden="1">'29.5 - L2'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="10" hidden="1">'3.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="11" hidden="1">'4.6'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="12" hidden="1">'5.6'!#REF!</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -175,6 +187,7 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -187,6 +200,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -199,6 +213,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -211,6 +226,7 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -223,6 +239,7 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -235,6 +252,7 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -247,6 +265,7 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -259,6 +278,7 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -271,6 +291,7 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -283,6 +304,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -295,6 +317,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -307,6 +330,7 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -319,6 +343,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="7" hidden="1">'29.5 - L2'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -331,6 +356,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="7" hidden="1">'29.5 - L2'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -353,7 +379,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="512">
   <si>
     <t>Release Date</t>
   </si>
@@ -1861,6 +1887,114 @@
   <si>
     <t>Eco LT-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</t>
   </si>
+  <si>
+    <t>S-2026-06-16</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0678</t>
+  </si>
+  <si>
+    <t>PVN-004438</t>
+  </si>
+  <si>
+    <t>Ortholite X-25 GREEN/16-5932TPX Flat Sheet 0.12D 20+/-4 Asker C 1.1M 2M 6.2mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-17</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0679</t>
+  </si>
+  <si>
+    <t>PVN-004350</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular SEEDPEARL/12-0703TPX Flat Sheet 0.13D 35+/-4 Asker C 1.1M 1.47M 13mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-18</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0680</t>
+  </si>
+  <si>
+    <t>PVN-002539</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 5mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-19</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0681</t>
+  </si>
+  <si>
+    <t>S-2026-06-24</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0686</t>
+  </si>
+  <si>
+    <t>S-2026-06-20</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0682</t>
+  </si>
+  <si>
+    <t>PVN-001452</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra SEEDPEARL/12-0703TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-21</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0683</t>
+  </si>
+  <si>
+    <t>PVN-004076</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular NEUTRAL GRAY/17-4402TPX Flat Sheet 0.13D 15+/-4 Asker C 1.1M 2M 24mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-22</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0684</t>
+  </si>
+  <si>
+    <t>PVN-003327</t>
+  </si>
+  <si>
+    <t>OrthoLite X-40 TRUE BLUE/19-4057TPX 0.16D 35+/-4 Asker C 1.1M 1.7M 4mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-23</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0685</t>
+  </si>
+  <si>
+    <t>PVN-004212</t>
+  </si>
+  <si>
+    <t>OrthoLite X-40-Hybrid TRUE BLUE/19-4057TPX Hybrid Flat Sheet 0.16D 25+/-4 Asker C 1.1M 2M 3mm</t>
+  </si>
+  <si>
+    <t>S-2026-05-84</t>
+  </si>
+  <si>
+    <t>RPRO-260605-0687</t>
+  </si>
+  <si>
+    <t>PVN-004430</t>
+  </si>
+  <si>
+    <t>OrthoLite HybridPlus-Recycled COLORO 063-98-46 (fluorescent) Hybrid 0.12D 25+/-4 Asker C 1.1M 2M 6mm</t>
+  </si>
 </sst>
 </file>
 
@@ -1870,7 +2004,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2084,6 +2218,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2214,7 +2355,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2456,6 +2597,12 @@
     <xf numFmtId="49" fontId="24" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2464,7 +2611,87 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="92">
+  <dxfs count="100">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3557,13 +3784,15 @@
       <sheetName val="1.6"/>
       <sheetName val="2.6"/>
       <sheetName val="3.6"/>
-      <sheetName val="form 2 (18)"/>
+      <sheetName val="4.6"/>
+      <sheetName val="5.6"/>
+      <sheetName val="form 2 (20)"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
-      <sheetName val="4.6"/>
+      <sheetName val="form 2 (18)"/>
       <sheetName val="form 2 (19)"/>
       <sheetName val="form 2 (17)"/>
       <sheetName val="form 2 (16)"/>
@@ -3749,49 +3978,84 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
+          <cell r="A1"/>
+          <cell r="B1"/>
           <cell r="C1" t="str">
             <v>TẠM THỜI NGƯNG NHẬN LAZY</v>
           </cell>
+          <cell r="D1"/>
+          <cell r="E1"/>
+          <cell r="F1"/>
           <cell r="G1" t="str">
             <v>ASICS 12MM DÙNG BOM 132 (roundup(12/132),5)</v>
           </cell>
+          <cell r="H1"/>
+          <cell r="I1"/>
+          <cell r="J1"/>
+          <cell r="K1"/>
+          <cell r="L1"/>
+          <cell r="M1"/>
+          <cell r="N1"/>
+          <cell r="O1"/>
+          <cell r="P1"/>
+          <cell r="Q1"/>
+          <cell r="R1"/>
+          <cell r="S1"/>
+          <cell r="T1"/>
+          <cell r="U1"/>
+          <cell r="V1"/>
+          <cell r="W1"/>
         </row>
         <row r="2">
+          <cell r="A2"/>
+          <cell r="B2"/>
+          <cell r="C2"/>
+          <cell r="D2"/>
+          <cell r="E2"/>
+          <cell r="F2"/>
           <cell r="G2" t="str">
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>70</v>
+            <v>24949</v>
           </cell>
           <cell r="I2">
-            <v>70</v>
+            <v>24949</v>
           </cell>
           <cell r="J2">
-            <v>55</v>
+            <v>23583</v>
           </cell>
           <cell r="K2">
-            <v>15</v>
+            <v>1366</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
           </cell>
+          <cell r="M2"/>
+          <cell r="N2"/>
+          <cell r="O2"/>
+          <cell r="P2"/>
           <cell r="Q2" t="str">
             <v>ETD hệ thống+1ngay</v>
           </cell>
           <cell r="R2" t="e">
             <v>#VALUE!</v>
           </cell>
+          <cell r="S2"/>
+          <cell r="T2"/>
           <cell r="U2">
             <v>12</v>
           </cell>
+          <cell r="V2"/>
           <cell r="W2">
-            <v>9</v>
+            <v>1271</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>NO.Order</v>
           </cell>
+          <cell r="B3"/>
           <cell r="C3" t="str">
             <v>Firm plan
 (PU PVN)</v>
@@ -3876,6 +4140,7 @@
           <cell r="A4" t="str">
             <v>S-2026-01-01</v>
           </cell>
+          <cell r="B4"/>
           <cell r="C4" t="str">
             <v>RPRO-260105-0668</v>
           </cell>
@@ -4228,6 +4493,7 @@
           <cell r="A9" t="str">
             <v>S-2026-01-06</v>
           </cell>
+          <cell r="B9"/>
           <cell r="C9" t="str">
             <v>RPRO-260105-0673</v>
           </cell>
@@ -4296,6 +4562,7 @@
           <cell r="A10" t="str">
             <v>S-2026-01-07</v>
           </cell>
+          <cell r="B10"/>
           <cell r="C10" t="str">
             <v>RPRO-260105-0674</v>
           </cell>
@@ -4364,6 +4631,7 @@
           <cell r="A11" t="str">
             <v>S-2026-01-08</v>
           </cell>
+          <cell r="B11"/>
           <cell r="C11" t="str">
             <v>RPRO-260105-0675</v>
           </cell>
@@ -4574,6 +4842,7 @@
           <cell r="A14" t="str">
             <v>L-2026-01-11</v>
           </cell>
+          <cell r="B14"/>
           <cell r="C14" t="str">
             <v>RPRO-260105-0678</v>
           </cell>
@@ -4607,6 +4876,7 @@
           <cell r="M14" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N14"/>
           <cell r="O14" t="str">
             <v>Lab test</v>
           </cell>
@@ -4639,6 +4909,7 @@
           <cell r="A15" t="str">
             <v>L-2026-01-12</v>
           </cell>
+          <cell r="B15"/>
           <cell r="C15" t="str">
             <v>RPRO-260105-0679</v>
           </cell>
@@ -4672,6 +4943,7 @@
           <cell r="M15" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N15"/>
           <cell r="O15" t="str">
             <v>Lab test</v>
           </cell>
@@ -4704,6 +4976,7 @@
           <cell r="A16" t="str">
             <v>L-2026-01-13</v>
           </cell>
+          <cell r="B16"/>
           <cell r="C16" t="str">
             <v>RPRO-260105-0680</v>
           </cell>
@@ -4737,6 +5010,7 @@
           <cell r="M16" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N16"/>
           <cell r="O16" t="str">
             <v>Lab test</v>
           </cell>
@@ -4769,6 +5043,7 @@
           <cell r="A17" t="str">
             <v>L-2026-01-14</v>
           </cell>
+          <cell r="B17"/>
           <cell r="C17" t="str">
             <v>RPRO-260105-0681</v>
           </cell>
@@ -4802,6 +5077,7 @@
           <cell r="M17" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N17"/>
           <cell r="O17" t="str">
             <v>Lab test</v>
           </cell>
@@ -4870,6 +5146,7 @@
           <cell r="M18" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N18"/>
           <cell r="O18" t="str">
             <v>Lab test</v>
           </cell>
@@ -4938,6 +5215,7 @@
           <cell r="M19" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N19"/>
           <cell r="O19" t="str">
             <v>Lab test</v>
           </cell>
@@ -5325,6 +5603,7 @@
           <cell r="A25" t="str">
             <v>L-2026-01-22</v>
           </cell>
+          <cell r="B25"/>
           <cell r="C25" t="str">
             <v>RPRO-260109-0095</v>
           </cell>
@@ -5358,6 +5637,7 @@
           <cell r="M25" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N25"/>
           <cell r="O25" t="str">
             <v>Lab test</v>
           </cell>
@@ -5390,6 +5670,7 @@
           <cell r="A26" t="str">
             <v>S-2026-01-23</v>
           </cell>
+          <cell r="B26"/>
           <cell r="C26" t="str">
             <v>RPRO-260113-0624</v>
           </cell>
@@ -5458,6 +5739,7 @@
           <cell r="A27" t="str">
             <v>S-2026-01-24</v>
           </cell>
+          <cell r="B27"/>
           <cell r="C27" t="str">
             <v>RPRO-260113-0625</v>
           </cell>
@@ -5526,6 +5808,7 @@
           <cell r="A28" t="str">
             <v>S-2026-01-25</v>
           </cell>
+          <cell r="B28"/>
           <cell r="C28" t="str">
             <v>RPRO-260113-0626</v>
           </cell>
@@ -5594,6 +5877,7 @@
           <cell r="A29" t="str">
             <v>S-2026-01-26</v>
           </cell>
+          <cell r="B29"/>
           <cell r="C29" t="str">
             <v>RPRO-260113-0627</v>
           </cell>
@@ -5662,6 +5946,7 @@
           <cell r="A30" t="str">
             <v>S-2026-01-27</v>
           </cell>
+          <cell r="B30"/>
           <cell r="C30" t="str">
             <v>RPRO-260113-0628</v>
           </cell>
@@ -5730,6 +6015,7 @@
           <cell r="A31" t="str">
             <v>S-2026-01-28</v>
           </cell>
+          <cell r="B31"/>
           <cell r="C31" t="str">
             <v>RPRO-260113-0629</v>
           </cell>
@@ -5798,6 +6084,7 @@
           <cell r="A32" t="str">
             <v>S-2026-01-29</v>
           </cell>
+          <cell r="B32"/>
           <cell r="C32" t="str">
             <v>RPRO-260113-0630</v>
           </cell>
@@ -5866,6 +6153,7 @@
           <cell r="A33" t="str">
             <v>S-2026-01-30</v>
           </cell>
+          <cell r="B33"/>
           <cell r="C33" t="str">
             <v>RPRO-260115-0298</v>
           </cell>
@@ -5934,6 +6222,7 @@
           <cell r="A34" t="str">
             <v>S-2026-01-31</v>
           </cell>
+          <cell r="B34"/>
           <cell r="C34" t="str">
             <v>RPRO-260115-0299</v>
           </cell>
@@ -6002,6 +6291,7 @@
           <cell r="A35" t="str">
             <v>S-2026-01-32</v>
           </cell>
+          <cell r="B35"/>
           <cell r="C35" t="str">
             <v>RPRO-260115-0300</v>
           </cell>
@@ -6070,6 +6360,7 @@
           <cell r="A36" t="str">
             <v>S-2026-01-33</v>
           </cell>
+          <cell r="B36"/>
           <cell r="C36" t="str">
             <v>RPRO-260115-0301</v>
           </cell>
@@ -6138,6 +6429,7 @@
           <cell r="A37" t="str">
             <v>S-2026-01-34</v>
           </cell>
+          <cell r="B37"/>
           <cell r="C37" t="str">
             <v>RPRO-260115-0302</v>
           </cell>
@@ -6206,6 +6498,7 @@
           <cell r="A38" t="str">
             <v>S-2026-01-35</v>
           </cell>
+          <cell r="B38"/>
           <cell r="C38" t="str">
             <v>RPRO-260115-0303</v>
           </cell>
@@ -6274,6 +6567,7 @@
           <cell r="A39" t="str">
             <v>S-2026-01-36</v>
           </cell>
+          <cell r="B39"/>
           <cell r="C39" t="str">
             <v>RPRO-260115-0304</v>
           </cell>
@@ -6342,6 +6636,7 @@
           <cell r="A40" t="str">
             <v>S-2026-01-37</v>
           </cell>
+          <cell r="B40"/>
           <cell r="C40" t="str">
             <v>RPRO-260115-0305</v>
           </cell>
@@ -6410,6 +6705,7 @@
           <cell r="A41" t="str">
             <v>S-2026-01-38</v>
           </cell>
+          <cell r="B41"/>
           <cell r="C41" t="str">
             <v>RPRO-260115-0306</v>
           </cell>
@@ -6478,6 +6774,7 @@
           <cell r="A42" t="str">
             <v>S-2026-01-39</v>
           </cell>
+          <cell r="B42"/>
           <cell r="C42" t="str">
             <v>RPRO-260115-0307</v>
           </cell>
@@ -6546,6 +6843,7 @@
           <cell r="A43" t="str">
             <v>S-2026-01-40</v>
           </cell>
+          <cell r="B43"/>
           <cell r="C43" t="str">
             <v>RPRO-260115-0308</v>
           </cell>
@@ -6614,6 +6912,7 @@
           <cell r="A44" t="str">
             <v>S-2026-01-41</v>
           </cell>
+          <cell r="B44"/>
           <cell r="C44" t="str">
             <v>RPRO-260115-0309</v>
           </cell>
@@ -6682,6 +6981,7 @@
           <cell r="A45" t="str">
             <v>S-2026-01-42</v>
           </cell>
+          <cell r="B45"/>
           <cell r="C45" t="str">
             <v>RPRO-260109-0096</v>
           </cell>
@@ -6750,6 +7050,7 @@
           <cell r="A46" t="str">
             <v>S-2026-01-43</v>
           </cell>
+          <cell r="B46"/>
           <cell r="C46" t="str">
             <v>RPRO-260109-0097</v>
           </cell>
@@ -6818,6 +7119,7 @@
           <cell r="A47" t="str">
             <v>S-2026-01-44</v>
           </cell>
+          <cell r="B47"/>
           <cell r="C47" t="str">
             <v>RPRO-260109-0098</v>
           </cell>
@@ -6886,6 +7188,7 @@
           <cell r="A48" t="str">
             <v>S-2026-01-45</v>
           </cell>
+          <cell r="B48"/>
           <cell r="C48" t="str">
             <v>RPRO-260109-0099</v>
           </cell>
@@ -6954,6 +7257,7 @@
           <cell r="A49" t="str">
             <v>S-2026-01-46</v>
           </cell>
+          <cell r="B49"/>
           <cell r="C49" t="str">
             <v>RPRO-260120-0349</v>
           </cell>
@@ -7022,6 +7326,7 @@
           <cell r="A50" t="str">
             <v>S-2026-01-47</v>
           </cell>
+          <cell r="B50"/>
           <cell r="C50" t="str">
             <v>RPRO-260120-0350</v>
           </cell>
@@ -7090,6 +7395,7 @@
           <cell r="A51" t="str">
             <v>S-2026-01-48</v>
           </cell>
+          <cell r="B51"/>
           <cell r="C51" t="str">
             <v>RPRO-260120-0351</v>
           </cell>
@@ -7158,6 +7464,7 @@
           <cell r="A52" t="str">
             <v>S-2026-01-49</v>
           </cell>
+          <cell r="B52"/>
           <cell r="C52" t="str">
             <v>RPRO-260120-0352</v>
           </cell>
@@ -7226,6 +7533,7 @@
           <cell r="A53" t="str">
             <v>S-2026-01-50</v>
           </cell>
+          <cell r="B53"/>
           <cell r="C53" t="str">
             <v>RPRO-260120-0353</v>
           </cell>
@@ -7294,6 +7602,7 @@
           <cell r="A54" t="str">
             <v>S-2026-01-51</v>
           </cell>
+          <cell r="B54"/>
           <cell r="C54" t="str">
             <v>RPRO-260120-0354</v>
           </cell>
@@ -7362,6 +7671,7 @@
           <cell r="A55" t="str">
             <v>S-2026-01-52</v>
           </cell>
+          <cell r="B55"/>
           <cell r="C55" t="str">
             <v>RPRO-260113-0631</v>
           </cell>
@@ -7430,6 +7740,7 @@
           <cell r="A56" t="str">
             <v>S-2026-01-53</v>
           </cell>
+          <cell r="B56"/>
           <cell r="C56" t="str">
             <v>RPRO-260120-0355</v>
           </cell>
@@ -7498,6 +7809,7 @@
           <cell r="A57" t="str">
             <v>S-2026-01-54</v>
           </cell>
+          <cell r="B57"/>
           <cell r="C57" t="str">
             <v>RPRO-260120-0356</v>
           </cell>
@@ -7566,6 +7878,7 @@
           <cell r="A58" t="str">
             <v>S-2026-01-55</v>
           </cell>
+          <cell r="B58"/>
           <cell r="C58" t="str">
             <v>RPRO-260120-0357</v>
           </cell>
@@ -7634,6 +7947,7 @@
           <cell r="A59" t="str">
             <v>S-2026-01-56</v>
           </cell>
+          <cell r="B59"/>
           <cell r="C59" t="str">
             <v>RPRO-260120-0358</v>
           </cell>
@@ -7702,6 +8016,7 @@
           <cell r="A60" t="str">
             <v>S-2026-01-57</v>
           </cell>
+          <cell r="B60"/>
           <cell r="C60" t="str">
             <v>RPRO-260120-0359</v>
           </cell>
@@ -7770,6 +8085,7 @@
           <cell r="A61" t="str">
             <v>S-2026-01-58</v>
           </cell>
+          <cell r="B61"/>
           <cell r="C61" t="str">
             <v>RPRO-260120-0360</v>
           </cell>
@@ -7838,6 +8154,7 @@
           <cell r="A62" t="str">
             <v>S-2026-01-59</v>
           </cell>
+          <cell r="B62"/>
           <cell r="C62" t="str">
             <v>RPRO-260116-0276</v>
           </cell>
@@ -7906,6 +8223,7 @@
           <cell r="A63" t="str">
             <v>S-2026-01-60</v>
           </cell>
+          <cell r="B63"/>
           <cell r="C63" t="str">
             <v>RPRO-260115-0310</v>
           </cell>
@@ -7974,6 +8292,7 @@
           <cell r="A64" t="str">
             <v>S-2026-01-61</v>
           </cell>
+          <cell r="B64"/>
           <cell r="C64" t="str">
             <v>RPRO-260120-0361</v>
           </cell>
@@ -8113,6 +8432,7 @@
           <cell r="A66" t="str">
             <v>S-2026-01-63</v>
           </cell>
+          <cell r="B66"/>
           <cell r="C66" t="str">
             <v>RPRO-260122-1562</v>
           </cell>
@@ -8181,6 +8501,7 @@
           <cell r="A67" t="str">
             <v>S-2026-01-64</v>
           </cell>
+          <cell r="B67"/>
           <cell r="C67" t="str">
             <v>RPRO-260122-1563</v>
           </cell>
@@ -8249,6 +8570,7 @@
           <cell r="A68" t="str">
             <v>S-2026-01-65</v>
           </cell>
+          <cell r="B68"/>
           <cell r="C68" t="str">
             <v>RPRO-260122-1564</v>
           </cell>
@@ -8317,6 +8639,7 @@
           <cell r="A69" t="str">
             <v>S-2026-01-66</v>
           </cell>
+          <cell r="B69"/>
           <cell r="C69" t="str">
             <v>RPRO-260122-1565</v>
           </cell>
@@ -8385,6 +8708,7 @@
           <cell r="A70" t="str">
             <v>S-2026-01-67</v>
           </cell>
+          <cell r="B70"/>
           <cell r="C70" t="str">
             <v>RPRO-260122-1566</v>
           </cell>
@@ -8453,6 +8777,7 @@
           <cell r="A71" t="str">
             <v>S-2026-01-68</v>
           </cell>
+          <cell r="B71"/>
           <cell r="C71" t="str">
             <v>RPRO-260122-1567</v>
           </cell>
@@ -8521,6 +8846,7 @@
           <cell r="A72" t="str">
             <v>S-2026-01-69</v>
           </cell>
+          <cell r="B72"/>
           <cell r="C72" t="str">
             <v>RPRO-260122-1568</v>
           </cell>
@@ -8589,6 +8915,7 @@
           <cell r="A73" t="str">
             <v>S-2026-01-70</v>
           </cell>
+          <cell r="B73"/>
           <cell r="C73" t="str">
             <v>RPRO-260122-1569</v>
           </cell>
@@ -8657,6 +8984,7 @@
           <cell r="A74" t="str">
             <v>S-2026-01-71</v>
           </cell>
+          <cell r="B74"/>
           <cell r="C74" t="str">
             <v>RPRO-260122-1570</v>
           </cell>
@@ -8725,6 +9053,7 @@
           <cell r="A75" t="str">
             <v>S-2026-01-72</v>
           </cell>
+          <cell r="B75"/>
           <cell r="C75" t="str">
             <v>RPRO-260122-1571</v>
           </cell>
@@ -9006,6 +9335,7 @@
           <cell r="A79" t="str">
             <v>S-2026-01-76</v>
           </cell>
+          <cell r="B79"/>
           <cell r="C79" t="str">
             <v>RPRO-260122-1573</v>
           </cell>
@@ -9074,6 +9404,7 @@
           <cell r="A80" t="str">
             <v>S-2026-01-77</v>
           </cell>
+          <cell r="B80"/>
           <cell r="C80" t="str">
             <v>RPRO-260122-1574</v>
           </cell>
@@ -9142,6 +9473,7 @@
           <cell r="A81" t="str">
             <v>S-2026-01-78</v>
           </cell>
+          <cell r="B81"/>
           <cell r="C81" t="str">
             <v>RPRO-260122-1575</v>
           </cell>
@@ -9210,6 +9542,7 @@
           <cell r="A82" t="str">
             <v>S-2026-01-79</v>
           </cell>
+          <cell r="B82"/>
           <cell r="C82" t="str">
             <v>RPRO-260122-1576</v>
           </cell>
@@ -9278,6 +9611,7 @@
           <cell r="A83" t="str">
             <v>S-2026-01-80</v>
           </cell>
+          <cell r="B83"/>
           <cell r="C83" t="str">
             <v>RPRO-260122-1577</v>
           </cell>
@@ -9346,6 +9680,7 @@
           <cell r="A84" t="str">
             <v>S-2026-01-81</v>
           </cell>
+          <cell r="B84"/>
           <cell r="C84" t="str">
             <v>RPRO-260122-1578</v>
           </cell>
@@ -9414,6 +9749,7 @@
           <cell r="A85" t="str">
             <v>S-2026-01-82</v>
           </cell>
+          <cell r="B85"/>
           <cell r="C85" t="str">
             <v>RPRO-260122-1579</v>
           </cell>
@@ -9482,6 +9818,7 @@
           <cell r="A86" t="str">
             <v>S-2026-01-83</v>
           </cell>
+          <cell r="B86"/>
           <cell r="C86" t="str">
             <v>RPRO-260122-1580</v>
           </cell>
@@ -9553,6 +9890,7 @@
           <cell r="B87" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C87"/>
           <cell r="D87" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9621,6 +9959,7 @@
           <cell r="B88" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C88"/>
           <cell r="D88" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9689,6 +10028,7 @@
           <cell r="B89" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C89"/>
           <cell r="D89" t="str">
             <v>OV-0385</v>
           </cell>
@@ -9754,6 +10094,7 @@
           <cell r="A90" t="str">
             <v>S-2026-01-87</v>
           </cell>
+          <cell r="B90"/>
           <cell r="C90" t="str">
             <v>RPRO-260127-0875</v>
           </cell>
@@ -9822,6 +10163,7 @@
           <cell r="A91" t="str">
             <v>S-2026-01-88</v>
           </cell>
+          <cell r="B91"/>
           <cell r="C91" t="str">
             <v>RPRO-260127-0877</v>
           </cell>
@@ -9890,6 +10232,7 @@
           <cell r="A92" t="str">
             <v>S-2026-01-89</v>
           </cell>
+          <cell r="B92"/>
           <cell r="C92" t="str">
             <v>RPRO-260127-0879</v>
           </cell>
@@ -9958,6 +10301,7 @@
           <cell r="A93" t="str">
             <v>S-2026-01-90</v>
           </cell>
+          <cell r="B93"/>
           <cell r="C93" t="str">
             <v>RPRO-260128-1270</v>
           </cell>
@@ -10026,6 +10370,7 @@
           <cell r="A94" t="str">
             <v>S-2026-01-91</v>
           </cell>
+          <cell r="B94"/>
           <cell r="C94" t="str">
             <v>RPRO-260128-1271</v>
           </cell>
@@ -10094,6 +10439,7 @@
           <cell r="A95" t="str">
             <v>S-2026-01-92</v>
           </cell>
+          <cell r="B95"/>
           <cell r="C95" t="str">
             <v>RPRO-260128-1272</v>
           </cell>
@@ -10162,6 +10508,7 @@
           <cell r="A96" t="str">
             <v>S-2026-01-93</v>
           </cell>
+          <cell r="B96"/>
           <cell r="C96" t="str">
             <v>RPRO-260128-1273</v>
           </cell>
@@ -10230,6 +10577,7 @@
           <cell r="A97" t="str">
             <v>S-2026-01-94</v>
           </cell>
+          <cell r="B97"/>
           <cell r="C97" t="str">
             <v>RPRO-260128-1274</v>
           </cell>
@@ -10298,6 +10646,7 @@
           <cell r="A98" t="str">
             <v>S-2026-01-95</v>
           </cell>
+          <cell r="B98"/>
           <cell r="C98" t="str">
             <v>RPRO-260128-1275</v>
           </cell>
@@ -10366,6 +10715,7 @@
           <cell r="A99" t="str">
             <v>S-2026-01-96</v>
           </cell>
+          <cell r="B99"/>
           <cell r="C99" t="str">
             <v>RPRO-260128-1276</v>
           </cell>
@@ -10434,6 +10784,7 @@
           <cell r="A100" t="str">
             <v>S-2026-01-97</v>
           </cell>
+          <cell r="B100"/>
           <cell r="C100" t="str">
             <v>RPRO-260128-1277</v>
           </cell>
@@ -10502,6 +10853,7 @@
           <cell r="A101" t="str">
             <v>S-2026-01-98</v>
           </cell>
+          <cell r="B101"/>
           <cell r="C101" t="str">
             <v>RPRO-260129-0656</v>
           </cell>
@@ -10570,6 +10922,7 @@
           <cell r="A102" t="str">
             <v>S-2026-02-01</v>
           </cell>
+          <cell r="B102"/>
           <cell r="C102" t="str">
             <v>RPRO-260203-0021</v>
           </cell>
@@ -10638,6 +10991,7 @@
           <cell r="A103" t="str">
             <v>S-2026-02-02</v>
           </cell>
+          <cell r="B103"/>
           <cell r="C103" t="str">
             <v>RPRO-260203-0022</v>
           </cell>
@@ -10706,6 +11060,7 @@
           <cell r="A104" t="str">
             <v>S-2026-02-03</v>
           </cell>
+          <cell r="B104"/>
           <cell r="C104" t="str">
             <v>RPRO-260203-0770</v>
           </cell>
@@ -10774,6 +11129,7 @@
           <cell r="A105" t="str">
             <v>S-2026-02-04</v>
           </cell>
+          <cell r="B105"/>
           <cell r="C105" t="str">
             <v>RPRO-260203-0771</v>
           </cell>
@@ -10842,6 +11198,7 @@
           <cell r="A106" t="str">
             <v>S-2026-02-05</v>
           </cell>
+          <cell r="B106"/>
           <cell r="C106" t="str">
             <v>RPRO-260203-0772</v>
           </cell>
@@ -10910,6 +11267,7 @@
           <cell r="A107" t="str">
             <v>S-2026-02-06</v>
           </cell>
+          <cell r="B107"/>
           <cell r="C107" t="str">
             <v>RPRO-260203-0773</v>
           </cell>
@@ -10978,6 +11336,7 @@
           <cell r="A108" t="str">
             <v>S-2026-02-07</v>
           </cell>
+          <cell r="B108"/>
           <cell r="C108" t="str">
             <v>RPRO-260203-0774</v>
           </cell>
@@ -11046,6 +11405,7 @@
           <cell r="A109" t="str">
             <v>S-2026-02-08</v>
           </cell>
+          <cell r="B109"/>
           <cell r="C109" t="str">
             <v>RPRO-260203-0775</v>
           </cell>
@@ -11114,6 +11474,7 @@
           <cell r="A110" t="str">
             <v>S-2026-02-09</v>
           </cell>
+          <cell r="B110"/>
           <cell r="C110" t="str">
             <v>RPRO-260203-0776</v>
           </cell>
@@ -11182,6 +11543,7 @@
           <cell r="A111" t="str">
             <v>S-2026-02-10</v>
           </cell>
+          <cell r="B111"/>
           <cell r="C111" t="str">
             <v>RPRO-260203-0777</v>
           </cell>
@@ -11250,6 +11612,7 @@
           <cell r="A112" t="str">
             <v>S-2026-02-11</v>
           </cell>
+          <cell r="B112"/>
           <cell r="C112" t="str">
             <v>RPRO-260203-0778</v>
           </cell>
@@ -11318,6 +11681,7 @@
           <cell r="A113" t="str">
             <v>S-2026-02-12</v>
           </cell>
+          <cell r="B113"/>
           <cell r="C113" t="str">
             <v>RPRO-260203-0779</v>
           </cell>
@@ -11386,6 +11750,7 @@
           <cell r="A114" t="str">
             <v>S-2026-02-13</v>
           </cell>
+          <cell r="B114"/>
           <cell r="C114" t="str">
             <v>RPRO-260203-0780</v>
           </cell>
@@ -11454,6 +11819,7 @@
           <cell r="A115" t="str">
             <v>S-2026-02-14</v>
           </cell>
+          <cell r="B115"/>
           <cell r="C115" t="str">
             <v>RPRO-260203-0781</v>
           </cell>
@@ -11522,6 +11888,7 @@
           <cell r="A116" t="str">
             <v>S-2026-02-15</v>
           </cell>
+          <cell r="B116"/>
           <cell r="C116" t="str">
             <v>RPRO-260203-0782</v>
           </cell>
@@ -11590,6 +11957,7 @@
           <cell r="A117" t="str">
             <v>S-2026-02-16</v>
           </cell>
+          <cell r="B117"/>
           <cell r="C117" t="str">
             <v>RPRO-260203-0783</v>
           </cell>
@@ -11658,6 +12026,7 @@
           <cell r="A118" t="str">
             <v>S-2026-02-17</v>
           </cell>
+          <cell r="B118"/>
           <cell r="C118" t="str">
             <v>RPRO-260203-0784</v>
           </cell>
@@ -11726,6 +12095,7 @@
           <cell r="A119" t="str">
             <v>S-2026-02-18</v>
           </cell>
+          <cell r="B119"/>
           <cell r="C119" t="str">
             <v>RPRO-260204-0399</v>
           </cell>
@@ -11794,6 +12164,7 @@
           <cell r="A120" t="str">
             <v>S-2026-02-19</v>
           </cell>
+          <cell r="B120"/>
           <cell r="C120" t="str">
             <v>RPRO-260204-0400</v>
           </cell>
@@ -11862,6 +12233,7 @@
           <cell r="A121" t="str">
             <v>L-2026-02-20</v>
           </cell>
+          <cell r="B121"/>
           <cell r="C121" t="str">
             <v>RPRO-260204-0401</v>
           </cell>
@@ -11895,6 +12267,7 @@
           <cell r="M121" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N121"/>
           <cell r="O121" t="str">
             <v>Lab test</v>
           </cell>
@@ -11927,6 +12300,7 @@
           <cell r="A122" t="str">
             <v>L-2026-02-21</v>
           </cell>
+          <cell r="B122"/>
           <cell r="C122" t="str">
             <v>RPRO-260204-0402</v>
           </cell>
@@ -11960,6 +12334,7 @@
           <cell r="M122" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N122"/>
           <cell r="O122" t="str">
             <v>Lab test</v>
           </cell>
@@ -12063,6 +12438,7 @@
           <cell r="A124" t="str">
             <v>S-2026-02-23</v>
           </cell>
+          <cell r="B124"/>
           <cell r="C124" t="str">
             <v>RPRO-260210-0003</v>
           </cell>
@@ -12202,6 +12578,7 @@
           <cell r="A126" t="str">
             <v>S-2026-02-25</v>
           </cell>
+          <cell r="B126"/>
           <cell r="C126" t="str">
             <v>RPRO-260210-0005</v>
           </cell>
@@ -12270,6 +12647,7 @@
           <cell r="A127" t="str">
             <v>S-2026-02-26</v>
           </cell>
+          <cell r="B127"/>
           <cell r="C127" t="str">
             <v>RPRO-260210-0006</v>
           </cell>
@@ -12338,6 +12716,7 @@
           <cell r="A128" t="str">
             <v>S-2026-02-27</v>
           </cell>
+          <cell r="B128"/>
           <cell r="C128" t="str">
             <v>RPRO-260210-0007</v>
           </cell>
@@ -12406,6 +12785,7 @@
           <cell r="A129" t="str">
             <v>S-2026-02-28</v>
           </cell>
+          <cell r="B129"/>
           <cell r="C129" t="str">
             <v>RPRO-260210-0008</v>
           </cell>
@@ -12474,6 +12854,7 @@
           <cell r="A130" t="str">
             <v>S-2026-02-29</v>
           </cell>
+          <cell r="B130"/>
           <cell r="C130" t="str">
             <v>RPRO-260210-0009</v>
           </cell>
@@ -12542,6 +12923,7 @@
           <cell r="A131" t="str">
             <v>S-2026-02-30</v>
           </cell>
+          <cell r="B131"/>
           <cell r="C131" t="str">
             <v>RPRO-260210-0010</v>
           </cell>
@@ -12610,6 +12992,7 @@
           <cell r="A132" t="str">
             <v>S-2026-02-31</v>
           </cell>
+          <cell r="B132"/>
           <cell r="C132" t="str">
             <v>RPRO-260210-0011</v>
           </cell>
@@ -12679,6 +13062,7 @@
           <cell r="A133" t="str">
             <v>S-2026-02-32</v>
           </cell>
+          <cell r="B133"/>
           <cell r="C133" t="str">
             <v>RPRO-260210-0012</v>
           </cell>
@@ -12748,6 +13132,7 @@
           <cell r="A134" t="str">
             <v>S-2026-02-33</v>
           </cell>
+          <cell r="B134"/>
           <cell r="C134" t="str">
             <v>RPRO-260210-0013</v>
           </cell>
@@ -12816,6 +13201,7 @@
           <cell r="A135" t="str">
             <v>S-2026-02-34</v>
           </cell>
+          <cell r="B135"/>
           <cell r="C135" t="str">
             <v>RPRO-260211-0001</v>
           </cell>
@@ -12886,6 +13272,7 @@
           <cell r="A136" t="str">
             <v>S-2026-02-35</v>
           </cell>
+          <cell r="B136"/>
           <cell r="C136" t="str">
             <v>RPRO-260227-0335</v>
           </cell>
@@ -12954,6 +13341,7 @@
           <cell r="A137" t="str">
             <v>S-2026-02-36</v>
           </cell>
+          <cell r="B137"/>
           <cell r="C137" t="str">
             <v>RPRO-260227-0336</v>
           </cell>
@@ -13022,6 +13410,7 @@
           <cell r="A138" t="str">
             <v>S-2026-02-37</v>
           </cell>
+          <cell r="B138"/>
           <cell r="C138" t="str">
             <v>RPRO-260227-0337</v>
           </cell>
@@ -13090,6 +13479,7 @@
           <cell r="A139" t="str">
             <v>S-2026-02-38</v>
           </cell>
+          <cell r="B139"/>
           <cell r="C139" t="str">
             <v>RPRO-260227-0338</v>
           </cell>
@@ -13158,6 +13548,7 @@
           <cell r="A140" t="str">
             <v>S-2026-02-39</v>
           </cell>
+          <cell r="B140"/>
           <cell r="C140" t="str">
             <v>RPRO-260227-0339</v>
           </cell>
@@ -13226,6 +13617,7 @@
           <cell r="A141" t="str">
             <v>L-2026-02-40</v>
           </cell>
+          <cell r="B141"/>
           <cell r="C141" t="str">
             <v>RPRO-260227-0340</v>
           </cell>
@@ -13259,6 +13651,7 @@
           <cell r="M141" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N141"/>
           <cell r="O141" t="str">
             <v>Lab test</v>
           </cell>
@@ -13291,6 +13684,7 @@
           <cell r="A142" t="str">
             <v>S-2026-02-41</v>
           </cell>
+          <cell r="B142"/>
           <cell r="C142" t="str">
             <v>RPRO-260227-0341</v>
           </cell>
@@ -13359,6 +13753,7 @@
           <cell r="A143" t="str">
             <v>S-2026-02-42</v>
           </cell>
+          <cell r="B143"/>
           <cell r="C143" t="str">
             <v>RPRO-260227-0342</v>
           </cell>
@@ -13427,6 +13822,7 @@
           <cell r="A144" t="str">
             <v>S-2026-02-43</v>
           </cell>
+          <cell r="B144"/>
           <cell r="C144" t="str">
             <v>RPRO-260227-0343</v>
           </cell>
@@ -13495,6 +13891,7 @@
           <cell r="A145" t="str">
             <v>S-2026-02-44</v>
           </cell>
+          <cell r="B145"/>
           <cell r="C145" t="str">
             <v>RPRO-260227-0344</v>
           </cell>
@@ -13563,6 +13960,7 @@
           <cell r="A146" t="str">
             <v>S-2026-02-45</v>
           </cell>
+          <cell r="B146"/>
           <cell r="C146" t="str">
             <v>RPRO-260227-0345</v>
           </cell>
@@ -13702,6 +14100,7 @@
           <cell r="A148" t="str">
             <v>S-2026-02-47</v>
           </cell>
+          <cell r="B148"/>
           <cell r="C148" t="str">
             <v>RPRO-260227-0347</v>
           </cell>
@@ -13770,6 +14169,7 @@
           <cell r="A149" t="str">
             <v>S-2026-02-48</v>
           </cell>
+          <cell r="B149"/>
           <cell r="C149" t="str">
             <v>RPRO-260227-0348</v>
           </cell>
@@ -13838,6 +14238,7 @@
           <cell r="A150" t="str">
             <v>S-2026-02-49</v>
           </cell>
+          <cell r="B150"/>
           <cell r="C150" t="str">
             <v>RPRO-260302-0004</v>
           </cell>
@@ -13906,6 +14307,7 @@
           <cell r="A151" t="str">
             <v>S-2026-02-50</v>
           </cell>
+          <cell r="B151"/>
           <cell r="C151" t="str">
             <v>RPRO-260227-0349</v>
           </cell>
@@ -13974,6 +14376,7 @@
           <cell r="A152" t="str">
             <v>S-2026-02-51</v>
           </cell>
+          <cell r="B152"/>
           <cell r="C152" t="str">
             <v>RPRO-260227-0350</v>
           </cell>
@@ -14042,6 +14445,7 @@
           <cell r="A153" t="str">
             <v>S-2026-02-52</v>
           </cell>
+          <cell r="B153"/>
           <cell r="C153" t="str">
             <v>RPRO-260227-0351</v>
           </cell>
@@ -14110,6 +14514,7 @@
           <cell r="A154" t="str">
             <v>S-2026-02-53</v>
           </cell>
+          <cell r="B154"/>
           <cell r="C154" t="str">
             <v>RPRO-260227-0352</v>
           </cell>
@@ -14178,6 +14583,7 @@
           <cell r="A155" t="str">
             <v>L-2026-03-01</v>
           </cell>
+          <cell r="B155"/>
           <cell r="C155" t="str">
             <v>RPRO-260303-0005</v>
           </cell>
@@ -14211,6 +14617,7 @@
           <cell r="M155" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N155"/>
           <cell r="O155" t="str">
             <v>Lab test</v>
           </cell>
@@ -14243,6 +14650,7 @@
           <cell r="A156" t="str">
             <v>L-2026-03-02</v>
           </cell>
+          <cell r="B156"/>
           <cell r="C156" t="str">
             <v>RPRO-260303-0006</v>
           </cell>
@@ -14276,6 +14684,7 @@
           <cell r="M156" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N156"/>
           <cell r="O156" t="str">
             <v>Lab test</v>
           </cell>
@@ -14592,6 +15001,7 @@
           <cell r="A161" t="str">
             <v>S-2026-03-07</v>
           </cell>
+          <cell r="B161"/>
           <cell r="C161" t="str">
             <v>RPRO-260303-0011</v>
           </cell>
@@ -14660,6 +15070,7 @@
           <cell r="A162" t="str">
             <v>S-2026-03-08</v>
           </cell>
+          <cell r="B162"/>
           <cell r="C162" t="str">
             <v>RPRO-260303-0012</v>
           </cell>
@@ -14728,6 +15139,7 @@
           <cell r="A163" t="str">
             <v>S-2026-03-09</v>
           </cell>
+          <cell r="B163"/>
           <cell r="C163" t="str">
             <v>RPRO-260303-0013</v>
           </cell>
@@ -14796,6 +15208,7 @@
           <cell r="A164" t="str">
             <v>S-2026-03-10</v>
           </cell>
+          <cell r="B164"/>
           <cell r="C164" t="str">
             <v>RPRO-260303-0014</v>
           </cell>
@@ -14864,6 +15277,7 @@
           <cell r="A165" t="str">
             <v>S-2026-03-11</v>
           </cell>
+          <cell r="B165"/>
           <cell r="C165" t="str">
             <v>RPRO-260313-0139</v>
           </cell>
@@ -14897,6 +15311,7 @@
           <cell r="M165" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N165"/>
           <cell r="O165" t="str">
             <v>Sample</v>
           </cell>
@@ -14929,6 +15344,7 @@
           <cell r="A166" t="str">
             <v>S-2026-03-12</v>
           </cell>
+          <cell r="B166"/>
           <cell r="C166" t="str">
             <v>RPRO-260313-0140</v>
           </cell>
@@ -14962,6 +15378,7 @@
           <cell r="M166" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N166"/>
           <cell r="O166" t="str">
             <v>Sample</v>
           </cell>
@@ -14994,6 +15411,7 @@
           <cell r="A167" t="str">
             <v>S-2026-03-13</v>
           </cell>
+          <cell r="B167"/>
           <cell r="C167" t="str">
             <v>RPRO-260313-0141</v>
           </cell>
@@ -15027,6 +15445,7 @@
           <cell r="M167" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N167"/>
           <cell r="O167" t="str">
             <v>Sample</v>
           </cell>
@@ -15130,6 +15549,7 @@
           <cell r="A169" t="str">
             <v>S-2026-03-15</v>
           </cell>
+          <cell r="B169"/>
           <cell r="C169" t="str">
             <v>RPRO-260306-1547</v>
           </cell>
@@ -15198,6 +15618,7 @@
           <cell r="A170" t="str">
             <v>S-2026-03-16</v>
           </cell>
+          <cell r="B170"/>
           <cell r="C170" t="str">
             <v>RPRO-260306-1548</v>
           </cell>
@@ -15266,6 +15687,7 @@
           <cell r="A171" t="str">
             <v>S-2026-03-17</v>
           </cell>
+          <cell r="B171"/>
           <cell r="C171" t="str">
             <v>RPRO-260306-1549</v>
           </cell>
@@ -15334,6 +15756,7 @@
           <cell r="A172" t="str">
             <v>S-2026-03-18</v>
           </cell>
+          <cell r="B172"/>
           <cell r="C172" t="str">
             <v>RPRO-260306-1550</v>
           </cell>
@@ -15402,6 +15825,7 @@
           <cell r="A173" t="str">
             <v>S-2026-03-19</v>
           </cell>
+          <cell r="B173"/>
           <cell r="C173" t="str">
             <v>RPRO-260306-1551</v>
           </cell>
@@ -15470,6 +15894,7 @@
           <cell r="A174" t="str">
             <v>S-2026-03-20</v>
           </cell>
+          <cell r="B174"/>
           <cell r="C174" t="str">
             <v>RPRO-260306-1552</v>
           </cell>
@@ -15538,6 +15963,7 @@
           <cell r="A175" t="str">
             <v>S-2026-03-21</v>
           </cell>
+          <cell r="B175"/>
           <cell r="C175" t="str">
             <v>RPRO-260306-1553</v>
           </cell>
@@ -15606,6 +16032,7 @@
           <cell r="A176" t="str">
             <v>S-2026-03-22</v>
           </cell>
+          <cell r="B176"/>
           <cell r="C176" t="str">
             <v>RPRO-260306-1554</v>
           </cell>
@@ -15674,6 +16101,7 @@
           <cell r="A177" t="str">
             <v>S-2026-03-23</v>
           </cell>
+          <cell r="B177"/>
           <cell r="C177" t="str">
             <v>RPRO-260306-1555</v>
           </cell>
@@ -15742,6 +16170,7 @@
           <cell r="A178" t="str">
             <v>S-2026-03-24</v>
           </cell>
+          <cell r="B178"/>
           <cell r="C178" t="str">
             <v>RPRO-260306-1556</v>
           </cell>
@@ -15881,6 +16310,7 @@
           <cell r="A180" t="str">
             <v>L-2026-03-26</v>
           </cell>
+          <cell r="B180"/>
           <cell r="C180" t="str">
             <v>RPRO-260305-1288</v>
           </cell>
@@ -15914,6 +16344,7 @@
           <cell r="M180" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N180"/>
           <cell r="O180" t="str">
             <v>Lab test</v>
           </cell>
@@ -16017,6 +16448,7 @@
           <cell r="A182" t="str">
             <v>S-2026-03-28</v>
           </cell>
+          <cell r="B182"/>
           <cell r="C182" t="str">
             <v>RPRO-260306-1559</v>
           </cell>
@@ -16085,6 +16517,7 @@
           <cell r="A183" t="str">
             <v>S-2026-03-29</v>
           </cell>
+          <cell r="B183"/>
           <cell r="C183" t="str">
             <v>RPRO-260306-1560</v>
           </cell>
@@ -16153,6 +16586,7 @@
           <cell r="A184" t="str">
             <v>S-2026-03-30</v>
           </cell>
+          <cell r="B184"/>
           <cell r="C184" t="str">
             <v>RPRO-260306-1561</v>
           </cell>
@@ -16221,6 +16655,7 @@
           <cell r="A185" t="str">
             <v>S-2026-03-31</v>
           </cell>
+          <cell r="B185"/>
           <cell r="C185" t="str">
             <v>RPRO-260306-1562</v>
           </cell>
@@ -16289,6 +16724,7 @@
           <cell r="A186" t="str">
             <v>S-2026-03-32</v>
           </cell>
+          <cell r="B186"/>
           <cell r="C186" t="str">
             <v>RPRO-260306-1563</v>
           </cell>
@@ -16357,6 +16793,7 @@
           <cell r="A187" t="str">
             <v>S-2026-03-33</v>
           </cell>
+          <cell r="B187"/>
           <cell r="C187" t="str">
             <v>RPRO-260306-1564</v>
           </cell>
@@ -16425,6 +16862,7 @@
           <cell r="A188" t="str">
             <v>S-2026-03-34</v>
           </cell>
+          <cell r="B188"/>
           <cell r="C188" t="str">
             <v>RPRO-260306-1565</v>
           </cell>
@@ -16493,6 +16931,7 @@
           <cell r="A189" t="str">
             <v>S-2026-03-35</v>
           </cell>
+          <cell r="B189"/>
           <cell r="C189" t="str">
             <v>RPRO-260306-1566</v>
           </cell>
@@ -16561,6 +17000,7 @@
           <cell r="A190" t="str">
             <v>S-2026-03-36</v>
           </cell>
+          <cell r="B190"/>
           <cell r="C190" t="str">
             <v>RPRO-260307-0080</v>
           </cell>
@@ -16629,6 +17069,7 @@
           <cell r="A191" t="str">
             <v>S-2026-03-37</v>
           </cell>
+          <cell r="B191"/>
           <cell r="C191" t="str">
             <v>RPRO-260306-1736</v>
           </cell>
@@ -16697,6 +17138,7 @@
           <cell r="A192" t="str">
             <v>S-2026-03-38</v>
           </cell>
+          <cell r="B192"/>
           <cell r="C192" t="str">
             <v>RPRO-260306-1737</v>
           </cell>
@@ -16765,6 +17207,7 @@
           <cell r="A193" t="str">
             <v>S-2026-03-39</v>
           </cell>
+          <cell r="B193"/>
           <cell r="C193" t="str">
             <v>RPRO-260306-1738</v>
           </cell>
@@ -16833,6 +17276,7 @@
           <cell r="A194" t="str">
             <v>S-2026-03-40</v>
           </cell>
+          <cell r="B194"/>
           <cell r="C194" t="str">
             <v>RPRO-260306-1739</v>
           </cell>
@@ -16901,6 +17345,7 @@
           <cell r="A195" t="str">
             <v>S-2026-03-41</v>
           </cell>
+          <cell r="B195"/>
           <cell r="C195" t="str">
             <v>RPRO-260306-1740</v>
           </cell>
@@ -16969,6 +17414,7 @@
           <cell r="A196" t="str">
             <v>S-2026-03-42</v>
           </cell>
+          <cell r="B196"/>
           <cell r="C196" t="str">
             <v>RPRO-260307-0081</v>
           </cell>
@@ -17037,6 +17483,7 @@
           <cell r="A197" t="str">
             <v>S-2026-03-43</v>
           </cell>
+          <cell r="B197"/>
           <cell r="C197" t="str">
             <v>RPRO-260307-0082</v>
           </cell>
@@ -17105,6 +17552,7 @@
           <cell r="A198" t="str">
             <v>S-2026-03-44</v>
           </cell>
+          <cell r="B198"/>
           <cell r="C198" t="str">
             <v>RPRO-260307-0083</v>
           </cell>
@@ -17173,6 +17621,7 @@
           <cell r="A199" t="str">
             <v>S-2026-03-45</v>
           </cell>
+          <cell r="B199"/>
           <cell r="C199" t="str">
             <v>RPRO-260307-0084</v>
           </cell>
@@ -17241,6 +17690,7 @@
           <cell r="A200" t="str">
             <v>S-2026-03-46</v>
           </cell>
+          <cell r="B200"/>
           <cell r="C200" t="str">
             <v>RPRO-260307-0085</v>
           </cell>
@@ -17309,6 +17759,7 @@
           <cell r="A201" t="str">
             <v>S-2026-03-47</v>
           </cell>
+          <cell r="B201"/>
           <cell r="C201" t="str">
             <v>RPRO-260310-0362</v>
           </cell>
@@ -17448,6 +17899,7 @@
           <cell r="A203" t="str">
             <v>S-2026-03-49</v>
           </cell>
+          <cell r="B203"/>
           <cell r="C203" t="str">
             <v>RPRO-260310-0364</v>
           </cell>
@@ -17516,6 +17968,7 @@
           <cell r="A204" t="str">
             <v>S-2026-03-50</v>
           </cell>
+          <cell r="B204"/>
           <cell r="C204" t="str">
             <v>RPRO-260310-0365</v>
           </cell>
@@ -17655,6 +18108,7 @@
           <cell r="A206" t="str">
             <v>S-2026-03-52</v>
           </cell>
+          <cell r="B206"/>
           <cell r="C206" t="str">
             <v>RPRO-260310-0367</v>
           </cell>
@@ -17723,6 +18177,7 @@
           <cell r="A207" t="str">
             <v>S-2026-03-53</v>
           </cell>
+          <cell r="B207"/>
           <cell r="C207" t="str">
             <v>RPRO-260310-0368</v>
           </cell>
@@ -17791,6 +18246,7 @@
           <cell r="A208" t="str">
             <v>S-2026-03-54</v>
           </cell>
+          <cell r="B208"/>
           <cell r="C208" t="str">
             <v>RPRO-260310-0369</v>
           </cell>
@@ -17859,6 +18315,7 @@
           <cell r="A209" t="str">
             <v>S-2026-03-55</v>
           </cell>
+          <cell r="B209"/>
           <cell r="C209" t="str">
             <v>RPRO-260310-0370</v>
           </cell>
@@ -17927,6 +18384,7 @@
           <cell r="A210" t="str">
             <v>S-2026-03-56</v>
           </cell>
+          <cell r="B210"/>
           <cell r="C210" t="str">
             <v>RPRO-260310-0371</v>
           </cell>
@@ -17995,6 +18453,7 @@
           <cell r="A211" t="str">
             <v>S-2026-03-57</v>
           </cell>
+          <cell r="B211"/>
           <cell r="C211" t="str">
             <v>RPRO-260310-0372</v>
           </cell>
@@ -18063,6 +18522,7 @@
           <cell r="A212" t="str">
             <v>S-2026-03-58</v>
           </cell>
+          <cell r="B212"/>
           <cell r="C212" t="str">
             <v>RPRO-260310-0373</v>
           </cell>
@@ -18131,6 +18591,7 @@
           <cell r="A213" t="str">
             <v>S-2026-03-59</v>
           </cell>
+          <cell r="B213"/>
           <cell r="C213" t="str">
             <v>RPRO-260310-0374</v>
           </cell>
@@ -18199,6 +18660,7 @@
           <cell r="A214" t="str">
             <v>S-2026-03-60</v>
           </cell>
+          <cell r="B214"/>
           <cell r="C214" t="str">
             <v>RPRO-260310-0375</v>
           </cell>
@@ -18267,6 +18729,7 @@
           <cell r="A215" t="str">
             <v>S-2026-03-61</v>
           </cell>
+          <cell r="B215"/>
           <cell r="C215" t="str">
             <v>RPRO-260310-0376</v>
           </cell>
@@ -18338,6 +18801,7 @@
           <cell r="B216" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C216"/>
           <cell r="D216" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -18368,6 +18832,7 @@
           <cell r="M216" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N216"/>
           <cell r="O216" t="str">
             <v>Lab test</v>
           </cell>
@@ -18403,6 +18868,7 @@
           <cell r="B217" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C217"/>
           <cell r="D217" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -18433,6 +18899,7 @@
           <cell r="M217" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N217"/>
           <cell r="O217" t="str">
             <v>Lab test</v>
           </cell>
@@ -18465,6 +18932,7 @@
           <cell r="A218" t="str">
             <v>S-2026-03-64</v>
           </cell>
+          <cell r="B218"/>
           <cell r="C218" t="str">
             <v>RPRO-260313-0142</v>
           </cell>
@@ -18533,6 +19001,7 @@
           <cell r="A219" t="str">
             <v>S-2026-03-65</v>
           </cell>
+          <cell r="B219"/>
           <cell r="C219" t="str">
             <v>RPRO-260313-0143</v>
           </cell>
@@ -18601,6 +19070,7 @@
           <cell r="A220" t="str">
             <v>S-2026-03-66</v>
           </cell>
+          <cell r="B220"/>
           <cell r="C220" t="str">
             <v>RPRO-260313-0144</v>
           </cell>
@@ -18669,6 +19139,7 @@
           <cell r="A221" t="str">
             <v>S-2026-03-67</v>
           </cell>
+          <cell r="B221"/>
           <cell r="C221" t="str">
             <v>RPRO-260313-0145</v>
           </cell>
@@ -18737,6 +19208,7 @@
           <cell r="A222" t="str">
             <v>S-2026-03-68</v>
           </cell>
+          <cell r="B222"/>
           <cell r="C222" t="str">
             <v>RPRO-260313-0146</v>
           </cell>
@@ -18805,6 +19277,7 @@
           <cell r="A223" t="str">
             <v>S-2026-03-69</v>
           </cell>
+          <cell r="B223"/>
           <cell r="C223" t="str">
             <v>RPRO-260313-0147</v>
           </cell>
@@ -18873,6 +19346,7 @@
           <cell r="A224" t="str">
             <v>S-2026-03-70</v>
           </cell>
+          <cell r="B224"/>
           <cell r="C224" t="str">
             <v>RPRO-260313-0148</v>
           </cell>
@@ -18941,6 +19415,7 @@
           <cell r="A225" t="str">
             <v>S-2026-03-71</v>
           </cell>
+          <cell r="B225"/>
           <cell r="C225" t="str">
             <v>RPRO-260313-0149</v>
           </cell>
@@ -19009,6 +19484,7 @@
           <cell r="A226" t="str">
             <v>S-2026-03-72</v>
           </cell>
+          <cell r="B226"/>
           <cell r="C226" t="str">
             <v>RPRO-260313-0150</v>
           </cell>
@@ -19077,6 +19553,7 @@
           <cell r="A227" t="str">
             <v>S-2026-03-73</v>
           </cell>
+          <cell r="B227"/>
           <cell r="C227" t="str">
             <v>RPRO-260313-0151</v>
           </cell>
@@ -19145,6 +19622,7 @@
           <cell r="A228" t="str">
             <v>S-2026-03-74</v>
           </cell>
+          <cell r="B228"/>
           <cell r="C228" t="str">
             <v>RPRO-260313-0152</v>
           </cell>
@@ -19213,6 +19691,7 @@
           <cell r="A229" t="str">
             <v>S-2026-03-75</v>
           </cell>
+          <cell r="B229"/>
           <cell r="C229" t="str">
             <v>RPRO-260313-0318</v>
           </cell>
@@ -19281,6 +19760,7 @@
           <cell r="A230" t="str">
             <v>S-2026-03-76</v>
           </cell>
+          <cell r="B230"/>
           <cell r="C230" t="str">
             <v>RPRO-260313-0319</v>
           </cell>
@@ -19349,6 +19829,7 @@
           <cell r="A231" t="str">
             <v>S-2026-03-77</v>
           </cell>
+          <cell r="B231"/>
           <cell r="C231" t="str">
             <v>RPRO-260314-0198</v>
           </cell>
@@ -19417,6 +19898,7 @@
           <cell r="A232" t="str">
             <v>S-2026-03-78</v>
           </cell>
+          <cell r="B232"/>
           <cell r="C232" t="str">
             <v>RPRO-260314-0199</v>
           </cell>
@@ -19485,6 +19967,7 @@
           <cell r="A233" t="str">
             <v>S-2026-03-79</v>
           </cell>
+          <cell r="B233"/>
           <cell r="C233" t="str">
             <v>RPRO-260317-0628</v>
           </cell>
@@ -19553,6 +20036,7 @@
           <cell r="A234" t="str">
             <v>S-2026-03-80</v>
           </cell>
+          <cell r="B234"/>
           <cell r="C234" t="str">
             <v>RPRO-260317-0629</v>
           </cell>
@@ -19621,6 +20105,7 @@
           <cell r="A235" t="str">
             <v>S-2026-03-81</v>
           </cell>
+          <cell r="B235"/>
           <cell r="C235" t="str">
             <v>RPRO-260317-0630</v>
           </cell>
@@ -19689,6 +20174,7 @@
           <cell r="A236" t="str">
             <v>S-2026-03-82</v>
           </cell>
+          <cell r="B236"/>
           <cell r="C236" t="str">
             <v>RPRO-260317-0631</v>
           </cell>
@@ -19757,6 +20243,7 @@
           <cell r="A237" t="str">
             <v>S-2026-03-83</v>
           </cell>
+          <cell r="B237"/>
           <cell r="C237" t="str">
             <v>RPRO-260317-0632</v>
           </cell>
@@ -19825,6 +20312,7 @@
           <cell r="A238" t="str">
             <v>S-2026-03-84</v>
           </cell>
+          <cell r="B238"/>
           <cell r="C238" t="str">
             <v>RPRO-260317-0633</v>
           </cell>
@@ -19893,6 +20381,7 @@
           <cell r="A239" t="str">
             <v>S-2026-03-85</v>
           </cell>
+          <cell r="B239"/>
           <cell r="C239" t="str">
             <v>RPRO-260317-0634</v>
           </cell>
@@ -19961,6 +20450,7 @@
           <cell r="A240" t="str">
             <v>S-2026-03-86</v>
           </cell>
+          <cell r="B240"/>
           <cell r="C240" t="str">
             <v>RPRO-260317-0635</v>
           </cell>
@@ -20029,6 +20519,7 @@
           <cell r="A241" t="str">
             <v>S-2026-03-87</v>
           </cell>
+          <cell r="B241"/>
           <cell r="C241" t="str">
             <v>RPRO-260317-0636</v>
           </cell>
@@ -20097,6 +20588,7 @@
           <cell r="A242" t="str">
             <v>L-2026-03-88</v>
           </cell>
+          <cell r="B242"/>
           <cell r="C242" t="str">
             <v>RPRO-260317-0637</v>
           </cell>
@@ -20130,6 +20622,7 @@
           <cell r="M242" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N242"/>
           <cell r="O242" t="str">
             <v>Lab test</v>
           </cell>
@@ -20198,6 +20691,7 @@
           <cell r="M243" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N243"/>
           <cell r="O243" t="str">
             <v>Lab test</v>
           </cell>
@@ -20230,6 +20724,7 @@
           <cell r="A244" t="str">
             <v>S-2026-03-90</v>
           </cell>
+          <cell r="B244"/>
           <cell r="C244" t="str">
             <v>RPRO-260317-0639</v>
           </cell>
@@ -20298,6 +20793,7 @@
           <cell r="A245" t="str">
             <v>S-2026-03-91</v>
           </cell>
+          <cell r="B245"/>
           <cell r="C245" t="str">
             <v>RPRO-260317-0640</v>
           </cell>
@@ -20366,6 +20862,7 @@
           <cell r="A246" t="str">
             <v>S-2026-03-92</v>
           </cell>
+          <cell r="B246"/>
           <cell r="C246" t="str">
             <v>RPRO-260317-0641</v>
           </cell>
@@ -20434,6 +20931,7 @@
           <cell r="A247" t="str">
             <v>L-2026-03-93</v>
           </cell>
+          <cell r="B247"/>
           <cell r="C247" t="str">
             <v>RPRO-260318-0477</v>
           </cell>
@@ -20467,6 +20965,7 @@
           <cell r="M247" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N247"/>
           <cell r="O247" t="str">
             <v>Lab test</v>
           </cell>
@@ -20499,6 +20998,7 @@
           <cell r="A248" t="str">
             <v>L-2026-03-94</v>
           </cell>
+          <cell r="B248"/>
           <cell r="C248" t="str">
             <v>RPRO-260318-0478</v>
           </cell>
@@ -20532,6 +21032,7 @@
           <cell r="M248" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N248"/>
           <cell r="O248" t="str">
             <v>Lab test</v>
           </cell>
@@ -20635,6 +21136,7 @@
           <cell r="A250" t="str">
             <v>S-2026-03-96</v>
           </cell>
+          <cell r="B250"/>
           <cell r="C250" t="str">
             <v>RPRO-260318-0482</v>
           </cell>
@@ -20703,6 +21205,7 @@
           <cell r="A251" t="str">
             <v>S-2026-03-97</v>
           </cell>
+          <cell r="B251"/>
           <cell r="C251" t="str">
             <v>RPRO-260324-0278</v>
           </cell>
@@ -20771,6 +21274,7 @@
           <cell r="A252" t="str">
             <v>S-2026-03-98</v>
           </cell>
+          <cell r="B252"/>
           <cell r="C252" t="str">
             <v>RPRO-260324-0279</v>
           </cell>
@@ -20910,6 +21414,7 @@
           <cell r="A254" t="str">
             <v>S-2026-03-100</v>
           </cell>
+          <cell r="B254"/>
           <cell r="C254" t="str">
             <v>RPRO-260324-0281</v>
           </cell>
@@ -20978,6 +21483,7 @@
           <cell r="A255" t="str">
             <v>S-2026-03-101</v>
           </cell>
+          <cell r="B255"/>
           <cell r="C255" t="str">
             <v>RPRO-260324-0282</v>
           </cell>
@@ -21046,6 +21552,7 @@
           <cell r="A256" t="str">
             <v>S-2026-03-102</v>
           </cell>
+          <cell r="B256"/>
           <cell r="C256" t="str">
             <v>RPRO-260324-0531</v>
           </cell>
@@ -21114,6 +21621,7 @@
           <cell r="A257" t="str">
             <v>S-2026-03-103</v>
           </cell>
+          <cell r="B257"/>
           <cell r="C257" t="str">
             <v>RPRO-260324-0283</v>
           </cell>
@@ -21182,6 +21690,7 @@
           <cell r="A258" t="str">
             <v>S-2026-03-104</v>
           </cell>
+          <cell r="B258"/>
           <cell r="C258" t="str">
             <v>RPRO-260324-0284</v>
           </cell>
@@ -21250,6 +21759,7 @@
           <cell r="A259" t="str">
             <v>L-2026-03-105</v>
           </cell>
+          <cell r="B259"/>
           <cell r="C259" t="str">
             <v>RPRO-260321-0027</v>
           </cell>
@@ -21283,6 +21793,7 @@
           <cell r="M259" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N259"/>
           <cell r="O259" t="str">
             <v>Lab test</v>
           </cell>
@@ -21315,6 +21826,7 @@
           <cell r="A260" t="str">
             <v>L-2026-03-106</v>
           </cell>
+          <cell r="B260"/>
           <cell r="C260" t="str">
             <v>RPRO-260321-0028</v>
           </cell>
@@ -21348,6 +21860,7 @@
           <cell r="M260" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N260"/>
           <cell r="O260" t="str">
             <v>Lab test</v>
           </cell>
@@ -21380,6 +21893,7 @@
           <cell r="A261" t="str">
             <v>S-2026-03-107</v>
           </cell>
+          <cell r="B261"/>
           <cell r="C261" t="str">
             <v>RPRO-260321-0029</v>
           </cell>
@@ -21448,6 +21962,7 @@
           <cell r="A262" t="str">
             <v>S-2026-03-108</v>
           </cell>
+          <cell r="B262"/>
           <cell r="C262" t="str">
             <v>RPRO-260324-0285</v>
           </cell>
@@ -21516,6 +22031,7 @@
           <cell r="A263" t="str">
             <v>L-2026-03-109</v>
           </cell>
+          <cell r="B263"/>
           <cell r="C263" t="str">
             <v>RPRO-260324-0286</v>
           </cell>
@@ -21543,9 +22059,11 @@
           <cell r="K263">
             <v>0</v>
           </cell>
+          <cell r="L263"/>
           <cell r="M263" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N263"/>
           <cell r="O263" t="str">
             <v>Lab test</v>
           </cell>
@@ -21578,6 +22096,7 @@
           <cell r="A264" t="str">
             <v>S-2026-03-110</v>
           </cell>
+          <cell r="B264"/>
           <cell r="C264" t="str">
             <v>RPRO-260324-0287</v>
           </cell>
@@ -21646,6 +22165,7 @@
           <cell r="A265" t="str">
             <v>S-2026-03-111</v>
           </cell>
+          <cell r="B265"/>
           <cell r="C265" t="str">
             <v>RPRO-260324-0288</v>
           </cell>
@@ -21714,6 +22234,7 @@
           <cell r="A266" t="str">
             <v>S-2026-03-112</v>
           </cell>
+          <cell r="B266"/>
           <cell r="C266" t="str">
             <v>RPRO-260324-0289</v>
           </cell>
@@ -21782,6 +22303,7 @@
           <cell r="A267" t="str">
             <v>S-2026-03-113</v>
           </cell>
+          <cell r="B267"/>
           <cell r="C267" t="str">
             <v>RPRO-260324-0532</v>
           </cell>
@@ -21850,6 +22372,7 @@
           <cell r="A268" t="str">
             <v>S-2026-03-114</v>
           </cell>
+          <cell r="B268"/>
           <cell r="C268" t="str">
             <v>RPRO-260324-0533</v>
           </cell>
@@ -21918,6 +22441,7 @@
           <cell r="A269" t="str">
             <v>S-2026-03-115</v>
           </cell>
+          <cell r="B269"/>
           <cell r="C269" t="str">
             <v>RPRO-260324-0534</v>
           </cell>
@@ -21986,6 +22510,7 @@
           <cell r="A270" t="str">
             <v>S-2026-03-116</v>
           </cell>
+          <cell r="B270"/>
           <cell r="C270" t="str">
             <v>RPRO-260325-0407</v>
           </cell>
@@ -22054,6 +22579,7 @@
           <cell r="A271" t="str">
             <v>S-2026-03-117</v>
           </cell>
+          <cell r="B271"/>
           <cell r="C271" t="str">
             <v>RPRO-260325-0408</v>
           </cell>
@@ -22122,6 +22648,7 @@
           <cell r="A272" t="str">
             <v>S-2026-03-118</v>
           </cell>
+          <cell r="B272"/>
           <cell r="C272" t="str">
             <v>RPRO-260325-0409</v>
           </cell>
@@ -22190,6 +22717,7 @@
           <cell r="A273" t="str">
             <v>S-2026-03-119</v>
           </cell>
+          <cell r="B273"/>
           <cell r="C273" t="str">
             <v>RPRO-260325-0410</v>
           </cell>
@@ -22258,6 +22786,7 @@
           <cell r="A274" t="str">
             <v>S-2026-03-120</v>
           </cell>
+          <cell r="B274"/>
           <cell r="C274" t="str">
             <v>RPRO-260325-0411</v>
           </cell>
@@ -22326,6 +22855,7 @@
           <cell r="A275" t="str">
             <v>S-2026-03-121</v>
           </cell>
+          <cell r="B275"/>
           <cell r="C275" t="str">
             <v>RPRO-260325-0412</v>
           </cell>
@@ -22394,6 +22924,7 @@
           <cell r="A276" t="str">
             <v>S-2026-03-122</v>
           </cell>
+          <cell r="B276"/>
           <cell r="C276" t="str">
             <v>RPRO-260325-0413</v>
           </cell>
@@ -22462,6 +22993,7 @@
           <cell r="A277" t="str">
             <v>S-2026-03-123</v>
           </cell>
+          <cell r="B277"/>
           <cell r="C277" t="str">
             <v>RPRO-260325-0414</v>
           </cell>
@@ -22530,6 +23062,7 @@
           <cell r="A278" t="str">
             <v>S-2026-03-124</v>
           </cell>
+          <cell r="B278"/>
           <cell r="C278" t="str">
             <v>RPRO-260325-0415</v>
           </cell>
@@ -22669,6 +23202,7 @@
           <cell r="A280" t="str">
             <v>S-2026-03-126</v>
           </cell>
+          <cell r="B280"/>
           <cell r="C280" t="str">
             <v>RPRO-260325-0417</v>
           </cell>
@@ -22737,6 +23271,7 @@
           <cell r="A281" t="str">
             <v>S-2026-03-127</v>
           </cell>
+          <cell r="B281"/>
           <cell r="C281" t="str">
             <v>RPRO-260325-0418</v>
           </cell>
@@ -22805,6 +23340,7 @@
           <cell r="A282" t="str">
             <v>S-2026-03-128</v>
           </cell>
+          <cell r="B282"/>
           <cell r="C282" t="str">
             <v>RPRO-260325-0419</v>
           </cell>
@@ -22873,6 +23409,7 @@
           <cell r="A283" t="str">
             <v>S-2026-03-129</v>
           </cell>
+          <cell r="B283"/>
           <cell r="C283" t="str">
             <v>RPRO-260325-0421</v>
           </cell>
@@ -22941,6 +23478,7 @@
           <cell r="A284" t="str">
             <v>S-2026-03-130</v>
           </cell>
+          <cell r="B284"/>
           <cell r="C284" t="str">
             <v>RPRO-260327-0930</v>
           </cell>
@@ -23151,6 +23689,7 @@
           <cell r="A287" t="str">
             <v>S-2026-03-133</v>
           </cell>
+          <cell r="B287"/>
           <cell r="C287" t="str">
             <v>RPRO-260327-0933</v>
           </cell>
@@ -23219,6 +23758,7 @@
           <cell r="A288" t="str">
             <v>S-2026-03-134</v>
           </cell>
+          <cell r="B288"/>
           <cell r="C288" t="str">
             <v>RPRO-260327-0934</v>
           </cell>
@@ -23429,6 +23969,7 @@
           <cell r="A291" t="str">
             <v>S-2026-03-137</v>
           </cell>
+          <cell r="B291"/>
           <cell r="C291" t="str">
             <v>RPRO-260327-0937</v>
           </cell>
@@ -23568,6 +24109,7 @@
           <cell r="A293" t="str">
             <v>S-2026-03-139</v>
           </cell>
+          <cell r="B293"/>
           <cell r="C293" t="str">
             <v>RPRO-260327-0939</v>
           </cell>
@@ -23707,6 +24249,7 @@
           <cell r="A295" t="str">
             <v>S-2026-03-141</v>
           </cell>
+          <cell r="B295"/>
           <cell r="C295" t="str">
             <v>RPRO-260327-0941</v>
           </cell>
@@ -23775,6 +24318,7 @@
           <cell r="A296" t="str">
             <v>S-2026-03-142</v>
           </cell>
+          <cell r="B296"/>
           <cell r="C296" t="str">
             <v>RPRO-260401-0245</v>
           </cell>
@@ -23914,6 +24458,7 @@
           <cell r="A298" t="str">
             <v>S-2026-03-144</v>
           </cell>
+          <cell r="B298"/>
           <cell r="C298" t="str">
             <v>RPRO-260401-0247</v>
           </cell>
@@ -23982,6 +24527,7 @@
           <cell r="A299" t="str">
             <v>S-2026-03-145</v>
           </cell>
+          <cell r="B299"/>
           <cell r="C299" t="str">
             <v>RPRO-260401-0248</v>
           </cell>
@@ -24050,6 +24596,7 @@
           <cell r="A300" t="str">
             <v>S-2026-03-146</v>
           </cell>
+          <cell r="B300"/>
           <cell r="C300" t="str">
             <v>RPRO-260401-0249</v>
           </cell>
@@ -24118,6 +24665,7 @@
           <cell r="A301" t="str">
             <v>S-2026-04-01</v>
           </cell>
+          <cell r="B301"/>
           <cell r="C301" t="str">
             <v>RPRO-260401-0250</v>
           </cell>
@@ -24186,6 +24734,7 @@
           <cell r="A302" t="str">
             <v>S-2026-04-02</v>
           </cell>
+          <cell r="B302"/>
           <cell r="C302" t="str">
             <v>RPRO-260401-0251</v>
           </cell>
@@ -24254,6 +24803,7 @@
           <cell r="A303" t="str">
             <v>S-2026-04-03</v>
           </cell>
+          <cell r="B303"/>
           <cell r="C303" t="str">
             <v>RPRO-260402-0737</v>
           </cell>
@@ -24322,6 +24872,7 @@
           <cell r="A304" t="str">
             <v>S-2026-04-04</v>
           </cell>
+          <cell r="B304"/>
           <cell r="C304" t="str">
             <v>RPRO-260402-0738</v>
           </cell>
@@ -24390,6 +24941,7 @@
           <cell r="A305" t="str">
             <v>S-2026-04-05</v>
           </cell>
+          <cell r="B305"/>
           <cell r="C305" t="str">
             <v>RPRO-260403-0489</v>
           </cell>
@@ -24458,6 +25010,7 @@
           <cell r="A306" t="str">
             <v>S-2026-04-06</v>
           </cell>
+          <cell r="B306"/>
           <cell r="C306" t="str">
             <v>RPRO-260403-0490</v>
           </cell>
@@ -24526,6 +25079,7 @@
           <cell r="A307" t="str">
             <v>S-2026-04-07</v>
           </cell>
+          <cell r="B307"/>
           <cell r="C307" t="str">
             <v>RPRO-260403-0491</v>
           </cell>
@@ -24594,6 +25148,7 @@
           <cell r="A308" t="str">
             <v>S-2026-04-08</v>
           </cell>
+          <cell r="B308"/>
           <cell r="C308" t="str">
             <v>RPRO-260403-0492</v>
           </cell>
@@ -24662,6 +25217,7 @@
           <cell r="A309" t="str">
             <v>S-2026-04-09</v>
           </cell>
+          <cell r="B309"/>
           <cell r="C309" t="str">
             <v>RPRO-260406-1201</v>
           </cell>
@@ -24730,6 +25286,7 @@
           <cell r="A310" t="str">
             <v>S-2026-04-10</v>
           </cell>
+          <cell r="B310"/>
           <cell r="C310" t="str">
             <v>RPRO-260406-1202</v>
           </cell>
@@ -24798,6 +25355,7 @@
           <cell r="A311" t="str">
             <v>S-2026-04-11</v>
           </cell>
+          <cell r="B311"/>
           <cell r="C311" t="str">
             <v>RPRO-260406-1203</v>
           </cell>
@@ -24866,6 +25424,7 @@
           <cell r="A312" t="str">
             <v>S-2026-04-12</v>
           </cell>
+          <cell r="B312"/>
           <cell r="C312" t="str">
             <v>RPRO-260407-0417</v>
           </cell>
@@ -24934,6 +25493,7 @@
           <cell r="A313" t="str">
             <v>S-2026-04-13</v>
           </cell>
+          <cell r="B313"/>
           <cell r="C313" t="str">
             <v>RPRO-260407-0418</v>
           </cell>
@@ -25002,6 +25562,7 @@
           <cell r="A314" t="str">
             <v>S-2026-04-14</v>
           </cell>
+          <cell r="B314"/>
           <cell r="C314" t="str">
             <v>RPRO-260407-0419</v>
           </cell>
@@ -25070,6 +25631,7 @@
           <cell r="A315" t="str">
             <v>S-2026-04-15</v>
           </cell>
+          <cell r="B315"/>
           <cell r="C315" t="str">
             <v>RPRO-260407-0420</v>
           </cell>
@@ -25138,6 +25700,7 @@
           <cell r="A316" t="str">
             <v>S-2026-04-16</v>
           </cell>
+          <cell r="B316"/>
           <cell r="C316" t="str">
             <v>RPRO-260409-0346</v>
           </cell>
@@ -25206,6 +25769,7 @@
           <cell r="A317" t="str">
             <v>S-2026-04-17</v>
           </cell>
+          <cell r="B317"/>
           <cell r="C317" t="str">
             <v>RPRO-260409-0347</v>
           </cell>
@@ -25274,6 +25838,7 @@
           <cell r="A318" t="str">
             <v>S-2026-04-18</v>
           </cell>
+          <cell r="B318"/>
           <cell r="C318" t="str">
             <v>RPRO-260409-0348</v>
           </cell>
@@ -25342,6 +25907,7 @@
           <cell r="A319" t="str">
             <v>S-2026-04-19</v>
           </cell>
+          <cell r="B319"/>
           <cell r="C319" t="str">
             <v>RPRO-260409-0349</v>
           </cell>
@@ -25410,6 +25976,7 @@
           <cell r="A320" t="str">
             <v>S-2026-04-20</v>
           </cell>
+          <cell r="B320"/>
           <cell r="C320" t="str">
             <v>RPRO-260409-0350</v>
           </cell>
@@ -25478,6 +26045,7 @@
           <cell r="A321" t="str">
             <v>L-2026-04-21</v>
           </cell>
+          <cell r="B321"/>
           <cell r="C321" t="str">
             <v>RPRO-260410-0280</v>
           </cell>
@@ -25511,6 +26079,7 @@
           <cell r="M321" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N321"/>
           <cell r="O321" t="str">
             <v>Lab test</v>
           </cell>
@@ -25543,6 +26112,7 @@
           <cell r="A322" t="str">
             <v>L-2026-04-22</v>
           </cell>
+          <cell r="B322"/>
           <cell r="C322" t="str">
             <v>RPRO-260410-0281</v>
           </cell>
@@ -25576,6 +26146,7 @@
           <cell r="M322" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N322"/>
           <cell r="O322" t="str">
             <v>Lab test</v>
           </cell>
@@ -25608,6 +26179,7 @@
           <cell r="A323" t="str">
             <v>S-2026-04-23</v>
           </cell>
+          <cell r="B323"/>
           <cell r="C323" t="str">
             <v>RPRO-260410-0282</v>
           </cell>
@@ -25676,6 +26248,7 @@
           <cell r="A324" t="str">
             <v>S-2026-04-24</v>
           </cell>
+          <cell r="B324"/>
           <cell r="C324" t="str">
             <v>RPRO-260410-0283</v>
           </cell>
@@ -25744,6 +26317,7 @@
           <cell r="A325" t="str">
             <v>S-2026-04-25</v>
           </cell>
+          <cell r="B325"/>
           <cell r="C325" t="str">
             <v>RPRO-260410-0284</v>
           </cell>
@@ -25812,6 +26386,7 @@
           <cell r="A326" t="str">
             <v>S-2026-04-26</v>
           </cell>
+          <cell r="B326"/>
           <cell r="C326" t="str">
             <v>RPRO-260410-0285</v>
           </cell>
@@ -25880,6 +26455,7 @@
           <cell r="A327" t="str">
             <v>S-2026-04-27</v>
           </cell>
+          <cell r="B327"/>
           <cell r="C327" t="str">
             <v>RPRO-260410-0286</v>
           </cell>
@@ -25948,6 +26524,7 @@
           <cell r="A328" t="str">
             <v>S-2026-04-28</v>
           </cell>
+          <cell r="B328"/>
           <cell r="C328" t="str">
             <v>RPRO-260410-0287</v>
           </cell>
@@ -26087,6 +26664,7 @@
           <cell r="A330" t="str">
             <v>S-2026-04-30</v>
           </cell>
+          <cell r="B330"/>
           <cell r="C330" t="str">
             <v>RPRO-260414-0202</v>
           </cell>
@@ -26155,6 +26733,7 @@
           <cell r="A331" t="str">
             <v>S-2026-04-31</v>
           </cell>
+          <cell r="B331"/>
           <cell r="C331" t="str">
             <v>RPRO-260414-0203</v>
           </cell>
@@ -26223,6 +26802,7 @@
           <cell r="A332" t="str">
             <v>S-2026-04-32</v>
           </cell>
+          <cell r="B332"/>
           <cell r="C332" t="str">
             <v>RPRO-260414-0204</v>
           </cell>
@@ -26291,6 +26871,7 @@
           <cell r="A333" t="str">
             <v>S-2026-04-33</v>
           </cell>
+          <cell r="B333"/>
           <cell r="C333" t="str">
             <v>RPRO-260414-0205</v>
           </cell>
@@ -26359,6 +26940,7 @@
           <cell r="A334" t="str">
             <v>S-2026-04-34</v>
           </cell>
+          <cell r="B334"/>
           <cell r="C334" t="str">
             <v>RPRO-260414-0206</v>
           </cell>
@@ -26427,6 +27009,7 @@
           <cell r="A335" t="str">
             <v>S-2026-04-35</v>
           </cell>
+          <cell r="B335"/>
           <cell r="C335" t="str">
             <v>RPRO-260414-0207</v>
           </cell>
@@ -26495,6 +27078,7 @@
           <cell r="A336" t="str">
             <v>S-2026-04-36</v>
           </cell>
+          <cell r="B336"/>
           <cell r="C336" t="str">
             <v>RPRO-260414-0208</v>
           </cell>
@@ -26563,6 +27147,7 @@
           <cell r="A337" t="str">
             <v>S-2026-04-37</v>
           </cell>
+          <cell r="B337"/>
           <cell r="C337" t="str">
             <v>RPRO-260414-0209</v>
           </cell>
@@ -26631,6 +27216,7 @@
           <cell r="A338" t="str">
             <v>S-2026-04-38</v>
           </cell>
+          <cell r="B338"/>
           <cell r="C338" t="str">
             <v>RPRO-260414-0210</v>
           </cell>
@@ -26699,6 +27285,7 @@
           <cell r="A339" t="str">
             <v>S-2026-04-39</v>
           </cell>
+          <cell r="B339"/>
           <cell r="C339" t="str">
             <v>RPRO-260414-0211</v>
           </cell>
@@ -26767,6 +27354,7 @@
           <cell r="A340" t="str">
             <v>S-2026-04-40</v>
           </cell>
+          <cell r="B340"/>
           <cell r="C340" t="str">
             <v>RPRO-260414-0212</v>
           </cell>
@@ -26871,6 +27459,7 @@
           <cell r="M341" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N341"/>
           <cell r="O341" t="str">
             <v>Lab test</v>
           </cell>
@@ -26939,6 +27528,7 @@
           <cell r="M342" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N342"/>
           <cell r="O342" t="str">
             <v>Lab test</v>
           </cell>
@@ -26971,6 +27561,7 @@
           <cell r="A343" t="str">
             <v>S-2026-04-43</v>
           </cell>
+          <cell r="B343"/>
           <cell r="C343" t="str">
             <v>RPRO-260417-0243</v>
           </cell>
@@ -27039,6 +27630,7 @@
           <cell r="A344" t="str">
             <v>S-2026-04-44</v>
           </cell>
+          <cell r="B344"/>
           <cell r="C344" t="str">
             <v>RPRO-260417-0244</v>
           </cell>
@@ -27107,6 +27699,7 @@
           <cell r="A345" t="str">
             <v>S-2026-04-45</v>
           </cell>
+          <cell r="B345"/>
           <cell r="C345" t="str">
             <v>RPRO-260417-0245</v>
           </cell>
@@ -27175,6 +27768,7 @@
           <cell r="A346" t="str">
             <v>S-2026-04-46</v>
           </cell>
+          <cell r="B346"/>
           <cell r="C346" t="str">
             <v>RPRO-260417-0246</v>
           </cell>
@@ -27243,6 +27837,7 @@
           <cell r="A347" t="str">
             <v>S-2026-04-47</v>
           </cell>
+          <cell r="B347"/>
           <cell r="C347" t="str">
             <v>RPRO-260417-0247</v>
           </cell>
@@ -27311,6 +27906,7 @@
           <cell r="A348" t="str">
             <v>S-2026-04-48</v>
           </cell>
+          <cell r="B348"/>
           <cell r="C348" t="str">
             <v>RPRO-260421-0623</v>
           </cell>
@@ -27379,6 +27975,7 @@
           <cell r="A349" t="str">
             <v>S-2026-04-49</v>
           </cell>
+          <cell r="B349"/>
           <cell r="C349" t="str">
             <v>RPRO-260421-0624</v>
           </cell>
@@ -27447,6 +28044,7 @@
           <cell r="A350" t="str">
             <v>S-2026-04-50</v>
           </cell>
+          <cell r="B350"/>
           <cell r="C350" t="str">
             <v>RPRO-260421-0625</v>
           </cell>
@@ -27515,6 +28113,7 @@
           <cell r="A351" t="str">
             <v>S-2026-04-51</v>
           </cell>
+          <cell r="B351"/>
           <cell r="C351" t="str">
             <v>RPRO-260421-0626</v>
           </cell>
@@ -27583,6 +28182,7 @@
           <cell r="A352" t="str">
             <v>S-2026-04-52</v>
           </cell>
+          <cell r="B352"/>
           <cell r="C352" t="str">
             <v>RPRO-260421-0627</v>
           </cell>
@@ -27651,6 +28251,7 @@
           <cell r="A353" t="str">
             <v>S-2026-04-53</v>
           </cell>
+          <cell r="B353"/>
           <cell r="C353" t="str">
             <v>RPRO-260421-0628</v>
           </cell>
@@ -27719,6 +28320,7 @@
           <cell r="A354" t="str">
             <v>S-2026-04-54</v>
           </cell>
+          <cell r="B354"/>
           <cell r="C354" t="str">
             <v>RPRO-260421-0629</v>
           </cell>
@@ -27787,6 +28389,7 @@
           <cell r="A355" t="str">
             <v>S-2026-04-55</v>
           </cell>
+          <cell r="B355"/>
           <cell r="C355" t="str">
             <v>RPRO-260421-0630</v>
           </cell>
@@ -27855,6 +28458,7 @@
           <cell r="A356" t="str">
             <v>S-2026-04-56</v>
           </cell>
+          <cell r="B356"/>
           <cell r="C356" t="str">
             <v>RPRO-260421-0631</v>
           </cell>
@@ -27923,6 +28527,7 @@
           <cell r="A357" t="str">
             <v>S-2026-04-57</v>
           </cell>
+          <cell r="B357"/>
           <cell r="C357" t="str">
             <v>RPRO-260421-0632</v>
           </cell>
@@ -27991,6 +28596,7 @@
           <cell r="A358" t="str">
             <v>S-2026-04-58</v>
           </cell>
+          <cell r="B358"/>
           <cell r="C358" t="str">
             <v>RPRO-260421-0633</v>
           </cell>
@@ -28059,6 +28665,7 @@
           <cell r="A359" t="str">
             <v>S-2026-04-59</v>
           </cell>
+          <cell r="B359"/>
           <cell r="C359" t="str">
             <v>RPRO-260422-0268</v>
           </cell>
@@ -28127,6 +28734,7 @@
           <cell r="A360" t="str">
             <v>S-2026-04-60</v>
           </cell>
+          <cell r="B360"/>
           <cell r="C360" t="str">
             <v>RPRO-260423-0486</v>
           </cell>
@@ -28195,6 +28803,7 @@
           <cell r="A361" t="str">
             <v>S-2026-04-61</v>
           </cell>
+          <cell r="B361"/>
           <cell r="C361" t="str">
             <v>RPRO-260423-0487</v>
           </cell>
@@ -28263,6 +28872,7 @@
           <cell r="A362" t="str">
             <v>S-2026-04-62</v>
           </cell>
+          <cell r="B362"/>
           <cell r="C362" t="str">
             <v>RPRO-260424-1197</v>
           </cell>
@@ -28331,6 +28941,7 @@
           <cell r="A363" t="str">
             <v>S-2026-04-63</v>
           </cell>
+          <cell r="B363"/>
           <cell r="C363" t="str">
             <v>RPRO-260424-1198</v>
           </cell>
@@ -28399,6 +29010,7 @@
           <cell r="A364" t="str">
             <v>S-2026-04-64</v>
           </cell>
+          <cell r="B364"/>
           <cell r="C364" t="str">
             <v>RPRO-260424-1199</v>
           </cell>
@@ -28467,6 +29079,7 @@
           <cell r="A365" t="str">
             <v>S-2026-04-65</v>
           </cell>
+          <cell r="B365"/>
           <cell r="C365" t="str">
             <v>RPRO-260424-1200</v>
           </cell>
@@ -28535,6 +29148,7 @@
           <cell r="A366" t="str">
             <v>S-2026-04-66</v>
           </cell>
+          <cell r="B366"/>
           <cell r="C366" t="str">
             <v>RPRO-260424-1201</v>
           </cell>
@@ -28674,6 +29288,7 @@
           <cell r="A368" t="str">
             <v>S-2026-04-68</v>
           </cell>
+          <cell r="B368"/>
           <cell r="C368" t="str">
             <v>RPRO-260424-1203</v>
           </cell>
@@ -28742,6 +29357,7 @@
           <cell r="A369" t="str">
             <v>S-2026-04-69</v>
           </cell>
+          <cell r="B369"/>
           <cell r="C369" t="str">
             <v>RPRO-260424-1204</v>
           </cell>
@@ -28810,6 +29426,7 @@
           <cell r="A370" t="str">
             <v>S-2026-04-70</v>
           </cell>
+          <cell r="B370"/>
           <cell r="C370" t="str">
             <v>RPRO-260424-1205</v>
           </cell>
@@ -28878,6 +29495,7 @@
           <cell r="A371" t="str">
             <v>S-2026-04-71</v>
           </cell>
+          <cell r="B371"/>
           <cell r="C371" t="str">
             <v>RPRO-260424-1206</v>
           </cell>
@@ -28946,6 +29564,7 @@
           <cell r="A372" t="str">
             <v>S-2026-04-72</v>
           </cell>
+          <cell r="B372"/>
           <cell r="C372" t="str">
             <v>RPRO-260428-0920</v>
           </cell>
@@ -29014,6 +29633,7 @@
           <cell r="A373" t="str">
             <v>S-2026-04-73</v>
           </cell>
+          <cell r="B373"/>
           <cell r="C373" t="str">
             <v>RPRO-260429-0109</v>
           </cell>
@@ -29082,6 +29702,7 @@
           <cell r="A374" t="str">
             <v>S-2026-04-74</v>
           </cell>
+          <cell r="B374"/>
           <cell r="C374" t="str">
             <v>RPRO-260429-0110</v>
           </cell>
@@ -29150,6 +29771,7 @@
           <cell r="A375" t="str">
             <v>S-2026-04-75</v>
           </cell>
+          <cell r="B375"/>
           <cell r="C375" t="str">
             <v>RPRO-260429-0126</v>
           </cell>
@@ -29218,6 +29840,7 @@
           <cell r="A376" t="str">
             <v>S-2026-04-76</v>
           </cell>
+          <cell r="B376"/>
           <cell r="C376" t="str">
             <v>RPRO-260429-0127</v>
           </cell>
@@ -29286,6 +29909,7 @@
           <cell r="A377" t="str">
             <v>S-2026-05-01</v>
           </cell>
+          <cell r="B377"/>
           <cell r="C377" t="str">
             <v>RPRO-260505-0654</v>
           </cell>
@@ -29425,6 +30049,7 @@
           <cell r="A379" t="str">
             <v>S-2026-05-03</v>
           </cell>
+          <cell r="B379"/>
           <cell r="C379" t="str">
             <v>RPRO-260505-0656</v>
           </cell>
@@ -29493,6 +30118,7 @@
           <cell r="A380" t="str">
             <v>S-2026-05-04</v>
           </cell>
+          <cell r="B380"/>
           <cell r="C380" t="str">
             <v>RPRO-260505-0657</v>
           </cell>
@@ -29561,6 +30187,7 @@
           <cell r="A381" t="str">
             <v>S-2026-05-05</v>
           </cell>
+          <cell r="B381"/>
           <cell r="C381" t="str">
             <v>RPRO-260505-0658</v>
           </cell>
@@ -29629,6 +30256,7 @@
           <cell r="A382" t="str">
             <v>S-2026-05-06</v>
           </cell>
+          <cell r="B382"/>
           <cell r="C382" t="str">
             <v>RPRO-260505-0659</v>
           </cell>
@@ -29697,6 +30325,7 @@
           <cell r="A383" t="str">
             <v>S-2026-05-07</v>
           </cell>
+          <cell r="B383"/>
           <cell r="C383" t="str">
             <v>RPRO-260505-0660</v>
           </cell>
@@ -29836,6 +30465,7 @@
           <cell r="A385" t="str">
             <v>S-2026-05-09</v>
           </cell>
+          <cell r="B385"/>
           <cell r="C385" t="str">
             <v>RPRO-260505-0662</v>
           </cell>
@@ -29904,6 +30534,7 @@
           <cell r="A386" t="str">
             <v>S-2026-05-10</v>
           </cell>
+          <cell r="B386"/>
           <cell r="C386" t="str">
             <v>RPRO-260505-0663</v>
           </cell>
@@ -30043,6 +30674,7 @@
           <cell r="A388" t="str">
             <v>S-2026-05-12</v>
           </cell>
+          <cell r="B388"/>
           <cell r="C388" t="str">
             <v>RPRO-260505-0802</v>
           </cell>
@@ -30111,6 +30743,7 @@
           <cell r="A389" t="str">
             <v>S-2026-05-13</v>
           </cell>
+          <cell r="B389"/>
           <cell r="C389" t="str">
             <v>RPRO-260505-0803</v>
           </cell>
@@ -30179,6 +30812,7 @@
           <cell r="A390" t="str">
             <v>S-2026-05-14</v>
           </cell>
+          <cell r="B390"/>
           <cell r="C390" t="str">
             <v>RPRO-260506-0394</v>
           </cell>
@@ -30247,6 +30881,7 @@
           <cell r="A391" t="str">
             <v>S-2026-05-15</v>
           </cell>
+          <cell r="B391"/>
           <cell r="C391" t="str">
             <v>RPRO-260506-0395</v>
           </cell>
@@ -30315,6 +30950,7 @@
           <cell r="A392" t="str">
             <v>S-2026-05-16</v>
           </cell>
+          <cell r="B392"/>
           <cell r="C392" t="str">
             <v>RPRO-260506-0396</v>
           </cell>
@@ -30383,6 +31019,7 @@
           <cell r="A393" t="str">
             <v>S-2026-05-17</v>
           </cell>
+          <cell r="B393"/>
           <cell r="C393" t="str">
             <v>RPRO-260506-0397</v>
           </cell>
@@ -30451,6 +31088,7 @@
           <cell r="A394" t="str">
             <v>S-2026-05-18</v>
           </cell>
+          <cell r="B394"/>
           <cell r="C394" t="str">
             <v>RPRO-260506-0415</v>
           </cell>
@@ -30519,6 +31157,7 @@
           <cell r="A395" t="str">
             <v>S-2026-05-19</v>
           </cell>
+          <cell r="B395"/>
           <cell r="C395" t="str">
             <v>RPRO-260508-0581</v>
           </cell>
@@ -30587,6 +31226,7 @@
           <cell r="A396" t="str">
             <v>S-2026-05-20</v>
           </cell>
+          <cell r="B396"/>
           <cell r="C396" t="str">
             <v>RPRO-260508-0582</v>
           </cell>
@@ -30655,6 +31295,7 @@
           <cell r="A397" t="str">
             <v>S-2026-05-21</v>
           </cell>
+          <cell r="B397"/>
           <cell r="C397" t="str">
             <v>RPRO-260508-0583</v>
           </cell>
@@ -30723,6 +31364,7 @@
           <cell r="A398" t="str">
             <v>S-2026-05-22</v>
           </cell>
+          <cell r="B398"/>
           <cell r="C398" t="str">
             <v>RPRO-260508-0584</v>
           </cell>
@@ -30791,6 +31433,7 @@
           <cell r="A399" t="str">
             <v>S-2026-05-23</v>
           </cell>
+          <cell r="B399"/>
           <cell r="C399" t="str">
             <v>RPRO-260508-0585</v>
           </cell>
@@ -30859,6 +31502,7 @@
           <cell r="A400" t="str">
             <v>S-2026-05-24</v>
           </cell>
+          <cell r="B400"/>
           <cell r="C400" t="str">
             <v>RPRO-260508-0586</v>
           </cell>
@@ -30927,6 +31571,7 @@
           <cell r="A401" t="str">
             <v>S-2026-05-25</v>
           </cell>
+          <cell r="B401"/>
           <cell r="C401" t="str">
             <v>RPRO-260508-0587</v>
           </cell>
@@ -30995,6 +31640,7 @@
           <cell r="A402" t="str">
             <v>S-2026-05-26</v>
           </cell>
+          <cell r="B402"/>
           <cell r="C402" t="str">
             <v>RPRO-260508-0588</v>
           </cell>
@@ -31063,6 +31709,7 @@
           <cell r="A403" t="str">
             <v>S-2026-05-27</v>
           </cell>
+          <cell r="B403"/>
           <cell r="C403" t="str">
             <v>RPRO-260512-0580</v>
           </cell>
@@ -31093,6 +31740,7 @@
           <cell r="L403" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M403"/>
           <cell r="N403" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -31128,6 +31776,7 @@
           <cell r="A404" t="str">
             <v>S-2026-05-28</v>
           </cell>
+          <cell r="B404"/>
           <cell r="C404" t="str">
             <v>RPRO-260512-0581</v>
           </cell>
@@ -31158,6 +31807,7 @@
           <cell r="L404" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M404"/>
           <cell r="N404" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -31193,6 +31843,7 @@
           <cell r="A405" t="str">
             <v>S-2026-05-29</v>
           </cell>
+          <cell r="B405"/>
           <cell r="C405" t="str">
             <v>RPRO-260512-0582</v>
           </cell>
@@ -31261,6 +31912,7 @@
           <cell r="A406" t="str">
             <v>S-2026-05-30</v>
           </cell>
+          <cell r="B406"/>
           <cell r="C406" t="str">
             <v>RPRO-260512-0583</v>
           </cell>
@@ -31329,6 +31981,7 @@
           <cell r="A407" t="str">
             <v>S-2026-05-31</v>
           </cell>
+          <cell r="B407"/>
           <cell r="C407" t="str">
             <v>RPRO-260513-0945</v>
           </cell>
@@ -31397,6 +32050,7 @@
           <cell r="A408" t="str">
             <v>S-2026-05-32</v>
           </cell>
+          <cell r="B408"/>
           <cell r="C408" t="str">
             <v>RPRO-260513-0946</v>
           </cell>
@@ -31465,6 +32119,7 @@
           <cell r="A409" t="str">
             <v>S-2026-05-33</v>
           </cell>
+          <cell r="B409"/>
           <cell r="C409" t="str">
             <v>RPRO-260513-0947</v>
           </cell>
@@ -31533,6 +32188,7 @@
           <cell r="A410" t="str">
             <v>S-2026-05-34</v>
           </cell>
+          <cell r="B410"/>
           <cell r="C410" t="str">
             <v>RPRO-260513-0948</v>
           </cell>
@@ -31672,6 +32328,7 @@
           <cell r="A412" t="str">
             <v>S-2026-05-36</v>
           </cell>
+          <cell r="B412"/>
           <cell r="C412" t="str">
             <v>RPRO-260513-0950</v>
           </cell>
@@ -31740,6 +32397,7 @@
           <cell r="A413" t="str">
             <v>S-2026-05-37</v>
           </cell>
+          <cell r="B413"/>
           <cell r="C413" t="str">
             <v>RPRO-260515-0272</v>
           </cell>
@@ -31808,6 +32466,7 @@
           <cell r="A414" t="str">
             <v>S-2026-05-38</v>
           </cell>
+          <cell r="B414"/>
           <cell r="C414" t="str">
             <v>RPRO-260515-0273</v>
           </cell>
@@ -31876,6 +32535,7 @@
           <cell r="A415" t="str">
             <v>S-2026-05-39</v>
           </cell>
+          <cell r="B415"/>
           <cell r="C415" t="str">
             <v>RPRO-260515-0274</v>
           </cell>
@@ -31944,6 +32604,7 @@
           <cell r="A416" t="str">
             <v>S-2026-05-40</v>
           </cell>
+          <cell r="B416"/>
           <cell r="C416" t="str">
             <v>RPRO-260515-0275</v>
           </cell>
@@ -32012,6 +32673,7 @@
           <cell r="A417" t="str">
             <v>S-2026-05-41</v>
           </cell>
+          <cell r="B417"/>
           <cell r="C417" t="str">
             <v>RPRO-260515-0276</v>
           </cell>
@@ -32080,6 +32742,7 @@
           <cell r="A418" t="str">
             <v>S-2026-05-42</v>
           </cell>
+          <cell r="B418"/>
           <cell r="C418" t="str">
             <v>RPRO-260515-0277</v>
           </cell>
@@ -32148,6 +32811,7 @@
           <cell r="A419" t="str">
             <v>S-2026-05-43</v>
           </cell>
+          <cell r="B419"/>
           <cell r="C419" t="str">
             <v>RPRO-260515-0278</v>
           </cell>
@@ -32216,6 +32880,7 @@
           <cell r="A420" t="str">
             <v>S-2026-05-44</v>
           </cell>
+          <cell r="B420"/>
           <cell r="C420" t="str">
             <v>RPRO-260515-0279</v>
           </cell>
@@ -32284,6 +32949,7 @@
           <cell r="A421" t="str">
             <v>S-2026-05-45</v>
           </cell>
+          <cell r="B421"/>
           <cell r="C421" t="str">
             <v>RPRO-260515-0280</v>
           </cell>
@@ -32352,6 +33018,7 @@
           <cell r="A422" t="str">
             <v>S-2026-05-46</v>
           </cell>
+          <cell r="B422"/>
           <cell r="C422" t="str">
             <v>RPRO-260518-0853</v>
           </cell>
@@ -32420,6 +33087,7 @@
           <cell r="A423" t="str">
             <v>S-2026-05-47</v>
           </cell>
+          <cell r="B423"/>
           <cell r="C423" t="str">
             <v>RPRO-260518-0854</v>
           </cell>
@@ -32488,6 +33156,7 @@
           <cell r="A424" t="str">
             <v>S-2026-05-48</v>
           </cell>
+          <cell r="B424"/>
           <cell r="C424" t="str">
             <v>RPRO-260518-0855</v>
           </cell>
@@ -32556,6 +33225,7 @@
           <cell r="A425" t="str">
             <v>S-2026-05-49</v>
           </cell>
+          <cell r="B425"/>
           <cell r="C425" t="str">
             <v>RPRO-260518-0856</v>
           </cell>
@@ -32837,6 +33507,7 @@
           <cell r="A429" t="str">
             <v>S-2026-05-53</v>
           </cell>
+          <cell r="B429"/>
           <cell r="C429" t="str">
             <v>RPRO-260518-0860</v>
           </cell>
@@ -32905,6 +33576,7 @@
           <cell r="A430" t="str">
             <v>S-2026-05-54</v>
           </cell>
+          <cell r="B430"/>
           <cell r="C430" t="str">
             <v>RPRO-260518-0861</v>
           </cell>
@@ -32973,6 +33645,7 @@
           <cell r="A431" t="str">
             <v>S-2026-05-55</v>
           </cell>
+          <cell r="B431"/>
           <cell r="C431" t="str">
             <v>RPRO-260518-0862</v>
           </cell>
@@ -33041,6 +33714,7 @@
           <cell r="A432" t="str">
             <v>S-2026-05-56</v>
           </cell>
+          <cell r="B432"/>
           <cell r="C432" t="str">
             <v>RPRO-260518-0863</v>
           </cell>
@@ -33109,6 +33783,7 @@
           <cell r="A433" t="str">
             <v>S-2026-05-57</v>
           </cell>
+          <cell r="B433"/>
           <cell r="C433" t="str">
             <v>RPRO-260518-0864</v>
           </cell>
@@ -33177,6 +33852,7 @@
           <cell r="A434" t="str">
             <v>S-2026-05-58</v>
           </cell>
+          <cell r="B434"/>
           <cell r="C434" t="str">
             <v>RPRO-260518-0865</v>
           </cell>
@@ -33245,6 +33921,7 @@
           <cell r="A435" t="str">
             <v>S-2026-05-59</v>
           </cell>
+          <cell r="B435"/>
           <cell r="C435" t="str">
             <v>RPRO-260518-0866</v>
           </cell>
@@ -33313,6 +33990,7 @@
           <cell r="A436" t="str">
             <v>S-2026-05-60</v>
           </cell>
+          <cell r="B436"/>
           <cell r="C436" t="str">
             <v>RPRO-260520-0192</v>
           </cell>
@@ -33381,6 +34059,7 @@
           <cell r="A437" t="str">
             <v>S-2026-05-61</v>
           </cell>
+          <cell r="B437"/>
           <cell r="C437" t="str">
             <v>RPRO-260520-0193</v>
           </cell>
@@ -33449,6 +34128,7 @@
           <cell r="A438" t="str">
             <v>S-2026-05-62</v>
           </cell>
+          <cell r="B438"/>
           <cell r="C438" t="str">
             <v>RPRO-260520-0194</v>
           </cell>
@@ -33517,6 +34197,7 @@
           <cell r="A439" t="str">
             <v>S-2026-05-63</v>
           </cell>
+          <cell r="B439"/>
           <cell r="C439" t="str">
             <v>RPRO-260520-0195</v>
           </cell>
@@ -33585,6 +34266,7 @@
           <cell r="A440" t="str">
             <v>S-2026-05-64</v>
           </cell>
+          <cell r="B440"/>
           <cell r="C440" t="str">
             <v>RPRO-260520-0196</v>
           </cell>
@@ -33653,6 +34335,7 @@
           <cell r="A441" t="str">
             <v>S-2026-05-65</v>
           </cell>
+          <cell r="B441"/>
           <cell r="C441" t="str">
             <v>RPRO-260520-0197</v>
           </cell>
@@ -33721,6 +34404,7 @@
           <cell r="A442" t="str">
             <v>S-2026-05-66</v>
           </cell>
+          <cell r="B442"/>
           <cell r="C442" t="str">
             <v>RPRO-260520-0225</v>
           </cell>
@@ -33789,6 +34473,7 @@
           <cell r="A443" t="str">
             <v>S-2026-05-67</v>
           </cell>
+          <cell r="B443"/>
           <cell r="C443" t="str">
             <v>RPRO-260520-0226</v>
           </cell>
@@ -33857,6 +34542,7 @@
           <cell r="A444" t="str">
             <v>S-2026-05-68</v>
           </cell>
+          <cell r="B444"/>
           <cell r="C444" t="str">
             <v>RPRO-260520-0227</v>
           </cell>
@@ -33925,6 +34611,7 @@
           <cell r="A445" t="str">
             <v>S-2026-05-69</v>
           </cell>
+          <cell r="B445"/>
           <cell r="C445" t="str">
             <v>RPRO-260520-0228</v>
           </cell>
@@ -33993,6 +34680,7 @@
           <cell r="A446" t="str">
             <v>S-2026-05-70</v>
           </cell>
+          <cell r="B446"/>
           <cell r="C446" t="str">
             <v>RPRO-260520-0229</v>
           </cell>
@@ -34061,6 +34749,7 @@
           <cell r="A447" t="str">
             <v>S-2026-05-71</v>
           </cell>
+          <cell r="B447"/>
           <cell r="C447" t="str">
             <v>RPRO-260521-0669</v>
           </cell>
@@ -34129,6 +34818,7 @@
           <cell r="A448" t="str">
             <v>S-2026-05-72</v>
           </cell>
+          <cell r="B448"/>
           <cell r="C448" t="str">
             <v>RPRO-260521-0670</v>
           </cell>
@@ -34197,6 +34887,7 @@
           <cell r="A449" t="str">
             <v>S-2026-05-73</v>
           </cell>
+          <cell r="B449"/>
           <cell r="C449" t="str">
             <v>RPRO-260523-0221</v>
           </cell>
@@ -34265,6 +34956,7 @@
           <cell r="A450" t="str">
             <v>S-2026-05-74</v>
           </cell>
+          <cell r="B450"/>
           <cell r="C450" t="str">
             <v>RPRO-260523-0222</v>
           </cell>
@@ -34333,6 +35025,7 @@
           <cell r="A451" t="str">
             <v>S-2026-05-75</v>
           </cell>
+          <cell r="B451"/>
           <cell r="C451" t="str">
             <v>RPRO-260523-0223</v>
           </cell>
@@ -34401,6 +35094,7 @@
           <cell r="A452" t="str">
             <v>S-2026-05-76</v>
           </cell>
+          <cell r="B452"/>
           <cell r="C452" t="str">
             <v>RPRO-260526-0394</v>
           </cell>
@@ -34469,6 +35163,7 @@
           <cell r="A453" t="str">
             <v>S-2026-05-77</v>
           </cell>
+          <cell r="B453"/>
           <cell r="C453" t="str">
             <v>RPRO-260526-0395</v>
           </cell>
@@ -34537,6 +35232,7 @@
           <cell r="A454" t="str">
             <v>S-2026-05-78</v>
           </cell>
+          <cell r="B454"/>
           <cell r="C454" t="str">
             <v>RPRO-260526-0396</v>
           </cell>
@@ -34605,6 +35301,7 @@
           <cell r="A455" t="str">
             <v>S-2026-05-79</v>
           </cell>
+          <cell r="B455"/>
           <cell r="C455" t="str">
             <v>RPRO-260526-0397</v>
           </cell>
@@ -34673,6 +35370,7 @@
           <cell r="A456" t="str">
             <v>S-2026-05-80</v>
           </cell>
+          <cell r="B456"/>
           <cell r="C456" t="str">
             <v>RPRO-260526-0398</v>
           </cell>
@@ -34741,6 +35439,7 @@
           <cell r="A457" t="str">
             <v>S-2026-05-81</v>
           </cell>
+          <cell r="B457"/>
           <cell r="C457" t="str">
             <v>RPRO-260526-0399</v>
           </cell>
@@ -34810,7 +35509,7 @@
             <v>S-2026-05-82</v>
           </cell>
           <cell r="B458" t="str">
-            <v>xin dời ETD 2-Jun-&gt; 6-Jun</v>
+            <v xml:space="preserve">sx xin dời ETD </v>
           </cell>
           <cell r="C458" t="str">
             <v>RPRO-260526-0400</v>
@@ -34855,16 +35554,16 @@
             <v>46167</v>
           </cell>
           <cell r="Q458">
-            <v>46175</v>
+            <v>46179</v>
           </cell>
           <cell r="R458">
-            <v>46172</v>
+            <v>46176</v>
           </cell>
           <cell r="S458">
             <v>6</v>
           </cell>
           <cell r="T458">
-            <v>8</v>
+            <v>12</v>
           </cell>
           <cell r="U458">
             <v>6</v>
@@ -34880,6 +35579,7 @@
           <cell r="A459" t="str">
             <v>S-2026-05-83</v>
           </cell>
+          <cell r="B459"/>
           <cell r="C459" t="str">
             <v>RPRO-260526-0401</v>
           </cell>
@@ -34951,6 +35651,7 @@
           <cell r="B460" t="str">
             <v>ƯU TIÊN GIAO 06-JUN KHI CÓ LIỆU</v>
           </cell>
+          <cell r="C460"/>
           <cell r="D460" t="str">
             <v>PUR2605250002S</v>
           </cell>
@@ -34991,19 +35692,19 @@
             <v>46167</v>
           </cell>
           <cell r="Q460">
-            <v>46179</v>
+            <v>46185</v>
           </cell>
           <cell r="R460">
-            <v>46176</v>
+            <v>46182</v>
           </cell>
           <cell r="S460">
             <v>6</v>
           </cell>
           <cell r="T460">
-            <v>12</v>
-          </cell>
-          <cell r="U460" t="str">
-            <v/>
+            <v>18</v>
+          </cell>
+          <cell r="U460">
+            <v>6</v>
           </cell>
           <cell r="V460">
             <v>4.3479999999999998E-2</v>
@@ -35016,6 +35717,7 @@
           <cell r="A461" t="str">
             <v>S-2026-05-85</v>
           </cell>
+          <cell r="B461"/>
           <cell r="C461" t="str">
             <v>RPRO-260526-0402</v>
           </cell>
@@ -35084,6 +35786,7 @@
           <cell r="A462" t="str">
             <v>S-2026-05-86</v>
           </cell>
+          <cell r="B462"/>
           <cell r="C462" t="str">
             <v>RPRO-260527-0578</v>
           </cell>
@@ -35152,6 +35855,7 @@
           <cell r="A463" t="str">
             <v>S-2026-05-87</v>
           </cell>
+          <cell r="B463"/>
           <cell r="C463" t="str">
             <v>RPRO-260527-0579</v>
           </cell>
@@ -35220,6 +35924,7 @@
           <cell r="A464" t="str">
             <v>S-2026-05-88</v>
           </cell>
+          <cell r="B464"/>
           <cell r="C464" t="str">
             <v>RPRO-260527-0580</v>
           </cell>
@@ -35288,6 +35993,7 @@
           <cell r="A465" t="str">
             <v>S-2026-05-89</v>
           </cell>
+          <cell r="B465"/>
           <cell r="C465" t="str">
             <v>RPRO-260527-0581</v>
           </cell>
@@ -35356,6 +36062,7 @@
           <cell r="A466" t="str">
             <v>S-2026-05-90</v>
           </cell>
+          <cell r="B466"/>
           <cell r="C466" t="str">
             <v>RPRO-260527-0582</v>
           </cell>
@@ -35424,6 +36131,7 @@
           <cell r="A467" t="str">
             <v>S-2026-05-91</v>
           </cell>
+          <cell r="B467"/>
           <cell r="C467" t="str">
             <v>RPRO-260527-0583</v>
           </cell>
@@ -35492,6 +36200,7 @@
           <cell r="A468" t="str">
             <v>S-2026-05-92</v>
           </cell>
+          <cell r="B468"/>
           <cell r="C468" t="str">
             <v>RPRO-260528-0001</v>
           </cell>
@@ -35560,6 +36269,7 @@
           <cell r="A469" t="str">
             <v>S-2026-05-93</v>
           </cell>
+          <cell r="B469"/>
           <cell r="C469" t="str">
             <v>RPRO-260529-0339</v>
           </cell>
@@ -35582,10 +36292,10 @@
             <v>50</v>
           </cell>
           <cell r="J469">
+            <v>50</v>
+          </cell>
+          <cell r="K469">
             <v>0</v>
-          </cell>
-          <cell r="K469">
-            <v>50</v>
           </cell>
           <cell r="L469" t="str">
             <v>ADIDAS</v>
@@ -35628,6 +36338,7 @@
           <cell r="A470" t="str">
             <v>S-2026-05-94</v>
           </cell>
+          <cell r="B470"/>
           <cell r="C470" t="str">
             <v>RPRO-260529-0340</v>
           </cell>
@@ -35650,10 +36361,10 @@
             <v>30</v>
           </cell>
           <cell r="J470">
+            <v>30</v>
+          </cell>
+          <cell r="K470">
             <v>0</v>
-          </cell>
-          <cell r="K470">
-            <v>30</v>
           </cell>
           <cell r="L470" t="str">
             <v>FOOTJOY</v>
@@ -35696,6 +36407,7 @@
           <cell r="A471" t="str">
             <v>S-2026-05-95</v>
           </cell>
+          <cell r="B471"/>
           <cell r="C471" t="str">
             <v>RPRO-260529-0341</v>
           </cell>
@@ -35764,9 +36476,7 @@
           <cell r="A472" t="str">
             <v>S-2026-05-96</v>
           </cell>
-          <cell r="B472" t="str">
-            <v>có kq lab sớm nên dời ETD 5/Jun-&gt;3/Jun giao hàng</v>
-          </cell>
+          <cell r="B472"/>
           <cell r="C472" t="str">
             <v>RPRO-260529-0342</v>
           </cell>
@@ -35835,9 +36545,7 @@
           <cell r="A473" t="str">
             <v>S-2026-05-97</v>
           </cell>
-          <cell r="B473" t="str">
-            <v>có kq lab sớm nên dời ETD 5/Jun-&gt;3/Jun giao hàng</v>
-          </cell>
+          <cell r="B473"/>
           <cell r="C473" t="str">
             <v>RPRO-260529-0343</v>
           </cell>
@@ -35906,6 +36614,7 @@
           <cell r="A474" t="str">
             <v>S-2026-05-98</v>
           </cell>
+          <cell r="B474"/>
           <cell r="C474" t="str">
             <v>RPRO-260529-0344</v>
           </cell>
@@ -35974,6 +36683,7 @@
           <cell r="A475" t="str">
             <v>S-2026-05-99</v>
           </cell>
+          <cell r="B475"/>
           <cell r="C475" t="str">
             <v>RPRO-260529-0345</v>
           </cell>
@@ -36042,9 +36752,7 @@
           <cell r="A476" t="str">
             <v>S-2026-05-100</v>
           </cell>
-          <cell r="B476" t="str">
-            <v>có kq lab sớm nên dời ETD 4/Jun-&gt;3/Jun giao hàng</v>
-          </cell>
+          <cell r="B476"/>
           <cell r="C476" t="str">
             <v>RPRO-260529-0346</v>
           </cell>
@@ -36113,6 +36821,7 @@
           <cell r="A477" t="str">
             <v>S-2026-05-102</v>
           </cell>
+          <cell r="B477"/>
           <cell r="C477" t="str">
             <v>RPRO-260601-0847</v>
           </cell>
@@ -36181,6 +36890,7 @@
           <cell r="A478" t="str">
             <v>S-2026-05-103</v>
           </cell>
+          <cell r="B478"/>
           <cell r="C478" t="str">
             <v>RPRO-260601-0848</v>
           </cell>
@@ -36249,6 +36959,7 @@
           <cell r="A479" t="str">
             <v>S-2026-05-104</v>
           </cell>
+          <cell r="B479"/>
           <cell r="C479" t="str">
             <v>RPRO-260601-0849</v>
           </cell>
@@ -36317,6 +37028,7 @@
           <cell r="A480" t="str">
             <v>S-2026-05-105</v>
           </cell>
+          <cell r="B480"/>
           <cell r="C480" t="str">
             <v>RPRO-260601-0850</v>
           </cell>
@@ -36385,6 +37097,7 @@
           <cell r="A481" t="str">
             <v>S-2026-05-106</v>
           </cell>
+          <cell r="B481"/>
           <cell r="C481" t="str">
             <v>RPRO-260601-0851</v>
           </cell>
@@ -36453,6 +37166,7 @@
           <cell r="A482" t="str">
             <v>S-2026-06-01</v>
           </cell>
+          <cell r="B482"/>
           <cell r="C482" t="str">
             <v>RPRO-260602-0720</v>
           </cell>
@@ -36508,8 +37222,8 @@
           <cell r="T482">
             <v>7</v>
           </cell>
-          <cell r="U482" t="str">
-            <v/>
+          <cell r="U482">
+            <v>15</v>
           </cell>
           <cell r="V482">
             <v>0.11111</v>
@@ -36522,6 +37236,7 @@
           <cell r="A483" t="str">
             <v>S-2026-06-02</v>
           </cell>
+          <cell r="B483"/>
           <cell r="C483" t="str">
             <v>RPRO-260602-0721</v>
           </cell>
@@ -36590,6 +37305,7 @@
           <cell r="A484" t="str">
             <v>S-2026-06-03</v>
           </cell>
+          <cell r="B484"/>
           <cell r="C484" t="str">
             <v>RPRO-260602-0722</v>
           </cell>
@@ -36658,6 +37374,7 @@
           <cell r="A485" t="str">
             <v>S-2026-06-04</v>
           </cell>
+          <cell r="B485"/>
           <cell r="C485" t="str">
             <v>RPRO-260602-0723</v>
           </cell>
@@ -36726,6 +37443,7 @@
           <cell r="A486" t="str">
             <v>S-2026-06-05</v>
           </cell>
+          <cell r="B486"/>
           <cell r="C486" t="str">
             <v>RPRO-260602-0724</v>
           </cell>
@@ -36794,6 +37512,7 @@
           <cell r="A487" t="str">
             <v>S-2026-06-06</v>
           </cell>
+          <cell r="B487"/>
           <cell r="C487" t="str">
             <v>RPRO-260602-0725</v>
           </cell>
@@ -36862,6 +37581,7 @@
           <cell r="A488" t="str">
             <v>S-2026-06-07</v>
           </cell>
+          <cell r="B488"/>
           <cell r="C488" t="str">
             <v>RPRO-260602-0726</v>
           </cell>
@@ -36930,6 +37650,7 @@
           <cell r="A489" t="str">
             <v>S-2026-06-08</v>
           </cell>
+          <cell r="B489"/>
           <cell r="C489" t="str">
             <v>RPRO-260602-0727</v>
           </cell>
@@ -37055,8 +37776,8 @@
           <cell r="T490">
             <v>7</v>
           </cell>
-          <cell r="U490" t="str">
-            <v/>
+          <cell r="U490">
+            <v>5</v>
           </cell>
           <cell r="V490">
             <v>3.5709999999999999E-2</v>
@@ -37069,9 +37790,7 @@
           <cell r="A491" t="str">
             <v>S-2026-06-10</v>
           </cell>
-          <cell r="B491" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B491"/>
           <cell r="C491" t="str">
             <v>RPRO-260603-0482</v>
           </cell>
@@ -37140,9 +37859,7 @@
           <cell r="A492" t="str">
             <v>S-2026-06-11</v>
           </cell>
-          <cell r="B492" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B492"/>
           <cell r="C492" t="str">
             <v>RPRO-260603-0483</v>
           </cell>
@@ -37211,9 +37928,7 @@
           <cell r="A493" t="str">
             <v>S-2026-06-12</v>
           </cell>
-          <cell r="B493" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B493"/>
           <cell r="C493" t="str">
             <v>RPRO-260603-0484</v>
           </cell>
@@ -37283,7 +37998,7 @@
             <v>S-2026-06-14</v>
           </cell>
           <cell r="B494" t="str">
-            <v>chua rl</v>
+            <v xml:space="preserve">Gấp 6.6 </v>
           </cell>
           <cell r="C494" t="str">
             <v>RPRO-260603-0485</v>
@@ -37353,9 +38068,7 @@
           <cell r="A495" t="str">
             <v>S-2026-06-15</v>
           </cell>
-          <cell r="B495" t="str">
-            <v>chua rl</v>
-          </cell>
+          <cell r="B495"/>
           <cell r="C495" t="str">
             <v>RPRO-260604-0522</v>
           </cell>
@@ -37363,7 +38076,7 @@
             <v>PUR2606030002S</v>
           </cell>
           <cell r="E495" t="str">
-            <v/>
+            <v>BDB-000307</v>
           </cell>
           <cell r="F495" t="str">
             <v>PVN-004437</v>
@@ -37410,20 +38123,21 @@
           <cell r="T495">
             <v>7</v>
           </cell>
-          <cell r="U495" t="str">
-            <v/>
-          </cell>
-          <cell r="V495" t="e">
-            <v>#N/A</v>
-          </cell>
-          <cell r="W495" t="str">
-            <v/>
+          <cell r="U495">
+            <v>8</v>
+          </cell>
+          <cell r="V495">
+            <v>5.5559999999999998E-2</v>
+          </cell>
+          <cell r="W495">
+            <v>2</v>
           </cell>
         </row>
         <row r="496">
           <cell r="A496" t="str">
             <v>L-2026-06-01</v>
           </cell>
+          <cell r="B496"/>
           <cell r="C496" t="str">
             <v>RPRO-260604-0523</v>
           </cell>
@@ -37431,7 +38145,7 @@
             <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
           </cell>
           <cell r="E496" t="str">
-            <v/>
+            <v>BDB-000131</v>
           </cell>
           <cell r="F496" t="str">
             <v>PVN-002424</v>
@@ -37449,11 +38163,13 @@
             <v>0</v>
           </cell>
           <cell r="K496">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="L496" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M496"/>
+          <cell r="N496"/>
           <cell r="O496" t="str">
             <v>Lab test</v>
           </cell>
@@ -37472,20 +38188,21 @@
           <cell r="T496">
             <v>7</v>
           </cell>
-          <cell r="U496" t="str">
-            <v/>
+          <cell r="U496">
+            <v>3.5</v>
           </cell>
           <cell r="V496">
-            <v>0</v>
+            <v>2.5000000000000001E-2</v>
           </cell>
           <cell r="W496">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="497">
           <cell r="A497" t="str">
             <v>L-2026-06-02</v>
           </cell>
+          <cell r="B497"/>
           <cell r="C497" t="str">
             <v>RPRO-260604-0524</v>
           </cell>
@@ -37493,7 +38210,7 @@
             <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
           </cell>
           <cell r="E497" t="str">
-            <v/>
+            <v>BDB-000131</v>
           </cell>
           <cell r="F497" t="str">
             <v>PVN-001635</v>
@@ -37511,11 +38228,13 @@
             <v>0</v>
           </cell>
           <cell r="K497">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="L497" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M497"/>
+          <cell r="N497"/>
           <cell r="O497" t="str">
             <v>Lab test</v>
           </cell>
@@ -37534,20 +38253,21 @@
           <cell r="T497">
             <v>7</v>
           </cell>
-          <cell r="U497" t="str">
-            <v/>
+          <cell r="U497">
+            <v>10</v>
           </cell>
           <cell r="V497">
-            <v>0</v>
+            <v>7.6920000000000002E-2</v>
           </cell>
           <cell r="W497">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="498">
           <cell r="A498" t="str">
             <v>L-2026-06-03</v>
           </cell>
+          <cell r="B498"/>
           <cell r="C498" t="str">
             <v>RPRO-260604-0525</v>
           </cell>
@@ -37555,7 +38275,7 @@
             <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
           </cell>
           <cell r="E498" t="str">
-            <v/>
+            <v>BDB-000221</v>
           </cell>
           <cell r="F498" t="str">
             <v>PVN-004123</v>
@@ -37573,11 +38293,13 @@
             <v>0</v>
           </cell>
           <cell r="K498">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="L498" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M498"/>
+          <cell r="N498"/>
           <cell r="O498" t="str">
             <v>Lab test</v>
           </cell>
@@ -37596,20 +38318,21 @@
           <cell r="T498">
             <v>7</v>
           </cell>
-          <cell r="U498" t="str">
-            <v/>
+          <cell r="U498">
+            <v>3</v>
           </cell>
           <cell r="V498">
-            <v>0</v>
+            <v>2.1739999999999999E-2</v>
           </cell>
           <cell r="W498">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="499">
           <cell r="A499" t="str">
             <v>L-2026-06-04</v>
           </cell>
+          <cell r="B499"/>
           <cell r="C499" t="str">
             <v>RPRO-260604-0526</v>
           </cell>
@@ -37617,7 +38340,7 @@
             <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
           </cell>
           <cell r="E499" t="str">
-            <v/>
+            <v>BDB-000221</v>
           </cell>
           <cell r="F499" t="str">
             <v>PVN-004124</v>
@@ -37635,11 +38358,13 @@
             <v>0</v>
           </cell>
           <cell r="K499">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="L499" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M499"/>
+          <cell r="N499"/>
           <cell r="O499" t="str">
             <v>Lab test</v>
           </cell>
@@ -37658,20 +38383,21 @@
           <cell r="T499">
             <v>7</v>
           </cell>
-          <cell r="U499" t="str">
-            <v/>
+          <cell r="U499">
+            <v>10</v>
           </cell>
           <cell r="V499">
-            <v>0</v>
+            <v>7.6920000000000002E-2</v>
           </cell>
           <cell r="W499">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="500">
           <cell r="A500" t="str">
             <v>L-2026-06-05</v>
           </cell>
+          <cell r="B500"/>
           <cell r="C500" t="str">
             <v>RPRO-260604-0527</v>
           </cell>
@@ -37679,7 +38405,7 @@
             <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
           </cell>
           <cell r="E500" t="str">
-            <v/>
+            <v>BDB-000097</v>
           </cell>
           <cell r="F500" t="str">
             <v>PVN-002512</v>
@@ -37697,11 +38423,13 @@
             <v>0</v>
           </cell>
           <cell r="K500">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="L500" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M500"/>
+          <cell r="N500"/>
           <cell r="O500" t="str">
             <v>Lab test</v>
           </cell>
@@ -37720,20 +38448,21 @@
           <cell r="T500">
             <v>7</v>
           </cell>
-          <cell r="U500" t="str">
-            <v/>
+          <cell r="U500">
+            <v>10</v>
           </cell>
           <cell r="V500">
-            <v>0</v>
+            <v>7.6920000000000002E-2</v>
           </cell>
           <cell r="W500">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="501">
           <cell r="A501" t="str">
             <v>L-2026-06-06</v>
           </cell>
+          <cell r="B501"/>
           <cell r="C501" t="str">
             <v>RPRO-260604-0528</v>
           </cell>
@@ -37741,7 +38470,7 @@
             <v xml:space="preserve">&lt;nguyet.bui@ortholite.vn&gt; </v>
           </cell>
           <cell r="E501" t="str">
-            <v/>
+            <v>BDB-000097</v>
           </cell>
           <cell r="F501" t="str">
             <v>PVN-002478</v>
@@ -37759,11 +38488,13 @@
             <v>0</v>
           </cell>
           <cell r="K501">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="L501" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M501"/>
+          <cell r="N501"/>
           <cell r="O501" t="str">
             <v>Lab test</v>
           </cell>
@@ -37782,20 +38513,21 @@
           <cell r="T501">
             <v>7</v>
           </cell>
-          <cell r="U501" t="str">
-            <v/>
+          <cell r="U501">
+            <v>4</v>
           </cell>
           <cell r="V501">
-            <v>0</v>
+            <v>2.8570000000000002E-2</v>
           </cell>
           <cell r="W501">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="502">
           <cell r="A502" t="str">
             <v>L-2026-06-07</v>
           </cell>
+          <cell r="B502"/>
           <cell r="C502" t="str">
             <v>RPRO-260604-0529</v>
           </cell>
@@ -37803,7 +38535,7 @@
             <v xml:space="preserve">&lt;anne.tran@ortholite.vn&gt; </v>
           </cell>
           <cell r="E502" t="str">
-            <v/>
+            <v>BDB-000113</v>
           </cell>
           <cell r="F502" t="str">
             <v>PVN-002699</v>
@@ -37821,11 +38553,13 @@
             <v>0</v>
           </cell>
           <cell r="K502">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="L502" t="str">
             <v>SHYANG HUNG TAH</v>
           </cell>
+          <cell r="M502"/>
+          <cell r="N502"/>
           <cell r="O502" t="str">
             <v>Lab test</v>
           </cell>
@@ -37844,28 +38578,29 @@
           <cell r="T502">
             <v>6</v>
           </cell>
-          <cell r="U502" t="str">
-            <v/>
+          <cell r="U502">
+            <v>4.5</v>
           </cell>
           <cell r="V502">
-            <v>0</v>
+            <v>3.2259999999999997E-2</v>
           </cell>
           <cell r="W502">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="503">
           <cell r="A503" t="str">
             <v>S-2026-06-16</v>
           </cell>
-          <cell r="B503" t="str">
-            <v>chua rl</v>
+          <cell r="B503"/>
+          <cell r="C503" t="str">
+            <v>RPRO-260605-0678</v>
           </cell>
           <cell r="D503" t="str">
             <v>PUR2606040001S</v>
           </cell>
           <cell r="E503" t="str">
-            <v/>
+            <v>BDB-000393</v>
           </cell>
           <cell r="F503" t="str">
             <v>PVN-004438</v>
@@ -37883,7 +38618,7 @@
             <v>0</v>
           </cell>
           <cell r="K503">
-            <v>0</v>
+            <v>70</v>
           </cell>
           <cell r="L503" t="str">
             <v>ADIDAS</v>
@@ -37912,75 +38647,828 @@
           <cell r="T503">
             <v>6</v>
           </cell>
-          <cell r="U503" t="str">
-            <v/>
+          <cell r="U503">
+            <v>6.2</v>
           </cell>
           <cell r="V503">
-            <v>0</v>
+            <v>4.3479999999999998E-2</v>
           </cell>
           <cell r="W503">
-            <v>0</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="504">
+          <cell r="A504" t="str">
+            <v>S-2026-06-17</v>
+          </cell>
+          <cell r="B504"/>
+          <cell r="C504" t="str">
+            <v>RPRO-260605-0679</v>
+          </cell>
+          <cell r="D504" t="str">
+            <v>PUR2606050002S</v>
+          </cell>
           <cell r="E504" t="str">
-            <v/>
+            <v>BDB-000353</v>
+          </cell>
+          <cell r="F504" t="str">
+            <v>PVN-004350</v>
+          </cell>
+          <cell r="G504" t="str">
+            <v>OrthoLite Regular SEEDPEARL/12-0703TPX Flat Sheet 0.13D 35+/-4 Asker C 1.1M 1.47M 13mm</v>
+          </cell>
+          <cell r="H504">
+            <v>10</v>
+          </cell>
+          <cell r="I504">
+            <v>10</v>
           </cell>
           <cell r="J504">
             <v>0</v>
           </cell>
           <cell r="K504">
-            <v>0</v>
-          </cell>
-          <cell r="U504" t="str">
-            <v/>
+            <v>10</v>
+          </cell>
+          <cell r="L504" t="str">
+            <v>CAMPER</v>
+          </cell>
+          <cell r="M504" t="str">
+            <v>SSO-2606-00239  - URGENT (6-13)</v>
+          </cell>
+          <cell r="N504" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O504" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P504">
+            <v>46178</v>
+          </cell>
+          <cell r="Q504">
+            <v>46185</v>
+          </cell>
+          <cell r="R504">
+            <v>46182</v>
+          </cell>
+          <cell r="S504">
+            <v>6</v>
+          </cell>
+          <cell r="T504">
+            <v>7</v>
+          </cell>
+          <cell r="U504">
+            <v>13</v>
           </cell>
           <cell r="V504">
-            <v>0</v>
+            <v>0.1</v>
           </cell>
           <cell r="W504">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="505">
+          <cell r="A505" t="str">
+            <v>S-2026-06-18</v>
+          </cell>
+          <cell r="B505"/>
+          <cell r="C505" t="str">
+            <v>RPRO-260605-0680</v>
+          </cell>
+          <cell r="D505" t="str">
+            <v>PUR2606050002S</v>
+          </cell>
           <cell r="E505" t="str">
-            <v/>
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F505" t="str">
+            <v>PVN-002539</v>
+          </cell>
+          <cell r="G505" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 5mm</v>
+          </cell>
+          <cell r="H505">
+            <v>50</v>
+          </cell>
+          <cell r="I505">
+            <v>50</v>
           </cell>
           <cell r="J505">
             <v>0</v>
           </cell>
           <cell r="K505">
-            <v>0</v>
-          </cell>
-          <cell r="U505" t="str">
-            <v/>
+            <v>50</v>
+          </cell>
+          <cell r="L505" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M505" t="str">
+            <v>Sample - URGENT (6-13)</v>
+          </cell>
+          <cell r="N505" t="str">
+            <v>Flat sheet + Die Cut</v>
+          </cell>
+          <cell r="O505" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P505">
+            <v>46178</v>
+          </cell>
+          <cell r="Q505">
+            <v>46185</v>
+          </cell>
+          <cell r="R505">
+            <v>46182</v>
+          </cell>
+          <cell r="S505">
+            <v>6</v>
+          </cell>
+          <cell r="T505">
+            <v>7</v>
+          </cell>
+          <cell r="U505">
+            <v>5</v>
           </cell>
           <cell r="V505">
-            <v>0</v>
+            <v>3.5709999999999999E-2</v>
           </cell>
           <cell r="W505">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="506">
+          <cell r="A506" t="str">
+            <v>S-2026-06-19</v>
+          </cell>
+          <cell r="B506"/>
+          <cell r="C506" t="str">
+            <v>RPRO-260605-0681</v>
+          </cell>
+          <cell r="D506" t="str">
+            <v>PUR2606050002S</v>
+          </cell>
           <cell r="E506" t="str">
-            <v/>
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F506" t="str">
+            <v>PVN-003300</v>
+          </cell>
+          <cell r="G506" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 2mm</v>
+          </cell>
+          <cell r="H506">
+            <v>50</v>
+          </cell>
+          <cell r="I506">
+            <v>50</v>
           </cell>
           <cell r="J506">
             <v>0</v>
           </cell>
           <cell r="K506">
+            <v>50</v>
+          </cell>
+          <cell r="L506" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M506" t="str">
+            <v>SSO-2606-00242 - URGENT (6-13)</v>
+          </cell>
+          <cell r="N506" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O506" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P506">
+            <v>46178</v>
+          </cell>
+          <cell r="Q506">
+            <v>46185</v>
+          </cell>
+          <cell r="R506">
+            <v>46182</v>
+          </cell>
+          <cell r="S506">
+            <v>6</v>
+          </cell>
+          <cell r="T506">
+            <v>7</v>
+          </cell>
+          <cell r="U506">
+            <v>2</v>
+          </cell>
+          <cell r="V506">
+            <v>1.4290000000000001E-2</v>
+          </cell>
+          <cell r="W506">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="507">
+          <cell r="A507" t="str">
+            <v>S-2026-06-20</v>
+          </cell>
+          <cell r="B507"/>
+          <cell r="C507" t="str">
+            <v>RPRO-260605-0682</v>
+          </cell>
+          <cell r="D507" t="str">
+            <v>PUR-202606050001S</v>
+          </cell>
+          <cell r="E507" t="str">
+            <v>BDB-000067</v>
+          </cell>
+          <cell r="F507" t="str">
+            <v>PVN-001452</v>
+          </cell>
+          <cell r="G507" t="str">
+            <v>OrthoLite Ultra SEEDPEARL/12-0703TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+          </cell>
+          <cell r="H507">
+            <v>10</v>
+          </cell>
+          <cell r="I507">
+            <v>10</v>
+          </cell>
+          <cell r="J507">
             <v>0</v>
           </cell>
-          <cell r="U506" t="str">
-            <v/>
-          </cell>
-          <cell r="V506">
+          <cell r="K507">
+            <v>10</v>
+          </cell>
+          <cell r="L507" t="str">
+            <v>PUMA</v>
+          </cell>
+          <cell r="M507" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N507" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O507" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P507">
+            <v>46178</v>
+          </cell>
+          <cell r="Q507">
+            <v>46185</v>
+          </cell>
+          <cell r="R507">
+            <v>46182</v>
+          </cell>
+          <cell r="S507">
+            <v>6</v>
+          </cell>
+          <cell r="T507">
+            <v>7</v>
+          </cell>
+          <cell r="U507">
+            <v>4.5</v>
+          </cell>
+          <cell r="V507">
+            <v>3.2259999999999997E-2</v>
+          </cell>
+          <cell r="W507">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="508">
+          <cell r="A508" t="str">
+            <v>S-2026-06-21</v>
+          </cell>
+          <cell r="B508"/>
+          <cell r="C508" t="str">
+            <v>RPRO-260605-0683</v>
+          </cell>
+          <cell r="D508" t="str">
+            <v>PUR-202606050001S</v>
+          </cell>
+          <cell r="E508" t="str">
+            <v>BDB-000317</v>
+          </cell>
+          <cell r="F508" t="str">
+            <v>PVN-004076</v>
+          </cell>
+          <cell r="G508" t="str">
+            <v>OrthoLite Regular NEUTRAL GRAY/17-4402TPX Flat Sheet 0.13D 15+/-4 Asker C 1.1M 2M 24mm</v>
+          </cell>
+          <cell r="H508">
+            <v>20</v>
+          </cell>
+          <cell r="I508">
+            <v>20</v>
+          </cell>
+          <cell r="J508">
             <v>0</v>
           </cell>
-          <cell r="W506">
+          <cell r="K508">
+            <v>20</v>
+          </cell>
+          <cell r="L508" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M508" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N508" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O508" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P508">
+            <v>46178</v>
+          </cell>
+          <cell r="Q508">
+            <v>46185</v>
+          </cell>
+          <cell r="R508">
+            <v>46182</v>
+          </cell>
+          <cell r="S508">
+            <v>6</v>
+          </cell>
+          <cell r="T508">
+            <v>7</v>
+          </cell>
+          <cell r="U508">
+            <v>24</v>
+          </cell>
+          <cell r="V508">
+            <v>0.2</v>
+          </cell>
+          <cell r="W508">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="509">
+          <cell r="A509" t="str">
+            <v>S-2026-06-22</v>
+          </cell>
+          <cell r="B509"/>
+          <cell r="C509" t="str">
+            <v>RPRO-260605-0684</v>
+          </cell>
+          <cell r="D509" t="str">
+            <v>PUR-202606050001S</v>
+          </cell>
+          <cell r="E509" t="str">
+            <v>BDB-000055</v>
+          </cell>
+          <cell r="F509" t="str">
+            <v>PVN-003327</v>
+          </cell>
+          <cell r="G509" t="str">
+            <v>OrthoLite X-40 TRUE BLUE/19-4057TPX 0.16D 35+/-4 Asker C 1.1M 1.7M 4mm</v>
+          </cell>
+          <cell r="H509">
+            <v>30</v>
+          </cell>
+          <cell r="I509">
+            <v>30</v>
+          </cell>
+          <cell r="J509">
             <v>0</v>
           </cell>
+          <cell r="K509">
+            <v>30</v>
+          </cell>
+          <cell r="L509" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M509" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N509" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O509" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P509">
+            <v>46178</v>
+          </cell>
+          <cell r="Q509">
+            <v>46185</v>
+          </cell>
+          <cell r="R509">
+            <v>46182</v>
+          </cell>
+          <cell r="S509">
+            <v>6</v>
+          </cell>
+          <cell r="T509">
+            <v>7</v>
+          </cell>
+          <cell r="U509">
+            <v>4</v>
+          </cell>
+          <cell r="V509">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W509">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="510">
+          <cell r="A510" t="str">
+            <v>S-2026-06-23</v>
+          </cell>
+          <cell r="B510"/>
+          <cell r="C510" t="str">
+            <v>RPRO-260605-0685</v>
+          </cell>
+          <cell r="D510" t="str">
+            <v>PUR-202606050001S</v>
+          </cell>
+          <cell r="E510" t="str">
+            <v>BDB-000328</v>
+          </cell>
+          <cell r="F510" t="str">
+            <v>PVN-004212</v>
+          </cell>
+          <cell r="G510" t="str">
+            <v>OrthoLite X-40-Hybrid TRUE BLUE/19-4057TPX Hybrid Flat Sheet 0.16D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H510">
+            <v>20</v>
+          </cell>
+          <cell r="I510">
+            <v>20</v>
+          </cell>
+          <cell r="J510">
+            <v>0</v>
+          </cell>
+          <cell r="K510">
+            <v>20</v>
+          </cell>
+          <cell r="L510" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M510" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N510" t="str">
+            <v>DIE-CUT</v>
+          </cell>
+          <cell r="O510" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P510">
+            <v>46178</v>
+          </cell>
+          <cell r="Q510">
+            <v>46185</v>
+          </cell>
+          <cell r="R510">
+            <v>46182</v>
+          </cell>
+          <cell r="S510">
+            <v>6</v>
+          </cell>
+          <cell r="T510">
+            <v>7</v>
+          </cell>
+          <cell r="U510">
+            <v>3</v>
+          </cell>
+          <cell r="V510">
+            <v>2.1739999999999999E-2</v>
+          </cell>
+          <cell r="W510">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="511">
+          <cell r="A511" t="str">
+            <v>S-2026-06-24</v>
+          </cell>
+          <cell r="B511"/>
+          <cell r="C511" t="str">
+            <v>RPRO-260605-0686</v>
+          </cell>
+          <cell r="D511" t="str">
+            <v>PUR-202606050001S</v>
+          </cell>
+          <cell r="E511" t="str">
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F511" t="str">
+            <v>PVN-002973</v>
+          </cell>
+          <cell r="G511" t="str">
+            <v>UltraLite-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+          </cell>
+          <cell r="H511">
+            <v>30</v>
+          </cell>
+          <cell r="I511">
+            <v>30</v>
+          </cell>
+          <cell r="J511">
+            <v>0</v>
+          </cell>
+          <cell r="K511">
+            <v>30</v>
+          </cell>
+          <cell r="L511" t="str">
+            <v>WILSON</v>
+          </cell>
+          <cell r="M511" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N511" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O511" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P511">
+            <v>46178</v>
+          </cell>
+          <cell r="Q511">
+            <v>46185</v>
+          </cell>
+          <cell r="R511">
+            <v>46182</v>
+          </cell>
+          <cell r="S511">
+            <v>6</v>
+          </cell>
+          <cell r="T511">
+            <v>7</v>
+          </cell>
+          <cell r="U511">
+            <v>4.5</v>
+          </cell>
+          <cell r="V511">
+            <v>3.2259999999999997E-2</v>
+          </cell>
+          <cell r="W511">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="512">
+          <cell r="A512"/>
+          <cell r="B512"/>
+          <cell r="C512"/>
+          <cell r="D512"/>
+          <cell r="E512"/>
+          <cell r="F512"/>
+          <cell r="G512"/>
+          <cell r="H512"/>
+          <cell r="I512"/>
+          <cell r="J512">
+            <v>0</v>
+          </cell>
+          <cell r="K512">
+            <v>0</v>
+          </cell>
+          <cell r="L512"/>
+          <cell r="M512"/>
+          <cell r="N512"/>
+          <cell r="O512"/>
+          <cell r="P512"/>
+          <cell r="Q512"/>
+          <cell r="R512"/>
+          <cell r="S512"/>
+          <cell r="T512"/>
+          <cell r="U512"/>
+          <cell r="V512"/>
+          <cell r="W512"/>
+        </row>
+        <row r="513">
+          <cell r="A513"/>
+          <cell r="B513"/>
+          <cell r="C513"/>
+          <cell r="D513"/>
+          <cell r="E513"/>
+          <cell r="F513"/>
+          <cell r="G513"/>
+          <cell r="H513"/>
+          <cell r="I513"/>
+          <cell r="J513">
+            <v>0</v>
+          </cell>
+          <cell r="K513">
+            <v>0</v>
+          </cell>
+          <cell r="L513"/>
+          <cell r="M513"/>
+          <cell r="N513"/>
+          <cell r="O513"/>
+          <cell r="P513"/>
+          <cell r="Q513"/>
+          <cell r="R513"/>
+          <cell r="S513"/>
+          <cell r="T513"/>
+          <cell r="U513"/>
+          <cell r="V513"/>
+          <cell r="W513"/>
+        </row>
+        <row r="514">
+          <cell r="A514"/>
+          <cell r="B514"/>
+          <cell r="C514"/>
+          <cell r="D514"/>
+          <cell r="E514"/>
+          <cell r="F514"/>
+          <cell r="G514"/>
+          <cell r="H514"/>
+          <cell r="I514"/>
+          <cell r="J514">
+            <v>0</v>
+          </cell>
+          <cell r="K514">
+            <v>0</v>
+          </cell>
+          <cell r="L514"/>
+          <cell r="M514"/>
+          <cell r="N514"/>
+          <cell r="O514"/>
+          <cell r="P514"/>
+          <cell r="Q514"/>
+          <cell r="R514"/>
+          <cell r="S514"/>
+          <cell r="T514"/>
+          <cell r="U514"/>
+          <cell r="V514"/>
+          <cell r="W514"/>
+        </row>
+        <row r="515">
+          <cell r="A515"/>
+          <cell r="B515"/>
+          <cell r="C515"/>
+          <cell r="D515"/>
+          <cell r="E515"/>
+          <cell r="F515"/>
+          <cell r="G515"/>
+          <cell r="H515"/>
+          <cell r="I515"/>
+          <cell r="J515">
+            <v>0</v>
+          </cell>
+          <cell r="K515">
+            <v>0</v>
+          </cell>
+          <cell r="L515"/>
+          <cell r="M515"/>
+          <cell r="N515"/>
+          <cell r="O515"/>
+          <cell r="P515"/>
+          <cell r="Q515"/>
+          <cell r="R515"/>
+          <cell r="S515"/>
+          <cell r="T515"/>
+          <cell r="U515"/>
+          <cell r="V515"/>
+          <cell r="W515"/>
+        </row>
+        <row r="516">
+          <cell r="A516"/>
+          <cell r="B516"/>
+          <cell r="C516"/>
+          <cell r="D516"/>
+          <cell r="E516"/>
+          <cell r="F516"/>
+          <cell r="G516"/>
+          <cell r="H516"/>
+          <cell r="I516"/>
+          <cell r="J516">
+            <v>0</v>
+          </cell>
+          <cell r="K516">
+            <v>0</v>
+          </cell>
+          <cell r="L516"/>
+          <cell r="M516"/>
+          <cell r="N516"/>
+          <cell r="O516"/>
+          <cell r="P516"/>
+          <cell r="Q516"/>
+          <cell r="R516"/>
+          <cell r="S516"/>
+          <cell r="T516"/>
+          <cell r="U516"/>
+          <cell r="V516"/>
+          <cell r="W516"/>
+        </row>
+        <row r="517">
+          <cell r="A517"/>
+          <cell r="B517"/>
+          <cell r="C517"/>
+          <cell r="D517"/>
+          <cell r="E517"/>
+          <cell r="F517"/>
+          <cell r="G517"/>
+          <cell r="H517"/>
+          <cell r="I517"/>
+          <cell r="J517">
+            <v>0</v>
+          </cell>
+          <cell r="K517">
+            <v>0</v>
+          </cell>
+          <cell r="L517"/>
+          <cell r="M517"/>
+          <cell r="N517"/>
+          <cell r="O517"/>
+          <cell r="P517"/>
+          <cell r="Q517"/>
+          <cell r="R517"/>
+          <cell r="S517"/>
+          <cell r="T517"/>
+          <cell r="U517"/>
+          <cell r="V517"/>
+          <cell r="W517"/>
+        </row>
+        <row r="518">
+          <cell r="A518"/>
+          <cell r="B518"/>
+          <cell r="C518"/>
+          <cell r="D518"/>
+          <cell r="E518"/>
+          <cell r="F518"/>
+          <cell r="G518"/>
+          <cell r="H518"/>
+          <cell r="I518"/>
+          <cell r="J518">
+            <v>0</v>
+          </cell>
+          <cell r="K518">
+            <v>0</v>
+          </cell>
+          <cell r="L518"/>
+          <cell r="M518"/>
+          <cell r="N518"/>
+          <cell r="O518"/>
+          <cell r="P518"/>
+          <cell r="Q518"/>
+          <cell r="R518"/>
+          <cell r="S518"/>
+          <cell r="T518"/>
+          <cell r="U518"/>
+          <cell r="V518"/>
+          <cell r="W518"/>
+        </row>
+        <row r="519">
+          <cell r="A519"/>
+          <cell r="B519"/>
+          <cell r="C519"/>
+          <cell r="D519"/>
+          <cell r="E519"/>
+          <cell r="F519"/>
+          <cell r="G519"/>
+          <cell r="H519"/>
+          <cell r="I519"/>
+          <cell r="J519">
+            <v>0</v>
+          </cell>
+          <cell r="K519">
+            <v>0</v>
+          </cell>
+          <cell r="L519"/>
+          <cell r="M519"/>
+          <cell r="N519"/>
+          <cell r="O519"/>
+          <cell r="P519"/>
+          <cell r="Q519"/>
+          <cell r="R519"/>
+          <cell r="S519"/>
+          <cell r="T519"/>
+          <cell r="U519"/>
+          <cell r="V519"/>
+          <cell r="W519"/>
+        </row>
+        <row r="520">
+          <cell r="A520"/>
+          <cell r="B520"/>
+          <cell r="C520"/>
+          <cell r="D520"/>
+          <cell r="E520"/>
+          <cell r="F520"/>
+          <cell r="G520"/>
+          <cell r="H520"/>
+          <cell r="I520"/>
+          <cell r="J520">
+            <v>0</v>
+          </cell>
+          <cell r="K520">
+            <v>0</v>
+          </cell>
+          <cell r="L520"/>
+          <cell r="M520"/>
+          <cell r="N520"/>
+          <cell r="O520"/>
+          <cell r="P520"/>
+          <cell r="Q520"/>
+          <cell r="R520"/>
+          <cell r="S520"/>
+          <cell r="T520"/>
+          <cell r="U520"/>
+          <cell r="V520"/>
+          <cell r="W520"/>
         </row>
       </sheetData>
       <sheetData sheetId="4"/>
@@ -37988,11 +39476,7 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
-        <row r="1">
-          <cell r="A1"/>
-        </row>
-      </sheetData>
+      <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
@@ -38087,19 +39571,19 @@
       <sheetData sheetId="101"/>
       <sheetData sheetId="102"/>
       <sheetData sheetId="103"/>
-      <sheetData sheetId="104">
+      <sheetData sheetId="104"/>
+      <sheetData sheetId="105"/>
+      <sheetData sheetId="106">
         <row r="1">
           <cell r="F1" t="str">
             <v>No_Item</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="105"/>
-      <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
-      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="108"/>
       <sheetData sheetId="109"/>
-      <sheetData sheetId="110"/>
+      <sheetData sheetId="110" refreshError="1"/>
       <sheetData sheetId="111" refreshError="1"/>
       <sheetData sheetId="112" refreshError="1"/>
       <sheetData sheetId="113" refreshError="1"/>
@@ -38276,6 +39760,8 @@
       <sheetData sheetId="284" refreshError="1"/>
       <sheetData sheetId="285" refreshError="1"/>
       <sheetData sheetId="286" refreshError="1"/>
+      <sheetData sheetId="287" refreshError="1"/>
+      <sheetData sheetId="288" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -38608,11 +40094,11 @@
       <c r="B1" s="1">
         <v>46155.681657291665</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -39902,23 +41388,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="91" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="90" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="89" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="86" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="85" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -39964,13 +41450,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122916665</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -41345,23 +42831,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -41407,13 +42893,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122800926</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -42788,23 +44274,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A22">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -42849,13 +44335,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122800926</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -44133,17 +45619,1535 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="22" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8272257-794B-4F96-B62F-69670D0E4B1D}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:O668"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="175.54296875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="121.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>18</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="C3" s="19" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000393</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>478</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="22">
+        <v>70</v>
+      </c>
+      <c r="G3" s="23">
+        <v>70</v>
+      </c>
+      <c r="H3" s="24">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00156  - URGENT (6-10)</v>
+      </c>
+      <c r="K3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Molded</v>
+      </c>
+      <c r="L3" s="26">
+        <v>4</v>
+      </c>
+      <c r="M3" s="81" t="s">
+        <v>301</v>
+      </c>
+      <c r="N3" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A3,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46180</v>
+      </c>
+      <c r="O3" s="82">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="76"/>
+    </row>
+    <row r="5" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="C5" s="19" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000353</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="F5" s="22">
+        <v>10</v>
+      </c>
+      <c r="G5" s="23">
+        <v>10</v>
+      </c>
+      <c r="H5" s="24">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,12,0)</f>
+        <v>CAMPER</v>
+      </c>
+      <c r="J5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00239  - URGENT (6-13)</v>
+      </c>
+      <c r="K5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L5" s="26">
+        <v>1</v>
+      </c>
+      <c r="M5" s="27"/>
+      <c r="N5" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A5,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="76"/>
+    </row>
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="C7" s="19" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="F7" s="22">
+        <v>50</v>
+      </c>
+      <c r="G7" s="23">
+        <v>50</v>
+      </c>
+      <c r="H7" s="24">
+        <f>VLOOKUP(A7,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I7" s="25" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J7" s="25" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample - URGENT (6-13)</v>
+      </c>
+      <c r="K7" s="25" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet + Die Cut</v>
+      </c>
+      <c r="L7" s="26">
+        <v>3</v>
+      </c>
+      <c r="M7" s="40"/>
+      <c r="N7" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A7,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="C8" s="19" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="F8" s="22">
+        <v>50</v>
+      </c>
+      <c r="G8" s="23">
+        <v>50</v>
+      </c>
+      <c r="H8" s="24">
+        <f>VLOOKUP(A8,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I8" s="25" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J8" s="25" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00242 - URGENT (6-13)</v>
+      </c>
+      <c r="K8" s="25" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L8" s="26"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A8,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C9" s="19" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="F9" s="22">
+        <v>30</v>
+      </c>
+      <c r="G9" s="23">
+        <v>30</v>
+      </c>
+      <c r="H9" s="24">
+        <f>VLOOKUP(A9,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="25" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,12,0)</f>
+        <v>WILSON</v>
+      </c>
+      <c r="J9" s="25" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K9" s="25" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,14,0)</f>
+        <v>MOLDED</v>
+      </c>
+      <c r="L9" s="26">
+        <v>1</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A9,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="76"/>
+    </row>
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="C11" s="19" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000067</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="F11" s="22">
+        <v>10</v>
+      </c>
+      <c r="G11" s="23">
+        <v>10</v>
+      </c>
+      <c r="H11" s="24">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I11" s="25" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,12,0)</f>
+        <v>PUMA</v>
+      </c>
+      <c r="J11" s="25" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K11" s="25" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,14,0)</f>
+        <v>MOLDED</v>
+      </c>
+      <c r="L11" s="26">
+        <v>1</v>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A11,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="76"/>
+    </row>
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>497</v>
+      </c>
+      <c r="C13" s="19" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000317</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>499</v>
+      </c>
+      <c r="F13" s="22">
+        <v>20</v>
+      </c>
+      <c r="G13" s="23">
+        <v>20</v>
+      </c>
+      <c r="H13" s="24">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ASICS</v>
+      </c>
+      <c r="J13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
+        <v>MOLDED</v>
+      </c>
+      <c r="L13" s="26">
+        <v>4</v>
+      </c>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A13,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+      <c r="O13" s="82">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="62"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="76"/>
+    </row>
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>501</v>
+      </c>
+      <c r="C15" s="19" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000055</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>503</v>
+      </c>
+      <c r="F15" s="22">
+        <v>30</v>
+      </c>
+      <c r="G15" s="23">
+        <v>30</v>
+      </c>
+      <c r="H15" s="24">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="25" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ASICS</v>
+      </c>
+      <c r="J15" s="25" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K15" s="25" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,14,0)</f>
+        <v>MOLDED</v>
+      </c>
+      <c r="L15" s="26">
+        <v>1</v>
+      </c>
+      <c r="M15" s="40"/>
+      <c r="N15" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="62"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="76"/>
+    </row>
+    <row r="17" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>505</v>
+      </c>
+      <c r="C17" s="19" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000328</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>507</v>
+      </c>
+      <c r="F17" s="22">
+        <v>20</v>
+      </c>
+      <c r="G17" s="23">
+        <v>20</v>
+      </c>
+      <c r="H17" s="24">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I17" s="25" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ASICS</v>
+      </c>
+      <c r="J17" s="25" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K17" s="25" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>DIE-CUT</v>
+      </c>
+      <c r="L17" s="26">
+        <v>1</v>
+      </c>
+      <c r="M17" s="27"/>
+      <c r="N17" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="62"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="76"/>
+    </row>
+    <row r="19" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>509</v>
+      </c>
+      <c r="C19" s="19" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000391</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>510</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="F19" s="22">
+        <v>40</v>
+      </c>
+      <c r="G19" s="23">
+        <v>40</v>
+      </c>
+      <c r="H19" s="24">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I19" s="25" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ON RUNNING</v>
+      </c>
+      <c r="J19" s="25" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2605-00765</v>
+      </c>
+      <c r="K19" s="25" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>OV-0408</v>
+      </c>
+      <c r="L19" s="26">
+        <v>2</v>
+      </c>
+      <c r="M19" s="40"/>
+      <c r="N19" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46182</v>
+      </c>
+      <c r="O19" s="82">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="62"/>
+      <c r="B20" s="63" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="64" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="65" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="66" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="67" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="68" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="69" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="70" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="70" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="71"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="62"/>
+      <c r="B21" s="63" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="64" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="65" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="66" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="67" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="68" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="69" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I21" s="70" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="70" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="71"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A21,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="62"/>
+      <c r="B22" s="63" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C22" s="64" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D22" s="65" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" s="66" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F22" s="67" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G22" s="68" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H22" s="69" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I22" s="70" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K22" s="70" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L22" s="71"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A22,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="62"/>
+      <c r="B23" s="63" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C23" s="64" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D23" s="65" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E23" s="66" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F23" s="67" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G23" s="68" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H23" s="69" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I23" s="70" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J23" s="25" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K23" s="70" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L23" s="71"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A23,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="62"/>
+      <c r="B24" s="63" t="e">
+        <f>VLOOKUP(A24,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C24" s="64" t="e">
+        <f>VLOOKUP($A24,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D24" s="65" t="e">
+        <f>VLOOKUP($A24,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E24" s="66" t="e">
+        <f>VLOOKUP(A24,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F24" s="67" t="e">
+        <f>VLOOKUP(A24,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G24" s="68" t="e">
+        <f>VLOOKUP(A24,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H24" s="69" t="e">
+        <f>VLOOKUP(A24,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I24" s="70" t="e">
+        <f>VLOOKUP($A24,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J24" s="25" t="e">
+        <f>VLOOKUP($A24,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K24" s="70" t="e">
+        <f>VLOOKUP($A24,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L24" s="71"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A24,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="3" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="41"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="51"/>
+    </row>
+    <row r="26" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="56"/>
+    </row>
+    <row r="28" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L28" s="56"/>
+    </row>
+    <row r="29" spans="1:15" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="55"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="58"/>
+    </row>
+    <row r="30" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L30" s="56"/>
+    </row>
+    <row r="31" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L31" s="56"/>
+    </row>
+    <row r="32" spans="1:15" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="57" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="58"/>
+    </row>
+    <row r="58" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="56"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="58"/>
+    </row>
+    <row r="59" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="2"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="53"/>
+      <c r="L59" s="56"/>
+      <c r="M59" s="57"/>
+      <c r="N59" s="58"/>
+    </row>
+    <row r="668" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A668" s="2"/>
+      <c r="B668" s="52"/>
+      <c r="C668" s="2"/>
+      <c r="D668" s="2"/>
+      <c r="E668" s="60"/>
+      <c r="H668" s="55"/>
+      <c r="I668" s="53"/>
+      <c r="J668" s="53"/>
+      <c r="K668" s="53"/>
+      <c r="L668" s="61"/>
+      <c r="M668" s="57"/>
+      <c r="N668" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E24" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N25" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="3">
+      <filters blank="1">
+        <filter val="PVN-001452"/>
+        <filter val="PVN-002539"/>
+        <filter val="PVN-002973"/>
+        <filter val="PVN-003300"/>
+        <filter val="PVN-003327"/>
+        <filter val="PVN-004076"/>
+        <filter val="PVN-004212"/>
+        <filter val="PVN-004350"/>
+        <filter val="PVN-004430"/>
+        <filter val="PVN-004438"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A24">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D19">
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
@@ -44153,12 +47157,12 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
-  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="22" max="15" man="1"/>
+    <brk id="25" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -44194,13 +47198,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122800926</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -45543,23 +48547,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="83" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="79" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="78" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -45604,13 +48608,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122800926</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -47011,23 +50015,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="77" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="76" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="75" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="74" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="72" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -47072,13 +50076,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122916665</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -48445,23 +51449,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="70" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -48505,13 +51509,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122916665</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -48725,11 +51729,11 @@
         <v>46167.440663078705</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
       <c r="H7" s="4"/>
       <c r="I7" s="5"/>
       <c r="J7" s="7"/>
@@ -49720,39 +52724,39 @@
     <mergeCell ref="D7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="63" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A6 A14:A18">
-    <cfRule type="duplicateValues" dxfId="62" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="61" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A13">
-    <cfRule type="duplicateValues" dxfId="60" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A1048576">
-    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C6 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="58" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C13">
-    <cfRule type="duplicateValues" dxfId="56" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:L8">
-    <cfRule type="duplicateValues" dxfId="54" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="duplicateValues" dxfId="52" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="51" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="9"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -49797,13 +52801,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122916665</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -51122,26 +54126,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A15">
-    <cfRule type="duplicateValues" dxfId="49" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A21">
-    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="44" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -51187,13 +54191,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122916665</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -52542,23 +55546,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="42" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="40" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -52603,13 +55607,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122916665</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -53991,24 +56995,24 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="34" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -54054,13 +57058,13 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.475122916665</v>
-      </c>
-      <c r="D1" s="81" t="s">
+        <v>46178.924539467589</v>
+      </c>
+      <c r="D1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
@@ -55399,23 +58403,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D650652-9D11-44C1-8210-99001EF99009}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{800C6EB4-0DF0-470E-8FE5-3E35347FBA1B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="12" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="12" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,11 @@
     <sheet name="3.6" sheetId="11" r:id="rId11"/>
     <sheet name="4.6" sheetId="12" r:id="rId12"/>
     <sheet name="5.6" sheetId="13" r:id="rId13"/>
+    <sheet name="6.6" sheetId="14" r:id="rId14"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
@@ -45,6 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'3.6'!$A$2:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'4.6'!$A$2:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'5.6'!$A$2:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'6.6'!$A$2:$M$18</definedName>
     <definedName name="AE" localSheetId="8">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -58,6 +60,7 @@
     <definedName name="AE" localSheetId="10">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="11">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="12">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="13">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'1.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
@@ -71,6 +74,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'3.6'!$A$1:$N$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'4.6'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'5.6'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'6.6'!$A$1:$M$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'1.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
@@ -84,6 +88,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'3.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'4.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'5.6'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'6.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -97,6 +102,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -110,6 +116,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -123,6 +130,7 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -136,6 +144,7 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -149,6 +158,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -162,6 +172,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="8" hidden="1">'1.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
@@ -175,6 +186,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="10" hidden="1">'3.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="11" hidden="1">'4.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="12" hidden="1">'5.6'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="13" hidden="1">'6.6'!#REF!</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -188,6 +200,7 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -201,6 +214,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -214,6 +228,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -227,6 +242,7 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -240,6 +256,7 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -253,6 +270,7 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -266,6 +284,7 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -279,6 +298,7 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -292,6 +312,7 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -305,6 +326,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -318,6 +340,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -331,6 +354,7 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -344,6 +368,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="10" hidden="1">'3.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -357,6 +382,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="10" hidden="1">'3.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -379,7 +405,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="515">
   <si>
     <t>Release Date</t>
   </si>
@@ -1995,6 +2021,15 @@
   <si>
     <t>OrthoLite HybridPlus-Recycled COLORO 063-98-46 (fluorescent) Hybrid 0.12D 25+/-4 Asker C 1.1M 2M 6mm</t>
   </si>
+  <si>
+    <t>S-2026-06-25</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>????</t>
+  </si>
 </sst>
 </file>
 
@@ -2611,7 +2646,67 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="100">
+  <dxfs count="106">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3786,12 +3881,14 @@
       <sheetName val="3.6"/>
       <sheetName val="4.6"/>
       <sheetName val="5.6"/>
-      <sheetName val="form 2 (20)"/>
+      <sheetName val="6.6"/>
+      <sheetName val="form 2 (21)"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
+      <sheetName val="form 2 (20)"/>
       <sheetName val="form 2 (18)"/>
       <sheetName val="form 2 (19)"/>
       <sheetName val="form 2 (17)"/>
@@ -3837,7 +3934,6 @@
       <sheetName val="22.5"/>
       <sheetName val="30.5"/>
       <sheetName val="3.6 (L)"/>
-      <sheetName val="6.6"/>
       <sheetName val="9.6"/>
       <sheetName val="9.6 (L)"/>
       <sheetName val="10.6"/>
@@ -4017,16 +4113,16 @@
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>24949</v>
+            <v>24969</v>
           </cell>
           <cell r="I2">
-            <v>24949</v>
+            <v>24969</v>
           </cell>
           <cell r="J2">
             <v>23583</v>
           </cell>
           <cell r="K2">
-            <v>1366</v>
+            <v>1386</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
@@ -4048,7 +4144,7 @@
           </cell>
           <cell r="V2"/>
           <cell r="W2">
-            <v>1271</v>
+            <v>1272</v>
           </cell>
         </row>
         <row r="3">
@@ -36614,7 +36710,9 @@
           <cell r="A474" t="str">
             <v>S-2026-05-98</v>
           </cell>
-          <cell r="B474"/>
+          <cell r="B474" t="str">
+            <v xml:space="preserve">Xịn dời ETD </v>
+          </cell>
           <cell r="C474" t="str">
             <v>RPRO-260529-0344</v>
           </cell>
@@ -39210,40 +39308,84 @@
           </cell>
         </row>
         <row r="512">
-          <cell r="A512"/>
-          <cell r="B512"/>
-          <cell r="C512"/>
-          <cell r="D512"/>
-          <cell r="E512"/>
-          <cell r="F512"/>
-          <cell r="G512"/>
-          <cell r="H512"/>
-          <cell r="I512"/>
+          <cell r="A512" t="str">
+            <v>S-2026-06-25</v>
+          </cell>
+          <cell r="B512" t="str">
+            <v>Chưa rl</v>
+          </cell>
+          <cell r="C512" t="str">
+            <v>RPRO-260606-0217</v>
+          </cell>
+          <cell r="D512" t="str">
+            <v xml:space="preserve">PUR2606050003S   </v>
+          </cell>
+          <cell r="E512" t="str">
+            <v>BDB-000067</v>
+          </cell>
+          <cell r="F512" t="str">
+            <v>PVN-003672</v>
+          </cell>
+          <cell r="G512" t="str">
+            <v>OrthoLite Ultra SEEDPEARL/12-0703TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H512">
+            <v>20</v>
+          </cell>
+          <cell r="I512">
+            <v>20</v>
+          </cell>
           <cell r="J512">
             <v>0</v>
           </cell>
           <cell r="K512">
-            <v>0</v>
-          </cell>
-          <cell r="L512"/>
-          <cell r="M512"/>
-          <cell r="N512"/>
-          <cell r="O512"/>
-          <cell r="P512"/>
-          <cell r="Q512"/>
-          <cell r="R512"/>
-          <cell r="S512"/>
-          <cell r="T512"/>
-          <cell r="U512"/>
-          <cell r="V512"/>
-          <cell r="W512"/>
+            <v>20</v>
+          </cell>
+          <cell r="L512" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M512" t="str">
+            <v>SSO-2606-00253  - URGENT (6-13)</v>
+          </cell>
+          <cell r="N512" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O512" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P512">
+            <v>46178</v>
+          </cell>
+          <cell r="Q512">
+            <v>46186</v>
+          </cell>
+          <cell r="R512">
+            <v>46183</v>
+          </cell>
+          <cell r="S512">
+            <v>6</v>
+          </cell>
+          <cell r="T512">
+            <v>8</v>
+          </cell>
+          <cell r="U512">
+            <v>3</v>
+          </cell>
+          <cell r="V512">
+            <v>2.1739999999999999E-2</v>
+          </cell>
+          <cell r="W512">
+            <v>1</v>
+          </cell>
         </row>
         <row r="513">
           <cell r="A513"/>
           <cell r="B513"/>
           <cell r="C513"/>
           <cell r="D513"/>
-          <cell r="E513"/>
+          <cell r="E513" t="str">
+            <v/>
+          </cell>
           <cell r="F513"/>
           <cell r="G513"/>
           <cell r="H513"/>
@@ -39272,7 +39414,9 @@
           <cell r="B514"/>
           <cell r="C514"/>
           <cell r="D514"/>
-          <cell r="E514"/>
+          <cell r="E514" t="str">
+            <v/>
+          </cell>
           <cell r="F514"/>
           <cell r="G514"/>
           <cell r="H514"/>
@@ -39301,7 +39445,9 @@
           <cell r="B515"/>
           <cell r="C515"/>
           <cell r="D515"/>
-          <cell r="E515"/>
+          <cell r="E515" t="str">
+            <v/>
+          </cell>
           <cell r="F515"/>
           <cell r="G515"/>
           <cell r="H515"/>
@@ -39330,7 +39476,9 @@
           <cell r="B516"/>
           <cell r="C516"/>
           <cell r="D516"/>
-          <cell r="E516"/>
+          <cell r="E516" t="str">
+            <v/>
+          </cell>
           <cell r="F516"/>
           <cell r="G516"/>
           <cell r="H516"/>
@@ -39359,7 +39507,9 @@
           <cell r="B517"/>
           <cell r="C517"/>
           <cell r="D517"/>
-          <cell r="E517"/>
+          <cell r="E517" t="str">
+            <v/>
+          </cell>
           <cell r="F517"/>
           <cell r="G517"/>
           <cell r="H517"/>
@@ -39388,7 +39538,9 @@
           <cell r="B518"/>
           <cell r="C518"/>
           <cell r="D518"/>
-          <cell r="E518"/>
+          <cell r="E518" t="str">
+            <v/>
+          </cell>
           <cell r="F518"/>
           <cell r="G518"/>
           <cell r="H518"/>
@@ -39417,7 +39569,9 @@
           <cell r="B519"/>
           <cell r="C519"/>
           <cell r="D519"/>
-          <cell r="E519"/>
+          <cell r="E519" t="str">
+            <v/>
+          </cell>
           <cell r="F519"/>
           <cell r="G519"/>
           <cell r="H519"/>
@@ -39573,18 +39727,18 @@
       <sheetData sheetId="103"/>
       <sheetData sheetId="104"/>
       <sheetData sheetId="105"/>
-      <sheetData sheetId="106">
+      <sheetData sheetId="106"/>
+      <sheetData sheetId="107">
         <row r="1">
           <cell r="F1" t="str">
             <v>No_Item</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="107"/>
       <sheetData sheetId="108"/>
       <sheetData sheetId="109"/>
-      <sheetData sheetId="110" refreshError="1"/>
-      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="110"/>
+      <sheetData sheetId="111"/>
       <sheetData sheetId="112" refreshError="1"/>
       <sheetData sheetId="113" refreshError="1"/>
       <sheetData sheetId="114" refreshError="1"/>
@@ -39762,6 +39916,7 @@
       <sheetData sheetId="286" refreshError="1"/>
       <sheetData sheetId="287" refreshError="1"/>
       <sheetData sheetId="288" refreshError="1"/>
+      <sheetData sheetId="289" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -41388,23 +41543,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="99" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="98" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="97" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="96" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="94" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="93" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -41450,7 +41605,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -42831,23 +42986,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -42893,7 +43048,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -44274,23 +44429,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A22">
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:A1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -44335,7 +44490,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -45619,23 +45774,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -45667,7 +45822,7 @@
     <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
     <col min="9" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="33.54296875" style="53" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="21.453125" style="61" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
     <col min="13" max="13" width="22" style="57" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
     <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
@@ -45680,7 +45835,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -45859,8 +46014,8 @@
         <f>_xlfn.IFNA(VLOOKUP(A5,'[2]master plan'!A:R,18,0),"")</f>
         <v>46182</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>320</v>
+      <c r="O5" s="58">
+        <v>46240</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -46093,6 +46248,9 @@
         <f>_xlfn.IFNA(VLOOKUP(A11,'[2]master plan'!A:R,18,0),"")</f>
         <v>46182</v>
       </c>
+      <c r="O11" s="58">
+        <v>46240</v>
+      </c>
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="62"/>
@@ -46224,6 +46382,9 @@
         <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
         <v>46182</v>
       </c>
+      <c r="O15" s="3" t="s">
+        <v>513</v>
+      </c>
     </row>
     <row r="16" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="62"/>
@@ -46287,6 +46448,9 @@
       <c r="N17" s="28">
         <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
         <v>46182</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -47134,26 +47298,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D19">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -47163,6 +47327,1296 @@
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="25" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D9B619B-ADEB-444B-B0C4-D546C9681600}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:M661"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="175.54296875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46179.701553935185</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>1</v>
+      </c>
+      <c r="M1" s="7"/>
+    </row>
+    <row r="2" spans="1:13" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>VLOOKUP(A3,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260606-0217</v>
+      </c>
+      <c r="C3" s="19" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000067</v>
+      </c>
+      <c r="D3" s="20" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-003672</v>
+      </c>
+      <c r="E3" s="21" t="str">
+        <f>VLOOKUP(A3,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra SEEDPEARL/12-0703TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+      </c>
+      <c r="F3" s="22">
+        <f>VLOOKUP(A3,'[2]master plan'!A:H,8,0)</f>
+        <v>20</v>
+      </c>
+      <c r="G3" s="23">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="24">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00253  - URGENT (6-13)</v>
+      </c>
+      <c r="K3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L3" s="26">
+        <v>1</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C4" s="19" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D4" s="20" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E4" s="21" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F4" s="22" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G4" s="23" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H4" s="24" t="e">
+        <f>VLOOKUP(A4,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I4" s="25" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J4" s="25" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K4" s="25" t="e">
+        <f>VLOOKUP($A4,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="27"/>
+    </row>
+    <row r="5" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C5" s="19" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D5" s="20" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E5" s="21" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F5" s="22" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G5" s="23" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H5" s="24" t="e">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I5" s="25" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J5" s="25" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K5" s="25" t="e">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L5" s="26"/>
+      <c r="M5" s="40"/>
+    </row>
+    <row r="6" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="e">
+        <f>VLOOKUP(A6,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C6" s="19" t="e">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D6" s="20" t="e">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E6" s="21" t="e">
+        <f>VLOOKUP(A6,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="22" t="e">
+        <f>VLOOKUP(A6,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G6" s="23" t="e">
+        <f>VLOOKUP(A6,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H6" s="24" t="e">
+        <f>VLOOKUP(A6,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I6" s="25" t="e">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J6" s="25" t="e">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K6" s="25" t="e">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L6" s="26"/>
+      <c r="M6" s="27"/>
+    </row>
+    <row r="7" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="e">
+        <f>VLOOKUP(A7,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C7" s="19" t="e">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D7" s="20" t="e">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E7" s="21" t="e">
+        <f>VLOOKUP(A7,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F7" s="22" t="e">
+        <f>VLOOKUP(A7,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G7" s="23" t="e">
+        <f>VLOOKUP(A7,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H7" s="24" t="e">
+        <f>VLOOKUP(A7,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I7" s="25" t="e">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J7" s="25" t="e">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K7" s="25" t="e">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L7" s="26"/>
+      <c r="M7" s="27"/>
+    </row>
+    <row r="8" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="e">
+        <f>VLOOKUP(A8,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C8" s="19" t="e">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D8" s="20" t="e">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E8" s="21" t="e">
+        <f>VLOOKUP(A8,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F8" s="22" t="e">
+        <f>VLOOKUP(A8,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G8" s="23" t="e">
+        <f>VLOOKUP(A8,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H8" s="24" t="e">
+        <f>VLOOKUP(A8,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I8" s="25" t="e">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J8" s="25" t="e">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K8" s="25" t="e">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L8" s="26"/>
+      <c r="M8" s="27"/>
+    </row>
+    <row r="9" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18" t="e">
+        <f>VLOOKUP(A9,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C9" s="19" t="e">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D9" s="20" t="e">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E9" s="21" t="e">
+        <f>VLOOKUP(A9,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F9" s="22" t="e">
+        <f>VLOOKUP(A9,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G9" s="23" t="e">
+        <f>VLOOKUP(A9,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H9" s="24" t="e">
+        <f>VLOOKUP(A9,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I9" s="25" t="e">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J9" s="25" t="e">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K9" s="25" t="e">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L9" s="26"/>
+      <c r="M9" s="40"/>
+    </row>
+    <row r="10" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="e">
+        <f>VLOOKUP(A10,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C10" s="19" t="e">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D10" s="20" t="e">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" s="21" t="e">
+        <f>VLOOKUP(A10,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F10" s="22" t="e">
+        <f>VLOOKUP(A10,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G10" s="23" t="e">
+        <f>VLOOKUP(A10,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H10" s="24" t="e">
+        <f>VLOOKUP(A10,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I10" s="25" t="e">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J10" s="25" t="e">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K10" s="25" t="e">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L10" s="26"/>
+      <c r="M10" s="27"/>
+    </row>
+    <row r="11" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C11" s="19" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D11" s="20" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="21" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" s="22" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G11" s="23" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H11" s="24" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L11" s="26"/>
+      <c r="M11" s="27"/>
+    </row>
+    <row r="12" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C12" s="19" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D12" s="20" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" s="21" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F12" s="22" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G12" s="23" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H12" s="24" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L12" s="26"/>
+      <c r="M12" s="40"/>
+    </row>
+    <row r="13" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C13" s="19" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="20" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="21" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" s="22" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="23" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H13" s="24" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L13" s="26"/>
+      <c r="M13" s="40"/>
+    </row>
+    <row r="14" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C14" s="19" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D14" s="20" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="21" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="22" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="23" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H14" s="24" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
+    </row>
+    <row r="15" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C15" s="19" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D15" s="20" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="21" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" s="22" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="23" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H15" s="24" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L15" s="26"/>
+      <c r="M15" s="40"/>
+    </row>
+    <row r="16" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C16" s="19" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="20" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="21" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="22" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="23" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H16" s="24" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L16" s="26"/>
+      <c r="M16" s="40"/>
+    </row>
+    <row r="17" spans="1:13" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C17" s="19" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="20" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="21" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="22" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="23" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H17" s="24" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="40"/>
+    </row>
+    <row r="18" spans="1:13" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="41"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="50"/>
+    </row>
+    <row r="19" spans="1:13" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L19" s="56"/>
+    </row>
+    <row r="20" spans="1:13" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L20" s="56"/>
+    </row>
+    <row r="21" spans="1:13" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L21" s="56"/>
+    </row>
+    <row r="22" spans="1:13" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="55"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="57"/>
+    </row>
+    <row r="23" spans="1:13" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L23" s="56"/>
+    </row>
+    <row r="24" spans="1:13" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="57"/>
+    </row>
+    <row r="26" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="57"/>
+    </row>
+    <row r="27" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="57"/>
+    </row>
+    <row r="28" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="57"/>
+    </row>
+    <row r="29" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+    </row>
+    <row r="30" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+    </row>
+    <row r="31" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+    </row>
+    <row r="32" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+    </row>
+    <row r="33" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+    </row>
+    <row r="34" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+    </row>
+    <row r="35" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+    </row>
+    <row r="36" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+    </row>
+    <row r="37" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+    </row>
+    <row r="38" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+    </row>
+    <row r="39" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+    </row>
+    <row r="40" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+    </row>
+    <row r="41" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+    </row>
+    <row r="42" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+    </row>
+    <row r="43" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+    </row>
+    <row r="44" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+    </row>
+    <row r="45" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+    </row>
+    <row r="46" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+    </row>
+    <row r="47" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+    </row>
+    <row r="48" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+    </row>
+    <row r="49" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+    </row>
+    <row r="50" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+    </row>
+    <row r="51" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+    </row>
+    <row r="52" spans="1:13" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+    </row>
+    <row r="661" spans="1:13" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A661" s="2"/>
+      <c r="B661" s="52"/>
+      <c r="C661" s="2"/>
+      <c r="D661" s="2"/>
+      <c r="E661" s="60"/>
+      <c r="H661" s="55"/>
+      <c r="I661" s="53"/>
+      <c r="J661" s="53"/>
+      <c r="K661" s="53"/>
+      <c r="L661" s="61"/>
+      <c r="M661" s="57"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E17" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:M18" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="3">
+      <filters blank="1">
+        <filter val="PVN-003672"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A17">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="18" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -47198,7 +48652,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -48547,23 +50001,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="92" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="91" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="89" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="87" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -48608,7 +50062,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -50015,23 +51469,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="85" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="84" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="83" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="79" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -50076,7 +51530,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -51449,23 +52903,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="78" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="77" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="76" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="73" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="72" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -51509,7 +52963,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -52724,39 +54178,39 @@
     <mergeCell ref="D7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A6 A14:A18">
-    <cfRule type="duplicateValues" dxfId="70" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="69" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A13">
-    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A1048576">
-    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C6 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="66" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C13">
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:L8">
-    <cfRule type="duplicateValues" dxfId="62" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="61" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="59" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="9"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -52801,7 +54255,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -54126,26 +55580,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="58" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A15">
-    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A21">
-    <cfRule type="duplicateValues" dxfId="56" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="52" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -54191,7 +55645,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -55546,23 +57000,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="49" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -55607,7 +57061,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -56995,24 +58449,24 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="43" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="42" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -57058,7 +58512,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46178.924539467589</v>
+        <v>46179.701554050924</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -58403,23 +59857,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="35" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="30" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{800C6EB4-0DF0-470E-8FE5-3E35347FBA1B}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75102B01-28E5-4879-8A68-12ED4C094023}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="12" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="14" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,11 @@
     <sheet name="4.6" sheetId="12" r:id="rId12"/>
     <sheet name="5.6" sheetId="13" r:id="rId13"/>
     <sheet name="6.6" sheetId="14" r:id="rId14"/>
+    <sheet name="8.6" sheetId="15" r:id="rId15"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
+    <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
@@ -47,6 +48,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'4.6'!$A$2:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'5.6'!$A$2:$N$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'6.6'!$A$2:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'8.6'!$A$2:$N$21</definedName>
     <definedName name="AE" localSheetId="8">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -61,6 +63,7 @@
     <definedName name="AE" localSheetId="11">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="12">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="13">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="14">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'1.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
@@ -75,6 +78,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="11">'4.6'!$A$1:$N$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'5.6'!$A$1:$N$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'6.6'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'8.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'1.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
@@ -89,6 +93,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'4.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'5.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'6.6'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'8.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -103,6 +108,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -117,6 +123,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -131,6 +138,7 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -145,6 +153,7 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -159,6 +168,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -173,6 +183,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="8" hidden="1">'1.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
@@ -187,6 +198,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="11" hidden="1">'4.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="12" hidden="1">'5.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="13" hidden="1">'6.6'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="14" hidden="1">'8.6'!#REF!</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -201,6 +213,7 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -215,6 +228,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -229,6 +243,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -243,6 +258,7 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -257,6 +273,7 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -271,6 +288,7 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -285,6 +303,7 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -299,6 +318,7 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -313,6 +333,7 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -327,6 +348,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -341,6 +363,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -355,6 +378,7 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -369,6 +393,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="11" hidden="1">'4.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -383,6 +408,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="11" hidden="1">'4.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -405,7 +431,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="534">
   <si>
     <t>Release Date</t>
   </si>
@@ -2030,6 +2056,63 @@
   <si>
     <t>????</t>
   </si>
+  <si>
+    <t>S-2026-06-26</t>
+  </si>
+  <si>
+    <t>RPRO-260608-1016</t>
+  </si>
+  <si>
+    <t>S-2026-06-27</t>
+  </si>
+  <si>
+    <t>RPRO-260608-1017</t>
+  </si>
+  <si>
+    <t>PVN-002413</t>
+  </si>
+  <si>
+    <t>OrthoLite Regular-Nike AIR BLUE/16-4134TPX Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4.2mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-28</t>
+  </si>
+  <si>
+    <t>RPRO-260608-1018</t>
+  </si>
+  <si>
+    <t>S-2026-06-29</t>
+  </si>
+  <si>
+    <t>RPRO-260608-1019</t>
+  </si>
+  <si>
+    <t>BDB-000305</t>
+  </si>
+  <si>
+    <t>PVN-004000</t>
+  </si>
+  <si>
+    <t>OrthoLite X-35-Nike YELLOW/13-0858TPX Flat Sheet 0.145D 25+/-4 Asker C 1.1M 2M 5.5mm</t>
+  </si>
+  <si>
+    <t>S-2026-06-30</t>
+  </si>
+  <si>
+    <t>RPRO-260608-1020</t>
+  </si>
+  <si>
+    <t>BDB-000349</t>
+  </si>
+  <si>
+    <t>PVN-004352</t>
+  </si>
+  <si>
+    <t>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 15+/-4 Asker C 1.1M 2M 11mm</t>
+  </si>
+  <si>
+    <t>BLACKYAK</t>
+  </si>
 </sst>
 </file>
 
@@ -2646,7 +2729,77 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="106">
+  <dxfs count="113">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3878,16 +4031,18 @@
       <sheetName val="29.5 - L2"/>
       <sheetName val="1.6"/>
       <sheetName val="2.6"/>
+      <sheetName val="5.6"/>
       <sheetName val="3.6"/>
       <sheetName val="4.6"/>
-      <sheetName val="5.6"/>
       <sheetName val="6.6"/>
-      <sheetName val="form 2 (21)"/>
+      <sheetName val="8.6"/>
+      <sheetName val="form 2 (22)"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
+      <sheetName val="form 2 (21)"/>
       <sheetName val="form 2 (20)"/>
       <sheetName val="form 2 (18)"/>
       <sheetName val="form 2 (19)"/>
@@ -4113,16 +4268,16 @@
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>24969</v>
+            <v>25179</v>
           </cell>
           <cell r="I2">
-            <v>24969</v>
+            <v>25179</v>
           </cell>
           <cell r="J2">
-            <v>23583</v>
+            <v>24163</v>
           </cell>
           <cell r="K2">
-            <v>1386</v>
+            <v>1016</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
@@ -4144,7 +4299,7 @@
           </cell>
           <cell r="V2"/>
           <cell r="W2">
-            <v>1272</v>
+            <v>1283</v>
           </cell>
         </row>
         <row r="3">
@@ -35629,10 +35784,10 @@
             <v>100</v>
           </cell>
           <cell r="J458">
+            <v>100</v>
+          </cell>
+          <cell r="K458">
             <v>0</v>
-          </cell>
-          <cell r="K458">
-            <v>100</v>
           </cell>
           <cell r="L458" t="str">
             <v>ASICS</v>
@@ -35747,7 +35902,9 @@
           <cell r="B460" t="str">
             <v>ƯU TIÊN GIAO 06-JUN KHI CÓ LIỆU</v>
           </cell>
-          <cell r="C460"/>
+          <cell r="C460" t="str">
+            <v>RPRO-260605-0687</v>
+          </cell>
           <cell r="D460" t="str">
             <v>PUR2605250002S</v>
           </cell>
@@ -36503,7 +36660,9 @@
           <cell r="A471" t="str">
             <v>S-2026-05-95</v>
           </cell>
-          <cell r="B471"/>
+          <cell r="B471" t="str">
+            <v>Xịn dời ETD</v>
+          </cell>
           <cell r="C471" t="str">
             <v>RPRO-260529-0341</v>
           </cell>
@@ -36526,10 +36685,10 @@
             <v>30</v>
           </cell>
           <cell r="J471">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="K471">
-            <v>30</v>
+            <v>-70</v>
           </cell>
           <cell r="L471" t="str">
             <v>FOOTJOY</v>
@@ -36547,16 +36706,16 @@
             <v>46171</v>
           </cell>
           <cell r="Q471">
+            <v>46181</v>
+          </cell>
+          <cell r="R471">
             <v>46178</v>
-          </cell>
-          <cell r="R471">
-            <v>46175</v>
           </cell>
           <cell r="S471">
             <v>6</v>
           </cell>
           <cell r="T471">
-            <v>7</v>
+            <v>10</v>
           </cell>
           <cell r="U471">
             <v>9.5</v>
@@ -36711,7 +36870,7 @@
             <v>S-2026-05-98</v>
           </cell>
           <cell r="B474" t="str">
-            <v xml:space="preserve">Xịn dời ETD </v>
+            <v>Xịn dời ETD</v>
           </cell>
           <cell r="C474" t="str">
             <v>RPRO-260529-0344</v>
@@ -36756,16 +36915,16 @@
             <v>46171</v>
           </cell>
           <cell r="Q474">
-            <v>46178</v>
+            <v>46182</v>
           </cell>
           <cell r="R474">
-            <v>46175</v>
+            <v>46179</v>
           </cell>
           <cell r="S474">
             <v>6</v>
           </cell>
           <cell r="T474">
-            <v>7</v>
+            <v>11</v>
           </cell>
           <cell r="U474">
             <v>9.8000000000000007</v>
@@ -36781,7 +36940,9 @@
           <cell r="A475" t="str">
             <v>S-2026-05-99</v>
           </cell>
-          <cell r="B475"/>
+          <cell r="B475" t="str">
+            <v>Xịn dời ETD</v>
+          </cell>
           <cell r="C475" t="str">
             <v>RPRO-260529-0345</v>
           </cell>
@@ -36804,10 +36965,10 @@
             <v>30</v>
           </cell>
           <cell r="J475">
+            <v>30</v>
+          </cell>
+          <cell r="K475">
             <v>0</v>
-          </cell>
-          <cell r="K475">
-            <v>30</v>
           </cell>
           <cell r="L475" t="str">
             <v>FOOTJOY</v>
@@ -36942,10 +37103,10 @@
             <v>100</v>
           </cell>
           <cell r="J477">
+            <v>100</v>
+          </cell>
+          <cell r="K477">
             <v>0</v>
-          </cell>
-          <cell r="K477">
-            <v>100</v>
           </cell>
           <cell r="L477" t="str">
             <v>SALOMON</v>
@@ -37011,10 +37172,10 @@
             <v>30</v>
           </cell>
           <cell r="J478">
+            <v>30</v>
+          </cell>
+          <cell r="K478">
             <v>0</v>
-          </cell>
-          <cell r="K478">
-            <v>30</v>
           </cell>
           <cell r="L478" t="str">
             <v>SALOMON</v>
@@ -37080,10 +37241,10 @@
             <v>50</v>
           </cell>
           <cell r="J479">
+            <v>50</v>
+          </cell>
+          <cell r="K479">
             <v>0</v>
-          </cell>
-          <cell r="K479">
-            <v>50</v>
           </cell>
           <cell r="L479" t="str">
             <v>ASICS</v>
@@ -37149,10 +37310,10 @@
             <v>30</v>
           </cell>
           <cell r="J480">
+            <v>30</v>
+          </cell>
+          <cell r="K480">
             <v>0</v>
-          </cell>
-          <cell r="K480">
-            <v>30</v>
           </cell>
           <cell r="L480" t="str">
             <v>UNDER ARMOUR</v>
@@ -37218,10 +37379,10 @@
             <v>50</v>
           </cell>
           <cell r="J481">
+            <v>50</v>
+          </cell>
+          <cell r="K481">
             <v>0</v>
-          </cell>
-          <cell r="K481">
-            <v>50</v>
           </cell>
           <cell r="L481" t="str">
             <v>CONVERSE</v>
@@ -37287,10 +37448,10 @@
             <v>10</v>
           </cell>
           <cell r="J482">
+            <v>10</v>
+          </cell>
+          <cell r="K482">
             <v>0</v>
-          </cell>
-          <cell r="K482">
-            <v>10</v>
           </cell>
           <cell r="L482" t="str">
             <v>ASICS</v>
@@ -37357,10 +37518,10 @@
             <v>30</v>
           </cell>
           <cell r="J483">
+            <v>30</v>
+          </cell>
+          <cell r="K483">
             <v>0</v>
-          </cell>
-          <cell r="K483">
-            <v>30</v>
           </cell>
           <cell r="L483" t="str">
             <v>FOOTJOY</v>
@@ -38120,10 +38281,10 @@
             <v>50</v>
           </cell>
           <cell r="J494">
+            <v>50</v>
+          </cell>
+          <cell r="K494">
             <v>0</v>
-          </cell>
-          <cell r="K494">
-            <v>50</v>
           </cell>
           <cell r="L494" t="str">
             <v>ADIDAS</v>
@@ -39311,9 +39472,7 @@
           <cell r="A512" t="str">
             <v>S-2026-06-25</v>
           </cell>
-          <cell r="B512" t="str">
-            <v>Chưa rl</v>
-          </cell>
+          <cell r="B512"/>
           <cell r="C512" t="str">
             <v>RPRO-260606-0217</v>
           </cell>
@@ -39379,159 +39538,349 @@
           </cell>
         </row>
         <row r="513">
-          <cell r="A513"/>
+          <cell r="A513" t="str">
+            <v>S-2026-06-26</v>
+          </cell>
           <cell r="B513"/>
-          <cell r="C513"/>
-          <cell r="D513"/>
+          <cell r="C513" t="str">
+            <v>RPRO-260608-1016</v>
+          </cell>
+          <cell r="D513" t="str">
+            <v>PUR2600600800001S</v>
+          </cell>
           <cell r="E513" t="str">
-            <v/>
-          </cell>
-          <cell r="F513"/>
-          <cell r="G513"/>
-          <cell r="H513"/>
-          <cell r="I513"/>
+            <v>BDB-000125</v>
+          </cell>
+          <cell r="F513" t="str">
+            <v>PVN-001579</v>
+          </cell>
+          <cell r="G513" t="str">
+            <v>OrthoLite Regular-Nike AIR BLUE/16-4134TPX Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H513">
+            <v>40</v>
+          </cell>
+          <cell r="I513">
+            <v>40</v>
+          </cell>
           <cell r="J513">
             <v>0</v>
           </cell>
           <cell r="K513">
-            <v>0</v>
-          </cell>
-          <cell r="L513"/>
-          <cell r="M513"/>
-          <cell r="N513"/>
-          <cell r="O513"/>
-          <cell r="P513"/>
-          <cell r="Q513"/>
-          <cell r="R513"/>
-          <cell r="S513"/>
-          <cell r="T513"/>
-          <cell r="U513"/>
-          <cell r="V513"/>
-          <cell r="W513"/>
+            <v>40</v>
+          </cell>
+          <cell r="L513" t="str">
+            <v>NIKE</v>
+          </cell>
+          <cell r="M513" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N513" t="str">
+            <v>DIE CUT</v>
+          </cell>
+          <cell r="O513" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P513">
+            <v>46181</v>
+          </cell>
+          <cell r="Q513">
+            <v>46188</v>
+          </cell>
+          <cell r="R513">
+            <v>46185</v>
+          </cell>
+          <cell r="S513">
+            <v>6</v>
+          </cell>
+          <cell r="T513">
+            <v>7</v>
+          </cell>
+          <cell r="U513">
+            <v>4</v>
+          </cell>
+          <cell r="V513">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W513">
+            <v>2</v>
+          </cell>
         </row>
         <row r="514">
-          <cell r="A514"/>
+          <cell r="A514" t="str">
+            <v>S-2026-06-27</v>
+          </cell>
           <cell r="B514"/>
-          <cell r="C514"/>
-          <cell r="D514"/>
+          <cell r="C514" t="str">
+            <v>RPRO-260608-1017</v>
+          </cell>
+          <cell r="D514" t="str">
+            <v>PUR2600600800001S</v>
+          </cell>
           <cell r="E514" t="str">
-            <v/>
-          </cell>
-          <cell r="F514"/>
-          <cell r="G514"/>
-          <cell r="H514"/>
-          <cell r="I514"/>
+            <v>BDB-000125</v>
+          </cell>
+          <cell r="F514" t="str">
+            <v>PVN-002413</v>
+          </cell>
+          <cell r="G514" t="str">
+            <v>OrthoLite Regular-Nike AIR BLUE/16-4134TPX Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4.2mm</v>
+          </cell>
+          <cell r="H514">
+            <v>70</v>
+          </cell>
+          <cell r="I514">
+            <v>70</v>
+          </cell>
           <cell r="J514">
             <v>0</v>
           </cell>
           <cell r="K514">
-            <v>0</v>
-          </cell>
-          <cell r="L514"/>
-          <cell r="M514"/>
-          <cell r="N514"/>
-          <cell r="O514"/>
-          <cell r="P514"/>
-          <cell r="Q514"/>
-          <cell r="R514"/>
-          <cell r="S514"/>
-          <cell r="T514"/>
-          <cell r="U514"/>
-          <cell r="V514"/>
-          <cell r="W514"/>
+            <v>70</v>
+          </cell>
+          <cell r="L514" t="str">
+            <v>NIKE</v>
+          </cell>
+          <cell r="M514" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N514" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O514" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P514">
+            <v>46181</v>
+          </cell>
+          <cell r="Q514">
+            <v>46188</v>
+          </cell>
+          <cell r="R514">
+            <v>46185</v>
+          </cell>
+          <cell r="S514">
+            <v>6</v>
+          </cell>
+          <cell r="T514">
+            <v>7</v>
+          </cell>
+          <cell r="U514">
+            <v>4.2</v>
+          </cell>
+          <cell r="V514">
+            <v>3.0300000000000001E-2</v>
+          </cell>
+          <cell r="W514">
+            <v>3</v>
+          </cell>
         </row>
         <row r="515">
-          <cell r="A515"/>
+          <cell r="A515" t="str">
+            <v>S-2026-06-28</v>
+          </cell>
           <cell r="B515"/>
-          <cell r="C515"/>
-          <cell r="D515"/>
+          <cell r="C515" t="str">
+            <v>RPRO-260608-1018</v>
+          </cell>
+          <cell r="D515" t="str">
+            <v>PUR2600600800001S</v>
+          </cell>
           <cell r="E515" t="str">
-            <v/>
-          </cell>
-          <cell r="F515"/>
-          <cell r="G515"/>
-          <cell r="H515"/>
-          <cell r="I515"/>
+            <v>BDB-000162</v>
+          </cell>
+          <cell r="F515" t="str">
+            <v>PVN-001566</v>
+          </cell>
+          <cell r="G515" t="str">
+            <v>OrthoLite Ultra-Nike SEEDPEARL/12-0703TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H515">
+            <v>50</v>
+          </cell>
+          <cell r="I515">
+            <v>50</v>
+          </cell>
           <cell r="J515">
             <v>0</v>
           </cell>
           <cell r="K515">
-            <v>0</v>
-          </cell>
-          <cell r="L515"/>
-          <cell r="M515"/>
-          <cell r="N515"/>
-          <cell r="O515"/>
-          <cell r="P515"/>
-          <cell r="Q515"/>
-          <cell r="R515"/>
-          <cell r="S515"/>
-          <cell r="T515"/>
-          <cell r="U515"/>
-          <cell r="V515"/>
-          <cell r="W515"/>
+            <v>50</v>
+          </cell>
+          <cell r="L515" t="str">
+            <v>NIKE</v>
+          </cell>
+          <cell r="M515" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N515" t="str">
+            <v>DIE CUT</v>
+          </cell>
+          <cell r="O515" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P515">
+            <v>46181</v>
+          </cell>
+          <cell r="Q515">
+            <v>46188</v>
+          </cell>
+          <cell r="R515">
+            <v>46185</v>
+          </cell>
+          <cell r="S515">
+            <v>6</v>
+          </cell>
+          <cell r="T515">
+            <v>7</v>
+          </cell>
+          <cell r="U515">
+            <v>4</v>
+          </cell>
+          <cell r="V515">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W515">
+            <v>2</v>
+          </cell>
         </row>
         <row r="516">
-          <cell r="A516"/>
+          <cell r="A516" t="str">
+            <v>S-2026-06-29</v>
+          </cell>
           <cell r="B516"/>
-          <cell r="C516"/>
-          <cell r="D516"/>
+          <cell r="C516" t="str">
+            <v>RPRO-260608-1019</v>
+          </cell>
+          <cell r="D516" t="str">
+            <v>PUR2600600800001S</v>
+          </cell>
           <cell r="E516" t="str">
-            <v/>
-          </cell>
-          <cell r="F516"/>
-          <cell r="G516"/>
-          <cell r="H516"/>
-          <cell r="I516"/>
+            <v>BDB-000305</v>
+          </cell>
+          <cell r="F516" t="str">
+            <v>PVN-004000</v>
+          </cell>
+          <cell r="G516" t="str">
+            <v>OrthoLite X-35-Nike YELLOW/13-0858TPX Flat Sheet 0.145D 25+/-4 Asker C 1.1M 2M 5.5mm</v>
+          </cell>
+          <cell r="H516">
+            <v>30</v>
+          </cell>
+          <cell r="I516">
+            <v>30</v>
+          </cell>
           <cell r="J516">
             <v>0</v>
           </cell>
           <cell r="K516">
-            <v>0</v>
-          </cell>
-          <cell r="L516"/>
-          <cell r="M516"/>
-          <cell r="N516"/>
-          <cell r="O516"/>
-          <cell r="P516"/>
-          <cell r="Q516"/>
-          <cell r="R516"/>
-          <cell r="S516"/>
-          <cell r="T516"/>
-          <cell r="U516"/>
-          <cell r="V516"/>
-          <cell r="W516"/>
+            <v>30</v>
+          </cell>
+          <cell r="L516" t="str">
+            <v>NIKE</v>
+          </cell>
+          <cell r="M516" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N516" t="str">
+            <v>DIE CUT</v>
+          </cell>
+          <cell r="O516" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P516">
+            <v>46181</v>
+          </cell>
+          <cell r="Q516">
+            <v>46188</v>
+          </cell>
+          <cell r="R516">
+            <v>46185</v>
+          </cell>
+          <cell r="S516">
+            <v>6</v>
+          </cell>
+          <cell r="T516">
+            <v>7</v>
+          </cell>
+          <cell r="U516">
+            <v>5.5</v>
+          </cell>
+          <cell r="V516">
+            <v>0.04</v>
+          </cell>
+          <cell r="W516">
+            <v>2</v>
+          </cell>
         </row>
         <row r="517">
-          <cell r="A517"/>
+          <cell r="A517" t="str">
+            <v>S-2026-06-30</v>
+          </cell>
           <cell r="B517"/>
-          <cell r="C517"/>
-          <cell r="D517"/>
+          <cell r="C517" t="str">
+            <v>RPRO-260608-1020</v>
+          </cell>
+          <cell r="D517" t="str">
+            <v>PUR2606080002S</v>
+          </cell>
           <cell r="E517" t="str">
-            <v/>
-          </cell>
-          <cell r="F517"/>
-          <cell r="G517"/>
-          <cell r="H517"/>
-          <cell r="I517"/>
+            <v>BDB-000349</v>
+          </cell>
+          <cell r="F517" t="str">
+            <v>PVN-004352</v>
+          </cell>
+          <cell r="G517" t="str">
+            <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 15+/-4 Asker C 1.1M 2M 11mm</v>
+          </cell>
+          <cell r="H517">
+            <v>20</v>
+          </cell>
+          <cell r="I517">
+            <v>20</v>
+          </cell>
           <cell r="J517">
             <v>0</v>
           </cell>
           <cell r="K517">
-            <v>0</v>
-          </cell>
-          <cell r="L517"/>
-          <cell r="M517"/>
-          <cell r="N517"/>
-          <cell r="O517"/>
-          <cell r="P517"/>
-          <cell r="Q517"/>
-          <cell r="R517"/>
-          <cell r="S517"/>
-          <cell r="T517"/>
-          <cell r="U517"/>
-          <cell r="V517"/>
-          <cell r="W517"/>
+            <v>20</v>
+          </cell>
+          <cell r="L517" t="str">
+            <v>BLACKYAK</v>
+          </cell>
+          <cell r="M517" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N517" t="str">
+            <v>Molded</v>
+          </cell>
+          <cell r="O517" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P517">
+            <v>46181</v>
+          </cell>
+          <cell r="Q517">
+            <v>46188</v>
+          </cell>
+          <cell r="R517">
+            <v>46185</v>
+          </cell>
+          <cell r="S517">
+            <v>6</v>
+          </cell>
+          <cell r="T517">
+            <v>7</v>
+          </cell>
+          <cell r="U517">
+            <v>11</v>
+          </cell>
+          <cell r="V517">
+            <v>8.3330000000000001E-2</v>
+          </cell>
+          <cell r="W517">
+            <v>2</v>
+          </cell>
         </row>
         <row r="518">
           <cell r="A518"/>
@@ -39728,13 +40077,7 @@
       <sheetData sheetId="104"/>
       <sheetData sheetId="105"/>
       <sheetData sheetId="106"/>
-      <sheetData sheetId="107">
-        <row r="1">
-          <cell r="F1" t="str">
-            <v>No_Item</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="107"/>
       <sheetData sheetId="108"/>
       <sheetData sheetId="109"/>
       <sheetData sheetId="110"/>
@@ -39917,6 +40260,8 @@
       <sheetData sheetId="287" refreshError="1"/>
       <sheetData sheetId="288" refreshError="1"/>
       <sheetData sheetId="289" refreshError="1"/>
+      <sheetData sheetId="290" refreshError="1"/>
+      <sheetData sheetId="291" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -41543,23 +41888,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="105" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="104" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="103" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="102" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="99" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -41605,7 +41950,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -42986,23 +43331,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -43048,7 +43393,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -44429,23 +44774,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A22">
-    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:A1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -44490,7 +44835,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -45774,23 +46119,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -45835,7 +46180,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -47298,26 +47643,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D19">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -47361,7 +47706,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701553935185</v>
+        <v>46182.334269212966</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -48594,20 +48939,20 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A17">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -48617,6 +48962,1405 @@
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2973554-5D10-4DAD-82DE-3915D53AF901}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:N664"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="162.54296875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46182.334269212966</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>11</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="22">
+        <v>40</v>
+      </c>
+      <c r="G3" s="23">
+        <v>2</v>
+      </c>
+      <c r="H3" s="24">
+        <v>2</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="L3" s="26">
+        <v>5</v>
+      </c>
+      <c r="M3" s="27"/>
+      <c r="N3" s="28">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>518</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>520</v>
+      </c>
+      <c r="F4" s="22">
+        <v>70</v>
+      </c>
+      <c r="G4" s="23">
+        <v>3</v>
+      </c>
+      <c r="H4" s="24">
+        <v>3</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="28">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="62"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="76"/>
+    </row>
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>522</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="F6" s="22">
+        <v>50</v>
+      </c>
+      <c r="G6" s="23">
+        <v>2</v>
+      </c>
+      <c r="H6" s="24">
+        <v>2</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="L6" s="26">
+        <v>2</v>
+      </c>
+      <c r="M6" s="40"/>
+      <c r="N6" s="28">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="76"/>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="F8" s="22">
+        <v>30</v>
+      </c>
+      <c r="G8" s="23">
+        <v>2</v>
+      </c>
+      <c r="H8" s="24">
+        <v>2</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="L8" s="26">
+        <v>2</v>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="28">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="76"/>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="F10" s="22">
+        <v>20</v>
+      </c>
+      <c r="G10" s="23">
+        <v>2</v>
+      </c>
+      <c r="H10" s="24">
+        <v>2</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="26">
+        <v>2</v>
+      </c>
+      <c r="M10" s="27"/>
+      <c r="N10" s="28">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C11" s="19" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D11" s="20" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="21" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" s="22" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G11" s="23" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H11" s="24" t="e">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K11" s="25" t="e">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L11" s="26"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A11,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C12" s="19" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D12" s="20" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" s="21" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F12" s="22" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G12" s="23" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H12" s="24" t="e">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K12" s="25" t="e">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L12" s="26"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A12,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C13" s="19" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="20" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="21" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" s="22" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="23" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H13" s="24" t="e">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K13" s="25" t="e">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L13" s="26"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A13,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C14" s="19" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D14" s="20" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="21" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="22" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="23" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H14" s="24" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A14,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C15" s="19" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D15" s="20" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="21" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" s="22" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="23" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H15" s="24" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L15" s="26"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C16" s="19" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="20" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="21" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="22" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="23" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H16" s="24" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L16" s="26"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A16,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C17" s="19" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="20" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="21" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="22" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="23" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H17" s="24" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="19" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="20" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="21" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="22" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="23" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H18" s="24" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A18,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="19" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="20" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="21" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F19" s="22" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="23" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H19" s="24" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="19" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="20" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="21" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="22" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="23" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="24" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="51"/>
+    </row>
+    <row r="22" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L22" s="56"/>
+    </row>
+    <row r="23" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L23" s="56"/>
+    </row>
+    <row r="24" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="55"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="58"/>
+    </row>
+    <row r="26" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="56"/>
+    </row>
+    <row r="28" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="58"/>
+    </row>
+    <row r="29" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="58"/>
+    </row>
+    <row r="30" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="664" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A664" s="2"/>
+      <c r="B664" s="52"/>
+      <c r="C664" s="2"/>
+      <c r="D664" s="2"/>
+      <c r="E664" s="60"/>
+      <c r="H664" s="55"/>
+      <c r="I664" s="53"/>
+      <c r="J664" s="53"/>
+      <c r="K664" s="53"/>
+      <c r="L664" s="61"/>
+      <c r="M664" s="57"/>
+      <c r="N664" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E20" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N21" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="RPRO-260608-1016"/>
+        <filter val="RPRO-260608-1017"/>
+        <filter val="RPRO-260608-1018"/>
+        <filter val="RPRO-260608-1019"/>
+        <filter val="RPRO-260608-1020"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A20">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="21" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -48652,7 +50396,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -50001,23 +51745,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="98" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="97" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="96" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="95" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="93" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -50062,7 +51806,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -51469,23 +53213,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="90" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="89" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="86" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -51530,7 +53274,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -52903,23 +54647,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="83" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="79" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="78" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -52963,7 +54707,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -54178,39 +55922,39 @@
     <mergeCell ref="D7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="77" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A6 A14:A18">
-    <cfRule type="duplicateValues" dxfId="76" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="75" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A13">
-    <cfRule type="duplicateValues" dxfId="74" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A1048576">
-    <cfRule type="duplicateValues" dxfId="73" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C6 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="72" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C13">
-    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:L8">
-    <cfRule type="duplicateValues" dxfId="68" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="67" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="65" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="9"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -54255,7 +55999,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -55580,26 +57324,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="64" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A15">
-    <cfRule type="duplicateValues" dxfId="63" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A21">
-    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -55645,7 +57389,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -57000,23 +58744,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -57061,7 +58805,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -58449,24 +60193,24 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="48" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="42" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -58512,7 +60256,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46179.701554050924</v>
+        <v>46182.334269444444</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -59857,23 +61601,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="41" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="40" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="117" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75102B01-28E5-4879-8A68-12ED4C094023}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="14" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="10" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -4229,84 +4229,49 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
-          <cell r="A1"/>
-          <cell r="B1"/>
           <cell r="C1" t="str">
             <v>TẠM THỜI NGƯNG NHẬN LAZY</v>
           </cell>
-          <cell r="D1"/>
-          <cell r="E1"/>
-          <cell r="F1"/>
           <cell r="G1" t="str">
             <v>ASICS 12MM DÙNG BOM 132 (roundup(12/132),5)</v>
           </cell>
-          <cell r="H1"/>
-          <cell r="I1"/>
-          <cell r="J1"/>
-          <cell r="K1"/>
-          <cell r="L1"/>
-          <cell r="M1"/>
-          <cell r="N1"/>
-          <cell r="O1"/>
-          <cell r="P1"/>
-          <cell r="Q1"/>
-          <cell r="R1"/>
-          <cell r="S1"/>
-          <cell r="T1"/>
-          <cell r="U1"/>
-          <cell r="V1"/>
-          <cell r="W1"/>
         </row>
         <row r="2">
-          <cell r="A2"/>
-          <cell r="B2"/>
-          <cell r="C2"/>
-          <cell r="D2"/>
-          <cell r="E2"/>
-          <cell r="F2"/>
           <cell r="G2" t="str">
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>25179</v>
+            <v>267</v>
           </cell>
           <cell r="I2">
-            <v>25179</v>
+            <v>267</v>
           </cell>
           <cell r="J2">
-            <v>24163</v>
+            <v>0</v>
           </cell>
           <cell r="K2">
-            <v>1016</v>
+            <v>267</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
           </cell>
-          <cell r="M2"/>
-          <cell r="N2"/>
-          <cell r="O2"/>
-          <cell r="P2"/>
           <cell r="Q2" t="str">
             <v>ETD hệ thống+1ngay</v>
           </cell>
           <cell r="R2" t="e">
             <v>#VALUE!</v>
           </cell>
-          <cell r="S2"/>
-          <cell r="T2"/>
           <cell r="U2">
             <v>12</v>
           </cell>
-          <cell r="V2"/>
           <cell r="W2">
-            <v>1283</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>NO.Order</v>
           </cell>
-          <cell r="B3"/>
           <cell r="C3" t="str">
             <v>Firm plan
 (PU PVN)</v>
@@ -4391,7 +4356,6 @@
           <cell r="A4" t="str">
             <v>S-2026-01-01</v>
           </cell>
-          <cell r="B4"/>
           <cell r="C4" t="str">
             <v>RPRO-260105-0668</v>
           </cell>
@@ -4744,7 +4708,6 @@
           <cell r="A9" t="str">
             <v>S-2026-01-06</v>
           </cell>
-          <cell r="B9"/>
           <cell r="C9" t="str">
             <v>RPRO-260105-0673</v>
           </cell>
@@ -4813,7 +4776,6 @@
           <cell r="A10" t="str">
             <v>S-2026-01-07</v>
           </cell>
-          <cell r="B10"/>
           <cell r="C10" t="str">
             <v>RPRO-260105-0674</v>
           </cell>
@@ -4882,7 +4844,6 @@
           <cell r="A11" t="str">
             <v>S-2026-01-08</v>
           </cell>
-          <cell r="B11"/>
           <cell r="C11" t="str">
             <v>RPRO-260105-0675</v>
           </cell>
@@ -5093,7 +5054,6 @@
           <cell r="A14" t="str">
             <v>L-2026-01-11</v>
           </cell>
-          <cell r="B14"/>
           <cell r="C14" t="str">
             <v>RPRO-260105-0678</v>
           </cell>
@@ -5127,7 +5087,6 @@
           <cell r="M14" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N14"/>
           <cell r="O14" t="str">
             <v>Lab test</v>
           </cell>
@@ -5160,7 +5119,6 @@
           <cell r="A15" t="str">
             <v>L-2026-01-12</v>
           </cell>
-          <cell r="B15"/>
           <cell r="C15" t="str">
             <v>RPRO-260105-0679</v>
           </cell>
@@ -5194,7 +5152,6 @@
           <cell r="M15" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N15"/>
           <cell r="O15" t="str">
             <v>Lab test</v>
           </cell>
@@ -5227,7 +5184,6 @@
           <cell r="A16" t="str">
             <v>L-2026-01-13</v>
           </cell>
-          <cell r="B16"/>
           <cell r="C16" t="str">
             <v>RPRO-260105-0680</v>
           </cell>
@@ -5261,7 +5217,6 @@
           <cell r="M16" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N16"/>
           <cell r="O16" t="str">
             <v>Lab test</v>
           </cell>
@@ -5294,7 +5249,6 @@
           <cell r="A17" t="str">
             <v>L-2026-01-14</v>
           </cell>
-          <cell r="B17"/>
           <cell r="C17" t="str">
             <v>RPRO-260105-0681</v>
           </cell>
@@ -5328,7 +5282,6 @@
           <cell r="M17" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N17"/>
           <cell r="O17" t="str">
             <v>Lab test</v>
           </cell>
@@ -5397,7 +5350,6 @@
           <cell r="M18" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N18"/>
           <cell r="O18" t="str">
             <v>Lab test</v>
           </cell>
@@ -5466,7 +5418,6 @@
           <cell r="M19" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N19"/>
           <cell r="O19" t="str">
             <v>Lab test</v>
           </cell>
@@ -5854,7 +5805,6 @@
           <cell r="A25" t="str">
             <v>L-2026-01-22</v>
           </cell>
-          <cell r="B25"/>
           <cell r="C25" t="str">
             <v>RPRO-260109-0095</v>
           </cell>
@@ -5888,7 +5838,6 @@
           <cell r="M25" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N25"/>
           <cell r="O25" t="str">
             <v>Lab test</v>
           </cell>
@@ -5921,7 +5870,6 @@
           <cell r="A26" t="str">
             <v>S-2026-01-23</v>
           </cell>
-          <cell r="B26"/>
           <cell r="C26" t="str">
             <v>RPRO-260113-0624</v>
           </cell>
@@ -5990,7 +5938,6 @@
           <cell r="A27" t="str">
             <v>S-2026-01-24</v>
           </cell>
-          <cell r="B27"/>
           <cell r="C27" t="str">
             <v>RPRO-260113-0625</v>
           </cell>
@@ -6059,7 +6006,6 @@
           <cell r="A28" t="str">
             <v>S-2026-01-25</v>
           </cell>
-          <cell r="B28"/>
           <cell r="C28" t="str">
             <v>RPRO-260113-0626</v>
           </cell>
@@ -6128,7 +6074,6 @@
           <cell r="A29" t="str">
             <v>S-2026-01-26</v>
           </cell>
-          <cell r="B29"/>
           <cell r="C29" t="str">
             <v>RPRO-260113-0627</v>
           </cell>
@@ -6197,7 +6142,6 @@
           <cell r="A30" t="str">
             <v>S-2026-01-27</v>
           </cell>
-          <cell r="B30"/>
           <cell r="C30" t="str">
             <v>RPRO-260113-0628</v>
           </cell>
@@ -6266,7 +6210,6 @@
           <cell r="A31" t="str">
             <v>S-2026-01-28</v>
           </cell>
-          <cell r="B31"/>
           <cell r="C31" t="str">
             <v>RPRO-260113-0629</v>
           </cell>
@@ -6335,7 +6278,6 @@
           <cell r="A32" t="str">
             <v>S-2026-01-29</v>
           </cell>
-          <cell r="B32"/>
           <cell r="C32" t="str">
             <v>RPRO-260113-0630</v>
           </cell>
@@ -6404,7 +6346,6 @@
           <cell r="A33" t="str">
             <v>S-2026-01-30</v>
           </cell>
-          <cell r="B33"/>
           <cell r="C33" t="str">
             <v>RPRO-260115-0298</v>
           </cell>
@@ -6473,7 +6414,6 @@
           <cell r="A34" t="str">
             <v>S-2026-01-31</v>
           </cell>
-          <cell r="B34"/>
           <cell r="C34" t="str">
             <v>RPRO-260115-0299</v>
           </cell>
@@ -6542,7 +6482,6 @@
           <cell r="A35" t="str">
             <v>S-2026-01-32</v>
           </cell>
-          <cell r="B35"/>
           <cell r="C35" t="str">
             <v>RPRO-260115-0300</v>
           </cell>
@@ -6611,7 +6550,6 @@
           <cell r="A36" t="str">
             <v>S-2026-01-33</v>
           </cell>
-          <cell r="B36"/>
           <cell r="C36" t="str">
             <v>RPRO-260115-0301</v>
           </cell>
@@ -6680,7 +6618,6 @@
           <cell r="A37" t="str">
             <v>S-2026-01-34</v>
           </cell>
-          <cell r="B37"/>
           <cell r="C37" t="str">
             <v>RPRO-260115-0302</v>
           </cell>
@@ -6749,7 +6686,6 @@
           <cell r="A38" t="str">
             <v>S-2026-01-35</v>
           </cell>
-          <cell r="B38"/>
           <cell r="C38" t="str">
             <v>RPRO-260115-0303</v>
           </cell>
@@ -6818,7 +6754,6 @@
           <cell r="A39" t="str">
             <v>S-2026-01-36</v>
           </cell>
-          <cell r="B39"/>
           <cell r="C39" t="str">
             <v>RPRO-260115-0304</v>
           </cell>
@@ -6887,7 +6822,6 @@
           <cell r="A40" t="str">
             <v>S-2026-01-37</v>
           </cell>
-          <cell r="B40"/>
           <cell r="C40" t="str">
             <v>RPRO-260115-0305</v>
           </cell>
@@ -6956,7 +6890,6 @@
           <cell r="A41" t="str">
             <v>S-2026-01-38</v>
           </cell>
-          <cell r="B41"/>
           <cell r="C41" t="str">
             <v>RPRO-260115-0306</v>
           </cell>
@@ -7025,7 +6958,6 @@
           <cell r="A42" t="str">
             <v>S-2026-01-39</v>
           </cell>
-          <cell r="B42"/>
           <cell r="C42" t="str">
             <v>RPRO-260115-0307</v>
           </cell>
@@ -7094,7 +7026,6 @@
           <cell r="A43" t="str">
             <v>S-2026-01-40</v>
           </cell>
-          <cell r="B43"/>
           <cell r="C43" t="str">
             <v>RPRO-260115-0308</v>
           </cell>
@@ -7163,7 +7094,6 @@
           <cell r="A44" t="str">
             <v>S-2026-01-41</v>
           </cell>
-          <cell r="B44"/>
           <cell r="C44" t="str">
             <v>RPRO-260115-0309</v>
           </cell>
@@ -7232,7 +7162,6 @@
           <cell r="A45" t="str">
             <v>S-2026-01-42</v>
           </cell>
-          <cell r="B45"/>
           <cell r="C45" t="str">
             <v>RPRO-260109-0096</v>
           </cell>
@@ -7301,7 +7230,6 @@
           <cell r="A46" t="str">
             <v>S-2026-01-43</v>
           </cell>
-          <cell r="B46"/>
           <cell r="C46" t="str">
             <v>RPRO-260109-0097</v>
           </cell>
@@ -7370,7 +7298,6 @@
           <cell r="A47" t="str">
             <v>S-2026-01-44</v>
           </cell>
-          <cell r="B47"/>
           <cell r="C47" t="str">
             <v>RPRO-260109-0098</v>
           </cell>
@@ -7439,7 +7366,6 @@
           <cell r="A48" t="str">
             <v>S-2026-01-45</v>
           </cell>
-          <cell r="B48"/>
           <cell r="C48" t="str">
             <v>RPRO-260109-0099</v>
           </cell>
@@ -7508,7 +7434,6 @@
           <cell r="A49" t="str">
             <v>S-2026-01-46</v>
           </cell>
-          <cell r="B49"/>
           <cell r="C49" t="str">
             <v>RPRO-260120-0349</v>
           </cell>
@@ -7577,7 +7502,6 @@
           <cell r="A50" t="str">
             <v>S-2026-01-47</v>
           </cell>
-          <cell r="B50"/>
           <cell r="C50" t="str">
             <v>RPRO-260120-0350</v>
           </cell>
@@ -7646,7 +7570,6 @@
           <cell r="A51" t="str">
             <v>S-2026-01-48</v>
           </cell>
-          <cell r="B51"/>
           <cell r="C51" t="str">
             <v>RPRO-260120-0351</v>
           </cell>
@@ -7715,7 +7638,6 @@
           <cell r="A52" t="str">
             <v>S-2026-01-49</v>
           </cell>
-          <cell r="B52"/>
           <cell r="C52" t="str">
             <v>RPRO-260120-0352</v>
           </cell>
@@ -7784,7 +7706,6 @@
           <cell r="A53" t="str">
             <v>S-2026-01-50</v>
           </cell>
-          <cell r="B53"/>
           <cell r="C53" t="str">
             <v>RPRO-260120-0353</v>
           </cell>
@@ -7853,7 +7774,6 @@
           <cell r="A54" t="str">
             <v>S-2026-01-51</v>
           </cell>
-          <cell r="B54"/>
           <cell r="C54" t="str">
             <v>RPRO-260120-0354</v>
           </cell>
@@ -7922,7 +7842,6 @@
           <cell r="A55" t="str">
             <v>S-2026-01-52</v>
           </cell>
-          <cell r="B55"/>
           <cell r="C55" t="str">
             <v>RPRO-260113-0631</v>
           </cell>
@@ -7991,7 +7910,6 @@
           <cell r="A56" t="str">
             <v>S-2026-01-53</v>
           </cell>
-          <cell r="B56"/>
           <cell r="C56" t="str">
             <v>RPRO-260120-0355</v>
           </cell>
@@ -8060,7 +7978,6 @@
           <cell r="A57" t="str">
             <v>S-2026-01-54</v>
           </cell>
-          <cell r="B57"/>
           <cell r="C57" t="str">
             <v>RPRO-260120-0356</v>
           </cell>
@@ -8129,7 +8046,6 @@
           <cell r="A58" t="str">
             <v>S-2026-01-55</v>
           </cell>
-          <cell r="B58"/>
           <cell r="C58" t="str">
             <v>RPRO-260120-0357</v>
           </cell>
@@ -8198,7 +8114,6 @@
           <cell r="A59" t="str">
             <v>S-2026-01-56</v>
           </cell>
-          <cell r="B59"/>
           <cell r="C59" t="str">
             <v>RPRO-260120-0358</v>
           </cell>
@@ -8267,7 +8182,6 @@
           <cell r="A60" t="str">
             <v>S-2026-01-57</v>
           </cell>
-          <cell r="B60"/>
           <cell r="C60" t="str">
             <v>RPRO-260120-0359</v>
           </cell>
@@ -8336,7 +8250,6 @@
           <cell r="A61" t="str">
             <v>S-2026-01-58</v>
           </cell>
-          <cell r="B61"/>
           <cell r="C61" t="str">
             <v>RPRO-260120-0360</v>
           </cell>
@@ -8405,7 +8318,6 @@
           <cell r="A62" t="str">
             <v>S-2026-01-59</v>
           </cell>
-          <cell r="B62"/>
           <cell r="C62" t="str">
             <v>RPRO-260116-0276</v>
           </cell>
@@ -8474,7 +8386,6 @@
           <cell r="A63" t="str">
             <v>S-2026-01-60</v>
           </cell>
-          <cell r="B63"/>
           <cell r="C63" t="str">
             <v>RPRO-260115-0310</v>
           </cell>
@@ -8543,7 +8454,6 @@
           <cell r="A64" t="str">
             <v>S-2026-01-61</v>
           </cell>
-          <cell r="B64"/>
           <cell r="C64" t="str">
             <v>RPRO-260120-0361</v>
           </cell>
@@ -8683,7 +8593,6 @@
           <cell r="A66" t="str">
             <v>S-2026-01-63</v>
           </cell>
-          <cell r="B66"/>
           <cell r="C66" t="str">
             <v>RPRO-260122-1562</v>
           </cell>
@@ -8752,7 +8661,6 @@
           <cell r="A67" t="str">
             <v>S-2026-01-64</v>
           </cell>
-          <cell r="B67"/>
           <cell r="C67" t="str">
             <v>RPRO-260122-1563</v>
           </cell>
@@ -8821,7 +8729,6 @@
           <cell r="A68" t="str">
             <v>S-2026-01-65</v>
           </cell>
-          <cell r="B68"/>
           <cell r="C68" t="str">
             <v>RPRO-260122-1564</v>
           </cell>
@@ -8890,7 +8797,6 @@
           <cell r="A69" t="str">
             <v>S-2026-01-66</v>
           </cell>
-          <cell r="B69"/>
           <cell r="C69" t="str">
             <v>RPRO-260122-1565</v>
           </cell>
@@ -8959,7 +8865,6 @@
           <cell r="A70" t="str">
             <v>S-2026-01-67</v>
           </cell>
-          <cell r="B70"/>
           <cell r="C70" t="str">
             <v>RPRO-260122-1566</v>
           </cell>
@@ -9028,7 +8933,6 @@
           <cell r="A71" t="str">
             <v>S-2026-01-68</v>
           </cell>
-          <cell r="B71"/>
           <cell r="C71" t="str">
             <v>RPRO-260122-1567</v>
           </cell>
@@ -9097,7 +9001,6 @@
           <cell r="A72" t="str">
             <v>S-2026-01-69</v>
           </cell>
-          <cell r="B72"/>
           <cell r="C72" t="str">
             <v>RPRO-260122-1568</v>
           </cell>
@@ -9166,7 +9069,6 @@
           <cell r="A73" t="str">
             <v>S-2026-01-70</v>
           </cell>
-          <cell r="B73"/>
           <cell r="C73" t="str">
             <v>RPRO-260122-1569</v>
           </cell>
@@ -9235,7 +9137,6 @@
           <cell r="A74" t="str">
             <v>S-2026-01-71</v>
           </cell>
-          <cell r="B74"/>
           <cell r="C74" t="str">
             <v>RPRO-260122-1570</v>
           </cell>
@@ -9304,7 +9205,6 @@
           <cell r="A75" t="str">
             <v>S-2026-01-72</v>
           </cell>
-          <cell r="B75"/>
           <cell r="C75" t="str">
             <v>RPRO-260122-1571</v>
           </cell>
@@ -9586,7 +9486,6 @@
           <cell r="A79" t="str">
             <v>S-2026-01-76</v>
           </cell>
-          <cell r="B79"/>
           <cell r="C79" t="str">
             <v>RPRO-260122-1573</v>
           </cell>
@@ -9655,7 +9554,6 @@
           <cell r="A80" t="str">
             <v>S-2026-01-77</v>
           </cell>
-          <cell r="B80"/>
           <cell r="C80" t="str">
             <v>RPRO-260122-1574</v>
           </cell>
@@ -9724,7 +9622,6 @@
           <cell r="A81" t="str">
             <v>S-2026-01-78</v>
           </cell>
-          <cell r="B81"/>
           <cell r="C81" t="str">
             <v>RPRO-260122-1575</v>
           </cell>
@@ -9793,7 +9690,6 @@
           <cell r="A82" t="str">
             <v>S-2026-01-79</v>
           </cell>
-          <cell r="B82"/>
           <cell r="C82" t="str">
             <v>RPRO-260122-1576</v>
           </cell>
@@ -9862,7 +9758,6 @@
           <cell r="A83" t="str">
             <v>S-2026-01-80</v>
           </cell>
-          <cell r="B83"/>
           <cell r="C83" t="str">
             <v>RPRO-260122-1577</v>
           </cell>
@@ -9931,7 +9826,6 @@
           <cell r="A84" t="str">
             <v>S-2026-01-81</v>
           </cell>
-          <cell r="B84"/>
           <cell r="C84" t="str">
             <v>RPRO-260122-1578</v>
           </cell>
@@ -10000,7 +9894,6 @@
           <cell r="A85" t="str">
             <v>S-2026-01-82</v>
           </cell>
-          <cell r="B85"/>
           <cell r="C85" t="str">
             <v>RPRO-260122-1579</v>
           </cell>
@@ -10069,7 +9962,6 @@
           <cell r="A86" t="str">
             <v>S-2026-01-83</v>
           </cell>
-          <cell r="B86"/>
           <cell r="C86" t="str">
             <v>RPRO-260122-1580</v>
           </cell>
@@ -10141,7 +10033,6 @@
           <cell r="B87" t="str">
             <v>hủy</v>
           </cell>
-          <cell r="C87"/>
           <cell r="D87" t="str">
             <v>OV-0385</v>
           </cell>
@@ -10210,7 +10101,6 @@
           <cell r="B88" t="str">
             <v>hủy</v>
           </cell>
-          <cell r="C88"/>
           <cell r="D88" t="str">
             <v>OV-0385</v>
           </cell>
@@ -10279,7 +10169,6 @@
           <cell r="B89" t="str">
             <v>hủy</v>
           </cell>
-          <cell r="C89"/>
           <cell r="D89" t="str">
             <v>OV-0385</v>
           </cell>
@@ -10345,7 +10234,6 @@
           <cell r="A90" t="str">
             <v>S-2026-01-87</v>
           </cell>
-          <cell r="B90"/>
           <cell r="C90" t="str">
             <v>RPRO-260127-0875</v>
           </cell>
@@ -10414,7 +10302,6 @@
           <cell r="A91" t="str">
             <v>S-2026-01-88</v>
           </cell>
-          <cell r="B91"/>
           <cell r="C91" t="str">
             <v>RPRO-260127-0877</v>
           </cell>
@@ -10483,7 +10370,6 @@
           <cell r="A92" t="str">
             <v>S-2026-01-89</v>
           </cell>
-          <cell r="B92"/>
           <cell r="C92" t="str">
             <v>RPRO-260127-0879</v>
           </cell>
@@ -10552,7 +10438,6 @@
           <cell r="A93" t="str">
             <v>S-2026-01-90</v>
           </cell>
-          <cell r="B93"/>
           <cell r="C93" t="str">
             <v>RPRO-260128-1270</v>
           </cell>
@@ -10621,7 +10506,6 @@
           <cell r="A94" t="str">
             <v>S-2026-01-91</v>
           </cell>
-          <cell r="B94"/>
           <cell r="C94" t="str">
             <v>RPRO-260128-1271</v>
           </cell>
@@ -10690,7 +10574,6 @@
           <cell r="A95" t="str">
             <v>S-2026-01-92</v>
           </cell>
-          <cell r="B95"/>
           <cell r="C95" t="str">
             <v>RPRO-260128-1272</v>
           </cell>
@@ -10759,7 +10642,6 @@
           <cell r="A96" t="str">
             <v>S-2026-01-93</v>
           </cell>
-          <cell r="B96"/>
           <cell r="C96" t="str">
             <v>RPRO-260128-1273</v>
           </cell>
@@ -10828,7 +10710,6 @@
           <cell r="A97" t="str">
             <v>S-2026-01-94</v>
           </cell>
-          <cell r="B97"/>
           <cell r="C97" t="str">
             <v>RPRO-260128-1274</v>
           </cell>
@@ -10897,7 +10778,6 @@
           <cell r="A98" t="str">
             <v>S-2026-01-95</v>
           </cell>
-          <cell r="B98"/>
           <cell r="C98" t="str">
             <v>RPRO-260128-1275</v>
           </cell>
@@ -10966,7 +10846,6 @@
           <cell r="A99" t="str">
             <v>S-2026-01-96</v>
           </cell>
-          <cell r="B99"/>
           <cell r="C99" t="str">
             <v>RPRO-260128-1276</v>
           </cell>
@@ -11035,7 +10914,6 @@
           <cell r="A100" t="str">
             <v>S-2026-01-97</v>
           </cell>
-          <cell r="B100"/>
           <cell r="C100" t="str">
             <v>RPRO-260128-1277</v>
           </cell>
@@ -11104,7 +10982,6 @@
           <cell r="A101" t="str">
             <v>S-2026-01-98</v>
           </cell>
-          <cell r="B101"/>
           <cell r="C101" t="str">
             <v>RPRO-260129-0656</v>
           </cell>
@@ -11173,7 +11050,6 @@
           <cell r="A102" t="str">
             <v>S-2026-02-01</v>
           </cell>
-          <cell r="B102"/>
           <cell r="C102" t="str">
             <v>RPRO-260203-0021</v>
           </cell>
@@ -11242,7 +11118,6 @@
           <cell r="A103" t="str">
             <v>S-2026-02-02</v>
           </cell>
-          <cell r="B103"/>
           <cell r="C103" t="str">
             <v>RPRO-260203-0022</v>
           </cell>
@@ -11311,7 +11186,6 @@
           <cell r="A104" t="str">
             <v>S-2026-02-03</v>
           </cell>
-          <cell r="B104"/>
           <cell r="C104" t="str">
             <v>RPRO-260203-0770</v>
           </cell>
@@ -11380,7 +11254,6 @@
           <cell r="A105" t="str">
             <v>S-2026-02-04</v>
           </cell>
-          <cell r="B105"/>
           <cell r="C105" t="str">
             <v>RPRO-260203-0771</v>
           </cell>
@@ -11449,7 +11322,6 @@
           <cell r="A106" t="str">
             <v>S-2026-02-05</v>
           </cell>
-          <cell r="B106"/>
           <cell r="C106" t="str">
             <v>RPRO-260203-0772</v>
           </cell>
@@ -11518,7 +11390,6 @@
           <cell r="A107" t="str">
             <v>S-2026-02-06</v>
           </cell>
-          <cell r="B107"/>
           <cell r="C107" t="str">
             <v>RPRO-260203-0773</v>
           </cell>
@@ -11587,7 +11458,6 @@
           <cell r="A108" t="str">
             <v>S-2026-02-07</v>
           </cell>
-          <cell r="B108"/>
           <cell r="C108" t="str">
             <v>RPRO-260203-0774</v>
           </cell>
@@ -11656,7 +11526,6 @@
           <cell r="A109" t="str">
             <v>S-2026-02-08</v>
           </cell>
-          <cell r="B109"/>
           <cell r="C109" t="str">
             <v>RPRO-260203-0775</v>
           </cell>
@@ -11725,7 +11594,6 @@
           <cell r="A110" t="str">
             <v>S-2026-02-09</v>
           </cell>
-          <cell r="B110"/>
           <cell r="C110" t="str">
             <v>RPRO-260203-0776</v>
           </cell>
@@ -11794,7 +11662,6 @@
           <cell r="A111" t="str">
             <v>S-2026-02-10</v>
           </cell>
-          <cell r="B111"/>
           <cell r="C111" t="str">
             <v>RPRO-260203-0777</v>
           </cell>
@@ -11863,7 +11730,6 @@
           <cell r="A112" t="str">
             <v>S-2026-02-11</v>
           </cell>
-          <cell r="B112"/>
           <cell r="C112" t="str">
             <v>RPRO-260203-0778</v>
           </cell>
@@ -11932,7 +11798,6 @@
           <cell r="A113" t="str">
             <v>S-2026-02-12</v>
           </cell>
-          <cell r="B113"/>
           <cell r="C113" t="str">
             <v>RPRO-260203-0779</v>
           </cell>
@@ -12001,7 +11866,6 @@
           <cell r="A114" t="str">
             <v>S-2026-02-13</v>
           </cell>
-          <cell r="B114"/>
           <cell r="C114" t="str">
             <v>RPRO-260203-0780</v>
           </cell>
@@ -12070,7 +11934,6 @@
           <cell r="A115" t="str">
             <v>S-2026-02-14</v>
           </cell>
-          <cell r="B115"/>
           <cell r="C115" t="str">
             <v>RPRO-260203-0781</v>
           </cell>
@@ -12139,7 +12002,6 @@
           <cell r="A116" t="str">
             <v>S-2026-02-15</v>
           </cell>
-          <cell r="B116"/>
           <cell r="C116" t="str">
             <v>RPRO-260203-0782</v>
           </cell>
@@ -12208,7 +12070,6 @@
           <cell r="A117" t="str">
             <v>S-2026-02-16</v>
           </cell>
-          <cell r="B117"/>
           <cell r="C117" t="str">
             <v>RPRO-260203-0783</v>
           </cell>
@@ -12277,7 +12138,6 @@
           <cell r="A118" t="str">
             <v>S-2026-02-17</v>
           </cell>
-          <cell r="B118"/>
           <cell r="C118" t="str">
             <v>RPRO-260203-0784</v>
           </cell>
@@ -12346,7 +12206,6 @@
           <cell r="A119" t="str">
             <v>S-2026-02-18</v>
           </cell>
-          <cell r="B119"/>
           <cell r="C119" t="str">
             <v>RPRO-260204-0399</v>
           </cell>
@@ -12415,7 +12274,6 @@
           <cell r="A120" t="str">
             <v>S-2026-02-19</v>
           </cell>
-          <cell r="B120"/>
           <cell r="C120" t="str">
             <v>RPRO-260204-0400</v>
           </cell>
@@ -12484,7 +12342,6 @@
           <cell r="A121" t="str">
             <v>L-2026-02-20</v>
           </cell>
-          <cell r="B121"/>
           <cell r="C121" t="str">
             <v>RPRO-260204-0401</v>
           </cell>
@@ -12518,7 +12375,6 @@
           <cell r="M121" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N121"/>
           <cell r="O121" t="str">
             <v>Lab test</v>
           </cell>
@@ -12551,7 +12407,6 @@
           <cell r="A122" t="str">
             <v>L-2026-02-21</v>
           </cell>
-          <cell r="B122"/>
           <cell r="C122" t="str">
             <v>RPRO-260204-0402</v>
           </cell>
@@ -12585,7 +12440,6 @@
           <cell r="M122" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N122"/>
           <cell r="O122" t="str">
             <v>Lab test</v>
           </cell>
@@ -12689,7 +12543,6 @@
           <cell r="A124" t="str">
             <v>S-2026-02-23</v>
           </cell>
-          <cell r="B124"/>
           <cell r="C124" t="str">
             <v>RPRO-260210-0003</v>
           </cell>
@@ -12829,7 +12682,6 @@
           <cell r="A126" t="str">
             <v>S-2026-02-25</v>
           </cell>
-          <cell r="B126"/>
           <cell r="C126" t="str">
             <v>RPRO-260210-0005</v>
           </cell>
@@ -12898,7 +12750,6 @@
           <cell r="A127" t="str">
             <v>S-2026-02-26</v>
           </cell>
-          <cell r="B127"/>
           <cell r="C127" t="str">
             <v>RPRO-260210-0006</v>
           </cell>
@@ -12967,7 +12818,6 @@
           <cell r="A128" t="str">
             <v>S-2026-02-27</v>
           </cell>
-          <cell r="B128"/>
           <cell r="C128" t="str">
             <v>RPRO-260210-0007</v>
           </cell>
@@ -13036,7 +12886,6 @@
           <cell r="A129" t="str">
             <v>S-2026-02-28</v>
           </cell>
-          <cell r="B129"/>
           <cell r="C129" t="str">
             <v>RPRO-260210-0008</v>
           </cell>
@@ -13105,7 +12954,6 @@
           <cell r="A130" t="str">
             <v>S-2026-02-29</v>
           </cell>
-          <cell r="B130"/>
           <cell r="C130" t="str">
             <v>RPRO-260210-0009</v>
           </cell>
@@ -13174,7 +13022,6 @@
           <cell r="A131" t="str">
             <v>S-2026-02-30</v>
           </cell>
-          <cell r="B131"/>
           <cell r="C131" t="str">
             <v>RPRO-260210-0010</v>
           </cell>
@@ -13243,7 +13090,6 @@
           <cell r="A132" t="str">
             <v>S-2026-02-31</v>
           </cell>
-          <cell r="B132"/>
           <cell r="C132" t="str">
             <v>RPRO-260210-0011</v>
           </cell>
@@ -13313,7 +13159,6 @@
           <cell r="A133" t="str">
             <v>S-2026-02-32</v>
           </cell>
-          <cell r="B133"/>
           <cell r="C133" t="str">
             <v>RPRO-260210-0012</v>
           </cell>
@@ -13383,7 +13228,6 @@
           <cell r="A134" t="str">
             <v>S-2026-02-33</v>
           </cell>
-          <cell r="B134"/>
           <cell r="C134" t="str">
             <v>RPRO-260210-0013</v>
           </cell>
@@ -13452,7 +13296,6 @@
           <cell r="A135" t="str">
             <v>S-2026-02-34</v>
           </cell>
-          <cell r="B135"/>
           <cell r="C135" t="str">
             <v>RPRO-260211-0001</v>
           </cell>
@@ -13523,7 +13366,6 @@
           <cell r="A136" t="str">
             <v>S-2026-02-35</v>
           </cell>
-          <cell r="B136"/>
           <cell r="C136" t="str">
             <v>RPRO-260227-0335</v>
           </cell>
@@ -13592,7 +13434,6 @@
           <cell r="A137" t="str">
             <v>S-2026-02-36</v>
           </cell>
-          <cell r="B137"/>
           <cell r="C137" t="str">
             <v>RPRO-260227-0336</v>
           </cell>
@@ -13661,7 +13502,6 @@
           <cell r="A138" t="str">
             <v>S-2026-02-37</v>
           </cell>
-          <cell r="B138"/>
           <cell r="C138" t="str">
             <v>RPRO-260227-0337</v>
           </cell>
@@ -13730,7 +13570,6 @@
           <cell r="A139" t="str">
             <v>S-2026-02-38</v>
           </cell>
-          <cell r="B139"/>
           <cell r="C139" t="str">
             <v>RPRO-260227-0338</v>
           </cell>
@@ -13799,7 +13638,6 @@
           <cell r="A140" t="str">
             <v>S-2026-02-39</v>
           </cell>
-          <cell r="B140"/>
           <cell r="C140" t="str">
             <v>RPRO-260227-0339</v>
           </cell>
@@ -13868,7 +13706,6 @@
           <cell r="A141" t="str">
             <v>L-2026-02-40</v>
           </cell>
-          <cell r="B141"/>
           <cell r="C141" t="str">
             <v>RPRO-260227-0340</v>
           </cell>
@@ -13902,7 +13739,6 @@
           <cell r="M141" t="str">
             <v>Lab test</v>
           </cell>
-          <cell r="N141"/>
           <cell r="O141" t="str">
             <v>Lab test</v>
           </cell>
@@ -13935,7 +13771,6 @@
           <cell r="A142" t="str">
             <v>S-2026-02-41</v>
           </cell>
-          <cell r="B142"/>
           <cell r="C142" t="str">
             <v>RPRO-260227-0341</v>
           </cell>
@@ -14004,7 +13839,6 @@
           <cell r="A143" t="str">
             <v>S-2026-02-42</v>
           </cell>
-          <cell r="B143"/>
           <cell r="C143" t="str">
             <v>RPRO-260227-0342</v>
           </cell>
@@ -14073,7 +13907,6 @@
           <cell r="A144" t="str">
             <v>S-2026-02-43</v>
           </cell>
-          <cell r="B144"/>
           <cell r="C144" t="str">
             <v>RPRO-260227-0343</v>
           </cell>
@@ -14142,7 +13975,6 @@
           <cell r="A145" t="str">
             <v>S-2026-02-44</v>
           </cell>
-          <cell r="B145"/>
           <cell r="C145" t="str">
             <v>RPRO-260227-0344</v>
           </cell>
@@ -14211,7 +14043,6 @@
           <cell r="A146" t="str">
             <v>S-2026-02-45</v>
           </cell>
-          <cell r="B146"/>
           <cell r="C146" t="str">
             <v>RPRO-260227-0345</v>
           </cell>
@@ -14351,7 +14182,6 @@
           <cell r="A148" t="str">
             <v>S-2026-02-47</v>
           </cell>
-          <cell r="B148"/>
           <cell r="C148" t="str">
             <v>RPRO-260227-0347</v>
           </cell>
@@ -14420,7 +14250,6 @@
           <cell r="A149" t="str">
             <v>S-2026-02-48</v>
           </cell>
-          <cell r="B149"/>
           <cell r="C149" t="str">
             <v>RPRO-260227-0348</v>
           </cell>
@@ -14489,7 +14318,6 @@
           <cell r="A150" t="str">
             <v>S-2026-02-49</v>
           </cell>
-          <cell r="B150"/>
           <cell r="C150" t="str">
             <v>RPRO-260302-0004</v>
           </cell>
@@ -14558,7 +14386,6 @@
           <cell r="A151" t="str">
             <v>S-2026-02-50</v>
           </cell>
-          <cell r="B151"/>
           <cell r="C151" t="str">
             <v>RPRO-260227-0349</v>
           </cell>
@@ -14627,7 +14454,6 @@
           <cell r="A152" t="str">
             <v>S-2026-02-51</v>
           </cell>
-          <cell r="B152"/>
           <cell r="C152" t="str">
             <v>RPRO-260227-0350</v>
           </cell>
@@ -14696,7 +14522,6 @@
           <cell r="A153" t="str">
             <v>S-2026-02-52</v>
           </cell>
-          <cell r="B153"/>
           <cell r="C153" t="str">
             <v>RPRO-260227-0351</v>
           </cell>
@@ -14765,7 +14590,6 @@
           <cell r="A154" t="str">
             <v>S-2026-02-53</v>
           </cell>
-          <cell r="B154"/>
           <cell r="C154" t="str">
             <v>RPRO-260227-0352</v>
           </cell>
@@ -14834,7 +14658,6 @@
           <cell r="A155" t="str">
             <v>L-2026-03-01</v>
           </cell>
-          <cell r="B155"/>
           <cell r="C155" t="str">
             <v>RPRO-260303-0005</v>
           </cell>
@@ -14868,7 +14691,6 @@
           <cell r="M155" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N155"/>
           <cell r="O155" t="str">
             <v>Lab test</v>
           </cell>
@@ -14901,7 +14723,6 @@
           <cell r="A156" t="str">
             <v>L-2026-03-02</v>
           </cell>
-          <cell r="B156"/>
           <cell r="C156" t="str">
             <v>RPRO-260303-0006</v>
           </cell>
@@ -14935,7 +14756,6 @@
           <cell r="M156" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N156"/>
           <cell r="O156" t="str">
             <v>Lab test</v>
           </cell>
@@ -15252,7 +15072,6 @@
           <cell r="A161" t="str">
             <v>S-2026-03-07</v>
           </cell>
-          <cell r="B161"/>
           <cell r="C161" t="str">
             <v>RPRO-260303-0011</v>
           </cell>
@@ -15321,7 +15140,6 @@
           <cell r="A162" t="str">
             <v>S-2026-03-08</v>
           </cell>
-          <cell r="B162"/>
           <cell r="C162" t="str">
             <v>RPRO-260303-0012</v>
           </cell>
@@ -15390,7 +15208,6 @@
           <cell r="A163" t="str">
             <v>S-2026-03-09</v>
           </cell>
-          <cell r="B163"/>
           <cell r="C163" t="str">
             <v>RPRO-260303-0013</v>
           </cell>
@@ -15459,7 +15276,6 @@
           <cell r="A164" t="str">
             <v>S-2026-03-10</v>
           </cell>
-          <cell r="B164"/>
           <cell r="C164" t="str">
             <v>RPRO-260303-0014</v>
           </cell>
@@ -15528,7 +15344,6 @@
           <cell r="A165" t="str">
             <v>S-2026-03-11</v>
           </cell>
-          <cell r="B165"/>
           <cell r="C165" t="str">
             <v>RPRO-260313-0139</v>
           </cell>
@@ -15562,7 +15377,6 @@
           <cell r="M165" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
-          <cell r="N165"/>
           <cell r="O165" t="str">
             <v>Sample</v>
           </cell>
@@ -15595,7 +15409,6 @@
           <cell r="A166" t="str">
             <v>S-2026-03-12</v>
           </cell>
-          <cell r="B166"/>
           <cell r="C166" t="str">
             <v>RPRO-260313-0140</v>
           </cell>
@@ -15629,7 +15442,6 @@
           <cell r="M166" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
-          <cell r="N166"/>
           <cell r="O166" t="str">
             <v>Sample</v>
           </cell>
@@ -15662,7 +15474,6 @@
           <cell r="A167" t="str">
             <v>S-2026-03-13</v>
           </cell>
-          <cell r="B167"/>
           <cell r="C167" t="str">
             <v>RPRO-260313-0141</v>
           </cell>
@@ -15696,7 +15507,6 @@
           <cell r="M167" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
-          <cell r="N167"/>
           <cell r="O167" t="str">
             <v>Sample</v>
           </cell>
@@ -15800,7 +15610,6 @@
           <cell r="A169" t="str">
             <v>S-2026-03-15</v>
           </cell>
-          <cell r="B169"/>
           <cell r="C169" t="str">
             <v>RPRO-260306-1547</v>
           </cell>
@@ -15869,7 +15678,6 @@
           <cell r="A170" t="str">
             <v>S-2026-03-16</v>
           </cell>
-          <cell r="B170"/>
           <cell r="C170" t="str">
             <v>RPRO-260306-1548</v>
           </cell>
@@ -15938,7 +15746,6 @@
           <cell r="A171" t="str">
             <v>S-2026-03-17</v>
           </cell>
-          <cell r="B171"/>
           <cell r="C171" t="str">
             <v>RPRO-260306-1549</v>
           </cell>
@@ -16007,7 +15814,6 @@
           <cell r="A172" t="str">
             <v>S-2026-03-18</v>
           </cell>
-          <cell r="B172"/>
           <cell r="C172" t="str">
             <v>RPRO-260306-1550</v>
           </cell>
@@ -16076,7 +15882,6 @@
           <cell r="A173" t="str">
             <v>S-2026-03-19</v>
           </cell>
-          <cell r="B173"/>
           <cell r="C173" t="str">
             <v>RPRO-260306-1551</v>
           </cell>
@@ -16145,7 +15950,6 @@
           <cell r="A174" t="str">
             <v>S-2026-03-20</v>
           </cell>
-          <cell r="B174"/>
           <cell r="C174" t="str">
             <v>RPRO-260306-1552</v>
           </cell>
@@ -16214,7 +16018,6 @@
           <cell r="A175" t="str">
             <v>S-2026-03-21</v>
           </cell>
-          <cell r="B175"/>
           <cell r="C175" t="str">
             <v>RPRO-260306-1553</v>
           </cell>
@@ -16283,7 +16086,6 @@
           <cell r="A176" t="str">
             <v>S-2026-03-22</v>
           </cell>
-          <cell r="B176"/>
           <cell r="C176" t="str">
             <v>RPRO-260306-1554</v>
           </cell>
@@ -16352,7 +16154,6 @@
           <cell r="A177" t="str">
             <v>S-2026-03-23</v>
           </cell>
-          <cell r="B177"/>
           <cell r="C177" t="str">
             <v>RPRO-260306-1555</v>
           </cell>
@@ -16421,7 +16222,6 @@
           <cell r="A178" t="str">
             <v>S-2026-03-24</v>
           </cell>
-          <cell r="B178"/>
           <cell r="C178" t="str">
             <v>RPRO-260306-1556</v>
           </cell>
@@ -16561,7 +16361,6 @@
           <cell r="A180" t="str">
             <v>L-2026-03-26</v>
           </cell>
-          <cell r="B180"/>
           <cell r="C180" t="str">
             <v>RPRO-260305-1288</v>
           </cell>
@@ -16595,7 +16394,6 @@
           <cell r="M180" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N180"/>
           <cell r="O180" t="str">
             <v>Lab test</v>
           </cell>
@@ -16699,7 +16497,6 @@
           <cell r="A182" t="str">
             <v>S-2026-03-28</v>
           </cell>
-          <cell r="B182"/>
           <cell r="C182" t="str">
             <v>RPRO-260306-1559</v>
           </cell>
@@ -16768,7 +16565,6 @@
           <cell r="A183" t="str">
             <v>S-2026-03-29</v>
           </cell>
-          <cell r="B183"/>
           <cell r="C183" t="str">
             <v>RPRO-260306-1560</v>
           </cell>
@@ -16837,7 +16633,6 @@
           <cell r="A184" t="str">
             <v>S-2026-03-30</v>
           </cell>
-          <cell r="B184"/>
           <cell r="C184" t="str">
             <v>RPRO-260306-1561</v>
           </cell>
@@ -16906,7 +16701,6 @@
           <cell r="A185" t="str">
             <v>S-2026-03-31</v>
           </cell>
-          <cell r="B185"/>
           <cell r="C185" t="str">
             <v>RPRO-260306-1562</v>
           </cell>
@@ -16975,7 +16769,6 @@
           <cell r="A186" t="str">
             <v>S-2026-03-32</v>
           </cell>
-          <cell r="B186"/>
           <cell r="C186" t="str">
             <v>RPRO-260306-1563</v>
           </cell>
@@ -17044,7 +16837,6 @@
           <cell r="A187" t="str">
             <v>S-2026-03-33</v>
           </cell>
-          <cell r="B187"/>
           <cell r="C187" t="str">
             <v>RPRO-260306-1564</v>
           </cell>
@@ -17113,7 +16905,6 @@
           <cell r="A188" t="str">
             <v>S-2026-03-34</v>
           </cell>
-          <cell r="B188"/>
           <cell r="C188" t="str">
             <v>RPRO-260306-1565</v>
           </cell>
@@ -17182,7 +16973,6 @@
           <cell r="A189" t="str">
             <v>S-2026-03-35</v>
           </cell>
-          <cell r="B189"/>
           <cell r="C189" t="str">
             <v>RPRO-260306-1566</v>
           </cell>
@@ -17251,7 +17041,6 @@
           <cell r="A190" t="str">
             <v>S-2026-03-36</v>
           </cell>
-          <cell r="B190"/>
           <cell r="C190" t="str">
             <v>RPRO-260307-0080</v>
           </cell>
@@ -17320,7 +17109,6 @@
           <cell r="A191" t="str">
             <v>S-2026-03-37</v>
           </cell>
-          <cell r="B191"/>
           <cell r="C191" t="str">
             <v>RPRO-260306-1736</v>
           </cell>
@@ -17389,7 +17177,6 @@
           <cell r="A192" t="str">
             <v>S-2026-03-38</v>
           </cell>
-          <cell r="B192"/>
           <cell r="C192" t="str">
             <v>RPRO-260306-1737</v>
           </cell>
@@ -17458,7 +17245,6 @@
           <cell r="A193" t="str">
             <v>S-2026-03-39</v>
           </cell>
-          <cell r="B193"/>
           <cell r="C193" t="str">
             <v>RPRO-260306-1738</v>
           </cell>
@@ -17527,7 +17313,6 @@
           <cell r="A194" t="str">
             <v>S-2026-03-40</v>
           </cell>
-          <cell r="B194"/>
           <cell r="C194" t="str">
             <v>RPRO-260306-1739</v>
           </cell>
@@ -17596,7 +17381,6 @@
           <cell r="A195" t="str">
             <v>S-2026-03-41</v>
           </cell>
-          <cell r="B195"/>
           <cell r="C195" t="str">
             <v>RPRO-260306-1740</v>
           </cell>
@@ -17665,7 +17449,6 @@
           <cell r="A196" t="str">
             <v>S-2026-03-42</v>
           </cell>
-          <cell r="B196"/>
           <cell r="C196" t="str">
             <v>RPRO-260307-0081</v>
           </cell>
@@ -17734,7 +17517,6 @@
           <cell r="A197" t="str">
             <v>S-2026-03-43</v>
           </cell>
-          <cell r="B197"/>
           <cell r="C197" t="str">
             <v>RPRO-260307-0082</v>
           </cell>
@@ -17803,7 +17585,6 @@
           <cell r="A198" t="str">
             <v>S-2026-03-44</v>
           </cell>
-          <cell r="B198"/>
           <cell r="C198" t="str">
             <v>RPRO-260307-0083</v>
           </cell>
@@ -17872,7 +17653,6 @@
           <cell r="A199" t="str">
             <v>S-2026-03-45</v>
           </cell>
-          <cell r="B199"/>
           <cell r="C199" t="str">
             <v>RPRO-260307-0084</v>
           </cell>
@@ -17941,7 +17721,6 @@
           <cell r="A200" t="str">
             <v>S-2026-03-46</v>
           </cell>
-          <cell r="B200"/>
           <cell r="C200" t="str">
             <v>RPRO-260307-0085</v>
           </cell>
@@ -18010,7 +17789,6 @@
           <cell r="A201" t="str">
             <v>S-2026-03-47</v>
           </cell>
-          <cell r="B201"/>
           <cell r="C201" t="str">
             <v>RPRO-260310-0362</v>
           </cell>
@@ -18150,7 +17928,6 @@
           <cell r="A203" t="str">
             <v>S-2026-03-49</v>
           </cell>
-          <cell r="B203"/>
           <cell r="C203" t="str">
             <v>RPRO-260310-0364</v>
           </cell>
@@ -18219,7 +17996,6 @@
           <cell r="A204" t="str">
             <v>S-2026-03-50</v>
           </cell>
-          <cell r="B204"/>
           <cell r="C204" t="str">
             <v>RPRO-260310-0365</v>
           </cell>
@@ -18359,7 +18135,6 @@
           <cell r="A206" t="str">
             <v>S-2026-03-52</v>
           </cell>
-          <cell r="B206"/>
           <cell r="C206" t="str">
             <v>RPRO-260310-0367</v>
           </cell>
@@ -18428,7 +18203,6 @@
           <cell r="A207" t="str">
             <v>S-2026-03-53</v>
           </cell>
-          <cell r="B207"/>
           <cell r="C207" t="str">
             <v>RPRO-260310-0368</v>
           </cell>
@@ -18497,7 +18271,6 @@
           <cell r="A208" t="str">
             <v>S-2026-03-54</v>
           </cell>
-          <cell r="B208"/>
           <cell r="C208" t="str">
             <v>RPRO-260310-0369</v>
           </cell>
@@ -18566,7 +18339,6 @@
           <cell r="A209" t="str">
             <v>S-2026-03-55</v>
           </cell>
-          <cell r="B209"/>
           <cell r="C209" t="str">
             <v>RPRO-260310-0370</v>
           </cell>
@@ -18635,7 +18407,6 @@
           <cell r="A210" t="str">
             <v>S-2026-03-56</v>
           </cell>
-          <cell r="B210"/>
           <cell r="C210" t="str">
             <v>RPRO-260310-0371</v>
           </cell>
@@ -18704,7 +18475,6 @@
           <cell r="A211" t="str">
             <v>S-2026-03-57</v>
           </cell>
-          <cell r="B211"/>
           <cell r="C211" t="str">
             <v>RPRO-260310-0372</v>
           </cell>
@@ -18773,7 +18543,6 @@
           <cell r="A212" t="str">
             <v>S-2026-03-58</v>
           </cell>
-          <cell r="B212"/>
           <cell r="C212" t="str">
             <v>RPRO-260310-0373</v>
           </cell>
@@ -18842,7 +18611,6 @@
           <cell r="A213" t="str">
             <v>S-2026-03-59</v>
           </cell>
-          <cell r="B213"/>
           <cell r="C213" t="str">
             <v>RPRO-260310-0374</v>
           </cell>
@@ -18911,7 +18679,6 @@
           <cell r="A214" t="str">
             <v>S-2026-03-60</v>
           </cell>
-          <cell r="B214"/>
           <cell r="C214" t="str">
             <v>RPRO-260310-0375</v>
           </cell>
@@ -18980,7 +18747,6 @@
           <cell r="A215" t="str">
             <v>S-2026-03-61</v>
           </cell>
-          <cell r="B215"/>
           <cell r="C215" t="str">
             <v>RPRO-260310-0376</v>
           </cell>
@@ -19052,7 +18818,6 @@
           <cell r="B216" t="str">
             <v>huy</v>
           </cell>
-          <cell r="C216"/>
           <cell r="D216" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -19083,7 +18848,6 @@
           <cell r="M216" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N216"/>
           <cell r="O216" t="str">
             <v>Lab test</v>
           </cell>
@@ -19119,7 +18883,6 @@
           <cell r="B217" t="str">
             <v>huy</v>
           </cell>
-          <cell r="C217"/>
           <cell r="D217" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -19150,7 +18913,6 @@
           <cell r="M217" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N217"/>
           <cell r="O217" t="str">
             <v>Lab test</v>
           </cell>
@@ -19183,7 +18945,6 @@
           <cell r="A218" t="str">
             <v>S-2026-03-64</v>
           </cell>
-          <cell r="B218"/>
           <cell r="C218" t="str">
             <v>RPRO-260313-0142</v>
           </cell>
@@ -19252,7 +19013,6 @@
           <cell r="A219" t="str">
             <v>S-2026-03-65</v>
           </cell>
-          <cell r="B219"/>
           <cell r="C219" t="str">
             <v>RPRO-260313-0143</v>
           </cell>
@@ -19321,7 +19081,6 @@
           <cell r="A220" t="str">
             <v>S-2026-03-66</v>
           </cell>
-          <cell r="B220"/>
           <cell r="C220" t="str">
             <v>RPRO-260313-0144</v>
           </cell>
@@ -19390,7 +19149,6 @@
           <cell r="A221" t="str">
             <v>S-2026-03-67</v>
           </cell>
-          <cell r="B221"/>
           <cell r="C221" t="str">
             <v>RPRO-260313-0145</v>
           </cell>
@@ -19459,7 +19217,6 @@
           <cell r="A222" t="str">
             <v>S-2026-03-68</v>
           </cell>
-          <cell r="B222"/>
           <cell r="C222" t="str">
             <v>RPRO-260313-0146</v>
           </cell>
@@ -19528,7 +19285,6 @@
           <cell r="A223" t="str">
             <v>S-2026-03-69</v>
           </cell>
-          <cell r="B223"/>
           <cell r="C223" t="str">
             <v>RPRO-260313-0147</v>
           </cell>
@@ -19597,7 +19353,6 @@
           <cell r="A224" t="str">
             <v>S-2026-03-70</v>
           </cell>
-          <cell r="B224"/>
           <cell r="C224" t="str">
             <v>RPRO-260313-0148</v>
           </cell>
@@ -19666,7 +19421,6 @@
           <cell r="A225" t="str">
             <v>S-2026-03-71</v>
           </cell>
-          <cell r="B225"/>
           <cell r="C225" t="str">
             <v>RPRO-260313-0149</v>
           </cell>
@@ -19735,7 +19489,6 @@
           <cell r="A226" t="str">
             <v>S-2026-03-72</v>
           </cell>
-          <cell r="B226"/>
           <cell r="C226" t="str">
             <v>RPRO-260313-0150</v>
           </cell>
@@ -19804,7 +19557,6 @@
           <cell r="A227" t="str">
             <v>S-2026-03-73</v>
           </cell>
-          <cell r="B227"/>
           <cell r="C227" t="str">
             <v>RPRO-260313-0151</v>
           </cell>
@@ -19873,7 +19625,6 @@
           <cell r="A228" t="str">
             <v>S-2026-03-74</v>
           </cell>
-          <cell r="B228"/>
           <cell r="C228" t="str">
             <v>RPRO-260313-0152</v>
           </cell>
@@ -19942,7 +19693,6 @@
           <cell r="A229" t="str">
             <v>S-2026-03-75</v>
           </cell>
-          <cell r="B229"/>
           <cell r="C229" t="str">
             <v>RPRO-260313-0318</v>
           </cell>
@@ -20011,7 +19761,6 @@
           <cell r="A230" t="str">
             <v>S-2026-03-76</v>
           </cell>
-          <cell r="B230"/>
           <cell r="C230" t="str">
             <v>RPRO-260313-0319</v>
           </cell>
@@ -20080,7 +19829,6 @@
           <cell r="A231" t="str">
             <v>S-2026-03-77</v>
           </cell>
-          <cell r="B231"/>
           <cell r="C231" t="str">
             <v>RPRO-260314-0198</v>
           </cell>
@@ -20149,7 +19897,6 @@
           <cell r="A232" t="str">
             <v>S-2026-03-78</v>
           </cell>
-          <cell r="B232"/>
           <cell r="C232" t="str">
             <v>RPRO-260314-0199</v>
           </cell>
@@ -20218,7 +19965,6 @@
           <cell r="A233" t="str">
             <v>S-2026-03-79</v>
           </cell>
-          <cell r="B233"/>
           <cell r="C233" t="str">
             <v>RPRO-260317-0628</v>
           </cell>
@@ -20287,7 +20033,6 @@
           <cell r="A234" t="str">
             <v>S-2026-03-80</v>
           </cell>
-          <cell r="B234"/>
           <cell r="C234" t="str">
             <v>RPRO-260317-0629</v>
           </cell>
@@ -20356,7 +20101,6 @@
           <cell r="A235" t="str">
             <v>S-2026-03-81</v>
           </cell>
-          <cell r="B235"/>
           <cell r="C235" t="str">
             <v>RPRO-260317-0630</v>
           </cell>
@@ -20425,7 +20169,6 @@
           <cell r="A236" t="str">
             <v>S-2026-03-82</v>
           </cell>
-          <cell r="B236"/>
           <cell r="C236" t="str">
             <v>RPRO-260317-0631</v>
           </cell>
@@ -20494,7 +20237,6 @@
           <cell r="A237" t="str">
             <v>S-2026-03-83</v>
           </cell>
-          <cell r="B237"/>
           <cell r="C237" t="str">
             <v>RPRO-260317-0632</v>
           </cell>
@@ -20563,7 +20305,6 @@
           <cell r="A238" t="str">
             <v>S-2026-03-84</v>
           </cell>
-          <cell r="B238"/>
           <cell r="C238" t="str">
             <v>RPRO-260317-0633</v>
           </cell>
@@ -20632,7 +20373,6 @@
           <cell r="A239" t="str">
             <v>S-2026-03-85</v>
           </cell>
-          <cell r="B239"/>
           <cell r="C239" t="str">
             <v>RPRO-260317-0634</v>
           </cell>
@@ -20701,7 +20441,6 @@
           <cell r="A240" t="str">
             <v>S-2026-03-86</v>
           </cell>
-          <cell r="B240"/>
           <cell r="C240" t="str">
             <v>RPRO-260317-0635</v>
           </cell>
@@ -20770,7 +20509,6 @@
           <cell r="A241" t="str">
             <v>S-2026-03-87</v>
           </cell>
-          <cell r="B241"/>
           <cell r="C241" t="str">
             <v>RPRO-260317-0636</v>
           </cell>
@@ -20839,7 +20577,6 @@
           <cell r="A242" t="str">
             <v>L-2026-03-88</v>
           </cell>
-          <cell r="B242"/>
           <cell r="C242" t="str">
             <v>RPRO-260317-0637</v>
           </cell>
@@ -20873,7 +20610,6 @@
           <cell r="M242" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N242"/>
           <cell r="O242" t="str">
             <v>Lab test</v>
           </cell>
@@ -20942,7 +20678,6 @@
           <cell r="M243" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N243"/>
           <cell r="O243" t="str">
             <v>Lab test</v>
           </cell>
@@ -20975,7 +20710,6 @@
           <cell r="A244" t="str">
             <v>S-2026-03-90</v>
           </cell>
-          <cell r="B244"/>
           <cell r="C244" t="str">
             <v>RPRO-260317-0639</v>
           </cell>
@@ -21044,7 +20778,6 @@
           <cell r="A245" t="str">
             <v>S-2026-03-91</v>
           </cell>
-          <cell r="B245"/>
           <cell r="C245" t="str">
             <v>RPRO-260317-0640</v>
           </cell>
@@ -21113,7 +20846,6 @@
           <cell r="A246" t="str">
             <v>S-2026-03-92</v>
           </cell>
-          <cell r="B246"/>
           <cell r="C246" t="str">
             <v>RPRO-260317-0641</v>
           </cell>
@@ -21182,7 +20914,6 @@
           <cell r="A247" t="str">
             <v>L-2026-03-93</v>
           </cell>
-          <cell r="B247"/>
           <cell r="C247" t="str">
             <v>RPRO-260318-0477</v>
           </cell>
@@ -21216,7 +20947,6 @@
           <cell r="M247" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N247"/>
           <cell r="O247" t="str">
             <v>Lab test</v>
           </cell>
@@ -21249,7 +20979,6 @@
           <cell r="A248" t="str">
             <v>L-2026-03-94</v>
           </cell>
-          <cell r="B248"/>
           <cell r="C248" t="str">
             <v>RPRO-260318-0478</v>
           </cell>
@@ -21283,7 +21012,6 @@
           <cell r="M248" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N248"/>
           <cell r="O248" t="str">
             <v>Lab test</v>
           </cell>
@@ -21387,7 +21115,6 @@
           <cell r="A250" t="str">
             <v>S-2026-03-96</v>
           </cell>
-          <cell r="B250"/>
           <cell r="C250" t="str">
             <v>RPRO-260318-0482</v>
           </cell>
@@ -21456,7 +21183,6 @@
           <cell r="A251" t="str">
             <v>S-2026-03-97</v>
           </cell>
-          <cell r="B251"/>
           <cell r="C251" t="str">
             <v>RPRO-260324-0278</v>
           </cell>
@@ -21525,7 +21251,6 @@
           <cell r="A252" t="str">
             <v>S-2026-03-98</v>
           </cell>
-          <cell r="B252"/>
           <cell r="C252" t="str">
             <v>RPRO-260324-0279</v>
           </cell>
@@ -21665,7 +21390,6 @@
           <cell r="A254" t="str">
             <v>S-2026-03-100</v>
           </cell>
-          <cell r="B254"/>
           <cell r="C254" t="str">
             <v>RPRO-260324-0281</v>
           </cell>
@@ -21734,7 +21458,6 @@
           <cell r="A255" t="str">
             <v>S-2026-03-101</v>
           </cell>
-          <cell r="B255"/>
           <cell r="C255" t="str">
             <v>RPRO-260324-0282</v>
           </cell>
@@ -21803,7 +21526,6 @@
           <cell r="A256" t="str">
             <v>S-2026-03-102</v>
           </cell>
-          <cell r="B256"/>
           <cell r="C256" t="str">
             <v>RPRO-260324-0531</v>
           </cell>
@@ -21872,7 +21594,6 @@
           <cell r="A257" t="str">
             <v>S-2026-03-103</v>
           </cell>
-          <cell r="B257"/>
           <cell r="C257" t="str">
             <v>RPRO-260324-0283</v>
           </cell>
@@ -21941,7 +21662,6 @@
           <cell r="A258" t="str">
             <v>S-2026-03-104</v>
           </cell>
-          <cell r="B258"/>
           <cell r="C258" t="str">
             <v>RPRO-260324-0284</v>
           </cell>
@@ -22010,7 +21730,6 @@
           <cell r="A259" t="str">
             <v>L-2026-03-105</v>
           </cell>
-          <cell r="B259"/>
           <cell r="C259" t="str">
             <v>RPRO-260321-0027</v>
           </cell>
@@ -22044,7 +21763,6 @@
           <cell r="M259" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N259"/>
           <cell r="O259" t="str">
             <v>Lab test</v>
           </cell>
@@ -22077,7 +21795,6 @@
           <cell r="A260" t="str">
             <v>L-2026-03-106</v>
           </cell>
-          <cell r="B260"/>
           <cell r="C260" t="str">
             <v>RPRO-260321-0028</v>
           </cell>
@@ -22111,7 +21828,6 @@
           <cell r="M260" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N260"/>
           <cell r="O260" t="str">
             <v>Lab test</v>
           </cell>
@@ -22144,7 +21860,6 @@
           <cell r="A261" t="str">
             <v>S-2026-03-107</v>
           </cell>
-          <cell r="B261"/>
           <cell r="C261" t="str">
             <v>RPRO-260321-0029</v>
           </cell>
@@ -22213,7 +21928,6 @@
           <cell r="A262" t="str">
             <v>S-2026-03-108</v>
           </cell>
-          <cell r="B262"/>
           <cell r="C262" t="str">
             <v>RPRO-260324-0285</v>
           </cell>
@@ -22282,7 +21996,6 @@
           <cell r="A263" t="str">
             <v>L-2026-03-109</v>
           </cell>
-          <cell r="B263"/>
           <cell r="C263" t="str">
             <v>RPRO-260324-0286</v>
           </cell>
@@ -22310,11 +22023,9 @@
           <cell r="K263">
             <v>0</v>
           </cell>
-          <cell r="L263"/>
           <cell r="M263" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N263"/>
           <cell r="O263" t="str">
             <v>Lab test</v>
           </cell>
@@ -22347,7 +22058,6 @@
           <cell r="A264" t="str">
             <v>S-2026-03-110</v>
           </cell>
-          <cell r="B264"/>
           <cell r="C264" t="str">
             <v>RPRO-260324-0287</v>
           </cell>
@@ -22416,7 +22126,6 @@
           <cell r="A265" t="str">
             <v>S-2026-03-111</v>
           </cell>
-          <cell r="B265"/>
           <cell r="C265" t="str">
             <v>RPRO-260324-0288</v>
           </cell>
@@ -22485,7 +22194,6 @@
           <cell r="A266" t="str">
             <v>S-2026-03-112</v>
           </cell>
-          <cell r="B266"/>
           <cell r="C266" t="str">
             <v>RPRO-260324-0289</v>
           </cell>
@@ -22554,7 +22262,6 @@
           <cell r="A267" t="str">
             <v>S-2026-03-113</v>
           </cell>
-          <cell r="B267"/>
           <cell r="C267" t="str">
             <v>RPRO-260324-0532</v>
           </cell>
@@ -22623,7 +22330,6 @@
           <cell r="A268" t="str">
             <v>S-2026-03-114</v>
           </cell>
-          <cell r="B268"/>
           <cell r="C268" t="str">
             <v>RPRO-260324-0533</v>
           </cell>
@@ -22692,7 +22398,6 @@
           <cell r="A269" t="str">
             <v>S-2026-03-115</v>
           </cell>
-          <cell r="B269"/>
           <cell r="C269" t="str">
             <v>RPRO-260324-0534</v>
           </cell>
@@ -22761,7 +22466,6 @@
           <cell r="A270" t="str">
             <v>S-2026-03-116</v>
           </cell>
-          <cell r="B270"/>
           <cell r="C270" t="str">
             <v>RPRO-260325-0407</v>
           </cell>
@@ -22830,7 +22534,6 @@
           <cell r="A271" t="str">
             <v>S-2026-03-117</v>
           </cell>
-          <cell r="B271"/>
           <cell r="C271" t="str">
             <v>RPRO-260325-0408</v>
           </cell>
@@ -22899,7 +22602,6 @@
           <cell r="A272" t="str">
             <v>S-2026-03-118</v>
           </cell>
-          <cell r="B272"/>
           <cell r="C272" t="str">
             <v>RPRO-260325-0409</v>
           </cell>
@@ -22968,7 +22670,6 @@
           <cell r="A273" t="str">
             <v>S-2026-03-119</v>
           </cell>
-          <cell r="B273"/>
           <cell r="C273" t="str">
             <v>RPRO-260325-0410</v>
           </cell>
@@ -23037,7 +22738,6 @@
           <cell r="A274" t="str">
             <v>S-2026-03-120</v>
           </cell>
-          <cell r="B274"/>
           <cell r="C274" t="str">
             <v>RPRO-260325-0411</v>
           </cell>
@@ -23106,7 +22806,6 @@
           <cell r="A275" t="str">
             <v>S-2026-03-121</v>
           </cell>
-          <cell r="B275"/>
           <cell r="C275" t="str">
             <v>RPRO-260325-0412</v>
           </cell>
@@ -23175,7 +22874,6 @@
           <cell r="A276" t="str">
             <v>S-2026-03-122</v>
           </cell>
-          <cell r="B276"/>
           <cell r="C276" t="str">
             <v>RPRO-260325-0413</v>
           </cell>
@@ -23244,7 +22942,6 @@
           <cell r="A277" t="str">
             <v>S-2026-03-123</v>
           </cell>
-          <cell r="B277"/>
           <cell r="C277" t="str">
             <v>RPRO-260325-0414</v>
           </cell>
@@ -23313,7 +23010,6 @@
           <cell r="A278" t="str">
             <v>S-2026-03-124</v>
           </cell>
-          <cell r="B278"/>
           <cell r="C278" t="str">
             <v>RPRO-260325-0415</v>
           </cell>
@@ -23453,7 +23149,6 @@
           <cell r="A280" t="str">
             <v>S-2026-03-126</v>
           </cell>
-          <cell r="B280"/>
           <cell r="C280" t="str">
             <v>RPRO-260325-0417</v>
           </cell>
@@ -23522,7 +23217,6 @@
           <cell r="A281" t="str">
             <v>S-2026-03-127</v>
           </cell>
-          <cell r="B281"/>
           <cell r="C281" t="str">
             <v>RPRO-260325-0418</v>
           </cell>
@@ -23591,7 +23285,6 @@
           <cell r="A282" t="str">
             <v>S-2026-03-128</v>
           </cell>
-          <cell r="B282"/>
           <cell r="C282" t="str">
             <v>RPRO-260325-0419</v>
           </cell>
@@ -23660,7 +23353,6 @@
           <cell r="A283" t="str">
             <v>S-2026-03-129</v>
           </cell>
-          <cell r="B283"/>
           <cell r="C283" t="str">
             <v>RPRO-260325-0421</v>
           </cell>
@@ -23729,7 +23421,6 @@
           <cell r="A284" t="str">
             <v>S-2026-03-130</v>
           </cell>
-          <cell r="B284"/>
           <cell r="C284" t="str">
             <v>RPRO-260327-0930</v>
           </cell>
@@ -23940,7 +23631,6 @@
           <cell r="A287" t="str">
             <v>S-2026-03-133</v>
           </cell>
-          <cell r="B287"/>
           <cell r="C287" t="str">
             <v>RPRO-260327-0933</v>
           </cell>
@@ -24009,7 +23699,6 @@
           <cell r="A288" t="str">
             <v>S-2026-03-134</v>
           </cell>
-          <cell r="B288"/>
           <cell r="C288" t="str">
             <v>RPRO-260327-0934</v>
           </cell>
@@ -24220,7 +23909,6 @@
           <cell r="A291" t="str">
             <v>S-2026-03-137</v>
           </cell>
-          <cell r="B291"/>
           <cell r="C291" t="str">
             <v>RPRO-260327-0937</v>
           </cell>
@@ -24360,7 +24048,6 @@
           <cell r="A293" t="str">
             <v>S-2026-03-139</v>
           </cell>
-          <cell r="B293"/>
           <cell r="C293" t="str">
             <v>RPRO-260327-0939</v>
           </cell>
@@ -24500,7 +24187,6 @@
           <cell r="A295" t="str">
             <v>S-2026-03-141</v>
           </cell>
-          <cell r="B295"/>
           <cell r="C295" t="str">
             <v>RPRO-260327-0941</v>
           </cell>
@@ -24569,7 +24255,6 @@
           <cell r="A296" t="str">
             <v>S-2026-03-142</v>
           </cell>
-          <cell r="B296"/>
           <cell r="C296" t="str">
             <v>RPRO-260401-0245</v>
           </cell>
@@ -24709,7 +24394,6 @@
           <cell r="A298" t="str">
             <v>S-2026-03-144</v>
           </cell>
-          <cell r="B298"/>
           <cell r="C298" t="str">
             <v>RPRO-260401-0247</v>
           </cell>
@@ -24778,7 +24462,6 @@
           <cell r="A299" t="str">
             <v>S-2026-03-145</v>
           </cell>
-          <cell r="B299"/>
           <cell r="C299" t="str">
             <v>RPRO-260401-0248</v>
           </cell>
@@ -24847,7 +24530,6 @@
           <cell r="A300" t="str">
             <v>S-2026-03-146</v>
           </cell>
-          <cell r="B300"/>
           <cell r="C300" t="str">
             <v>RPRO-260401-0249</v>
           </cell>
@@ -24916,7 +24598,6 @@
           <cell r="A301" t="str">
             <v>S-2026-04-01</v>
           </cell>
-          <cell r="B301"/>
           <cell r="C301" t="str">
             <v>RPRO-260401-0250</v>
           </cell>
@@ -24985,7 +24666,6 @@
           <cell r="A302" t="str">
             <v>S-2026-04-02</v>
           </cell>
-          <cell r="B302"/>
           <cell r="C302" t="str">
             <v>RPRO-260401-0251</v>
           </cell>
@@ -25054,7 +24734,6 @@
           <cell r="A303" t="str">
             <v>S-2026-04-03</v>
           </cell>
-          <cell r="B303"/>
           <cell r="C303" t="str">
             <v>RPRO-260402-0737</v>
           </cell>
@@ -25123,7 +24802,6 @@
           <cell r="A304" t="str">
             <v>S-2026-04-04</v>
           </cell>
-          <cell r="B304"/>
           <cell r="C304" t="str">
             <v>RPRO-260402-0738</v>
           </cell>
@@ -25192,7 +24870,6 @@
           <cell r="A305" t="str">
             <v>S-2026-04-05</v>
           </cell>
-          <cell r="B305"/>
           <cell r="C305" t="str">
             <v>RPRO-260403-0489</v>
           </cell>
@@ -25261,7 +24938,6 @@
           <cell r="A306" t="str">
             <v>S-2026-04-06</v>
           </cell>
-          <cell r="B306"/>
           <cell r="C306" t="str">
             <v>RPRO-260403-0490</v>
           </cell>
@@ -25330,7 +25006,6 @@
           <cell r="A307" t="str">
             <v>S-2026-04-07</v>
           </cell>
-          <cell r="B307"/>
           <cell r="C307" t="str">
             <v>RPRO-260403-0491</v>
           </cell>
@@ -25399,7 +25074,6 @@
           <cell r="A308" t="str">
             <v>S-2026-04-08</v>
           </cell>
-          <cell r="B308"/>
           <cell r="C308" t="str">
             <v>RPRO-260403-0492</v>
           </cell>
@@ -25468,7 +25142,6 @@
           <cell r="A309" t="str">
             <v>S-2026-04-09</v>
           </cell>
-          <cell r="B309"/>
           <cell r="C309" t="str">
             <v>RPRO-260406-1201</v>
           </cell>
@@ -25537,7 +25210,6 @@
           <cell r="A310" t="str">
             <v>S-2026-04-10</v>
           </cell>
-          <cell r="B310"/>
           <cell r="C310" t="str">
             <v>RPRO-260406-1202</v>
           </cell>
@@ -25606,7 +25278,6 @@
           <cell r="A311" t="str">
             <v>S-2026-04-11</v>
           </cell>
-          <cell r="B311"/>
           <cell r="C311" t="str">
             <v>RPRO-260406-1203</v>
           </cell>
@@ -25675,7 +25346,6 @@
           <cell r="A312" t="str">
             <v>S-2026-04-12</v>
           </cell>
-          <cell r="B312"/>
           <cell r="C312" t="str">
             <v>RPRO-260407-0417</v>
           </cell>
@@ -25744,7 +25414,6 @@
           <cell r="A313" t="str">
             <v>S-2026-04-13</v>
           </cell>
-          <cell r="B313"/>
           <cell r="C313" t="str">
             <v>RPRO-260407-0418</v>
           </cell>
@@ -25813,7 +25482,6 @@
           <cell r="A314" t="str">
             <v>S-2026-04-14</v>
           </cell>
-          <cell r="B314"/>
           <cell r="C314" t="str">
             <v>RPRO-260407-0419</v>
           </cell>
@@ -25882,7 +25550,6 @@
           <cell r="A315" t="str">
             <v>S-2026-04-15</v>
           </cell>
-          <cell r="B315"/>
           <cell r="C315" t="str">
             <v>RPRO-260407-0420</v>
           </cell>
@@ -25951,7 +25618,6 @@
           <cell r="A316" t="str">
             <v>S-2026-04-16</v>
           </cell>
-          <cell r="B316"/>
           <cell r="C316" t="str">
             <v>RPRO-260409-0346</v>
           </cell>
@@ -26020,7 +25686,6 @@
           <cell r="A317" t="str">
             <v>S-2026-04-17</v>
           </cell>
-          <cell r="B317"/>
           <cell r="C317" t="str">
             <v>RPRO-260409-0347</v>
           </cell>
@@ -26089,7 +25754,6 @@
           <cell r="A318" t="str">
             <v>S-2026-04-18</v>
           </cell>
-          <cell r="B318"/>
           <cell r="C318" t="str">
             <v>RPRO-260409-0348</v>
           </cell>
@@ -26158,7 +25822,6 @@
           <cell r="A319" t="str">
             <v>S-2026-04-19</v>
           </cell>
-          <cell r="B319"/>
           <cell r="C319" t="str">
             <v>RPRO-260409-0349</v>
           </cell>
@@ -26227,7 +25890,6 @@
           <cell r="A320" t="str">
             <v>S-2026-04-20</v>
           </cell>
-          <cell r="B320"/>
           <cell r="C320" t="str">
             <v>RPRO-260409-0350</v>
           </cell>
@@ -26296,7 +25958,6 @@
           <cell r="A321" t="str">
             <v>L-2026-04-21</v>
           </cell>
-          <cell r="B321"/>
           <cell r="C321" t="str">
             <v>RPRO-260410-0280</v>
           </cell>
@@ -26330,7 +25991,6 @@
           <cell r="M321" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N321"/>
           <cell r="O321" t="str">
             <v>Lab test</v>
           </cell>
@@ -26363,7 +26023,6 @@
           <cell r="A322" t="str">
             <v>L-2026-04-22</v>
           </cell>
-          <cell r="B322"/>
           <cell r="C322" t="str">
             <v>RPRO-260410-0281</v>
           </cell>
@@ -26397,7 +26056,6 @@
           <cell r="M322" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N322"/>
           <cell r="O322" t="str">
             <v>Lab test</v>
           </cell>
@@ -26430,7 +26088,6 @@
           <cell r="A323" t="str">
             <v>S-2026-04-23</v>
           </cell>
-          <cell r="B323"/>
           <cell r="C323" t="str">
             <v>RPRO-260410-0282</v>
           </cell>
@@ -26499,7 +26156,6 @@
           <cell r="A324" t="str">
             <v>S-2026-04-24</v>
           </cell>
-          <cell r="B324"/>
           <cell r="C324" t="str">
             <v>RPRO-260410-0283</v>
           </cell>
@@ -26568,7 +26224,6 @@
           <cell r="A325" t="str">
             <v>S-2026-04-25</v>
           </cell>
-          <cell r="B325"/>
           <cell r="C325" t="str">
             <v>RPRO-260410-0284</v>
           </cell>
@@ -26637,7 +26292,6 @@
           <cell r="A326" t="str">
             <v>S-2026-04-26</v>
           </cell>
-          <cell r="B326"/>
           <cell r="C326" t="str">
             <v>RPRO-260410-0285</v>
           </cell>
@@ -26706,7 +26360,6 @@
           <cell r="A327" t="str">
             <v>S-2026-04-27</v>
           </cell>
-          <cell r="B327"/>
           <cell r="C327" t="str">
             <v>RPRO-260410-0286</v>
           </cell>
@@ -26775,7 +26428,6 @@
           <cell r="A328" t="str">
             <v>S-2026-04-28</v>
           </cell>
-          <cell r="B328"/>
           <cell r="C328" t="str">
             <v>RPRO-260410-0287</v>
           </cell>
@@ -26915,7 +26567,6 @@
           <cell r="A330" t="str">
             <v>S-2026-04-30</v>
           </cell>
-          <cell r="B330"/>
           <cell r="C330" t="str">
             <v>RPRO-260414-0202</v>
           </cell>
@@ -26984,7 +26635,6 @@
           <cell r="A331" t="str">
             <v>S-2026-04-31</v>
           </cell>
-          <cell r="B331"/>
           <cell r="C331" t="str">
             <v>RPRO-260414-0203</v>
           </cell>
@@ -27053,7 +26703,6 @@
           <cell r="A332" t="str">
             <v>S-2026-04-32</v>
           </cell>
-          <cell r="B332"/>
           <cell r="C332" t="str">
             <v>RPRO-260414-0204</v>
           </cell>
@@ -27122,7 +26771,6 @@
           <cell r="A333" t="str">
             <v>S-2026-04-33</v>
           </cell>
-          <cell r="B333"/>
           <cell r="C333" t="str">
             <v>RPRO-260414-0205</v>
           </cell>
@@ -27191,7 +26839,6 @@
           <cell r="A334" t="str">
             <v>S-2026-04-34</v>
           </cell>
-          <cell r="B334"/>
           <cell r="C334" t="str">
             <v>RPRO-260414-0206</v>
           </cell>
@@ -27260,7 +26907,6 @@
           <cell r="A335" t="str">
             <v>S-2026-04-35</v>
           </cell>
-          <cell r="B335"/>
           <cell r="C335" t="str">
             <v>RPRO-260414-0207</v>
           </cell>
@@ -27329,7 +26975,6 @@
           <cell r="A336" t="str">
             <v>S-2026-04-36</v>
           </cell>
-          <cell r="B336"/>
           <cell r="C336" t="str">
             <v>RPRO-260414-0208</v>
           </cell>
@@ -27398,7 +27043,6 @@
           <cell r="A337" t="str">
             <v>S-2026-04-37</v>
           </cell>
-          <cell r="B337"/>
           <cell r="C337" t="str">
             <v>RPRO-260414-0209</v>
           </cell>
@@ -27467,7 +27111,6 @@
           <cell r="A338" t="str">
             <v>S-2026-04-38</v>
           </cell>
-          <cell r="B338"/>
           <cell r="C338" t="str">
             <v>RPRO-260414-0210</v>
           </cell>
@@ -27536,7 +27179,6 @@
           <cell r="A339" t="str">
             <v>S-2026-04-39</v>
           </cell>
-          <cell r="B339"/>
           <cell r="C339" t="str">
             <v>RPRO-260414-0211</v>
           </cell>
@@ -27605,7 +27247,6 @@
           <cell r="A340" t="str">
             <v>S-2026-04-40</v>
           </cell>
-          <cell r="B340"/>
           <cell r="C340" t="str">
             <v>RPRO-260414-0212</v>
           </cell>
@@ -27710,7 +27351,6 @@
           <cell r="M341" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N341"/>
           <cell r="O341" t="str">
             <v>Lab test</v>
           </cell>
@@ -27779,7 +27419,6 @@
           <cell r="M342" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
-          <cell r="N342"/>
           <cell r="O342" t="str">
             <v>Lab test</v>
           </cell>
@@ -27812,7 +27451,6 @@
           <cell r="A343" t="str">
             <v>S-2026-04-43</v>
           </cell>
-          <cell r="B343"/>
           <cell r="C343" t="str">
             <v>RPRO-260417-0243</v>
           </cell>
@@ -27881,7 +27519,6 @@
           <cell r="A344" t="str">
             <v>S-2026-04-44</v>
           </cell>
-          <cell r="B344"/>
           <cell r="C344" t="str">
             <v>RPRO-260417-0244</v>
           </cell>
@@ -27950,7 +27587,6 @@
           <cell r="A345" t="str">
             <v>S-2026-04-45</v>
           </cell>
-          <cell r="B345"/>
           <cell r="C345" t="str">
             <v>RPRO-260417-0245</v>
           </cell>
@@ -28019,7 +27655,6 @@
           <cell r="A346" t="str">
             <v>S-2026-04-46</v>
           </cell>
-          <cell r="B346"/>
           <cell r="C346" t="str">
             <v>RPRO-260417-0246</v>
           </cell>
@@ -28088,7 +27723,6 @@
           <cell r="A347" t="str">
             <v>S-2026-04-47</v>
           </cell>
-          <cell r="B347"/>
           <cell r="C347" t="str">
             <v>RPRO-260417-0247</v>
           </cell>
@@ -28157,7 +27791,6 @@
           <cell r="A348" t="str">
             <v>S-2026-04-48</v>
           </cell>
-          <cell r="B348"/>
           <cell r="C348" t="str">
             <v>RPRO-260421-0623</v>
           </cell>
@@ -28226,7 +27859,6 @@
           <cell r="A349" t="str">
             <v>S-2026-04-49</v>
           </cell>
-          <cell r="B349"/>
           <cell r="C349" t="str">
             <v>RPRO-260421-0624</v>
           </cell>
@@ -28295,7 +27927,6 @@
           <cell r="A350" t="str">
             <v>S-2026-04-50</v>
           </cell>
-          <cell r="B350"/>
           <cell r="C350" t="str">
             <v>RPRO-260421-0625</v>
           </cell>
@@ -28364,7 +27995,6 @@
           <cell r="A351" t="str">
             <v>S-2026-04-51</v>
           </cell>
-          <cell r="B351"/>
           <cell r="C351" t="str">
             <v>RPRO-260421-0626</v>
           </cell>
@@ -28433,7 +28063,6 @@
           <cell r="A352" t="str">
             <v>S-2026-04-52</v>
           </cell>
-          <cell r="B352"/>
           <cell r="C352" t="str">
             <v>RPRO-260421-0627</v>
           </cell>
@@ -28502,7 +28131,6 @@
           <cell r="A353" t="str">
             <v>S-2026-04-53</v>
           </cell>
-          <cell r="B353"/>
           <cell r="C353" t="str">
             <v>RPRO-260421-0628</v>
           </cell>
@@ -28571,7 +28199,6 @@
           <cell r="A354" t="str">
             <v>S-2026-04-54</v>
           </cell>
-          <cell r="B354"/>
           <cell r="C354" t="str">
             <v>RPRO-260421-0629</v>
           </cell>
@@ -28640,7 +28267,6 @@
           <cell r="A355" t="str">
             <v>S-2026-04-55</v>
           </cell>
-          <cell r="B355"/>
           <cell r="C355" t="str">
             <v>RPRO-260421-0630</v>
           </cell>
@@ -28709,7 +28335,6 @@
           <cell r="A356" t="str">
             <v>S-2026-04-56</v>
           </cell>
-          <cell r="B356"/>
           <cell r="C356" t="str">
             <v>RPRO-260421-0631</v>
           </cell>
@@ -28778,7 +28403,6 @@
           <cell r="A357" t="str">
             <v>S-2026-04-57</v>
           </cell>
-          <cell r="B357"/>
           <cell r="C357" t="str">
             <v>RPRO-260421-0632</v>
           </cell>
@@ -28847,7 +28471,6 @@
           <cell r="A358" t="str">
             <v>S-2026-04-58</v>
           </cell>
-          <cell r="B358"/>
           <cell r="C358" t="str">
             <v>RPRO-260421-0633</v>
           </cell>
@@ -28916,7 +28539,6 @@
           <cell r="A359" t="str">
             <v>S-2026-04-59</v>
           </cell>
-          <cell r="B359"/>
           <cell r="C359" t="str">
             <v>RPRO-260422-0268</v>
           </cell>
@@ -28985,7 +28607,6 @@
           <cell r="A360" t="str">
             <v>S-2026-04-60</v>
           </cell>
-          <cell r="B360"/>
           <cell r="C360" t="str">
             <v>RPRO-260423-0486</v>
           </cell>
@@ -29054,7 +28675,6 @@
           <cell r="A361" t="str">
             <v>S-2026-04-61</v>
           </cell>
-          <cell r="B361"/>
           <cell r="C361" t="str">
             <v>RPRO-260423-0487</v>
           </cell>
@@ -29123,7 +28743,6 @@
           <cell r="A362" t="str">
             <v>S-2026-04-62</v>
           </cell>
-          <cell r="B362"/>
           <cell r="C362" t="str">
             <v>RPRO-260424-1197</v>
           </cell>
@@ -29192,7 +28811,6 @@
           <cell r="A363" t="str">
             <v>S-2026-04-63</v>
           </cell>
-          <cell r="B363"/>
           <cell r="C363" t="str">
             <v>RPRO-260424-1198</v>
           </cell>
@@ -29261,7 +28879,6 @@
           <cell r="A364" t="str">
             <v>S-2026-04-64</v>
           </cell>
-          <cell r="B364"/>
           <cell r="C364" t="str">
             <v>RPRO-260424-1199</v>
           </cell>
@@ -29330,7 +28947,6 @@
           <cell r="A365" t="str">
             <v>S-2026-04-65</v>
           </cell>
-          <cell r="B365"/>
           <cell r="C365" t="str">
             <v>RPRO-260424-1200</v>
           </cell>
@@ -29399,7 +29015,6 @@
           <cell r="A366" t="str">
             <v>S-2026-04-66</v>
           </cell>
-          <cell r="B366"/>
           <cell r="C366" t="str">
             <v>RPRO-260424-1201</v>
           </cell>
@@ -29539,7 +29154,6 @@
           <cell r="A368" t="str">
             <v>S-2026-04-68</v>
           </cell>
-          <cell r="B368"/>
           <cell r="C368" t="str">
             <v>RPRO-260424-1203</v>
           </cell>
@@ -29608,7 +29222,6 @@
           <cell r="A369" t="str">
             <v>S-2026-04-69</v>
           </cell>
-          <cell r="B369"/>
           <cell r="C369" t="str">
             <v>RPRO-260424-1204</v>
           </cell>
@@ -29677,7 +29290,6 @@
           <cell r="A370" t="str">
             <v>S-2026-04-70</v>
           </cell>
-          <cell r="B370"/>
           <cell r="C370" t="str">
             <v>RPRO-260424-1205</v>
           </cell>
@@ -29746,7 +29358,6 @@
           <cell r="A371" t="str">
             <v>S-2026-04-71</v>
           </cell>
-          <cell r="B371"/>
           <cell r="C371" t="str">
             <v>RPRO-260424-1206</v>
           </cell>
@@ -29815,7 +29426,6 @@
           <cell r="A372" t="str">
             <v>S-2026-04-72</v>
           </cell>
-          <cell r="B372"/>
           <cell r="C372" t="str">
             <v>RPRO-260428-0920</v>
           </cell>
@@ -29884,7 +29494,6 @@
           <cell r="A373" t="str">
             <v>S-2026-04-73</v>
           </cell>
-          <cell r="B373"/>
           <cell r="C373" t="str">
             <v>RPRO-260429-0109</v>
           </cell>
@@ -29953,7 +29562,6 @@
           <cell r="A374" t="str">
             <v>S-2026-04-74</v>
           </cell>
-          <cell r="B374"/>
           <cell r="C374" t="str">
             <v>RPRO-260429-0110</v>
           </cell>
@@ -30022,7 +29630,6 @@
           <cell r="A375" t="str">
             <v>S-2026-04-75</v>
           </cell>
-          <cell r="B375"/>
           <cell r="C375" t="str">
             <v>RPRO-260429-0126</v>
           </cell>
@@ -30091,7 +29698,6 @@
           <cell r="A376" t="str">
             <v>S-2026-04-76</v>
           </cell>
-          <cell r="B376"/>
           <cell r="C376" t="str">
             <v>RPRO-260429-0127</v>
           </cell>
@@ -30160,7 +29766,6 @@
           <cell r="A377" t="str">
             <v>S-2026-05-01</v>
           </cell>
-          <cell r="B377"/>
           <cell r="C377" t="str">
             <v>RPRO-260505-0654</v>
           </cell>
@@ -30300,7 +29905,6 @@
           <cell r="A379" t="str">
             <v>S-2026-05-03</v>
           </cell>
-          <cell r="B379"/>
           <cell r="C379" t="str">
             <v>RPRO-260505-0656</v>
           </cell>
@@ -30369,7 +29973,6 @@
           <cell r="A380" t="str">
             <v>S-2026-05-04</v>
           </cell>
-          <cell r="B380"/>
           <cell r="C380" t="str">
             <v>RPRO-260505-0657</v>
           </cell>
@@ -30438,7 +30041,6 @@
           <cell r="A381" t="str">
             <v>S-2026-05-05</v>
           </cell>
-          <cell r="B381"/>
           <cell r="C381" t="str">
             <v>RPRO-260505-0658</v>
           </cell>
@@ -30507,7 +30109,6 @@
           <cell r="A382" t="str">
             <v>S-2026-05-06</v>
           </cell>
-          <cell r="B382"/>
           <cell r="C382" t="str">
             <v>RPRO-260505-0659</v>
           </cell>
@@ -30576,7 +30177,6 @@
           <cell r="A383" t="str">
             <v>S-2026-05-07</v>
           </cell>
-          <cell r="B383"/>
           <cell r="C383" t="str">
             <v>RPRO-260505-0660</v>
           </cell>
@@ -30716,7 +30316,6 @@
           <cell r="A385" t="str">
             <v>S-2026-05-09</v>
           </cell>
-          <cell r="B385"/>
           <cell r="C385" t="str">
             <v>RPRO-260505-0662</v>
           </cell>
@@ -30785,7 +30384,6 @@
           <cell r="A386" t="str">
             <v>S-2026-05-10</v>
           </cell>
-          <cell r="B386"/>
           <cell r="C386" t="str">
             <v>RPRO-260505-0663</v>
           </cell>
@@ -30925,7 +30523,6 @@
           <cell r="A388" t="str">
             <v>S-2026-05-12</v>
           </cell>
-          <cell r="B388"/>
           <cell r="C388" t="str">
             <v>RPRO-260505-0802</v>
           </cell>
@@ -30994,7 +30591,6 @@
           <cell r="A389" t="str">
             <v>S-2026-05-13</v>
           </cell>
-          <cell r="B389"/>
           <cell r="C389" t="str">
             <v>RPRO-260505-0803</v>
           </cell>
@@ -31063,7 +30659,6 @@
           <cell r="A390" t="str">
             <v>S-2026-05-14</v>
           </cell>
-          <cell r="B390"/>
           <cell r="C390" t="str">
             <v>RPRO-260506-0394</v>
           </cell>
@@ -31132,7 +30727,6 @@
           <cell r="A391" t="str">
             <v>S-2026-05-15</v>
           </cell>
-          <cell r="B391"/>
           <cell r="C391" t="str">
             <v>RPRO-260506-0395</v>
           </cell>
@@ -31201,7 +30795,6 @@
           <cell r="A392" t="str">
             <v>S-2026-05-16</v>
           </cell>
-          <cell r="B392"/>
           <cell r="C392" t="str">
             <v>RPRO-260506-0396</v>
           </cell>
@@ -31270,7 +30863,6 @@
           <cell r="A393" t="str">
             <v>S-2026-05-17</v>
           </cell>
-          <cell r="B393"/>
           <cell r="C393" t="str">
             <v>RPRO-260506-0397</v>
           </cell>
@@ -31339,7 +30931,6 @@
           <cell r="A394" t="str">
             <v>S-2026-05-18</v>
           </cell>
-          <cell r="B394"/>
           <cell r="C394" t="str">
             <v>RPRO-260506-0415</v>
           </cell>
@@ -31408,7 +30999,6 @@
           <cell r="A395" t="str">
             <v>S-2026-05-19</v>
           </cell>
-          <cell r="B395"/>
           <cell r="C395" t="str">
             <v>RPRO-260508-0581</v>
           </cell>
@@ -31477,7 +31067,6 @@
           <cell r="A396" t="str">
             <v>S-2026-05-20</v>
           </cell>
-          <cell r="B396"/>
           <cell r="C396" t="str">
             <v>RPRO-260508-0582</v>
           </cell>
@@ -31546,7 +31135,6 @@
           <cell r="A397" t="str">
             <v>S-2026-05-21</v>
           </cell>
-          <cell r="B397"/>
           <cell r="C397" t="str">
             <v>RPRO-260508-0583</v>
           </cell>
@@ -31615,7 +31203,6 @@
           <cell r="A398" t="str">
             <v>S-2026-05-22</v>
           </cell>
-          <cell r="B398"/>
           <cell r="C398" t="str">
             <v>RPRO-260508-0584</v>
           </cell>
@@ -31684,7 +31271,6 @@
           <cell r="A399" t="str">
             <v>S-2026-05-23</v>
           </cell>
-          <cell r="B399"/>
           <cell r="C399" t="str">
             <v>RPRO-260508-0585</v>
           </cell>
@@ -31753,7 +31339,6 @@
           <cell r="A400" t="str">
             <v>S-2026-05-24</v>
           </cell>
-          <cell r="B400"/>
           <cell r="C400" t="str">
             <v>RPRO-260508-0586</v>
           </cell>
@@ -31822,7 +31407,6 @@
           <cell r="A401" t="str">
             <v>S-2026-05-25</v>
           </cell>
-          <cell r="B401"/>
           <cell r="C401" t="str">
             <v>RPRO-260508-0587</v>
           </cell>
@@ -31891,7 +31475,6 @@
           <cell r="A402" t="str">
             <v>S-2026-05-26</v>
           </cell>
-          <cell r="B402"/>
           <cell r="C402" t="str">
             <v>RPRO-260508-0588</v>
           </cell>
@@ -31960,7 +31543,6 @@
           <cell r="A403" t="str">
             <v>S-2026-05-27</v>
           </cell>
-          <cell r="B403"/>
           <cell r="C403" t="str">
             <v>RPRO-260512-0580</v>
           </cell>
@@ -31991,7 +31573,6 @@
           <cell r="L403" t="str">
             <v>TBS</v>
           </cell>
-          <cell r="M403"/>
           <cell r="N403" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -32027,7 +31608,6 @@
           <cell r="A404" t="str">
             <v>S-2026-05-28</v>
           </cell>
-          <cell r="B404"/>
           <cell r="C404" t="str">
             <v>RPRO-260512-0581</v>
           </cell>
@@ -32058,7 +31638,6 @@
           <cell r="L404" t="str">
             <v>TBS</v>
           </cell>
-          <cell r="M404"/>
           <cell r="N404" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -32094,7 +31673,6 @@
           <cell r="A405" t="str">
             <v>S-2026-05-29</v>
           </cell>
-          <cell r="B405"/>
           <cell r="C405" t="str">
             <v>RPRO-260512-0582</v>
           </cell>
@@ -32163,7 +31741,6 @@
           <cell r="A406" t="str">
             <v>S-2026-05-30</v>
           </cell>
-          <cell r="B406"/>
           <cell r="C406" t="str">
             <v>RPRO-260512-0583</v>
           </cell>
@@ -32232,7 +31809,6 @@
           <cell r="A407" t="str">
             <v>S-2026-05-31</v>
           </cell>
-          <cell r="B407"/>
           <cell r="C407" t="str">
             <v>RPRO-260513-0945</v>
           </cell>
@@ -32301,7 +31877,6 @@
           <cell r="A408" t="str">
             <v>S-2026-05-32</v>
           </cell>
-          <cell r="B408"/>
           <cell r="C408" t="str">
             <v>RPRO-260513-0946</v>
           </cell>
@@ -32370,7 +31945,6 @@
           <cell r="A409" t="str">
             <v>S-2026-05-33</v>
           </cell>
-          <cell r="B409"/>
           <cell r="C409" t="str">
             <v>RPRO-260513-0947</v>
           </cell>
@@ -32439,7 +32013,6 @@
           <cell r="A410" t="str">
             <v>S-2026-05-34</v>
           </cell>
-          <cell r="B410"/>
           <cell r="C410" t="str">
             <v>RPRO-260513-0948</v>
           </cell>
@@ -32579,7 +32152,6 @@
           <cell r="A412" t="str">
             <v>S-2026-05-36</v>
           </cell>
-          <cell r="B412"/>
           <cell r="C412" t="str">
             <v>RPRO-260513-0950</v>
           </cell>
@@ -32648,7 +32220,6 @@
           <cell r="A413" t="str">
             <v>S-2026-05-37</v>
           </cell>
-          <cell r="B413"/>
           <cell r="C413" t="str">
             <v>RPRO-260515-0272</v>
           </cell>
@@ -32717,7 +32288,6 @@
           <cell r="A414" t="str">
             <v>S-2026-05-38</v>
           </cell>
-          <cell r="B414"/>
           <cell r="C414" t="str">
             <v>RPRO-260515-0273</v>
           </cell>
@@ -32786,7 +32356,6 @@
           <cell r="A415" t="str">
             <v>S-2026-05-39</v>
           </cell>
-          <cell r="B415"/>
           <cell r="C415" t="str">
             <v>RPRO-260515-0274</v>
           </cell>
@@ -32855,7 +32424,6 @@
           <cell r="A416" t="str">
             <v>S-2026-05-40</v>
           </cell>
-          <cell r="B416"/>
           <cell r="C416" t="str">
             <v>RPRO-260515-0275</v>
           </cell>
@@ -32924,7 +32492,6 @@
           <cell r="A417" t="str">
             <v>S-2026-05-41</v>
           </cell>
-          <cell r="B417"/>
           <cell r="C417" t="str">
             <v>RPRO-260515-0276</v>
           </cell>
@@ -32993,7 +32560,6 @@
           <cell r="A418" t="str">
             <v>S-2026-05-42</v>
           </cell>
-          <cell r="B418"/>
           <cell r="C418" t="str">
             <v>RPRO-260515-0277</v>
           </cell>
@@ -33062,7 +32628,6 @@
           <cell r="A419" t="str">
             <v>S-2026-05-43</v>
           </cell>
-          <cell r="B419"/>
           <cell r="C419" t="str">
             <v>RPRO-260515-0278</v>
           </cell>
@@ -33131,7 +32696,6 @@
           <cell r="A420" t="str">
             <v>S-2026-05-44</v>
           </cell>
-          <cell r="B420"/>
           <cell r="C420" t="str">
             <v>RPRO-260515-0279</v>
           </cell>
@@ -33200,7 +32764,6 @@
           <cell r="A421" t="str">
             <v>S-2026-05-45</v>
           </cell>
-          <cell r="B421"/>
           <cell r="C421" t="str">
             <v>RPRO-260515-0280</v>
           </cell>
@@ -33269,7 +32832,6 @@
           <cell r="A422" t="str">
             <v>S-2026-05-46</v>
           </cell>
-          <cell r="B422"/>
           <cell r="C422" t="str">
             <v>RPRO-260518-0853</v>
           </cell>
@@ -33338,7 +32900,6 @@
           <cell r="A423" t="str">
             <v>S-2026-05-47</v>
           </cell>
-          <cell r="B423"/>
           <cell r="C423" t="str">
             <v>RPRO-260518-0854</v>
           </cell>
@@ -33407,7 +32968,6 @@
           <cell r="A424" t="str">
             <v>S-2026-05-48</v>
           </cell>
-          <cell r="B424"/>
           <cell r="C424" t="str">
             <v>RPRO-260518-0855</v>
           </cell>
@@ -33476,7 +33036,6 @@
           <cell r="A425" t="str">
             <v>S-2026-05-49</v>
           </cell>
-          <cell r="B425"/>
           <cell r="C425" t="str">
             <v>RPRO-260518-0856</v>
           </cell>
@@ -33758,7 +33317,6 @@
           <cell r="A429" t="str">
             <v>S-2026-05-53</v>
           </cell>
-          <cell r="B429"/>
           <cell r="C429" t="str">
             <v>RPRO-260518-0860</v>
           </cell>
@@ -33827,7 +33385,6 @@
           <cell r="A430" t="str">
             <v>S-2026-05-54</v>
           </cell>
-          <cell r="B430"/>
           <cell r="C430" t="str">
             <v>RPRO-260518-0861</v>
           </cell>
@@ -33896,7 +33453,6 @@
           <cell r="A431" t="str">
             <v>S-2026-05-55</v>
           </cell>
-          <cell r="B431"/>
           <cell r="C431" t="str">
             <v>RPRO-260518-0862</v>
           </cell>
@@ -33965,7 +33521,6 @@
           <cell r="A432" t="str">
             <v>S-2026-05-56</v>
           </cell>
-          <cell r="B432"/>
           <cell r="C432" t="str">
             <v>RPRO-260518-0863</v>
           </cell>
@@ -34034,7 +33589,6 @@
           <cell r="A433" t="str">
             <v>S-2026-05-57</v>
           </cell>
-          <cell r="B433"/>
           <cell r="C433" t="str">
             <v>RPRO-260518-0864</v>
           </cell>
@@ -34103,7 +33657,6 @@
           <cell r="A434" t="str">
             <v>S-2026-05-58</v>
           </cell>
-          <cell r="B434"/>
           <cell r="C434" t="str">
             <v>RPRO-260518-0865</v>
           </cell>
@@ -34172,7 +33725,6 @@
           <cell r="A435" t="str">
             <v>S-2026-05-59</v>
           </cell>
-          <cell r="B435"/>
           <cell r="C435" t="str">
             <v>RPRO-260518-0866</v>
           </cell>
@@ -34241,7 +33793,6 @@
           <cell r="A436" t="str">
             <v>S-2026-05-60</v>
           </cell>
-          <cell r="B436"/>
           <cell r="C436" t="str">
             <v>RPRO-260520-0192</v>
           </cell>
@@ -34310,7 +33861,6 @@
           <cell r="A437" t="str">
             <v>S-2026-05-61</v>
           </cell>
-          <cell r="B437"/>
           <cell r="C437" t="str">
             <v>RPRO-260520-0193</v>
           </cell>
@@ -34379,7 +33929,6 @@
           <cell r="A438" t="str">
             <v>S-2026-05-62</v>
           </cell>
-          <cell r="B438"/>
           <cell r="C438" t="str">
             <v>RPRO-260520-0194</v>
           </cell>
@@ -34448,7 +33997,6 @@
           <cell r="A439" t="str">
             <v>S-2026-05-63</v>
           </cell>
-          <cell r="B439"/>
           <cell r="C439" t="str">
             <v>RPRO-260520-0195</v>
           </cell>
@@ -34517,7 +34065,6 @@
           <cell r="A440" t="str">
             <v>S-2026-05-64</v>
           </cell>
-          <cell r="B440"/>
           <cell r="C440" t="str">
             <v>RPRO-260520-0196</v>
           </cell>
@@ -34586,7 +34133,6 @@
           <cell r="A441" t="str">
             <v>S-2026-05-65</v>
           </cell>
-          <cell r="B441"/>
           <cell r="C441" t="str">
             <v>RPRO-260520-0197</v>
           </cell>
@@ -34655,7 +34201,6 @@
           <cell r="A442" t="str">
             <v>S-2026-05-66</v>
           </cell>
-          <cell r="B442"/>
           <cell r="C442" t="str">
             <v>RPRO-260520-0225</v>
           </cell>
@@ -34724,7 +34269,6 @@
           <cell r="A443" t="str">
             <v>S-2026-05-67</v>
           </cell>
-          <cell r="B443"/>
           <cell r="C443" t="str">
             <v>RPRO-260520-0226</v>
           </cell>
@@ -34793,7 +34337,6 @@
           <cell r="A444" t="str">
             <v>S-2026-05-68</v>
           </cell>
-          <cell r="B444"/>
           <cell r="C444" t="str">
             <v>RPRO-260520-0227</v>
           </cell>
@@ -34862,7 +34405,6 @@
           <cell r="A445" t="str">
             <v>S-2026-05-69</v>
           </cell>
-          <cell r="B445"/>
           <cell r="C445" t="str">
             <v>RPRO-260520-0228</v>
           </cell>
@@ -34931,7 +34473,6 @@
           <cell r="A446" t="str">
             <v>S-2026-05-70</v>
           </cell>
-          <cell r="B446"/>
           <cell r="C446" t="str">
             <v>RPRO-260520-0229</v>
           </cell>
@@ -35000,7 +34541,6 @@
           <cell r="A447" t="str">
             <v>S-2026-05-71</v>
           </cell>
-          <cell r="B447"/>
           <cell r="C447" t="str">
             <v>RPRO-260521-0669</v>
           </cell>
@@ -35069,7 +34609,6 @@
           <cell r="A448" t="str">
             <v>S-2026-05-72</v>
           </cell>
-          <cell r="B448"/>
           <cell r="C448" t="str">
             <v>RPRO-260521-0670</v>
           </cell>
@@ -35138,7 +34677,6 @@
           <cell r="A449" t="str">
             <v>S-2026-05-73</v>
           </cell>
-          <cell r="B449"/>
           <cell r="C449" t="str">
             <v>RPRO-260523-0221</v>
           </cell>
@@ -35207,7 +34745,6 @@
           <cell r="A450" t="str">
             <v>S-2026-05-74</v>
           </cell>
-          <cell r="B450"/>
           <cell r="C450" t="str">
             <v>RPRO-260523-0222</v>
           </cell>
@@ -35276,7 +34813,6 @@
           <cell r="A451" t="str">
             <v>S-2026-05-75</v>
           </cell>
-          <cell r="B451"/>
           <cell r="C451" t="str">
             <v>RPRO-260523-0223</v>
           </cell>
@@ -35345,7 +34881,6 @@
           <cell r="A452" t="str">
             <v>S-2026-05-76</v>
           </cell>
-          <cell r="B452"/>
           <cell r="C452" t="str">
             <v>RPRO-260526-0394</v>
           </cell>
@@ -35414,7 +34949,6 @@
           <cell r="A453" t="str">
             <v>S-2026-05-77</v>
           </cell>
-          <cell r="B453"/>
           <cell r="C453" t="str">
             <v>RPRO-260526-0395</v>
           </cell>
@@ -35483,7 +35017,6 @@
           <cell r="A454" t="str">
             <v>S-2026-05-78</v>
           </cell>
-          <cell r="B454"/>
           <cell r="C454" t="str">
             <v>RPRO-260526-0396</v>
           </cell>
@@ -35552,7 +35085,6 @@
           <cell r="A455" t="str">
             <v>S-2026-05-79</v>
           </cell>
-          <cell r="B455"/>
           <cell r="C455" t="str">
             <v>RPRO-260526-0397</v>
           </cell>
@@ -35621,7 +35153,6 @@
           <cell r="A456" t="str">
             <v>S-2026-05-80</v>
           </cell>
-          <cell r="B456"/>
           <cell r="C456" t="str">
             <v>RPRO-260526-0398</v>
           </cell>
@@ -35690,7 +35221,6 @@
           <cell r="A457" t="str">
             <v>S-2026-05-81</v>
           </cell>
-          <cell r="B457"/>
           <cell r="C457" t="str">
             <v>RPRO-260526-0399</v>
           </cell>
@@ -35830,7 +35360,6 @@
           <cell r="A459" t="str">
             <v>S-2026-05-83</v>
           </cell>
-          <cell r="B459"/>
           <cell r="C459" t="str">
             <v>RPRO-260526-0401</v>
           </cell>
@@ -35970,7 +35499,6 @@
           <cell r="A461" t="str">
             <v>S-2026-05-85</v>
           </cell>
-          <cell r="B461"/>
           <cell r="C461" t="str">
             <v>RPRO-260526-0402</v>
           </cell>
@@ -36039,7 +35567,6 @@
           <cell r="A462" t="str">
             <v>S-2026-05-86</v>
           </cell>
-          <cell r="B462"/>
           <cell r="C462" t="str">
             <v>RPRO-260527-0578</v>
           </cell>
@@ -36108,7 +35635,6 @@
           <cell r="A463" t="str">
             <v>S-2026-05-87</v>
           </cell>
-          <cell r="B463"/>
           <cell r="C463" t="str">
             <v>RPRO-260527-0579</v>
           </cell>
@@ -36177,7 +35703,6 @@
           <cell r="A464" t="str">
             <v>S-2026-05-88</v>
           </cell>
-          <cell r="B464"/>
           <cell r="C464" t="str">
             <v>RPRO-260527-0580</v>
           </cell>
@@ -36246,7 +35771,6 @@
           <cell r="A465" t="str">
             <v>S-2026-05-89</v>
           </cell>
-          <cell r="B465"/>
           <cell r="C465" t="str">
             <v>RPRO-260527-0581</v>
           </cell>
@@ -36315,7 +35839,6 @@
           <cell r="A466" t="str">
             <v>S-2026-05-90</v>
           </cell>
-          <cell r="B466"/>
           <cell r="C466" t="str">
             <v>RPRO-260527-0582</v>
           </cell>
@@ -36384,7 +35907,6 @@
           <cell r="A467" t="str">
             <v>S-2026-05-91</v>
           </cell>
-          <cell r="B467"/>
           <cell r="C467" t="str">
             <v>RPRO-260527-0583</v>
           </cell>
@@ -36453,7 +35975,6 @@
           <cell r="A468" t="str">
             <v>S-2026-05-92</v>
           </cell>
-          <cell r="B468"/>
           <cell r="C468" t="str">
             <v>RPRO-260528-0001</v>
           </cell>
@@ -36522,7 +36043,6 @@
           <cell r="A469" t="str">
             <v>S-2026-05-93</v>
           </cell>
-          <cell r="B469"/>
           <cell r="C469" t="str">
             <v>RPRO-260529-0339</v>
           </cell>
@@ -36591,7 +36111,6 @@
           <cell r="A470" t="str">
             <v>S-2026-05-94</v>
           </cell>
-          <cell r="B470"/>
           <cell r="C470" t="str">
             <v>RPRO-260529-0340</v>
           </cell>
@@ -36731,7 +36250,6 @@
           <cell r="A472" t="str">
             <v>S-2026-05-96</v>
           </cell>
-          <cell r="B472"/>
           <cell r="C472" t="str">
             <v>RPRO-260529-0342</v>
           </cell>
@@ -36800,7 +36318,6 @@
           <cell r="A473" t="str">
             <v>S-2026-05-97</v>
           </cell>
-          <cell r="B473"/>
           <cell r="C473" t="str">
             <v>RPRO-260529-0343</v>
           </cell>
@@ -37011,7 +36528,6 @@
           <cell r="A476" t="str">
             <v>S-2026-05-100</v>
           </cell>
-          <cell r="B476"/>
           <cell r="C476" t="str">
             <v>RPRO-260529-0346</v>
           </cell>
@@ -37080,7 +36596,6 @@
           <cell r="A477" t="str">
             <v>S-2026-05-102</v>
           </cell>
-          <cell r="B477"/>
           <cell r="C477" t="str">
             <v>RPRO-260601-0847</v>
           </cell>
@@ -37149,7 +36664,6 @@
           <cell r="A478" t="str">
             <v>S-2026-05-103</v>
           </cell>
-          <cell r="B478"/>
           <cell r="C478" t="str">
             <v>RPRO-260601-0848</v>
           </cell>
@@ -37218,7 +36732,6 @@
           <cell r="A479" t="str">
             <v>S-2026-05-104</v>
           </cell>
-          <cell r="B479"/>
           <cell r="C479" t="str">
             <v>RPRO-260601-0849</v>
           </cell>
@@ -37287,7 +36800,6 @@
           <cell r="A480" t="str">
             <v>S-2026-05-105</v>
           </cell>
-          <cell r="B480"/>
           <cell r="C480" t="str">
             <v>RPRO-260601-0850</v>
           </cell>
@@ -37356,7 +36868,6 @@
           <cell r="A481" t="str">
             <v>S-2026-05-106</v>
           </cell>
-          <cell r="B481"/>
           <cell r="C481" t="str">
             <v>RPRO-260601-0851</v>
           </cell>
@@ -37425,7 +36936,6 @@
           <cell r="A482" t="str">
             <v>S-2026-06-01</v>
           </cell>
-          <cell r="B482"/>
           <cell r="C482" t="str">
             <v>RPRO-260602-0720</v>
           </cell>
@@ -37495,7 +37005,6 @@
           <cell r="A483" t="str">
             <v>S-2026-06-02</v>
           </cell>
-          <cell r="B483"/>
           <cell r="C483" t="str">
             <v>RPRO-260602-0721</v>
           </cell>
@@ -37564,7 +37073,6 @@
           <cell r="A484" t="str">
             <v>S-2026-06-03</v>
           </cell>
-          <cell r="B484"/>
           <cell r="C484" t="str">
             <v>RPRO-260602-0722</v>
           </cell>
@@ -37633,7 +37141,6 @@
           <cell r="A485" t="str">
             <v>S-2026-06-04</v>
           </cell>
-          <cell r="B485"/>
           <cell r="C485" t="str">
             <v>RPRO-260602-0723</v>
           </cell>
@@ -37702,7 +37209,6 @@
           <cell r="A486" t="str">
             <v>S-2026-06-05</v>
           </cell>
-          <cell r="B486"/>
           <cell r="C486" t="str">
             <v>RPRO-260602-0724</v>
           </cell>
@@ -37771,7 +37277,6 @@
           <cell r="A487" t="str">
             <v>S-2026-06-06</v>
           </cell>
-          <cell r="B487"/>
           <cell r="C487" t="str">
             <v>RPRO-260602-0725</v>
           </cell>
@@ -37840,7 +37345,6 @@
           <cell r="A488" t="str">
             <v>S-2026-06-07</v>
           </cell>
-          <cell r="B488"/>
           <cell r="C488" t="str">
             <v>RPRO-260602-0726</v>
           </cell>
@@ -37909,7 +37413,6 @@
           <cell r="A489" t="str">
             <v>S-2026-06-08</v>
           </cell>
-          <cell r="B489"/>
           <cell r="C489" t="str">
             <v>RPRO-260602-0727</v>
           </cell>
@@ -38049,7 +37552,6 @@
           <cell r="A491" t="str">
             <v>S-2026-06-10</v>
           </cell>
-          <cell r="B491"/>
           <cell r="C491" t="str">
             <v>RPRO-260603-0482</v>
           </cell>
@@ -38118,7 +37620,6 @@
           <cell r="A492" t="str">
             <v>S-2026-06-11</v>
           </cell>
-          <cell r="B492"/>
           <cell r="C492" t="str">
             <v>RPRO-260603-0483</v>
           </cell>
@@ -38187,7 +37688,6 @@
           <cell r="A493" t="str">
             <v>S-2026-06-12</v>
           </cell>
-          <cell r="B493"/>
           <cell r="C493" t="str">
             <v>RPRO-260603-0484</v>
           </cell>
@@ -38327,7 +37827,6 @@
           <cell r="A495" t="str">
             <v>S-2026-06-15</v>
           </cell>
-          <cell r="B495"/>
           <cell r="C495" t="str">
             <v>RPRO-260604-0522</v>
           </cell>
@@ -38396,7 +37895,6 @@
           <cell r="A496" t="str">
             <v>L-2026-06-01</v>
           </cell>
-          <cell r="B496"/>
           <cell r="C496" t="str">
             <v>RPRO-260604-0523</v>
           </cell>
@@ -38427,8 +37925,6 @@
           <cell r="L496" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
-          <cell r="M496"/>
-          <cell r="N496"/>
           <cell r="O496" t="str">
             <v>Lab test</v>
           </cell>
@@ -38461,7 +37957,6 @@
           <cell r="A497" t="str">
             <v>L-2026-06-02</v>
           </cell>
-          <cell r="B497"/>
           <cell r="C497" t="str">
             <v>RPRO-260604-0524</v>
           </cell>
@@ -38492,8 +37987,6 @@
           <cell r="L497" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
-          <cell r="M497"/>
-          <cell r="N497"/>
           <cell r="O497" t="str">
             <v>Lab test</v>
           </cell>
@@ -38526,7 +38019,6 @@
           <cell r="A498" t="str">
             <v>L-2026-06-03</v>
           </cell>
-          <cell r="B498"/>
           <cell r="C498" t="str">
             <v>RPRO-260604-0525</v>
           </cell>
@@ -38557,8 +38049,6 @@
           <cell r="L498" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
-          <cell r="M498"/>
-          <cell r="N498"/>
           <cell r="O498" t="str">
             <v>Lab test</v>
           </cell>
@@ -38591,7 +38081,6 @@
           <cell r="A499" t="str">
             <v>L-2026-06-04</v>
           </cell>
-          <cell r="B499"/>
           <cell r="C499" t="str">
             <v>RPRO-260604-0526</v>
           </cell>
@@ -38622,8 +38111,6 @@
           <cell r="L499" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
-          <cell r="M499"/>
-          <cell r="N499"/>
           <cell r="O499" t="str">
             <v>Lab test</v>
           </cell>
@@ -38656,7 +38143,6 @@
           <cell r="A500" t="str">
             <v>L-2026-06-05</v>
           </cell>
-          <cell r="B500"/>
           <cell r="C500" t="str">
             <v>RPRO-260604-0527</v>
           </cell>
@@ -38687,8 +38173,6 @@
           <cell r="L500" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
-          <cell r="M500"/>
-          <cell r="N500"/>
           <cell r="O500" t="str">
             <v>Lab test</v>
           </cell>
@@ -38721,7 +38205,6 @@
           <cell r="A501" t="str">
             <v>L-2026-06-06</v>
           </cell>
-          <cell r="B501"/>
           <cell r="C501" t="str">
             <v>RPRO-260604-0528</v>
           </cell>
@@ -38752,8 +38235,6 @@
           <cell r="L501" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
-          <cell r="M501"/>
-          <cell r="N501"/>
           <cell r="O501" t="str">
             <v>Lab test</v>
           </cell>
@@ -38786,7 +38267,6 @@
           <cell r="A502" t="str">
             <v>L-2026-06-07</v>
           </cell>
-          <cell r="B502"/>
           <cell r="C502" t="str">
             <v>RPRO-260604-0529</v>
           </cell>
@@ -38817,8 +38297,6 @@
           <cell r="L502" t="str">
             <v>SHYANG HUNG TAH</v>
           </cell>
-          <cell r="M502"/>
-          <cell r="N502"/>
           <cell r="O502" t="str">
             <v>Lab test</v>
           </cell>
@@ -38851,7 +38329,6 @@
           <cell r="A503" t="str">
             <v>S-2026-06-16</v>
           </cell>
-          <cell r="B503"/>
           <cell r="C503" t="str">
             <v>RPRO-260605-0678</v>
           </cell>
@@ -38920,7 +38397,6 @@
           <cell r="A504" t="str">
             <v>S-2026-06-17</v>
           </cell>
-          <cell r="B504"/>
           <cell r="C504" t="str">
             <v>RPRO-260605-0679</v>
           </cell>
@@ -38989,7 +38465,6 @@
           <cell r="A505" t="str">
             <v>S-2026-06-18</v>
           </cell>
-          <cell r="B505"/>
           <cell r="C505" t="str">
             <v>RPRO-260605-0680</v>
           </cell>
@@ -39058,7 +38533,6 @@
           <cell r="A506" t="str">
             <v>S-2026-06-19</v>
           </cell>
-          <cell r="B506"/>
           <cell r="C506" t="str">
             <v>RPRO-260605-0681</v>
           </cell>
@@ -39127,7 +38601,6 @@
           <cell r="A507" t="str">
             <v>S-2026-06-20</v>
           </cell>
-          <cell r="B507"/>
           <cell r="C507" t="str">
             <v>RPRO-260605-0682</v>
           </cell>
@@ -39196,7 +38669,6 @@
           <cell r="A508" t="str">
             <v>S-2026-06-21</v>
           </cell>
-          <cell r="B508"/>
           <cell r="C508" t="str">
             <v>RPRO-260605-0683</v>
           </cell>
@@ -39265,7 +38737,6 @@
           <cell r="A509" t="str">
             <v>S-2026-06-22</v>
           </cell>
-          <cell r="B509"/>
           <cell r="C509" t="str">
             <v>RPRO-260605-0684</v>
           </cell>
@@ -39334,7 +38805,6 @@
           <cell r="A510" t="str">
             <v>S-2026-06-23</v>
           </cell>
-          <cell r="B510"/>
           <cell r="C510" t="str">
             <v>RPRO-260605-0685</v>
           </cell>
@@ -39403,7 +38873,6 @@
           <cell r="A511" t="str">
             <v>S-2026-06-24</v>
           </cell>
-          <cell r="B511"/>
           <cell r="C511" t="str">
             <v>RPRO-260605-0686</v>
           </cell>
@@ -39472,7 +38941,6 @@
           <cell r="A512" t="str">
             <v>S-2026-06-25</v>
           </cell>
-          <cell r="B512"/>
           <cell r="C512" t="str">
             <v>RPRO-260606-0217</v>
           </cell>
@@ -39541,7 +39009,6 @@
           <cell r="A513" t="str">
             <v>S-2026-06-26</v>
           </cell>
-          <cell r="B513"/>
           <cell r="C513" t="str">
             <v>RPRO-260608-1016</v>
           </cell>
@@ -39610,7 +39077,6 @@
           <cell r="A514" t="str">
             <v>S-2026-06-27</v>
           </cell>
-          <cell r="B514"/>
           <cell r="C514" t="str">
             <v>RPRO-260608-1017</v>
           </cell>
@@ -39679,7 +39145,6 @@
           <cell r="A515" t="str">
             <v>S-2026-06-28</v>
           </cell>
-          <cell r="B515"/>
           <cell r="C515" t="str">
             <v>RPRO-260608-1018</v>
           </cell>
@@ -39748,7 +39213,6 @@
           <cell r="A516" t="str">
             <v>S-2026-06-29</v>
           </cell>
-          <cell r="B516"/>
           <cell r="C516" t="str">
             <v>RPRO-260608-1019</v>
           </cell>
@@ -39817,7 +39281,6 @@
           <cell r="A517" t="str">
             <v>S-2026-06-30</v>
           </cell>
-          <cell r="B517"/>
           <cell r="C517" t="str">
             <v>RPRO-260608-1020</v>
           </cell>
@@ -39883,95 +39346,30 @@
           </cell>
         </row>
         <row r="518">
-          <cell r="A518"/>
-          <cell r="B518"/>
-          <cell r="C518"/>
-          <cell r="D518"/>
-          <cell r="E518" t="str">
-            <v/>
-          </cell>
-          <cell r="F518"/>
-          <cell r="G518"/>
-          <cell r="H518"/>
-          <cell r="I518"/>
+          <cell r="E518"/>
           <cell r="J518">
             <v>0</v>
           </cell>
           <cell r="K518">
             <v>0</v>
           </cell>
-          <cell r="L518"/>
-          <cell r="M518"/>
-          <cell r="N518"/>
-          <cell r="O518"/>
-          <cell r="P518"/>
-          <cell r="Q518"/>
-          <cell r="R518"/>
-          <cell r="S518"/>
-          <cell r="T518"/>
-          <cell r="U518"/>
-          <cell r="V518"/>
-          <cell r="W518"/>
         </row>
         <row r="519">
-          <cell r="A519"/>
-          <cell r="B519"/>
-          <cell r="C519"/>
-          <cell r="D519"/>
-          <cell r="E519" t="str">
-            <v/>
-          </cell>
-          <cell r="F519"/>
-          <cell r="G519"/>
-          <cell r="H519"/>
-          <cell r="I519"/>
+          <cell r="E519"/>
           <cell r="J519">
             <v>0</v>
           </cell>
           <cell r="K519">
             <v>0</v>
           </cell>
-          <cell r="L519"/>
-          <cell r="M519"/>
-          <cell r="N519"/>
-          <cell r="O519"/>
-          <cell r="P519"/>
-          <cell r="Q519"/>
-          <cell r="R519"/>
-          <cell r="S519"/>
-          <cell r="T519"/>
-          <cell r="U519"/>
-          <cell r="V519"/>
-          <cell r="W519"/>
         </row>
         <row r="520">
-          <cell r="A520"/>
-          <cell r="B520"/>
-          <cell r="C520"/>
-          <cell r="D520"/>
-          <cell r="E520"/>
-          <cell r="F520"/>
-          <cell r="G520"/>
-          <cell r="H520"/>
-          <cell r="I520"/>
           <cell r="J520">
             <v>0</v>
           </cell>
           <cell r="K520">
             <v>0</v>
           </cell>
-          <cell r="L520"/>
-          <cell r="M520"/>
-          <cell r="N520"/>
-          <cell r="O520"/>
-          <cell r="P520"/>
-          <cell r="Q520"/>
-          <cell r="R520"/>
-          <cell r="S520"/>
-          <cell r="T520"/>
-          <cell r="U520"/>
-          <cell r="V520"/>
-          <cell r="W520"/>
         </row>
       </sheetData>
       <sheetData sheetId="4"/>
@@ -40078,7 +39476,13 @@
       <sheetData sheetId="105"/>
       <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
-      <sheetData sheetId="108"/>
+      <sheetData sheetId="108">
+        <row r="1">
+          <cell r="F1" t="str">
+            <v>No_Item</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="109"/>
       <sheetData sheetId="110"/>
       <sheetData sheetId="111"/>
@@ -41950,7 +41354,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -43393,7 +42797,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -44835,7 +44239,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -46180,7 +45584,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -47706,7 +47110,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269212966</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -48998,7 +48402,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269212966</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -50396,7 +49800,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -51806,7 +51210,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -53274,7 +52678,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -54707,7 +54111,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -55999,7 +55403,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -57389,7 +56793,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -58805,7 +58209,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -60256,7 +59660,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.334269444444</v>
+        <v>46182.483680439815</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75102B01-28E5-4879-8A68-12ED4C094023}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B315981E-A25C-4A9B-9B20-C465E730CDAC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="10" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="14" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -28,10 +28,11 @@
     <sheet name="5.6" sheetId="13" r:id="rId13"/>
     <sheet name="6.6" sheetId="14" r:id="rId14"/>
     <sheet name="8.6" sheetId="15" r:id="rId15"/>
+    <sheet name="9.6" sheetId="16" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
@@ -49,6 +50,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'5.6'!$A$2:$N$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'6.6'!$A$2:$M$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'8.6'!$A$2:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'9.6'!$A$2:$N$24</definedName>
     <definedName name="AE" localSheetId="8">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -64,6 +66,7 @@
     <definedName name="AE" localSheetId="12">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="13">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="14">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="15">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'1.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
@@ -79,6 +82,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'5.6'!$A$1:$N$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'6.6'!$A$1:$M$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'8.6'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'9.6'!$A$1:$N$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'1.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
@@ -94,6 +98,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'5.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'6.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'8.6'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'9.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -109,6 +114,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -124,6 +130,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -139,6 +146,7 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -154,6 +162,7 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -169,6 +178,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -184,6 +194,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="8" hidden="1">'1.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
@@ -199,6 +210,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="12" hidden="1">'5.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="13" hidden="1">'6.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="14" hidden="1">'8.6'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="15" hidden="1">'9.6'!#REF!</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -214,6 +226,7 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -229,6 +242,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -244,6 +258,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -259,6 +274,7 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -274,6 +290,7 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -289,6 +306,7 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -304,6 +322,7 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -319,6 +338,7 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -334,6 +354,7 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
@@ -349,6 +370,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -364,6 +386,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
@@ -379,6 +402,7 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
@@ -394,6 +418,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="12" hidden="1">'5.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="13" hidden="1">'6.6'!$A$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
@@ -409,6 +434,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="12" hidden="1">'5.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="13" hidden="1">'6.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -431,7 +457,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="546">
   <si>
     <t>Release Date</t>
   </si>
@@ -2113,6 +2139,42 @@
   <si>
     <t>BLACKYAK</t>
   </si>
+  <si>
+    <t>S-2026-06-36</t>
+  </si>
+  <si>
+    <t>S-2026-06-31</t>
+  </si>
+  <si>
+    <t>S-2026-06-32</t>
+  </si>
+  <si>
+    <t>S-2026-06-38</t>
+  </si>
+  <si>
+    <t>S-2026-06-33</t>
+  </si>
+  <si>
+    <t>S-2026-06-34</t>
+  </si>
+  <si>
+    <t>S-2026-06-35</t>
+  </si>
+  <si>
+    <t>S-2026-06-37</t>
+  </si>
+  <si>
+    <t>S-2026-06-40</t>
+  </si>
+  <si>
+    <t>S-2026-06-39</t>
+  </si>
+  <si>
+    <t>S-2026-06-41</t>
+  </si>
+  <si>
+    <t>KIỂM TRA XEM CÒN TỒN KO</t>
+  </si>
 </sst>
 </file>
 
@@ -2729,7 +2791,97 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="122">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4036,12 +4188,14 @@
       <sheetName val="4.6"/>
       <sheetName val="6.6"/>
       <sheetName val="8.6"/>
-      <sheetName val="form 2 (22)"/>
+      <sheetName val="9.6"/>
+      <sheetName val="form 2 (23)"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
+      <sheetName val="form 2 (22)"/>
       <sheetName val="form 2 (21)"/>
       <sheetName val="form 2 (20)"/>
       <sheetName val="form 2 (18)"/>
@@ -4089,7 +4243,6 @@
       <sheetName val="22.5"/>
       <sheetName val="30.5"/>
       <sheetName val="3.6 (L)"/>
-      <sheetName val="9.6"/>
       <sheetName val="9.6 (L)"/>
       <sheetName val="10.6"/>
       <sheetName val="11.6"/>
@@ -4229,49 +4382,84 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
+          <cell r="A1"/>
+          <cell r="B1"/>
           <cell r="C1" t="str">
             <v>TẠM THỜI NGƯNG NHẬN LAZY</v>
           </cell>
+          <cell r="D1"/>
+          <cell r="E1"/>
+          <cell r="F1"/>
           <cell r="G1" t="str">
             <v>ASICS 12MM DÙNG BOM 132 (roundup(12/132),5)</v>
           </cell>
+          <cell r="H1"/>
+          <cell r="I1"/>
+          <cell r="J1"/>
+          <cell r="K1"/>
+          <cell r="L1"/>
+          <cell r="M1"/>
+          <cell r="N1"/>
+          <cell r="O1"/>
+          <cell r="P1"/>
+          <cell r="Q1"/>
+          <cell r="R1"/>
+          <cell r="S1"/>
+          <cell r="T1"/>
+          <cell r="U1"/>
+          <cell r="V1"/>
+          <cell r="W1"/>
         </row>
         <row r="2">
+          <cell r="A2"/>
+          <cell r="B2"/>
+          <cell r="C2"/>
+          <cell r="D2"/>
+          <cell r="E2"/>
+          <cell r="F2"/>
           <cell r="G2" t="str">
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>267</v>
+            <v>25869</v>
           </cell>
           <cell r="I2">
-            <v>267</v>
+            <v>25869</v>
           </cell>
           <cell r="J2">
-            <v>0</v>
+            <v>24163</v>
           </cell>
           <cell r="K2">
-            <v>267</v>
+            <v>1706</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
           </cell>
+          <cell r="M2"/>
+          <cell r="N2"/>
+          <cell r="O2"/>
+          <cell r="P2"/>
           <cell r="Q2" t="str">
             <v>ETD hệ thống+1ngay</v>
           </cell>
           <cell r="R2" t="e">
             <v>#VALUE!</v>
           </cell>
+          <cell r="S2"/>
+          <cell r="T2"/>
           <cell r="U2">
             <v>12</v>
           </cell>
+          <cell r="V2"/>
           <cell r="W2">
-            <v>10</v>
+            <v>1308</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>NO.Order</v>
           </cell>
+          <cell r="B3"/>
           <cell r="C3" t="str">
             <v>Firm plan
 (PU PVN)</v>
@@ -4356,6 +4544,7 @@
           <cell r="A4" t="str">
             <v>S-2026-01-01</v>
           </cell>
+          <cell r="B4"/>
           <cell r="C4" t="str">
             <v>RPRO-260105-0668</v>
           </cell>
@@ -4708,6 +4897,7 @@
           <cell r="A9" t="str">
             <v>S-2026-01-06</v>
           </cell>
+          <cell r="B9"/>
           <cell r="C9" t="str">
             <v>RPRO-260105-0673</v>
           </cell>
@@ -4776,6 +4966,7 @@
           <cell r="A10" t="str">
             <v>S-2026-01-07</v>
           </cell>
+          <cell r="B10"/>
           <cell r="C10" t="str">
             <v>RPRO-260105-0674</v>
           </cell>
@@ -4844,6 +5035,7 @@
           <cell r="A11" t="str">
             <v>S-2026-01-08</v>
           </cell>
+          <cell r="B11"/>
           <cell r="C11" t="str">
             <v>RPRO-260105-0675</v>
           </cell>
@@ -5054,6 +5246,7 @@
           <cell r="A14" t="str">
             <v>L-2026-01-11</v>
           </cell>
+          <cell r="B14"/>
           <cell r="C14" t="str">
             <v>RPRO-260105-0678</v>
           </cell>
@@ -5087,6 +5280,7 @@
           <cell r="M14" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N14"/>
           <cell r="O14" t="str">
             <v>Lab test</v>
           </cell>
@@ -5119,6 +5313,7 @@
           <cell r="A15" t="str">
             <v>L-2026-01-12</v>
           </cell>
+          <cell r="B15"/>
           <cell r="C15" t="str">
             <v>RPRO-260105-0679</v>
           </cell>
@@ -5152,6 +5347,7 @@
           <cell r="M15" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N15"/>
           <cell r="O15" t="str">
             <v>Lab test</v>
           </cell>
@@ -5184,6 +5380,7 @@
           <cell r="A16" t="str">
             <v>L-2026-01-13</v>
           </cell>
+          <cell r="B16"/>
           <cell r="C16" t="str">
             <v>RPRO-260105-0680</v>
           </cell>
@@ -5217,6 +5414,7 @@
           <cell r="M16" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N16"/>
           <cell r="O16" t="str">
             <v>Lab test</v>
           </cell>
@@ -5249,6 +5447,7 @@
           <cell r="A17" t="str">
             <v>L-2026-01-14</v>
           </cell>
+          <cell r="B17"/>
           <cell r="C17" t="str">
             <v>RPRO-260105-0681</v>
           </cell>
@@ -5282,6 +5481,7 @@
           <cell r="M17" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N17"/>
           <cell r="O17" t="str">
             <v>Lab test</v>
           </cell>
@@ -5350,6 +5550,7 @@
           <cell r="M18" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N18"/>
           <cell r="O18" t="str">
             <v>Lab test</v>
           </cell>
@@ -5418,6 +5619,7 @@
           <cell r="M19" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N19"/>
           <cell r="O19" t="str">
             <v>Lab test</v>
           </cell>
@@ -5805,6 +6007,7 @@
           <cell r="A25" t="str">
             <v>L-2026-01-22</v>
           </cell>
+          <cell r="B25"/>
           <cell r="C25" t="str">
             <v>RPRO-260109-0095</v>
           </cell>
@@ -5838,6 +6041,7 @@
           <cell r="M25" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N25"/>
           <cell r="O25" t="str">
             <v>Lab test</v>
           </cell>
@@ -5870,6 +6074,7 @@
           <cell r="A26" t="str">
             <v>S-2026-01-23</v>
           </cell>
+          <cell r="B26"/>
           <cell r="C26" t="str">
             <v>RPRO-260113-0624</v>
           </cell>
@@ -5938,6 +6143,7 @@
           <cell r="A27" t="str">
             <v>S-2026-01-24</v>
           </cell>
+          <cell r="B27"/>
           <cell r="C27" t="str">
             <v>RPRO-260113-0625</v>
           </cell>
@@ -6006,6 +6212,7 @@
           <cell r="A28" t="str">
             <v>S-2026-01-25</v>
           </cell>
+          <cell r="B28"/>
           <cell r="C28" t="str">
             <v>RPRO-260113-0626</v>
           </cell>
@@ -6074,6 +6281,7 @@
           <cell r="A29" t="str">
             <v>S-2026-01-26</v>
           </cell>
+          <cell r="B29"/>
           <cell r="C29" t="str">
             <v>RPRO-260113-0627</v>
           </cell>
@@ -6142,6 +6350,7 @@
           <cell r="A30" t="str">
             <v>S-2026-01-27</v>
           </cell>
+          <cell r="B30"/>
           <cell r="C30" t="str">
             <v>RPRO-260113-0628</v>
           </cell>
@@ -6210,6 +6419,7 @@
           <cell r="A31" t="str">
             <v>S-2026-01-28</v>
           </cell>
+          <cell r="B31"/>
           <cell r="C31" t="str">
             <v>RPRO-260113-0629</v>
           </cell>
@@ -6278,6 +6488,7 @@
           <cell r="A32" t="str">
             <v>S-2026-01-29</v>
           </cell>
+          <cell r="B32"/>
           <cell r="C32" t="str">
             <v>RPRO-260113-0630</v>
           </cell>
@@ -6346,6 +6557,7 @@
           <cell r="A33" t="str">
             <v>S-2026-01-30</v>
           </cell>
+          <cell r="B33"/>
           <cell r="C33" t="str">
             <v>RPRO-260115-0298</v>
           </cell>
@@ -6414,6 +6626,7 @@
           <cell r="A34" t="str">
             <v>S-2026-01-31</v>
           </cell>
+          <cell r="B34"/>
           <cell r="C34" t="str">
             <v>RPRO-260115-0299</v>
           </cell>
@@ -6482,6 +6695,7 @@
           <cell r="A35" t="str">
             <v>S-2026-01-32</v>
           </cell>
+          <cell r="B35"/>
           <cell r="C35" t="str">
             <v>RPRO-260115-0300</v>
           </cell>
@@ -6550,6 +6764,7 @@
           <cell r="A36" t="str">
             <v>S-2026-01-33</v>
           </cell>
+          <cell r="B36"/>
           <cell r="C36" t="str">
             <v>RPRO-260115-0301</v>
           </cell>
@@ -6618,6 +6833,7 @@
           <cell r="A37" t="str">
             <v>S-2026-01-34</v>
           </cell>
+          <cell r="B37"/>
           <cell r="C37" t="str">
             <v>RPRO-260115-0302</v>
           </cell>
@@ -6686,6 +6902,7 @@
           <cell r="A38" t="str">
             <v>S-2026-01-35</v>
           </cell>
+          <cell r="B38"/>
           <cell r="C38" t="str">
             <v>RPRO-260115-0303</v>
           </cell>
@@ -6754,6 +6971,7 @@
           <cell r="A39" t="str">
             <v>S-2026-01-36</v>
           </cell>
+          <cell r="B39"/>
           <cell r="C39" t="str">
             <v>RPRO-260115-0304</v>
           </cell>
@@ -6822,6 +7040,7 @@
           <cell r="A40" t="str">
             <v>S-2026-01-37</v>
           </cell>
+          <cell r="B40"/>
           <cell r="C40" t="str">
             <v>RPRO-260115-0305</v>
           </cell>
@@ -6890,6 +7109,7 @@
           <cell r="A41" t="str">
             <v>S-2026-01-38</v>
           </cell>
+          <cell r="B41"/>
           <cell r="C41" t="str">
             <v>RPRO-260115-0306</v>
           </cell>
@@ -6958,6 +7178,7 @@
           <cell r="A42" t="str">
             <v>S-2026-01-39</v>
           </cell>
+          <cell r="B42"/>
           <cell r="C42" t="str">
             <v>RPRO-260115-0307</v>
           </cell>
@@ -7026,6 +7247,7 @@
           <cell r="A43" t="str">
             <v>S-2026-01-40</v>
           </cell>
+          <cell r="B43"/>
           <cell r="C43" t="str">
             <v>RPRO-260115-0308</v>
           </cell>
@@ -7094,6 +7316,7 @@
           <cell r="A44" t="str">
             <v>S-2026-01-41</v>
           </cell>
+          <cell r="B44"/>
           <cell r="C44" t="str">
             <v>RPRO-260115-0309</v>
           </cell>
@@ -7162,6 +7385,7 @@
           <cell r="A45" t="str">
             <v>S-2026-01-42</v>
           </cell>
+          <cell r="B45"/>
           <cell r="C45" t="str">
             <v>RPRO-260109-0096</v>
           </cell>
@@ -7230,6 +7454,7 @@
           <cell r="A46" t="str">
             <v>S-2026-01-43</v>
           </cell>
+          <cell r="B46"/>
           <cell r="C46" t="str">
             <v>RPRO-260109-0097</v>
           </cell>
@@ -7298,6 +7523,7 @@
           <cell r="A47" t="str">
             <v>S-2026-01-44</v>
           </cell>
+          <cell r="B47"/>
           <cell r="C47" t="str">
             <v>RPRO-260109-0098</v>
           </cell>
@@ -7366,6 +7592,7 @@
           <cell r="A48" t="str">
             <v>S-2026-01-45</v>
           </cell>
+          <cell r="B48"/>
           <cell r="C48" t="str">
             <v>RPRO-260109-0099</v>
           </cell>
@@ -7434,6 +7661,7 @@
           <cell r="A49" t="str">
             <v>S-2026-01-46</v>
           </cell>
+          <cell r="B49"/>
           <cell r="C49" t="str">
             <v>RPRO-260120-0349</v>
           </cell>
@@ -7502,6 +7730,7 @@
           <cell r="A50" t="str">
             <v>S-2026-01-47</v>
           </cell>
+          <cell r="B50"/>
           <cell r="C50" t="str">
             <v>RPRO-260120-0350</v>
           </cell>
@@ -7570,6 +7799,7 @@
           <cell r="A51" t="str">
             <v>S-2026-01-48</v>
           </cell>
+          <cell r="B51"/>
           <cell r="C51" t="str">
             <v>RPRO-260120-0351</v>
           </cell>
@@ -7638,6 +7868,7 @@
           <cell r="A52" t="str">
             <v>S-2026-01-49</v>
           </cell>
+          <cell r="B52"/>
           <cell r="C52" t="str">
             <v>RPRO-260120-0352</v>
           </cell>
@@ -7706,6 +7937,7 @@
           <cell r="A53" t="str">
             <v>S-2026-01-50</v>
           </cell>
+          <cell r="B53"/>
           <cell r="C53" t="str">
             <v>RPRO-260120-0353</v>
           </cell>
@@ -7774,6 +8006,7 @@
           <cell r="A54" t="str">
             <v>S-2026-01-51</v>
           </cell>
+          <cell r="B54"/>
           <cell r="C54" t="str">
             <v>RPRO-260120-0354</v>
           </cell>
@@ -7842,6 +8075,7 @@
           <cell r="A55" t="str">
             <v>S-2026-01-52</v>
           </cell>
+          <cell r="B55"/>
           <cell r="C55" t="str">
             <v>RPRO-260113-0631</v>
           </cell>
@@ -7910,6 +8144,7 @@
           <cell r="A56" t="str">
             <v>S-2026-01-53</v>
           </cell>
+          <cell r="B56"/>
           <cell r="C56" t="str">
             <v>RPRO-260120-0355</v>
           </cell>
@@ -7978,6 +8213,7 @@
           <cell r="A57" t="str">
             <v>S-2026-01-54</v>
           </cell>
+          <cell r="B57"/>
           <cell r="C57" t="str">
             <v>RPRO-260120-0356</v>
           </cell>
@@ -8046,6 +8282,7 @@
           <cell r="A58" t="str">
             <v>S-2026-01-55</v>
           </cell>
+          <cell r="B58"/>
           <cell r="C58" t="str">
             <v>RPRO-260120-0357</v>
           </cell>
@@ -8114,6 +8351,7 @@
           <cell r="A59" t="str">
             <v>S-2026-01-56</v>
           </cell>
+          <cell r="B59"/>
           <cell r="C59" t="str">
             <v>RPRO-260120-0358</v>
           </cell>
@@ -8182,6 +8420,7 @@
           <cell r="A60" t="str">
             <v>S-2026-01-57</v>
           </cell>
+          <cell r="B60"/>
           <cell r="C60" t="str">
             <v>RPRO-260120-0359</v>
           </cell>
@@ -8250,6 +8489,7 @@
           <cell r="A61" t="str">
             <v>S-2026-01-58</v>
           </cell>
+          <cell r="B61"/>
           <cell r="C61" t="str">
             <v>RPRO-260120-0360</v>
           </cell>
@@ -8318,6 +8558,7 @@
           <cell r="A62" t="str">
             <v>S-2026-01-59</v>
           </cell>
+          <cell r="B62"/>
           <cell r="C62" t="str">
             <v>RPRO-260116-0276</v>
           </cell>
@@ -8386,6 +8627,7 @@
           <cell r="A63" t="str">
             <v>S-2026-01-60</v>
           </cell>
+          <cell r="B63"/>
           <cell r="C63" t="str">
             <v>RPRO-260115-0310</v>
           </cell>
@@ -8454,6 +8696,7 @@
           <cell r="A64" t="str">
             <v>S-2026-01-61</v>
           </cell>
+          <cell r="B64"/>
           <cell r="C64" t="str">
             <v>RPRO-260120-0361</v>
           </cell>
@@ -8593,6 +8836,7 @@
           <cell r="A66" t="str">
             <v>S-2026-01-63</v>
           </cell>
+          <cell r="B66"/>
           <cell r="C66" t="str">
             <v>RPRO-260122-1562</v>
           </cell>
@@ -8661,6 +8905,7 @@
           <cell r="A67" t="str">
             <v>S-2026-01-64</v>
           </cell>
+          <cell r="B67"/>
           <cell r="C67" t="str">
             <v>RPRO-260122-1563</v>
           </cell>
@@ -8729,6 +8974,7 @@
           <cell r="A68" t="str">
             <v>S-2026-01-65</v>
           </cell>
+          <cell r="B68"/>
           <cell r="C68" t="str">
             <v>RPRO-260122-1564</v>
           </cell>
@@ -8797,6 +9043,7 @@
           <cell r="A69" t="str">
             <v>S-2026-01-66</v>
           </cell>
+          <cell r="B69"/>
           <cell r="C69" t="str">
             <v>RPRO-260122-1565</v>
           </cell>
@@ -8865,6 +9112,7 @@
           <cell r="A70" t="str">
             <v>S-2026-01-67</v>
           </cell>
+          <cell r="B70"/>
           <cell r="C70" t="str">
             <v>RPRO-260122-1566</v>
           </cell>
@@ -8933,6 +9181,7 @@
           <cell r="A71" t="str">
             <v>S-2026-01-68</v>
           </cell>
+          <cell r="B71"/>
           <cell r="C71" t="str">
             <v>RPRO-260122-1567</v>
           </cell>
@@ -9001,6 +9250,7 @@
           <cell r="A72" t="str">
             <v>S-2026-01-69</v>
           </cell>
+          <cell r="B72"/>
           <cell r="C72" t="str">
             <v>RPRO-260122-1568</v>
           </cell>
@@ -9069,6 +9319,7 @@
           <cell r="A73" t="str">
             <v>S-2026-01-70</v>
           </cell>
+          <cell r="B73"/>
           <cell r="C73" t="str">
             <v>RPRO-260122-1569</v>
           </cell>
@@ -9137,6 +9388,7 @@
           <cell r="A74" t="str">
             <v>S-2026-01-71</v>
           </cell>
+          <cell r="B74"/>
           <cell r="C74" t="str">
             <v>RPRO-260122-1570</v>
           </cell>
@@ -9205,6 +9457,7 @@
           <cell r="A75" t="str">
             <v>S-2026-01-72</v>
           </cell>
+          <cell r="B75"/>
           <cell r="C75" t="str">
             <v>RPRO-260122-1571</v>
           </cell>
@@ -9486,6 +9739,7 @@
           <cell r="A79" t="str">
             <v>S-2026-01-76</v>
           </cell>
+          <cell r="B79"/>
           <cell r="C79" t="str">
             <v>RPRO-260122-1573</v>
           </cell>
@@ -9554,6 +9808,7 @@
           <cell r="A80" t="str">
             <v>S-2026-01-77</v>
           </cell>
+          <cell r="B80"/>
           <cell r="C80" t="str">
             <v>RPRO-260122-1574</v>
           </cell>
@@ -9622,6 +9877,7 @@
           <cell r="A81" t="str">
             <v>S-2026-01-78</v>
           </cell>
+          <cell r="B81"/>
           <cell r="C81" t="str">
             <v>RPRO-260122-1575</v>
           </cell>
@@ -9690,6 +9946,7 @@
           <cell r="A82" t="str">
             <v>S-2026-01-79</v>
           </cell>
+          <cell r="B82"/>
           <cell r="C82" t="str">
             <v>RPRO-260122-1576</v>
           </cell>
@@ -9758,6 +10015,7 @@
           <cell r="A83" t="str">
             <v>S-2026-01-80</v>
           </cell>
+          <cell r="B83"/>
           <cell r="C83" t="str">
             <v>RPRO-260122-1577</v>
           </cell>
@@ -9826,6 +10084,7 @@
           <cell r="A84" t="str">
             <v>S-2026-01-81</v>
           </cell>
+          <cell r="B84"/>
           <cell r="C84" t="str">
             <v>RPRO-260122-1578</v>
           </cell>
@@ -9894,6 +10153,7 @@
           <cell r="A85" t="str">
             <v>S-2026-01-82</v>
           </cell>
+          <cell r="B85"/>
           <cell r="C85" t="str">
             <v>RPRO-260122-1579</v>
           </cell>
@@ -9962,6 +10222,7 @@
           <cell r="A86" t="str">
             <v>S-2026-01-83</v>
           </cell>
+          <cell r="B86"/>
           <cell r="C86" t="str">
             <v>RPRO-260122-1580</v>
           </cell>
@@ -10033,6 +10294,7 @@
           <cell r="B87" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C87"/>
           <cell r="D87" t="str">
             <v>OV-0385</v>
           </cell>
@@ -10101,6 +10363,7 @@
           <cell r="B88" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C88"/>
           <cell r="D88" t="str">
             <v>OV-0385</v>
           </cell>
@@ -10169,6 +10432,7 @@
           <cell r="B89" t="str">
             <v>hủy</v>
           </cell>
+          <cell r="C89"/>
           <cell r="D89" t="str">
             <v>OV-0385</v>
           </cell>
@@ -10234,6 +10498,7 @@
           <cell r="A90" t="str">
             <v>S-2026-01-87</v>
           </cell>
+          <cell r="B90"/>
           <cell r="C90" t="str">
             <v>RPRO-260127-0875</v>
           </cell>
@@ -10302,6 +10567,7 @@
           <cell r="A91" t="str">
             <v>S-2026-01-88</v>
           </cell>
+          <cell r="B91"/>
           <cell r="C91" t="str">
             <v>RPRO-260127-0877</v>
           </cell>
@@ -10370,6 +10636,7 @@
           <cell r="A92" t="str">
             <v>S-2026-01-89</v>
           </cell>
+          <cell r="B92"/>
           <cell r="C92" t="str">
             <v>RPRO-260127-0879</v>
           </cell>
@@ -10438,6 +10705,7 @@
           <cell r="A93" t="str">
             <v>S-2026-01-90</v>
           </cell>
+          <cell r="B93"/>
           <cell r="C93" t="str">
             <v>RPRO-260128-1270</v>
           </cell>
@@ -10506,6 +10774,7 @@
           <cell r="A94" t="str">
             <v>S-2026-01-91</v>
           </cell>
+          <cell r="B94"/>
           <cell r="C94" t="str">
             <v>RPRO-260128-1271</v>
           </cell>
@@ -10574,6 +10843,7 @@
           <cell r="A95" t="str">
             <v>S-2026-01-92</v>
           </cell>
+          <cell r="B95"/>
           <cell r="C95" t="str">
             <v>RPRO-260128-1272</v>
           </cell>
@@ -10642,6 +10912,7 @@
           <cell r="A96" t="str">
             <v>S-2026-01-93</v>
           </cell>
+          <cell r="B96"/>
           <cell r="C96" t="str">
             <v>RPRO-260128-1273</v>
           </cell>
@@ -10710,6 +10981,7 @@
           <cell r="A97" t="str">
             <v>S-2026-01-94</v>
           </cell>
+          <cell r="B97"/>
           <cell r="C97" t="str">
             <v>RPRO-260128-1274</v>
           </cell>
@@ -10778,6 +11050,7 @@
           <cell r="A98" t="str">
             <v>S-2026-01-95</v>
           </cell>
+          <cell r="B98"/>
           <cell r="C98" t="str">
             <v>RPRO-260128-1275</v>
           </cell>
@@ -10846,6 +11119,7 @@
           <cell r="A99" t="str">
             <v>S-2026-01-96</v>
           </cell>
+          <cell r="B99"/>
           <cell r="C99" t="str">
             <v>RPRO-260128-1276</v>
           </cell>
@@ -10914,6 +11188,7 @@
           <cell r="A100" t="str">
             <v>S-2026-01-97</v>
           </cell>
+          <cell r="B100"/>
           <cell r="C100" t="str">
             <v>RPRO-260128-1277</v>
           </cell>
@@ -10982,6 +11257,7 @@
           <cell r="A101" t="str">
             <v>S-2026-01-98</v>
           </cell>
+          <cell r="B101"/>
           <cell r="C101" t="str">
             <v>RPRO-260129-0656</v>
           </cell>
@@ -11050,6 +11326,7 @@
           <cell r="A102" t="str">
             <v>S-2026-02-01</v>
           </cell>
+          <cell r="B102"/>
           <cell r="C102" t="str">
             <v>RPRO-260203-0021</v>
           </cell>
@@ -11118,6 +11395,7 @@
           <cell r="A103" t="str">
             <v>S-2026-02-02</v>
           </cell>
+          <cell r="B103"/>
           <cell r="C103" t="str">
             <v>RPRO-260203-0022</v>
           </cell>
@@ -11186,6 +11464,7 @@
           <cell r="A104" t="str">
             <v>S-2026-02-03</v>
           </cell>
+          <cell r="B104"/>
           <cell r="C104" t="str">
             <v>RPRO-260203-0770</v>
           </cell>
@@ -11254,6 +11533,7 @@
           <cell r="A105" t="str">
             <v>S-2026-02-04</v>
           </cell>
+          <cell r="B105"/>
           <cell r="C105" t="str">
             <v>RPRO-260203-0771</v>
           </cell>
@@ -11322,6 +11602,7 @@
           <cell r="A106" t="str">
             <v>S-2026-02-05</v>
           </cell>
+          <cell r="B106"/>
           <cell r="C106" t="str">
             <v>RPRO-260203-0772</v>
           </cell>
@@ -11390,6 +11671,7 @@
           <cell r="A107" t="str">
             <v>S-2026-02-06</v>
           </cell>
+          <cell r="B107"/>
           <cell r="C107" t="str">
             <v>RPRO-260203-0773</v>
           </cell>
@@ -11458,6 +11740,7 @@
           <cell r="A108" t="str">
             <v>S-2026-02-07</v>
           </cell>
+          <cell r="B108"/>
           <cell r="C108" t="str">
             <v>RPRO-260203-0774</v>
           </cell>
@@ -11526,6 +11809,7 @@
           <cell r="A109" t="str">
             <v>S-2026-02-08</v>
           </cell>
+          <cell r="B109"/>
           <cell r="C109" t="str">
             <v>RPRO-260203-0775</v>
           </cell>
@@ -11594,6 +11878,7 @@
           <cell r="A110" t="str">
             <v>S-2026-02-09</v>
           </cell>
+          <cell r="B110"/>
           <cell r="C110" t="str">
             <v>RPRO-260203-0776</v>
           </cell>
@@ -11662,6 +11947,7 @@
           <cell r="A111" t="str">
             <v>S-2026-02-10</v>
           </cell>
+          <cell r="B111"/>
           <cell r="C111" t="str">
             <v>RPRO-260203-0777</v>
           </cell>
@@ -11730,6 +12016,7 @@
           <cell r="A112" t="str">
             <v>S-2026-02-11</v>
           </cell>
+          <cell r="B112"/>
           <cell r="C112" t="str">
             <v>RPRO-260203-0778</v>
           </cell>
@@ -11798,6 +12085,7 @@
           <cell r="A113" t="str">
             <v>S-2026-02-12</v>
           </cell>
+          <cell r="B113"/>
           <cell r="C113" t="str">
             <v>RPRO-260203-0779</v>
           </cell>
@@ -11866,6 +12154,7 @@
           <cell r="A114" t="str">
             <v>S-2026-02-13</v>
           </cell>
+          <cell r="B114"/>
           <cell r="C114" t="str">
             <v>RPRO-260203-0780</v>
           </cell>
@@ -11934,6 +12223,7 @@
           <cell r="A115" t="str">
             <v>S-2026-02-14</v>
           </cell>
+          <cell r="B115"/>
           <cell r="C115" t="str">
             <v>RPRO-260203-0781</v>
           </cell>
@@ -12002,6 +12292,7 @@
           <cell r="A116" t="str">
             <v>S-2026-02-15</v>
           </cell>
+          <cell r="B116"/>
           <cell r="C116" t="str">
             <v>RPRO-260203-0782</v>
           </cell>
@@ -12070,6 +12361,7 @@
           <cell r="A117" t="str">
             <v>S-2026-02-16</v>
           </cell>
+          <cell r="B117"/>
           <cell r="C117" t="str">
             <v>RPRO-260203-0783</v>
           </cell>
@@ -12138,6 +12430,7 @@
           <cell r="A118" t="str">
             <v>S-2026-02-17</v>
           </cell>
+          <cell r="B118"/>
           <cell r="C118" t="str">
             <v>RPRO-260203-0784</v>
           </cell>
@@ -12206,6 +12499,7 @@
           <cell r="A119" t="str">
             <v>S-2026-02-18</v>
           </cell>
+          <cell r="B119"/>
           <cell r="C119" t="str">
             <v>RPRO-260204-0399</v>
           </cell>
@@ -12274,6 +12568,7 @@
           <cell r="A120" t="str">
             <v>S-2026-02-19</v>
           </cell>
+          <cell r="B120"/>
           <cell r="C120" t="str">
             <v>RPRO-260204-0400</v>
           </cell>
@@ -12342,6 +12637,7 @@
           <cell r="A121" t="str">
             <v>L-2026-02-20</v>
           </cell>
+          <cell r="B121"/>
           <cell r="C121" t="str">
             <v>RPRO-260204-0401</v>
           </cell>
@@ -12375,6 +12671,7 @@
           <cell r="M121" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N121"/>
           <cell r="O121" t="str">
             <v>Lab test</v>
           </cell>
@@ -12407,6 +12704,7 @@
           <cell r="A122" t="str">
             <v>L-2026-02-21</v>
           </cell>
+          <cell r="B122"/>
           <cell r="C122" t="str">
             <v>RPRO-260204-0402</v>
           </cell>
@@ -12440,6 +12738,7 @@
           <cell r="M122" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N122"/>
           <cell r="O122" t="str">
             <v>Lab test</v>
           </cell>
@@ -12543,6 +12842,7 @@
           <cell r="A124" t="str">
             <v>S-2026-02-23</v>
           </cell>
+          <cell r="B124"/>
           <cell r="C124" t="str">
             <v>RPRO-260210-0003</v>
           </cell>
@@ -12682,6 +12982,7 @@
           <cell r="A126" t="str">
             <v>S-2026-02-25</v>
           </cell>
+          <cell r="B126"/>
           <cell r="C126" t="str">
             <v>RPRO-260210-0005</v>
           </cell>
@@ -12750,6 +13051,7 @@
           <cell r="A127" t="str">
             <v>S-2026-02-26</v>
           </cell>
+          <cell r="B127"/>
           <cell r="C127" t="str">
             <v>RPRO-260210-0006</v>
           </cell>
@@ -12818,6 +13120,7 @@
           <cell r="A128" t="str">
             <v>S-2026-02-27</v>
           </cell>
+          <cell r="B128"/>
           <cell r="C128" t="str">
             <v>RPRO-260210-0007</v>
           </cell>
@@ -12886,6 +13189,7 @@
           <cell r="A129" t="str">
             <v>S-2026-02-28</v>
           </cell>
+          <cell r="B129"/>
           <cell r="C129" t="str">
             <v>RPRO-260210-0008</v>
           </cell>
@@ -12954,6 +13258,7 @@
           <cell r="A130" t="str">
             <v>S-2026-02-29</v>
           </cell>
+          <cell r="B130"/>
           <cell r="C130" t="str">
             <v>RPRO-260210-0009</v>
           </cell>
@@ -13022,6 +13327,7 @@
           <cell r="A131" t="str">
             <v>S-2026-02-30</v>
           </cell>
+          <cell r="B131"/>
           <cell r="C131" t="str">
             <v>RPRO-260210-0010</v>
           </cell>
@@ -13090,6 +13396,7 @@
           <cell r="A132" t="str">
             <v>S-2026-02-31</v>
           </cell>
+          <cell r="B132"/>
           <cell r="C132" t="str">
             <v>RPRO-260210-0011</v>
           </cell>
@@ -13159,6 +13466,7 @@
           <cell r="A133" t="str">
             <v>S-2026-02-32</v>
           </cell>
+          <cell r="B133"/>
           <cell r="C133" t="str">
             <v>RPRO-260210-0012</v>
           </cell>
@@ -13228,6 +13536,7 @@
           <cell r="A134" t="str">
             <v>S-2026-02-33</v>
           </cell>
+          <cell r="B134"/>
           <cell r="C134" t="str">
             <v>RPRO-260210-0013</v>
           </cell>
@@ -13296,6 +13605,7 @@
           <cell r="A135" t="str">
             <v>S-2026-02-34</v>
           </cell>
+          <cell r="B135"/>
           <cell r="C135" t="str">
             <v>RPRO-260211-0001</v>
           </cell>
@@ -13366,6 +13676,7 @@
           <cell r="A136" t="str">
             <v>S-2026-02-35</v>
           </cell>
+          <cell r="B136"/>
           <cell r="C136" t="str">
             <v>RPRO-260227-0335</v>
           </cell>
@@ -13434,6 +13745,7 @@
           <cell r="A137" t="str">
             <v>S-2026-02-36</v>
           </cell>
+          <cell r="B137"/>
           <cell r="C137" t="str">
             <v>RPRO-260227-0336</v>
           </cell>
@@ -13502,6 +13814,7 @@
           <cell r="A138" t="str">
             <v>S-2026-02-37</v>
           </cell>
+          <cell r="B138"/>
           <cell r="C138" t="str">
             <v>RPRO-260227-0337</v>
           </cell>
@@ -13570,6 +13883,7 @@
           <cell r="A139" t="str">
             <v>S-2026-02-38</v>
           </cell>
+          <cell r="B139"/>
           <cell r="C139" t="str">
             <v>RPRO-260227-0338</v>
           </cell>
@@ -13638,6 +13952,7 @@
           <cell r="A140" t="str">
             <v>S-2026-02-39</v>
           </cell>
+          <cell r="B140"/>
           <cell r="C140" t="str">
             <v>RPRO-260227-0339</v>
           </cell>
@@ -13706,6 +14021,7 @@
           <cell r="A141" t="str">
             <v>L-2026-02-40</v>
           </cell>
+          <cell r="B141"/>
           <cell r="C141" t="str">
             <v>RPRO-260227-0340</v>
           </cell>
@@ -13739,6 +14055,7 @@
           <cell r="M141" t="str">
             <v>Lab test</v>
           </cell>
+          <cell r="N141"/>
           <cell r="O141" t="str">
             <v>Lab test</v>
           </cell>
@@ -13771,6 +14088,7 @@
           <cell r="A142" t="str">
             <v>S-2026-02-41</v>
           </cell>
+          <cell r="B142"/>
           <cell r="C142" t="str">
             <v>RPRO-260227-0341</v>
           </cell>
@@ -13839,6 +14157,7 @@
           <cell r="A143" t="str">
             <v>S-2026-02-42</v>
           </cell>
+          <cell r="B143"/>
           <cell r="C143" t="str">
             <v>RPRO-260227-0342</v>
           </cell>
@@ -13907,6 +14226,7 @@
           <cell r="A144" t="str">
             <v>S-2026-02-43</v>
           </cell>
+          <cell r="B144"/>
           <cell r="C144" t="str">
             <v>RPRO-260227-0343</v>
           </cell>
@@ -13975,6 +14295,7 @@
           <cell r="A145" t="str">
             <v>S-2026-02-44</v>
           </cell>
+          <cell r="B145"/>
           <cell r="C145" t="str">
             <v>RPRO-260227-0344</v>
           </cell>
@@ -14043,6 +14364,7 @@
           <cell r="A146" t="str">
             <v>S-2026-02-45</v>
           </cell>
+          <cell r="B146"/>
           <cell r="C146" t="str">
             <v>RPRO-260227-0345</v>
           </cell>
@@ -14182,6 +14504,7 @@
           <cell r="A148" t="str">
             <v>S-2026-02-47</v>
           </cell>
+          <cell r="B148"/>
           <cell r="C148" t="str">
             <v>RPRO-260227-0347</v>
           </cell>
@@ -14250,6 +14573,7 @@
           <cell r="A149" t="str">
             <v>S-2026-02-48</v>
           </cell>
+          <cell r="B149"/>
           <cell r="C149" t="str">
             <v>RPRO-260227-0348</v>
           </cell>
@@ -14318,6 +14642,7 @@
           <cell r="A150" t="str">
             <v>S-2026-02-49</v>
           </cell>
+          <cell r="B150"/>
           <cell r="C150" t="str">
             <v>RPRO-260302-0004</v>
           </cell>
@@ -14386,6 +14711,7 @@
           <cell r="A151" t="str">
             <v>S-2026-02-50</v>
           </cell>
+          <cell r="B151"/>
           <cell r="C151" t="str">
             <v>RPRO-260227-0349</v>
           </cell>
@@ -14454,6 +14780,7 @@
           <cell r="A152" t="str">
             <v>S-2026-02-51</v>
           </cell>
+          <cell r="B152"/>
           <cell r="C152" t="str">
             <v>RPRO-260227-0350</v>
           </cell>
@@ -14522,6 +14849,7 @@
           <cell r="A153" t="str">
             <v>S-2026-02-52</v>
           </cell>
+          <cell r="B153"/>
           <cell r="C153" t="str">
             <v>RPRO-260227-0351</v>
           </cell>
@@ -14590,6 +14918,7 @@
           <cell r="A154" t="str">
             <v>S-2026-02-53</v>
           </cell>
+          <cell r="B154"/>
           <cell r="C154" t="str">
             <v>RPRO-260227-0352</v>
           </cell>
@@ -14658,6 +14987,7 @@
           <cell r="A155" t="str">
             <v>L-2026-03-01</v>
           </cell>
+          <cell r="B155"/>
           <cell r="C155" t="str">
             <v>RPRO-260303-0005</v>
           </cell>
@@ -14691,6 +15021,7 @@
           <cell r="M155" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N155"/>
           <cell r="O155" t="str">
             <v>Lab test</v>
           </cell>
@@ -14723,6 +15054,7 @@
           <cell r="A156" t="str">
             <v>L-2026-03-02</v>
           </cell>
+          <cell r="B156"/>
           <cell r="C156" t="str">
             <v>RPRO-260303-0006</v>
           </cell>
@@ -14756,6 +15088,7 @@
           <cell r="M156" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N156"/>
           <cell r="O156" t="str">
             <v>Lab test</v>
           </cell>
@@ -15072,6 +15405,7 @@
           <cell r="A161" t="str">
             <v>S-2026-03-07</v>
           </cell>
+          <cell r="B161"/>
           <cell r="C161" t="str">
             <v>RPRO-260303-0011</v>
           </cell>
@@ -15140,6 +15474,7 @@
           <cell r="A162" t="str">
             <v>S-2026-03-08</v>
           </cell>
+          <cell r="B162"/>
           <cell r="C162" t="str">
             <v>RPRO-260303-0012</v>
           </cell>
@@ -15208,6 +15543,7 @@
           <cell r="A163" t="str">
             <v>S-2026-03-09</v>
           </cell>
+          <cell r="B163"/>
           <cell r="C163" t="str">
             <v>RPRO-260303-0013</v>
           </cell>
@@ -15276,6 +15612,7 @@
           <cell r="A164" t="str">
             <v>S-2026-03-10</v>
           </cell>
+          <cell r="B164"/>
           <cell r="C164" t="str">
             <v>RPRO-260303-0014</v>
           </cell>
@@ -15344,6 +15681,7 @@
           <cell r="A165" t="str">
             <v>S-2026-03-11</v>
           </cell>
+          <cell r="B165"/>
           <cell r="C165" t="str">
             <v>RPRO-260313-0139</v>
           </cell>
@@ -15377,6 +15715,7 @@
           <cell r="M165" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N165"/>
           <cell r="O165" t="str">
             <v>Sample</v>
           </cell>
@@ -15409,6 +15748,7 @@
           <cell r="A166" t="str">
             <v>S-2026-03-12</v>
           </cell>
+          <cell r="B166"/>
           <cell r="C166" t="str">
             <v>RPRO-260313-0140</v>
           </cell>
@@ -15442,6 +15782,7 @@
           <cell r="M166" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N166"/>
           <cell r="O166" t="str">
             <v>Sample</v>
           </cell>
@@ -15474,6 +15815,7 @@
           <cell r="A167" t="str">
             <v>S-2026-03-13</v>
           </cell>
+          <cell r="B167"/>
           <cell r="C167" t="str">
             <v>RPRO-260313-0141</v>
           </cell>
@@ -15507,6 +15849,7 @@
           <cell r="M167" t="str">
             <v>INSOLE/ MOLDED/ FLAT SHEET or DIE CUT</v>
           </cell>
+          <cell r="N167"/>
           <cell r="O167" t="str">
             <v>Sample</v>
           </cell>
@@ -15610,6 +15953,7 @@
           <cell r="A169" t="str">
             <v>S-2026-03-15</v>
           </cell>
+          <cell r="B169"/>
           <cell r="C169" t="str">
             <v>RPRO-260306-1547</v>
           </cell>
@@ -15678,6 +16022,7 @@
           <cell r="A170" t="str">
             <v>S-2026-03-16</v>
           </cell>
+          <cell r="B170"/>
           <cell r="C170" t="str">
             <v>RPRO-260306-1548</v>
           </cell>
@@ -15746,6 +16091,7 @@
           <cell r="A171" t="str">
             <v>S-2026-03-17</v>
           </cell>
+          <cell r="B171"/>
           <cell r="C171" t="str">
             <v>RPRO-260306-1549</v>
           </cell>
@@ -15814,6 +16160,7 @@
           <cell r="A172" t="str">
             <v>S-2026-03-18</v>
           </cell>
+          <cell r="B172"/>
           <cell r="C172" t="str">
             <v>RPRO-260306-1550</v>
           </cell>
@@ -15882,6 +16229,7 @@
           <cell r="A173" t="str">
             <v>S-2026-03-19</v>
           </cell>
+          <cell r="B173"/>
           <cell r="C173" t="str">
             <v>RPRO-260306-1551</v>
           </cell>
@@ -15950,6 +16298,7 @@
           <cell r="A174" t="str">
             <v>S-2026-03-20</v>
           </cell>
+          <cell r="B174"/>
           <cell r="C174" t="str">
             <v>RPRO-260306-1552</v>
           </cell>
@@ -16018,6 +16367,7 @@
           <cell r="A175" t="str">
             <v>S-2026-03-21</v>
           </cell>
+          <cell r="B175"/>
           <cell r="C175" t="str">
             <v>RPRO-260306-1553</v>
           </cell>
@@ -16086,6 +16436,7 @@
           <cell r="A176" t="str">
             <v>S-2026-03-22</v>
           </cell>
+          <cell r="B176"/>
           <cell r="C176" t="str">
             <v>RPRO-260306-1554</v>
           </cell>
@@ -16154,6 +16505,7 @@
           <cell r="A177" t="str">
             <v>S-2026-03-23</v>
           </cell>
+          <cell r="B177"/>
           <cell r="C177" t="str">
             <v>RPRO-260306-1555</v>
           </cell>
@@ -16222,6 +16574,7 @@
           <cell r="A178" t="str">
             <v>S-2026-03-24</v>
           </cell>
+          <cell r="B178"/>
           <cell r="C178" t="str">
             <v>RPRO-260306-1556</v>
           </cell>
@@ -16361,6 +16714,7 @@
           <cell r="A180" t="str">
             <v>L-2026-03-26</v>
           </cell>
+          <cell r="B180"/>
           <cell r="C180" t="str">
             <v>RPRO-260305-1288</v>
           </cell>
@@ -16394,6 +16748,7 @@
           <cell r="M180" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N180"/>
           <cell r="O180" t="str">
             <v>Lab test</v>
           </cell>
@@ -16497,6 +16852,7 @@
           <cell r="A182" t="str">
             <v>S-2026-03-28</v>
           </cell>
+          <cell r="B182"/>
           <cell r="C182" t="str">
             <v>RPRO-260306-1559</v>
           </cell>
@@ -16565,6 +16921,7 @@
           <cell r="A183" t="str">
             <v>S-2026-03-29</v>
           </cell>
+          <cell r="B183"/>
           <cell r="C183" t="str">
             <v>RPRO-260306-1560</v>
           </cell>
@@ -16633,6 +16990,7 @@
           <cell r="A184" t="str">
             <v>S-2026-03-30</v>
           </cell>
+          <cell r="B184"/>
           <cell r="C184" t="str">
             <v>RPRO-260306-1561</v>
           </cell>
@@ -16701,6 +17059,7 @@
           <cell r="A185" t="str">
             <v>S-2026-03-31</v>
           </cell>
+          <cell r="B185"/>
           <cell r="C185" t="str">
             <v>RPRO-260306-1562</v>
           </cell>
@@ -16769,6 +17128,7 @@
           <cell r="A186" t="str">
             <v>S-2026-03-32</v>
           </cell>
+          <cell r="B186"/>
           <cell r="C186" t="str">
             <v>RPRO-260306-1563</v>
           </cell>
@@ -16837,6 +17197,7 @@
           <cell r="A187" t="str">
             <v>S-2026-03-33</v>
           </cell>
+          <cell r="B187"/>
           <cell r="C187" t="str">
             <v>RPRO-260306-1564</v>
           </cell>
@@ -16905,6 +17266,7 @@
           <cell r="A188" t="str">
             <v>S-2026-03-34</v>
           </cell>
+          <cell r="B188"/>
           <cell r="C188" t="str">
             <v>RPRO-260306-1565</v>
           </cell>
@@ -16973,6 +17335,7 @@
           <cell r="A189" t="str">
             <v>S-2026-03-35</v>
           </cell>
+          <cell r="B189"/>
           <cell r="C189" t="str">
             <v>RPRO-260306-1566</v>
           </cell>
@@ -17041,6 +17404,7 @@
           <cell r="A190" t="str">
             <v>S-2026-03-36</v>
           </cell>
+          <cell r="B190"/>
           <cell r="C190" t="str">
             <v>RPRO-260307-0080</v>
           </cell>
@@ -17109,6 +17473,7 @@
           <cell r="A191" t="str">
             <v>S-2026-03-37</v>
           </cell>
+          <cell r="B191"/>
           <cell r="C191" t="str">
             <v>RPRO-260306-1736</v>
           </cell>
@@ -17177,6 +17542,7 @@
           <cell r="A192" t="str">
             <v>S-2026-03-38</v>
           </cell>
+          <cell r="B192"/>
           <cell r="C192" t="str">
             <v>RPRO-260306-1737</v>
           </cell>
@@ -17245,6 +17611,7 @@
           <cell r="A193" t="str">
             <v>S-2026-03-39</v>
           </cell>
+          <cell r="B193"/>
           <cell r="C193" t="str">
             <v>RPRO-260306-1738</v>
           </cell>
@@ -17313,6 +17680,7 @@
           <cell r="A194" t="str">
             <v>S-2026-03-40</v>
           </cell>
+          <cell r="B194"/>
           <cell r="C194" t="str">
             <v>RPRO-260306-1739</v>
           </cell>
@@ -17381,6 +17749,7 @@
           <cell r="A195" t="str">
             <v>S-2026-03-41</v>
           </cell>
+          <cell r="B195"/>
           <cell r="C195" t="str">
             <v>RPRO-260306-1740</v>
           </cell>
@@ -17449,6 +17818,7 @@
           <cell r="A196" t="str">
             <v>S-2026-03-42</v>
           </cell>
+          <cell r="B196"/>
           <cell r="C196" t="str">
             <v>RPRO-260307-0081</v>
           </cell>
@@ -17517,6 +17887,7 @@
           <cell r="A197" t="str">
             <v>S-2026-03-43</v>
           </cell>
+          <cell r="B197"/>
           <cell r="C197" t="str">
             <v>RPRO-260307-0082</v>
           </cell>
@@ -17585,6 +17956,7 @@
           <cell r="A198" t="str">
             <v>S-2026-03-44</v>
           </cell>
+          <cell r="B198"/>
           <cell r="C198" t="str">
             <v>RPRO-260307-0083</v>
           </cell>
@@ -17653,6 +18025,7 @@
           <cell r="A199" t="str">
             <v>S-2026-03-45</v>
           </cell>
+          <cell r="B199"/>
           <cell r="C199" t="str">
             <v>RPRO-260307-0084</v>
           </cell>
@@ -17721,6 +18094,7 @@
           <cell r="A200" t="str">
             <v>S-2026-03-46</v>
           </cell>
+          <cell r="B200"/>
           <cell r="C200" t="str">
             <v>RPRO-260307-0085</v>
           </cell>
@@ -17789,6 +18163,7 @@
           <cell r="A201" t="str">
             <v>S-2026-03-47</v>
           </cell>
+          <cell r="B201"/>
           <cell r="C201" t="str">
             <v>RPRO-260310-0362</v>
           </cell>
@@ -17928,6 +18303,7 @@
           <cell r="A203" t="str">
             <v>S-2026-03-49</v>
           </cell>
+          <cell r="B203"/>
           <cell r="C203" t="str">
             <v>RPRO-260310-0364</v>
           </cell>
@@ -17996,6 +18372,7 @@
           <cell r="A204" t="str">
             <v>S-2026-03-50</v>
           </cell>
+          <cell r="B204"/>
           <cell r="C204" t="str">
             <v>RPRO-260310-0365</v>
           </cell>
@@ -18135,6 +18512,7 @@
           <cell r="A206" t="str">
             <v>S-2026-03-52</v>
           </cell>
+          <cell r="B206"/>
           <cell r="C206" t="str">
             <v>RPRO-260310-0367</v>
           </cell>
@@ -18203,6 +18581,7 @@
           <cell r="A207" t="str">
             <v>S-2026-03-53</v>
           </cell>
+          <cell r="B207"/>
           <cell r="C207" t="str">
             <v>RPRO-260310-0368</v>
           </cell>
@@ -18271,6 +18650,7 @@
           <cell r="A208" t="str">
             <v>S-2026-03-54</v>
           </cell>
+          <cell r="B208"/>
           <cell r="C208" t="str">
             <v>RPRO-260310-0369</v>
           </cell>
@@ -18339,6 +18719,7 @@
           <cell r="A209" t="str">
             <v>S-2026-03-55</v>
           </cell>
+          <cell r="B209"/>
           <cell r="C209" t="str">
             <v>RPRO-260310-0370</v>
           </cell>
@@ -18407,6 +18788,7 @@
           <cell r="A210" t="str">
             <v>S-2026-03-56</v>
           </cell>
+          <cell r="B210"/>
           <cell r="C210" t="str">
             <v>RPRO-260310-0371</v>
           </cell>
@@ -18475,6 +18857,7 @@
           <cell r="A211" t="str">
             <v>S-2026-03-57</v>
           </cell>
+          <cell r="B211"/>
           <cell r="C211" t="str">
             <v>RPRO-260310-0372</v>
           </cell>
@@ -18543,6 +18926,7 @@
           <cell r="A212" t="str">
             <v>S-2026-03-58</v>
           </cell>
+          <cell r="B212"/>
           <cell r="C212" t="str">
             <v>RPRO-260310-0373</v>
           </cell>
@@ -18611,6 +18995,7 @@
           <cell r="A213" t="str">
             <v>S-2026-03-59</v>
           </cell>
+          <cell r="B213"/>
           <cell r="C213" t="str">
             <v>RPRO-260310-0374</v>
           </cell>
@@ -18679,6 +19064,7 @@
           <cell r="A214" t="str">
             <v>S-2026-03-60</v>
           </cell>
+          <cell r="B214"/>
           <cell r="C214" t="str">
             <v>RPRO-260310-0375</v>
           </cell>
@@ -18747,6 +19133,7 @@
           <cell r="A215" t="str">
             <v>S-2026-03-61</v>
           </cell>
+          <cell r="B215"/>
           <cell r="C215" t="str">
             <v>RPRO-260310-0376</v>
           </cell>
@@ -18818,6 +19205,7 @@
           <cell r="B216" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C216"/>
           <cell r="D216" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -18848,6 +19236,7 @@
           <cell r="M216" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N216"/>
           <cell r="O216" t="str">
             <v>Lab test</v>
           </cell>
@@ -18883,6 +19272,7 @@
           <cell r="B217" t="str">
             <v>huy</v>
           </cell>
+          <cell r="C217"/>
           <cell r="D217" t="str">
             <v>ly.vtc@ortholite.vn</v>
           </cell>
@@ -18913,6 +19303,7 @@
           <cell r="M217" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N217"/>
           <cell r="O217" t="str">
             <v>Lab test</v>
           </cell>
@@ -18945,6 +19336,7 @@
           <cell r="A218" t="str">
             <v>S-2026-03-64</v>
           </cell>
+          <cell r="B218"/>
           <cell r="C218" t="str">
             <v>RPRO-260313-0142</v>
           </cell>
@@ -19013,6 +19405,7 @@
           <cell r="A219" t="str">
             <v>S-2026-03-65</v>
           </cell>
+          <cell r="B219"/>
           <cell r="C219" t="str">
             <v>RPRO-260313-0143</v>
           </cell>
@@ -19081,6 +19474,7 @@
           <cell r="A220" t="str">
             <v>S-2026-03-66</v>
           </cell>
+          <cell r="B220"/>
           <cell r="C220" t="str">
             <v>RPRO-260313-0144</v>
           </cell>
@@ -19149,6 +19543,7 @@
           <cell r="A221" t="str">
             <v>S-2026-03-67</v>
           </cell>
+          <cell r="B221"/>
           <cell r="C221" t="str">
             <v>RPRO-260313-0145</v>
           </cell>
@@ -19217,6 +19612,7 @@
           <cell r="A222" t="str">
             <v>S-2026-03-68</v>
           </cell>
+          <cell r="B222"/>
           <cell r="C222" t="str">
             <v>RPRO-260313-0146</v>
           </cell>
@@ -19285,6 +19681,7 @@
           <cell r="A223" t="str">
             <v>S-2026-03-69</v>
           </cell>
+          <cell r="B223"/>
           <cell r="C223" t="str">
             <v>RPRO-260313-0147</v>
           </cell>
@@ -19353,6 +19750,7 @@
           <cell r="A224" t="str">
             <v>S-2026-03-70</v>
           </cell>
+          <cell r="B224"/>
           <cell r="C224" t="str">
             <v>RPRO-260313-0148</v>
           </cell>
@@ -19421,6 +19819,7 @@
           <cell r="A225" t="str">
             <v>S-2026-03-71</v>
           </cell>
+          <cell r="B225"/>
           <cell r="C225" t="str">
             <v>RPRO-260313-0149</v>
           </cell>
@@ -19489,6 +19888,7 @@
           <cell r="A226" t="str">
             <v>S-2026-03-72</v>
           </cell>
+          <cell r="B226"/>
           <cell r="C226" t="str">
             <v>RPRO-260313-0150</v>
           </cell>
@@ -19557,6 +19957,7 @@
           <cell r="A227" t="str">
             <v>S-2026-03-73</v>
           </cell>
+          <cell r="B227"/>
           <cell r="C227" t="str">
             <v>RPRO-260313-0151</v>
           </cell>
@@ -19625,6 +20026,7 @@
           <cell r="A228" t="str">
             <v>S-2026-03-74</v>
           </cell>
+          <cell r="B228"/>
           <cell r="C228" t="str">
             <v>RPRO-260313-0152</v>
           </cell>
@@ -19693,6 +20095,7 @@
           <cell r="A229" t="str">
             <v>S-2026-03-75</v>
           </cell>
+          <cell r="B229"/>
           <cell r="C229" t="str">
             <v>RPRO-260313-0318</v>
           </cell>
@@ -19761,6 +20164,7 @@
           <cell r="A230" t="str">
             <v>S-2026-03-76</v>
           </cell>
+          <cell r="B230"/>
           <cell r="C230" t="str">
             <v>RPRO-260313-0319</v>
           </cell>
@@ -19829,6 +20233,7 @@
           <cell r="A231" t="str">
             <v>S-2026-03-77</v>
           </cell>
+          <cell r="B231"/>
           <cell r="C231" t="str">
             <v>RPRO-260314-0198</v>
           </cell>
@@ -19897,6 +20302,7 @@
           <cell r="A232" t="str">
             <v>S-2026-03-78</v>
           </cell>
+          <cell r="B232"/>
           <cell r="C232" t="str">
             <v>RPRO-260314-0199</v>
           </cell>
@@ -19965,6 +20371,7 @@
           <cell r="A233" t="str">
             <v>S-2026-03-79</v>
           </cell>
+          <cell r="B233"/>
           <cell r="C233" t="str">
             <v>RPRO-260317-0628</v>
           </cell>
@@ -20033,6 +20440,7 @@
           <cell r="A234" t="str">
             <v>S-2026-03-80</v>
           </cell>
+          <cell r="B234"/>
           <cell r="C234" t="str">
             <v>RPRO-260317-0629</v>
           </cell>
@@ -20101,6 +20509,7 @@
           <cell r="A235" t="str">
             <v>S-2026-03-81</v>
           </cell>
+          <cell r="B235"/>
           <cell r="C235" t="str">
             <v>RPRO-260317-0630</v>
           </cell>
@@ -20169,6 +20578,7 @@
           <cell r="A236" t="str">
             <v>S-2026-03-82</v>
           </cell>
+          <cell r="B236"/>
           <cell r="C236" t="str">
             <v>RPRO-260317-0631</v>
           </cell>
@@ -20237,6 +20647,7 @@
           <cell r="A237" t="str">
             <v>S-2026-03-83</v>
           </cell>
+          <cell r="B237"/>
           <cell r="C237" t="str">
             <v>RPRO-260317-0632</v>
           </cell>
@@ -20305,6 +20716,7 @@
           <cell r="A238" t="str">
             <v>S-2026-03-84</v>
           </cell>
+          <cell r="B238"/>
           <cell r="C238" t="str">
             <v>RPRO-260317-0633</v>
           </cell>
@@ -20373,6 +20785,7 @@
           <cell r="A239" t="str">
             <v>S-2026-03-85</v>
           </cell>
+          <cell r="B239"/>
           <cell r="C239" t="str">
             <v>RPRO-260317-0634</v>
           </cell>
@@ -20441,6 +20854,7 @@
           <cell r="A240" t="str">
             <v>S-2026-03-86</v>
           </cell>
+          <cell r="B240"/>
           <cell r="C240" t="str">
             <v>RPRO-260317-0635</v>
           </cell>
@@ -20509,6 +20923,7 @@
           <cell r="A241" t="str">
             <v>S-2026-03-87</v>
           </cell>
+          <cell r="B241"/>
           <cell r="C241" t="str">
             <v>RPRO-260317-0636</v>
           </cell>
@@ -20577,6 +20992,7 @@
           <cell r="A242" t="str">
             <v>L-2026-03-88</v>
           </cell>
+          <cell r="B242"/>
           <cell r="C242" t="str">
             <v>RPRO-260317-0637</v>
           </cell>
@@ -20610,6 +21026,7 @@
           <cell r="M242" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N242"/>
           <cell r="O242" t="str">
             <v>Lab test</v>
           </cell>
@@ -20678,6 +21095,7 @@
           <cell r="M243" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N243"/>
           <cell r="O243" t="str">
             <v>Lab test</v>
           </cell>
@@ -20710,6 +21128,7 @@
           <cell r="A244" t="str">
             <v>S-2026-03-90</v>
           </cell>
+          <cell r="B244"/>
           <cell r="C244" t="str">
             <v>RPRO-260317-0639</v>
           </cell>
@@ -20778,6 +21197,7 @@
           <cell r="A245" t="str">
             <v>S-2026-03-91</v>
           </cell>
+          <cell r="B245"/>
           <cell r="C245" t="str">
             <v>RPRO-260317-0640</v>
           </cell>
@@ -20846,6 +21266,7 @@
           <cell r="A246" t="str">
             <v>S-2026-03-92</v>
           </cell>
+          <cell r="B246"/>
           <cell r="C246" t="str">
             <v>RPRO-260317-0641</v>
           </cell>
@@ -20914,6 +21335,7 @@
           <cell r="A247" t="str">
             <v>L-2026-03-93</v>
           </cell>
+          <cell r="B247"/>
           <cell r="C247" t="str">
             <v>RPRO-260318-0477</v>
           </cell>
@@ -20947,6 +21369,7 @@
           <cell r="M247" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N247"/>
           <cell r="O247" t="str">
             <v>Lab test</v>
           </cell>
@@ -20979,6 +21402,7 @@
           <cell r="A248" t="str">
             <v>L-2026-03-94</v>
           </cell>
+          <cell r="B248"/>
           <cell r="C248" t="str">
             <v>RPRO-260318-0478</v>
           </cell>
@@ -21012,6 +21436,7 @@
           <cell r="M248" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N248"/>
           <cell r="O248" t="str">
             <v>Lab test</v>
           </cell>
@@ -21115,6 +21540,7 @@
           <cell r="A250" t="str">
             <v>S-2026-03-96</v>
           </cell>
+          <cell r="B250"/>
           <cell r="C250" t="str">
             <v>RPRO-260318-0482</v>
           </cell>
@@ -21183,6 +21609,7 @@
           <cell r="A251" t="str">
             <v>S-2026-03-97</v>
           </cell>
+          <cell r="B251"/>
           <cell r="C251" t="str">
             <v>RPRO-260324-0278</v>
           </cell>
@@ -21251,6 +21678,7 @@
           <cell r="A252" t="str">
             <v>S-2026-03-98</v>
           </cell>
+          <cell r="B252"/>
           <cell r="C252" t="str">
             <v>RPRO-260324-0279</v>
           </cell>
@@ -21390,6 +21818,7 @@
           <cell r="A254" t="str">
             <v>S-2026-03-100</v>
           </cell>
+          <cell r="B254"/>
           <cell r="C254" t="str">
             <v>RPRO-260324-0281</v>
           </cell>
@@ -21458,6 +21887,7 @@
           <cell r="A255" t="str">
             <v>S-2026-03-101</v>
           </cell>
+          <cell r="B255"/>
           <cell r="C255" t="str">
             <v>RPRO-260324-0282</v>
           </cell>
@@ -21526,6 +21956,7 @@
           <cell r="A256" t="str">
             <v>S-2026-03-102</v>
           </cell>
+          <cell r="B256"/>
           <cell r="C256" t="str">
             <v>RPRO-260324-0531</v>
           </cell>
@@ -21594,6 +22025,7 @@
           <cell r="A257" t="str">
             <v>S-2026-03-103</v>
           </cell>
+          <cell r="B257"/>
           <cell r="C257" t="str">
             <v>RPRO-260324-0283</v>
           </cell>
@@ -21662,6 +22094,7 @@
           <cell r="A258" t="str">
             <v>S-2026-03-104</v>
           </cell>
+          <cell r="B258"/>
           <cell r="C258" t="str">
             <v>RPRO-260324-0284</v>
           </cell>
@@ -21730,6 +22163,7 @@
           <cell r="A259" t="str">
             <v>L-2026-03-105</v>
           </cell>
+          <cell r="B259"/>
           <cell r="C259" t="str">
             <v>RPRO-260321-0027</v>
           </cell>
@@ -21763,6 +22197,7 @@
           <cell r="M259" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N259"/>
           <cell r="O259" t="str">
             <v>Lab test</v>
           </cell>
@@ -21795,6 +22230,7 @@
           <cell r="A260" t="str">
             <v>L-2026-03-106</v>
           </cell>
+          <cell r="B260"/>
           <cell r="C260" t="str">
             <v>RPRO-260321-0028</v>
           </cell>
@@ -21828,6 +22264,7 @@
           <cell r="M260" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N260"/>
           <cell r="O260" t="str">
             <v>Lab test</v>
           </cell>
@@ -21860,6 +22297,7 @@
           <cell r="A261" t="str">
             <v>S-2026-03-107</v>
           </cell>
+          <cell r="B261"/>
           <cell r="C261" t="str">
             <v>RPRO-260321-0029</v>
           </cell>
@@ -21928,6 +22366,7 @@
           <cell r="A262" t="str">
             <v>S-2026-03-108</v>
           </cell>
+          <cell r="B262"/>
           <cell r="C262" t="str">
             <v>RPRO-260324-0285</v>
           </cell>
@@ -21996,6 +22435,7 @@
           <cell r="A263" t="str">
             <v>L-2026-03-109</v>
           </cell>
+          <cell r="B263"/>
           <cell r="C263" t="str">
             <v>RPRO-260324-0286</v>
           </cell>
@@ -22023,9 +22463,11 @@
           <cell r="K263">
             <v>0</v>
           </cell>
+          <cell r="L263"/>
           <cell r="M263" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N263"/>
           <cell r="O263" t="str">
             <v>Lab test</v>
           </cell>
@@ -22058,6 +22500,7 @@
           <cell r="A264" t="str">
             <v>S-2026-03-110</v>
           </cell>
+          <cell r="B264"/>
           <cell r="C264" t="str">
             <v>RPRO-260324-0287</v>
           </cell>
@@ -22126,6 +22569,7 @@
           <cell r="A265" t="str">
             <v>S-2026-03-111</v>
           </cell>
+          <cell r="B265"/>
           <cell r="C265" t="str">
             <v>RPRO-260324-0288</v>
           </cell>
@@ -22194,6 +22638,7 @@
           <cell r="A266" t="str">
             <v>S-2026-03-112</v>
           </cell>
+          <cell r="B266"/>
           <cell r="C266" t="str">
             <v>RPRO-260324-0289</v>
           </cell>
@@ -22262,6 +22707,7 @@
           <cell r="A267" t="str">
             <v>S-2026-03-113</v>
           </cell>
+          <cell r="B267"/>
           <cell r="C267" t="str">
             <v>RPRO-260324-0532</v>
           </cell>
@@ -22330,6 +22776,7 @@
           <cell r="A268" t="str">
             <v>S-2026-03-114</v>
           </cell>
+          <cell r="B268"/>
           <cell r="C268" t="str">
             <v>RPRO-260324-0533</v>
           </cell>
@@ -22398,6 +22845,7 @@
           <cell r="A269" t="str">
             <v>S-2026-03-115</v>
           </cell>
+          <cell r="B269"/>
           <cell r="C269" t="str">
             <v>RPRO-260324-0534</v>
           </cell>
@@ -22466,6 +22914,7 @@
           <cell r="A270" t="str">
             <v>S-2026-03-116</v>
           </cell>
+          <cell r="B270"/>
           <cell r="C270" t="str">
             <v>RPRO-260325-0407</v>
           </cell>
@@ -22534,6 +22983,7 @@
           <cell r="A271" t="str">
             <v>S-2026-03-117</v>
           </cell>
+          <cell r="B271"/>
           <cell r="C271" t="str">
             <v>RPRO-260325-0408</v>
           </cell>
@@ -22602,6 +23052,7 @@
           <cell r="A272" t="str">
             <v>S-2026-03-118</v>
           </cell>
+          <cell r="B272"/>
           <cell r="C272" t="str">
             <v>RPRO-260325-0409</v>
           </cell>
@@ -22670,6 +23121,7 @@
           <cell r="A273" t="str">
             <v>S-2026-03-119</v>
           </cell>
+          <cell r="B273"/>
           <cell r="C273" t="str">
             <v>RPRO-260325-0410</v>
           </cell>
@@ -22738,6 +23190,7 @@
           <cell r="A274" t="str">
             <v>S-2026-03-120</v>
           </cell>
+          <cell r="B274"/>
           <cell r="C274" t="str">
             <v>RPRO-260325-0411</v>
           </cell>
@@ -22806,6 +23259,7 @@
           <cell r="A275" t="str">
             <v>S-2026-03-121</v>
           </cell>
+          <cell r="B275"/>
           <cell r="C275" t="str">
             <v>RPRO-260325-0412</v>
           </cell>
@@ -22874,6 +23328,7 @@
           <cell r="A276" t="str">
             <v>S-2026-03-122</v>
           </cell>
+          <cell r="B276"/>
           <cell r="C276" t="str">
             <v>RPRO-260325-0413</v>
           </cell>
@@ -22942,6 +23397,7 @@
           <cell r="A277" t="str">
             <v>S-2026-03-123</v>
           </cell>
+          <cell r="B277"/>
           <cell r="C277" t="str">
             <v>RPRO-260325-0414</v>
           </cell>
@@ -23010,6 +23466,7 @@
           <cell r="A278" t="str">
             <v>S-2026-03-124</v>
           </cell>
+          <cell r="B278"/>
           <cell r="C278" t="str">
             <v>RPRO-260325-0415</v>
           </cell>
@@ -23149,6 +23606,7 @@
           <cell r="A280" t="str">
             <v>S-2026-03-126</v>
           </cell>
+          <cell r="B280"/>
           <cell r="C280" t="str">
             <v>RPRO-260325-0417</v>
           </cell>
@@ -23217,6 +23675,7 @@
           <cell r="A281" t="str">
             <v>S-2026-03-127</v>
           </cell>
+          <cell r="B281"/>
           <cell r="C281" t="str">
             <v>RPRO-260325-0418</v>
           </cell>
@@ -23285,6 +23744,7 @@
           <cell r="A282" t="str">
             <v>S-2026-03-128</v>
           </cell>
+          <cell r="B282"/>
           <cell r="C282" t="str">
             <v>RPRO-260325-0419</v>
           </cell>
@@ -23353,6 +23813,7 @@
           <cell r="A283" t="str">
             <v>S-2026-03-129</v>
           </cell>
+          <cell r="B283"/>
           <cell r="C283" t="str">
             <v>RPRO-260325-0421</v>
           </cell>
@@ -23421,6 +23882,7 @@
           <cell r="A284" t="str">
             <v>S-2026-03-130</v>
           </cell>
+          <cell r="B284"/>
           <cell r="C284" t="str">
             <v>RPRO-260327-0930</v>
           </cell>
@@ -23631,6 +24093,7 @@
           <cell r="A287" t="str">
             <v>S-2026-03-133</v>
           </cell>
+          <cell r="B287"/>
           <cell r="C287" t="str">
             <v>RPRO-260327-0933</v>
           </cell>
@@ -23699,6 +24162,7 @@
           <cell r="A288" t="str">
             <v>S-2026-03-134</v>
           </cell>
+          <cell r="B288"/>
           <cell r="C288" t="str">
             <v>RPRO-260327-0934</v>
           </cell>
@@ -23909,6 +24373,7 @@
           <cell r="A291" t="str">
             <v>S-2026-03-137</v>
           </cell>
+          <cell r="B291"/>
           <cell r="C291" t="str">
             <v>RPRO-260327-0937</v>
           </cell>
@@ -24048,6 +24513,7 @@
           <cell r="A293" t="str">
             <v>S-2026-03-139</v>
           </cell>
+          <cell r="B293"/>
           <cell r="C293" t="str">
             <v>RPRO-260327-0939</v>
           </cell>
@@ -24187,6 +24653,7 @@
           <cell r="A295" t="str">
             <v>S-2026-03-141</v>
           </cell>
+          <cell r="B295"/>
           <cell r="C295" t="str">
             <v>RPRO-260327-0941</v>
           </cell>
@@ -24255,6 +24722,7 @@
           <cell r="A296" t="str">
             <v>S-2026-03-142</v>
           </cell>
+          <cell r="B296"/>
           <cell r="C296" t="str">
             <v>RPRO-260401-0245</v>
           </cell>
@@ -24394,6 +24862,7 @@
           <cell r="A298" t="str">
             <v>S-2026-03-144</v>
           </cell>
+          <cell r="B298"/>
           <cell r="C298" t="str">
             <v>RPRO-260401-0247</v>
           </cell>
@@ -24462,6 +24931,7 @@
           <cell r="A299" t="str">
             <v>S-2026-03-145</v>
           </cell>
+          <cell r="B299"/>
           <cell r="C299" t="str">
             <v>RPRO-260401-0248</v>
           </cell>
@@ -24530,6 +25000,7 @@
           <cell r="A300" t="str">
             <v>S-2026-03-146</v>
           </cell>
+          <cell r="B300"/>
           <cell r="C300" t="str">
             <v>RPRO-260401-0249</v>
           </cell>
@@ -24598,6 +25069,7 @@
           <cell r="A301" t="str">
             <v>S-2026-04-01</v>
           </cell>
+          <cell r="B301"/>
           <cell r="C301" t="str">
             <v>RPRO-260401-0250</v>
           </cell>
@@ -24666,6 +25138,7 @@
           <cell r="A302" t="str">
             <v>S-2026-04-02</v>
           </cell>
+          <cell r="B302"/>
           <cell r="C302" t="str">
             <v>RPRO-260401-0251</v>
           </cell>
@@ -24734,6 +25207,7 @@
           <cell r="A303" t="str">
             <v>S-2026-04-03</v>
           </cell>
+          <cell r="B303"/>
           <cell r="C303" t="str">
             <v>RPRO-260402-0737</v>
           </cell>
@@ -24802,6 +25276,7 @@
           <cell r="A304" t="str">
             <v>S-2026-04-04</v>
           </cell>
+          <cell r="B304"/>
           <cell r="C304" t="str">
             <v>RPRO-260402-0738</v>
           </cell>
@@ -24870,6 +25345,7 @@
           <cell r="A305" t="str">
             <v>S-2026-04-05</v>
           </cell>
+          <cell r="B305"/>
           <cell r="C305" t="str">
             <v>RPRO-260403-0489</v>
           </cell>
@@ -24938,6 +25414,7 @@
           <cell r="A306" t="str">
             <v>S-2026-04-06</v>
           </cell>
+          <cell r="B306"/>
           <cell r="C306" t="str">
             <v>RPRO-260403-0490</v>
           </cell>
@@ -25006,6 +25483,7 @@
           <cell r="A307" t="str">
             <v>S-2026-04-07</v>
           </cell>
+          <cell r="B307"/>
           <cell r="C307" t="str">
             <v>RPRO-260403-0491</v>
           </cell>
@@ -25074,6 +25552,7 @@
           <cell r="A308" t="str">
             <v>S-2026-04-08</v>
           </cell>
+          <cell r="B308"/>
           <cell r="C308" t="str">
             <v>RPRO-260403-0492</v>
           </cell>
@@ -25142,6 +25621,7 @@
           <cell r="A309" t="str">
             <v>S-2026-04-09</v>
           </cell>
+          <cell r="B309"/>
           <cell r="C309" t="str">
             <v>RPRO-260406-1201</v>
           </cell>
@@ -25210,6 +25690,7 @@
           <cell r="A310" t="str">
             <v>S-2026-04-10</v>
           </cell>
+          <cell r="B310"/>
           <cell r="C310" t="str">
             <v>RPRO-260406-1202</v>
           </cell>
@@ -25278,6 +25759,7 @@
           <cell r="A311" t="str">
             <v>S-2026-04-11</v>
           </cell>
+          <cell r="B311"/>
           <cell r="C311" t="str">
             <v>RPRO-260406-1203</v>
           </cell>
@@ -25346,6 +25828,7 @@
           <cell r="A312" t="str">
             <v>S-2026-04-12</v>
           </cell>
+          <cell r="B312"/>
           <cell r="C312" t="str">
             <v>RPRO-260407-0417</v>
           </cell>
@@ -25414,6 +25897,7 @@
           <cell r="A313" t="str">
             <v>S-2026-04-13</v>
           </cell>
+          <cell r="B313"/>
           <cell r="C313" t="str">
             <v>RPRO-260407-0418</v>
           </cell>
@@ -25482,6 +25966,7 @@
           <cell r="A314" t="str">
             <v>S-2026-04-14</v>
           </cell>
+          <cell r="B314"/>
           <cell r="C314" t="str">
             <v>RPRO-260407-0419</v>
           </cell>
@@ -25550,6 +26035,7 @@
           <cell r="A315" t="str">
             <v>S-2026-04-15</v>
           </cell>
+          <cell r="B315"/>
           <cell r="C315" t="str">
             <v>RPRO-260407-0420</v>
           </cell>
@@ -25618,6 +26104,7 @@
           <cell r="A316" t="str">
             <v>S-2026-04-16</v>
           </cell>
+          <cell r="B316"/>
           <cell r="C316" t="str">
             <v>RPRO-260409-0346</v>
           </cell>
@@ -25686,6 +26173,7 @@
           <cell r="A317" t="str">
             <v>S-2026-04-17</v>
           </cell>
+          <cell r="B317"/>
           <cell r="C317" t="str">
             <v>RPRO-260409-0347</v>
           </cell>
@@ -25754,6 +26242,7 @@
           <cell r="A318" t="str">
             <v>S-2026-04-18</v>
           </cell>
+          <cell r="B318"/>
           <cell r="C318" t="str">
             <v>RPRO-260409-0348</v>
           </cell>
@@ -25822,6 +26311,7 @@
           <cell r="A319" t="str">
             <v>S-2026-04-19</v>
           </cell>
+          <cell r="B319"/>
           <cell r="C319" t="str">
             <v>RPRO-260409-0349</v>
           </cell>
@@ -25890,6 +26380,7 @@
           <cell r="A320" t="str">
             <v>S-2026-04-20</v>
           </cell>
+          <cell r="B320"/>
           <cell r="C320" t="str">
             <v>RPRO-260409-0350</v>
           </cell>
@@ -25958,6 +26449,7 @@
           <cell r="A321" t="str">
             <v>L-2026-04-21</v>
           </cell>
+          <cell r="B321"/>
           <cell r="C321" t="str">
             <v>RPRO-260410-0280</v>
           </cell>
@@ -25991,6 +26483,7 @@
           <cell r="M321" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N321"/>
           <cell r="O321" t="str">
             <v>Lab test</v>
           </cell>
@@ -26023,6 +26516,7 @@
           <cell r="A322" t="str">
             <v>L-2026-04-22</v>
           </cell>
+          <cell r="B322"/>
           <cell r="C322" t="str">
             <v>RPRO-260410-0281</v>
           </cell>
@@ -26056,6 +26550,7 @@
           <cell r="M322" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N322"/>
           <cell r="O322" t="str">
             <v>Lab test</v>
           </cell>
@@ -26088,6 +26583,7 @@
           <cell r="A323" t="str">
             <v>S-2026-04-23</v>
           </cell>
+          <cell r="B323"/>
           <cell r="C323" t="str">
             <v>RPRO-260410-0282</v>
           </cell>
@@ -26156,6 +26652,7 @@
           <cell r="A324" t="str">
             <v>S-2026-04-24</v>
           </cell>
+          <cell r="B324"/>
           <cell r="C324" t="str">
             <v>RPRO-260410-0283</v>
           </cell>
@@ -26224,6 +26721,7 @@
           <cell r="A325" t="str">
             <v>S-2026-04-25</v>
           </cell>
+          <cell r="B325"/>
           <cell r="C325" t="str">
             <v>RPRO-260410-0284</v>
           </cell>
@@ -26292,6 +26790,7 @@
           <cell r="A326" t="str">
             <v>S-2026-04-26</v>
           </cell>
+          <cell r="B326"/>
           <cell r="C326" t="str">
             <v>RPRO-260410-0285</v>
           </cell>
@@ -26360,6 +26859,7 @@
           <cell r="A327" t="str">
             <v>S-2026-04-27</v>
           </cell>
+          <cell r="B327"/>
           <cell r="C327" t="str">
             <v>RPRO-260410-0286</v>
           </cell>
@@ -26428,6 +26928,7 @@
           <cell r="A328" t="str">
             <v>S-2026-04-28</v>
           </cell>
+          <cell r="B328"/>
           <cell r="C328" t="str">
             <v>RPRO-260410-0287</v>
           </cell>
@@ -26567,6 +27068,7 @@
           <cell r="A330" t="str">
             <v>S-2026-04-30</v>
           </cell>
+          <cell r="B330"/>
           <cell r="C330" t="str">
             <v>RPRO-260414-0202</v>
           </cell>
@@ -26635,6 +27137,7 @@
           <cell r="A331" t="str">
             <v>S-2026-04-31</v>
           </cell>
+          <cell r="B331"/>
           <cell r="C331" t="str">
             <v>RPRO-260414-0203</v>
           </cell>
@@ -26703,6 +27206,7 @@
           <cell r="A332" t="str">
             <v>S-2026-04-32</v>
           </cell>
+          <cell r="B332"/>
           <cell r="C332" t="str">
             <v>RPRO-260414-0204</v>
           </cell>
@@ -26771,6 +27275,7 @@
           <cell r="A333" t="str">
             <v>S-2026-04-33</v>
           </cell>
+          <cell r="B333"/>
           <cell r="C333" t="str">
             <v>RPRO-260414-0205</v>
           </cell>
@@ -26839,6 +27344,7 @@
           <cell r="A334" t="str">
             <v>S-2026-04-34</v>
           </cell>
+          <cell r="B334"/>
           <cell r="C334" t="str">
             <v>RPRO-260414-0206</v>
           </cell>
@@ -26907,6 +27413,7 @@
           <cell r="A335" t="str">
             <v>S-2026-04-35</v>
           </cell>
+          <cell r="B335"/>
           <cell r="C335" t="str">
             <v>RPRO-260414-0207</v>
           </cell>
@@ -26975,6 +27482,7 @@
           <cell r="A336" t="str">
             <v>S-2026-04-36</v>
           </cell>
+          <cell r="B336"/>
           <cell r="C336" t="str">
             <v>RPRO-260414-0208</v>
           </cell>
@@ -27043,6 +27551,7 @@
           <cell r="A337" t="str">
             <v>S-2026-04-37</v>
           </cell>
+          <cell r="B337"/>
           <cell r="C337" t="str">
             <v>RPRO-260414-0209</v>
           </cell>
@@ -27111,6 +27620,7 @@
           <cell r="A338" t="str">
             <v>S-2026-04-38</v>
           </cell>
+          <cell r="B338"/>
           <cell r="C338" t="str">
             <v>RPRO-260414-0210</v>
           </cell>
@@ -27179,6 +27689,7 @@
           <cell r="A339" t="str">
             <v>S-2026-04-39</v>
           </cell>
+          <cell r="B339"/>
           <cell r="C339" t="str">
             <v>RPRO-260414-0211</v>
           </cell>
@@ -27247,6 +27758,7 @@
           <cell r="A340" t="str">
             <v>S-2026-04-40</v>
           </cell>
+          <cell r="B340"/>
           <cell r="C340" t="str">
             <v>RPRO-260414-0212</v>
           </cell>
@@ -27351,6 +27863,7 @@
           <cell r="M341" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N341"/>
           <cell r="O341" t="str">
             <v>Lab test</v>
           </cell>
@@ -27419,6 +27932,7 @@
           <cell r="M342" t="str">
             <v xml:space="preserve">Lab test </v>
           </cell>
+          <cell r="N342"/>
           <cell r="O342" t="str">
             <v>Lab test</v>
           </cell>
@@ -27451,6 +27965,7 @@
           <cell r="A343" t="str">
             <v>S-2026-04-43</v>
           </cell>
+          <cell r="B343"/>
           <cell r="C343" t="str">
             <v>RPRO-260417-0243</v>
           </cell>
@@ -27519,6 +28034,7 @@
           <cell r="A344" t="str">
             <v>S-2026-04-44</v>
           </cell>
+          <cell r="B344"/>
           <cell r="C344" t="str">
             <v>RPRO-260417-0244</v>
           </cell>
@@ -27587,6 +28103,7 @@
           <cell r="A345" t="str">
             <v>S-2026-04-45</v>
           </cell>
+          <cell r="B345"/>
           <cell r="C345" t="str">
             <v>RPRO-260417-0245</v>
           </cell>
@@ -27655,6 +28172,7 @@
           <cell r="A346" t="str">
             <v>S-2026-04-46</v>
           </cell>
+          <cell r="B346"/>
           <cell r="C346" t="str">
             <v>RPRO-260417-0246</v>
           </cell>
@@ -27723,6 +28241,7 @@
           <cell r="A347" t="str">
             <v>S-2026-04-47</v>
           </cell>
+          <cell r="B347"/>
           <cell r="C347" t="str">
             <v>RPRO-260417-0247</v>
           </cell>
@@ -27791,6 +28310,7 @@
           <cell r="A348" t="str">
             <v>S-2026-04-48</v>
           </cell>
+          <cell r="B348"/>
           <cell r="C348" t="str">
             <v>RPRO-260421-0623</v>
           </cell>
@@ -27859,6 +28379,7 @@
           <cell r="A349" t="str">
             <v>S-2026-04-49</v>
           </cell>
+          <cell r="B349"/>
           <cell r="C349" t="str">
             <v>RPRO-260421-0624</v>
           </cell>
@@ -27927,6 +28448,7 @@
           <cell r="A350" t="str">
             <v>S-2026-04-50</v>
           </cell>
+          <cell r="B350"/>
           <cell r="C350" t="str">
             <v>RPRO-260421-0625</v>
           </cell>
@@ -27995,6 +28517,7 @@
           <cell r="A351" t="str">
             <v>S-2026-04-51</v>
           </cell>
+          <cell r="B351"/>
           <cell r="C351" t="str">
             <v>RPRO-260421-0626</v>
           </cell>
@@ -28063,6 +28586,7 @@
           <cell r="A352" t="str">
             <v>S-2026-04-52</v>
           </cell>
+          <cell r="B352"/>
           <cell r="C352" t="str">
             <v>RPRO-260421-0627</v>
           </cell>
@@ -28131,6 +28655,7 @@
           <cell r="A353" t="str">
             <v>S-2026-04-53</v>
           </cell>
+          <cell r="B353"/>
           <cell r="C353" t="str">
             <v>RPRO-260421-0628</v>
           </cell>
@@ -28199,6 +28724,7 @@
           <cell r="A354" t="str">
             <v>S-2026-04-54</v>
           </cell>
+          <cell r="B354"/>
           <cell r="C354" t="str">
             <v>RPRO-260421-0629</v>
           </cell>
@@ -28267,6 +28793,7 @@
           <cell r="A355" t="str">
             <v>S-2026-04-55</v>
           </cell>
+          <cell r="B355"/>
           <cell r="C355" t="str">
             <v>RPRO-260421-0630</v>
           </cell>
@@ -28335,6 +28862,7 @@
           <cell r="A356" t="str">
             <v>S-2026-04-56</v>
           </cell>
+          <cell r="B356"/>
           <cell r="C356" t="str">
             <v>RPRO-260421-0631</v>
           </cell>
@@ -28403,6 +28931,7 @@
           <cell r="A357" t="str">
             <v>S-2026-04-57</v>
           </cell>
+          <cell r="B357"/>
           <cell r="C357" t="str">
             <v>RPRO-260421-0632</v>
           </cell>
@@ -28471,6 +29000,7 @@
           <cell r="A358" t="str">
             <v>S-2026-04-58</v>
           </cell>
+          <cell r="B358"/>
           <cell r="C358" t="str">
             <v>RPRO-260421-0633</v>
           </cell>
@@ -28539,6 +29069,7 @@
           <cell r="A359" t="str">
             <v>S-2026-04-59</v>
           </cell>
+          <cell r="B359"/>
           <cell r="C359" t="str">
             <v>RPRO-260422-0268</v>
           </cell>
@@ -28607,6 +29138,7 @@
           <cell r="A360" t="str">
             <v>S-2026-04-60</v>
           </cell>
+          <cell r="B360"/>
           <cell r="C360" t="str">
             <v>RPRO-260423-0486</v>
           </cell>
@@ -28675,6 +29207,7 @@
           <cell r="A361" t="str">
             <v>S-2026-04-61</v>
           </cell>
+          <cell r="B361"/>
           <cell r="C361" t="str">
             <v>RPRO-260423-0487</v>
           </cell>
@@ -28743,6 +29276,7 @@
           <cell r="A362" t="str">
             <v>S-2026-04-62</v>
           </cell>
+          <cell r="B362"/>
           <cell r="C362" t="str">
             <v>RPRO-260424-1197</v>
           </cell>
@@ -28811,6 +29345,7 @@
           <cell r="A363" t="str">
             <v>S-2026-04-63</v>
           </cell>
+          <cell r="B363"/>
           <cell r="C363" t="str">
             <v>RPRO-260424-1198</v>
           </cell>
@@ -28879,6 +29414,7 @@
           <cell r="A364" t="str">
             <v>S-2026-04-64</v>
           </cell>
+          <cell r="B364"/>
           <cell r="C364" t="str">
             <v>RPRO-260424-1199</v>
           </cell>
@@ -28947,6 +29483,7 @@
           <cell r="A365" t="str">
             <v>S-2026-04-65</v>
           </cell>
+          <cell r="B365"/>
           <cell r="C365" t="str">
             <v>RPRO-260424-1200</v>
           </cell>
@@ -29015,6 +29552,7 @@
           <cell r="A366" t="str">
             <v>S-2026-04-66</v>
           </cell>
+          <cell r="B366"/>
           <cell r="C366" t="str">
             <v>RPRO-260424-1201</v>
           </cell>
@@ -29154,6 +29692,7 @@
           <cell r="A368" t="str">
             <v>S-2026-04-68</v>
           </cell>
+          <cell r="B368"/>
           <cell r="C368" t="str">
             <v>RPRO-260424-1203</v>
           </cell>
@@ -29222,6 +29761,7 @@
           <cell r="A369" t="str">
             <v>S-2026-04-69</v>
           </cell>
+          <cell r="B369"/>
           <cell r="C369" t="str">
             <v>RPRO-260424-1204</v>
           </cell>
@@ -29290,6 +29830,7 @@
           <cell r="A370" t="str">
             <v>S-2026-04-70</v>
           </cell>
+          <cell r="B370"/>
           <cell r="C370" t="str">
             <v>RPRO-260424-1205</v>
           </cell>
@@ -29358,6 +29899,7 @@
           <cell r="A371" t="str">
             <v>S-2026-04-71</v>
           </cell>
+          <cell r="B371"/>
           <cell r="C371" t="str">
             <v>RPRO-260424-1206</v>
           </cell>
@@ -29426,6 +29968,7 @@
           <cell r="A372" t="str">
             <v>S-2026-04-72</v>
           </cell>
+          <cell r="B372"/>
           <cell r="C372" t="str">
             <v>RPRO-260428-0920</v>
           </cell>
@@ -29494,6 +30037,7 @@
           <cell r="A373" t="str">
             <v>S-2026-04-73</v>
           </cell>
+          <cell r="B373"/>
           <cell r="C373" t="str">
             <v>RPRO-260429-0109</v>
           </cell>
@@ -29562,6 +30106,7 @@
           <cell r="A374" t="str">
             <v>S-2026-04-74</v>
           </cell>
+          <cell r="B374"/>
           <cell r="C374" t="str">
             <v>RPRO-260429-0110</v>
           </cell>
@@ -29630,6 +30175,7 @@
           <cell r="A375" t="str">
             <v>S-2026-04-75</v>
           </cell>
+          <cell r="B375"/>
           <cell r="C375" t="str">
             <v>RPRO-260429-0126</v>
           </cell>
@@ -29698,6 +30244,7 @@
           <cell r="A376" t="str">
             <v>S-2026-04-76</v>
           </cell>
+          <cell r="B376"/>
           <cell r="C376" t="str">
             <v>RPRO-260429-0127</v>
           </cell>
@@ -29766,6 +30313,7 @@
           <cell r="A377" t="str">
             <v>S-2026-05-01</v>
           </cell>
+          <cell r="B377"/>
           <cell r="C377" t="str">
             <v>RPRO-260505-0654</v>
           </cell>
@@ -29905,6 +30453,7 @@
           <cell r="A379" t="str">
             <v>S-2026-05-03</v>
           </cell>
+          <cell r="B379"/>
           <cell r="C379" t="str">
             <v>RPRO-260505-0656</v>
           </cell>
@@ -29973,6 +30522,7 @@
           <cell r="A380" t="str">
             <v>S-2026-05-04</v>
           </cell>
+          <cell r="B380"/>
           <cell r="C380" t="str">
             <v>RPRO-260505-0657</v>
           </cell>
@@ -30041,6 +30591,7 @@
           <cell r="A381" t="str">
             <v>S-2026-05-05</v>
           </cell>
+          <cell r="B381"/>
           <cell r="C381" t="str">
             <v>RPRO-260505-0658</v>
           </cell>
@@ -30109,6 +30660,7 @@
           <cell r="A382" t="str">
             <v>S-2026-05-06</v>
           </cell>
+          <cell r="B382"/>
           <cell r="C382" t="str">
             <v>RPRO-260505-0659</v>
           </cell>
@@ -30177,6 +30729,7 @@
           <cell r="A383" t="str">
             <v>S-2026-05-07</v>
           </cell>
+          <cell r="B383"/>
           <cell r="C383" t="str">
             <v>RPRO-260505-0660</v>
           </cell>
@@ -30316,6 +30869,7 @@
           <cell r="A385" t="str">
             <v>S-2026-05-09</v>
           </cell>
+          <cell r="B385"/>
           <cell r="C385" t="str">
             <v>RPRO-260505-0662</v>
           </cell>
@@ -30384,6 +30938,7 @@
           <cell r="A386" t="str">
             <v>S-2026-05-10</v>
           </cell>
+          <cell r="B386"/>
           <cell r="C386" t="str">
             <v>RPRO-260505-0663</v>
           </cell>
@@ -30523,6 +31078,7 @@
           <cell r="A388" t="str">
             <v>S-2026-05-12</v>
           </cell>
+          <cell r="B388"/>
           <cell r="C388" t="str">
             <v>RPRO-260505-0802</v>
           </cell>
@@ -30591,6 +31147,7 @@
           <cell r="A389" t="str">
             <v>S-2026-05-13</v>
           </cell>
+          <cell r="B389"/>
           <cell r="C389" t="str">
             <v>RPRO-260505-0803</v>
           </cell>
@@ -30659,6 +31216,7 @@
           <cell r="A390" t="str">
             <v>S-2026-05-14</v>
           </cell>
+          <cell r="B390"/>
           <cell r="C390" t="str">
             <v>RPRO-260506-0394</v>
           </cell>
@@ -30727,6 +31285,7 @@
           <cell r="A391" t="str">
             <v>S-2026-05-15</v>
           </cell>
+          <cell r="B391"/>
           <cell r="C391" t="str">
             <v>RPRO-260506-0395</v>
           </cell>
@@ -30795,6 +31354,7 @@
           <cell r="A392" t="str">
             <v>S-2026-05-16</v>
           </cell>
+          <cell r="B392"/>
           <cell r="C392" t="str">
             <v>RPRO-260506-0396</v>
           </cell>
@@ -30863,6 +31423,7 @@
           <cell r="A393" t="str">
             <v>S-2026-05-17</v>
           </cell>
+          <cell r="B393"/>
           <cell r="C393" t="str">
             <v>RPRO-260506-0397</v>
           </cell>
@@ -30931,6 +31492,7 @@
           <cell r="A394" t="str">
             <v>S-2026-05-18</v>
           </cell>
+          <cell r="B394"/>
           <cell r="C394" t="str">
             <v>RPRO-260506-0415</v>
           </cell>
@@ -30999,6 +31561,7 @@
           <cell r="A395" t="str">
             <v>S-2026-05-19</v>
           </cell>
+          <cell r="B395"/>
           <cell r="C395" t="str">
             <v>RPRO-260508-0581</v>
           </cell>
@@ -31067,6 +31630,7 @@
           <cell r="A396" t="str">
             <v>S-2026-05-20</v>
           </cell>
+          <cell r="B396"/>
           <cell r="C396" t="str">
             <v>RPRO-260508-0582</v>
           </cell>
@@ -31135,6 +31699,7 @@
           <cell r="A397" t="str">
             <v>S-2026-05-21</v>
           </cell>
+          <cell r="B397"/>
           <cell r="C397" t="str">
             <v>RPRO-260508-0583</v>
           </cell>
@@ -31203,6 +31768,7 @@
           <cell r="A398" t="str">
             <v>S-2026-05-22</v>
           </cell>
+          <cell r="B398"/>
           <cell r="C398" t="str">
             <v>RPRO-260508-0584</v>
           </cell>
@@ -31271,6 +31837,7 @@
           <cell r="A399" t="str">
             <v>S-2026-05-23</v>
           </cell>
+          <cell r="B399"/>
           <cell r="C399" t="str">
             <v>RPRO-260508-0585</v>
           </cell>
@@ -31339,6 +31906,7 @@
           <cell r="A400" t="str">
             <v>S-2026-05-24</v>
           </cell>
+          <cell r="B400"/>
           <cell r="C400" t="str">
             <v>RPRO-260508-0586</v>
           </cell>
@@ -31407,6 +31975,7 @@
           <cell r="A401" t="str">
             <v>S-2026-05-25</v>
           </cell>
+          <cell r="B401"/>
           <cell r="C401" t="str">
             <v>RPRO-260508-0587</v>
           </cell>
@@ -31475,6 +32044,7 @@
           <cell r="A402" t="str">
             <v>S-2026-05-26</v>
           </cell>
+          <cell r="B402"/>
           <cell r="C402" t="str">
             <v>RPRO-260508-0588</v>
           </cell>
@@ -31543,6 +32113,7 @@
           <cell r="A403" t="str">
             <v>S-2026-05-27</v>
           </cell>
+          <cell r="B403"/>
           <cell r="C403" t="str">
             <v>RPRO-260512-0580</v>
           </cell>
@@ -31573,6 +32144,7 @@
           <cell r="L403" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M403"/>
           <cell r="N403" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -31608,6 +32180,7 @@
           <cell r="A404" t="str">
             <v>S-2026-05-28</v>
           </cell>
+          <cell r="B404"/>
           <cell r="C404" t="str">
             <v>RPRO-260512-0581</v>
           </cell>
@@ -31638,6 +32211,7 @@
           <cell r="L404" t="str">
             <v>TBS</v>
           </cell>
+          <cell r="M404"/>
           <cell r="N404" t="str">
             <v>INSOLE/ MOLDED</v>
           </cell>
@@ -31673,6 +32247,7 @@
           <cell r="A405" t="str">
             <v>S-2026-05-29</v>
           </cell>
+          <cell r="B405"/>
           <cell r="C405" t="str">
             <v>RPRO-260512-0582</v>
           </cell>
@@ -31741,6 +32316,7 @@
           <cell r="A406" t="str">
             <v>S-2026-05-30</v>
           </cell>
+          <cell r="B406"/>
           <cell r="C406" t="str">
             <v>RPRO-260512-0583</v>
           </cell>
@@ -31809,6 +32385,7 @@
           <cell r="A407" t="str">
             <v>S-2026-05-31</v>
           </cell>
+          <cell r="B407"/>
           <cell r="C407" t="str">
             <v>RPRO-260513-0945</v>
           </cell>
@@ -31877,6 +32454,7 @@
           <cell r="A408" t="str">
             <v>S-2026-05-32</v>
           </cell>
+          <cell r="B408"/>
           <cell r="C408" t="str">
             <v>RPRO-260513-0946</v>
           </cell>
@@ -31945,6 +32523,7 @@
           <cell r="A409" t="str">
             <v>S-2026-05-33</v>
           </cell>
+          <cell r="B409"/>
           <cell r="C409" t="str">
             <v>RPRO-260513-0947</v>
           </cell>
@@ -32013,6 +32592,7 @@
           <cell r="A410" t="str">
             <v>S-2026-05-34</v>
           </cell>
+          <cell r="B410"/>
           <cell r="C410" t="str">
             <v>RPRO-260513-0948</v>
           </cell>
@@ -32152,6 +32732,7 @@
           <cell r="A412" t="str">
             <v>S-2026-05-36</v>
           </cell>
+          <cell r="B412"/>
           <cell r="C412" t="str">
             <v>RPRO-260513-0950</v>
           </cell>
@@ -32220,6 +32801,7 @@
           <cell r="A413" t="str">
             <v>S-2026-05-37</v>
           </cell>
+          <cell r="B413"/>
           <cell r="C413" t="str">
             <v>RPRO-260515-0272</v>
           </cell>
@@ -32288,6 +32870,7 @@
           <cell r="A414" t="str">
             <v>S-2026-05-38</v>
           </cell>
+          <cell r="B414"/>
           <cell r="C414" t="str">
             <v>RPRO-260515-0273</v>
           </cell>
@@ -32356,6 +32939,7 @@
           <cell r="A415" t="str">
             <v>S-2026-05-39</v>
           </cell>
+          <cell r="B415"/>
           <cell r="C415" t="str">
             <v>RPRO-260515-0274</v>
           </cell>
@@ -32424,6 +33008,7 @@
           <cell r="A416" t="str">
             <v>S-2026-05-40</v>
           </cell>
+          <cell r="B416"/>
           <cell r="C416" t="str">
             <v>RPRO-260515-0275</v>
           </cell>
@@ -32492,6 +33077,7 @@
           <cell r="A417" t="str">
             <v>S-2026-05-41</v>
           </cell>
+          <cell r="B417"/>
           <cell r="C417" t="str">
             <v>RPRO-260515-0276</v>
           </cell>
@@ -32560,6 +33146,7 @@
           <cell r="A418" t="str">
             <v>S-2026-05-42</v>
           </cell>
+          <cell r="B418"/>
           <cell r="C418" t="str">
             <v>RPRO-260515-0277</v>
           </cell>
@@ -32628,6 +33215,7 @@
           <cell r="A419" t="str">
             <v>S-2026-05-43</v>
           </cell>
+          <cell r="B419"/>
           <cell r="C419" t="str">
             <v>RPRO-260515-0278</v>
           </cell>
@@ -32696,6 +33284,7 @@
           <cell r="A420" t="str">
             <v>S-2026-05-44</v>
           </cell>
+          <cell r="B420"/>
           <cell r="C420" t="str">
             <v>RPRO-260515-0279</v>
           </cell>
@@ -32764,6 +33353,7 @@
           <cell r="A421" t="str">
             <v>S-2026-05-45</v>
           </cell>
+          <cell r="B421"/>
           <cell r="C421" t="str">
             <v>RPRO-260515-0280</v>
           </cell>
@@ -32832,6 +33422,7 @@
           <cell r="A422" t="str">
             <v>S-2026-05-46</v>
           </cell>
+          <cell r="B422"/>
           <cell r="C422" t="str">
             <v>RPRO-260518-0853</v>
           </cell>
@@ -32900,6 +33491,7 @@
           <cell r="A423" t="str">
             <v>S-2026-05-47</v>
           </cell>
+          <cell r="B423"/>
           <cell r="C423" t="str">
             <v>RPRO-260518-0854</v>
           </cell>
@@ -32968,6 +33560,7 @@
           <cell r="A424" t="str">
             <v>S-2026-05-48</v>
           </cell>
+          <cell r="B424"/>
           <cell r="C424" t="str">
             <v>RPRO-260518-0855</v>
           </cell>
@@ -33036,6 +33629,7 @@
           <cell r="A425" t="str">
             <v>S-2026-05-49</v>
           </cell>
+          <cell r="B425"/>
           <cell r="C425" t="str">
             <v>RPRO-260518-0856</v>
           </cell>
@@ -33317,6 +33911,7 @@
           <cell r="A429" t="str">
             <v>S-2026-05-53</v>
           </cell>
+          <cell r="B429"/>
           <cell r="C429" t="str">
             <v>RPRO-260518-0860</v>
           </cell>
@@ -33385,6 +33980,7 @@
           <cell r="A430" t="str">
             <v>S-2026-05-54</v>
           </cell>
+          <cell r="B430"/>
           <cell r="C430" t="str">
             <v>RPRO-260518-0861</v>
           </cell>
@@ -33453,6 +34049,7 @@
           <cell r="A431" t="str">
             <v>S-2026-05-55</v>
           </cell>
+          <cell r="B431"/>
           <cell r="C431" t="str">
             <v>RPRO-260518-0862</v>
           </cell>
@@ -33521,6 +34118,7 @@
           <cell r="A432" t="str">
             <v>S-2026-05-56</v>
           </cell>
+          <cell r="B432"/>
           <cell r="C432" t="str">
             <v>RPRO-260518-0863</v>
           </cell>
@@ -33589,6 +34187,7 @@
           <cell r="A433" t="str">
             <v>S-2026-05-57</v>
           </cell>
+          <cell r="B433"/>
           <cell r="C433" t="str">
             <v>RPRO-260518-0864</v>
           </cell>
@@ -33657,6 +34256,7 @@
           <cell r="A434" t="str">
             <v>S-2026-05-58</v>
           </cell>
+          <cell r="B434"/>
           <cell r="C434" t="str">
             <v>RPRO-260518-0865</v>
           </cell>
@@ -33725,6 +34325,7 @@
           <cell r="A435" t="str">
             <v>S-2026-05-59</v>
           </cell>
+          <cell r="B435"/>
           <cell r="C435" t="str">
             <v>RPRO-260518-0866</v>
           </cell>
@@ -33793,6 +34394,7 @@
           <cell r="A436" t="str">
             <v>S-2026-05-60</v>
           </cell>
+          <cell r="B436"/>
           <cell r="C436" t="str">
             <v>RPRO-260520-0192</v>
           </cell>
@@ -33861,6 +34463,7 @@
           <cell r="A437" t="str">
             <v>S-2026-05-61</v>
           </cell>
+          <cell r="B437"/>
           <cell r="C437" t="str">
             <v>RPRO-260520-0193</v>
           </cell>
@@ -33929,6 +34532,7 @@
           <cell r="A438" t="str">
             <v>S-2026-05-62</v>
           </cell>
+          <cell r="B438"/>
           <cell r="C438" t="str">
             <v>RPRO-260520-0194</v>
           </cell>
@@ -33997,6 +34601,7 @@
           <cell r="A439" t="str">
             <v>S-2026-05-63</v>
           </cell>
+          <cell r="B439"/>
           <cell r="C439" t="str">
             <v>RPRO-260520-0195</v>
           </cell>
@@ -34065,6 +34670,7 @@
           <cell r="A440" t="str">
             <v>S-2026-05-64</v>
           </cell>
+          <cell r="B440"/>
           <cell r="C440" t="str">
             <v>RPRO-260520-0196</v>
           </cell>
@@ -34133,6 +34739,7 @@
           <cell r="A441" t="str">
             <v>S-2026-05-65</v>
           </cell>
+          <cell r="B441"/>
           <cell r="C441" t="str">
             <v>RPRO-260520-0197</v>
           </cell>
@@ -34201,6 +34808,7 @@
           <cell r="A442" t="str">
             <v>S-2026-05-66</v>
           </cell>
+          <cell r="B442"/>
           <cell r="C442" t="str">
             <v>RPRO-260520-0225</v>
           </cell>
@@ -34269,6 +34877,7 @@
           <cell r="A443" t="str">
             <v>S-2026-05-67</v>
           </cell>
+          <cell r="B443"/>
           <cell r="C443" t="str">
             <v>RPRO-260520-0226</v>
           </cell>
@@ -34337,6 +34946,7 @@
           <cell r="A444" t="str">
             <v>S-2026-05-68</v>
           </cell>
+          <cell r="B444"/>
           <cell r="C444" t="str">
             <v>RPRO-260520-0227</v>
           </cell>
@@ -34405,6 +35015,7 @@
           <cell r="A445" t="str">
             <v>S-2026-05-69</v>
           </cell>
+          <cell r="B445"/>
           <cell r="C445" t="str">
             <v>RPRO-260520-0228</v>
           </cell>
@@ -34473,6 +35084,7 @@
           <cell r="A446" t="str">
             <v>S-2026-05-70</v>
           </cell>
+          <cell r="B446"/>
           <cell r="C446" t="str">
             <v>RPRO-260520-0229</v>
           </cell>
@@ -34541,6 +35153,7 @@
           <cell r="A447" t="str">
             <v>S-2026-05-71</v>
           </cell>
+          <cell r="B447"/>
           <cell r="C447" t="str">
             <v>RPRO-260521-0669</v>
           </cell>
@@ -34609,6 +35222,7 @@
           <cell r="A448" t="str">
             <v>S-2026-05-72</v>
           </cell>
+          <cell r="B448"/>
           <cell r="C448" t="str">
             <v>RPRO-260521-0670</v>
           </cell>
@@ -34677,6 +35291,7 @@
           <cell r="A449" t="str">
             <v>S-2026-05-73</v>
           </cell>
+          <cell r="B449"/>
           <cell r="C449" t="str">
             <v>RPRO-260523-0221</v>
           </cell>
@@ -34745,6 +35360,7 @@
           <cell r="A450" t="str">
             <v>S-2026-05-74</v>
           </cell>
+          <cell r="B450"/>
           <cell r="C450" t="str">
             <v>RPRO-260523-0222</v>
           </cell>
@@ -34813,6 +35429,7 @@
           <cell r="A451" t="str">
             <v>S-2026-05-75</v>
           </cell>
+          <cell r="B451"/>
           <cell r="C451" t="str">
             <v>RPRO-260523-0223</v>
           </cell>
@@ -34881,6 +35498,7 @@
           <cell r="A452" t="str">
             <v>S-2026-05-76</v>
           </cell>
+          <cell r="B452"/>
           <cell r="C452" t="str">
             <v>RPRO-260526-0394</v>
           </cell>
@@ -34949,6 +35567,7 @@
           <cell r="A453" t="str">
             <v>S-2026-05-77</v>
           </cell>
+          <cell r="B453"/>
           <cell r="C453" t="str">
             <v>RPRO-260526-0395</v>
           </cell>
@@ -35017,6 +35636,7 @@
           <cell r="A454" t="str">
             <v>S-2026-05-78</v>
           </cell>
+          <cell r="B454"/>
           <cell r="C454" t="str">
             <v>RPRO-260526-0396</v>
           </cell>
@@ -35085,6 +35705,7 @@
           <cell r="A455" t="str">
             <v>S-2026-05-79</v>
           </cell>
+          <cell r="B455"/>
           <cell r="C455" t="str">
             <v>RPRO-260526-0397</v>
           </cell>
@@ -35153,6 +35774,7 @@
           <cell r="A456" t="str">
             <v>S-2026-05-80</v>
           </cell>
+          <cell r="B456"/>
           <cell r="C456" t="str">
             <v>RPRO-260526-0398</v>
           </cell>
@@ -35221,6 +35843,7 @@
           <cell r="A457" t="str">
             <v>S-2026-05-81</v>
           </cell>
+          <cell r="B457"/>
           <cell r="C457" t="str">
             <v>RPRO-260526-0399</v>
           </cell>
@@ -35360,6 +35983,7 @@
           <cell r="A459" t="str">
             <v>S-2026-05-83</v>
           </cell>
+          <cell r="B459"/>
           <cell r="C459" t="str">
             <v>RPRO-260526-0401</v>
           </cell>
@@ -35499,6 +36123,7 @@
           <cell r="A461" t="str">
             <v>S-2026-05-85</v>
           </cell>
+          <cell r="B461"/>
           <cell r="C461" t="str">
             <v>RPRO-260526-0402</v>
           </cell>
@@ -35567,6 +36192,7 @@
           <cell r="A462" t="str">
             <v>S-2026-05-86</v>
           </cell>
+          <cell r="B462"/>
           <cell r="C462" t="str">
             <v>RPRO-260527-0578</v>
           </cell>
@@ -35635,6 +36261,7 @@
           <cell r="A463" t="str">
             <v>S-2026-05-87</v>
           </cell>
+          <cell r="B463"/>
           <cell r="C463" t="str">
             <v>RPRO-260527-0579</v>
           </cell>
@@ -35703,6 +36330,7 @@
           <cell r="A464" t="str">
             <v>S-2026-05-88</v>
           </cell>
+          <cell r="B464"/>
           <cell r="C464" t="str">
             <v>RPRO-260527-0580</v>
           </cell>
@@ -35771,6 +36399,7 @@
           <cell r="A465" t="str">
             <v>S-2026-05-89</v>
           </cell>
+          <cell r="B465"/>
           <cell r="C465" t="str">
             <v>RPRO-260527-0581</v>
           </cell>
@@ -35839,6 +36468,7 @@
           <cell r="A466" t="str">
             <v>S-2026-05-90</v>
           </cell>
+          <cell r="B466"/>
           <cell r="C466" t="str">
             <v>RPRO-260527-0582</v>
           </cell>
@@ -35907,6 +36537,7 @@
           <cell r="A467" t="str">
             <v>S-2026-05-91</v>
           </cell>
+          <cell r="B467"/>
           <cell r="C467" t="str">
             <v>RPRO-260527-0583</v>
           </cell>
@@ -35975,6 +36606,7 @@
           <cell r="A468" t="str">
             <v>S-2026-05-92</v>
           </cell>
+          <cell r="B468"/>
           <cell r="C468" t="str">
             <v>RPRO-260528-0001</v>
           </cell>
@@ -36043,6 +36675,7 @@
           <cell r="A469" t="str">
             <v>S-2026-05-93</v>
           </cell>
+          <cell r="B469"/>
           <cell r="C469" t="str">
             <v>RPRO-260529-0339</v>
           </cell>
@@ -36111,6 +36744,7 @@
           <cell r="A470" t="str">
             <v>S-2026-05-94</v>
           </cell>
+          <cell r="B470"/>
           <cell r="C470" t="str">
             <v>RPRO-260529-0340</v>
           </cell>
@@ -36250,6 +36884,7 @@
           <cell r="A472" t="str">
             <v>S-2026-05-96</v>
           </cell>
+          <cell r="B472"/>
           <cell r="C472" t="str">
             <v>RPRO-260529-0342</v>
           </cell>
@@ -36318,6 +36953,7 @@
           <cell r="A473" t="str">
             <v>S-2026-05-97</v>
           </cell>
+          <cell r="B473"/>
           <cell r="C473" t="str">
             <v>RPRO-260529-0343</v>
           </cell>
@@ -36528,6 +37164,7 @@
           <cell r="A476" t="str">
             <v>S-2026-05-100</v>
           </cell>
+          <cell r="B476"/>
           <cell r="C476" t="str">
             <v>RPRO-260529-0346</v>
           </cell>
@@ -36596,6 +37233,7 @@
           <cell r="A477" t="str">
             <v>S-2026-05-102</v>
           </cell>
+          <cell r="B477"/>
           <cell r="C477" t="str">
             <v>RPRO-260601-0847</v>
           </cell>
@@ -36664,6 +37302,7 @@
           <cell r="A478" t="str">
             <v>S-2026-05-103</v>
           </cell>
+          <cell r="B478"/>
           <cell r="C478" t="str">
             <v>RPRO-260601-0848</v>
           </cell>
@@ -36732,6 +37371,7 @@
           <cell r="A479" t="str">
             <v>S-2026-05-104</v>
           </cell>
+          <cell r="B479"/>
           <cell r="C479" t="str">
             <v>RPRO-260601-0849</v>
           </cell>
@@ -36800,6 +37440,7 @@
           <cell r="A480" t="str">
             <v>S-2026-05-105</v>
           </cell>
+          <cell r="B480"/>
           <cell r="C480" t="str">
             <v>RPRO-260601-0850</v>
           </cell>
@@ -36868,6 +37509,7 @@
           <cell r="A481" t="str">
             <v>S-2026-05-106</v>
           </cell>
+          <cell r="B481"/>
           <cell r="C481" t="str">
             <v>RPRO-260601-0851</v>
           </cell>
@@ -36936,6 +37578,7 @@
           <cell r="A482" t="str">
             <v>S-2026-06-01</v>
           </cell>
+          <cell r="B482"/>
           <cell r="C482" t="str">
             <v>RPRO-260602-0720</v>
           </cell>
@@ -37005,6 +37648,7 @@
           <cell r="A483" t="str">
             <v>S-2026-06-02</v>
           </cell>
+          <cell r="B483"/>
           <cell r="C483" t="str">
             <v>RPRO-260602-0721</v>
           </cell>
@@ -37073,6 +37717,7 @@
           <cell r="A484" t="str">
             <v>S-2026-06-03</v>
           </cell>
+          <cell r="B484"/>
           <cell r="C484" t="str">
             <v>RPRO-260602-0722</v>
           </cell>
@@ -37141,6 +37786,7 @@
           <cell r="A485" t="str">
             <v>S-2026-06-04</v>
           </cell>
+          <cell r="B485"/>
           <cell r="C485" t="str">
             <v>RPRO-260602-0723</v>
           </cell>
@@ -37209,6 +37855,7 @@
           <cell r="A486" t="str">
             <v>S-2026-06-05</v>
           </cell>
+          <cell r="B486"/>
           <cell r="C486" t="str">
             <v>RPRO-260602-0724</v>
           </cell>
@@ -37277,6 +37924,7 @@
           <cell r="A487" t="str">
             <v>S-2026-06-06</v>
           </cell>
+          <cell r="B487"/>
           <cell r="C487" t="str">
             <v>RPRO-260602-0725</v>
           </cell>
@@ -37345,6 +37993,7 @@
           <cell r="A488" t="str">
             <v>S-2026-06-07</v>
           </cell>
+          <cell r="B488"/>
           <cell r="C488" t="str">
             <v>RPRO-260602-0726</v>
           </cell>
@@ -37413,6 +38062,7 @@
           <cell r="A489" t="str">
             <v>S-2026-06-08</v>
           </cell>
+          <cell r="B489"/>
           <cell r="C489" t="str">
             <v>RPRO-260602-0727</v>
           </cell>
@@ -37552,6 +38202,7 @@
           <cell r="A491" t="str">
             <v>S-2026-06-10</v>
           </cell>
+          <cell r="B491"/>
           <cell r="C491" t="str">
             <v>RPRO-260603-0482</v>
           </cell>
@@ -37620,6 +38271,7 @@
           <cell r="A492" t="str">
             <v>S-2026-06-11</v>
           </cell>
+          <cell r="B492"/>
           <cell r="C492" t="str">
             <v>RPRO-260603-0483</v>
           </cell>
@@ -37688,6 +38340,7 @@
           <cell r="A493" t="str">
             <v>S-2026-06-12</v>
           </cell>
+          <cell r="B493"/>
           <cell r="C493" t="str">
             <v>RPRO-260603-0484</v>
           </cell>
@@ -37827,6 +38480,7 @@
           <cell r="A495" t="str">
             <v>S-2026-06-15</v>
           </cell>
+          <cell r="B495"/>
           <cell r="C495" t="str">
             <v>RPRO-260604-0522</v>
           </cell>
@@ -37895,6 +38549,7 @@
           <cell r="A496" t="str">
             <v>L-2026-06-01</v>
           </cell>
+          <cell r="B496"/>
           <cell r="C496" t="str">
             <v>RPRO-260604-0523</v>
           </cell>
@@ -37925,6 +38580,8 @@
           <cell r="L496" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M496"/>
+          <cell r="N496"/>
           <cell r="O496" t="str">
             <v>Lab test</v>
           </cell>
@@ -37957,6 +38614,7 @@
           <cell r="A497" t="str">
             <v>L-2026-06-02</v>
           </cell>
+          <cell r="B497"/>
           <cell r="C497" t="str">
             <v>RPRO-260604-0524</v>
           </cell>
@@ -37987,6 +38645,8 @@
           <cell r="L497" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M497"/>
+          <cell r="N497"/>
           <cell r="O497" t="str">
             <v>Lab test</v>
           </cell>
@@ -38019,6 +38679,7 @@
           <cell r="A498" t="str">
             <v>L-2026-06-03</v>
           </cell>
+          <cell r="B498"/>
           <cell r="C498" t="str">
             <v>RPRO-260604-0525</v>
           </cell>
@@ -38049,6 +38710,8 @@
           <cell r="L498" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M498"/>
+          <cell r="N498"/>
           <cell r="O498" t="str">
             <v>Lab test</v>
           </cell>
@@ -38081,6 +38744,7 @@
           <cell r="A499" t="str">
             <v>L-2026-06-04</v>
           </cell>
+          <cell r="B499"/>
           <cell r="C499" t="str">
             <v>RPRO-260604-0526</v>
           </cell>
@@ -38111,6 +38775,8 @@
           <cell r="L499" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M499"/>
+          <cell r="N499"/>
           <cell r="O499" t="str">
             <v>Lab test</v>
           </cell>
@@ -38143,6 +38809,7 @@
           <cell r="A500" t="str">
             <v>L-2026-06-05</v>
           </cell>
+          <cell r="B500"/>
           <cell r="C500" t="str">
             <v>RPRO-260604-0527</v>
           </cell>
@@ -38173,6 +38840,8 @@
           <cell r="L500" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M500"/>
+          <cell r="N500"/>
           <cell r="O500" t="str">
             <v>Lab test</v>
           </cell>
@@ -38205,6 +38874,7 @@
           <cell r="A501" t="str">
             <v>L-2026-06-06</v>
           </cell>
+          <cell r="B501"/>
           <cell r="C501" t="str">
             <v>RPRO-260604-0528</v>
           </cell>
@@ -38235,6 +38905,8 @@
           <cell r="L501" t="str">
             <v>NIKE-POU CHEN VÀ CONVERSE</v>
           </cell>
+          <cell r="M501"/>
+          <cell r="N501"/>
           <cell r="O501" t="str">
             <v>Lab test</v>
           </cell>
@@ -38267,6 +38939,7 @@
           <cell r="A502" t="str">
             <v>L-2026-06-07</v>
           </cell>
+          <cell r="B502"/>
           <cell r="C502" t="str">
             <v>RPRO-260604-0529</v>
           </cell>
@@ -38297,6 +38970,8 @@
           <cell r="L502" t="str">
             <v>SHYANG HUNG TAH</v>
           </cell>
+          <cell r="M502"/>
+          <cell r="N502"/>
           <cell r="O502" t="str">
             <v>Lab test</v>
           </cell>
@@ -38329,6 +39004,7 @@
           <cell r="A503" t="str">
             <v>S-2026-06-16</v>
           </cell>
+          <cell r="B503"/>
           <cell r="C503" t="str">
             <v>RPRO-260605-0678</v>
           </cell>
@@ -38397,6 +39073,7 @@
           <cell r="A504" t="str">
             <v>S-2026-06-17</v>
           </cell>
+          <cell r="B504"/>
           <cell r="C504" t="str">
             <v>RPRO-260605-0679</v>
           </cell>
@@ -38465,6 +39142,7 @@
           <cell r="A505" t="str">
             <v>S-2026-06-18</v>
           </cell>
+          <cell r="B505"/>
           <cell r="C505" t="str">
             <v>RPRO-260605-0680</v>
           </cell>
@@ -38533,6 +39211,7 @@
           <cell r="A506" t="str">
             <v>S-2026-06-19</v>
           </cell>
+          <cell r="B506"/>
           <cell r="C506" t="str">
             <v>RPRO-260605-0681</v>
           </cell>
@@ -38601,6 +39280,7 @@
           <cell r="A507" t="str">
             <v>S-2026-06-20</v>
           </cell>
+          <cell r="B507"/>
           <cell r="C507" t="str">
             <v>RPRO-260605-0682</v>
           </cell>
@@ -38669,6 +39349,7 @@
           <cell r="A508" t="str">
             <v>S-2026-06-21</v>
           </cell>
+          <cell r="B508"/>
           <cell r="C508" t="str">
             <v>RPRO-260605-0683</v>
           </cell>
@@ -38737,6 +39418,7 @@
           <cell r="A509" t="str">
             <v>S-2026-06-22</v>
           </cell>
+          <cell r="B509"/>
           <cell r="C509" t="str">
             <v>RPRO-260605-0684</v>
           </cell>
@@ -38805,6 +39487,7 @@
           <cell r="A510" t="str">
             <v>S-2026-06-23</v>
           </cell>
+          <cell r="B510"/>
           <cell r="C510" t="str">
             <v>RPRO-260605-0685</v>
           </cell>
@@ -38873,6 +39556,7 @@
           <cell r="A511" t="str">
             <v>S-2026-06-24</v>
           </cell>
+          <cell r="B511"/>
           <cell r="C511" t="str">
             <v>RPRO-260605-0686</v>
           </cell>
@@ -38941,6 +39625,7 @@
           <cell r="A512" t="str">
             <v>S-2026-06-25</v>
           </cell>
+          <cell r="B512"/>
           <cell r="C512" t="str">
             <v>RPRO-260606-0217</v>
           </cell>
@@ -39009,6 +39694,7 @@
           <cell r="A513" t="str">
             <v>S-2026-06-26</v>
           </cell>
+          <cell r="B513"/>
           <cell r="C513" t="str">
             <v>RPRO-260608-1016</v>
           </cell>
@@ -39077,6 +39763,7 @@
           <cell r="A514" t="str">
             <v>S-2026-06-27</v>
           </cell>
+          <cell r="B514"/>
           <cell r="C514" t="str">
             <v>RPRO-260608-1017</v>
           </cell>
@@ -39145,6 +39832,7 @@
           <cell r="A515" t="str">
             <v>S-2026-06-28</v>
           </cell>
+          <cell r="B515"/>
           <cell r="C515" t="str">
             <v>RPRO-260608-1018</v>
           </cell>
@@ -39213,6 +39901,7 @@
           <cell r="A516" t="str">
             <v>S-2026-06-29</v>
           </cell>
+          <cell r="B516"/>
           <cell r="C516" t="str">
             <v>RPRO-260608-1019</v>
           </cell>
@@ -39281,6 +39970,7 @@
           <cell r="A517" t="str">
             <v>S-2026-06-30</v>
           </cell>
+          <cell r="B517"/>
           <cell r="C517" t="str">
             <v>RPRO-260608-1020</v>
           </cell>
@@ -39324,16 +40014,16 @@
             <v>46181</v>
           </cell>
           <cell r="Q517">
-            <v>46188</v>
+            <v>46189</v>
           </cell>
           <cell r="R517">
-            <v>46185</v>
+            <v>46186</v>
           </cell>
           <cell r="S517">
             <v>6</v>
           </cell>
           <cell r="T517">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="U517">
             <v>11</v>
@@ -39346,30 +40036,926 @@
           </cell>
         </row>
         <row r="518">
-          <cell r="E518"/>
+          <cell r="A518" t="str">
+            <v>S-2026-06-31</v>
+          </cell>
+          <cell r="B518"/>
+          <cell r="C518" t="str">
+            <v>RPRO-260609-0497</v>
+          </cell>
+          <cell r="D518" t="str">
+            <v>PUR2606080003S</v>
+          </cell>
+          <cell r="E518" t="str">
+            <v>BDB-000116</v>
+          </cell>
+          <cell r="F518" t="str">
+            <v>PVN-002530</v>
+          </cell>
+          <cell r="G518" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H518">
+            <v>10</v>
+          </cell>
+          <cell r="I518">
+            <v>10</v>
+          </cell>
           <cell r="J518">
             <v>0</v>
           </cell>
           <cell r="K518">
-            <v>0</v>
+            <v>10</v>
+          </cell>
+          <cell r="L518" t="str">
+            <v>KATE SPADE</v>
+          </cell>
+          <cell r="M518" t="str">
+            <v>SSO-2606-00328</v>
+          </cell>
+          <cell r="N518" t="str">
+            <v>sheet</v>
+          </cell>
+          <cell r="O518" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P518">
+            <v>46181</v>
+          </cell>
+          <cell r="Q518">
+            <v>46189</v>
+          </cell>
+          <cell r="R518">
+            <v>46186</v>
+          </cell>
+          <cell r="S518">
+            <v>6</v>
+          </cell>
+          <cell r="T518">
+            <v>8</v>
+          </cell>
+          <cell r="U518">
+            <v>3</v>
+          </cell>
+          <cell r="V518">
+            <v>2.1739999999999999E-2</v>
+          </cell>
+          <cell r="W518">
+            <v>1</v>
           </cell>
         </row>
         <row r="519">
-          <cell r="E519"/>
+          <cell r="A519" t="str">
+            <v>S-2026-06-32</v>
+          </cell>
+          <cell r="B519"/>
+          <cell r="C519" t="str">
+            <v>RPRO-260609-0498</v>
+          </cell>
+          <cell r="D519" t="str">
+            <v>PUR2606080003S</v>
+          </cell>
+          <cell r="E519" t="str">
+            <v>BDB-000116</v>
+          </cell>
+          <cell r="F519" t="str">
+            <v>PVN-002710</v>
+          </cell>
+          <cell r="G519" t="str">
+            <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 5mm</v>
+          </cell>
+          <cell r="H519">
+            <v>10</v>
+          </cell>
+          <cell r="I519">
+            <v>10</v>
+          </cell>
           <cell r="J519">
             <v>0</v>
           </cell>
           <cell r="K519">
-            <v>0</v>
+            <v>10</v>
+          </cell>
+          <cell r="L519" t="str">
+            <v>KATE SPADE</v>
+          </cell>
+          <cell r="M519" t="str">
+            <v>SSO-2606-00328</v>
+          </cell>
+          <cell r="N519" t="str">
+            <v>sheet</v>
+          </cell>
+          <cell r="O519" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P519">
+            <v>46181</v>
+          </cell>
+          <cell r="Q519">
+            <v>46189</v>
+          </cell>
+          <cell r="R519">
+            <v>46186</v>
+          </cell>
+          <cell r="S519">
+            <v>6</v>
+          </cell>
+          <cell r="T519">
+            <v>8</v>
+          </cell>
+          <cell r="U519">
+            <v>5</v>
+          </cell>
+          <cell r="V519">
+            <v>3.5709999999999999E-2</v>
+          </cell>
+          <cell r="W519">
+            <v>1</v>
           </cell>
         </row>
         <row r="520">
+          <cell r="A520" t="str">
+            <v>S-2026-06-33</v>
+          </cell>
+          <cell r="B520"/>
+          <cell r="C520" t="str">
+            <v>RPRO-260609-0499</v>
+          </cell>
+          <cell r="D520" t="str">
+            <v>PUR2606090001S</v>
+          </cell>
+          <cell r="E520" t="str">
+            <v>BDB-000243</v>
+          </cell>
+          <cell r="F520" t="str">
+            <v>PVN-004444</v>
+          </cell>
+          <cell r="G520" t="str">
+            <v>OrthoLite Ultra-Hybrid GREEN/16-5932TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H520">
+            <v>70</v>
+          </cell>
+          <cell r="I520">
+            <v>70</v>
+          </cell>
           <cell r="J520">
             <v>0</v>
           </cell>
           <cell r="K520">
+            <v>70</v>
+          </cell>
+          <cell r="L520" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M520" t="str">
+            <v>SSO-2606-00325 - URGENT (6-17)</v>
+          </cell>
+          <cell r="N520" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O520" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P520">
+            <v>46182</v>
+          </cell>
+          <cell r="Q520">
+            <v>46190</v>
+          </cell>
+          <cell r="R520">
+            <v>46187</v>
+          </cell>
+          <cell r="S520">
+            <v>6</v>
+          </cell>
+          <cell r="T520">
+            <v>8</v>
+          </cell>
+          <cell r="U520" t="str">
+            <v/>
+          </cell>
+          <cell r="V520">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W520">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="521">
+          <cell r="A521" t="str">
+            <v>S-2026-06-34</v>
+          </cell>
+          <cell r="B521"/>
+          <cell r="C521" t="str">
+            <v>RPRO-260609-0500</v>
+          </cell>
+          <cell r="D521" t="str">
+            <v>PUR2606090001S</v>
+          </cell>
+          <cell r="E521" t="str">
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F521" t="str">
+            <v>PVN-003298</v>
+          </cell>
+          <cell r="G521" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H521">
+            <v>100</v>
+          </cell>
+          <cell r="I521">
+            <v>100</v>
+          </cell>
+          <cell r="J521">
             <v>0</v>
           </cell>
+          <cell r="K521">
+            <v>100</v>
+          </cell>
+          <cell r="L521" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M521" t="str">
+            <v>SSO-2606-00327  - URGENT (6-17)</v>
+          </cell>
+          <cell r="N521" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O521" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P521">
+            <v>46182</v>
+          </cell>
+          <cell r="Q521">
+            <v>46190</v>
+          </cell>
+          <cell r="R521">
+            <v>46187</v>
+          </cell>
+          <cell r="S521">
+            <v>6</v>
+          </cell>
+          <cell r="T521">
+            <v>8</v>
+          </cell>
+          <cell r="U521">
+            <v>4</v>
+          </cell>
+          <cell r="V521">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W521">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="522">
+          <cell r="A522" t="str">
+            <v>S-2026-06-35</v>
+          </cell>
+          <cell r="B522"/>
+          <cell r="C522" t="str">
+            <v>RPRO-260609-0501</v>
+          </cell>
+          <cell r="D522" t="str">
+            <v>PUR2606090001S</v>
+          </cell>
+          <cell r="E522" t="str">
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F522" t="str">
+            <v>PVN-003299</v>
+          </cell>
+          <cell r="G522" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H522">
+            <v>50</v>
+          </cell>
+          <cell r="I522">
+            <v>50</v>
+          </cell>
+          <cell r="J522">
+            <v>0</v>
+          </cell>
+          <cell r="K522">
+            <v>50</v>
+          </cell>
+          <cell r="L522" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M522" t="str">
+            <v>SSO-2606-00327  - URGENT (6-17)</v>
+          </cell>
+          <cell r="N522" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O522" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P522">
+            <v>46182</v>
+          </cell>
+          <cell r="Q522">
+            <v>46190</v>
+          </cell>
+          <cell r="R522">
+            <v>46187</v>
+          </cell>
+          <cell r="S522">
+            <v>6</v>
+          </cell>
+          <cell r="T522">
+            <v>8</v>
+          </cell>
+          <cell r="U522">
+            <v>3</v>
+          </cell>
+          <cell r="V522">
+            <v>2.1739999999999999E-2</v>
+          </cell>
+          <cell r="W522">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="523">
+          <cell r="A523" t="str">
+            <v>S-2026-06-36</v>
+          </cell>
+          <cell r="B523"/>
+          <cell r="C523" t="str">
+            <v>RPRO-260609-0502</v>
+          </cell>
+          <cell r="D523" t="str">
+            <v>PUR-202606090002S</v>
+          </cell>
+          <cell r="E523" t="str">
+            <v>BDB-000015</v>
+          </cell>
+          <cell r="F523" t="str">
+            <v>PVN-000437</v>
+          </cell>
+          <cell r="G523" t="str">
+            <v>OrthoLite Regular AIR BLUE/16-4134TPX 0.13D 25+/-4 Asker C 1.1M 2M 3.5mm</v>
+          </cell>
+          <cell r="H523">
+            <v>20</v>
+          </cell>
+          <cell r="I523">
+            <v>20</v>
+          </cell>
+          <cell r="J523">
+            <v>0</v>
+          </cell>
+          <cell r="K523">
+            <v>20</v>
+          </cell>
+          <cell r="L523" t="str">
+            <v>ASICS</v>
+          </cell>
+          <cell r="M523" t="str">
+            <v>Sample
+URGENT (6-15)</v>
+          </cell>
+          <cell r="N523" t="str">
+            <v>DIE-CUT</v>
+          </cell>
+          <cell r="O523" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P523">
+            <v>46182</v>
+          </cell>
+          <cell r="Q523">
+            <v>46188</v>
+          </cell>
+          <cell r="R523">
+            <v>46185</v>
+          </cell>
+          <cell r="S523">
+            <v>6</v>
+          </cell>
+          <cell r="T523">
+            <v>6</v>
+          </cell>
+          <cell r="U523">
+            <v>3.5</v>
+          </cell>
+          <cell r="V523">
+            <v>2.5000000000000001E-2</v>
+          </cell>
+          <cell r="W523">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="524">
+          <cell r="A524" t="str">
+            <v>S-2026-06-37</v>
+          </cell>
+          <cell r="B524"/>
+          <cell r="C524" t="str">
+            <v>RPRO-260609-0503</v>
+          </cell>
+          <cell r="D524" t="str">
+            <v>PUR-202606090002S</v>
+          </cell>
+          <cell r="E524" t="str">
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F524" t="str">
+            <v>PVN-002973</v>
+          </cell>
+          <cell r="G524" t="str">
+            <v>UltraLite-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+          </cell>
+          <cell r="H524">
+            <v>50</v>
+          </cell>
+          <cell r="I524">
+            <v>50</v>
+          </cell>
+          <cell r="J524">
+            <v>0</v>
+          </cell>
+          <cell r="K524">
+            <v>50</v>
+          </cell>
+          <cell r="L524" t="str">
+            <v>SALOMON</v>
+          </cell>
+          <cell r="M524" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N524" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O524" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P524">
+            <v>46182</v>
+          </cell>
+          <cell r="Q524">
+            <v>46190</v>
+          </cell>
+          <cell r="R524">
+            <v>46187</v>
+          </cell>
+          <cell r="S524">
+            <v>6</v>
+          </cell>
+          <cell r="T524">
+            <v>8</v>
+          </cell>
+          <cell r="U524">
+            <v>4.5</v>
+          </cell>
+          <cell r="V524">
+            <v>3.2259999999999997E-2</v>
+          </cell>
+          <cell r="W524">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="525">
+          <cell r="A525" t="str">
+            <v>S-2026-06-38</v>
+          </cell>
+          <cell r="B525"/>
+          <cell r="C525" t="str">
+            <v>RPRO-260609-0504</v>
+          </cell>
+          <cell r="D525" t="str">
+            <v>PUR2606090003S</v>
+          </cell>
+          <cell r="E525" t="str">
+            <v>BDB-000348</v>
+          </cell>
+          <cell r="F525" t="str">
+            <v>PVN-004195</v>
+          </cell>
+          <cell r="G525" t="str">
+            <v>OrthoLite IMPERIAL SEEDPEARL/12-0703TPX Flat Sheet 0.22D 25+/-4 Asker C 1.1M 1.47M 4mm</v>
+          </cell>
+          <cell r="H525">
+            <v>250</v>
+          </cell>
+          <cell r="I525">
+            <v>250</v>
+          </cell>
+          <cell r="J525">
+            <v>0</v>
+          </cell>
+          <cell r="K525">
+            <v>250</v>
+          </cell>
+          <cell r="L525" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M525" t="str">
+            <v>SSO-2606-00371/00379 - URGENT (6-13)</v>
+          </cell>
+          <cell r="N525" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O525" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P525">
+            <v>46182</v>
+          </cell>
+          <cell r="Q525">
+            <v>46189</v>
+          </cell>
+          <cell r="R525">
+            <v>46186</v>
+          </cell>
+          <cell r="S525">
+            <v>6</v>
+          </cell>
+          <cell r="T525">
+            <v>7</v>
+          </cell>
+          <cell r="U525">
+            <v>4</v>
+          </cell>
+          <cell r="V525">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W525">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="526">
+          <cell r="A526" t="str">
+            <v>S-2026-06-39</v>
+          </cell>
+          <cell r="B526"/>
+          <cell r="C526" t="str">
+            <v>RPRO-260609-0505</v>
+          </cell>
+          <cell r="D526" t="str">
+            <v>PUR2606090003S</v>
+          </cell>
+          <cell r="E526" t="str">
+            <v>BDB-000058</v>
+          </cell>
+          <cell r="F526" t="str">
+            <v>PVN-001319</v>
+          </cell>
+          <cell r="G526" t="str">
+            <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 5mm</v>
+          </cell>
+          <cell r="H526">
+            <v>50</v>
+          </cell>
+          <cell r="I526">
+            <v>50</v>
+          </cell>
+          <cell r="J526">
+            <v>0</v>
+          </cell>
+          <cell r="K526">
+            <v>50</v>
+          </cell>
+          <cell r="L526" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M526" t="str">
+            <v>SSO-2606-00358/00359 - URGENT (6-16)</v>
+          </cell>
+          <cell r="N526" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O526" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P526">
+            <v>46182</v>
+          </cell>
+          <cell r="Q526">
+            <v>46190</v>
+          </cell>
+          <cell r="R526">
+            <v>46187</v>
+          </cell>
+          <cell r="S526">
+            <v>6</v>
+          </cell>
+          <cell r="T526">
+            <v>8</v>
+          </cell>
+          <cell r="U526">
+            <v>5</v>
+          </cell>
+          <cell r="V526">
+            <v>3.5709999999999999E-2</v>
+          </cell>
+          <cell r="W526">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="527">
+          <cell r="A527" t="str">
+            <v>S-2026-06-40</v>
+          </cell>
+          <cell r="B527"/>
+          <cell r="C527" t="str">
+            <v>RPRO-260609-0506</v>
+          </cell>
+          <cell r="D527" t="str">
+            <v>PUR2606090003S</v>
+          </cell>
+          <cell r="E527" t="str">
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F527" t="str">
+            <v>PVN-003299</v>
+          </cell>
+          <cell r="G527" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H527">
+            <v>50</v>
+          </cell>
+          <cell r="I527">
+            <v>50</v>
+          </cell>
+          <cell r="J527">
+            <v>0</v>
+          </cell>
+          <cell r="K527">
+            <v>50</v>
+          </cell>
+          <cell r="L527" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M527" t="str">
+            <v>SSO-2606-00375/00400 - URGENT (6-16)</v>
+          </cell>
+          <cell r="N527" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O527" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P527">
+            <v>46182</v>
+          </cell>
+          <cell r="Q527">
+            <v>46190</v>
+          </cell>
+          <cell r="R527">
+            <v>46187</v>
+          </cell>
+          <cell r="S527">
+            <v>6</v>
+          </cell>
+          <cell r="T527">
+            <v>8</v>
+          </cell>
+          <cell r="U527">
+            <v>3</v>
+          </cell>
+          <cell r="V527">
+            <v>2.1739999999999999E-2</v>
+          </cell>
+          <cell r="W527">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="528">
+          <cell r="A528" t="str">
+            <v>S-2026-06-41</v>
+          </cell>
+          <cell r="B528"/>
+          <cell r="C528" t="str">
+            <v>RPRO-260609-0507</v>
+          </cell>
+          <cell r="D528" t="str">
+            <v>PUR2606090003S</v>
+          </cell>
+          <cell r="E528" t="str">
+            <v>BDB-000200</v>
+          </cell>
+          <cell r="F528" t="str">
+            <v>PVN-003425</v>
+          </cell>
+          <cell r="G528" t="str">
+            <v>OrthoLite Ultra SEEDPEARL/12-0703TPX Flat Sheet 0.085D 78-90 Asker F 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H528">
+            <v>30</v>
+          </cell>
+          <cell r="I528">
+            <v>30</v>
+          </cell>
+          <cell r="J528">
+            <v>0</v>
+          </cell>
+          <cell r="K528">
+            <v>30</v>
+          </cell>
+          <cell r="L528" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M528" t="str">
+            <v>SSO-2606-00377 - URGENT (6-16)</v>
+          </cell>
+          <cell r="N528" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O528" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P528">
+            <v>46182</v>
+          </cell>
+          <cell r="Q528">
+            <v>46190</v>
+          </cell>
+          <cell r="R528">
+            <v>46187</v>
+          </cell>
+          <cell r="S528">
+            <v>6</v>
+          </cell>
+          <cell r="T528">
+            <v>8</v>
+          </cell>
+          <cell r="U528">
+            <v>4</v>
+          </cell>
+          <cell r="V528">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W528">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="529">
+          <cell r="A529"/>
+          <cell r="B529"/>
+          <cell r="C529"/>
+          <cell r="D529"/>
+          <cell r="E529" t="str">
+            <v/>
+          </cell>
+          <cell r="F529"/>
+          <cell r="G529"/>
+          <cell r="H529"/>
+          <cell r="I529"/>
+          <cell r="J529"/>
+          <cell r="K529"/>
+          <cell r="L529"/>
+          <cell r="M529"/>
+          <cell r="N529"/>
+          <cell r="O529"/>
+          <cell r="P529"/>
+          <cell r="Q529"/>
+          <cell r="R529"/>
+          <cell r="S529"/>
+          <cell r="T529"/>
+          <cell r="U529"/>
+          <cell r="V529"/>
+          <cell r="W529"/>
+        </row>
+        <row r="530">
+          <cell r="A530"/>
+          <cell r="B530"/>
+          <cell r="C530"/>
+          <cell r="D530"/>
+          <cell r="E530" t="str">
+            <v/>
+          </cell>
+          <cell r="F530"/>
+          <cell r="G530"/>
+          <cell r="H530"/>
+          <cell r="I530"/>
+          <cell r="J530"/>
+          <cell r="K530"/>
+          <cell r="L530"/>
+          <cell r="M530"/>
+          <cell r="N530"/>
+          <cell r="O530"/>
+          <cell r="P530"/>
+          <cell r="Q530"/>
+          <cell r="R530"/>
+          <cell r="S530"/>
+          <cell r="T530"/>
+          <cell r="U530"/>
+          <cell r="V530"/>
+          <cell r="W530"/>
+        </row>
+        <row r="531">
+          <cell r="A531"/>
+          <cell r="B531"/>
+          <cell r="C531"/>
+          <cell r="D531"/>
+          <cell r="E531" t="str">
+            <v/>
+          </cell>
+          <cell r="F531"/>
+          <cell r="G531"/>
+          <cell r="H531"/>
+          <cell r="I531"/>
+          <cell r="J531"/>
+          <cell r="K531"/>
+          <cell r="L531"/>
+          <cell r="M531"/>
+          <cell r="N531"/>
+          <cell r="O531"/>
+          <cell r="P531"/>
+          <cell r="Q531"/>
+          <cell r="R531"/>
+          <cell r="S531"/>
+          <cell r="T531"/>
+          <cell r="U531"/>
+          <cell r="V531"/>
+          <cell r="W531"/>
+        </row>
+        <row r="532">
+          <cell r="A532"/>
+          <cell r="B532"/>
+          <cell r="C532"/>
+          <cell r="D532"/>
+          <cell r="E532" t="str">
+            <v/>
+          </cell>
+          <cell r="F532"/>
+          <cell r="G532"/>
+          <cell r="H532"/>
+          <cell r="I532"/>
+          <cell r="J532"/>
+          <cell r="K532"/>
+          <cell r="L532"/>
+          <cell r="M532"/>
+          <cell r="N532"/>
+          <cell r="O532"/>
+          <cell r="P532"/>
+          <cell r="Q532"/>
+          <cell r="R532"/>
+          <cell r="S532"/>
+          <cell r="T532"/>
+          <cell r="U532"/>
+          <cell r="V532"/>
+          <cell r="W532"/>
+        </row>
+        <row r="533">
+          <cell r="A533"/>
+          <cell r="B533"/>
+          <cell r="C533"/>
+          <cell r="D533"/>
+          <cell r="E533" t="str">
+            <v/>
+          </cell>
+          <cell r="F533"/>
+          <cell r="G533"/>
+          <cell r="H533"/>
+          <cell r="I533"/>
+          <cell r="J533"/>
+          <cell r="K533"/>
+          <cell r="L533"/>
+          <cell r="M533"/>
+          <cell r="N533"/>
+          <cell r="O533"/>
+          <cell r="P533"/>
+          <cell r="Q533"/>
+          <cell r="R533"/>
+          <cell r="S533"/>
+          <cell r="T533"/>
+          <cell r="U533"/>
+          <cell r="V533"/>
+          <cell r="W533"/>
+        </row>
+        <row r="534">
+          <cell r="A534"/>
+          <cell r="B534"/>
+          <cell r="C534"/>
+          <cell r="D534"/>
+          <cell r="E534" t="str">
+            <v/>
+          </cell>
+          <cell r="F534"/>
+          <cell r="G534"/>
+          <cell r="H534"/>
+          <cell r="I534"/>
+          <cell r="J534"/>
+          <cell r="K534"/>
+          <cell r="L534"/>
+          <cell r="M534"/>
+          <cell r="N534"/>
+          <cell r="O534"/>
+          <cell r="P534"/>
+          <cell r="Q534"/>
+          <cell r="R534"/>
+          <cell r="S534"/>
+          <cell r="T534"/>
+          <cell r="U534"/>
+          <cell r="V534"/>
+          <cell r="W534"/>
         </row>
       </sheetData>
       <sheetData sheetId="4"/>
@@ -39476,17 +41062,11 @@
       <sheetData sheetId="105"/>
       <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
-      <sheetData sheetId="108">
-        <row r="1">
-          <cell r="F1" t="str">
-            <v>No_Item</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="108"/>
       <sheetData sheetId="109"/>
       <sheetData sheetId="110"/>
       <sheetData sheetId="111"/>
-      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="112"/>
       <sheetData sheetId="113" refreshError="1"/>
       <sheetData sheetId="114" refreshError="1"/>
       <sheetData sheetId="115" refreshError="1"/>
@@ -39666,6 +41246,7 @@
       <sheetData sheetId="289" refreshError="1"/>
       <sheetData sheetId="290" refreshError="1"/>
       <sheetData sheetId="291" refreshError="1"/>
+      <sheetData sheetId="292" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -41292,23 +42873,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="112" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="111" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="110" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="109" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="107" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="106" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -41354,7 +42935,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -42735,23 +44316,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="41" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="40" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -42797,7 +44378,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -44178,23 +45759,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A22">
-    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:A1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -44239,7 +45820,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -45523,23 +47104,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -45584,7 +47165,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -47047,26 +48628,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D19">
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -47110,7 +48691,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -48343,20 +49924,20 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A17">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -48375,7 +49956,7 @@
   <sheetPr filterMode="1">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:N664"/>
+  <dimension ref="A1:O664"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
@@ -48396,13 +49977,13 @@
     <col min="16" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -48421,7 +50002,7 @@
       <c r="M1" s="7"/>
       <c r="N1" s="9"/>
     </row>
-    <row r="2" spans="1:14" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
@@ -48465,7 +50046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>515</v>
       </c>
@@ -48502,12 +50083,14 @@
       <c r="L3" s="26">
         <v>5</v>
       </c>
-      <c r="M3" s="27"/>
+      <c r="M3" s="27" t="s">
+        <v>246</v>
+      </c>
       <c r="N3" s="28">
         <v>46185</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>517</v>
       </c>
@@ -48547,7 +50130,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="62"/>
       <c r="B5" s="63"/>
       <c r="C5" s="64"/>
@@ -48563,7 +50146,7 @@
       <c r="M5" s="72"/>
       <c r="N5" s="76"/>
     </row>
-    <row r="6" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>521</v>
       </c>
@@ -48604,8 +50187,11 @@
       <c r="N6" s="28">
         <v>46185</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O6" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="62"/>
       <c r="B7" s="63"/>
       <c r="C7" s="64"/>
@@ -48621,7 +50207,7 @@
       <c r="M7" s="73"/>
       <c r="N7" s="76"/>
     </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>523</v>
       </c>
@@ -48662,8 +50248,11 @@
       <c r="N8" s="28">
         <v>46185</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O8" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="62"/>
       <c r="B9" s="63"/>
       <c r="C9" s="64"/>
@@ -48679,7 +50268,7 @@
       <c r="M9" s="72"/>
       <c r="N9" s="76"/>
     </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>528</v>
       </c>
@@ -48720,8 +50309,11 @@
       <c r="N10" s="28">
         <v>46185</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O10" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="e">
         <f>VLOOKUP(A11,'[2]master plan'!A:C,3,0)</f>
@@ -48770,7 +50362,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="e">
         <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
@@ -48819,7 +50411,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="e">
         <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
@@ -48868,7 +50460,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="e">
         <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
@@ -48917,7 +50509,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="e">
         <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
@@ -48966,7 +50558,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="e">
         <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
@@ -49739,23 +51331,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -49765,6 +51357,1555 @@
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="21" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0165BE40-D7AA-487D-B762-5C6D7005823B}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:O667"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="175.54296875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46182.753058449074</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>25</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>VLOOKUP(A3,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0502</v>
+      </c>
+      <c r="C3" s="19" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000015</v>
+      </c>
+      <c r="D3" s="20" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-000437</v>
+      </c>
+      <c r="E3" s="21" t="str">
+        <f>VLOOKUP(A3,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Regular AIR BLUE/16-4134TPX 0.13D 25+/-4 Asker C 1.1M 2M 3.5mm</v>
+      </c>
+      <c r="F3" s="22">
+        <f>VLOOKUP(A3,'[2]master plan'!A:H,8,0)</f>
+        <v>20</v>
+      </c>
+      <c r="G3" s="23">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="24">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ASICS</v>
+      </c>
+      <c r="J3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample
+URGENT (6-15)</v>
+      </c>
+      <c r="K3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,14,0)</f>
+        <v>DIE-CUT</v>
+      </c>
+      <c r="L3" s="26">
+        <v>1</v>
+      </c>
+      <c r="M3" s="27"/>
+      <c r="N3" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A3,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46185</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="76"/>
+    </row>
+    <row r="5" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>VLOOKUP(A5,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0497</v>
+      </c>
+      <c r="C5" s="19" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000116</v>
+      </c>
+      <c r="D5" s="20" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-002530</v>
+      </c>
+      <c r="E5" s="21" t="str">
+        <f>VLOOKUP(A5,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 3mm</v>
+      </c>
+      <c r="F5" s="22">
+        <f>VLOOKUP(A5,'[2]master plan'!A:H,8,0)</f>
+        <v>10</v>
+      </c>
+      <c r="G5" s="23">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="24">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,12,0)</f>
+        <v>KATE SPADE</v>
+      </c>
+      <c r="J5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00328</v>
+      </c>
+      <c r="K5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,14,0)</f>
+        <v>sheet</v>
+      </c>
+      <c r="L5" s="26">
+        <v>2</v>
+      </c>
+      <c r="M5" s="27"/>
+      <c r="N5" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A5,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46186</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>VLOOKUP(A6,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0498</v>
+      </c>
+      <c r="C6" s="19" t="str">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000116</v>
+      </c>
+      <c r="D6" s="20" t="str">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-002710</v>
+      </c>
+      <c r="E6" s="21" t="str">
+        <f>VLOOKUP(A6,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Regular-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.13D 25+/-4 Asker C 1.1M 2M 5mm</v>
+      </c>
+      <c r="F6" s="22">
+        <f>VLOOKUP(A6,'[2]master plan'!A:H,8,0)</f>
+        <v>10</v>
+      </c>
+      <c r="G6" s="23">
+        <f>VLOOKUP(A6,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H6" s="24">
+        <f>VLOOKUP(A6,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I6" s="25" t="str">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,12,0)</f>
+        <v>KATE SPADE</v>
+      </c>
+      <c r="J6" s="25" t="str">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00328</v>
+      </c>
+      <c r="K6" s="25" t="str">
+        <f>VLOOKUP($A6,'[2]master plan'!$A:$N,14,0)</f>
+        <v>sheet</v>
+      </c>
+      <c r="L6" s="26"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A6,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="76"/>
+    </row>
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>VLOOKUP(A8,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0504</v>
+      </c>
+      <c r="C8" s="19" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000348</v>
+      </c>
+      <c r="D8" s="20" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-004195</v>
+      </c>
+      <c r="E8" s="21" t="str">
+        <f>VLOOKUP(A8,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite IMPERIAL SEEDPEARL/12-0703TPX Flat Sheet 0.22D 25+/-4 Asker C 1.1M 1.47M 4mm</v>
+      </c>
+      <c r="F8" s="22">
+        <f>VLOOKUP(A8,'[2]master plan'!A:H,8,0)</f>
+        <v>250</v>
+      </c>
+      <c r="G8" s="23">
+        <f>VLOOKUP(A8,'[2]master plan'!A:W,23,0)</f>
+        <v>8</v>
+      </c>
+      <c r="H8" s="24">
+        <f>VLOOKUP(A8,'[2]master plan'!A:W,23,0)</f>
+        <v>8</v>
+      </c>
+      <c r="I8" s="25" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J8" s="25" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00371/00379 - URGENT (6-13)</v>
+      </c>
+      <c r="K8" s="25" t="str">
+        <f>VLOOKUP($A8,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L8" s="26">
+        <v>8</v>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A8,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46186</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="76"/>
+    </row>
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>VLOOKUP(A10,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0499</v>
+      </c>
+      <c r="C10" s="19" t="str">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000243</v>
+      </c>
+      <c r="D10" s="20" t="str">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-004444</v>
+      </c>
+      <c r="E10" s="21" t="str">
+        <f>VLOOKUP(A10,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra-Hybrid GREEN/16-5932TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+      </c>
+      <c r="F10" s="22">
+        <f>VLOOKUP(A10,'[2]master plan'!A:H,8,0)</f>
+        <v>70</v>
+      </c>
+      <c r="G10" s="23">
+        <f>VLOOKUP(A10,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="24">
+        <f>VLOOKUP(A10,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I10" s="25" t="str">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00325 - URGENT (6-17)</v>
+      </c>
+      <c r="K10" s="25" t="str">
+        <f>VLOOKUP($A10,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L10" s="26">
+        <v>2</v>
+      </c>
+      <c r="M10" s="40"/>
+      <c r="N10" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A10,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="76"/>
+    </row>
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0500</v>
+      </c>
+      <c r="C12" s="19" t="str">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D12" s="20" t="str">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-003298</v>
+      </c>
+      <c r="E12" s="21" t="str">
+        <f>VLOOKUP(A12,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+      </c>
+      <c r="F12" s="22">
+        <f>VLOOKUP(A12,'[2]master plan'!A:H,8,0)</f>
+        <v>100</v>
+      </c>
+      <c r="G12" s="23">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H12" s="24">
+        <f>VLOOKUP(A12,'[2]master plan'!A:W,23,0)</f>
+        <v>3</v>
+      </c>
+      <c r="I12" s="25" t="str">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J12" s="25" t="str">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00327  - URGENT (6-17)</v>
+      </c>
+      <c r="K12" s="25" t="str">
+        <f>VLOOKUP($A12,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L12" s="26">
+        <v>9</v>
+      </c>
+      <c r="M12" s="27"/>
+      <c r="N12" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A12,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
+        <v>540</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0501</v>
+      </c>
+      <c r="C13" s="19" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D13" s="20" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-003299</v>
+      </c>
+      <c r="E13" s="21" t="str">
+        <f>VLOOKUP(A13,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+      </c>
+      <c r="F13" s="22">
+        <f>VLOOKUP(A13,'[2]master plan'!A:H,8,0)</f>
+        <v>50</v>
+      </c>
+      <c r="G13" s="23">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="H13" s="24">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00327  - URGENT (6-17)</v>
+      </c>
+      <c r="K13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L13" s="26"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A13,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0503</v>
+      </c>
+      <c r="C14" s="19" t="str">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D14" s="20" t="str">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-002973</v>
+      </c>
+      <c r="E14" s="21" t="str">
+        <f>VLOOKUP(A14,'[2]master plan'!A:G,7,0)</f>
+        <v>UltraLite-Hybrid OrthoLite SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+      </c>
+      <c r="F14" s="22">
+        <f>VLOOKUP(A14,'[2]master plan'!A:H,8,0)</f>
+        <v>50</v>
+      </c>
+      <c r="G14" s="23">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="24">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I14" s="25" t="str">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,12,0)</f>
+        <v>SALOMON</v>
+      </c>
+      <c r="J14" s="25" t="str">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K14" s="25" t="str">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,14,0)</f>
+        <v>MOLDED</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A14,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B15" s="18" t="str">
+        <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0506</v>
+      </c>
+      <c r="C15" s="19" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D15" s="20" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-003299</v>
+      </c>
+      <c r="E15" s="21" t="str">
+        <f>VLOOKUP(A15,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+      </c>
+      <c r="F15" s="22">
+        <f>VLOOKUP(A15,'[2]master plan'!A:H,8,0)</f>
+        <v>50</v>
+      </c>
+      <c r="G15" s="23">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="H15" s="24">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I15" s="25" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J15" s="25" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00375/00400 - URGENT (6-16)</v>
+      </c>
+      <c r="K15" s="25" t="str">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L15" s="26"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="62"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="76"/>
+    </row>
+    <row r="17" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B17" s="18" t="str">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0505</v>
+      </c>
+      <c r="C17" s="19" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000058</v>
+      </c>
+      <c r="D17" s="20" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-001319</v>
+      </c>
+      <c r="E17" s="21" t="str">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 5mm</v>
+      </c>
+      <c r="F17" s="22">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>50</v>
+      </c>
+      <c r="G17" s="23">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="H17" s="24">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I17" s="25" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J17" s="25" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00358/00359 - URGENT (6-16)</v>
+      </c>
+      <c r="K17" s="25" t="str">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L17" s="26">
+        <v>2</v>
+      </c>
+      <c r="M17" s="27"/>
+      <c r="N17" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="62"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="76"/>
+    </row>
+    <row r="19" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="B19" s="18" t="str">
+        <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260609-0507</v>
+      </c>
+      <c r="C19" s="19" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000200</v>
+      </c>
+      <c r="D19" s="20" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-003425</v>
+      </c>
+      <c r="E19" s="21" t="str">
+        <f>VLOOKUP(A19,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra SEEDPEARL/12-0703TPX Flat Sheet 0.085D 78-90 Asker F 1.1M 2M 4mm</v>
+      </c>
+      <c r="F19" s="22">
+        <f>VLOOKUP(A19,'[2]master plan'!A:H,8,0)</f>
+        <v>30</v>
+      </c>
+      <c r="G19" s="23">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="24">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I19" s="25" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J19" s="25" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00377 - URGENT (6-16)</v>
+      </c>
+      <c r="K19" s="25" t="str">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L19" s="26">
+        <v>1</v>
+      </c>
+      <c r="M19" s="40"/>
+      <c r="N19" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="78"/>
+      <c r="B20" s="63" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="64" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="65" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="66" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="67" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="68" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="69" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="70" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="70" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="71"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="62"/>
+      <c r="B21" s="63" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="64" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="65" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="66" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="67" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="68" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="69" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I21" s="70" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="70" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="71"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A21,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="62"/>
+      <c r="B22" s="63" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C22" s="64" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D22" s="65" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" s="66" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F22" s="67" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G22" s="68" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H22" s="69" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I22" s="70" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K22" s="70" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L22" s="71"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A22,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="62"/>
+      <c r="B23" s="63" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C23" s="64" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D23" s="65" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E23" s="66" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F23" s="67" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G23" s="68" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H23" s="69" t="e">
+        <f>VLOOKUP(A23,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I23" s="70" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J23" s="25" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K23" s="70" t="e">
+        <f>VLOOKUP($A23,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L23" s="71"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="76" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A23,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="41"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="51"/>
+    </row>
+    <row r="25" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="56"/>
+    </row>
+    <row r="26" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="56"/>
+    </row>
+    <row r="28" spans="1:15" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="55"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="58"/>
+    </row>
+    <row r="29" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L29" s="56"/>
+    </row>
+    <row r="30" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L30" s="56"/>
+    </row>
+    <row r="31" spans="1:15" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:15" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="57" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="58"/>
+    </row>
+    <row r="58" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="56"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="58"/>
+    </row>
+    <row r="667" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A667" s="2"/>
+      <c r="B667" s="52"/>
+      <c r="C667" s="2"/>
+      <c r="D667" s="2"/>
+      <c r="E667" s="60"/>
+      <c r="H667" s="55"/>
+      <c r="I667" s="53"/>
+      <c r="J667" s="53"/>
+      <c r="K667" s="53"/>
+      <c r="L667" s="61"/>
+      <c r="M667" s="57"/>
+      <c r="N667" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E23" name="Range1_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="A20" name="Range1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N24" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="2">
+      <filters blank="1">
+        <filter val="BDB-000015"/>
+        <filter val="BDB-000058"/>
+        <filter val="BDB-000116"/>
+        <filter val="BDB-000123"/>
+        <filter val="BDB-000200"/>
+        <filter val="BDB-000243"/>
+        <filter val="BDB-000348"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:A23 A3:A19">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="15" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -49800,7 +52941,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -51149,23 +54290,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="105" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="104" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="103" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="102" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="100" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="99" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -51210,7 +54351,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -52617,23 +55758,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="98" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="97" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A1048576">
-    <cfRule type="duplicateValues" dxfId="96" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="95" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="93" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -52678,7 +55819,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -54051,23 +57192,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A25">
-    <cfRule type="duplicateValues" dxfId="90" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="89" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="86" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -54111,7 +57252,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -55326,39 +58467,39 @@
     <mergeCell ref="D7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="84" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A6 A14:A18">
-    <cfRule type="duplicateValues" dxfId="83" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="82" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A13">
-    <cfRule type="duplicateValues" dxfId="81" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A1048576">
-    <cfRule type="duplicateValues" dxfId="80" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C6 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="79" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C13">
-    <cfRule type="duplicateValues" dxfId="77" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:L8">
-    <cfRule type="duplicateValues" dxfId="75" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="74" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="72" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="9"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -55403,7 +58544,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -56728,26 +59869,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="71" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A15">
-    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A21">
-    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="68" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -56793,7 +59934,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -58148,23 +61289,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -58209,7 +61350,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -59597,24 +62738,24 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="56" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="55" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="49" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -59660,7 +62801,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.483680439815</v>
+        <v>46182.753058449074</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -61005,23 +64146,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="48" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="47" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="46" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="43" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>

--- a/Kế hoach sản xuất Sample.xlsx
+++ b/Kế hoach sản xuất Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B315981E-A25C-4A9B-9B20-C465E730CDAC}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{C12FF075-160F-4BB4-977C-4D56BABB08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77F985A2-01BA-45C3-97C3-AD463EE6DF94}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="14" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="5" activeTab="16" xr2:uid="{E780E912-92A1-4ADF-95B1-638FE58CE194}"/>
   </bookViews>
   <sheets>
     <sheet name="13.5" sheetId="1" r:id="rId1"/>
@@ -29,13 +29,15 @@
     <sheet name="6.6" sheetId="14" r:id="rId14"/>
     <sheet name="8.6" sheetId="15" r:id="rId15"/>
     <sheet name="9.6" sheetId="16" r:id="rId16"/>
+    <sheet name="10.6" sheetId="17" r:id="rId17"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId17"/>
     <externalReference r:id="rId18"/>
+    <externalReference r:id="rId19"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'1.6'!$A$2:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'10.6'!$A$2:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'13.5'!$A$2:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'15.5'!$A$2:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'18.5'!$A$2:$N$3</definedName>
@@ -52,6 +54,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'8.6'!$A$2:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'9.6'!$A$2:$N$24</definedName>
     <definedName name="AE" localSheetId="8">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE" localSheetId="16">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="0">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="1">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="2">'[1]Molding-báo cáo BUn'!#REF!</definedName>
@@ -67,7 +70,9 @@
     <definedName name="AE" localSheetId="13">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="14">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="AE" localSheetId="15">'[1]Molding-báo cáo BUn'!#REF!</definedName>
+    <definedName name="AE">'[1]Molding-báo cáo BUn'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'1.6'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'10.6'!$A$1:$N$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'13.5'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'15.5'!$A$1:$N$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'18.5'!$A$1:$N$29</definedName>
@@ -84,6 +89,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'8.6'!$A$1:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'9.6'!$A$1:$N$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'1.6'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'10.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'13.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'15.5'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'18.5'!$1:$2</definedName>
@@ -100,6 +106,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'8.6'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'9.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -116,6 +123,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
+    <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="16" hidden="1">'10.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -132,6 +140,7 @@
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_1811EAD5_BD80_4EFF_9596_8EF0EFF4AD2A_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -148,6 +157,7 @@
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_18A7E0A3_1642_489C_8130_3CC9FF80B04E_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -164,6 +174,7 @@
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_2653C0F9_59B0_4DB3_BD8D_CACC833527F0_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -180,6 +191,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="16" hidden="1">'10.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -196,6 +208,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="8" hidden="1">'1.6'!#REF!</definedName>
+    <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="16" hidden="1">'10.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="0" hidden="1">'13.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="1" hidden="1">'15.5'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="2" hidden="1">'18.5'!#REF!</definedName>
@@ -212,6 +225,7 @@
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="14" hidden="1">'8.6'!#REF!</definedName>
     <definedName name="Z_289C1146_6484_4C42_9E78_5D7EBC42FBCC_.wvu.Rows" localSheetId="15" hidden="1">'9.6'!#REF!</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -228,6 +242,7 @@
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_314949E3_0D3B_4560_AE70_4D3C4970782A_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
@@ -244,6 +259,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$N$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
+    <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="16" hidden="1">'10.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -260,6 +276,7 @@
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_318C8B1E_0627_4DC9_8089_60901FDA475B_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -276,6 +293,7 @@
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_323B6797_06D8_47A1_B001_797373BE57F2_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -292,6 +310,7 @@
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_6A9DC2EA_1959_4EB9_A839_907E58591C36_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -308,6 +327,7 @@
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866BE165_7CE2_41D4_AD4C_D79698D432B1_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
@@ -324,6 +344,7 @@
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
     <definedName name="Z_866CB300_9BE2_4E49_BCB4_72634A7939D7_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -340,6 +361,7 @@
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_8CF255E0_B8BB_4016_A366_4FCF106965CF_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -356,6 +378,7 @@
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_A4A1FC39_A54C_43AC_9912_8824EB6833F5_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$N$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$N$2</definedName>
@@ -372,6 +395,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$N$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
+    <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="16" hidden="1">'10.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -388,6 +412,7 @@
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="14" hidden="1">'8.6'!$1:$2</definedName>
     <definedName name="Z_AF6B2EAC_2950_4809_A605_2107D254FC8D_.wvu.PrintTitles" localSheetId="15" hidden="1">'9.6'!$1:$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$B$2:$M$2</definedName>
+    <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$B$2:$M$2</definedName>
@@ -404,6 +429,7 @@
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$B$2:$M$2</definedName>
     <definedName name="Z_CA92E8A2_92C9_4575_A139_6FE5DA69269F_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$B$2:$M$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="8" hidden="1">'1.6'!$A$2:$N$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="16" hidden="1">'10.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="0" hidden="1">'13.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="1" hidden="1">'15.5'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="2" hidden="1">'18.5'!$A$2:$N$2</definedName>
@@ -420,6 +446,7 @@
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="14" hidden="1">'8.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.FilterData" localSheetId="15" hidden="1">'9.6'!$A$2:$N$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="8" hidden="1">'1.6'!$1:$2</definedName>
+    <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="16" hidden="1">'10.6'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="0" hidden="1">'13.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="1" hidden="1">'15.5'!$1:$2</definedName>
     <definedName name="Z_DF644A2B_B913_48D6_B430_E57F3B482B79_.wvu.PrintTitles" localSheetId="2" hidden="1">'18.5'!$1:$2</definedName>
@@ -457,7 +484,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="549">
   <si>
     <t>Release Date</t>
   </si>
@@ -2077,12 +2104,6 @@
     <t>S-2026-06-25</t>
   </si>
   <si>
-    <t>???</t>
-  </si>
-  <si>
-    <t>????</t>
-  </si>
-  <si>
     <t>S-2026-06-26</t>
   </si>
   <si>
@@ -2173,7 +2194,22 @@
     <t>S-2026-06-41</t>
   </si>
   <si>
-    <t>KIỂM TRA XEM CÒN TỒN KO</t>
+    <t>S-2026-06-43</t>
+  </si>
+  <si>
+    <t>S-2026-06-47</t>
+  </si>
+  <si>
+    <t>S-2026-06-42</t>
+  </si>
+  <si>
+    <t>S-2026-06-44</t>
+  </si>
+  <si>
+    <t>S-2026-06-45</t>
+  </si>
+  <si>
+    <t>S-2026-06-46</t>
   </si>
 </sst>
 </file>
@@ -2791,7 +2827,77 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="122">
+  <dxfs count="129">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4083,6 +4189,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1 (2)"/>
+      <sheetName val="change status "/>
       <sheetName val="form Lab"/>
       <sheetName val="Form hệ thống"/>
       <sheetName val="master plan"/>
@@ -4183,18 +4290,21 @@
       <sheetName val="29.5 - L2"/>
       <sheetName val="1.6"/>
       <sheetName val="2.6"/>
-      <sheetName val="5.6"/>
       <sheetName val="3.6"/>
       <sheetName val="4.6"/>
+      <sheetName val="5.6"/>
       <sheetName val="6.6"/>
       <sheetName val="8.6"/>
       <sheetName val="9.6"/>
-      <sheetName val="form 2 (23)"/>
+      <sheetName val="10.6"/>
+      <sheetName val="BCN 10.6"/>
+      <sheetName val="form 2 (25)"/>
       <sheetName val="In đơn"/>
       <sheetName val="Production BOM"/>
       <sheetName val="Items"/>
       <sheetName val="mm Pu"/>
       <sheetName val="master plan (2)"/>
+      <sheetName val="form 2 (23)"/>
       <sheetName val="form 2 (22)"/>
       <sheetName val="form 2 (21)"/>
       <sheetName val="form 2 (20)"/>
@@ -4244,7 +4354,6 @@
       <sheetName val="30.5"/>
       <sheetName val="3.6 (L)"/>
       <sheetName val="9.6 (L)"/>
-      <sheetName val="10.6"/>
       <sheetName val="11.6"/>
       <sheetName val="12.6"/>
       <sheetName val="12.6 (L)"/>
@@ -4372,15 +4481,13 @@
       <sheetName val="BCN 22.4"/>
       <sheetName val="form 2 (4)"/>
       <sheetName val="form 2 (3)"/>
-      <sheetName val="form 2"/>
-      <sheetName val="25.4 (2)"/>
-      <sheetName val="form 2 (9)"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
         <row r="1">
           <cell r="A1"/>
           <cell r="B1"/>
@@ -4421,16 +4528,16 @@
             <v>SAMPLE</v>
           </cell>
           <cell r="H2">
-            <v>25869</v>
+            <v>26409</v>
           </cell>
           <cell r="I2">
-            <v>25869</v>
+            <v>26409</v>
           </cell>
           <cell r="J2">
-            <v>24163</v>
+            <v>24470</v>
           </cell>
           <cell r="K2">
-            <v>1706</v>
+            <v>1939</v>
           </cell>
           <cell r="L2" t="str">
             <v>ASICS</v>
@@ -4452,7 +4559,7 @@
           </cell>
           <cell r="V2"/>
           <cell r="W2">
-            <v>1308</v>
+            <v>1324</v>
           </cell>
         </row>
         <row r="3">
@@ -36077,10 +36184,10 @@
             <v>40</v>
           </cell>
           <cell r="J460">
+            <v>40</v>
+          </cell>
+          <cell r="K460">
             <v>0</v>
-          </cell>
-          <cell r="K460">
-            <v>40</v>
           </cell>
           <cell r="L460" t="str">
             <v>ON RUNNING</v>
@@ -36838,10 +36945,10 @@
             <v>30</v>
           </cell>
           <cell r="J471">
-            <v>100</v>
+            <v>30</v>
           </cell>
           <cell r="K471">
-            <v>-70</v>
+            <v>0</v>
           </cell>
           <cell r="L471" t="str">
             <v>FOOTJOY</v>
@@ -37047,10 +37154,10 @@
             <v>20</v>
           </cell>
           <cell r="J474">
+            <v>20</v>
+          </cell>
+          <cell r="K474">
             <v>0</v>
-          </cell>
-          <cell r="K474">
-            <v>20</v>
           </cell>
           <cell r="L474" t="str">
             <v>FOOTJOY</v>
@@ -37740,10 +37847,10 @@
             <v>30</v>
           </cell>
           <cell r="J484">
+            <v>30</v>
+          </cell>
+          <cell r="K484">
             <v>0</v>
-          </cell>
-          <cell r="K484">
-            <v>30</v>
           </cell>
           <cell r="L484" t="str">
             <v>LOWA</v>
@@ -37809,10 +37916,10 @@
             <v>20</v>
           </cell>
           <cell r="J485">
+            <v>20</v>
+          </cell>
+          <cell r="K485">
             <v>0</v>
-          </cell>
-          <cell r="K485">
-            <v>20</v>
           </cell>
           <cell r="L485" t="str">
             <v>LOWA</v>
@@ -37878,10 +37985,10 @@
             <v>30</v>
           </cell>
           <cell r="J486">
+            <v>30</v>
+          </cell>
+          <cell r="K486">
             <v>0</v>
-          </cell>
-          <cell r="K486">
-            <v>30</v>
           </cell>
           <cell r="L486" t="str">
             <v>LOWA</v>
@@ -37947,10 +38054,10 @@
             <v>30</v>
           </cell>
           <cell r="J487">
+            <v>30</v>
+          </cell>
+          <cell r="K487">
             <v>0</v>
-          </cell>
-          <cell r="K487">
-            <v>30</v>
           </cell>
           <cell r="L487" t="str">
             <v>ADIDAS</v>
@@ -38016,10 +38123,10 @@
             <v>60</v>
           </cell>
           <cell r="J488">
+            <v>60</v>
+          </cell>
+          <cell r="K488">
             <v>0</v>
-          </cell>
-          <cell r="K488">
-            <v>60</v>
           </cell>
           <cell r="L488" t="str">
             <v>ADIDAS</v>
@@ -38085,10 +38192,10 @@
             <v>50</v>
           </cell>
           <cell r="J489">
+            <v>50</v>
+          </cell>
+          <cell r="K489">
             <v>0</v>
-          </cell>
-          <cell r="K489">
-            <v>50</v>
           </cell>
           <cell r="L489" t="str">
             <v>ADIDAS</v>
@@ -38156,10 +38263,10 @@
             <v>20</v>
           </cell>
           <cell r="J490">
+            <v>20</v>
+          </cell>
+          <cell r="K490">
             <v>0</v>
-          </cell>
-          <cell r="K490">
-            <v>20</v>
           </cell>
           <cell r="L490" t="str">
             <v>PAYNTR</v>
@@ -38225,10 +38332,10 @@
             <v>50</v>
           </cell>
           <cell r="J491">
+            <v>50</v>
+          </cell>
+          <cell r="K491">
             <v>0</v>
-          </cell>
-          <cell r="K491">
-            <v>50</v>
           </cell>
           <cell r="L491" t="str">
             <v>ADIDAS</v>
@@ -38294,10 +38401,10 @@
             <v>25</v>
           </cell>
           <cell r="J492">
+            <v>25</v>
+          </cell>
+          <cell r="K492">
             <v>0</v>
-          </cell>
-          <cell r="K492">
-            <v>25</v>
           </cell>
           <cell r="L492" t="str">
             <v>NIKE</v>
@@ -38962,10 +39069,10 @@
             <v>2</v>
           </cell>
           <cell r="J502">
+            <v>2</v>
+          </cell>
+          <cell r="K502">
             <v>0</v>
-          </cell>
-          <cell r="K502">
-            <v>2</v>
           </cell>
           <cell r="L502" t="str">
             <v>SHYANG HUNG TAH</v>
@@ -40232,8 +40339,8 @@
           <cell r="T520">
             <v>8</v>
           </cell>
-          <cell r="U520" t="str">
-            <v/>
+          <cell r="U520">
+            <v>4</v>
           </cell>
           <cell r="V520">
             <v>2.8570000000000002E-2</v>
@@ -40796,169 +40903,832 @@
           </cell>
         </row>
         <row r="529">
-          <cell r="A529"/>
+          <cell r="A529" t="str">
+            <v>S-2026-06-42</v>
+          </cell>
           <cell r="B529"/>
-          <cell r="C529"/>
-          <cell r="D529"/>
+          <cell r="C529" t="str">
+            <v>RPRO-260610-0503</v>
+          </cell>
+          <cell r="D529" t="str">
+            <v>PUR2600601000001S</v>
+          </cell>
           <cell r="E529" t="str">
-            <v/>
-          </cell>
-          <cell r="F529"/>
-          <cell r="G529"/>
-          <cell r="H529"/>
-          <cell r="I529"/>
-          <cell r="J529"/>
-          <cell r="K529"/>
-          <cell r="L529"/>
-          <cell r="M529"/>
-          <cell r="N529"/>
-          <cell r="O529"/>
-          <cell r="P529"/>
-          <cell r="Q529"/>
-          <cell r="R529"/>
-          <cell r="S529"/>
-          <cell r="T529"/>
-          <cell r="U529"/>
-          <cell r="V529"/>
-          <cell r="W529"/>
+            <v>BDB-000331</v>
+          </cell>
+          <cell r="F529" t="str">
+            <v>PVN-004446</v>
+          </cell>
+          <cell r="G529" t="str">
+            <v>OrthoLite X-35-Nike FOSSIL/17-0909TPX 0.145D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+          </cell>
+          <cell r="H529">
+            <v>20</v>
+          </cell>
+          <cell r="I529">
+            <v>20</v>
+          </cell>
+          <cell r="J529">
+            <v>0</v>
+          </cell>
+          <cell r="K529">
+            <v>20</v>
+          </cell>
+          <cell r="L529" t="str">
+            <v>NIKE</v>
+          </cell>
+          <cell r="M529" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N529" t="str">
+            <v>MOLDED</v>
+          </cell>
+          <cell r="O529" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P529">
+            <v>46183</v>
+          </cell>
+          <cell r="Q529">
+            <v>46192</v>
+          </cell>
+          <cell r="R529">
+            <v>46189</v>
+          </cell>
+          <cell r="S529">
+            <v>6</v>
+          </cell>
+          <cell r="T529">
+            <v>9</v>
+          </cell>
+          <cell r="U529">
+            <v>4.5</v>
+          </cell>
+          <cell r="V529">
+            <v>3.125E-2</v>
+          </cell>
+          <cell r="W529">
+            <v>1</v>
+          </cell>
         </row>
         <row r="530">
-          <cell r="A530"/>
+          <cell r="A530" t="str">
+            <v>S-2026-06-43</v>
+          </cell>
           <cell r="B530"/>
-          <cell r="C530"/>
-          <cell r="D530"/>
+          <cell r="C530" t="str">
+            <v>RPRO-260610-0504</v>
+          </cell>
+          <cell r="D530" t="str">
+            <v xml:space="preserve">PUR2606100002S  </v>
+          </cell>
           <cell r="E530" t="str">
-            <v/>
-          </cell>
-          <cell r="F530"/>
-          <cell r="G530"/>
-          <cell r="H530"/>
-          <cell r="I530"/>
-          <cell r="J530"/>
-          <cell r="K530"/>
-          <cell r="L530"/>
-          <cell r="M530"/>
-          <cell r="N530"/>
-          <cell r="O530"/>
-          <cell r="P530"/>
-          <cell r="Q530"/>
-          <cell r="R530"/>
-          <cell r="S530"/>
-          <cell r="T530"/>
-          <cell r="U530"/>
-          <cell r="V530"/>
-          <cell r="W530"/>
+            <v>BDB-000123</v>
+          </cell>
+          <cell r="F530" t="str">
+            <v>PVN-003299</v>
+          </cell>
+          <cell r="G530" t="str">
+            <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+          </cell>
+          <cell r="H530">
+            <v>250</v>
+          </cell>
+          <cell r="I530">
+            <v>250</v>
+          </cell>
+          <cell r="J530">
+            <v>0</v>
+          </cell>
+          <cell r="K530">
+            <v>250</v>
+          </cell>
+          <cell r="L530" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M530" t="str">
+            <v>SSO-2606-00410/00419 - URGENT (6-14)</v>
+          </cell>
+          <cell r="N530" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O530" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P530">
+            <v>46183</v>
+          </cell>
+          <cell r="Q530">
+            <v>46190</v>
+          </cell>
+          <cell r="R530">
+            <v>46187</v>
+          </cell>
+          <cell r="S530">
+            <v>6</v>
+          </cell>
+          <cell r="T530">
+            <v>7</v>
+          </cell>
+          <cell r="U530">
+            <v>3</v>
+          </cell>
+          <cell r="V530">
+            <v>2.1739999999999999E-2</v>
+          </cell>
+          <cell r="W530">
+            <v>6</v>
+          </cell>
         </row>
         <row r="531">
-          <cell r="A531"/>
+          <cell r="A531" t="str">
+            <v>S-2026-06-44</v>
+          </cell>
           <cell r="B531"/>
-          <cell r="C531"/>
-          <cell r="D531"/>
+          <cell r="C531" t="str">
+            <v>RPRO-260610-0505</v>
+          </cell>
+          <cell r="D531" t="str">
+            <v xml:space="preserve">PUR2606100002S  </v>
+          </cell>
           <cell r="E531" t="str">
-            <v/>
-          </cell>
-          <cell r="F531"/>
-          <cell r="G531"/>
-          <cell r="H531"/>
-          <cell r="I531"/>
-          <cell r="J531"/>
-          <cell r="K531"/>
-          <cell r="L531"/>
-          <cell r="M531"/>
-          <cell r="N531"/>
-          <cell r="O531"/>
-          <cell r="P531"/>
-          <cell r="Q531"/>
-          <cell r="R531"/>
-          <cell r="S531"/>
-          <cell r="T531"/>
-          <cell r="U531"/>
-          <cell r="V531"/>
-          <cell r="W531"/>
+            <v>BDB-000055</v>
+          </cell>
+          <cell r="F531" t="str">
+            <v>PVN-004155</v>
+          </cell>
+          <cell r="G531" t="str">
+            <v>OrthoLite X-40 TRUE BLUE/19-4057TPX Flat Sheet 0.16D 35+/-4 Asker C 1.1M 1.7M 3.2mm</v>
+          </cell>
+          <cell r="H531">
+            <v>10</v>
+          </cell>
+          <cell r="I531">
+            <v>10</v>
+          </cell>
+          <cell r="J531">
+            <v>0</v>
+          </cell>
+          <cell r="K531">
+            <v>10</v>
+          </cell>
+          <cell r="L531" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M531" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="N531" t="str">
+            <v>Molded</v>
+          </cell>
+          <cell r="O531" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P531">
+            <v>46183</v>
+          </cell>
+          <cell r="Q531">
+            <v>46192</v>
+          </cell>
+          <cell r="R531">
+            <v>46189</v>
+          </cell>
+          <cell r="S531">
+            <v>6</v>
+          </cell>
+          <cell r="T531">
+            <v>9</v>
+          </cell>
+          <cell r="U531">
+            <v>3.2</v>
+          </cell>
+          <cell r="V531">
+            <v>2.3259999999999999E-2</v>
+          </cell>
+          <cell r="W531">
+            <v>1</v>
+          </cell>
         </row>
         <row r="532">
-          <cell r="A532"/>
+          <cell r="A532" t="str">
+            <v>S-2026-06-45</v>
+          </cell>
           <cell r="B532"/>
-          <cell r="C532"/>
-          <cell r="D532"/>
+          <cell r="C532" t="str">
+            <v>RPRO-260610-0506</v>
+          </cell>
+          <cell r="D532" t="str">
+            <v>PUR2606100004S</v>
+          </cell>
           <cell r="E532" t="str">
-            <v/>
-          </cell>
-          <cell r="F532"/>
-          <cell r="G532"/>
-          <cell r="H532"/>
-          <cell r="I532"/>
-          <cell r="J532"/>
-          <cell r="K532"/>
-          <cell r="L532"/>
-          <cell r="M532"/>
-          <cell r="N532"/>
-          <cell r="O532"/>
-          <cell r="P532"/>
-          <cell r="Q532"/>
-          <cell r="R532"/>
-          <cell r="S532"/>
-          <cell r="T532"/>
-          <cell r="U532"/>
-          <cell r="V532"/>
-          <cell r="W532"/>
+            <v>BDB-000209</v>
+          </cell>
+          <cell r="F532" t="str">
+            <v>PVN-003537</v>
+          </cell>
+          <cell r="G532" t="str">
+            <v>OrthoLite HybridPlus-Recycled MINT GREEN/11-4805TPX Hybrid 0.12D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+          </cell>
+          <cell r="H532">
+            <v>30</v>
+          </cell>
+          <cell r="I532">
+            <v>30</v>
+          </cell>
+          <cell r="J532">
+            <v>0</v>
+          </cell>
+          <cell r="K532">
+            <v>30</v>
+          </cell>
+          <cell r="L532" t="str">
+            <v>AKU</v>
+          </cell>
+          <cell r="M532" t="str">
+            <v>SSO-2606-00451</v>
+          </cell>
+          <cell r="N532" t="str">
+            <v>OE-0111A</v>
+          </cell>
+          <cell r="O532" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P532">
+            <v>46183</v>
+          </cell>
+          <cell r="Q532">
+            <v>46192</v>
+          </cell>
+          <cell r="R532">
+            <v>46189</v>
+          </cell>
+          <cell r="S532">
+            <v>6</v>
+          </cell>
+          <cell r="T532">
+            <v>9</v>
+          </cell>
+          <cell r="U532">
+            <v>4.5</v>
+          </cell>
+          <cell r="V532">
+            <v>3.2259999999999997E-2</v>
+          </cell>
+          <cell r="W532">
+            <v>1</v>
+          </cell>
         </row>
         <row r="533">
-          <cell r="A533"/>
+          <cell r="A533" t="str">
+            <v>S-2026-06-46</v>
+          </cell>
           <cell r="B533"/>
-          <cell r="C533"/>
-          <cell r="D533"/>
+          <cell r="C533" t="str">
+            <v>RPRO-260610-0507</v>
+          </cell>
+          <cell r="D533" t="str">
+            <v>PUR2606100005S</v>
+          </cell>
           <cell r="E533" t="str">
-            <v/>
-          </cell>
-          <cell r="F533"/>
-          <cell r="G533"/>
-          <cell r="H533"/>
-          <cell r="I533"/>
-          <cell r="J533"/>
-          <cell r="K533"/>
-          <cell r="L533"/>
-          <cell r="M533"/>
-          <cell r="N533"/>
-          <cell r="O533"/>
-          <cell r="P533"/>
-          <cell r="Q533"/>
-          <cell r="R533"/>
-          <cell r="S533"/>
-          <cell r="T533"/>
-          <cell r="U533"/>
-          <cell r="V533"/>
-          <cell r="W533"/>
+            <v>BDB-000083</v>
+          </cell>
+          <cell r="F533" t="str">
+            <v>PVN-000935</v>
+          </cell>
+          <cell r="G533" t="str">
+            <v>OrthoLite Eco LT 300C(ADIDAS BLUEBIRD) Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H533">
+            <v>200</v>
+          </cell>
+          <cell r="I533">
+            <v>200</v>
+          </cell>
+          <cell r="J533">
+            <v>0</v>
+          </cell>
+          <cell r="K533">
+            <v>200</v>
+          </cell>
+          <cell r="L533" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M533" t="str">
+            <v>SSO-2606-00449 - URGENT (6-20)</v>
+          </cell>
+          <cell r="N533" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O533" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P533">
+            <v>46183</v>
+          </cell>
+          <cell r="Q533">
+            <v>46192</v>
+          </cell>
+          <cell r="R533">
+            <v>46189</v>
+          </cell>
+          <cell r="S533">
+            <v>6</v>
+          </cell>
+          <cell r="T533">
+            <v>9</v>
+          </cell>
+          <cell r="U533">
+            <v>4</v>
+          </cell>
+          <cell r="V533">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W533">
+            <v>6</v>
+          </cell>
         </row>
         <row r="534">
-          <cell r="A534"/>
+          <cell r="A534" t="str">
+            <v>S-2026-06-47</v>
+          </cell>
           <cell r="B534"/>
-          <cell r="C534"/>
-          <cell r="D534"/>
+          <cell r="C534" t="str">
+            <v>RPRO-260610-0508</v>
+          </cell>
+          <cell r="D534" t="str">
+            <v>PUR2606100005S</v>
+          </cell>
           <cell r="E534" t="str">
+            <v>BDB-000058</v>
+          </cell>
+          <cell r="F534" t="str">
+            <v>PVN-001277</v>
+          </cell>
+          <cell r="G534" t="str">
+            <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+          </cell>
+          <cell r="H534">
+            <v>30</v>
+          </cell>
+          <cell r="I534">
+            <v>30</v>
+          </cell>
+          <cell r="J534">
+            <v>0</v>
+          </cell>
+          <cell r="K534">
+            <v>30</v>
+          </cell>
+          <cell r="L534" t="str">
+            <v>ADIDAS</v>
+          </cell>
+          <cell r="M534" t="str">
+            <v>SSO-2606-00356 - URGENT (6-14)</v>
+          </cell>
+          <cell r="N534" t="str">
+            <v>Flat sheet</v>
+          </cell>
+          <cell r="O534" t="str">
+            <v>Sample</v>
+          </cell>
+          <cell r="P534">
+            <v>46183</v>
+          </cell>
+          <cell r="Q534">
+            <v>46191</v>
+          </cell>
+          <cell r="R534">
+            <v>46188</v>
+          </cell>
+          <cell r="S534">
+            <v>6</v>
+          </cell>
+          <cell r="T534">
+            <v>8</v>
+          </cell>
+          <cell r="U534">
+            <v>4</v>
+          </cell>
+          <cell r="V534">
+            <v>2.8570000000000002E-2</v>
+          </cell>
+          <cell r="W534">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="535">
+          <cell r="A535"/>
+          <cell r="B535"/>
+          <cell r="C535"/>
+          <cell r="D535"/>
+          <cell r="E535" t="str">
             <v/>
           </cell>
-          <cell r="F534"/>
-          <cell r="G534"/>
-          <cell r="H534"/>
-          <cell r="I534"/>
-          <cell r="J534"/>
-          <cell r="K534"/>
-          <cell r="L534"/>
-          <cell r="M534"/>
-          <cell r="N534"/>
-          <cell r="O534"/>
-          <cell r="P534"/>
-          <cell r="Q534"/>
-          <cell r="R534"/>
-          <cell r="S534"/>
-          <cell r="T534"/>
-          <cell r="U534"/>
-          <cell r="V534"/>
-          <cell r="W534"/>
+          <cell r="F535"/>
+          <cell r="G535"/>
+          <cell r="H535"/>
+          <cell r="I535"/>
+          <cell r="J535">
+            <v>0</v>
+          </cell>
+          <cell r="K535">
+            <v>0</v>
+          </cell>
+          <cell r="L535"/>
+          <cell r="M535"/>
+          <cell r="N535"/>
+          <cell r="O535"/>
+          <cell r="P535"/>
+          <cell r="Q535"/>
+          <cell r="R535">
+            <v>-3</v>
+          </cell>
+          <cell r="S535">
+            <v>6</v>
+          </cell>
+          <cell r="T535">
+            <v>0</v>
+          </cell>
+          <cell r="U535"/>
+          <cell r="V535">
+            <v>0</v>
+          </cell>
+          <cell r="W535">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="536">
+          <cell r="A536"/>
+          <cell r="B536"/>
+          <cell r="C536"/>
+          <cell r="D536"/>
+          <cell r="E536" t="str">
+            <v/>
+          </cell>
+          <cell r="F536"/>
+          <cell r="G536"/>
+          <cell r="H536"/>
+          <cell r="I536"/>
+          <cell r="J536">
+            <v>0</v>
+          </cell>
+          <cell r="K536">
+            <v>0</v>
+          </cell>
+          <cell r="L536"/>
+          <cell r="M536"/>
+          <cell r="N536"/>
+          <cell r="O536"/>
+          <cell r="P536"/>
+          <cell r="Q536"/>
+          <cell r="R536">
+            <v>-3</v>
+          </cell>
+          <cell r="S536">
+            <v>6</v>
+          </cell>
+          <cell r="T536">
+            <v>0</v>
+          </cell>
+          <cell r="U536"/>
+          <cell r="V536">
+            <v>0</v>
+          </cell>
+          <cell r="W536">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="537">
+          <cell r="A537"/>
+          <cell r="B537"/>
+          <cell r="C537"/>
+          <cell r="D537"/>
+          <cell r="E537" t="str">
+            <v/>
+          </cell>
+          <cell r="F537"/>
+          <cell r="G537"/>
+          <cell r="H537"/>
+          <cell r="I537"/>
+          <cell r="J537">
+            <v>0</v>
+          </cell>
+          <cell r="K537">
+            <v>0</v>
+          </cell>
+          <cell r="L537"/>
+          <cell r="M537"/>
+          <cell r="N537"/>
+          <cell r="O537"/>
+          <cell r="P537"/>
+          <cell r="Q537"/>
+          <cell r="R537">
+            <v>-3</v>
+          </cell>
+          <cell r="S537">
+            <v>6</v>
+          </cell>
+          <cell r="T537">
+            <v>0</v>
+          </cell>
+          <cell r="U537"/>
+          <cell r="V537">
+            <v>0</v>
+          </cell>
+          <cell r="W537">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="538">
+          <cell r="A538"/>
+          <cell r="B538"/>
+          <cell r="C538"/>
+          <cell r="D538"/>
+          <cell r="E538" t="str">
+            <v/>
+          </cell>
+          <cell r="F538"/>
+          <cell r="G538"/>
+          <cell r="H538"/>
+          <cell r="I538"/>
+          <cell r="J538">
+            <v>0</v>
+          </cell>
+          <cell r="K538">
+            <v>0</v>
+          </cell>
+          <cell r="L538"/>
+          <cell r="M538"/>
+          <cell r="N538"/>
+          <cell r="O538"/>
+          <cell r="P538"/>
+          <cell r="Q538"/>
+          <cell r="R538">
+            <v>-3</v>
+          </cell>
+          <cell r="S538">
+            <v>6</v>
+          </cell>
+          <cell r="T538">
+            <v>0</v>
+          </cell>
+          <cell r="U538"/>
+          <cell r="V538">
+            <v>0</v>
+          </cell>
+          <cell r="W538">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="539">
+          <cell r="A539"/>
+          <cell r="B539"/>
+          <cell r="C539"/>
+          <cell r="D539"/>
+          <cell r="E539" t="str">
+            <v/>
+          </cell>
+          <cell r="F539"/>
+          <cell r="G539"/>
+          <cell r="H539"/>
+          <cell r="I539"/>
+          <cell r="J539">
+            <v>0</v>
+          </cell>
+          <cell r="K539">
+            <v>0</v>
+          </cell>
+          <cell r="L539"/>
+          <cell r="M539"/>
+          <cell r="N539"/>
+          <cell r="O539"/>
+          <cell r="P539"/>
+          <cell r="Q539"/>
+          <cell r="R539">
+            <v>-3</v>
+          </cell>
+          <cell r="S539">
+            <v>6</v>
+          </cell>
+          <cell r="T539">
+            <v>0</v>
+          </cell>
+          <cell r="U539"/>
+          <cell r="V539">
+            <v>0</v>
+          </cell>
+          <cell r="W539">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="540">
+          <cell r="A540"/>
+          <cell r="B540"/>
+          <cell r="C540"/>
+          <cell r="D540"/>
+          <cell r="E540" t="str">
+            <v/>
+          </cell>
+          <cell r="F540"/>
+          <cell r="G540"/>
+          <cell r="H540"/>
+          <cell r="I540"/>
+          <cell r="J540">
+            <v>0</v>
+          </cell>
+          <cell r="K540">
+            <v>0</v>
+          </cell>
+          <cell r="L540"/>
+          <cell r="M540"/>
+          <cell r="N540"/>
+          <cell r="O540"/>
+          <cell r="P540"/>
+          <cell r="Q540"/>
+          <cell r="R540">
+            <v>-3</v>
+          </cell>
+          <cell r="S540">
+            <v>6</v>
+          </cell>
+          <cell r="T540">
+            <v>0</v>
+          </cell>
+          <cell r="U540"/>
+          <cell r="V540">
+            <v>0</v>
+          </cell>
+          <cell r="W540">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="541">
+          <cell r="A541"/>
+          <cell r="B541"/>
+          <cell r="C541"/>
+          <cell r="D541"/>
+          <cell r="E541" t="str">
+            <v/>
+          </cell>
+          <cell r="F541"/>
+          <cell r="G541"/>
+          <cell r="H541"/>
+          <cell r="I541"/>
+          <cell r="J541">
+            <v>0</v>
+          </cell>
+          <cell r="K541">
+            <v>0</v>
+          </cell>
+          <cell r="L541"/>
+          <cell r="M541"/>
+          <cell r="N541"/>
+          <cell r="O541"/>
+          <cell r="P541"/>
+          <cell r="Q541"/>
+          <cell r="R541"/>
+          <cell r="S541"/>
+          <cell r="T541"/>
+          <cell r="U541"/>
+          <cell r="V541"/>
+          <cell r="W541"/>
+        </row>
+        <row r="542">
+          <cell r="A542"/>
+          <cell r="B542"/>
+          <cell r="C542"/>
+          <cell r="D542"/>
+          <cell r="E542" t="str">
+            <v/>
+          </cell>
+          <cell r="F542"/>
+          <cell r="G542"/>
+          <cell r="H542"/>
+          <cell r="I542"/>
+          <cell r="J542"/>
+          <cell r="K542"/>
+          <cell r="L542"/>
+          <cell r="M542"/>
+          <cell r="N542"/>
+          <cell r="O542"/>
+          <cell r="P542"/>
+          <cell r="Q542"/>
+          <cell r="R542"/>
+          <cell r="S542"/>
+          <cell r="T542"/>
+          <cell r="U542"/>
+          <cell r="V542"/>
+          <cell r="W542"/>
+        </row>
+        <row r="543">
+          <cell r="A543"/>
+          <cell r="B543"/>
+          <cell r="C543"/>
+          <cell r="D543"/>
+          <cell r="E543" t="str">
+            <v/>
+          </cell>
+          <cell r="F543"/>
+          <cell r="G543"/>
+          <cell r="H543"/>
+          <cell r="I543"/>
+          <cell r="J543"/>
+          <cell r="K543"/>
+          <cell r="L543"/>
+          <cell r="M543"/>
+          <cell r="N543"/>
+          <cell r="O543"/>
+          <cell r="P543"/>
+          <cell r="Q543"/>
+          <cell r="R543"/>
+          <cell r="S543"/>
+          <cell r="T543"/>
+          <cell r="U543"/>
+          <cell r="V543"/>
+          <cell r="W543"/>
+        </row>
+        <row r="544">
+          <cell r="A544"/>
+          <cell r="B544"/>
+          <cell r="C544"/>
+          <cell r="D544"/>
+          <cell r="E544" t="str">
+            <v/>
+          </cell>
+          <cell r="F544"/>
+          <cell r="G544"/>
+          <cell r="H544"/>
+          <cell r="I544"/>
+          <cell r="J544"/>
+          <cell r="K544"/>
+          <cell r="L544"/>
+          <cell r="M544"/>
+          <cell r="N544"/>
+          <cell r="O544"/>
+          <cell r="P544"/>
+          <cell r="Q544"/>
+          <cell r="R544"/>
+          <cell r="S544"/>
+          <cell r="T544"/>
+          <cell r="U544"/>
+          <cell r="V544"/>
+          <cell r="W544"/>
+        </row>
+        <row r="545">
+          <cell r="A545"/>
+          <cell r="B545"/>
+          <cell r="C545"/>
+          <cell r="D545"/>
+          <cell r="E545" t="str">
+            <v/>
+          </cell>
+          <cell r="F545"/>
+          <cell r="G545"/>
+          <cell r="H545"/>
+          <cell r="I545"/>
+          <cell r="J545"/>
+          <cell r="K545"/>
+          <cell r="L545"/>
+          <cell r="M545"/>
+          <cell r="N545"/>
+          <cell r="O545"/>
+          <cell r="P545"/>
+          <cell r="Q545"/>
+          <cell r="R545"/>
+          <cell r="S545"/>
+          <cell r="T545"/>
+          <cell r="U545"/>
+          <cell r="V545"/>
+          <cell r="W545"/>
+        </row>
+        <row r="546">
+          <cell r="A546"/>
+          <cell r="B546"/>
+          <cell r="C546"/>
+          <cell r="D546"/>
+          <cell r="E546" t="str">
+            <v/>
+          </cell>
+          <cell r="F546"/>
+          <cell r="G546"/>
+          <cell r="H546"/>
+          <cell r="I546"/>
+          <cell r="J546"/>
+          <cell r="K546"/>
+          <cell r="L546"/>
+          <cell r="M546"/>
+          <cell r="N546"/>
+          <cell r="O546"/>
+          <cell r="P546"/>
+          <cell r="Q546"/>
+          <cell r="R546"/>
+          <cell r="S546"/>
+          <cell r="T546"/>
+          <cell r="U546"/>
+          <cell r="V546"/>
+          <cell r="W546"/>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
@@ -41067,9 +41837,9 @@
       <sheetData sheetId="110"/>
       <sheetData sheetId="111"/>
       <sheetData sheetId="112"/>
-      <sheetData sheetId="113" refreshError="1"/>
-      <sheetData sheetId="114" refreshError="1"/>
-      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="113"/>
+      <sheetData sheetId="114"/>
+      <sheetData sheetId="115"/>
       <sheetData sheetId="116" refreshError="1"/>
       <sheetData sheetId="117" refreshError="1"/>
       <sheetData sheetId="118" refreshError="1"/>
@@ -42873,23 +43643,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="121" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="120" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="119" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="118" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="116" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="115" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -42935,7 +43705,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.753058449074</v>
+        <v>46184.373055439813</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -44316,23 +45086,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A23">
-    <cfRule type="duplicateValues" dxfId="49" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -44378,7 +45148,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.753058449074</v>
+        <v>46184.373055439813</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -45759,23 +46529,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A22">
-    <cfRule type="duplicateValues" dxfId="42" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:A1048576">
-    <cfRule type="duplicateValues" dxfId="41" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="37" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -45820,7 +46590,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.753058449074</v>
+        <v>46184.373055439813</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -47104,23 +47874,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A21">
-    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A1048576">
-    <cfRule type="duplicateValues" dxfId="34" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="31" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -47165,7 +47935,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.753058449074</v>
+        <v>46184.373055439813</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -47712,8 +48482,8 @@
         <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
         <v>46182</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>513</v>
+      <c r="O15" s="58">
+        <v>46332</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -47731,6 +48501,9 @@
       <c r="L16" s="71"/>
       <c r="M16" s="73"/>
       <c r="N16" s="76"/>
+      <c r="O16" s="58">
+        <v>46332</v>
+      </c>
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
@@ -47779,8 +48552,8 @@
         <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
         <v>46182</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>514</v>
+      <c r="O17" s="58">
+        <v>46332</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -48628,26 +49401,26 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A24">
-    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D19">
-    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -48691,7 +49464,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.753058449074</v>
+        <v>46184.373055439813</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -49924,20 +50697,20 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A17">
-    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -49983,7 +50756,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.753058449074</v>
+        <v>46184.373055439813</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -50048,10 +50821,10 @@
     </row>
     <row r="3" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>202</v>
@@ -50092,19 +50865,19 @@
     </row>
     <row r="4" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>202</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F4" s="22">
         <v>70</v>
@@ -50148,10 +50921,10 @@
     </row>
     <row r="6" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>296</v>
@@ -50188,7 +50961,7 @@
         <v>46185</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>545</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -50209,19 +50982,19 @@
     </row>
     <row r="8" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>522</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>523</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="D8" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="E8" s="21" t="s">
         <v>525</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>526</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>527</v>
       </c>
       <c r="F8" s="22">
         <v>30</v>
@@ -50249,7 +51022,7 @@
         <v>46185</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>545</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
@@ -50270,19 +51043,19 @@
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>527</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>528</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>529</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="E10" s="21" t="s">
         <v>530</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>531</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>532</v>
       </c>
       <c r="F10" s="22">
         <v>20</v>
@@ -50294,7 +51067,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="J10" s="25" t="s">
         <v>27</v>
@@ -50310,7 +51083,7 @@
         <v>46185</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>545</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -51331,23 +52104,23 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A20">
-    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -51393,7 +52166,7 @@
       </c>
       <c r="B1" s="1">
         <f ca="1">NOW()</f>
-        <v>46182.753058449074</v>
+        <v>46184.373055439813</v>
       </c>
       <c r="D1" s="83" t="s">
         <v>1</v>
@@ -51458,7 +52231,7 @@
     </row>
     <row r="3" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B3" s="18" t="str">
         <f>VLOOKUP(A3,'[2]master plan'!A:C,3,0)</f>
@@ -51531,7 +52304,7 @@
     </row>
     <row r="5" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B5" s="18" t="str">
         <f>VLOOKUP(A5,'[2]master plan'!A:C,3,0)</f>
@@ -51587,7 +52360,7 @@
     </row>
     <row r="6" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B6" s="18" t="str">
         <f>VLOOKUP(A6,'[2]master plan'!A:C,3,0)</f>
@@ -51654,7 +52427,7 @@
     </row>
     <row r="8" spans="1:15" s="3" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B8" s="18" t="str">
         <f>VLOOKUP(A8,'[2]master plan'!A:C,3,0)</f>
@@ -51726,7 +52499,7 @@
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B10" s="18" t="str">
         <f>VLOOKUP(A10,'[2]master plan'!A:C,3,0)</f>
@@ -51798,7 +52571,7 @@
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B12" s="18" t="str">
         <f>VLOOKUP(A12,'[2]master plan'!A:C,3,0)</f>
@@ -51854,7 +52627,7 @@
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B13" s="18" t="str">
         <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
@@ -51905,7 +52678,7 @@
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B14" s="18" t="str">
         <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
@@ -51956,7 +52729,7 @@
     </row>
     <row r="15" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B15" s="18" t="str">
         <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
@@ -52023,7 +52796,7 @@
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B17" s="18" t="str">
         <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
@@ -52095,7 +52868,7 @@
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="17" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B19" s="18" t="str">
         <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
@@ -52876,27 +53649,27 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A23 A3:A19">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.18" right="0.17" top="0.5" bottom="0" header="0.17" footer="0.17"/>
@@ -52906,6 +53679,1517 @@
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="24" max="15" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2F773E-A39E-4B13-B24A-BDA1F62B9A92}">
+  <sheetPr filterMode="1">
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:O666"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="74.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="175.54296875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="19" style="54" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="53" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="33.54296875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="21.453125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="22" style="57" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" style="58" customWidth="1"/>
+    <col min="15" max="15" width="23" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <f ca="1">NOW()</f>
+        <v>46184.373055439813</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8">
+        <f>SUBTOTAL(9,L2:L1048576)</f>
+        <v>16</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="132.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>VLOOKUP(A3,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260610-0504</v>
+      </c>
+      <c r="C3" s="19" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000123</v>
+      </c>
+      <c r="D3" s="20" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-003299</v>
+      </c>
+      <c r="E3" s="21" t="str">
+        <f>VLOOKUP(A3,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra-Hybrid SEEDPEARL/12-0703TPX Hybrid Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 3mm</v>
+      </c>
+      <c r="F3" s="22">
+        <f>VLOOKUP(A3,'[2]master plan'!A:H,8,0)</f>
+        <v>250</v>
+      </c>
+      <c r="G3" s="23">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H3" s="24">
+        <f>VLOOKUP(A3,'[2]master plan'!A:W,23,0)</f>
+        <v>6</v>
+      </c>
+      <c r="I3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00410/00419 - URGENT (6-14)</v>
+      </c>
+      <c r="K3" s="25" t="str">
+        <f>VLOOKUP($A3,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L3" s="26">
+        <v>6</v>
+      </c>
+      <c r="M3" s="27"/>
+      <c r="N3" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A3,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46187</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="76"/>
+    </row>
+    <row r="5" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>VLOOKUP(A5,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260610-0508</v>
+      </c>
+      <c r="C5" s="19" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000058</v>
+      </c>
+      <c r="D5" s="20" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-001277</v>
+      </c>
+      <c r="E5" s="21" t="str">
+        <f>VLOOKUP(A5,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Ultra GREEN/16-5932TPX Flat Sheet 0.085D 25+/-4 Asker C 1.1M 2M 4mm</v>
+      </c>
+      <c r="F5" s="22">
+        <f>VLOOKUP(A5,'[2]master plan'!A:H,8,0)</f>
+        <v>30</v>
+      </c>
+      <c r="G5" s="23">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="24">
+        <f>VLOOKUP(A5,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00356 - URGENT (6-14)</v>
+      </c>
+      <c r="K5" s="25" t="str">
+        <f>VLOOKUP($A5,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L5" s="26">
+        <v>1</v>
+      </c>
+      <c r="M5" s="27"/>
+      <c r="N5" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A5,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46188</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="76"/>
+    </row>
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>VLOOKUP(A7,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260610-0503</v>
+      </c>
+      <c r="C7" s="19" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000331</v>
+      </c>
+      <c r="D7" s="20" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-004446</v>
+      </c>
+      <c r="E7" s="21" t="str">
+        <f>VLOOKUP(A7,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite X-35-Nike FOSSIL/17-0909TPX 0.145D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+      </c>
+      <c r="F7" s="22">
+        <f>VLOOKUP(A7,'[2]master plan'!A:H,8,0)</f>
+        <v>20</v>
+      </c>
+      <c r="G7" s="23">
+        <f>VLOOKUP(A7,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="24">
+        <f>VLOOKUP(A7,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I7" s="25" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,12,0)</f>
+        <v>NIKE</v>
+      </c>
+      <c r="J7" s="25" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K7" s="25" t="str">
+        <f>VLOOKUP($A7,'[2]master plan'!$A:$N,14,0)</f>
+        <v>MOLDED</v>
+      </c>
+      <c r="L7" s="26">
+        <v>1</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A7,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46189</v>
+      </c>
+      <c r="O7" s="58">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="76"/>
+    </row>
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>VLOOKUP(A9,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260610-0505</v>
+      </c>
+      <c r="C9" s="19" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000055</v>
+      </c>
+      <c r="D9" s="20" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-004155</v>
+      </c>
+      <c r="E9" s="21" t="str">
+        <f>VLOOKUP(A9,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite X-40 TRUE BLUE/19-4057TPX Flat Sheet 0.16D 35+/-4 Asker C 1.1M 1.7M 3.2mm</v>
+      </c>
+      <c r="F9" s="22">
+        <f>VLOOKUP(A9,'[2]master plan'!A:H,8,0)</f>
+        <v>10</v>
+      </c>
+      <c r="G9" s="23">
+        <f>VLOOKUP(A9,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H9" s="24">
+        <f>VLOOKUP(A9,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="25" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J9" s="25" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,13,0)</f>
+        <v>Sample</v>
+      </c>
+      <c r="K9" s="25" t="str">
+        <f>VLOOKUP($A9,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Molded</v>
+      </c>
+      <c r="L9" s="26">
+        <v>1</v>
+      </c>
+      <c r="M9" s="40"/>
+      <c r="N9" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A9,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46189</v>
+      </c>
+      <c r="O9" s="58">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="76"/>
+    </row>
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>VLOOKUP(A11,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260610-0506</v>
+      </c>
+      <c r="C11" s="19" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000209</v>
+      </c>
+      <c r="D11" s="20" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-003537</v>
+      </c>
+      <c r="E11" s="21" t="str">
+        <f>VLOOKUP(A11,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite HybridPlus-Recycled MINT GREEN/11-4805TPX Hybrid 0.12D 25+/-4 Asker C 1.1M 2M 4.5mm</v>
+      </c>
+      <c r="F11" s="22">
+        <f>VLOOKUP(A11,'[2]master plan'!A:H,8,0)</f>
+        <v>30</v>
+      </c>
+      <c r="G11" s="23">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H11" s="24">
+        <f>VLOOKUP(A11,'[2]master plan'!A:W,23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I11" s="25" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,12,0)</f>
+        <v>AKU</v>
+      </c>
+      <c r="J11" s="25" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00451</v>
+      </c>
+      <c r="K11" s="25" t="str">
+        <f>VLOOKUP($A11,'[2]master plan'!$A:$N,14,0)</f>
+        <v>OE-0111A</v>
+      </c>
+      <c r="L11" s="26">
+        <v>1</v>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A11,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46189</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="76"/>
+    </row>
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f>VLOOKUP(A13,'[2]master plan'!A:C,3,0)</f>
+        <v>RPRO-260610-0507</v>
+      </c>
+      <c r="C13" s="19" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,5,0)</f>
+        <v>BDB-000083</v>
+      </c>
+      <c r="D13" s="20" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,6,0)</f>
+        <v>PVN-000935</v>
+      </c>
+      <c r="E13" s="21" t="str">
+        <f>VLOOKUP(A13,'[2]master plan'!A:G,7,0)</f>
+        <v>OrthoLite Eco LT 300C(ADIDAS BLUEBIRD) Flat Sheet 0.11D 25+/-4 Asker C 1.1M 2M 4mm</v>
+      </c>
+      <c r="F13" s="22">
+        <f>VLOOKUP(A13,'[2]master plan'!A:H,8,0)</f>
+        <v>200</v>
+      </c>
+      <c r="G13" s="23">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H13" s="24">
+        <f>VLOOKUP(A13,'[2]master plan'!A:W,23,0)</f>
+        <v>6</v>
+      </c>
+      <c r="I13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,12,0)</f>
+        <v>ADIDAS</v>
+      </c>
+      <c r="J13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,13,0)</f>
+        <v>SSO-2606-00449 - URGENT (6-20)</v>
+      </c>
+      <c r="K13" s="25" t="str">
+        <f>VLOOKUP($A13,'[2]master plan'!$A:$N,14,0)</f>
+        <v>Flat sheet</v>
+      </c>
+      <c r="L13" s="26">
+        <v>6</v>
+      </c>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28">
+        <f>_xlfn.IFNA(VLOOKUP(A13,'[2]master plan'!A:R,18,0),"")</f>
+        <v>46189</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C14" s="19" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D14" s="20" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="21" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="22" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="23" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H14" s="24" t="e">
+        <f>VLOOKUP(A14,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K14" s="25" t="e">
+        <f>VLOOKUP($A14,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A14,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C15" s="19" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D15" s="20" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="21" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" s="22" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="23" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H15" s="24" t="e">
+        <f>VLOOKUP(A15,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K15" s="25" t="e">
+        <f>VLOOKUP($A15,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A15,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C16" s="19" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="20" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="21" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="22" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="23" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H16" s="24" t="e">
+        <f>VLOOKUP(A16,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K16" s="25" t="e">
+        <f>VLOOKUP($A16,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L16" s="26"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A16,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C17" s="19" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="20" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="21" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="22" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="23" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H17" s="24" t="e">
+        <f>VLOOKUP(A17,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17" s="25" t="e">
+        <f>VLOOKUP($A17,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A17,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="19" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="20" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="21" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="22" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="23" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H18" s="24" t="e">
+        <f>VLOOKUP(A18,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="25" t="e">
+        <f>VLOOKUP($A18,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A18,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="19" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="20" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="21" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F19" s="22" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="23" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H19" s="24" t="e">
+        <f>VLOOKUP(A19,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K19" s="25" t="e">
+        <f>VLOOKUP($A19,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A19,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="19" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="20" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="21" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="22" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="23" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H20" s="24" t="e">
+        <f>VLOOKUP(A20,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="25" t="e">
+        <f>VLOOKUP($A20,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A20,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="19" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="20" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="21" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="22" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="23" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="24" t="e">
+        <f>VLOOKUP(A21,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="25" t="e">
+        <f>VLOOKUP($A21,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="26"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A21,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="17"/>
+      <c r="B22" s="18" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:C,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C22" s="19" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D22" s="20" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" s="21" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:G,7,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F22" s="22" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:H,8,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G22" s="23" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H22" s="24" t="e">
+        <f>VLOOKUP(A22,'[2]master plan'!A:W,23,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,12,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,13,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K22" s="25" t="e">
+        <f>VLOOKUP($A22,'[2]master plan'!$A:$N,14,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L22" s="26"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="28" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A22,'[2]master plan'!A:R,18,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="41"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="51"/>
+    </row>
+    <row r="24" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="56"/>
+    </row>
+    <row r="26" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="55"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="58"/>
+    </row>
+    <row r="28" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L28" s="56"/>
+    </row>
+    <row r="29" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L29" s="56"/>
+    </row>
+    <row r="30" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="57" spans="1:14" s="10" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="58"/>
+    </row>
+    <row r="666" spans="1:14" s="54" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A666" s="2"/>
+      <c r="B666" s="52"/>
+      <c r="C666" s="2"/>
+      <c r="D666" s="2"/>
+      <c r="E666" s="60"/>
+      <c r="H666" s="55"/>
+      <c r="I666" s="53"/>
+      <c r="J666" s="53"/>
+      <c r="K666" s="53"/>
+      <c r="L666" s="61"/>
+      <c r="M666" s="57"/>
+      <c r="N666" s="58"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="e1FOu1UlwA7reaiyQlEGzbU6dAFPyHPlKfgo6VzFBBobawyOfUsh2c/+wjC8bICpcXVPmRerMGA9+qKsw5p7Iw==" saltValue="UD2tVZrxqZTGI3vDzMBrHw==" spinCount="100000" sqref="E3:E22" name="Range1_1"/>
+  </protectedRanges>
+  <autoFilter ref="A2:N23" xr:uid="{E2BC4C4A-3703-4A99-A30B-53817C3A378F}">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="RPRO-260610-0503"/>
+        <filter val="RPRO-260610-0504"/>
+        <filter val="RPRO-260610-0505"/>
+        <filter val="RPRO-260610-0506"/>
+        <filter val="RPRO-260610-0507"/>
+        <filter val="RPRO-260610-0508"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A22">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M2">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="